--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re415231b40dd47cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="Rb1cfa9cb2afb41c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="Rb742b2f175694345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rb630045894764ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" r:id="R82e4e60e556c4ab4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3000f6fd7a144cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R90f7212e09e44cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R11d36480f2564cbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="R4b93e39749f94139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" r:id="R476126707b004552"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -304,7 +304,7 @@
     <x:col min="6" max="6" width="13.010000228881836" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="9.449999809265137" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -398,13 +398,13 @@
         <x:v>0.11764705882352938</x:v>
       </x:c>
       <x:c r="G4" s="21" t="n">
-        <x:v>0.8506792500011215</x:v>
+        <x:v>0.8547921669996867</x:v>
       </x:c>
       <x:c r="H4" s="21" t="n">
-        <x:v>2.3105257919996802</x:v>
+        <x:v>2.2029229999970994</x:v>
       </x:c>
       <x:c r="I4" s="21" t="n">
-        <x:v>2.716095158071193</x:v>
+        <x:v>2.5771445797512866</x:v>
       </x:c>
       <x:c r="J4" s="17"/>
       <x:c r="K4" s="17"/>
@@ -421,25 +421,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="19" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="19" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="20" t="n">
-        <x:v>0</x:v>
+        <x:v>0.05882352941176472</x:v>
       </x:c>
       <x:c r="G5" s="21" t="n">
-        <x:v>1.9246857079997426</x:v>
+        <x:v>1.8751434579971828</x:v>
       </x:c>
       <x:c r="H5" s="21" t="n">
-        <x:v>5.19315262499731</x:v>
+        <x:v>5.199965666997741</x:v>
       </x:c>
       <x:c r="I5" s="21" t="n">
-        <x:v>2.6981821517209523</x:v>
+        <x:v>2.7731028497157006</x:v>
       </x:c>
       <x:c r="J5" s="17"/>
       <x:c r="K5" s="17"/>
@@ -3786,6 +3786,7 @@
     <x:col min="12" max="12" width="3.930000066757202" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="9.6899995803833" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="9.6899995803833" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="3.799999952316284" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -3831,7 +3832,9 @@
       <x:c r="N1" s="18" t="str">
         <x:v>Delta Scale</x:v>
       </x:c>
-      <x:c r="O1" s="17"/>
+      <x:c r="O1" s="18" t="str">
+        <x:v>Split</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="19" t="str">
@@ -3850,7 +3853,7 @@
         <x:v>0.29411764705882354</x:v>
       </x:c>
       <x:c r="F2" s="21" t="n">
-        <x:v>0.8506792500011215</x:v>
+        <x:v>0.8547921669996867</x:v>
       </x:c>
       <x:c r="G2" s="19" t="n">
         <x:v>0</x:v>
@@ -3876,7 +3879,9 @@
       <x:c r="N2" s="19" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O2" s="17"/>
+      <x:c r="O2" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="19" t="str">
@@ -3895,7 +3900,7 @@
         <x:v>0.4117647058823529</x:v>
       </x:c>
       <x:c r="F3" s="21" t="n">
-        <x:v>2.3105257919996802</x:v>
+        <x:v>2.2029229999970994</x:v>
       </x:c>
       <x:c r="G3" s="19" t="n">
         <x:v>1</x:v>
@@ -3921,7 +3926,9 @@
       <x:c r="N3" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O3" s="17"/>
+      <x:c r="O3" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="19" t="str">
@@ -3940,7 +3947,7 @@
         <x:v>0.5882352941176471</x:v>
       </x:c>
       <x:c r="F4" s="21" t="n">
-        <x:v>1.9246857079997426</x:v>
+        <x:v>1.8751434579971828</x:v>
       </x:c>
       <x:c r="G4" s="19" t="n">
         <x:v>0</x:v>
@@ -3966,7 +3973,9 @@
       <x:c r="N4" s="19" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="O4" s="17"/>
+      <x:c r="O4" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
@@ -3976,16 +3985,16 @@
         <x:v>HRM H=1 blend=0.2</x:v>
       </x:c>
       <x:c r="C5" s="19" t="n">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="20" t="n">
-        <x:v>0.5882352941176471</x:v>
+        <x:v>0.6470588235294118</x:v>
       </x:c>
       <x:c r="F5" s="21" t="n">
-        <x:v>5.19315262499731</x:v>
+        <x:v>5.199965666997741</x:v>
       </x:c>
       <x:c r="G5" s="19" t="n">
         <x:v>1</x:v>
@@ -4011,7 +4020,9 @@
       <x:c r="N5" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O5" s="17"/>
+      <x:c r="O5" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="17"/>
@@ -9293,16 +9304,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G53" s="21" t="n">
-        <x:v>-3.272796630859375</x:v>
+        <x:v>-4.322700500488281</x:v>
       </x:c>
       <x:c r="H53" s="21" t="n">
-        <x:v>-0.147796630859375</x:v>
+        <x:v>-0.07270050048828125</x:v>
       </x:c>
       <x:c r="I53" s="21" t="n">
-        <x:v>-6.585296630859375</x:v>
+        <x:v>-5.822700500488281</x:v>
       </x:c>
       <x:c r="J53" s="21" t="n">
-        <x:v>-4.647796630859375</x:v>
+        <x:v>-4.572700500488281</x:v>
       </x:c>
       <x:c r="K53" s="17"/>
       <x:c r="L53" s="17"/>
@@ -9330,16 +9341,16 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="G54" s="21" t="n">
-        <x:v>-2.4892539978027344</x:v>
+        <x:v>-2.0501537322998047</x:v>
       </x:c>
       <x:c r="H54" s="21" t="n">
-        <x:v>-3.1142539978027344</x:v>
+        <x:v>-2.1751537322998047</x:v>
       </x:c>
       <x:c r="I54" s="21" t="n">
-        <x:v>-5.801753997802734</x:v>
+        <x:v>-5.300153732299805</x:v>
       </x:c>
       <x:c r="J54" s="21" t="n">
-        <x:v>-0.6142539978027344</x:v>
+        <x:v>-0.8001537322998047</x:v>
       </x:c>
       <x:c r="K54" s="17"/>
       <x:c r="L54" s="17"/>
@@ -9367,16 +9378,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G55" s="21" t="n">
-        <x:v>-5.922243118286133</x:v>
+        <x:v>-7.559175491333008</x:v>
       </x:c>
       <x:c r="H55" s="21" t="n">
-        <x:v>-5.234743118286133</x:v>
+        <x:v>-6.559175491333008</x:v>
       </x:c>
       <x:c r="I55" s="21" t="n">
-        <x:v>-0.8597431182861328</x:v>
+        <x:v>-0.05917549133300781</x:v>
       </x:c>
       <x:c r="J55" s="21" t="n">
-        <x:v>-4.609743118286133</x:v>
+        <x:v>-5.934175491333008</x:v>
       </x:c>
       <x:c r="K55" s="17"/>
       <x:c r="L55" s="17"/>
@@ -9404,16 +9415,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G56" s="21" t="n">
-        <x:v>-3.2651805877685547</x:v>
+        <x:v>-3.0930557250976562</x:v>
       </x:c>
       <x:c r="H56" s="21" t="n">
-        <x:v>-2.7651805877685547</x:v>
+        <x:v>-1.3430557250976562</x:v>
       </x:c>
       <x:c r="I56" s="21" t="n">
-        <x:v>-3.7651805877685547</x:v>
+        <x:v>-2.5930557250976562</x:v>
       </x:c>
       <x:c r="J56" s="21" t="n">
-        <x:v>-4.952680587768555</x:v>
+        <x:v>-4.218055725097656</x:v>
       </x:c>
       <x:c r="K56" s="17"/>
       <x:c r="L56" s="17"/>
@@ -9441,16 +9452,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G57" s="21" t="n">
-        <x:v>-3.366971969604492</x:v>
+        <x:v>-3.564645767211914</x:v>
       </x:c>
       <x:c r="H57" s="21" t="n">
-        <x:v>-1.3669719696044922</x:v>
+        <x:v>-0.6896457672119141</x:v>
       </x:c>
       <x:c r="I57" s="21" t="n">
-        <x:v>-3.366971969604492</x:v>
+        <x:v>-3.439645767211914</x:v>
       </x:c>
       <x:c r="J57" s="21" t="n">
-        <x:v>-2.116971969604492</x:v>
+        <x:v>-2.314645767211914</x:v>
       </x:c>
       <x:c r="K57" s="17"/>
       <x:c r="L57" s="17"/>
@@ -9478,16 +9489,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G58" s="21" t="n">
-        <x:v>-0.5525951385498047</x:v>
+        <x:v>-0.2689208984375</x:v>
       </x:c>
       <x:c r="H58" s="21" t="n">
-        <x:v>-4.552595138549805</x:v>
+        <x:v>-2.8939208984375</x:v>
       </x:c>
       <x:c r="I58" s="21" t="n">
-        <x:v>-7.615095138549805</x:v>
+        <x:v>-6.0189208984375</x:v>
       </x:c>
       <x:c r="J58" s="21" t="n">
-        <x:v>-6.177595138549805</x:v>
+        <x:v>-5.7689208984375</x:v>
       </x:c>
       <x:c r="K58" s="17"/>
       <x:c r="L58" s="17"/>
@@ -9515,16 +9526,16 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="G59" s="21" t="n">
-        <x:v>-1.3303813934326172</x:v>
+        <x:v>-0.974853515625</x:v>
       </x:c>
       <x:c r="H59" s="21" t="n">
-        <x:v>-2.580381393432617</x:v>
+        <x:v>-1.974853515625</x:v>
       </x:c>
       <x:c r="I59" s="21" t="n">
-        <x:v>-3.830381393432617</x:v>
+        <x:v>-3.349853515625</x:v>
       </x:c>
       <x:c r="J59" s="21" t="n">
-        <x:v>-2.455381393432617</x:v>
+        <x:v>-2.724853515625</x:v>
       </x:c>
       <x:c r="K59" s="17"/>
       <x:c r="L59" s="17"/>
@@ -9552,16 +9563,16 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="G60" s="21" t="n">
-        <x:v>-3.6177024841308594</x:v>
+        <x:v>-4.051446914672852</x:v>
       </x:c>
       <x:c r="H60" s="21" t="n">
-        <x:v>-0.8677024841308594</x:v>
+        <x:v>-0.5514469146728516</x:v>
       </x:c>
       <x:c r="I60" s="21" t="n">
-        <x:v>-3.8677024841308594</x:v>
+        <x:v>-2.9264469146728516</x:v>
       </x:c>
       <x:c r="J60" s="21" t="n">
-        <x:v>-2.4927024841308594</x:v>
+        <x:v>-2.3014469146728516</x:v>
       </x:c>
       <x:c r="K60" s="17"/>
       <x:c r="L60" s="17"/>
@@ -9589,16 +9600,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G61" s="21" t="n">
-        <x:v>-2.124410629272461</x:v>
+        <x:v>-2.569225311279297</x:v>
       </x:c>
       <x:c r="H61" s="21" t="n">
-        <x:v>-1.624410629272461</x:v>
+        <x:v>-0.8192253112792969</x:v>
       </x:c>
       <x:c r="I61" s="21" t="n">
-        <x:v>-3.499410629272461</x:v>
+        <x:v>-2.819225311279297</x:v>
       </x:c>
       <x:c r="J61" s="21" t="n">
-        <x:v>-2.374410629272461</x:v>
+        <x:v>-2.444225311279297</x:v>
       </x:c>
       <x:c r="K61" s="17"/>
       <x:c r="L61" s="17"/>
@@ -9626,16 +9637,16 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="G62" s="21" t="n">
-        <x:v>-3.165487289428711</x:v>
+        <x:v>-3.3412837982177734</x:v>
       </x:c>
       <x:c r="H62" s="21" t="n">
-        <x:v>-0.9154872894287109</x:v>
+        <x:v>-0.46628379821777344</x:v>
       </x:c>
       <x:c r="I62" s="21" t="n">
-        <x:v>-4.165487289428711</x:v>
+        <x:v>-3.2162837982177734</x:v>
       </x:c>
       <x:c r="J62" s="21" t="n">
-        <x:v>-2.040487289428711</x:v>
+        <x:v>-2.2162837982177734</x:v>
       </x:c>
       <x:c r="K62" s="17"/>
       <x:c r="L62" s="17"/>
@@ -9657,22 +9668,22 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="E63" s="19" t="str">
-        <x:v>D</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="F63" s="19" t="str">
         <x:v>False</x:v>
       </x:c>
       <x:c r="G63" s="21" t="n">
-        <x:v>-4.914545059204102</x:v>
+        <x:v>-4.733434677124023</x:v>
       </x:c>
       <x:c r="H63" s="21" t="n">
-        <x:v>-5.602045059204102</x:v>
+        <x:v>-4.108434677124023</x:v>
       </x:c>
       <x:c r="I63" s="21" t="n">
-        <x:v>-1.5395450592041016</x:v>
+        <x:v>-0.9834346771240234</x:v>
       </x:c>
       <x:c r="J63" s="21" t="n">
-        <x:v>-1.0395450592041016</x:v>
+        <x:v>-1.1084346771240234</x:v>
       </x:c>
       <x:c r="K63" s="17"/>
       <x:c r="L63" s="17"/>
@@ -9700,16 +9711,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G64" s="21" t="n">
-        <x:v>-3.017488479614258</x:v>
+        <x:v>-3.7428150177001953</x:v>
       </x:c>
       <x:c r="H64" s="21" t="n">
-        <x:v>-0.2674884796142578</x:v>
+        <x:v>-0.11781501770019531</x:v>
       </x:c>
       <x:c r="I64" s="21" t="n">
-        <x:v>-5.392488479614258</x:v>
+        <x:v>-5.242815017700195</x:v>
       </x:c>
       <x:c r="J64" s="21" t="n">
-        <x:v>-5.392488479614258</x:v>
+        <x:v>-5.617815017700195</x:v>
       </x:c>
       <x:c r="K64" s="17"/>
       <x:c r="L64" s="17"/>
@@ -9737,16 +9748,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G65" s="21" t="n">
-        <x:v>-3.137056350708008</x:v>
+        <x:v>-3.3665695190429688</x:v>
       </x:c>
       <x:c r="H65" s="21" t="n">
-        <x:v>-5.387056350708008</x:v>
+        <x:v>-5.116569519042969</x:v>
       </x:c>
       <x:c r="I65" s="21" t="n">
-        <x:v>-0.5120563507080078</x:v>
+        <x:v>-0.24156951904296875</x:v>
       </x:c>
       <x:c r="J65" s="21" t="n">
-        <x:v>-4.762056350708008</x:v>
+        <x:v>-5.116569519042969</x:v>
       </x:c>
       <x:c r="K65" s="17"/>
       <x:c r="L65" s="17"/>
@@ -9774,16 +9785,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G66" s="21" t="n">
-        <x:v>-6.42302131652832</x:v>
+        <x:v>-6.340250015258789</x:v>
       </x:c>
       <x:c r="H66" s="21" t="n">
-        <x:v>-0.2980213165283203</x:v>
+        <x:v>-0.09025001525878906</x:v>
       </x:c>
       <x:c r="I66" s="21" t="n">
-        <x:v>-7.17302131652832</x:v>
+        <x:v>-5.965250015258789</x:v>
       </x:c>
       <x:c r="J66" s="21" t="n">
-        <x:v>-7.86052131652832</x:v>
+        <x:v>-8.090250015258789</x:v>
       </x:c>
       <x:c r="K66" s="17"/>
       <x:c r="L66" s="17"/>
@@ -9811,16 +9822,16 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G67" s="21" t="n">
-        <x:v>-5.322458267211914</x:v>
+        <x:v>-6.554983139038086</x:v>
       </x:c>
       <x:c r="H67" s="21" t="n">
-        <x:v>-8.634958267211914</x:v>
+        <x:v>-8.929983139038086</x:v>
       </x:c>
       <x:c r="I67" s="21" t="n">
-        <x:v>-0.19745826721191406</x:v>
+        <x:v>-0.05498313903808594</x:v>
       </x:c>
       <x:c r="J67" s="21" t="n">
-        <x:v>-8.384958267211914</x:v>
+        <x:v>-9.242483139038086</x:v>
       </x:c>
       <x:c r="K67" s="17"/>
       <x:c r="L67" s="17"/>
@@ -9842,22 +9853,22 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="E68" s="19" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="F68" s="19" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G68" s="21" t="n">
-        <x:v>-1.851114273071289</x:v>
+        <x:v>-2.011505126953125</x:v>
       </x:c>
       <x:c r="H68" s="21" t="n">
-        <x:v>-2.351114273071289</x:v>
+        <x:v>-1.636505126953125</x:v>
       </x:c>
       <x:c r="I68" s="21" t="n">
-        <x:v>-2.726114273071289</x:v>
+        <x:v>-2.011505126953125</x:v>
       </x:c>
       <x:c r="J68" s="21" t="n">
-        <x:v>-1.976114273071289</x:v>
+        <x:v>-1.886505126953125</x:v>
       </x:c>
       <x:c r="K68" s="17"/>
       <x:c r="L68" s="17"/>
@@ -9885,16 +9896,16 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="G69" s="21" t="n">
-        <x:v>-3.8990612030029297</x:v>
+        <x:v>-4.422727584838867</x:v>
       </x:c>
       <x:c r="H69" s="21" t="n">
-        <x:v>-4.39906120300293</x:v>
+        <x:v>-3.297727584838867</x:v>
       </x:c>
       <x:c r="I69" s="21" t="n">
-        <x:v>-3.2740612030029297</x:v>
+        <x:v>-2.672727584838867</x:v>
       </x:c>
       <x:c r="J69" s="21" t="n">
-        <x:v>-1.1490612030029297</x:v>
+        <x:v>-0.4227275848388672</x:v>
       </x:c>
       <x:c r="K69" s="17"/>
       <x:c r="L69" s="17"/>
@@ -12153,6 +12164,8 @@
     <x:col min="13" max="13" width="3.930000066757202" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="9.6899995803833" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="9.6899995803833" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="3.799999952316284" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="35.95000076293945" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -12201,6 +12214,12 @@
       <x:c r="O1" s="18" t="str">
         <x:v>Delta Scale</x:v>
       </x:c>
+      <x:c r="P1" s="8" t="str">
+        <x:v>Split</x:v>
+      </x:c>
+      <x:c r="Q1" s="8" t="str">
+        <x:v>Source</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="19" t="str">
@@ -12248,6 +12267,10 @@
       <x:c r="O2" s="19" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="P2" s="10"/>
+      <x:c r="Q2" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="19" t="str">
@@ -12295,6 +12318,10 @@
       <x:c r="O3" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P3" s="10"/>
+      <x:c r="Q3" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="19" t="str">
@@ -12342,6 +12369,10 @@
       <x:c r="O4" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P4" s="10"/>
+      <x:c r="Q4" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="19" t="str">
@@ -12389,6 +12420,10 @@
       <x:c r="O5" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P5" s="10"/>
+      <x:c r="Q5" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="19" t="str">
@@ -12436,6 +12471,10 @@
       <x:c r="O6" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P6" s="10"/>
+      <x:c r="Q6" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="19" t="str">
@@ -12483,6 +12522,10 @@
       <x:c r="O7" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P7" s="10"/>
+      <x:c r="Q7" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="19" t="str">
@@ -12530,6 +12573,10 @@
       <x:c r="O8" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P8" s="10"/>
+      <x:c r="Q8" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="19" t="str">
@@ -12577,6 +12624,10 @@
       <x:c r="O9" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P9" s="10"/>
+      <x:c r="Q9" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="19" t="str">
@@ -12624,6 +12675,10 @@
       <x:c r="O10" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P10" s="10"/>
+      <x:c r="Q10" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="19" t="str">
@@ -12671,6 +12726,10 @@
       <x:c r="O11" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P11" s="10"/>
+      <x:c r="Q11" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="19" t="str">
@@ -12718,6 +12777,10 @@
       <x:c r="O12" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P12" s="10"/>
+      <x:c r="Q12" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="19" t="str">
@@ -12765,6 +12828,10 @@
       <x:c r="O13" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P13" s="10"/>
+      <x:c r="Q13" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="19" t="str">
@@ -12812,6 +12879,10 @@
       <x:c r="O14" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P14" s="10"/>
+      <x:c r="Q14" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="19" t="str">
@@ -12859,6 +12930,10 @@
       <x:c r="O15" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P15" s="10"/>
+      <x:c r="Q15" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="19" t="str">
@@ -12906,6 +12981,10 @@
       <x:c r="O16" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P16" s="10"/>
+      <x:c r="Q16" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="19" t="str">
@@ -12953,6 +13032,10 @@
       <x:c r="O17" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P17" s="10"/>
+      <x:c r="Q17" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="19" t="str">
@@ -13000,6 +13083,10 @@
       <x:c r="O18" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P18" s="10"/>
+      <x:c r="Q18" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="19" t="str">
@@ -13047,6 +13134,10 @@
       <x:c r="O19" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P19" s="10"/>
+      <x:c r="Q19" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="19" t="str">
@@ -13094,6 +13185,10 @@
       <x:c r="O20" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P20" s="10"/>
+      <x:c r="Q20" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="19" t="str">
@@ -13141,6 +13236,10 @@
       <x:c r="O21" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P21" s="10"/>
+      <x:c r="Q21" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="19" t="str">
@@ -13188,6 +13287,10 @@
       <x:c r="O22" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P22" s="10"/>
+      <x:c r="Q22" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="19" t="str">
@@ -13235,6 +13338,10 @@
       <x:c r="O23" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P23" s="10"/>
+      <x:c r="Q23" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="19" t="str">
@@ -13282,6 +13389,10 @@
       <x:c r="O24" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P24" s="10"/>
+      <x:c r="Q24" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="19" t="str">
@@ -13329,6 +13440,10 @@
       <x:c r="O25" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P25" s="10"/>
+      <x:c r="Q25" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="19" t="str">
@@ -13376,6 +13491,10 @@
       <x:c r="O26" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P26" s="10"/>
+      <x:c r="Q26" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="19" t="str">
@@ -13423,6 +13542,10 @@
       <x:c r="O27" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P27" s="10"/>
+      <x:c r="Q27" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="19" t="str">
@@ -13470,6 +13593,10 @@
       <x:c r="O28" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P28" s="10"/>
+      <x:c r="Q28" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="19" t="str">
@@ -13517,6 +13644,10 @@
       <x:c r="O29" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P29" s="10"/>
+      <x:c r="Q29" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="19" t="str">
@@ -13564,6 +13695,10 @@
       <x:c r="O30" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P30" s="10"/>
+      <x:c r="Q30" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="19" t="str">
@@ -13611,6 +13746,10 @@
       <x:c r="O31" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P31" s="10"/>
+      <x:c r="Q31" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="19" t="str">
@@ -13658,6 +13797,10 @@
       <x:c r="O32" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P32" s="10"/>
+      <x:c r="Q32" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="19" t="str">
@@ -13705,6 +13848,10 @@
       <x:c r="O33" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P33" s="10"/>
+      <x:c r="Q33" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="19" t="str">
@@ -13752,6 +13899,10 @@
       <x:c r="O34" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P34" s="10"/>
+      <x:c r="Q34" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="19" t="str">
@@ -13799,6 +13950,10 @@
       <x:c r="O35" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P35" s="10"/>
+      <x:c r="Q35" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="19" t="str">
@@ -13846,6 +14001,10 @@
       <x:c r="O36" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P36" s="10"/>
+      <x:c r="Q36" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="19" t="str">
@@ -13893,6 +14052,10 @@
       <x:c r="O37" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P37" s="10"/>
+      <x:c r="Q37" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="19" t="str">
@@ -13940,6 +14103,10 @@
       <x:c r="O38" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P38" s="10"/>
+      <x:c r="Q38" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="19" t="str">
@@ -13987,6 +14154,10 @@
       <x:c r="O39" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P39" s="10"/>
+      <x:c r="Q39" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="19" t="str">
@@ -14034,6 +14205,10 @@
       <x:c r="O40" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P40" s="10"/>
+      <x:c r="Q40" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="19" t="str">
@@ -14081,6 +14256,10 @@
       <x:c r="O41" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P41" s="10"/>
+      <x:c r="Q41" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="19" t="str">
@@ -14128,6 +14307,10 @@
       <x:c r="O42" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P42" s="10"/>
+      <x:c r="Q42" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="19" t="str">
@@ -14175,6 +14358,10 @@
       <x:c r="O43" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P43" s="10"/>
+      <x:c r="Q43" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="19" t="str">
@@ -14222,6 +14409,10 @@
       <x:c r="O44" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P44" s="10"/>
+      <x:c r="Q44" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="19" t="str">
@@ -14269,6 +14460,10 @@
       <x:c r="O45" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P45" s="10"/>
+      <x:c r="Q45" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="19" t="str">
@@ -14316,6 +14511,10 @@
       <x:c r="O46" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P46" s="10"/>
+      <x:c r="Q46" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="19" t="str">
@@ -14363,6 +14562,10 @@
       <x:c r="O47" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P47" s="10"/>
+      <x:c r="Q47" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="19" t="str">
@@ -14410,6 +14613,10 @@
       <x:c r="O48" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P48" s="10"/>
+      <x:c r="Q48" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="19" t="str">
@@ -14457,6 +14664,10 @@
       <x:c r="O49" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P49" s="10"/>
+      <x:c r="Q49" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="19" t="str">
@@ -14504,6 +14715,10 @@
       <x:c r="O50" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P50" s="10"/>
+      <x:c r="Q50" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="19" t="str">
@@ -14551,6 +14766,10 @@
       <x:c r="O51" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P51" s="10"/>
+      <x:c r="Q51" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="19" t="str">
@@ -14598,6 +14817,10 @@
       <x:c r="O52" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P52" s="10"/>
+      <x:c r="Q52" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="19" t="str">
@@ -14645,6 +14868,10 @@
       <x:c r="O53" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P53" s="10"/>
+      <x:c r="Q53" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="19" t="str">
@@ -14692,6 +14919,10 @@
       <x:c r="O54" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P54" s="10"/>
+      <x:c r="Q54" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="19" t="str">
@@ -14739,6 +14970,10 @@
       <x:c r="O55" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P55" s="10"/>
+      <x:c r="Q55" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="19" t="str">
@@ -14786,6 +15021,10 @@
       <x:c r="O56" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P56" s="10"/>
+      <x:c r="Q56" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="19" t="str">
@@ -14833,6 +15072,10 @@
       <x:c r="O57" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P57" s="10"/>
+      <x:c r="Q57" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="19" t="str">
@@ -14880,6 +15123,10 @@
       <x:c r="O58" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P58" s="10"/>
+      <x:c r="Q58" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="19" t="str">
@@ -14927,6 +15174,10 @@
       <x:c r="O59" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P59" s="10"/>
+      <x:c r="Q59" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="19" t="str">
@@ -14974,6 +15225,10 @@
       <x:c r="O60" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P60" s="10"/>
+      <x:c r="Q60" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="19" t="str">
@@ -15021,6 +15276,10 @@
       <x:c r="O61" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P61" s="10"/>
+      <x:c r="Q61" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="19" t="str">
@@ -15068,6 +15327,10 @@
       <x:c r="O62" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P62" s="10"/>
+      <x:c r="Q62" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="19" t="str">
@@ -15115,6 +15378,10 @@
       <x:c r="O63" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P63" s="10"/>
+      <x:c r="Q63" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="19" t="str">
@@ -15162,6 +15429,10 @@
       <x:c r="O64" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P64" s="10"/>
+      <x:c r="Q64" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="19" t="str">
@@ -15209,6 +15480,10 @@
       <x:c r="O65" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P65" s="10"/>
+      <x:c r="Q65" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="19" t="str">
@@ -15256,6 +15531,10 @@
       <x:c r="O66" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P66" s="10"/>
+      <x:c r="Q66" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="19" t="str">
@@ -15303,6 +15582,10 @@
       <x:c r="O67" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P67" s="10"/>
+      <x:c r="Q67" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="19" t="str">
@@ -15350,6 +15633,10 @@
       <x:c r="O68" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P68" s="10"/>
+      <x:c r="Q68" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="19" t="str">
@@ -15397,6 +15684,10 @@
       <x:c r="O69" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P69" s="10"/>
+      <x:c r="Q69" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="19" t="str">
@@ -15444,6 +15735,10 @@
       <x:c r="O70" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P70" s="10"/>
+      <x:c r="Q70" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="19" t="str">
@@ -15491,1519 +15786,4727 @@
       <x:c r="O71" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="P71" s="10"/>
+      <x:c r="Q71" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_expanded_focused.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="17"/>
-      <x:c r="B72" s="17"/>
-      <x:c r="C72" s="17"/>
-      <x:c r="D72" s="17"/>
-      <x:c r="E72" s="17"/>
-      <x:c r="F72" s="22"/>
-      <x:c r="G72" s="23"/>
-      <x:c r="H72" s="17"/>
-      <x:c r="I72" s="17"/>
-      <x:c r="J72" s="17"/>
-      <x:c r="K72" s="17"/>
-      <x:c r="L72" s="17"/>
-      <x:c r="M72" s="17"/>
-      <x:c r="N72" s="17"/>
-      <x:c r="O72" s="17"/>
+      <x:c r="A72" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C72" s="19" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="D72" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E72" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F72" s="20" t="n">
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="G72" s="21" t="n">
+        <x:v>0.9657060410027043</x:v>
+      </x:c>
+      <x:c r="H72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N72" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O72" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P72" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q72" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="17"/>
-      <x:c r="B73" s="17"/>
-      <x:c r="C73" s="17"/>
-      <x:c r="D73" s="17"/>
-      <x:c r="E73" s="17"/>
-      <x:c r="F73" s="22"/>
-      <x:c r="G73" s="23"/>
-      <x:c r="H73" s="17"/>
-      <x:c r="I73" s="17"/>
-      <x:c r="J73" s="17"/>
-      <x:c r="K73" s="17"/>
-      <x:c r="L73" s="17"/>
-      <x:c r="M73" s="17"/>
-      <x:c r="N73" s="17"/>
-      <x:c r="O73" s="17"/>
+      <x:c r="A73" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B73" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C73" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D73" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E73" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F73" s="20" t="n">
+        <x:v>0.17647058823529413</x:v>
+      </x:c>
+      <x:c r="G73" s="21" t="n">
+        <x:v>2.5137185829989903</x:v>
+      </x:c>
+      <x:c r="H73" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I73" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J73" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K73" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L73" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M73" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N73" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O73" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P73" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q73" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="17"/>
-      <x:c r="B74" s="17"/>
-      <x:c r="C74" s="17"/>
-      <x:c r="D74" s="17"/>
-      <x:c r="E74" s="17"/>
-      <x:c r="F74" s="22"/>
-      <x:c r="G74" s="23"/>
-      <x:c r="H74" s="17"/>
-      <x:c r="I74" s="17"/>
-      <x:c r="J74" s="17"/>
-      <x:c r="K74" s="17"/>
-      <x:c r="L74" s="17"/>
-      <x:c r="M74" s="17"/>
-      <x:c r="N74" s="17"/>
-      <x:c r="O74" s="17"/>
+      <x:c r="A74" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B74" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C74" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D74" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E74" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F74" s="20" t="n">
+        <x:v>0.23529411764705882</x:v>
+      </x:c>
+      <x:c r="G74" s="21" t="n">
+        <x:v>2.5219668749996345</x:v>
+      </x:c>
+      <x:c r="H74" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I74" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J74" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K74" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L74" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M74" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N74" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O74" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P74" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q74" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="17"/>
-      <x:c r="B75" s="17"/>
-      <x:c r="C75" s="17"/>
-      <x:c r="D75" s="17"/>
-      <x:c r="E75" s="17"/>
-      <x:c r="F75" s="22"/>
-      <x:c r="G75" s="23"/>
-      <x:c r="H75" s="17"/>
-      <x:c r="I75" s="17"/>
-      <x:c r="J75" s="17"/>
-      <x:c r="K75" s="17"/>
-      <x:c r="L75" s="17"/>
-      <x:c r="M75" s="17"/>
-      <x:c r="N75" s="17"/>
-      <x:c r="O75" s="17"/>
+      <x:c r="A75" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B75" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C75" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D75" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E75" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F75" s="20" t="n">
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="G75" s="21" t="n">
+        <x:v>2.522030000000086</x:v>
+      </x:c>
+      <x:c r="H75" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I75" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J75" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K75" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L75" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M75" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N75" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O75" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P75" s="10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="Q75" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="17"/>
-      <x:c r="B76" s="17"/>
-      <x:c r="C76" s="17"/>
-      <x:c r="D76" s="17"/>
-      <x:c r="E76" s="17"/>
-      <x:c r="F76" s="22"/>
-      <x:c r="G76" s="23"/>
-      <x:c r="H76" s="17"/>
-      <x:c r="I76" s="17"/>
-      <x:c r="J76" s="17"/>
-      <x:c r="K76" s="17"/>
-      <x:c r="L76" s="17"/>
-      <x:c r="M76" s="17"/>
-      <x:c r="N76" s="17"/>
-      <x:c r="O76" s="17"/>
+      <x:c r="A76" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B76" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C76" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D76" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E76" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F76" s="20" t="n">
+        <x:v>0.4117647058823529</x:v>
+      </x:c>
+      <x:c r="G76" s="21" t="n">
+        <x:v>2.5227774580016558</x:v>
+      </x:c>
+      <x:c r="H76" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I76" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J76" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K76" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L76" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M76" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N76" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O76" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P76" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q76" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="17"/>
-      <x:c r="B77" s="17"/>
-      <x:c r="C77" s="17"/>
-      <x:c r="D77" s="17"/>
-      <x:c r="E77" s="17"/>
-      <x:c r="F77" s="22"/>
-      <x:c r="G77" s="23"/>
-      <x:c r="H77" s="17"/>
-      <x:c r="I77" s="17"/>
-      <x:c r="J77" s="17"/>
-      <x:c r="K77" s="17"/>
-      <x:c r="L77" s="17"/>
-      <x:c r="M77" s="17"/>
-      <x:c r="N77" s="17"/>
-      <x:c r="O77" s="17"/>
+      <x:c r="A77" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B77" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C77" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D77" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E77" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F77" s="20" t="n">
+        <x:v>0.23529411764705882</x:v>
+      </x:c>
+      <x:c r="G77" s="21" t="n">
+        <x:v>2.512188917000458</x:v>
+      </x:c>
+      <x:c r="H77" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I77" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J77" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K77" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L77" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M77" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N77" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O77" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P77" s="10" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q77" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="17"/>
-      <x:c r="B78" s="17"/>
-      <x:c r="C78" s="17"/>
-      <x:c r="D78" s="17"/>
-      <x:c r="E78" s="17"/>
-      <x:c r="F78" s="22"/>
-      <x:c r="G78" s="23"/>
-      <x:c r="H78" s="17"/>
-      <x:c r="I78" s="17"/>
-      <x:c r="J78" s="17"/>
-      <x:c r="K78" s="17"/>
-      <x:c r="L78" s="17"/>
-      <x:c r="M78" s="17"/>
-      <x:c r="N78" s="17"/>
-      <x:c r="O78" s="17"/>
+      <x:c r="A78" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B78" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C78" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D78" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E78" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F78" s="20" t="n">
+        <x:v>0.23529411764705882</x:v>
+      </x:c>
+      <x:c r="G78" s="21" t="n">
+        <x:v>2.5305892910000694</x:v>
+      </x:c>
+      <x:c r="H78" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I78" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J78" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K78" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L78" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M78" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N78" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O78" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P78" s="10" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q78" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="17"/>
-      <x:c r="B79" s="17"/>
-      <x:c r="C79" s="17"/>
-      <x:c r="D79" s="17"/>
-      <x:c r="E79" s="17"/>
-      <x:c r="F79" s="22"/>
-      <x:c r="G79" s="23"/>
-      <x:c r="H79" s="17"/>
-      <x:c r="I79" s="17"/>
-      <x:c r="J79" s="17"/>
-      <x:c r="K79" s="17"/>
-      <x:c r="L79" s="17"/>
-      <x:c r="M79" s="17"/>
-      <x:c r="N79" s="17"/>
-      <x:c r="O79" s="17"/>
+      <x:c r="A79" s="19" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B79" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C79" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D79" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E79" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F79" s="20" t="n">
+        <x:v>0.17647058823529413</x:v>
+      </x:c>
+      <x:c r="G79" s="21" t="n">
+        <x:v>2.533768584002246</x:v>
+      </x:c>
+      <x:c r="H79" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I79" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J79" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K79" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L79" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M79" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N79" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O79" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P79" s="10" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q79" s="10" t="str">
+        <x:v>sweep_qwen3_0_6b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="17"/>
-      <x:c r="B80" s="17"/>
-      <x:c r="C80" s="17"/>
-      <x:c r="D80" s="17"/>
-      <x:c r="E80" s="17"/>
-      <x:c r="F80" s="22"/>
-      <x:c r="G80" s="23"/>
-      <x:c r="H80" s="17"/>
-      <x:c r="I80" s="17"/>
-      <x:c r="J80" s="17"/>
-      <x:c r="K80" s="17"/>
-      <x:c r="L80" s="17"/>
-      <x:c r="M80" s="17"/>
-      <x:c r="N80" s="17"/>
-      <x:c r="O80" s="17"/>
+      <x:c r="A80" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C80" s="19" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="D80" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E80" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F80" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G80" s="21" t="n">
+        <x:v>2.1548257079994073</x:v>
+      </x:c>
+      <x:c r="H80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I80" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N80" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O80" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P80" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q80" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="17"/>
-      <x:c r="B81" s="17"/>
-      <x:c r="C81" s="17"/>
-      <x:c r="D81" s="17"/>
-      <x:c r="E81" s="17"/>
-      <x:c r="F81" s="22"/>
-      <x:c r="G81" s="23"/>
-      <x:c r="H81" s="17"/>
-      <x:c r="I81" s="17"/>
-      <x:c r="J81" s="17"/>
-      <x:c r="K81" s="17"/>
-      <x:c r="L81" s="17"/>
-      <x:c r="M81" s="17"/>
-      <x:c r="N81" s="17"/>
-      <x:c r="O81" s="17"/>
+      <x:c r="A81" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B81" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C81" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D81" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E81" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F81" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G81" s="21" t="n">
+        <x:v>5.693695250000019</x:v>
+      </x:c>
+      <x:c r="H81" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I81" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J81" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K81" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L81" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M81" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N81" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O81" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P81" s="10" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q81" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="17"/>
-      <x:c r="B82" s="17"/>
-      <x:c r="C82" s="17"/>
-      <x:c r="D82" s="17"/>
-      <x:c r="E82" s="17"/>
-      <x:c r="F82" s="22"/>
-      <x:c r="G82" s="23"/>
-      <x:c r="H82" s="17"/>
-      <x:c r="I82" s="17"/>
-      <x:c r="J82" s="17"/>
-      <x:c r="K82" s="17"/>
-      <x:c r="L82" s="17"/>
-      <x:c r="M82" s="17"/>
-      <x:c r="N82" s="17"/>
-      <x:c r="O82" s="17"/>
+      <x:c r="A82" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B82" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C82" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D82" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E82" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F82" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G82" s="21" t="n">
+        <x:v>5.383480458000122</x:v>
+      </x:c>
+      <x:c r="H82" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I82" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J82" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K82" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L82" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M82" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N82" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O82" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P82" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q82" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="17"/>
-      <x:c r="B83" s="17"/>
-      <x:c r="C83" s="17"/>
-      <x:c r="D83" s="17"/>
-      <x:c r="E83" s="17"/>
-      <x:c r="F83" s="22"/>
-      <x:c r="G83" s="23"/>
-      <x:c r="H83" s="17"/>
-      <x:c r="I83" s="17"/>
-      <x:c r="J83" s="17"/>
-      <x:c r="K83" s="17"/>
-      <x:c r="L83" s="17"/>
-      <x:c r="M83" s="17"/>
-      <x:c r="N83" s="17"/>
-      <x:c r="O83" s="17"/>
+      <x:c r="A83" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B83" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C83" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D83" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E83" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F83" s="20" t="n">
+        <x:v>0.5294117647058824</x:v>
+      </x:c>
+      <x:c r="G83" s="21" t="n">
+        <x:v>5.245653582998784</x:v>
+      </x:c>
+      <x:c r="H83" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I83" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J83" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K83" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L83" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M83" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N83" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O83" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P83" s="10" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="Q83" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="17"/>
-      <x:c r="B84" s="17"/>
-      <x:c r="C84" s="17"/>
-      <x:c r="D84" s="17"/>
-      <x:c r="E84" s="17"/>
-      <x:c r="F84" s="22"/>
-      <x:c r="G84" s="23"/>
-      <x:c r="H84" s="17"/>
-      <x:c r="I84" s="17"/>
-      <x:c r="J84" s="17"/>
-      <x:c r="K84" s="17"/>
-      <x:c r="L84" s="17"/>
-      <x:c r="M84" s="17"/>
-      <x:c r="N84" s="17"/>
-      <x:c r="O84" s="17"/>
+      <x:c r="A84" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B84" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C84" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D84" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E84" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F84" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G84" s="21" t="n">
+        <x:v>5.210926332998497</x:v>
+      </x:c>
+      <x:c r="H84" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I84" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J84" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K84" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L84" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M84" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N84" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O84" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P84" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q84" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="17"/>
-      <x:c r="B85" s="17"/>
-      <x:c r="C85" s="17"/>
-      <x:c r="D85" s="17"/>
-      <x:c r="E85" s="17"/>
-      <x:c r="F85" s="22"/>
-      <x:c r="G85" s="23"/>
-      <x:c r="H85" s="17"/>
-      <x:c r="I85" s="17"/>
-      <x:c r="J85" s="17"/>
-      <x:c r="K85" s="17"/>
-      <x:c r="L85" s="17"/>
-      <x:c r="M85" s="17"/>
-      <x:c r="N85" s="17"/>
-      <x:c r="O85" s="17"/>
+      <x:c r="A85" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B85" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C85" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D85" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E85" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F85" s="20" t="n">
+        <x:v>0.5294117647058824</x:v>
+      </x:c>
+      <x:c r="G85" s="21" t="n">
+        <x:v>5.252349292000872</x:v>
+      </x:c>
+      <x:c r="H85" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I85" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J85" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K85" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L85" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M85" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N85" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O85" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P85" s="10" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q85" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="17"/>
-      <x:c r="B86" s="17"/>
-      <x:c r="C86" s="17"/>
-      <x:c r="D86" s="17"/>
-      <x:c r="E86" s="17"/>
-      <x:c r="F86" s="22"/>
-      <x:c r="G86" s="23"/>
-      <x:c r="H86" s="17"/>
-      <x:c r="I86" s="17"/>
-      <x:c r="J86" s="17"/>
-      <x:c r="K86" s="17"/>
-      <x:c r="L86" s="17"/>
-      <x:c r="M86" s="17"/>
-      <x:c r="N86" s="17"/>
-      <x:c r="O86" s="17"/>
+      <x:c r="A86" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B86" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C86" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D86" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E86" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F86" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G86" s="21" t="n">
+        <x:v>5.260390416999144</x:v>
+      </x:c>
+      <x:c r="H86" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I86" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J86" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K86" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L86" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M86" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N86" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O86" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P86" s="10" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="Q86" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="17"/>
-      <x:c r="B87" s="17"/>
-      <x:c r="C87" s="17"/>
-      <x:c r="D87" s="17"/>
-      <x:c r="E87" s="17"/>
-      <x:c r="F87" s="22"/>
-      <x:c r="G87" s="23"/>
-      <x:c r="H87" s="17"/>
-      <x:c r="I87" s="17"/>
-      <x:c r="J87" s="17"/>
-      <x:c r="K87" s="17"/>
-      <x:c r="L87" s="17"/>
-      <x:c r="M87" s="17"/>
-      <x:c r="N87" s="17"/>
-      <x:c r="O87" s="17"/>
+      <x:c r="A87" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B87" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C87" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D87" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E87" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F87" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G87" s="21" t="n">
+        <x:v>5.222566958000243</x:v>
+      </x:c>
+      <x:c r="H87" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I87" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J87" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K87" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L87" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M87" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N87" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O87" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P87" s="10" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="Q87" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="17"/>
-      <x:c r="B88" s="17"/>
-      <x:c r="C88" s="17"/>
-      <x:c r="D88" s="17"/>
-      <x:c r="E88" s="17"/>
-      <x:c r="F88" s="22"/>
-      <x:c r="G88" s="23"/>
-      <x:c r="H88" s="17"/>
-      <x:c r="I88" s="17"/>
-      <x:c r="J88" s="17"/>
-      <x:c r="K88" s="17"/>
-      <x:c r="L88" s="17"/>
-      <x:c r="M88" s="17"/>
-      <x:c r="N88" s="17"/>
-      <x:c r="O88" s="17"/>
+      <x:c r="A88" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C88" s="19" t="str">
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="D88" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E88" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F88" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G88" s="21" t="n">
+        <x:v>1.9532605000022158</x:v>
+      </x:c>
+      <x:c r="H88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I88" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N88" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O88" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P88" s="10" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q88" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="17"/>
-      <x:c r="B89" s="17"/>
-      <x:c r="C89" s="17"/>
-      <x:c r="D89" s="17"/>
-      <x:c r="E89" s="17"/>
-      <x:c r="F89" s="22"/>
-      <x:c r="G89" s="23"/>
-      <x:c r="H89" s="17"/>
-      <x:c r="I89" s="17"/>
-      <x:c r="J89" s="17"/>
-      <x:c r="K89" s="17"/>
-      <x:c r="L89" s="17"/>
-      <x:c r="M89" s="17"/>
-      <x:c r="N89" s="17"/>
-      <x:c r="O89" s="17"/>
+      <x:c r="A89" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B89" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C89" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D89" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E89" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F89" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G89" s="21" t="n">
+        <x:v>5.8019277499988675</x:v>
+      </x:c>
+      <x:c r="H89" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I89" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J89" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K89" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L89" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M89" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N89" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O89" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P89" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q89" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="17"/>
-      <x:c r="B90" s="17"/>
-      <x:c r="C90" s="17"/>
-      <x:c r="D90" s="17"/>
-      <x:c r="E90" s="17"/>
-      <x:c r="F90" s="22"/>
-      <x:c r="G90" s="23"/>
-      <x:c r="H90" s="17"/>
-      <x:c r="I90" s="17"/>
-      <x:c r="J90" s="17"/>
-      <x:c r="K90" s="17"/>
-      <x:c r="L90" s="17"/>
-      <x:c r="M90" s="17"/>
-      <x:c r="N90" s="17"/>
-      <x:c r="O90" s="17"/>
+      <x:c r="A90" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B90" s="19" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C90" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D90" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E90" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F90" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G90" s="21" t="n">
+        <x:v>5.979782291000447</x:v>
+      </x:c>
+      <x:c r="H90" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I90" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J90" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K90" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L90" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M90" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N90" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O90" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P90" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q90" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="17"/>
-      <x:c r="B91" s="17"/>
-      <x:c r="C91" s="17"/>
-      <x:c r="D91" s="17"/>
-      <x:c r="E91" s="17"/>
-      <x:c r="F91" s="22"/>
-      <x:c r="G91" s="23"/>
-      <x:c r="H91" s="17"/>
-      <x:c r="I91" s="17"/>
-      <x:c r="J91" s="17"/>
-      <x:c r="K91" s="17"/>
-      <x:c r="L91" s="17"/>
-      <x:c r="M91" s="17"/>
-      <x:c r="N91" s="17"/>
-      <x:c r="O91" s="17"/>
+      <x:c r="A91" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B91" s="19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C91" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D91" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E91" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F91" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G91" s="21" t="n">
+        <x:v>5.385983165997459</x:v>
+      </x:c>
+      <x:c r="H91" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I91" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J91" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K91" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L91" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M91" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N91" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O91" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P91" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q91" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="17"/>
-      <x:c r="B92" s="17"/>
-      <x:c r="C92" s="17"/>
-      <x:c r="D92" s="17"/>
-      <x:c r="E92" s="17"/>
-      <x:c r="F92" s="22"/>
-      <x:c r="G92" s="23"/>
-      <x:c r="H92" s="17"/>
-      <x:c r="I92" s="17"/>
-      <x:c r="J92" s="17"/>
-      <x:c r="K92" s="17"/>
-      <x:c r="L92" s="17"/>
-      <x:c r="M92" s="17"/>
-      <x:c r="N92" s="17"/>
-      <x:c r="O92" s="17"/>
+      <x:c r="A92" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B92" s="19" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C92" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D92" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E92" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F92" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G92" s="21" t="n">
+        <x:v>5.207741542002623</x:v>
+      </x:c>
+      <x:c r="H92" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I92" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J92" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K92" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L92" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M92" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N92" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O92" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P92" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q92" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="17"/>
-      <x:c r="B93" s="17"/>
-      <x:c r="C93" s="17"/>
-      <x:c r="D93" s="17"/>
-      <x:c r="E93" s="17"/>
-      <x:c r="F93" s="22"/>
-      <x:c r="G93" s="23"/>
-      <x:c r="H93" s="17"/>
-      <x:c r="I93" s="17"/>
-      <x:c r="J93" s="17"/>
-      <x:c r="K93" s="17"/>
-      <x:c r="L93" s="17"/>
-      <x:c r="M93" s="17"/>
-      <x:c r="N93" s="17"/>
-      <x:c r="O93" s="17"/>
+      <x:c r="A93" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B93" s="19" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C93" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D93" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E93" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F93" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G93" s="21" t="n">
+        <x:v>5.215950666999561</x:v>
+      </x:c>
+      <x:c r="H93" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I93" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J93" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K93" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L93" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M93" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N93" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O93" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P93" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q93" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="17"/>
-      <x:c r="B94" s="17"/>
-      <x:c r="C94" s="17"/>
-      <x:c r="D94" s="17"/>
-      <x:c r="E94" s="17"/>
-      <x:c r="F94" s="22"/>
-      <x:c r="G94" s="23"/>
-      <x:c r="H94" s="17"/>
-      <x:c r="I94" s="17"/>
-      <x:c r="J94" s="17"/>
-      <x:c r="K94" s="17"/>
-      <x:c r="L94" s="17"/>
-      <x:c r="M94" s="17"/>
-      <x:c r="N94" s="17"/>
-      <x:c r="O94" s="17"/>
+      <x:c r="A94" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B94" s="19" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C94" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D94" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E94" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F94" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G94" s="21" t="n">
+        <x:v>5.217273082998872</x:v>
+      </x:c>
+      <x:c r="H94" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I94" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J94" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K94" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L94" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M94" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N94" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O94" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P94" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q94" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="17"/>
-      <x:c r="B95" s="17"/>
-      <x:c r="C95" s="17"/>
-      <x:c r="D95" s="17"/>
-      <x:c r="E95" s="17"/>
-      <x:c r="F95" s="22"/>
-      <x:c r="G95" s="23"/>
-      <x:c r="H95" s="17"/>
-      <x:c r="I95" s="17"/>
-      <x:c r="J95" s="17"/>
-      <x:c r="K95" s="17"/>
-      <x:c r="L95" s="17"/>
-      <x:c r="M95" s="17"/>
-      <x:c r="N95" s="17"/>
-      <x:c r="O95" s="17"/>
+      <x:c r="A95" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B95" s="19" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C95" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D95" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E95" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F95" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G95" s="21" t="n">
+        <x:v>5.2204393339998205</x:v>
+      </x:c>
+      <x:c r="H95" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I95" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J95" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K95" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L95" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M95" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N95" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O95" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P95" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q95" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="17"/>
-      <x:c r="B96" s="17"/>
-      <x:c r="C96" s="17"/>
-      <x:c r="D96" s="17"/>
-      <x:c r="E96" s="17"/>
-      <x:c r="F96" s="22"/>
-      <x:c r="G96" s="23"/>
-      <x:c r="H96" s="17"/>
-      <x:c r="I96" s="17"/>
-      <x:c r="J96" s="17"/>
-      <x:c r="K96" s="17"/>
-      <x:c r="L96" s="17"/>
-      <x:c r="M96" s="17"/>
-      <x:c r="N96" s="17"/>
-      <x:c r="O96" s="17"/>
+      <x:c r="A96" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B96" s="19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C96" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D96" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E96" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F96" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G96" s="21" t="n">
+        <x:v>5.220912084001611</x:v>
+      </x:c>
+      <x:c r="H96" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I96" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J96" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K96" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L96" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M96" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N96" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O96" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P96" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q96" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="17"/>
-      <x:c r="B97" s="17"/>
-      <x:c r="C97" s="17"/>
-      <x:c r="D97" s="17"/>
-      <x:c r="E97" s="17"/>
-      <x:c r="F97" s="22"/>
-      <x:c r="G97" s="23"/>
-      <x:c r="H97" s="17"/>
-      <x:c r="I97" s="17"/>
-      <x:c r="J97" s="17"/>
-      <x:c r="K97" s="17"/>
-      <x:c r="L97" s="17"/>
-      <x:c r="M97" s="17"/>
-      <x:c r="N97" s="17"/>
-      <x:c r="O97" s="17"/>
+      <x:c r="A97" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B97" s="19" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C97" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D97" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E97" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F97" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G97" s="21" t="n">
+        <x:v>5.21840558400072</x:v>
+      </x:c>
+      <x:c r="H97" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I97" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J97" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K97" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L97" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M97" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N97" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O97" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P97" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q97" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="17"/>
-      <x:c r="B98" s="17"/>
-      <x:c r="C98" s="17"/>
-      <x:c r="D98" s="17"/>
-      <x:c r="E98" s="17"/>
-      <x:c r="F98" s="22"/>
-      <x:c r="G98" s="23"/>
-      <x:c r="H98" s="17"/>
-      <x:c r="I98" s="17"/>
-      <x:c r="J98" s="17"/>
-      <x:c r="K98" s="17"/>
-      <x:c r="L98" s="17"/>
-      <x:c r="M98" s="17"/>
-      <x:c r="N98" s="17"/>
-      <x:c r="O98" s="17"/>
+      <x:c r="A98" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B98" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C98" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D98" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E98" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F98" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G98" s="21" t="n">
+        <x:v>5.221170209002594</x:v>
+      </x:c>
+      <x:c r="H98" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I98" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J98" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K98" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L98" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M98" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N98" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O98" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P98" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q98" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="17"/>
-      <x:c r="B99" s="17"/>
-      <x:c r="C99" s="17"/>
-      <x:c r="D99" s="17"/>
-      <x:c r="E99" s="17"/>
-      <x:c r="F99" s="22"/>
-      <x:c r="G99" s="23"/>
-      <x:c r="H99" s="17"/>
-      <x:c r="I99" s="17"/>
-      <x:c r="J99" s="17"/>
-      <x:c r="K99" s="17"/>
-      <x:c r="L99" s="17"/>
-      <x:c r="M99" s="17"/>
-      <x:c r="N99" s="17"/>
-      <x:c r="O99" s="17"/>
+      <x:c r="A99" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B99" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C99" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D99" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E99" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F99" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G99" s="21" t="n">
+        <x:v>5.223314584000036</x:v>
+      </x:c>
+      <x:c r="H99" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I99" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J99" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K99" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L99" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M99" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N99" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O99" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P99" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q99" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="17"/>
-      <x:c r="B100" s="17"/>
-      <x:c r="C100" s="17"/>
-      <x:c r="D100" s="17"/>
-      <x:c r="E100" s="17"/>
-      <x:c r="F100" s="22"/>
-      <x:c r="G100" s="23"/>
-      <x:c r="H100" s="17"/>
-      <x:c r="I100" s="17"/>
-      <x:c r="J100" s="17"/>
-      <x:c r="K100" s="17"/>
-      <x:c r="L100" s="17"/>
-      <x:c r="M100" s="17"/>
-      <x:c r="N100" s="17"/>
-      <x:c r="O100" s="17"/>
+      <x:c r="A100" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B100" s="19" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C100" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D100" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E100" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F100" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G100" s="21" t="n">
+        <x:v>5.217210833001445</x:v>
+      </x:c>
+      <x:c r="H100" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I100" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J100" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K100" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L100" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M100" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N100" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O100" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P100" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q100" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="17"/>
-      <x:c r="B101" s="17"/>
-      <x:c r="C101" s="17"/>
-      <x:c r="D101" s="17"/>
-      <x:c r="E101" s="17"/>
-      <x:c r="F101" s="22"/>
-      <x:c r="G101" s="23"/>
-      <x:c r="H101" s="17"/>
-      <x:c r="I101" s="17"/>
-      <x:c r="J101" s="17"/>
-      <x:c r="K101" s="17"/>
-      <x:c r="L101" s="17"/>
-      <x:c r="M101" s="17"/>
-      <x:c r="N101" s="17"/>
-      <x:c r="O101" s="17"/>
+      <x:c r="A101" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B101" s="19" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C101" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D101" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E101" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F101" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G101" s="21" t="n">
+        <x:v>5.215535415998602</x:v>
+      </x:c>
+      <x:c r="H101" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I101" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J101" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K101" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L101" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M101" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N101" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O101" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P101" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q101" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="17"/>
-      <x:c r="B102" s="17"/>
-      <x:c r="C102" s="17"/>
-      <x:c r="D102" s="17"/>
-      <x:c r="E102" s="17"/>
-      <x:c r="F102" s="22"/>
-      <x:c r="G102" s="23"/>
-      <x:c r="H102" s="17"/>
-      <x:c r="I102" s="17"/>
-      <x:c r="J102" s="17"/>
-      <x:c r="K102" s="17"/>
-      <x:c r="L102" s="17"/>
-      <x:c r="M102" s="17"/>
-      <x:c r="N102" s="17"/>
-      <x:c r="O102" s="17"/>
+      <x:c r="A102" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B102" s="19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C102" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D102" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E102" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F102" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G102" s="21" t="n">
+        <x:v>5.214486374999979</x:v>
+      </x:c>
+      <x:c r="H102" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I102" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J102" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K102" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L102" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M102" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N102" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O102" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P102" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q102" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="17"/>
-      <x:c r="B103" s="17"/>
-      <x:c r="C103" s="17"/>
-      <x:c r="D103" s="17"/>
-      <x:c r="E103" s="17"/>
-      <x:c r="F103" s="22"/>
-      <x:c r="G103" s="23"/>
-      <x:c r="H103" s="17"/>
-      <x:c r="I103" s="17"/>
-      <x:c r="J103" s="17"/>
-      <x:c r="K103" s="17"/>
-      <x:c r="L103" s="17"/>
-      <x:c r="M103" s="17"/>
-      <x:c r="N103" s="17"/>
-      <x:c r="O103" s="17"/>
+      <x:c r="A103" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B103" s="19" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C103" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D103" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E103" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F103" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G103" s="21" t="n">
+        <x:v>5.3037565410013485</x:v>
+      </x:c>
+      <x:c r="H103" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I103" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J103" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K103" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L103" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M103" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N103" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O103" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P103" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q103" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="17"/>
-      <x:c r="B104" s="17"/>
-      <x:c r="C104" s="17"/>
-      <x:c r="D104" s="17"/>
-      <x:c r="E104" s="17"/>
-      <x:c r="F104" s="22"/>
-      <x:c r="G104" s="23"/>
-      <x:c r="H104" s="17"/>
-      <x:c r="I104" s="17"/>
-      <x:c r="J104" s="17"/>
-      <x:c r="K104" s="17"/>
-      <x:c r="L104" s="17"/>
-      <x:c r="M104" s="17"/>
-      <x:c r="N104" s="17"/>
-      <x:c r="O104" s="17"/>
+      <x:c r="A104" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B104" s="19" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C104" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D104" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E104" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F104" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G104" s="21" t="n">
+        <x:v>5.585930583001755</x:v>
+      </x:c>
+      <x:c r="H104" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I104" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J104" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K104" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L104" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M104" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N104" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O104" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P104" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q104" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="17"/>
-      <x:c r="B105" s="17"/>
-      <x:c r="C105" s="17"/>
-      <x:c r="D105" s="17"/>
-      <x:c r="E105" s="17"/>
-      <x:c r="F105" s="22"/>
-      <x:c r="G105" s="23"/>
-      <x:c r="H105" s="17"/>
-      <x:c r="I105" s="17"/>
-      <x:c r="J105" s="17"/>
-      <x:c r="K105" s="17"/>
-      <x:c r="L105" s="17"/>
-      <x:c r="M105" s="17"/>
-      <x:c r="N105" s="17"/>
-      <x:c r="O105" s="17"/>
+      <x:c r="A105" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B105" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C105" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D105" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E105" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F105" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G105" s="21" t="n">
+        <x:v>5.208725666998362</x:v>
+      </x:c>
+      <x:c r="H105" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I105" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J105" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K105" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L105" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M105" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N105" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O105" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P105" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q105" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="17"/>
-      <x:c r="B106" s="17"/>
-      <x:c r="C106" s="17"/>
-      <x:c r="D106" s="17"/>
-      <x:c r="E106" s="17"/>
-      <x:c r="F106" s="22"/>
-      <x:c r="G106" s="23"/>
-      <x:c r="H106" s="17"/>
-      <x:c r="I106" s="17"/>
-      <x:c r="J106" s="17"/>
-      <x:c r="K106" s="17"/>
-      <x:c r="L106" s="17"/>
-      <x:c r="M106" s="17"/>
-      <x:c r="N106" s="17"/>
-      <x:c r="O106" s="17"/>
+      <x:c r="A106" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B106" s="19" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C106" s="19" t="str">
+        <x:v>HRM H=1 blend=0.12</x:v>
+      </x:c>
+      <x:c r="D106" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E106" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F106" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G106" s="21" t="n">
+        <x:v>5.215329541999381</x:v>
+      </x:c>
+      <x:c r="H106" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I106" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J106" s="19" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="K106" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L106" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M106" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N106" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O106" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P106" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q106" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="17"/>
-      <x:c r="B107" s="17"/>
-      <x:c r="C107" s="17"/>
-      <x:c r="D107" s="17"/>
-      <x:c r="E107" s="17"/>
-      <x:c r="F107" s="22"/>
-      <x:c r="G107" s="23"/>
-      <x:c r="H107" s="17"/>
-      <x:c r="I107" s="17"/>
-      <x:c r="J107" s="17"/>
-      <x:c r="K107" s="17"/>
-      <x:c r="L107" s="17"/>
-      <x:c r="M107" s="17"/>
-      <x:c r="N107" s="17"/>
-      <x:c r="O107" s="17"/>
+      <x:c r="A107" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B107" s="19" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C107" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D107" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E107" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F107" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G107" s="21" t="n">
+        <x:v>5.216904958000669</x:v>
+      </x:c>
+      <x:c r="H107" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I107" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J107" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K107" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L107" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M107" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N107" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O107" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P107" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q107" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="17"/>
-      <x:c r="B108" s="17"/>
-      <x:c r="C108" s="17"/>
-      <x:c r="D108" s="17"/>
-      <x:c r="E108" s="17"/>
-      <x:c r="F108" s="22"/>
-      <x:c r="G108" s="23"/>
-      <x:c r="H108" s="17"/>
-      <x:c r="I108" s="17"/>
-      <x:c r="J108" s="17"/>
-      <x:c r="K108" s="17"/>
-      <x:c r="L108" s="17"/>
-      <x:c r="M108" s="17"/>
-      <x:c r="N108" s="17"/>
-      <x:c r="O108" s="17"/>
+      <x:c r="A108" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B108" s="19" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C108" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D108" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E108" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F108" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G108" s="21" t="n">
+        <x:v>5.220081832998403</x:v>
+      </x:c>
+      <x:c r="H108" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I108" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J108" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K108" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L108" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M108" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N108" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O108" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P108" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q108" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="17"/>
-      <x:c r="B109" s="17"/>
-      <x:c r="C109" s="17"/>
-      <x:c r="D109" s="17"/>
-      <x:c r="E109" s="17"/>
-      <x:c r="F109" s="22"/>
-      <x:c r="G109" s="23"/>
-      <x:c r="H109" s="17"/>
-      <x:c r="I109" s="17"/>
-      <x:c r="J109" s="17"/>
-      <x:c r="K109" s="17"/>
-      <x:c r="L109" s="17"/>
-      <x:c r="M109" s="17"/>
-      <x:c r="N109" s="17"/>
-      <x:c r="O109" s="17"/>
+      <x:c r="A109" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B109" s="19" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C109" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D109" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E109" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F109" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G109" s="21" t="n">
+        <x:v>5.21975512499921</x:v>
+      </x:c>
+      <x:c r="H109" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I109" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J109" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K109" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L109" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M109" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N109" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O109" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P109" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q109" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="17"/>
-      <x:c r="B110" s="17"/>
-      <x:c r="C110" s="17"/>
-      <x:c r="D110" s="17"/>
-      <x:c r="E110" s="17"/>
-      <x:c r="F110" s="22"/>
-      <x:c r="G110" s="23"/>
-      <x:c r="H110" s="17"/>
-      <x:c r="I110" s="17"/>
-      <x:c r="J110" s="17"/>
-      <x:c r="K110" s="17"/>
-      <x:c r="L110" s="17"/>
-      <x:c r="M110" s="17"/>
-      <x:c r="N110" s="17"/>
-      <x:c r="O110" s="17"/>
+      <x:c r="A110" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B110" s="19" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C110" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D110" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E110" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F110" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G110" s="21" t="n">
+        <x:v>5.217237875000137</x:v>
+      </x:c>
+      <x:c r="H110" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I110" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J110" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K110" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L110" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M110" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N110" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O110" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P110" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q110" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="17"/>
-      <x:c r="B111" s="17"/>
-      <x:c r="C111" s="17"/>
-      <x:c r="D111" s="17"/>
-      <x:c r="E111" s="17"/>
-      <x:c r="F111" s="22"/>
-      <x:c r="G111" s="23"/>
-      <x:c r="H111" s="17"/>
-      <x:c r="I111" s="17"/>
-      <x:c r="J111" s="17"/>
-      <x:c r="K111" s="17"/>
-      <x:c r="L111" s="17"/>
-      <x:c r="M111" s="17"/>
-      <x:c r="N111" s="17"/>
-      <x:c r="O111" s="17"/>
+      <x:c r="A111" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B111" s="19" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C111" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D111" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E111" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F111" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G111" s="21" t="n">
+        <x:v>5.217231082999206</x:v>
+      </x:c>
+      <x:c r="H111" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I111" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J111" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K111" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L111" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M111" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N111" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O111" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P111" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q111" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="17"/>
-      <x:c r="B112" s="17"/>
-      <x:c r="C112" s="17"/>
-      <x:c r="D112" s="17"/>
-      <x:c r="E112" s="17"/>
-      <x:c r="F112" s="22"/>
-      <x:c r="G112" s="23"/>
-      <x:c r="H112" s="17"/>
-      <x:c r="I112" s="17"/>
-      <x:c r="J112" s="17"/>
-      <x:c r="K112" s="17"/>
-      <x:c r="L112" s="17"/>
-      <x:c r="M112" s="17"/>
-      <x:c r="N112" s="17"/>
-      <x:c r="O112" s="17"/>
+      <x:c r="A112" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B112" s="19" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C112" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D112" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E112" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F112" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G112" s="21" t="n">
+        <x:v>5.22437366700251</x:v>
+      </x:c>
+      <x:c r="H112" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I112" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J112" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K112" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L112" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M112" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N112" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O112" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P112" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q112" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="17"/>
-      <x:c r="B113" s="17"/>
-      <x:c r="C113" s="17"/>
-      <x:c r="D113" s="17"/>
-      <x:c r="E113" s="17"/>
-      <x:c r="F113" s="22"/>
-      <x:c r="G113" s="23"/>
-      <x:c r="H113" s="17"/>
-      <x:c r="I113" s="17"/>
-      <x:c r="J113" s="17"/>
-      <x:c r="K113" s="17"/>
-      <x:c r="L113" s="17"/>
-      <x:c r="M113" s="17"/>
-      <x:c r="N113" s="17"/>
-      <x:c r="O113" s="17"/>
+      <x:c r="A113" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B113" s="19" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C113" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D113" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E113" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F113" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G113" s="21" t="n">
+        <x:v>5.218991333000304</x:v>
+      </x:c>
+      <x:c r="H113" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I113" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J113" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K113" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L113" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M113" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N113" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O113" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P113" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q113" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="17"/>
-      <x:c r="B114" s="17"/>
-      <x:c r="C114" s="17"/>
-      <x:c r="D114" s="17"/>
-      <x:c r="E114" s="17"/>
-      <x:c r="F114" s="22"/>
-      <x:c r="G114" s="23"/>
-      <x:c r="H114" s="17"/>
-      <x:c r="I114" s="17"/>
-      <x:c r="J114" s="17"/>
-      <x:c r="K114" s="17"/>
-      <x:c r="L114" s="17"/>
-      <x:c r="M114" s="17"/>
-      <x:c r="N114" s="17"/>
-      <x:c r="O114" s="17"/>
+      <x:c r="A114" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B114" s="19" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C114" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D114" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E114" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F114" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G114" s="21" t="n">
+        <x:v>5.214443832999677</x:v>
+      </x:c>
+      <x:c r="H114" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I114" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J114" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K114" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L114" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M114" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N114" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O114" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P114" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q114" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="17"/>
-      <x:c r="B115" s="17"/>
-      <x:c r="C115" s="17"/>
-      <x:c r="D115" s="17"/>
-      <x:c r="E115" s="17"/>
-      <x:c r="F115" s="22"/>
-      <x:c r="G115" s="23"/>
-      <x:c r="H115" s="17"/>
-      <x:c r="I115" s="17"/>
-      <x:c r="J115" s="17"/>
-      <x:c r="K115" s="17"/>
-      <x:c r="L115" s="17"/>
-      <x:c r="M115" s="17"/>
-      <x:c r="N115" s="17"/>
-      <x:c r="O115" s="17"/>
+      <x:c r="A115" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B115" s="19" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C115" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D115" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E115" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F115" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G115" s="21" t="n">
+        <x:v>5.2016239580007095</x:v>
+      </x:c>
+      <x:c r="H115" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I115" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J115" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K115" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L115" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M115" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N115" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O115" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P115" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q115" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="17"/>
-      <x:c r="B116" s="17"/>
-      <x:c r="C116" s="17"/>
-      <x:c r="D116" s="17"/>
-      <x:c r="E116" s="17"/>
-      <x:c r="F116" s="22"/>
-      <x:c r="G116" s="23"/>
-      <x:c r="H116" s="17"/>
-      <x:c r="I116" s="17"/>
-      <x:c r="J116" s="17"/>
-      <x:c r="K116" s="17"/>
-      <x:c r="L116" s="17"/>
-      <x:c r="M116" s="17"/>
-      <x:c r="N116" s="17"/>
-      <x:c r="O116" s="17"/>
+      <x:c r="A116" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B116" s="19" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C116" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D116" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E116" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F116" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G116" s="21" t="n">
+        <x:v>5.209255416997621</x:v>
+      </x:c>
+      <x:c r="H116" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I116" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J116" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K116" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L116" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M116" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N116" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O116" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P116" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q116" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="17"/>
-      <x:c r="B117" s="17"/>
-      <x:c r="C117" s="17"/>
-      <x:c r="D117" s="17"/>
-      <x:c r="E117" s="17"/>
-      <x:c r="F117" s="22"/>
-      <x:c r="G117" s="23"/>
-      <x:c r="H117" s="17"/>
-      <x:c r="I117" s="17"/>
-      <x:c r="J117" s="17"/>
-      <x:c r="K117" s="17"/>
-      <x:c r="L117" s="17"/>
-      <x:c r="M117" s="17"/>
-      <x:c r="N117" s="17"/>
-      <x:c r="O117" s="17"/>
+      <x:c r="A117" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B117" s="19" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C117" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D117" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E117" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F117" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G117" s="21" t="n">
+        <x:v>5.217655167001794</x:v>
+      </x:c>
+      <x:c r="H117" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I117" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J117" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K117" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L117" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M117" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N117" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O117" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P117" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q117" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="17"/>
-      <x:c r="B118" s="17"/>
-      <x:c r="C118" s="17"/>
-      <x:c r="D118" s="17"/>
-      <x:c r="E118" s="17"/>
-      <x:c r="F118" s="22"/>
-      <x:c r="G118" s="23"/>
-      <x:c r="H118" s="17"/>
-      <x:c r="I118" s="17"/>
-      <x:c r="J118" s="17"/>
-      <x:c r="K118" s="17"/>
-      <x:c r="L118" s="17"/>
-      <x:c r="M118" s="17"/>
-      <x:c r="N118" s="17"/>
-      <x:c r="O118" s="17"/>
+      <x:c r="A118" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B118" s="19" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C118" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D118" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E118" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F118" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G118" s="21" t="n">
+        <x:v>5.21432195899979</x:v>
+      </x:c>
+      <x:c r="H118" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I118" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J118" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K118" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L118" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M118" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N118" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O118" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P118" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q118" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="17"/>
-      <x:c r="B119" s="17"/>
-      <x:c r="C119" s="17"/>
-      <x:c r="D119" s="17"/>
-      <x:c r="E119" s="17"/>
-      <x:c r="F119" s="22"/>
-      <x:c r="G119" s="23"/>
-      <x:c r="H119" s="17"/>
-      <x:c r="I119" s="17"/>
-      <x:c r="J119" s="17"/>
-      <x:c r="K119" s="17"/>
-      <x:c r="L119" s="17"/>
-      <x:c r="M119" s="17"/>
-      <x:c r="N119" s="17"/>
-      <x:c r="O119" s="17"/>
+      <x:c r="A119" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B119" s="19" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C119" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D119" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E119" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F119" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G119" s="21" t="n">
+        <x:v>5.219495541001379</x:v>
+      </x:c>
+      <x:c r="H119" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I119" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J119" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K119" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L119" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M119" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N119" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O119" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P119" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q119" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="17"/>
-      <x:c r="B120" s="17"/>
-      <x:c r="C120" s="17"/>
-      <x:c r="D120" s="17"/>
-      <x:c r="E120" s="17"/>
-      <x:c r="F120" s="22"/>
-      <x:c r="G120" s="23"/>
-      <x:c r="H120" s="17"/>
-      <x:c r="I120" s="17"/>
-      <x:c r="J120" s="17"/>
-      <x:c r="K120" s="17"/>
-      <x:c r="L120" s="17"/>
-      <x:c r="M120" s="17"/>
-      <x:c r="N120" s="17"/>
-      <x:c r="O120" s="17"/>
+      <x:c r="A120" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B120" s="19" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C120" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D120" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E120" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F120" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G120" s="21" t="n">
+        <x:v>5.214636249998875</x:v>
+      </x:c>
+      <x:c r="H120" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I120" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J120" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K120" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L120" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M120" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N120" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O120" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P120" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q120" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="17"/>
-      <x:c r="B121" s="17"/>
-      <x:c r="C121" s="17"/>
-      <x:c r="D121" s="17"/>
-      <x:c r="E121" s="17"/>
-      <x:c r="F121" s="22"/>
-      <x:c r="G121" s="23"/>
-      <x:c r="H121" s="17"/>
-      <x:c r="I121" s="17"/>
-      <x:c r="J121" s="17"/>
-      <x:c r="K121" s="17"/>
-      <x:c r="L121" s="17"/>
-      <x:c r="M121" s="17"/>
-      <x:c r="N121" s="17"/>
-      <x:c r="O121" s="17"/>
+      <x:c r="A121" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B121" s="19" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C121" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D121" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E121" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F121" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G121" s="21" t="n">
+        <x:v>5.217913374999625</x:v>
+      </x:c>
+      <x:c r="H121" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I121" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J121" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K121" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L121" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M121" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N121" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O121" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P121" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q121" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="17"/>
-      <x:c r="B122" s="17"/>
-      <x:c r="C122" s="17"/>
-      <x:c r="D122" s="17"/>
-      <x:c r="E122" s="17"/>
-      <x:c r="F122" s="22"/>
-      <x:c r="G122" s="23"/>
-      <x:c r="H122" s="17"/>
-      <x:c r="I122" s="17"/>
-      <x:c r="J122" s="17"/>
-      <x:c r="K122" s="17"/>
-      <x:c r="L122" s="17"/>
-      <x:c r="M122" s="17"/>
-      <x:c r="N122" s="17"/>
-      <x:c r="O122" s="17"/>
+      <x:c r="A122" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B122" s="19" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C122" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D122" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E122" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F122" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G122" s="21" t="n">
+        <x:v>5.214042209001491</x:v>
+      </x:c>
+      <x:c r="H122" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I122" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J122" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K122" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L122" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M122" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N122" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O122" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P122" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q122" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="17"/>
-      <x:c r="B123" s="17"/>
-      <x:c r="C123" s="17"/>
-      <x:c r="D123" s="17"/>
-      <x:c r="E123" s="17"/>
-      <x:c r="F123" s="22"/>
-      <x:c r="G123" s="23"/>
-      <x:c r="H123" s="17"/>
-      <x:c r="I123" s="17"/>
-      <x:c r="J123" s="17"/>
-      <x:c r="K123" s="17"/>
-      <x:c r="L123" s="17"/>
-      <x:c r="M123" s="17"/>
-      <x:c r="N123" s="17"/>
-      <x:c r="O123" s="17"/>
+      <x:c r="A123" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B123" s="19" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C123" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D123" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E123" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F123" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G123" s="21" t="n">
+        <x:v>5.2195898330028285</x:v>
+      </x:c>
+      <x:c r="H123" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I123" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J123" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K123" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L123" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M123" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N123" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O123" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P123" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q123" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="17"/>
-      <x:c r="B124" s="17"/>
-      <x:c r="C124" s="17"/>
-      <x:c r="D124" s="17"/>
-      <x:c r="E124" s="17"/>
-      <x:c r="F124" s="22"/>
-      <x:c r="G124" s="23"/>
-      <x:c r="H124" s="17"/>
-      <x:c r="I124" s="17"/>
-      <x:c r="J124" s="17"/>
-      <x:c r="K124" s="17"/>
-      <x:c r="L124" s="17"/>
-      <x:c r="M124" s="17"/>
-      <x:c r="N124" s="17"/>
-      <x:c r="O124" s="17"/>
+      <x:c r="A124" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B124" s="19" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C124" s="19" t="str">
+        <x:v>HRM H=1 blend=0.16</x:v>
+      </x:c>
+      <x:c r="D124" s="19" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E124" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F124" s="20" t="n">
+        <x:v>0.5882352941176471</x:v>
+      </x:c>
+      <x:c r="G124" s="21" t="n">
+        <x:v>5.216202416999295</x:v>
+      </x:c>
+      <x:c r="H124" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I124" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J124" s="19" t="n">
+        <x:v>0.16</x:v>
+      </x:c>
+      <x:c r="K124" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L124" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M124" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N124" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O124" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P124" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q124" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="17"/>
-      <x:c r="B125" s="17"/>
-      <x:c r="C125" s="17"/>
-      <x:c r="D125" s="17"/>
-      <x:c r="E125" s="17"/>
-      <x:c r="F125" s="22"/>
-      <x:c r="G125" s="23"/>
-      <x:c r="H125" s="17"/>
-      <x:c r="I125" s="17"/>
-      <x:c r="J125" s="17"/>
-      <x:c r="K125" s="17"/>
-      <x:c r="L125" s="17"/>
-      <x:c r="M125" s="17"/>
-      <x:c r="N125" s="17"/>
-      <x:c r="O125" s="17"/>
+      <x:c r="A125" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B125" s="19" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C125" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D125" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E125" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F125" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G125" s="21" t="n">
+        <x:v>5.219844458999432</x:v>
+      </x:c>
+      <x:c r="H125" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I125" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J125" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K125" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L125" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M125" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N125" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O125" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P125" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q125" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="17"/>
-      <x:c r="B126" s="17"/>
-      <x:c r="C126" s="17"/>
-      <x:c r="D126" s="17"/>
-      <x:c r="E126" s="17"/>
-      <x:c r="F126" s="22"/>
-      <x:c r="G126" s="23"/>
-      <x:c r="H126" s="17"/>
-      <x:c r="I126" s="17"/>
-      <x:c r="J126" s="17"/>
-      <x:c r="K126" s="17"/>
-      <x:c r="L126" s="17"/>
-      <x:c r="M126" s="17"/>
-      <x:c r="N126" s="17"/>
-      <x:c r="O126" s="17"/>
+      <x:c r="A126" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B126" s="19" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C126" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D126" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E126" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F126" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G126" s="21" t="n">
+        <x:v>5.2069017909998365</x:v>
+      </x:c>
+      <x:c r="H126" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I126" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J126" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K126" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L126" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M126" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N126" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O126" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P126" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q126" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="17"/>
-      <x:c r="B127" s="17"/>
-      <x:c r="C127" s="17"/>
-      <x:c r="D127" s="17"/>
-      <x:c r="E127" s="17"/>
-      <x:c r="F127" s="22"/>
-      <x:c r="G127" s="23"/>
-      <x:c r="H127" s="17"/>
-      <x:c r="I127" s="17"/>
-      <x:c r="J127" s="17"/>
-      <x:c r="K127" s="17"/>
-      <x:c r="L127" s="17"/>
-      <x:c r="M127" s="17"/>
-      <x:c r="N127" s="17"/>
-      <x:c r="O127" s="17"/>
+      <x:c r="A127" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B127" s="19" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C127" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D127" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E127" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F127" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G127" s="21" t="n">
+        <x:v>5.22128829200301</x:v>
+      </x:c>
+      <x:c r="H127" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I127" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J127" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K127" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L127" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M127" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N127" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O127" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P127" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q127" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="17"/>
-      <x:c r="B128" s="17"/>
-      <x:c r="C128" s="17"/>
-      <x:c r="D128" s="17"/>
-      <x:c r="E128" s="17"/>
-      <x:c r="F128" s="22"/>
-      <x:c r="G128" s="23"/>
-      <x:c r="H128" s="17"/>
-      <x:c r="I128" s="17"/>
-      <x:c r="J128" s="17"/>
-      <x:c r="K128" s="17"/>
-      <x:c r="L128" s="17"/>
-      <x:c r="M128" s="17"/>
-      <x:c r="N128" s="17"/>
-      <x:c r="O128" s="17"/>
+      <x:c r="A128" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B128" s="19" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C128" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D128" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E128" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F128" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G128" s="21" t="n">
+        <x:v>5.2175958339976205</x:v>
+      </x:c>
+      <x:c r="H128" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I128" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J128" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K128" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L128" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M128" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N128" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O128" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P128" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q128" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="17"/>
-      <x:c r="B129" s="17"/>
-      <x:c r="C129" s="17"/>
-      <x:c r="D129" s="17"/>
-      <x:c r="E129" s="17"/>
-      <x:c r="F129" s="22"/>
-      <x:c r="G129" s="23"/>
-      <x:c r="H129" s="17"/>
-      <x:c r="I129" s="17"/>
-      <x:c r="J129" s="17"/>
-      <x:c r="K129" s="17"/>
-      <x:c r="L129" s="17"/>
-      <x:c r="M129" s="17"/>
-      <x:c r="N129" s="17"/>
-      <x:c r="O129" s="17"/>
+      <x:c r="A129" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B129" s="19" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C129" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D129" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E129" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F129" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G129" s="21" t="n">
+        <x:v>5.2166444579997915</x:v>
+      </x:c>
+      <x:c r="H129" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I129" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J129" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K129" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L129" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M129" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N129" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O129" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P129" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q129" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="17"/>
-      <x:c r="B130" s="17"/>
-      <x:c r="C130" s="17"/>
-      <x:c r="D130" s="17"/>
-      <x:c r="E130" s="17"/>
-      <x:c r="F130" s="22"/>
-      <x:c r="G130" s="23"/>
-      <x:c r="H130" s="17"/>
-      <x:c r="I130" s="17"/>
-      <x:c r="J130" s="17"/>
-      <x:c r="K130" s="17"/>
-      <x:c r="L130" s="17"/>
-      <x:c r="M130" s="17"/>
-      <x:c r="N130" s="17"/>
-      <x:c r="O130" s="17"/>
+      <x:c r="A130" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B130" s="19" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C130" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D130" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E130" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F130" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G130" s="21" t="n">
+        <x:v>5.210669833999418</x:v>
+      </x:c>
+      <x:c r="H130" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I130" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J130" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K130" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L130" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M130" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N130" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O130" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P130" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q130" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="17"/>
-      <x:c r="B131" s="17"/>
-      <x:c r="C131" s="17"/>
-      <x:c r="D131" s="17"/>
-      <x:c r="E131" s="17"/>
-      <x:c r="F131" s="22"/>
-      <x:c r="G131" s="23"/>
-      <x:c r="H131" s="17"/>
-      <x:c r="I131" s="17"/>
-      <x:c r="J131" s="17"/>
-      <x:c r="K131" s="17"/>
-      <x:c r="L131" s="17"/>
-      <x:c r="M131" s="17"/>
-      <x:c r="N131" s="17"/>
-      <x:c r="O131" s="17"/>
+      <x:c r="A131" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B131" s="19" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C131" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D131" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E131" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F131" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G131" s="21" t="n">
+        <x:v>5.2113132500016945</x:v>
+      </x:c>
+      <x:c r="H131" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I131" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J131" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K131" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L131" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M131" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N131" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O131" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P131" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q131" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="17"/>
-      <x:c r="B132" s="17"/>
-      <x:c r="C132" s="17"/>
-      <x:c r="D132" s="17"/>
-      <x:c r="E132" s="17"/>
-      <x:c r="F132" s="22"/>
-      <x:c r="G132" s="23"/>
-      <x:c r="H132" s="17"/>
-      <x:c r="I132" s="17"/>
-      <x:c r="J132" s="17"/>
-      <x:c r="K132" s="17"/>
-      <x:c r="L132" s="17"/>
-      <x:c r="M132" s="17"/>
-      <x:c r="N132" s="17"/>
-      <x:c r="O132" s="17"/>
+      <x:c r="A132" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B132" s="19" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C132" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D132" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E132" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F132" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G132" s="21" t="n">
+        <x:v>5.214321542000107</x:v>
+      </x:c>
+      <x:c r="H132" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I132" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J132" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K132" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L132" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M132" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N132" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O132" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P132" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q132" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="17"/>
-      <x:c r="B133" s="17"/>
-      <x:c r="C133" s="17"/>
-      <x:c r="D133" s="17"/>
-      <x:c r="E133" s="17"/>
-      <x:c r="F133" s="22"/>
-      <x:c r="G133" s="23"/>
-      <x:c r="H133" s="17"/>
-      <x:c r="I133" s="17"/>
-      <x:c r="J133" s="17"/>
-      <x:c r="K133" s="17"/>
-      <x:c r="L133" s="17"/>
-      <x:c r="M133" s="17"/>
-      <x:c r="N133" s="17"/>
-      <x:c r="O133" s="17"/>
+      <x:c r="A133" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B133" s="19" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C133" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D133" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E133" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F133" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G133" s="21" t="n">
+        <x:v>5.216254916998878</x:v>
+      </x:c>
+      <x:c r="H133" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I133" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J133" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K133" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L133" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M133" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N133" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O133" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P133" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q133" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="17"/>
-      <x:c r="B134" s="17"/>
-      <x:c r="C134" s="17"/>
-      <x:c r="D134" s="17"/>
-      <x:c r="E134" s="17"/>
-      <x:c r="F134" s="22"/>
-      <x:c r="G134" s="23"/>
-      <x:c r="H134" s="17"/>
-      <x:c r="I134" s="17"/>
-      <x:c r="J134" s="17"/>
-      <x:c r="K134" s="17"/>
-      <x:c r="L134" s="17"/>
-      <x:c r="M134" s="17"/>
-      <x:c r="N134" s="17"/>
-      <x:c r="O134" s="17"/>
+      <x:c r="A134" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B134" s="19" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C134" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D134" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E134" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F134" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G134" s="21" t="n">
+        <x:v>5.210024667001562</x:v>
+      </x:c>
+      <x:c r="H134" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I134" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J134" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K134" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L134" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M134" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N134" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O134" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P134" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q134" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="17"/>
-      <x:c r="B135" s="17"/>
-      <x:c r="C135" s="17"/>
-      <x:c r="D135" s="17"/>
-      <x:c r="E135" s="17"/>
-      <x:c r="F135" s="22"/>
-      <x:c r="G135" s="23"/>
-      <x:c r="H135" s="17"/>
-      <x:c r="I135" s="17"/>
-      <x:c r="J135" s="17"/>
-      <x:c r="K135" s="17"/>
-      <x:c r="L135" s="17"/>
-      <x:c r="M135" s="17"/>
-      <x:c r="N135" s="17"/>
-      <x:c r="O135" s="17"/>
+      <x:c r="A135" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B135" s="19" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C135" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D135" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E135" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F135" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G135" s="21" t="n">
+        <x:v>5.311519499999122</x:v>
+      </x:c>
+      <x:c r="H135" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I135" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J135" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K135" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L135" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M135" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N135" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O135" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P135" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q135" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="17"/>
-      <x:c r="B136" s="17"/>
-      <x:c r="C136" s="17"/>
-      <x:c r="D136" s="17"/>
-      <x:c r="E136" s="17"/>
-      <x:c r="F136" s="22"/>
-      <x:c r="G136" s="23"/>
-      <x:c r="H136" s="17"/>
-      <x:c r="I136" s="17"/>
-      <x:c r="J136" s="17"/>
-      <x:c r="K136" s="17"/>
-      <x:c r="L136" s="17"/>
-      <x:c r="M136" s="17"/>
-      <x:c r="N136" s="17"/>
-      <x:c r="O136" s="17"/>
+      <x:c r="A136" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B136" s="19" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C136" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D136" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E136" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F136" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G136" s="21" t="n">
+        <x:v>5.369228542000201</x:v>
+      </x:c>
+      <x:c r="H136" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I136" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J136" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K136" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L136" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M136" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N136" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O136" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P136" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q136" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="17"/>
-      <x:c r="B137" s="17"/>
-      <x:c r="C137" s="17"/>
-      <x:c r="D137" s="17"/>
-      <x:c r="E137" s="17"/>
-      <x:c r="F137" s="22"/>
-      <x:c r="G137" s="23"/>
-      <x:c r="H137" s="17"/>
-      <x:c r="I137" s="17"/>
-      <x:c r="J137" s="17"/>
-      <x:c r="K137" s="17"/>
-      <x:c r="L137" s="17"/>
-      <x:c r="M137" s="17"/>
-      <x:c r="N137" s="17"/>
-      <x:c r="O137" s="17"/>
+      <x:c r="A137" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B137" s="19" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C137" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D137" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E137" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F137" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G137" s="21" t="n">
+        <x:v>5.225958667000668</x:v>
+      </x:c>
+      <x:c r="H137" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I137" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J137" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K137" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L137" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M137" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N137" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O137" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P137" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q137" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="17"/>
-      <x:c r="B138" s="17"/>
-      <x:c r="C138" s="17"/>
-      <x:c r="D138" s="17"/>
-      <x:c r="E138" s="17"/>
-      <x:c r="F138" s="22"/>
-      <x:c r="G138" s="23"/>
-      <x:c r="H138" s="17"/>
-      <x:c r="I138" s="17"/>
-      <x:c r="J138" s="17"/>
-      <x:c r="K138" s="17"/>
-      <x:c r="L138" s="17"/>
-      <x:c r="M138" s="17"/>
-      <x:c r="N138" s="17"/>
-      <x:c r="O138" s="17"/>
+      <x:c r="A138" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B138" s="19" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C138" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D138" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E138" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F138" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G138" s="21" t="n">
+        <x:v>5.758427124997979</x:v>
+      </x:c>
+      <x:c r="H138" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I138" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J138" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K138" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L138" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M138" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N138" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O138" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P138" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q138" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="17"/>
-      <x:c r="B139" s="17"/>
-      <x:c r="C139" s="17"/>
-      <x:c r="D139" s="17"/>
-      <x:c r="E139" s="17"/>
-      <x:c r="F139" s="22"/>
-      <x:c r="G139" s="23"/>
-      <x:c r="H139" s="17"/>
-      <x:c r="I139" s="17"/>
-      <x:c r="J139" s="17"/>
-      <x:c r="K139" s="17"/>
-      <x:c r="L139" s="17"/>
-      <x:c r="M139" s="17"/>
-      <x:c r="N139" s="17"/>
-      <x:c r="O139" s="17"/>
+      <x:c r="A139" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B139" s="19" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C139" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D139" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E139" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F139" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G139" s="21" t="n">
+        <x:v>5.727142167001148</x:v>
+      </x:c>
+      <x:c r="H139" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I139" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J139" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K139" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L139" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M139" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N139" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O139" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P139" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q139" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="17"/>
-      <x:c r="B140" s="17"/>
-      <x:c r="C140" s="17"/>
-      <x:c r="D140" s="17"/>
-      <x:c r="E140" s="17"/>
-      <x:c r="F140" s="22"/>
-      <x:c r="G140" s="23"/>
-      <x:c r="H140" s="17"/>
-      <x:c r="I140" s="17"/>
-      <x:c r="J140" s="17"/>
-      <x:c r="K140" s="17"/>
-      <x:c r="L140" s="17"/>
-      <x:c r="M140" s="17"/>
-      <x:c r="N140" s="17"/>
-      <x:c r="O140" s="17"/>
+      <x:c r="A140" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B140" s="19" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C140" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D140" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E140" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F140" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G140" s="21" t="n">
+        <x:v>5.941191124999023</x:v>
+      </x:c>
+      <x:c r="H140" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I140" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J140" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K140" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L140" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M140" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N140" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O140" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P140" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q140" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="17"/>
-      <x:c r="B141" s="17"/>
-      <x:c r="C141" s="17"/>
-      <x:c r="D141" s="17"/>
-      <x:c r="E141" s="17"/>
-      <x:c r="F141" s="22"/>
-      <x:c r="G141" s="23"/>
-      <x:c r="H141" s="17"/>
-      <x:c r="I141" s="17"/>
-      <x:c r="J141" s="17"/>
-      <x:c r="K141" s="17"/>
-      <x:c r="L141" s="17"/>
-      <x:c r="M141" s="17"/>
-      <x:c r="N141" s="17"/>
-      <x:c r="O141" s="17"/>
+      <x:c r="A141" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B141" s="19" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C141" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D141" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E141" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F141" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G141" s="21" t="n">
+        <x:v>5.705029916000058</x:v>
+      </x:c>
+      <x:c r="H141" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I141" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J141" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K141" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L141" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M141" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N141" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O141" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P141" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q141" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="17"/>
-      <x:c r="B142" s="17"/>
-      <x:c r="C142" s="17"/>
-      <x:c r="D142" s="17"/>
-      <x:c r="E142" s="17"/>
-      <x:c r="F142" s="22"/>
-      <x:c r="G142" s="23"/>
-      <x:c r="H142" s="17"/>
-      <x:c r="I142" s="17"/>
-      <x:c r="J142" s="17"/>
-      <x:c r="K142" s="17"/>
-      <x:c r="L142" s="17"/>
-      <x:c r="M142" s="17"/>
-      <x:c r="N142" s="17"/>
-      <x:c r="O142" s="17"/>
+      <x:c r="A142" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B142" s="19" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C142" s="19" t="str">
+        <x:v>HRM H=1 blend=0.2</x:v>
+      </x:c>
+      <x:c r="D142" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E142" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F142" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G142" s="21" t="n">
+        <x:v>5.569942042002367</x:v>
+      </x:c>
+      <x:c r="H142" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I142" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J142" s="19" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K142" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L142" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M142" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N142" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O142" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P142" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q142" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="17"/>
-      <x:c r="B143" s="17"/>
-      <x:c r="C143" s="17"/>
-      <x:c r="D143" s="17"/>
-      <x:c r="E143" s="17"/>
-      <x:c r="F143" s="22"/>
-      <x:c r="G143" s="23"/>
-      <x:c r="H143" s="17"/>
-      <x:c r="I143" s="17"/>
-      <x:c r="J143" s="17"/>
-      <x:c r="K143" s="17"/>
-      <x:c r="L143" s="17"/>
-      <x:c r="M143" s="17"/>
-      <x:c r="N143" s="17"/>
-      <x:c r="O143" s="17"/>
+      <x:c r="A143" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B143" s="19" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C143" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D143" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E143" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F143" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G143" s="21" t="n">
+        <x:v>5.619275874996674</x:v>
+      </x:c>
+      <x:c r="H143" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I143" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J143" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K143" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L143" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M143" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N143" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O143" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P143" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q143" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="17"/>
-      <x:c r="B144" s="17"/>
-      <x:c r="C144" s="17"/>
-      <x:c r="D144" s="17"/>
-      <x:c r="E144" s="17"/>
-      <x:c r="F144" s="22"/>
-      <x:c r="G144" s="23"/>
-      <x:c r="H144" s="17"/>
-      <x:c r="I144" s="17"/>
-      <x:c r="J144" s="17"/>
-      <x:c r="K144" s="17"/>
-      <x:c r="L144" s="17"/>
-      <x:c r="M144" s="17"/>
-      <x:c r="N144" s="17"/>
-      <x:c r="O144" s="17"/>
+      <x:c r="A144" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B144" s="19" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C144" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D144" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E144" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F144" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G144" s="21" t="n">
+        <x:v>5.611761957999988</x:v>
+      </x:c>
+      <x:c r="H144" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I144" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J144" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K144" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L144" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M144" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N144" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O144" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P144" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q144" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="17"/>
-      <x:c r="B145" s="17"/>
-      <x:c r="C145" s="17"/>
-      <x:c r="D145" s="17"/>
-      <x:c r="E145" s="17"/>
-      <x:c r="F145" s="22"/>
-      <x:c r="G145" s="23"/>
-      <x:c r="H145" s="17"/>
-      <x:c r="I145" s="17"/>
-      <x:c r="J145" s="17"/>
-      <x:c r="K145" s="17"/>
-      <x:c r="L145" s="17"/>
-      <x:c r="M145" s="17"/>
-      <x:c r="N145" s="17"/>
-      <x:c r="O145" s="17"/>
+      <x:c r="A145" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B145" s="19" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C145" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D145" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E145" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F145" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G145" s="21" t="n">
+        <x:v>5.501682291000179</x:v>
+      </x:c>
+      <x:c r="H145" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I145" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J145" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K145" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L145" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M145" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N145" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O145" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P145" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q145" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="17"/>
-      <x:c r="B146" s="17"/>
-      <x:c r="C146" s="17"/>
-      <x:c r="D146" s="17"/>
-      <x:c r="E146" s="17"/>
-      <x:c r="F146" s="22"/>
-      <x:c r="G146" s="23"/>
-      <x:c r="H146" s="17"/>
-      <x:c r="I146" s="17"/>
-      <x:c r="J146" s="17"/>
-      <x:c r="K146" s="17"/>
-      <x:c r="L146" s="17"/>
-      <x:c r="M146" s="17"/>
-      <x:c r="N146" s="17"/>
-      <x:c r="O146" s="17"/>
+      <x:c r="A146" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B146" s="19" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C146" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D146" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E146" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F146" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G146" s="21" t="n">
+        <x:v>5.488123500002985</x:v>
+      </x:c>
+      <x:c r="H146" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I146" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J146" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K146" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L146" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M146" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N146" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O146" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P146" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q146" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="17"/>
-      <x:c r="B147" s="17"/>
-      <x:c r="C147" s="17"/>
-      <x:c r="D147" s="17"/>
-      <x:c r="E147" s="17"/>
-      <x:c r="F147" s="22"/>
-      <x:c r="G147" s="23"/>
-      <x:c r="H147" s="17"/>
-      <x:c r="I147" s="17"/>
-      <x:c r="J147" s="17"/>
-      <x:c r="K147" s="17"/>
-      <x:c r="L147" s="17"/>
-      <x:c r="M147" s="17"/>
-      <x:c r="N147" s="17"/>
-      <x:c r="O147" s="17"/>
+      <x:c r="A147" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B147" s="19" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C147" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D147" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E147" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F147" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G147" s="21" t="n">
+        <x:v>5.673213583999313</x:v>
+      </x:c>
+      <x:c r="H147" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I147" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J147" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K147" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L147" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M147" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N147" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O147" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P147" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q147" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="17"/>
-      <x:c r="B148" s="17"/>
-      <x:c r="C148" s="17"/>
-      <x:c r="D148" s="17"/>
-      <x:c r="E148" s="17"/>
-      <x:c r="F148" s="22"/>
-      <x:c r="G148" s="23"/>
-      <x:c r="H148" s="17"/>
-      <x:c r="I148" s="17"/>
-      <x:c r="J148" s="17"/>
-      <x:c r="K148" s="17"/>
-      <x:c r="L148" s="17"/>
-      <x:c r="M148" s="17"/>
-      <x:c r="N148" s="17"/>
-      <x:c r="O148" s="17"/>
+      <x:c r="A148" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B148" s="19" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C148" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D148" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E148" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F148" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G148" s="21" t="n">
+        <x:v>5.559646500001691</x:v>
+      </x:c>
+      <x:c r="H148" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I148" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J148" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K148" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="L148" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M148" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N148" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O148" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P148" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q148" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="17"/>
-      <x:c r="B149" s="17"/>
-      <x:c r="C149" s="17"/>
-      <x:c r="D149" s="17"/>
-      <x:c r="E149" s="17"/>
-      <x:c r="F149" s="22"/>
-      <x:c r="G149" s="23"/>
-      <x:c r="H149" s="17"/>
-      <x:c r="I149" s="17"/>
-      <x:c r="J149" s="17"/>
-      <x:c r="K149" s="17"/>
-      <x:c r="L149" s="17"/>
-      <x:c r="M149" s="17"/>
-      <x:c r="N149" s="17"/>
-      <x:c r="O149" s="17"/>
+      <x:c r="A149" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B149" s="19" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C149" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D149" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E149" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F149" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G149" s="21" t="n">
+        <x:v>5.297865625001577</x:v>
+      </x:c>
+      <x:c r="H149" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I149" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J149" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K149" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L149" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M149" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N149" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O149" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P149" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q149" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="17"/>
-      <x:c r="B150" s="17"/>
-      <x:c r="C150" s="17"/>
-      <x:c r="D150" s="17"/>
-      <x:c r="E150" s="17"/>
-      <x:c r="F150" s="22"/>
-      <x:c r="G150" s="23"/>
-      <x:c r="H150" s="17"/>
-      <x:c r="I150" s="17"/>
-      <x:c r="J150" s="17"/>
-      <x:c r="K150" s="17"/>
-      <x:c r="L150" s="17"/>
-      <x:c r="M150" s="17"/>
-      <x:c r="N150" s="17"/>
-      <x:c r="O150" s="17"/>
+      <x:c r="A150" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B150" s="19" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C150" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D150" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E150" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F150" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G150" s="21" t="n">
+        <x:v>5.205257875000825</x:v>
+      </x:c>
+      <x:c r="H150" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I150" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J150" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K150" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L150" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M150" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N150" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O150" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P150" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q150" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="17"/>
-      <x:c r="B151" s="17"/>
-      <x:c r="C151" s="17"/>
-      <x:c r="D151" s="17"/>
-      <x:c r="E151" s="17"/>
-      <x:c r="F151" s="22"/>
-      <x:c r="G151" s="23"/>
-      <x:c r="H151" s="17"/>
-      <x:c r="I151" s="17"/>
-      <x:c r="J151" s="17"/>
-      <x:c r="K151" s="17"/>
-      <x:c r="L151" s="17"/>
-      <x:c r="M151" s="17"/>
-      <x:c r="N151" s="17"/>
-      <x:c r="O151" s="17"/>
+      <x:c r="A151" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B151" s="19" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C151" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D151" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E151" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F151" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G151" s="21" t="n">
+        <x:v>5.214359666999371</x:v>
+      </x:c>
+      <x:c r="H151" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I151" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J151" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K151" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L151" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M151" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N151" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O151" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P151" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q151" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="17"/>
-      <x:c r="B152" s="17"/>
-      <x:c r="C152" s="17"/>
-      <x:c r="D152" s="17"/>
-      <x:c r="E152" s="17"/>
-      <x:c r="F152" s="22"/>
-      <x:c r="G152" s="23"/>
-      <x:c r="H152" s="17"/>
-      <x:c r="I152" s="17"/>
-      <x:c r="J152" s="17"/>
-      <x:c r="K152" s="17"/>
-      <x:c r="L152" s="17"/>
-      <x:c r="M152" s="17"/>
-      <x:c r="N152" s="17"/>
-      <x:c r="O152" s="17"/>
+      <x:c r="A152" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B152" s="19" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C152" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D152" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E152" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F152" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G152" s="21" t="n">
+        <x:v>5.22666795799887</x:v>
+      </x:c>
+      <x:c r="H152" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I152" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J152" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K152" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L152" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M152" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N152" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O152" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P152" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q152" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="17"/>
-      <x:c r="B153" s="17"/>
-      <x:c r="C153" s="17"/>
-      <x:c r="D153" s="17"/>
-      <x:c r="E153" s="17"/>
-      <x:c r="F153" s="22"/>
-      <x:c r="G153" s="23"/>
-      <x:c r="H153" s="17"/>
-      <x:c r="I153" s="17"/>
-      <x:c r="J153" s="17"/>
-      <x:c r="K153" s="17"/>
-      <x:c r="L153" s="17"/>
-      <x:c r="M153" s="17"/>
-      <x:c r="N153" s="17"/>
-      <x:c r="O153" s="17"/>
+      <x:c r="A153" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B153" s="19" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C153" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D153" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E153" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F153" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G153" s="21" t="n">
+        <x:v>5.246614832998603</x:v>
+      </x:c>
+      <x:c r="H153" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I153" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J153" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K153" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L153" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M153" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N153" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O153" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P153" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q153" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="17"/>
-      <x:c r="B154" s="17"/>
-      <x:c r="C154" s="17"/>
-      <x:c r="D154" s="17"/>
-      <x:c r="E154" s="17"/>
-      <x:c r="F154" s="22"/>
-      <x:c r="G154" s="23"/>
-      <x:c r="H154" s="17"/>
-      <x:c r="I154" s="17"/>
-      <x:c r="J154" s="17"/>
-      <x:c r="K154" s="17"/>
-      <x:c r="L154" s="17"/>
-      <x:c r="M154" s="17"/>
-      <x:c r="N154" s="17"/>
-      <x:c r="O154" s="17"/>
+      <x:c r="A154" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B154" s="19" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C154" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D154" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E154" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F154" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G154" s="21" t="n">
+        <x:v>5.200734999998531</x:v>
+      </x:c>
+      <x:c r="H154" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I154" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J154" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K154" s="19" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="L154" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M154" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N154" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O154" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P154" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q154" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="17"/>
-      <x:c r="B155" s="17"/>
-      <x:c r="C155" s="17"/>
-      <x:c r="D155" s="17"/>
-      <x:c r="E155" s="17"/>
-      <x:c r="F155" s="22"/>
-      <x:c r="G155" s="23"/>
-      <x:c r="H155" s="17"/>
-      <x:c r="I155" s="17"/>
-      <x:c r="J155" s="17"/>
-      <x:c r="K155" s="17"/>
-      <x:c r="L155" s="17"/>
-      <x:c r="M155" s="17"/>
-      <x:c r="N155" s="17"/>
-      <x:c r="O155" s="17"/>
+      <x:c r="A155" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B155" s="19" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C155" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D155" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E155" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F155" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G155" s="21" t="n">
+        <x:v>5.213806499999919</x:v>
+      </x:c>
+      <x:c r="H155" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I155" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J155" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K155" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L155" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M155" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N155" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O155" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P155" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q155" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="17"/>
-      <x:c r="B156" s="17"/>
-      <x:c r="C156" s="17"/>
-      <x:c r="D156" s="17"/>
-      <x:c r="E156" s="17"/>
-      <x:c r="F156" s="22"/>
-      <x:c r="G156" s="23"/>
-      <x:c r="H156" s="17"/>
-      <x:c r="I156" s="17"/>
-      <x:c r="J156" s="17"/>
-      <x:c r="K156" s="17"/>
-      <x:c r="L156" s="17"/>
-      <x:c r="M156" s="17"/>
-      <x:c r="N156" s="17"/>
-      <x:c r="O156" s="17"/>
+      <x:c r="A156" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B156" s="19" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C156" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D156" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E156" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F156" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G156" s="21" t="n">
+        <x:v>5.207577291002963</x:v>
+      </x:c>
+      <x:c r="H156" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I156" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J156" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K156" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L156" s="19" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="M156" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N156" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O156" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P156" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q156" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="17"/>
-      <x:c r="B157" s="17"/>
-      <x:c r="C157" s="17"/>
-      <x:c r="D157" s="17"/>
-      <x:c r="E157" s="17"/>
-      <x:c r="F157" s="22"/>
-      <x:c r="G157" s="23"/>
-      <x:c r="H157" s="17"/>
-      <x:c r="I157" s="17"/>
-      <x:c r="J157" s="17"/>
-      <x:c r="K157" s="17"/>
-      <x:c r="L157" s="17"/>
-      <x:c r="M157" s="17"/>
-      <x:c r="N157" s="17"/>
-      <x:c r="O157" s="17"/>
+      <x:c r="A157" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B157" s="19" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C157" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D157" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E157" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F157" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G157" s="21" t="n">
+        <x:v>5.431209250000393</x:v>
+      </x:c>
+      <x:c r="H157" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I157" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J157" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K157" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L157" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M157" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N157" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O157" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P157" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q157" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="17"/>
-      <x:c r="B158" s="17"/>
-      <x:c r="C158" s="17"/>
-      <x:c r="D158" s="17"/>
-      <x:c r="E158" s="17"/>
-      <x:c r="F158" s="22"/>
-      <x:c r="G158" s="23"/>
-      <x:c r="H158" s="17"/>
-      <x:c r="I158" s="17"/>
-      <x:c r="J158" s="17"/>
-      <x:c r="K158" s="17"/>
-      <x:c r="L158" s="17"/>
-      <x:c r="M158" s="17"/>
-      <x:c r="N158" s="17"/>
-      <x:c r="O158" s="17"/>
+      <x:c r="A158" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B158" s="19" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C158" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D158" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E158" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F158" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G158" s="21" t="n">
+        <x:v>5.442251917000249</x:v>
+      </x:c>
+      <x:c r="H158" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I158" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J158" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K158" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L158" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="M158" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N158" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O158" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P158" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q158" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="17"/>
-      <x:c r="B159" s="17"/>
-      <x:c r="C159" s="17"/>
-      <x:c r="D159" s="17"/>
-      <x:c r="E159" s="17"/>
-      <x:c r="F159" s="22"/>
-      <x:c r="G159" s="23"/>
-      <x:c r="H159" s="17"/>
-      <x:c r="I159" s="17"/>
-      <x:c r="J159" s="17"/>
-      <x:c r="K159" s="17"/>
-      <x:c r="L159" s="17"/>
-      <x:c r="M159" s="17"/>
-      <x:c r="N159" s="17"/>
-      <x:c r="O159" s="17"/>
+      <x:c r="A159" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B159" s="19" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C159" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D159" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E159" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F159" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G159" s="21" t="n">
+        <x:v>5.435296165996988</x:v>
+      </x:c>
+      <x:c r="H159" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I159" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J159" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K159" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L159" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M159" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N159" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O159" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P159" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q159" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="17"/>
-      <x:c r="B160" s="17"/>
-      <x:c r="C160" s="17"/>
-      <x:c r="D160" s="17"/>
-      <x:c r="E160" s="17"/>
-      <x:c r="F160" s="22"/>
-      <x:c r="G160" s="23"/>
-      <x:c r="H160" s="17"/>
-      <x:c r="I160" s="17"/>
-      <x:c r="J160" s="17"/>
-      <x:c r="K160" s="17"/>
-      <x:c r="L160" s="17"/>
-      <x:c r="M160" s="17"/>
-      <x:c r="N160" s="17"/>
-      <x:c r="O160" s="17"/>
+      <x:c r="A160" s="19" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B160" s="19" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C160" s="19" t="str">
+        <x:v>HRM H=1 blend=0.24</x:v>
+      </x:c>
+      <x:c r="D160" s="19" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E160" s="19" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F160" s="20" t="n">
+        <x:v>0.6470588235294118</x:v>
+      </x:c>
+      <x:c r="G160" s="21" t="n">
+        <x:v>5.634808875001909</x:v>
+      </x:c>
+      <x:c r="H160" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I160" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J160" s="19" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="K160" s="19" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L160" s="19" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="M160" s="19" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="N160" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O160" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P160" s="10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q160" s="10" t="str">
+        <x:v>sweep_qwen3_1_7b_split10_tight.csv</x:v>
+      </x:c>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="17"/>
@@ -18895,7 +22398,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.670000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="89.81999969482422" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="96.19999694824219" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -18942,10 +22445,10 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="25" t="str">
-        <x:v>Current win</x:v>
+        <x:v>Current wins</x:v>
       </x:c>
       <x:c r="B3" s="25" t="str">
-        <x:v>Qwen3-0.6B-4bit improves from 5/17 to 7/17 with H=1, L=1, blend=0.2, alpha_l=0.03, alpha_h=0.05, beta=0.01.</x:v>
+        <x:v>Qwen3-0.6B-4bit improves from 5/17 to 7/17 with split 14; Qwen3-1.7B-4bit improves from 10/17 to 11/17 with split 10.</x:v>
       </x:c>
       <x:c r="C3" s="17"/>
       <x:c r="D3" s="17"/>
@@ -18963,10 +22466,10 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="25" t="str">
-        <x:v>No win</x:v>
+        <x:v>Split finding</x:v>
       </x:c>
       <x:c r="B4" s="25" t="str">
-        <x:v>Qwen3-1.7B-4bit remains 10/17 under the same setting; HRM changes margins but not accuracy.</x:v>
+        <x:v>The symmetric 14/14 split is best for 0.6B; an earlier split at 10 lower layers is best for 1.7B on the corrected probe.</x:v>
       </x:c>
       <x:c r="C4" s="17"/>
       <x:c r="D4" s="17"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R489b153ed78248b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R5fff4c1c869645d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R5a78dbad18044a85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rba35bacd1ac04cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="Ref627b9935584f11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R8974cf3ece8046ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R258aeff5b1f94c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9f695a055fe4498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R0050cb5734004c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="Rbd34d2c65ec84487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rfd55c807e1f64c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R5fef01b4fb294ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R759d8ba4148941c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R78b7baacc6a643b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -666,13 +666,13 @@
         <x:v>Base</x:v>
       </x:c>
       <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="34" t="n">
-        <x:v>0.23529411764705882</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F12" s="33" t="n">
         <x:v>0</x:v>
@@ -701,16 +701,16 @@
         <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="34" t="n">
-        <x:v>0.29411764705882354</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F13" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G13" s="35" t="n">
         <x:v>27.241536667996115</x:v>
@@ -736,20 +736,20 @@
         <x:v>HRM-Text</x:v>
       </x:c>
       <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D14" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="34" t="n">
-        <x:v>0.17647058823529413</x:v>
+        <x:v>0.9411764705882353</x:v>
       </x:c>
       <x:c r="F14" s="33" t="str"/>
       <x:c r="G14" s="35" t="n">
-        <x:v>39.10392216801483</x:v>
+        <x:v>104.68802758599998</x:v>
       </x:c>
       <x:c r="H14" s="35" t="n">
-        <x:v>2.3002307157655784</x:v>
+        <x:v>6.158119269764704</x:v>
       </x:c>
       <x:c r="I14" s="31"/>
       <x:c r="J14" s="31"/>
@@ -769,20 +769,20 @@
         <x:v>HRM-Text</x:v>
       </x:c>
       <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D15" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="34" t="n">
-        <x:v>0.058823529411764705</x:v>
+        <x:v>0.9411764705882353</x:v>
       </x:c>
       <x:c r="F15" s="33" t="str"/>
       <x:c r="G15" s="35" t="n">
-        <x:v>84.48929779399987</x:v>
+        <x:v>338.2124144539998</x:v>
       </x:c>
       <x:c r="H15" s="35" t="n">
-        <x:v>4.969958693764698</x:v>
+        <x:v>19.894847909058814</x:v>
       </x:c>
       <x:c r="I15" s="31"/>
       <x:c r="J15" s="31"/>
@@ -33854,8 +33854,8 @@
     <x:col min="5" max="5" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="37.90999984741211" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="23.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="141.47000122070312" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="31.65999984741211" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -33977,13 +33977,13 @@
         <x:v>Base</x:v>
       </x:c>
       <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E4" s="34" t="n">
-        <x:v>0.23529411764705882</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F4" s="35" t="n">
         <x:v>11.462043749994336</x:v>
@@ -33992,7 +33992,7 @@
         <x:v>0.6742378676467257</x:v>
       </x:c>
       <x:c r="H4" s="33" t="str">
-        <x:v>sequence, reverse_discount, average, coins</x:v>
+        <x:v>boxes, probability, sequence, reverse_discount, average, coins</x:v>
       </x:c>
       <x:c r="I4" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
@@ -34014,13 +34014,13 @@
         <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E5" s="34" t="n">
-        <x:v>0.29411764705882354</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F5" s="35" t="n">
         <x:v>27.241536667996115</x:v>
@@ -34029,7 +34029,7 @@
         <x:v>1.6024433334115362</x:v>
       </x:c>
       <x:c r="H5" s="33" t="str">
-        <x:v>markup, probability, sequence, rectangle, coins</x:v>
+        <x:v>markup, boxes, probability, sequence, rectangle, coins</x:v>
       </x:c>
       <x:c r="I5" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
@@ -34051,25 +34051,25 @@
         <x:v>HRM-Text</x:v>
       </x:c>
       <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="34" t="n">
-        <x:v>0.17647058823529413</x:v>
+        <x:v>0.9411764705882353</x:v>
       </x:c>
       <x:c r="F6" s="35" t="n">
-        <x:v>39.10392216801483</x:v>
+        <x:v>104.68802758599998</x:v>
       </x:c>
       <x:c r="G6" s="35" t="n">
-        <x:v>2.3002307157655784</x:v>
+        <x:v>6.158119269764704</x:v>
       </x:c>
       <x:c r="H6" s="33" t="str">
-        <x:v>sequence, average, modular_small</x:v>
+        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
       </x:c>
       <x:c r="I6" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="J6" s="31"/>
       <x:c r="K6" s="31"/>
@@ -34088,25 +34088,25 @@
         <x:v>HRM-Text</x:v>
       </x:c>
       <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D7" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="34" t="n">
-        <x:v>0.058823529411764705</x:v>
+        <x:v>0.9411764705882353</x:v>
       </x:c>
       <x:c r="F7" s="35" t="n">
-        <x:v>84.48929779399987</x:v>
+        <x:v>338.2124144539998</x:v>
       </x:c>
       <x:c r="G7" s="35" t="n">
-        <x:v>4.969958693764698</x:v>
+        <x:v>19.894847909058814</x:v>
       </x:c>
       <x:c r="H7" s="33" t="str">
-        <x:v>syllogism</x:v>
+        <x:v>algebra, markup, boxes, inclusion, modular, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, syllogism</x:v>
       </x:c>
       <x:c r="I7" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="J7" s="31"/>
       <x:c r="K7" s="31"/>
@@ -39700,7 +39700,7 @@
     <x:col min="5" max="5" width="255" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31.65999984741211" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -39786,9 +39786,7 @@
       <x:c r="D3" s="33" t="str">
         <x:v>96|$96</x:v>
       </x:c>
-      <x:c r="E3" s="33" t="str">
-        <x:v>Hmm, let's break it down step by step. Let me think. When something is marked up by 25%, that means the original price is reduced by 25% of the original price. Wait, no, actually, when you mark up something, you're increasing its</x:v>
-      </x:c>
+      <x:c r="E3" s="33" t="str"/>
       <x:c r="F3" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
@@ -40555,7 +40553,7 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E25" s="33" t="str">
-        <x:v>'- 4: 4 + 4 = 8</x:v>
+        <x:v>\text{answer}</x:v>
       </x:c>
       <x:c r="F25" s="33" t="str">
         <x:v>False</x:v>
@@ -41013,7 +41011,7 @@
         <x:v>To determine which box to open, we need to figure out the correct labels based on the information given. Since all the labels are wrong, we can use the fact that the Mixed box is the only one that could have both apples and oranges. If we take one fruit from the Mixed box, we can determine if it's apples or oranges. If it's apples, then the Mixed box is actually apples, but since all labels are wrong, the Mixed box can't be correct. If it's oranges, then the Mixed box is actually oranges, but since all labels are wrong, the Mixed box can't be correct. Therefore,</x:v>
       </x:c>
       <x:c r="F38" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G38" s="35" t="n">
         <x:v>0.6743095830024686</x:v>
@@ -41153,7 +41151,7 @@
         <x:v>\boxed{\dfrac{1}{9}}.</x:v>
       </x:c>
       <x:c r="F42" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G42" s="35" t="n">
         <x:v>0.667745416998514</x:v>
@@ -41608,7 +41606,7 @@
         <x:v>Now, the "Mixed" box must have either apples</x:v>
       </x:c>
       <x:c r="F55" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G55" s="35" t="n">
         <x:v>1.6641501670019352</x:v>
@@ -42130,16 +42128,16 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E70" s="33" t="str">
-        <x:v>Step 4: Add 21 to both sides of the equation to isolate the</x:v>
+        <x:v>\dfrac{25}{2}</x:v>
       </x:c>
       <x:c r="F70" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G70" s="35" t="n">
-        <x:v>2.7778973340027733</x:v>
+        <x:v>7.580443959000007</x:v>
       </x:c>
       <x:c r="H70" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I70" s="31"/>
       <x:c r="J70" s="31"/>
@@ -42165,16 +42163,16 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E71" s="33" t="str">
-        <x:v>4. Calculate the product of 1.25 and 0.8</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F71" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G71" s="35" t="n">
-        <x:v>2.734651083999779</x:v>
+        <x:v>6.407860625000012</x:v>
       </x:c>
       <x:c r="H71" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I71" s="31"/>
       <x:c r="J71" s="31"/>
@@ -42200,16 +42198,16 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E72" s="33" t="str">
-        <x:v>your answer**</x:v>
+        <x:v>Mixed</x:v>
       </x:c>
       <x:c r="F72" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G72" s="35" t="n">
-        <x:v>2.5394804999996268</x:v>
+        <x:v>6.2715228750000165</x:v>
       </x:c>
       <x:c r="H72" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I72" s="31"/>
       <x:c r="J72" s="31"/>
@@ -42235,16 +42233,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E73" s="33" t="str">
-        <x:v>The largest multiple of 5 less than or equal to 200 is 200. So, the number of</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F73" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G73" s="35" t="n">
-        <x:v>2.6089392920002865</x:v>
+        <x:v>4.775222624999998</x:v>
       </x:c>
       <x:c r="H73" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I73" s="31"/>
       <x:c r="J73" s="31"/>
@@ -42270,16 +42268,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E74" s="33" t="str">
-        <x:v>7^6 ≡ 7 * 11 ≡ 7</x:v>
+        <x:v>'- \(7^8 \equiv 9^2</x:v>
       </x:c>
       <x:c r="F74" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
       <x:c r="G74" s="35" t="n">
-        <x:v>2.560868417000165</x:v>
+        <x:v>14.03727679100001</x:v>
       </x:c>
       <x:c r="H74" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I74" s="31"/>
       <x:c r="J74" s="31"/>
@@ -42305,16 +42303,16 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E75" s="33" t="str">
-        <x:v>\frac{1}{6} = \frac{5}{30} \quad \text{and} \</x:v>
+        <x:v>\dfrac{15}{4}</x:v>
       </x:c>
       <x:c r="F75" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G75" s="35" t="n">
-        <x:v>2.554322083000443</x:v>
+        <x:v>6.176148500000011</x:v>
       </x:c>
       <x:c r="H75" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I75" s="31"/>
       <x:c r="J75" s="31"/>
@@ -42340,16 +42338,16 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E76" s="33" t="str">
-        <x:v>your answer</x:v>
+        <x:v>\dfrac{1}{9}</x:v>
       </x:c>
       <x:c r="F76" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G76" s="35" t="n">
-        <x:v>1.3759969169987016</x:v>
+        <x:v>4.10938950000002</x:v>
       </x:c>
       <x:c r="H76" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I76" s="31"/>
       <x:c r="J76" s="31"/>
@@ -42381,10 +42379,10 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G77" s="35" t="n">
-        <x:v>2.2476258749993576</x:v>
+        <x:v>8.457965874999957</x:v>
       </x:c>
       <x:c r="H77" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I77" s="31"/>
       <x:c r="J77" s="31"/>
@@ -42410,16 +42408,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E78" s="33" t="str">
-        <x:v>2x &amp;= 31 - 9 \\</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F78" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G78" s="35" t="n">
-        <x:v>2.5328067080008623</x:v>
+        <x:v>4.77963704199999</x:v>
       </x:c>
       <x:c r="H78" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I78" s="31"/>
       <x:c r="J78" s="31"/>
@@ -42445,16 +42443,16 @@
         <x:v>80|$80</x:v>
       </x:c>
       <x:c r="E79" s="33" t="str">
-        <x:v>P = \frac{</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F79" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G79" s="35" t="n">
-        <x:v>2.9531720420018246</x:v>
+        <x:v>4.465110458999959</x:v>
       </x:c>
       <x:c r="H79" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I79" s="31"/>
       <x:c r="J79" s="31"/>
@@ -42480,16 +42478,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E80" s="33" t="str">
-        <x:v>The largest integer less than 100 that is divisible by</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F80" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G80" s="35" t="n">
-        <x:v>2.88598975000059</x:v>
+        <x:v>4.0312850840000465</x:v>
       </x:c>
       <x:c r="H80" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I80" s="31"/>
       <x:c r="J80" s="31"/>
@@ -42515,16 +42513,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E81" s="33" t="str">
-        <x:v>3. **Solve</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F81" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G81" s="35" t="n">
-        <x:v>2.7802965410010074</x:v>
+        <x:v>4.098184124999989</x:v>
       </x:c>
       <x:c r="H81" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I81" s="31"/>
       <x:c r="J81" s="31"/>
@@ -42556,10 +42554,10 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G82" s="35" t="n">
-        <x:v>2.5419051670032786</x:v>
+        <x:v>3.955258875000027</x:v>
       </x:c>
       <x:c r="H82" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I82" s="31"/>
       <x:c r="J82" s="31"/>
@@ -42585,16 +42583,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E83" s="33" t="str">
-        <x:v>= (6 × 5 × 4 × 3 × 2 × 1) / ((2 × 1)(4 × 3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F83" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G83" s="35" t="n">
-        <x:v>2.8596924170014972</x:v>
+        <x:v>6.499252583999976</x:v>
       </x:c>
       <x:c r="H83" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I83" s="31"/>
       <x:c r="J83" s="31"/>
@@ -42620,16 +42618,16 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E84" s="33" t="str">
-        <x:v>$\boxed{\frac{3}{8}}$</x:v>
+        <x:v>\dfrac{3}{8}</x:v>
       </x:c>
       <x:c r="F84" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G84" s="35" t="n">
-        <x:v>1.3579884579994541</x:v>
+        <x:v>2.2782300830000395</x:v>
       </x:c>
       <x:c r="H84" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I84" s="31"/>
       <x:c r="J84" s="31"/>
@@ -42661,10 +42659,10 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G85" s="35" t="n">
-        <x:v>1.2371588330024679</x:v>
+        <x:v>12.253404416999956</x:v>
       </x:c>
       <x:c r="H85" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I85" s="31"/>
       <x:c r="J85" s="31"/>
@@ -42690,16 +42688,16 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E86" s="33" t="str">
-        <x:v>your answer</x:v>
+        <x:v>Yes, all bloops must be lazzies.</x:v>
       </x:c>
       <x:c r="F86" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G86" s="35" t="n">
-        <x:v>0.5551307500027178</x:v>
+        <x:v>4.511834166999961</x:v>
       </x:c>
       <x:c r="H86" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit.csv</x:v>
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
       </x:c>
       <x:c r="I86" s="31"/>
       <x:c r="J86" s="31"/>
@@ -42725,16 +42723,16 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E87" s="33" t="str">
-        <x:v>Step 4: Add 21 to both sides of the equation to isolate</x:v>
+        <x:v>\dfrac{25}{2}</x:v>
       </x:c>
       <x:c r="F87" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G87" s="35" t="n">
-        <x:v>5.188138792000245</x:v>
+        <x:v>16.656210082999962</x:v>
       </x:c>
       <x:c r="H87" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I87" s="31"/>
       <x:c r="J87" s="31"/>
@@ -42760,16 +42758,16 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E88" s="33" t="str">
-        <x:v>4. Calculate the product of 1.25 and 0.8</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F88" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G88" s="35" t="n">
-        <x:v>5.103107375001855</x:v>
+        <x:v>12.64156225000005</x:v>
       </x:c>
       <x:c r="H88" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I88" s="31"/>
       <x:c r="J88" s="31"/>
@@ -42795,16 +42793,16 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E89" s="33" t="str">
-        <x:v>your answer**</x:v>
+        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
       </x:c>
       <x:c r="F89" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G89" s="35" t="n">
-        <x:v>4.371220457996969</x:v>
+        <x:v>19.97141316599999</x:v>
       </x:c>
       <x:c r="H89" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I89" s="31"/>
       <x:c r="J89" s="31"/>
@@ -42830,16 +42828,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E90" s="33" t="str">
-        <x:v>The largest integer less than or equal to 200 that is divisible by 5 is 200. So,</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F90" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G90" s="35" t="n">
-        <x:v>5.096478874998866</x:v>
+        <x:v>12.902716834000046</x:v>
       </x:c>
       <x:c r="H90" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I90" s="31"/>
       <x:c r="J90" s="31"/>
@@ -42865,16 +42863,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E91" s="33" t="str">
-        <x:v>\[ 7^{103} = 7^{12 \times</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F91" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G91" s="35" t="n">
-        <x:v>5.095068083999649</x:v>
+        <x:v>50.31506079099995</x:v>
       </x:c>
       <x:c r="H91" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I91" s="31"/>
       <x:c r="J91" s="31"/>
@@ -42900,16 +42898,16 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E92" s="33" t="str">
-        <x:v>\frac{1}{6} = \frac{5}{30} \quad \text{and} \quad \frac{1}{10} = \frac{3}{</x:v>
+        <x:v>3.75</x:v>
       </x:c>
       <x:c r="F92" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G92" s="35" t="n">
-        <x:v>5.09630420800022</x:v>
+        <x:v>33.462693083999966</x:v>
       </x:c>
       <x:c r="H92" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I92" s="31"/>
       <x:c r="J92" s="31"/>
@@ -42935,16 +42933,16 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E93" s="33" t="str">
-        <x:v>your answer</x:v>
+        <x:v>\dfrac{1}{9}</x:v>
       </x:c>
       <x:c r="F93" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G93" s="35" t="n">
-        <x:v>2.531712209001853</x:v>
+        <x:v>7.085368707999919</x:v>
       </x:c>
       <x:c r="H93" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I93" s="31"/>
       <x:c r="J93" s="31"/>
@@ -42970,16 +42968,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E94" s="33" t="str">
-        <x:v>So, a_4 = \</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F94" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G94" s="35" t="n">
-        <x:v>5.103402249998908</x:v>
+        <x:v>15.824353458000019</x:v>
       </x:c>
       <x:c r="H94" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I94" s="31"/>
       <x:c r="J94" s="31"/>
@@ -43005,16 +43003,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E95" s="33" t="str">
-        <x:v>2x &amp;= 22 \\</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F95" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G95" s="35" t="n">
-        <x:v>5.092639833997964</x:v>
+        <x:v>8.149854707999907</x:v>
       </x:c>
       <x:c r="H95" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I95" s="31"/>
       <x:c r="J95" s="31"/>
@@ -43040,16 +43038,16 @@
         <x:v>80|$80</x:v>
       </x:c>
       <x:c r="E96" s="33" t="str">
-        <x:v>Verification: A 10% discount on $80 is $8, so the discounted price is $80 - $8 = $72, which matches</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F96" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G96" s="35" t="n">
-        <x:v>5.0926331669979845</x:v>
+        <x:v>6.157211500000017</x:v>
       </x:c>
       <x:c r="H96" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I96" s="31"/>
       <x:c r="J96" s="31"/>
@@ -43075,16 +43073,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E97" s="33" t="str">
-        <x:v>The largest integer less than 100 that is divisible by</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F97" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G97" s="35" t="n">
-        <x:v>5.080499875002715</x:v>
+        <x:v>21.503388040999994</x:v>
       </x:c>
       <x:c r="H97" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I97" s="31"/>
       <x:c r="J97" s="31"/>
@@ -43110,16 +43108,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E98" s="33" t="str">
-        <x:v>3. **Solve</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F98" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G98" s="35" t="n">
-        <x:v>5.522503542000777</x:v>
+        <x:v>7.560139790999983</x:v>
       </x:c>
       <x:c r="H98" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I98" s="31"/>
       <x:c r="J98" s="31"/>
@@ -43145,16 +43143,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E99" s="33" t="str">
-        <x:v>Thus</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F99" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G99" s="35" t="n">
-        <x:v>5.390843000001041</x:v>
+        <x:v>8.231041165999955</x:v>
       </x:c>
       <x:c r="H99" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I99" s="31"/>
       <x:c r="J99" s="31"/>
@@ -43180,16 +43178,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E100" s="33" t="str">
-        <x:v>\[ 6! = 6 \times 5 \times</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F100" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G100" s="35" t="n">
-        <x:v>5.357839625001361</x:v>
+        <x:v>30.73365029099989</x:v>
       </x:c>
       <x:c r="H100" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I100" s="31"/>
       <x:c r="J100" s="31"/>
@@ -43215,16 +43213,16 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E101" s="33" t="str">
-        <x:v>There are 3 favorable outcomes. The probability is calculated by dividing the number of favorable outcomes by t</x:v>
+        <x:v>\dfrac{3}{8}</x:v>
       </x:c>
       <x:c r="F101" s="33" t="str">
-        <x:v>False</x:v>
+        <x:v>True</x:v>
       </x:c>
       <x:c r="G101" s="35" t="n">
-        <x:v>5.398683916999289</x:v>
+        <x:v>11.049620875000073</x:v>
       </x:c>
       <x:c r="H101" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I101" s="31"/>
       <x:c r="J101" s="31"/>
@@ -43250,16 +43248,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E102" s="33" t="str">
-        <x:v>\[ \</x:v>
+        <x:v>All methods confirm that the remainder when</x:v>
       </x:c>
       <x:c r="F102" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
       <x:c r="G102" s="35" t="n">
-        <x:v>5.481146750000335</x:v>
+        <x:v>67.06586500000003</x:v>
       </x:c>
       <x:c r="H102" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I102" s="31"/>
       <x:c r="J102" s="31"/>
@@ -43285,16 +43283,16 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E103" s="33" t="str">
-        <x:v>Final answer: yes</x:v>
+        <x:v>Yes, all bloops must be lazzies.</x:v>
       </x:c>
       <x:c r="F103" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="G103" s="35" t="n">
-        <x:v>4.487075832999835</x:v>
+        <x:v>8.902264708000075</x:v>
       </x:c>
       <x:c r="H103" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16.csv</x:v>
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
       <x:c r="I103" s="31"/>
       <x:c r="J103" s="31"/>
@@ -47059,7 +47057,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="125.5199966430664" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="150.17999267578125" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -47159,7 +47157,7 @@
         <x:v>Exact-answer probe</x:v>
       </x:c>
       <x:c r="B5" s="41" t="str">
-        <x:v>Added a stricter generative probe with exact extraction. Qwen3-0.6B moves from 1/17 base to 2/17 HRM; Qwen3-1.7B moves from 4/17 base to 5/17 HRM.</x:v>
+        <x:v>Added a stricter generative probe with exact extraction. Qwen3-0.6B moves from 1/17 base to 2/17 HRM; Qwen3-1.7B is 6/17 for both base and HRM after corrected text-answer scoring.</x:v>
       </x:c>
       <x:c r="C5" s="31"/>
       <x:c r="D5" s="31"/>
@@ -47182,7 +47180,7 @@
         <x:v>HRM-Text comparison</x:v>
       </x:c>
       <x:c r="B6" s="41" t="str">
-        <x:v>Local HRM-Text-1B scored 3/17 for 4-bit and 1/17 for BF16 on this exact prompt set; treat this as prompt-sensitive, not a definitive model ranking.</x:v>
+        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
       </x:c>
       <x:c r="C6" s="31"/>
       <x:c r="D6" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9f695a055fe4498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R0050cb5734004c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="Rbd34d2c65ec84487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rfd55c807e1f64c9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R5fef01b4fb294ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R759d8ba4148941c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R78b7baacc6a643b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R08085e55eaf64418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R5f17f2d6ec9942d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="Reea18092198148ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rdb45f27c4811498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R5261d6bffb54427c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R470a2b0611b84815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R115ebbfbe3f54a03"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -342,7 +342,7 @@
     <x:col min="6" max="6" width="11.65999984741211" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="41.599998474121094" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -578,7 +578,9 @@
       <x:c r="H9" s="39" t="str">
         <x:v>Avg Case s</x:v>
       </x:c>
-      <x:c r="I9" s="37"/>
+      <x:c r="I9" s="39" t="str">
+        <x:v>Source</x:v>
+      </x:c>
       <x:c r="J9" s="31"/>
       <x:c r="K9" s="31"/>
       <x:c r="L9" s="31"/>
@@ -613,7 +615,9 @@
       <x:c r="H10" s="35" t="n">
         <x:v>0.3888904019995072</x:v>
       </x:c>
-      <x:c r="I10" s="37"/>
+      <x:c r="I10" s="35" t="str">
+        <x:v>exact_qwen3_0_6b_base.csv</x:v>
+      </x:c>
       <x:c r="J10" s="31"/>
       <x:c r="K10" s="31"/>
       <x:c r="L10" s="31"/>
@@ -648,7 +652,9 @@
       <x:c r="H11" s="35" t="n">
         <x:v>0.877024556411711</x:v>
       </x:c>
-      <x:c r="I11" s="31"/>
+      <x:c r="I11" s="33" t="str">
+        <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
+      </x:c>
       <x:c r="J11" s="31"/>
       <x:c r="K11" s="31"/>
       <x:c r="L11" s="31"/>
@@ -683,7 +689,9 @@
       <x:c r="H12" s="35" t="n">
         <x:v>0.6742378676467257</x:v>
       </x:c>
-      <x:c r="I12" s="31"/>
+      <x:c r="I12" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base.csv</x:v>
+      </x:c>
       <x:c r="J12" s="31"/>
       <x:c r="K12" s="31"/>
       <x:c r="L12" s="31"/>
@@ -718,7 +726,9 @@
       <x:c r="H13" s="35" t="n">
         <x:v>1.6024433334115362</x:v>
       </x:c>
-      <x:c r="I13" s="31"/>
+      <x:c r="I13" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
+      </x:c>
       <x:c r="J13" s="31"/>
       <x:c r="K13" s="31"/>
       <x:c r="L13" s="31"/>
@@ -730,28 +740,32 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B14" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C14" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E14" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str"/>
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="F14" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G14" s="35" t="n">
-        <x:v>104.68802758599998</x:v>
+        <x:v>21.145844373000273</x:v>
       </x:c>
       <x:c r="H14" s="35" t="n">
-        <x:v>6.158119269764704</x:v>
-      </x:c>
-      <x:c r="I14" s="31"/>
+        <x:v>1.2438731984117808</x:v>
+      </x:c>
+      <x:c r="I14" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="J14" s="31"/>
       <x:c r="K14" s="31"/>
       <x:c r="L14" s="31"/>
@@ -763,28 +777,32 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B15" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C15" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D15" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
-      </x:c>
-      <x:c r="F15" s="33" t="str"/>
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="F15" s="33" t="n">
+        <x:v>-1</x:v>
+      </x:c>
       <x:c r="G15" s="35" t="n">
-        <x:v>338.2124144539998</x:v>
+        <x:v>54.02931174700029</x:v>
       </x:c>
       <x:c r="H15" s="35" t="n">
-        <x:v>19.894847909058814</x:v>
-      </x:c>
-      <x:c r="I15" s="31"/>
+        <x:v>3.178194808647076</x:v>
+      </x:c>
+      <x:c r="I15" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="J15" s="31"/>
       <x:c r="K15" s="31"/>
       <x:c r="L15" s="31"/>
@@ -795,15 +813,33 @@
       <x:c r="Q15" s="31"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="31"/>
-      <x:c r="B16" s="31"/>
-      <x:c r="C16" s="31"/>
-      <x:c r="D16" s="31"/>
-      <x:c r="E16" s="36"/>
-      <x:c r="F16" s="31"/>
-      <x:c r="G16" s="37"/>
-      <x:c r="H16" s="37"/>
-      <x:c r="I16" s="31"/>
+      <x:c r="A16" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B16" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="n">
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="F16" s="33" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="G16" s="35" t="n">
+        <x:v>53.94164416799936</x:v>
+      </x:c>
+      <x:c r="H16" s="35" t="n">
+        <x:v>3.1730378922352562</x:v>
+      </x:c>
+      <x:c r="I16" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="J16" s="31"/>
       <x:c r="K16" s="31"/>
       <x:c r="L16" s="31"/>
@@ -814,15 +850,33 @@
       <x:c r="Q16" s="31"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="31"/>
-      <x:c r="B17" s="31"/>
-      <x:c r="C17" s="31"/>
-      <x:c r="D17" s="31"/>
-      <x:c r="E17" s="36"/>
-      <x:c r="F17" s="31"/>
-      <x:c r="G17" s="37"/>
-      <x:c r="H17" s="37"/>
-      <x:c r="I17" s="31"/>
+      <x:c r="A17" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B17" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D17" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="34" t="n">
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="F17" s="33" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="G17" s="35" t="n">
+        <x:v>51.153985081999735</x:v>
+      </x:c>
+      <x:c r="H17" s="35" t="n">
+        <x:v>3.0090579459999844</x:v>
+      </x:c>
+      <x:c r="I17" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="J17" s="31"/>
       <x:c r="K17" s="31"/>
       <x:c r="L17" s="31"/>
@@ -833,15 +887,31 @@
       <x:c r="Q17" s="31"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="31"/>
-      <x:c r="B18" s="31"/>
-      <x:c r="C18" s="31"/>
-      <x:c r="D18" s="31"/>
-      <x:c r="E18" s="36"/>
-      <x:c r="F18" s="31"/>
-      <x:c r="G18" s="37"/>
-      <x:c r="H18" s="37"/>
-      <x:c r="I18" s="31"/>
+      <x:c r="A18" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B18" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C18" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D18" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F18" s="33" t="str"/>
+      <x:c r="G18" s="35" t="n">
+        <x:v>104.68802758599998</x:v>
+      </x:c>
+      <x:c r="H18" s="35" t="n">
+        <x:v>6.158119269764704</x:v>
+      </x:c>
+      <x:c r="I18" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="J18" s="31"/>
       <x:c r="K18" s="31"/>
       <x:c r="L18" s="31"/>
@@ -852,15 +922,31 @@
       <x:c r="Q18" s="31"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="31"/>
-      <x:c r="B19" s="31"/>
-      <x:c r="C19" s="31"/>
-      <x:c r="D19" s="31"/>
-      <x:c r="E19" s="36"/>
-      <x:c r="F19" s="31"/>
-      <x:c r="G19" s="37"/>
-      <x:c r="H19" s="37"/>
-      <x:c r="I19" s="31"/>
+      <x:c r="A19" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B19" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C19" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D19" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F19" s="33" t="str"/>
+      <x:c r="G19" s="35" t="n">
+        <x:v>338.2124144539998</x:v>
+      </x:c>
+      <x:c r="H19" s="35" t="n">
+        <x:v>19.894847909058814</x:v>
+      </x:c>
+      <x:c r="I19" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="J19" s="31"/>
       <x:c r="K19" s="31"/>
       <x:c r="L19" s="31"/>
@@ -33854,8 +33940,12 @@
     <x:col min="5" max="5" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="141.47000122070312" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="31.65999984741211" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12.390000343322754" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="7.239999771118164" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="4.909999847412109" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="141.47000122070312" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="41.599998474121094" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -33881,15 +33971,23 @@
         <x:v>Avg Case s</x:v>
       </x:c>
       <x:c r="H1" s="32" t="str">
+        <x:v>Prompt Style</x:v>
+      </x:c>
+      <x:c r="I1" s="32" t="str">
+        <x:v>Chat Template</x:v>
+      </x:c>
+      <x:c r="J1" s="32" t="str">
+        <x:v>Thinking</x:v>
+      </x:c>
+      <x:c r="K1" s="32" t="str">
+        <x:v>Blend</x:v>
+      </x:c>
+      <x:c r="L1" s="32" t="str">
         <x:v>Correct Cases</x:v>
       </x:c>
-      <x:c r="I1" s="32" t="str">
+      <x:c r="M1" s="32" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
-      <x:c r="M1" s="31"/>
       <x:c r="N1" s="31"/>
       <x:c r="O1" s="31"/>
       <x:c r="P1" s="31"/>
@@ -33917,16 +34015,16 @@
       <x:c r="G2" s="35" t="n">
         <x:v>0.3888904019995072</x:v>
       </x:c>
-      <x:c r="H2" s="33" t="str">
+      <x:c r="H2" s="33" t="str"/>
+      <x:c r="I2" s="33" t="str"/>
+      <x:c r="J2" s="33" t="str"/>
+      <x:c r="K2" s="33" t="str"/>
+      <x:c r="L2" s="33" t="str">
         <x:v>combinations</x:v>
       </x:c>
-      <x:c r="I2" s="33" t="str">
+      <x:c r="M2" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="J2" s="31"/>
-      <x:c r="K2" s="31"/>
-      <x:c r="L2" s="31"/>
-      <x:c r="M2" s="31"/>
       <x:c r="N2" s="31"/>
       <x:c r="O2" s="31"/>
       <x:c r="P2" s="31"/>
@@ -33954,16 +34052,16 @@
       <x:c r="G3" s="35" t="n">
         <x:v>0.877024556411711</x:v>
       </x:c>
-      <x:c r="H3" s="33" t="str">
+      <x:c r="H3" s="33" t="str"/>
+      <x:c r="I3" s="33" t="str"/>
+      <x:c r="J3" s="33" t="str"/>
+      <x:c r="K3" s="33" t="str"/>
+      <x:c r="L3" s="33" t="str">
         <x:v>average, modular_small</x:v>
       </x:c>
-      <x:c r="I3" s="33" t="str">
+      <x:c r="M3" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="J3" s="31"/>
-      <x:c r="K3" s="31"/>
-      <x:c r="L3" s="31"/>
-      <x:c r="M3" s="31"/>
       <x:c r="N3" s="31"/>
       <x:c r="O3" s="31"/>
       <x:c r="P3" s="31"/>
@@ -33991,16 +34089,16 @@
       <x:c r="G4" s="35" t="n">
         <x:v>0.6742378676467257</x:v>
       </x:c>
-      <x:c r="H4" s="33" t="str">
+      <x:c r="H4" s="33" t="str"/>
+      <x:c r="I4" s="33" t="str"/>
+      <x:c r="J4" s="33" t="str"/>
+      <x:c r="K4" s="33" t="str"/>
+      <x:c r="L4" s="33" t="str">
         <x:v>boxes, probability, sequence, reverse_discount, average, coins</x:v>
       </x:c>
-      <x:c r="I4" s="33" t="str">
+      <x:c r="M4" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="J4" s="31"/>
-      <x:c r="K4" s="31"/>
-      <x:c r="L4" s="31"/>
-      <x:c r="M4" s="31"/>
       <x:c r="N4" s="31"/>
       <x:c r="O4" s="31"/>
       <x:c r="P4" s="31"/>
@@ -34028,16 +34126,16 @@
       <x:c r="G5" s="35" t="n">
         <x:v>1.6024433334115362</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="str">
+      <x:c r="H5" s="33" t="str"/>
+      <x:c r="I5" s="33" t="str"/>
+      <x:c r="J5" s="33" t="str"/>
+      <x:c r="K5" s="33" t="str"/>
+      <x:c r="L5" s="33" t="str">
         <x:v>markup, boxes, probability, sequence, rectangle, coins</x:v>
       </x:c>
-      <x:c r="I5" s="33" t="str">
+      <x:c r="M5" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="J5" s="31"/>
-      <x:c r="K5" s="31"/>
-      <x:c r="L5" s="31"/>
-      <x:c r="M5" s="31"/>
       <x:c r="N5" s="31"/>
       <x:c r="O5" s="31"/>
       <x:c r="P5" s="31"/>
@@ -34045,36 +34143,42 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B6" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C6" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D6" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E6" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F6" s="35" t="n">
-        <x:v>104.68802758599998</x:v>
+        <x:v>21.145844373000273</x:v>
       </x:c>
       <x:c r="G6" s="35" t="n">
-        <x:v>6.158119269764704</x:v>
+        <x:v>1.2438731984117808</x:v>
       </x:c>
       <x:c r="H6" s="33" t="str">
-        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
+        <x:v>boxed</x:v>
       </x:c>
       <x:c r="I6" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="J6" s="31"/>
-      <x:c r="K6" s="31"/>
-      <x:c r="L6" s="31"/>
-      <x:c r="M6" s="31"/>
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J6" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K6" s="33" t="str"/>
+      <x:c r="L6" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="M6" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="N6" s="31"/>
       <x:c r="O6" s="31"/>
       <x:c r="P6" s="31"/>
@@ -34082,112 +34186,206 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B7" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C7" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D7" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
+        <x:v>0.29411764705882354</x:v>
       </x:c>
       <x:c r="F7" s="35" t="n">
-        <x:v>338.2124144539998</x:v>
+        <x:v>54.02931174700029</x:v>
       </x:c>
       <x:c r="G7" s="35" t="n">
-        <x:v>19.894847909058814</x:v>
+        <x:v>3.178194808647076</x:v>
       </x:c>
       <x:c r="H7" s="33" t="str">
-        <x:v>algebra, markup, boxes, inclusion, modular, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, syllogism</x:v>
+        <x:v>boxed</x:v>
       </x:c>
       <x:c r="I7" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="J7" s="31"/>
-      <x:c r="K7" s="31"/>
-      <x:c r="L7" s="31"/>
-      <x:c r="M7" s="31"/>
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J7" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="str"/>
+      <x:c r="L7" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small</x:v>
+      </x:c>
+      <x:c r="M7" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="N7" s="31"/>
       <x:c r="O7" s="31"/>
       <x:c r="P7" s="31"/>
       <x:c r="Q7" s="31"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="31"/>
-      <x:c r="B8" s="31"/>
-      <x:c r="C8" s="31"/>
-      <x:c r="D8" s="31"/>
-      <x:c r="E8" s="36"/>
-      <x:c r="F8" s="37"/>
-      <x:c r="G8" s="37"/>
-      <x:c r="H8" s="31"/>
-      <x:c r="I8" s="31"/>
-      <x:c r="J8" s="31"/>
-      <x:c r="K8" s="31"/>
-      <x:c r="L8" s="31"/>
-      <x:c r="M8" s="31"/>
+      <x:c r="A8" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="n">
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="F8" s="35" t="n">
+        <x:v>53.94164416799936</x:v>
+      </x:c>
+      <x:c r="G8" s="35" t="n">
+        <x:v>3.1730378922352562</x:v>
+      </x:c>
+      <x:c r="H8" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I8" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L8" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, syllogism</x:v>
+      </x:c>
+      <x:c r="M8" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="N8" s="31"/>
       <x:c r="O8" s="31"/>
       <x:c r="P8" s="31"/>
       <x:c r="Q8" s="31"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="31"/>
-      <x:c r="B9" s="31"/>
-      <x:c r="C9" s="31"/>
-      <x:c r="D9" s="31"/>
-      <x:c r="E9" s="36"/>
-      <x:c r="F9" s="37"/>
-      <x:c r="G9" s="37"/>
-      <x:c r="H9" s="31"/>
-      <x:c r="I9" s="31"/>
-      <x:c r="J9" s="31"/>
-      <x:c r="K9" s="31"/>
-      <x:c r="L9" s="31"/>
-      <x:c r="M9" s="31"/>
+      <x:c r="A9" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B9" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="n">
+        <x:v>0.29411764705882354</x:v>
+      </x:c>
+      <x:c r="F9" s="35" t="n">
+        <x:v>51.153985081999735</x:v>
+      </x:c>
+      <x:c r="G9" s="35" t="n">
+        <x:v>3.0090579459999844</x:v>
+      </x:c>
+      <x:c r="H9" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I9" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J9" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K9" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L9" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, syllogism</x:v>
+      </x:c>
+      <x:c r="M9" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="N9" s="31"/>
       <x:c r="O9" s="31"/>
       <x:c r="P9" s="31"/>
       <x:c r="Q9" s="31"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="31"/>
-      <x:c r="B10" s="31"/>
-      <x:c r="C10" s="31"/>
-      <x:c r="D10" s="31"/>
-      <x:c r="E10" s="36"/>
-      <x:c r="F10" s="37"/>
-      <x:c r="G10" s="37"/>
-      <x:c r="H10" s="31"/>
-      <x:c r="I10" s="31"/>
-      <x:c r="J10" s="31"/>
-      <x:c r="K10" s="31"/>
-      <x:c r="L10" s="31"/>
-      <x:c r="M10" s="31"/>
+      <x:c r="A10" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F10" s="35" t="n">
+        <x:v>104.68802758599998</x:v>
+      </x:c>
+      <x:c r="G10" s="35" t="n">
+        <x:v>6.158119269764704</x:v>
+      </x:c>
+      <x:c r="H10" s="33" t="str"/>
+      <x:c r="I10" s="33" t="str"/>
+      <x:c r="J10" s="33" t="str"/>
+      <x:c r="K10" s="33" t="str"/>
+      <x:c r="L10" s="33" t="str">
+        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="M10" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="N10" s="31"/>
       <x:c r="O10" s="31"/>
       <x:c r="P10" s="31"/>
       <x:c r="Q10" s="31"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="31"/>
-      <x:c r="B11" s="31"/>
-      <x:c r="C11" s="31"/>
-      <x:c r="D11" s="31"/>
-      <x:c r="E11" s="36"/>
-      <x:c r="F11" s="37"/>
-      <x:c r="G11" s="37"/>
-      <x:c r="H11" s="31"/>
-      <x:c r="I11" s="31"/>
-      <x:c r="J11" s="31"/>
-      <x:c r="K11" s="31"/>
-      <x:c r="L11" s="31"/>
-      <x:c r="M11" s="31"/>
+      <x:c r="A11" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B11" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C11" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D11" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F11" s="35" t="n">
+        <x:v>338.2124144539998</x:v>
+      </x:c>
+      <x:c r="G11" s="35" t="n">
+        <x:v>19.894847909058814</x:v>
+      </x:c>
+      <x:c r="H11" s="33" t="str"/>
+      <x:c r="I11" s="33" t="str"/>
+      <x:c r="J11" s="33" t="str"/>
+      <x:c r="K11" s="33" t="str"/>
+      <x:c r="L11" s="33" t="str">
+        <x:v>algebra, markup, boxes, inclusion, modular, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, syllogism</x:v>
+      </x:c>
+      <x:c r="M11" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="N11" s="31"/>
       <x:c r="O11" s="31"/>
       <x:c r="P11" s="31"/>
@@ -39700,7 +39898,11 @@
     <x:col min="5" max="5" width="255" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="31.65999984741211" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12.390000343322754" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="7.239999771118164" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="4.909999847412109" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="41.599998474121094" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -39726,12 +39928,20 @@
         <x:v>Elapsed s</x:v>
       </x:c>
       <x:c r="H1" s="32" t="str">
+        <x:v>Prompt Style</x:v>
+      </x:c>
+      <x:c r="I1" s="32" t="str">
+        <x:v>Chat Template</x:v>
+      </x:c>
+      <x:c r="J1" s="32" t="str">
+        <x:v>Thinking</x:v>
+      </x:c>
+      <x:c r="K1" s="32" t="str">
+        <x:v>Blend</x:v>
+      </x:c>
+      <x:c r="L1" s="32" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="I1" s="31"/>
-      <x:c r="J1" s="31"/>
-      <x:c r="K1" s="31"/>
-      <x:c r="L1" s="31"/>
       <x:c r="M1" s="31"/>
       <x:c r="N1" s="31"/>
       <x:c r="O1" s="31"/>
@@ -39760,13 +39970,13 @@
       <x:c r="G2" s="35" t="n">
         <x:v>0.4178812919999473</x:v>
       </x:c>
-      <x:c r="H2" s="33" t="str">
+      <x:c r="H2" s="33" t="str"/>
+      <x:c r="I2" s="33" t="str"/>
+      <x:c r="J2" s="33" t="str"/>
+      <x:c r="K2" s="33" t="str"/>
+      <x:c r="L2" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I2" s="31"/>
-      <x:c r="J2" s="31"/>
-      <x:c r="K2" s="31"/>
-      <x:c r="L2" s="31"/>
       <x:c r="M2" s="31"/>
       <x:c r="N2" s="31"/>
       <x:c r="O2" s="31"/>
@@ -39793,13 +40003,13 @@
       <x:c r="G3" s="35" t="n">
         <x:v>0.39678941699821735</x:v>
       </x:c>
-      <x:c r="H3" s="33" t="str">
+      <x:c r="H3" s="33" t="str"/>
+      <x:c r="I3" s="33" t="str"/>
+      <x:c r="J3" s="33" t="str"/>
+      <x:c r="K3" s="33" t="str"/>
+      <x:c r="L3" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I3" s="31"/>
-      <x:c r="J3" s="31"/>
-      <x:c r="K3" s="31"/>
-      <x:c r="L3" s="31"/>
       <x:c r="M3" s="31"/>
       <x:c r="N3" s="31"/>
       <x:c r="O3" s="31"/>
@@ -39828,13 +40038,13 @@
       <x:c r="G4" s="35" t="n">
         <x:v>0.39339241700145067</x:v>
       </x:c>
-      <x:c r="H4" s="33" t="str">
+      <x:c r="H4" s="33" t="str"/>
+      <x:c r="I4" s="33" t="str"/>
+      <x:c r="J4" s="33" t="str"/>
+      <x:c r="K4" s="33" t="str"/>
+      <x:c r="L4" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I4" s="31"/>
-      <x:c r="J4" s="31"/>
-      <x:c r="K4" s="31"/>
-      <x:c r="L4" s="31"/>
       <x:c r="M4" s="31"/>
       <x:c r="N4" s="31"/>
       <x:c r="O4" s="31"/>
@@ -39863,13 +40073,13 @@
       <x:c r="G5" s="35" t="n">
         <x:v>0.38704341699849465</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="str">
+      <x:c r="H5" s="33" t="str"/>
+      <x:c r="I5" s="33" t="str"/>
+      <x:c r="J5" s="33" t="str"/>
+      <x:c r="K5" s="33" t="str"/>
+      <x:c r="L5" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I5" s="31"/>
-      <x:c r="J5" s="31"/>
-      <x:c r="K5" s="31"/>
-      <x:c r="L5" s="31"/>
       <x:c r="M5" s="31"/>
       <x:c r="N5" s="31"/>
       <x:c r="O5" s="31"/>
@@ -39898,13 +40108,13 @@
       <x:c r="G6" s="35" t="n">
         <x:v>0.38243591699938406</x:v>
       </x:c>
-      <x:c r="H6" s="33" t="str">
+      <x:c r="H6" s="33" t="str"/>
+      <x:c r="I6" s="33" t="str"/>
+      <x:c r="J6" s="33" t="str"/>
+      <x:c r="K6" s="33" t="str"/>
+      <x:c r="L6" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I6" s="31"/>
-      <x:c r="J6" s="31"/>
-      <x:c r="K6" s="31"/>
-      <x:c r="L6" s="31"/>
       <x:c r="M6" s="31"/>
       <x:c r="N6" s="31"/>
       <x:c r="O6" s="31"/>
@@ -39933,13 +40143,13 @@
       <x:c r="G7" s="35" t="n">
         <x:v>0.3804630000013276</x:v>
       </x:c>
-      <x:c r="H7" s="33" t="str">
+      <x:c r="H7" s="33" t="str"/>
+      <x:c r="I7" s="33" t="str"/>
+      <x:c r="J7" s="33" t="str"/>
+      <x:c r="K7" s="33" t="str"/>
+      <x:c r="L7" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I7" s="31"/>
-      <x:c r="J7" s="31"/>
-      <x:c r="K7" s="31"/>
-      <x:c r="L7" s="31"/>
       <x:c r="M7" s="31"/>
       <x:c r="N7" s="31"/>
       <x:c r="O7" s="31"/>
@@ -39968,13 +40178,13 @@
       <x:c r="G8" s="35" t="n">
         <x:v>0.3763529579991882</x:v>
       </x:c>
-      <x:c r="H8" s="33" t="str">
+      <x:c r="H8" s="33" t="str"/>
+      <x:c r="I8" s="33" t="str"/>
+      <x:c r="J8" s="33" t="str"/>
+      <x:c r="K8" s="33" t="str"/>
+      <x:c r="L8" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I8" s="31"/>
-      <x:c r="J8" s="31"/>
-      <x:c r="K8" s="31"/>
-      <x:c r="L8" s="31"/>
       <x:c r="M8" s="31"/>
       <x:c r="N8" s="31"/>
       <x:c r="O8" s="31"/>
@@ -40003,13 +40213,13 @@
       <x:c r="G9" s="35" t="n">
         <x:v>0.4004015829996206</x:v>
       </x:c>
-      <x:c r="H9" s="33" t="str">
+      <x:c r="H9" s="33" t="str"/>
+      <x:c r="I9" s="33" t="str"/>
+      <x:c r="J9" s="33" t="str"/>
+      <x:c r="K9" s="33" t="str"/>
+      <x:c r="L9" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I9" s="31"/>
-      <x:c r="J9" s="31"/>
-      <x:c r="K9" s="31"/>
-      <x:c r="L9" s="31"/>
       <x:c r="M9" s="31"/>
       <x:c r="N9" s="31"/>
       <x:c r="O9" s="31"/>
@@ -40038,13 +40248,13 @@
       <x:c r="G10" s="35" t="n">
         <x:v>0.3935052920023736</x:v>
       </x:c>
-      <x:c r="H10" s="33" t="str">
+      <x:c r="H10" s="33" t="str"/>
+      <x:c r="I10" s="33" t="str"/>
+      <x:c r="J10" s="33" t="str"/>
+      <x:c r="K10" s="33" t="str"/>
+      <x:c r="L10" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I10" s="31"/>
-      <x:c r="J10" s="31"/>
-      <x:c r="K10" s="31"/>
-      <x:c r="L10" s="31"/>
       <x:c r="M10" s="31"/>
       <x:c r="N10" s="31"/>
       <x:c r="O10" s="31"/>
@@ -40073,13 +40283,13 @@
       <x:c r="G11" s="35" t="n">
         <x:v>0.38551141599964467</x:v>
       </x:c>
-      <x:c r="H11" s="33" t="str">
+      <x:c r="H11" s="33" t="str"/>
+      <x:c r="I11" s="33" t="str"/>
+      <x:c r="J11" s="33" t="str"/>
+      <x:c r="K11" s="33" t="str"/>
+      <x:c r="L11" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I11" s="31"/>
-      <x:c r="J11" s="31"/>
-      <x:c r="K11" s="31"/>
-      <x:c r="L11" s="31"/>
       <x:c r="M11" s="31"/>
       <x:c r="N11" s="31"/>
       <x:c r="O11" s="31"/>
@@ -40108,13 +40318,13 @@
       <x:c r="G12" s="35" t="n">
         <x:v>0.386956749996898</x:v>
       </x:c>
-      <x:c r="H12" s="33" t="str">
+      <x:c r="H12" s="33" t="str"/>
+      <x:c r="I12" s="33" t="str"/>
+      <x:c r="J12" s="33" t="str"/>
+      <x:c r="K12" s="33" t="str"/>
+      <x:c r="L12" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I12" s="31"/>
-      <x:c r="J12" s="31"/>
-      <x:c r="K12" s="31"/>
-      <x:c r="L12" s="31"/>
       <x:c r="M12" s="31"/>
       <x:c r="N12" s="31"/>
       <x:c r="O12" s="31"/>
@@ -40143,13 +40353,13 @@
       <x:c r="G13" s="35" t="n">
         <x:v>0.3845894169971871</x:v>
       </x:c>
-      <x:c r="H13" s="33" t="str">
+      <x:c r="H13" s="33" t="str"/>
+      <x:c r="I13" s="33" t="str"/>
+      <x:c r="J13" s="33" t="str"/>
+      <x:c r="K13" s="33" t="str"/>
+      <x:c r="L13" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I13" s="31"/>
-      <x:c r="J13" s="31"/>
-      <x:c r="K13" s="31"/>
-      <x:c r="L13" s="31"/>
       <x:c r="M13" s="31"/>
       <x:c r="N13" s="31"/>
       <x:c r="O13" s="31"/>
@@ -40178,13 +40388,13 @@
       <x:c r="G14" s="35" t="n">
         <x:v>0.38798374999896623</x:v>
       </x:c>
-      <x:c r="H14" s="33" t="str">
+      <x:c r="H14" s="33" t="str"/>
+      <x:c r="I14" s="33" t="str"/>
+      <x:c r="J14" s="33" t="str"/>
+      <x:c r="K14" s="33" t="str"/>
+      <x:c r="L14" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I14" s="31"/>
-      <x:c r="J14" s="31"/>
-      <x:c r="K14" s="31"/>
-      <x:c r="L14" s="31"/>
       <x:c r="M14" s="31"/>
       <x:c r="N14" s="31"/>
       <x:c r="O14" s="31"/>
@@ -40213,13 +40423,13 @@
       <x:c r="G15" s="35" t="n">
         <x:v>0.3841970419998688</x:v>
       </x:c>
-      <x:c r="H15" s="33" t="str">
+      <x:c r="H15" s="33" t="str"/>
+      <x:c r="I15" s="33" t="str"/>
+      <x:c r="J15" s="33" t="str"/>
+      <x:c r="K15" s="33" t="str"/>
+      <x:c r="L15" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I15" s="31"/>
-      <x:c r="J15" s="31"/>
-      <x:c r="K15" s="31"/>
-      <x:c r="L15" s="31"/>
       <x:c r="M15" s="31"/>
       <x:c r="N15" s="31"/>
       <x:c r="O15" s="31"/>
@@ -40248,13 +40458,13 @@
       <x:c r="G16" s="35" t="n">
         <x:v>0.3841249170000083</x:v>
       </x:c>
-      <x:c r="H16" s="33" t="str">
+      <x:c r="H16" s="33" t="str"/>
+      <x:c r="I16" s="33" t="str"/>
+      <x:c r="J16" s="33" t="str"/>
+      <x:c r="K16" s="33" t="str"/>
+      <x:c r="L16" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I16" s="31"/>
-      <x:c r="J16" s="31"/>
-      <x:c r="K16" s="31"/>
-      <x:c r="L16" s="31"/>
       <x:c r="M16" s="31"/>
       <x:c r="N16" s="31"/>
       <x:c r="O16" s="31"/>
@@ -40283,13 +40493,13 @@
       <x:c r="G17" s="35" t="n">
         <x:v>0.38242904099752195</x:v>
       </x:c>
-      <x:c r="H17" s="33" t="str">
+      <x:c r="H17" s="33" t="str"/>
+      <x:c r="I17" s="33" t="str"/>
+      <x:c r="J17" s="33" t="str"/>
+      <x:c r="K17" s="33" t="str"/>
+      <x:c r="L17" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I17" s="31"/>
-      <x:c r="J17" s="31"/>
-      <x:c r="K17" s="31"/>
-      <x:c r="L17" s="31"/>
       <x:c r="M17" s="31"/>
       <x:c r="N17" s="31"/>
       <x:c r="O17" s="31"/>
@@ -40318,13 +40528,13 @@
       <x:c r="G18" s="35" t="n">
         <x:v>0.3870792080015235</x:v>
       </x:c>
-      <x:c r="H18" s="33" t="str">
+      <x:c r="H18" s="33" t="str"/>
+      <x:c r="I18" s="33" t="str"/>
+      <x:c r="J18" s="33" t="str"/>
+      <x:c r="K18" s="33" t="str"/>
+      <x:c r="L18" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="I18" s="31"/>
-      <x:c r="J18" s="31"/>
-      <x:c r="K18" s="31"/>
-      <x:c r="L18" s="31"/>
       <x:c r="M18" s="31"/>
       <x:c r="N18" s="31"/>
       <x:c r="O18" s="31"/>
@@ -40353,13 +40563,13 @@
       <x:c r="G19" s="35" t="n">
         <x:v>0.8767275410027651</x:v>
       </x:c>
-      <x:c r="H19" s="33" t="str">
+      <x:c r="H19" s="33" t="str"/>
+      <x:c r="I19" s="33" t="str"/>
+      <x:c r="J19" s="33" t="str"/>
+      <x:c r="K19" s="33" t="str"/>
+      <x:c r="L19" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I19" s="31"/>
-      <x:c r="J19" s="31"/>
-      <x:c r="K19" s="31"/>
-      <x:c r="L19" s="31"/>
       <x:c r="M19" s="31"/>
       <x:c r="N19" s="31"/>
       <x:c r="O19" s="31"/>
@@ -40386,13 +40596,13 @@
       <x:c r="G20" s="35" t="n">
         <x:v>0.864771374999691</x:v>
       </x:c>
-      <x:c r="H20" s="33" t="str">
+      <x:c r="H20" s="33" t="str"/>
+      <x:c r="I20" s="33" t="str"/>
+      <x:c r="J20" s="33" t="str"/>
+      <x:c r="K20" s="33" t="str"/>
+      <x:c r="L20" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I20" s="31"/>
-      <x:c r="J20" s="31"/>
-      <x:c r="K20" s="31"/>
-      <x:c r="L20" s="31"/>
       <x:c r="M20" s="31"/>
       <x:c r="N20" s="31"/>
       <x:c r="O20" s="31"/>
@@ -40421,13 +40631,13 @@
       <x:c r="G21" s="35" t="n">
         <x:v>0.8631313750011032</x:v>
       </x:c>
-      <x:c r="H21" s="33" t="str">
+      <x:c r="H21" s="33" t="str"/>
+      <x:c r="I21" s="33" t="str"/>
+      <x:c r="J21" s="33" t="str"/>
+      <x:c r="K21" s="33" t="str"/>
+      <x:c r="L21" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I21" s="31"/>
-      <x:c r="J21" s="31"/>
-      <x:c r="K21" s="31"/>
-      <x:c r="L21" s="31"/>
       <x:c r="M21" s="31"/>
       <x:c r="N21" s="31"/>
       <x:c r="O21" s="31"/>
@@ -40456,13 +40666,13 @@
       <x:c r="G22" s="35" t="n">
         <x:v>0.8547794579972106</x:v>
       </x:c>
-      <x:c r="H22" s="33" t="str">
+      <x:c r="H22" s="33" t="str"/>
+      <x:c r="I22" s="33" t="str"/>
+      <x:c r="J22" s="33" t="str"/>
+      <x:c r="K22" s="33" t="str"/>
+      <x:c r="L22" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I22" s="31"/>
-      <x:c r="J22" s="31"/>
-      <x:c r="K22" s="31"/>
-      <x:c r="L22" s="31"/>
       <x:c r="M22" s="31"/>
       <x:c r="N22" s="31"/>
       <x:c r="O22" s="31"/>
@@ -40491,13 +40701,13 @@
       <x:c r="G23" s="35" t="n">
         <x:v>0.8541005839979334</x:v>
       </x:c>
-      <x:c r="H23" s="33" t="str">
+      <x:c r="H23" s="33" t="str"/>
+      <x:c r="I23" s="33" t="str"/>
+      <x:c r="J23" s="33" t="str"/>
+      <x:c r="K23" s="33" t="str"/>
+      <x:c r="L23" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I23" s="31"/>
-      <x:c r="J23" s="31"/>
-      <x:c r="K23" s="31"/>
-      <x:c r="L23" s="31"/>
       <x:c r="M23" s="31"/>
       <x:c r="N23" s="31"/>
       <x:c r="O23" s="31"/>
@@ -40526,13 +40736,13 @@
       <x:c r="G24" s="35" t="n">
         <x:v>0.8571479580023151</x:v>
       </x:c>
-      <x:c r="H24" s="33" t="str">
+      <x:c r="H24" s="33" t="str"/>
+      <x:c r="I24" s="33" t="str"/>
+      <x:c r="J24" s="33" t="str"/>
+      <x:c r="K24" s="33" t="str"/>
+      <x:c r="L24" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I24" s="31"/>
-      <x:c r="J24" s="31"/>
-      <x:c r="K24" s="31"/>
-      <x:c r="L24" s="31"/>
       <x:c r="M24" s="31"/>
       <x:c r="N24" s="31"/>
       <x:c r="O24" s="31"/>
@@ -40561,13 +40771,13 @@
       <x:c r="G25" s="35" t="n">
         <x:v>0.8552251670007536</x:v>
       </x:c>
-      <x:c r="H25" s="33" t="str">
+      <x:c r="H25" s="33" t="str"/>
+      <x:c r="I25" s="33" t="str"/>
+      <x:c r="J25" s="33" t="str"/>
+      <x:c r="K25" s="33" t="str"/>
+      <x:c r="L25" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I25" s="31"/>
-      <x:c r="J25" s="31"/>
-      <x:c r="K25" s="31"/>
-      <x:c r="L25" s="31"/>
       <x:c r="M25" s="31"/>
       <x:c r="N25" s="31"/>
       <x:c r="O25" s="31"/>
@@ -40596,13 +40806,13 @@
       <x:c r="G26" s="35" t="n">
         <x:v>0.8664512920004199</x:v>
       </x:c>
-      <x:c r="H26" s="33" t="str">
+      <x:c r="H26" s="33" t="str"/>
+      <x:c r="I26" s="33" t="str"/>
+      <x:c r="J26" s="33" t="str"/>
+      <x:c r="K26" s="33" t="str"/>
+      <x:c r="L26" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I26" s="31"/>
-      <x:c r="J26" s="31"/>
-      <x:c r="K26" s="31"/>
-      <x:c r="L26" s="31"/>
       <x:c r="M26" s="31"/>
       <x:c r="N26" s="31"/>
       <x:c r="O26" s="31"/>
@@ -40631,13 +40841,13 @@
       <x:c r="G27" s="35" t="n">
         <x:v>0.8610935420001624</x:v>
       </x:c>
-      <x:c r="H27" s="33" t="str">
+      <x:c r="H27" s="33" t="str"/>
+      <x:c r="I27" s="33" t="str"/>
+      <x:c r="J27" s="33" t="str"/>
+      <x:c r="K27" s="33" t="str"/>
+      <x:c r="L27" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I27" s="31"/>
-      <x:c r="J27" s="31"/>
-      <x:c r="K27" s="31"/>
-      <x:c r="L27" s="31"/>
       <x:c r="M27" s="31"/>
       <x:c r="N27" s="31"/>
       <x:c r="O27" s="31"/>
@@ -40666,13 +40876,13 @@
       <x:c r="G28" s="35" t="n">
         <x:v>0.8592157499988389</x:v>
       </x:c>
-      <x:c r="H28" s="33" t="str">
+      <x:c r="H28" s="33" t="str"/>
+      <x:c r="I28" s="33" t="str"/>
+      <x:c r="J28" s="33" t="str"/>
+      <x:c r="K28" s="33" t="str"/>
+      <x:c r="L28" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I28" s="31"/>
-      <x:c r="J28" s="31"/>
-      <x:c r="K28" s="31"/>
-      <x:c r="L28" s="31"/>
       <x:c r="M28" s="31"/>
       <x:c r="N28" s="31"/>
       <x:c r="O28" s="31"/>
@@ -40701,13 +40911,13 @@
       <x:c r="G29" s="35" t="n">
         <x:v>0.8618990420000046</x:v>
       </x:c>
-      <x:c r="H29" s="33" t="str">
+      <x:c r="H29" s="33" t="str"/>
+      <x:c r="I29" s="33" t="str"/>
+      <x:c r="J29" s="33" t="str"/>
+      <x:c r="K29" s="33" t="str"/>
+      <x:c r="L29" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I29" s="31"/>
-      <x:c r="J29" s="31"/>
-      <x:c r="K29" s="31"/>
-      <x:c r="L29" s="31"/>
       <x:c r="M29" s="31"/>
       <x:c r="N29" s="31"/>
       <x:c r="O29" s="31"/>
@@ -40736,13 +40946,13 @@
       <x:c r="G30" s="35" t="n">
         <x:v>0.8620276249966992</x:v>
       </x:c>
-      <x:c r="H30" s="33" t="str">
+      <x:c r="H30" s="33" t="str"/>
+      <x:c r="I30" s="33" t="str"/>
+      <x:c r="J30" s="33" t="str"/>
+      <x:c r="K30" s="33" t="str"/>
+      <x:c r="L30" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I30" s="31"/>
-      <x:c r="J30" s="31"/>
-      <x:c r="K30" s="31"/>
-      <x:c r="L30" s="31"/>
       <x:c r="M30" s="31"/>
       <x:c r="N30" s="31"/>
       <x:c r="O30" s="31"/>
@@ -40771,13 +40981,13 @@
       <x:c r="G31" s="35" t="n">
         <x:v>0.8713674169994192</x:v>
       </x:c>
-      <x:c r="H31" s="33" t="str">
+      <x:c r="H31" s="33" t="str"/>
+      <x:c r="I31" s="33" t="str"/>
+      <x:c r="J31" s="33" t="str"/>
+      <x:c r="K31" s="33" t="str"/>
+      <x:c r="L31" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I31" s="31"/>
-      <x:c r="J31" s="31"/>
-      <x:c r="K31" s="31"/>
-      <x:c r="L31" s="31"/>
       <x:c r="M31" s="31"/>
       <x:c r="N31" s="31"/>
       <x:c r="O31" s="31"/>
@@ -40806,13 +41016,13 @@
       <x:c r="G32" s="35" t="n">
         <x:v>0.9271873329998925</x:v>
       </x:c>
-      <x:c r="H32" s="33" t="str">
+      <x:c r="H32" s="33" t="str"/>
+      <x:c r="I32" s="33" t="str"/>
+      <x:c r="J32" s="33" t="str"/>
+      <x:c r="K32" s="33" t="str"/>
+      <x:c r="L32" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I32" s="31"/>
-      <x:c r="J32" s="31"/>
-      <x:c r="K32" s="31"/>
-      <x:c r="L32" s="31"/>
       <x:c r="M32" s="31"/>
       <x:c r="N32" s="31"/>
       <x:c r="O32" s="31"/>
@@ -40841,13 +41051,13 @@
       <x:c r="G33" s="35" t="n">
         <x:v>0.895853291000094</x:v>
       </x:c>
-      <x:c r="H33" s="33" t="str">
+      <x:c r="H33" s="33" t="str"/>
+      <x:c r="I33" s="33" t="str"/>
+      <x:c r="J33" s="33" t="str"/>
+      <x:c r="K33" s="33" t="str"/>
+      <x:c r="L33" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I33" s="31"/>
-      <x:c r="J33" s="31"/>
-      <x:c r="K33" s="31"/>
-      <x:c r="L33" s="31"/>
       <x:c r="M33" s="31"/>
       <x:c r="N33" s="31"/>
       <x:c r="O33" s="31"/>
@@ -40876,13 +41086,13 @@
       <x:c r="G34" s="35" t="n">
         <x:v>0.8587658750002447</x:v>
       </x:c>
-      <x:c r="H34" s="33" t="str">
+      <x:c r="H34" s="33" t="str"/>
+      <x:c r="I34" s="33" t="str"/>
+      <x:c r="J34" s="33" t="str"/>
+      <x:c r="K34" s="33" t="str"/>
+      <x:c r="L34" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I34" s="31"/>
-      <x:c r="J34" s="31"/>
-      <x:c r="K34" s="31"/>
-      <x:c r="L34" s="31"/>
       <x:c r="M34" s="31"/>
       <x:c r="N34" s="31"/>
       <x:c r="O34" s="31"/>
@@ -40911,13 +41121,13 @@
       <x:c r="G35" s="35" t="n">
         <x:v>1.0196728340015397</x:v>
       </x:c>
-      <x:c r="H35" s="33" t="str">
+      <x:c r="H35" s="33" t="str"/>
+      <x:c r="I35" s="33" t="str"/>
+      <x:c r="J35" s="33" t="str"/>
+      <x:c r="K35" s="33" t="str"/>
+      <x:c r="L35" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I35" s="31"/>
-      <x:c r="J35" s="31"/>
-      <x:c r="K35" s="31"/>
-      <x:c r="L35" s="31"/>
       <x:c r="M35" s="31"/>
       <x:c r="N35" s="31"/>
       <x:c r="O35" s="31"/>
@@ -40946,13 +41156,13 @@
       <x:c r="G36" s="35" t="n">
         <x:v>0.7289004999984172</x:v>
       </x:c>
-      <x:c r="H36" s="33" t="str">
+      <x:c r="H36" s="33" t="str"/>
+      <x:c r="I36" s="33" t="str"/>
+      <x:c r="J36" s="33" t="str"/>
+      <x:c r="K36" s="33" t="str"/>
+      <x:c r="L36" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I36" s="31"/>
-      <x:c r="J36" s="31"/>
-      <x:c r="K36" s="31"/>
-      <x:c r="L36" s="31"/>
       <x:c r="M36" s="31"/>
       <x:c r="N36" s="31"/>
       <x:c r="O36" s="31"/>
@@ -40981,13 +41191,13 @@
       <x:c r="G37" s="35" t="n">
         <x:v>0.6929169579998415</x:v>
       </x:c>
-      <x:c r="H37" s="33" t="str">
+      <x:c r="H37" s="33" t="str"/>
+      <x:c r="I37" s="33" t="str"/>
+      <x:c r="J37" s="33" t="str"/>
+      <x:c r="K37" s="33" t="str"/>
+      <x:c r="L37" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I37" s="31"/>
-      <x:c r="J37" s="31"/>
-      <x:c r="K37" s="31"/>
-      <x:c r="L37" s="31"/>
       <x:c r="M37" s="31"/>
       <x:c r="N37" s="31"/>
       <x:c r="O37" s="31"/>
@@ -41016,13 +41226,13 @@
       <x:c r="G38" s="35" t="n">
         <x:v>0.6743095830024686</x:v>
       </x:c>
-      <x:c r="H38" s="33" t="str">
+      <x:c r="H38" s="33" t="str"/>
+      <x:c r="I38" s="33" t="str"/>
+      <x:c r="J38" s="33" t="str"/>
+      <x:c r="K38" s="33" t="str"/>
+      <x:c r="L38" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I38" s="31"/>
-      <x:c r="J38" s="31"/>
-      <x:c r="K38" s="31"/>
-      <x:c r="L38" s="31"/>
       <x:c r="M38" s="31"/>
       <x:c r="N38" s="31"/>
       <x:c r="O38" s="31"/>
@@ -41051,13 +41261,13 @@
       <x:c r="G39" s="35" t="n">
         <x:v>0.6829507500006002</x:v>
       </x:c>
-      <x:c r="H39" s="33" t="str">
+      <x:c r="H39" s="33" t="str"/>
+      <x:c r="I39" s="33" t="str"/>
+      <x:c r="J39" s="33" t="str"/>
+      <x:c r="K39" s="33" t="str"/>
+      <x:c r="L39" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I39" s="31"/>
-      <x:c r="J39" s="31"/>
-      <x:c r="K39" s="31"/>
-      <x:c r="L39" s="31"/>
       <x:c r="M39" s="31"/>
       <x:c r="N39" s="31"/>
       <x:c r="O39" s="31"/>
@@ -41086,13 +41296,13 @@
       <x:c r="G40" s="35" t="n">
         <x:v>0.6713423339970177</x:v>
       </x:c>
-      <x:c r="H40" s="33" t="str">
+      <x:c r="H40" s="33" t="str"/>
+      <x:c r="I40" s="33" t="str"/>
+      <x:c r="J40" s="33" t="str"/>
+      <x:c r="K40" s="33" t="str"/>
+      <x:c r="L40" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I40" s="31"/>
-      <x:c r="J40" s="31"/>
-      <x:c r="K40" s="31"/>
-      <x:c r="L40" s="31"/>
       <x:c r="M40" s="31"/>
       <x:c r="N40" s="31"/>
       <x:c r="O40" s="31"/>
@@ -41121,13 +41331,13 @@
       <x:c r="G41" s="35" t="n">
         <x:v>0.6777662500026054</x:v>
       </x:c>
-      <x:c r="H41" s="33" t="str">
+      <x:c r="H41" s="33" t="str"/>
+      <x:c r="I41" s="33" t="str"/>
+      <x:c r="J41" s="33" t="str"/>
+      <x:c r="K41" s="33" t="str"/>
+      <x:c r="L41" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I41" s="31"/>
-      <x:c r="J41" s="31"/>
-      <x:c r="K41" s="31"/>
-      <x:c r="L41" s="31"/>
       <x:c r="M41" s="31"/>
       <x:c r="N41" s="31"/>
       <x:c r="O41" s="31"/>
@@ -41156,13 +41366,13 @@
       <x:c r="G42" s="35" t="n">
         <x:v>0.667745416998514</x:v>
       </x:c>
-      <x:c r="H42" s="33" t="str">
+      <x:c r="H42" s="33" t="str"/>
+      <x:c r="I42" s="33" t="str"/>
+      <x:c r="J42" s="33" t="str"/>
+      <x:c r="K42" s="33" t="str"/>
+      <x:c r="L42" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I42" s="31"/>
-      <x:c r="J42" s="31"/>
-      <x:c r="K42" s="31"/>
-      <x:c r="L42" s="31"/>
       <x:c r="M42" s="31"/>
       <x:c r="N42" s="31"/>
       <x:c r="O42" s="31"/>
@@ -41191,13 +41401,13 @@
       <x:c r="G43" s="35" t="n">
         <x:v>0.6665247089986224</x:v>
       </x:c>
-      <x:c r="H43" s="33" t="str">
+      <x:c r="H43" s="33" t="str"/>
+      <x:c r="I43" s="33" t="str"/>
+      <x:c r="J43" s="33" t="str"/>
+      <x:c r="K43" s="33" t="str"/>
+      <x:c r="L43" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I43" s="31"/>
-      <x:c r="J43" s="31"/>
-      <x:c r="K43" s="31"/>
-      <x:c r="L43" s="31"/>
       <x:c r="M43" s="31"/>
       <x:c r="N43" s="31"/>
       <x:c r="O43" s="31"/>
@@ -41226,13 +41436,13 @@
       <x:c r="G44" s="35" t="n">
         <x:v>0.667189125000732</x:v>
       </x:c>
-      <x:c r="H44" s="33" t="str">
+      <x:c r="H44" s="33" t="str"/>
+      <x:c r="I44" s="33" t="str"/>
+      <x:c r="J44" s="33" t="str"/>
+      <x:c r="K44" s="33" t="str"/>
+      <x:c r="L44" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I44" s="31"/>
-      <x:c r="J44" s="31"/>
-      <x:c r="K44" s="31"/>
-      <x:c r="L44" s="31"/>
       <x:c r="M44" s="31"/>
       <x:c r="N44" s="31"/>
       <x:c r="O44" s="31"/>
@@ -41261,13 +41471,13 @@
       <x:c r="G45" s="35" t="n">
         <x:v>0.667051000000356</x:v>
       </x:c>
-      <x:c r="H45" s="33" t="str">
+      <x:c r="H45" s="33" t="str"/>
+      <x:c r="I45" s="33" t="str"/>
+      <x:c r="J45" s="33" t="str"/>
+      <x:c r="K45" s="33" t="str"/>
+      <x:c r="L45" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I45" s="31"/>
-      <x:c r="J45" s="31"/>
-      <x:c r="K45" s="31"/>
-      <x:c r="L45" s="31"/>
       <x:c r="M45" s="31"/>
       <x:c r="N45" s="31"/>
       <x:c r="O45" s="31"/>
@@ -41296,13 +41506,13 @@
       <x:c r="G46" s="35" t="n">
         <x:v>0.6656283749980503</x:v>
       </x:c>
-      <x:c r="H46" s="33" t="str">
+      <x:c r="H46" s="33" t="str"/>
+      <x:c r="I46" s="33" t="str"/>
+      <x:c r="J46" s="33" t="str"/>
+      <x:c r="K46" s="33" t="str"/>
+      <x:c r="L46" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I46" s="31"/>
-      <x:c r="J46" s="31"/>
-      <x:c r="K46" s="31"/>
-      <x:c r="L46" s="31"/>
       <x:c r="M46" s="31"/>
       <x:c r="N46" s="31"/>
       <x:c r="O46" s="31"/>
@@ -41331,13 +41541,13 @@
       <x:c r="G47" s="35" t="n">
         <x:v>0.6653752909987816</x:v>
       </x:c>
-      <x:c r="H47" s="33" t="str">
+      <x:c r="H47" s="33" t="str"/>
+      <x:c r="I47" s="33" t="str"/>
+      <x:c r="J47" s="33" t="str"/>
+      <x:c r="K47" s="33" t="str"/>
+      <x:c r="L47" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I47" s="31"/>
-      <x:c r="J47" s="31"/>
-      <x:c r="K47" s="31"/>
-      <x:c r="L47" s="31"/>
       <x:c r="M47" s="31"/>
       <x:c r="N47" s="31"/>
       <x:c r="O47" s="31"/>
@@ -41366,13 +41576,13 @@
       <x:c r="G48" s="35" t="n">
         <x:v>0.6708209999997052</x:v>
       </x:c>
-      <x:c r="H48" s="33" t="str">
+      <x:c r="H48" s="33" t="str"/>
+      <x:c r="I48" s="33" t="str"/>
+      <x:c r="J48" s="33" t="str"/>
+      <x:c r="K48" s="33" t="str"/>
+      <x:c r="L48" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I48" s="31"/>
-      <x:c r="J48" s="31"/>
-      <x:c r="K48" s="31"/>
-      <x:c r="L48" s="31"/>
       <x:c r="M48" s="31"/>
       <x:c r="N48" s="31"/>
       <x:c r="O48" s="31"/>
@@ -41401,13 +41611,13 @@
       <x:c r="G49" s="35" t="n">
         <x:v>0.6702556659984111</x:v>
       </x:c>
-      <x:c r="H49" s="33" t="str">
+      <x:c r="H49" s="33" t="str"/>
+      <x:c r="I49" s="33" t="str"/>
+      <x:c r="J49" s="33" t="str"/>
+      <x:c r="K49" s="33" t="str"/>
+      <x:c r="L49" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I49" s="31"/>
-      <x:c r="J49" s="31"/>
-      <x:c r="K49" s="31"/>
-      <x:c r="L49" s="31"/>
       <x:c r="M49" s="31"/>
       <x:c r="N49" s="31"/>
       <x:c r="O49" s="31"/>
@@ -41436,13 +41646,13 @@
       <x:c r="G50" s="35" t="n">
         <x:v>0.664872875000583</x:v>
       </x:c>
-      <x:c r="H50" s="33" t="str">
+      <x:c r="H50" s="33" t="str"/>
+      <x:c r="I50" s="33" t="str"/>
+      <x:c r="J50" s="33" t="str"/>
+      <x:c r="K50" s="33" t="str"/>
+      <x:c r="L50" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I50" s="31"/>
-      <x:c r="J50" s="31"/>
-      <x:c r="K50" s="31"/>
-      <x:c r="L50" s="31"/>
       <x:c r="M50" s="31"/>
       <x:c r="N50" s="31"/>
       <x:c r="O50" s="31"/>
@@ -41471,13 +41681,13 @@
       <x:c r="G51" s="35" t="n">
         <x:v>0.6573060419977992</x:v>
       </x:c>
-      <x:c r="H51" s="33" t="str">
+      <x:c r="H51" s="33" t="str"/>
+      <x:c r="I51" s="33" t="str"/>
+      <x:c r="J51" s="33" t="str"/>
+      <x:c r="K51" s="33" t="str"/>
+      <x:c r="L51" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I51" s="31"/>
-      <x:c r="J51" s="31"/>
-      <x:c r="K51" s="31"/>
-      <x:c r="L51" s="31"/>
       <x:c r="M51" s="31"/>
       <x:c r="N51" s="31"/>
       <x:c r="O51" s="31"/>
@@ -41506,13 +41716,13 @@
       <x:c r="G52" s="35" t="n">
         <x:v>0.671087875001831</x:v>
       </x:c>
-      <x:c r="H52" s="33" t="str">
+      <x:c r="H52" s="33" t="str"/>
+      <x:c r="I52" s="33" t="str"/>
+      <x:c r="J52" s="33" t="str"/>
+      <x:c r="K52" s="33" t="str"/>
+      <x:c r="L52" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="I52" s="31"/>
-      <x:c r="J52" s="31"/>
-      <x:c r="K52" s="31"/>
-      <x:c r="L52" s="31"/>
       <x:c r="M52" s="31"/>
       <x:c r="N52" s="31"/>
       <x:c r="O52" s="31"/>
@@ -41541,13 +41751,13 @@
       <x:c r="G53" s="35" t="n">
         <x:v>1.5837817909996375</x:v>
       </x:c>
-      <x:c r="H53" s="33" t="str">
+      <x:c r="H53" s="33" t="str"/>
+      <x:c r="I53" s="33" t="str"/>
+      <x:c r="J53" s="33" t="str"/>
+      <x:c r="K53" s="33" t="str"/>
+      <x:c r="L53" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I53" s="31"/>
-      <x:c r="J53" s="31"/>
-      <x:c r="K53" s="31"/>
-      <x:c r="L53" s="31"/>
       <x:c r="M53" s="31"/>
       <x:c r="N53" s="31"/>
       <x:c r="O53" s="31"/>
@@ -41576,13 +41786,13 @@
       <x:c r="G54" s="35" t="n">
         <x:v>1.5882722079986706</x:v>
       </x:c>
-      <x:c r="H54" s="33" t="str">
+      <x:c r="H54" s="33" t="str"/>
+      <x:c r="I54" s="33" t="str"/>
+      <x:c r="J54" s="33" t="str"/>
+      <x:c r="K54" s="33" t="str"/>
+      <x:c r="L54" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I54" s="31"/>
-      <x:c r="J54" s="31"/>
-      <x:c r="K54" s="31"/>
-      <x:c r="L54" s="31"/>
       <x:c r="M54" s="31"/>
       <x:c r="N54" s="31"/>
       <x:c r="O54" s="31"/>
@@ -41611,13 +41821,13 @@
       <x:c r="G55" s="35" t="n">
         <x:v>1.6641501670019352</x:v>
       </x:c>
-      <x:c r="H55" s="33" t="str">
+      <x:c r="H55" s="33" t="str"/>
+      <x:c r="I55" s="33" t="str"/>
+      <x:c r="J55" s="33" t="str"/>
+      <x:c r="K55" s="33" t="str"/>
+      <x:c r="L55" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I55" s="31"/>
-      <x:c r="J55" s="31"/>
-      <x:c r="K55" s="31"/>
-      <x:c r="L55" s="31"/>
       <x:c r="M55" s="31"/>
       <x:c r="N55" s="31"/>
       <x:c r="O55" s="31"/>
@@ -41646,13 +41856,13 @@
       <x:c r="G56" s="35" t="n">
         <x:v>1.5962577909995161</x:v>
       </x:c>
-      <x:c r="H56" s="33" t="str">
+      <x:c r="H56" s="33" t="str"/>
+      <x:c r="I56" s="33" t="str"/>
+      <x:c r="J56" s="33" t="str"/>
+      <x:c r="K56" s="33" t="str"/>
+      <x:c r="L56" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I56" s="31"/>
-      <x:c r="J56" s="31"/>
-      <x:c r="K56" s="31"/>
-      <x:c r="L56" s="31"/>
       <x:c r="M56" s="31"/>
       <x:c r="N56" s="31"/>
       <x:c r="O56" s="31"/>
@@ -41681,13 +41891,13 @@
       <x:c r="G57" s="35" t="n">
         <x:v>1.5777221669995924</x:v>
       </x:c>
-      <x:c r="H57" s="33" t="str">
+      <x:c r="H57" s="33" t="str"/>
+      <x:c r="I57" s="33" t="str"/>
+      <x:c r="J57" s="33" t="str"/>
+      <x:c r="K57" s="33" t="str"/>
+      <x:c r="L57" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I57" s="31"/>
-      <x:c r="J57" s="31"/>
-      <x:c r="K57" s="31"/>
-      <x:c r="L57" s="31"/>
       <x:c r="M57" s="31"/>
       <x:c r="N57" s="31"/>
       <x:c r="O57" s="31"/>
@@ -41716,13 +41926,13 @@
       <x:c r="G58" s="35" t="n">
         <x:v>1.5640662080004404</x:v>
       </x:c>
-      <x:c r="H58" s="33" t="str">
+      <x:c r="H58" s="33" t="str"/>
+      <x:c r="I58" s="33" t="str"/>
+      <x:c r="J58" s="33" t="str"/>
+      <x:c r="K58" s="33" t="str"/>
+      <x:c r="L58" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I58" s="31"/>
-      <x:c r="J58" s="31"/>
-      <x:c r="K58" s="31"/>
-      <x:c r="L58" s="31"/>
       <x:c r="M58" s="31"/>
       <x:c r="N58" s="31"/>
       <x:c r="O58" s="31"/>
@@ -41751,13 +41961,13 @@
       <x:c r="G59" s="35" t="n">
         <x:v>1.5576800419985375</x:v>
       </x:c>
-      <x:c r="H59" s="33" t="str">
+      <x:c r="H59" s="33" t="str"/>
+      <x:c r="I59" s="33" t="str"/>
+      <x:c r="J59" s="33" t="str"/>
+      <x:c r="K59" s="33" t="str"/>
+      <x:c r="L59" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I59" s="31"/>
-      <x:c r="J59" s="31"/>
-      <x:c r="K59" s="31"/>
-      <x:c r="L59" s="31"/>
       <x:c r="M59" s="31"/>
       <x:c r="N59" s="31"/>
       <x:c r="O59" s="31"/>
@@ -41786,13 +41996,13 @@
       <x:c r="G60" s="35" t="n">
         <x:v>1.5804141250009707</x:v>
       </x:c>
-      <x:c r="H60" s="33" t="str">
+      <x:c r="H60" s="33" t="str"/>
+      <x:c r="I60" s="33" t="str"/>
+      <x:c r="J60" s="33" t="str"/>
+      <x:c r="K60" s="33" t="str"/>
+      <x:c r="L60" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I60" s="31"/>
-      <x:c r="J60" s="31"/>
-      <x:c r="K60" s="31"/>
-      <x:c r="L60" s="31"/>
       <x:c r="M60" s="31"/>
       <x:c r="N60" s="31"/>
       <x:c r="O60" s="31"/>
@@ -41821,13 +42031,13 @@
       <x:c r="G61" s="35" t="n">
         <x:v>1.603532584002096</x:v>
       </x:c>
-      <x:c r="H61" s="33" t="str">
+      <x:c r="H61" s="33" t="str"/>
+      <x:c r="I61" s="33" t="str"/>
+      <x:c r="J61" s="33" t="str"/>
+      <x:c r="K61" s="33" t="str"/>
+      <x:c r="L61" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I61" s="31"/>
-      <x:c r="J61" s="31"/>
-      <x:c r="K61" s="31"/>
-      <x:c r="L61" s="31"/>
       <x:c r="M61" s="31"/>
       <x:c r="N61" s="31"/>
       <x:c r="O61" s="31"/>
@@ -41856,13 +42066,13 @@
       <x:c r="G62" s="35" t="n">
         <x:v>1.5912155000005441</x:v>
       </x:c>
-      <x:c r="H62" s="33" t="str">
+      <x:c r="H62" s="33" t="str"/>
+      <x:c r="I62" s="33" t="str"/>
+      <x:c r="J62" s="33" t="str"/>
+      <x:c r="K62" s="33" t="str"/>
+      <x:c r="L62" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I62" s="31"/>
-      <x:c r="J62" s="31"/>
-      <x:c r="K62" s="31"/>
-      <x:c r="L62" s="31"/>
       <x:c r="M62" s="31"/>
       <x:c r="N62" s="31"/>
       <x:c r="O62" s="31"/>
@@ -41891,13 +42101,13 @@
       <x:c r="G63" s="35" t="n">
         <x:v>1.588785584001016</x:v>
       </x:c>
-      <x:c r="H63" s="33" t="str">
+      <x:c r="H63" s="33" t="str"/>
+      <x:c r="I63" s="33" t="str"/>
+      <x:c r="J63" s="33" t="str"/>
+      <x:c r="K63" s="33" t="str"/>
+      <x:c r="L63" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I63" s="31"/>
-      <x:c r="J63" s="31"/>
-      <x:c r="K63" s="31"/>
-      <x:c r="L63" s="31"/>
       <x:c r="M63" s="31"/>
       <x:c r="N63" s="31"/>
       <x:c r="O63" s="31"/>
@@ -41926,13 +42136,13 @@
       <x:c r="G64" s="35" t="n">
         <x:v>1.6004410419991473</x:v>
       </x:c>
-      <x:c r="H64" s="33" t="str">
+      <x:c r="H64" s="33" t="str"/>
+      <x:c r="I64" s="33" t="str"/>
+      <x:c r="J64" s="33" t="str"/>
+      <x:c r="K64" s="33" t="str"/>
+      <x:c r="L64" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I64" s="31"/>
-      <x:c r="J64" s="31"/>
-      <x:c r="K64" s="31"/>
-      <x:c r="L64" s="31"/>
       <x:c r="M64" s="31"/>
       <x:c r="N64" s="31"/>
       <x:c r="O64" s="31"/>
@@ -41961,13 +42171,13 @@
       <x:c r="G65" s="35" t="n">
         <x:v>1.624553375000687</x:v>
       </x:c>
-      <x:c r="H65" s="33" t="str">
+      <x:c r="H65" s="33" t="str"/>
+      <x:c r="I65" s="33" t="str"/>
+      <x:c r="J65" s="33" t="str"/>
+      <x:c r="K65" s="33" t="str"/>
+      <x:c r="L65" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I65" s="31"/>
-      <x:c r="J65" s="31"/>
-      <x:c r="K65" s="31"/>
-      <x:c r="L65" s="31"/>
       <x:c r="M65" s="31"/>
       <x:c r="N65" s="31"/>
       <x:c r="O65" s="31"/>
@@ -41996,13 +42206,13 @@
       <x:c r="G66" s="35" t="n">
         <x:v>1.5585467499986407</x:v>
       </x:c>
-      <x:c r="H66" s="33" t="str">
+      <x:c r="H66" s="33" t="str"/>
+      <x:c r="I66" s="33" t="str"/>
+      <x:c r="J66" s="33" t="str"/>
+      <x:c r="K66" s="33" t="str"/>
+      <x:c r="L66" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I66" s="31"/>
-      <x:c r="J66" s="31"/>
-      <x:c r="K66" s="31"/>
-      <x:c r="L66" s="31"/>
       <x:c r="M66" s="31"/>
       <x:c r="N66" s="31"/>
       <x:c r="O66" s="31"/>
@@ -42031,13 +42241,13 @@
       <x:c r="G67" s="35" t="n">
         <x:v>1.8249316249966796</x:v>
       </x:c>
-      <x:c r="H67" s="33" t="str">
+      <x:c r="H67" s="33" t="str"/>
+      <x:c r="I67" s="33" t="str"/>
+      <x:c r="J67" s="33" t="str"/>
+      <x:c r="K67" s="33" t="str"/>
+      <x:c r="L67" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I67" s="31"/>
-      <x:c r="J67" s="31"/>
-      <x:c r="K67" s="31"/>
-      <x:c r="L67" s="31"/>
       <x:c r="M67" s="31"/>
       <x:c r="N67" s="31"/>
       <x:c r="O67" s="31"/>
@@ -42066,13 +42276,13 @@
       <x:c r="G68" s="35" t="n">
         <x:v>1.5758329999989655</x:v>
       </x:c>
-      <x:c r="H68" s="33" t="str">
+      <x:c r="H68" s="33" t="str"/>
+      <x:c r="I68" s="33" t="str"/>
+      <x:c r="J68" s="33" t="str"/>
+      <x:c r="K68" s="33" t="str"/>
+      <x:c r="L68" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I68" s="31"/>
-      <x:c r="J68" s="31"/>
-      <x:c r="K68" s="31"/>
-      <x:c r="L68" s="31"/>
       <x:c r="M68" s="31"/>
       <x:c r="N68" s="31"/>
       <x:c r="O68" s="31"/>
@@ -42101,13 +42311,13 @@
       <x:c r="G69" s="35" t="n">
         <x:v>1.5613527089990384</x:v>
       </x:c>
-      <x:c r="H69" s="33" t="str">
+      <x:c r="H69" s="33" t="str"/>
+      <x:c r="I69" s="33" t="str"/>
+      <x:c r="J69" s="33" t="str"/>
+      <x:c r="K69" s="33" t="str"/>
+      <x:c r="L69" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="I69" s="31"/>
-      <x:c r="J69" s="31"/>
-      <x:c r="K69" s="31"/>
-      <x:c r="L69" s="31"/>
       <x:c r="M69" s="31"/>
       <x:c r="N69" s="31"/>
       <x:c r="O69" s="31"/>
@@ -42116,10 +42326,10 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B70" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C70" s="33" t="str">
         <x:v>algebra</x:v>
@@ -42128,21 +42338,27 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E70" s="33" t="str">
-        <x:v>\dfrac{25}{2}</x:v>
+        <x:v>### **Step 5: Divide both sides by 4</x:v>
       </x:c>
       <x:c r="F70" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G70" s="35" t="n">
+        <x:v>1.343527333000111</x:v>
+      </x:c>
+      <x:c r="H70" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I70" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G70" s="35" t="n">
-        <x:v>7.580443959000007</x:v>
-      </x:c>
-      <x:c r="H70" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I70" s="31"/>
-      <x:c r="J70" s="31"/>
-      <x:c r="K70" s="31"/>
-      <x:c r="L70" s="31"/>
+      <x:c r="J70" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K70" s="33" t="str"/>
+      <x:c r="L70" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M70" s="31"/>
       <x:c r="N70" s="31"/>
       <x:c r="O70" s="31"/>
@@ -42151,10 +42367,10 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B71" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C71" s="33" t="str">
         <x:v>markup</x:v>
@@ -42163,21 +42379,27 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E71" s="33" t="str">
-        <x:v>96</x:v>
+        <x:v>0.80x = 96</x:v>
       </x:c>
       <x:c r="F71" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G71" s="35" t="n">
+        <x:v>1.3103257079999366</x:v>
+      </x:c>
+      <x:c r="H71" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I71" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G71" s="35" t="n">
-        <x:v>6.407860625000012</x:v>
-      </x:c>
-      <x:c r="H71" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I71" s="31"/>
-      <x:c r="J71" s="31"/>
-      <x:c r="K71" s="31"/>
-      <x:c r="L71" s="31"/>
+      <x:c r="J71" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K71" s="33" t="str"/>
+      <x:c r="L71" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M71" s="31"/>
       <x:c r="N71" s="31"/>
       <x:c r="O71" s="31"/>
@@ -42186,10 +42408,10 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B72" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C72" s="33" t="str">
         <x:v>boxes</x:v>
@@ -42198,21 +42420,27 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E72" s="33" t="str">
-        <x:v>Mixed</x:v>
+        <x:v>'- The</x:v>
       </x:c>
       <x:c r="F72" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G72" s="35" t="n">
+        <x:v>1.3203434580000248</x:v>
+      </x:c>
+      <x:c r="H72" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I72" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G72" s="35" t="n">
-        <x:v>6.2715228750000165</x:v>
-      </x:c>
-      <x:c r="H72" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I72" s="31"/>
-      <x:c r="J72" s="31"/>
-      <x:c r="K72" s="31"/>
-      <x:c r="L72" s="31"/>
+      <x:c r="J72" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K72" s="33" t="str"/>
+      <x:c r="L72" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M72" s="31"/>
       <x:c r="N72" s="31"/>
       <x:c r="O72" s="31"/>
@@ -42221,10 +42449,10 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B73" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C73" s="33" t="str">
         <x:v>inclusion</x:v>
@@ -42233,21 +42461,27 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E73" s="33" t="str">
-        <x:v>80</x:v>
+        <x:v>|A \cup B| - |C| = |A</x:v>
       </x:c>
       <x:c r="F73" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G73" s="35" t="n">
+        <x:v>1.3116173749999689</x:v>
+      </x:c>
+      <x:c r="H73" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I73" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G73" s="35" t="n">
-        <x:v>4.775222624999998</x:v>
-      </x:c>
-      <x:c r="H73" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I73" s="31"/>
-      <x:c r="J73" s="31"/>
-      <x:c r="K73" s="31"/>
-      <x:c r="L73" s="31"/>
+      <x:c r="J73" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K73" s="33" t="str"/>
+      <x:c r="L73" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M73" s="31"/>
       <x:c r="N73" s="31"/>
       <x:c r="O73" s="31"/>
@@ -42256,10 +42490,10 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B74" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C74" s="33" t="str">
         <x:v>modular</x:v>
@@ -42268,21 +42502,27 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E74" s="33" t="str">
-        <x:v>'- \(7^8 \equiv 9^2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F74" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
       <x:c r="G74" s="35" t="n">
-        <x:v>14.03727679100001</x:v>
+        <x:v>1.3291511250001804</x:v>
       </x:c>
       <x:c r="H74" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I74" s="31"/>
-      <x:c r="J74" s="31"/>
-      <x:c r="K74" s="31"/>
-      <x:c r="L74" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I74" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J74" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K74" s="33" t="str"/>
+      <x:c r="L74" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M74" s="31"/>
       <x:c r="N74" s="31"/>
       <x:c r="O74" s="31"/>
@@ -42291,10 +42531,10 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B75" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C75" s="33" t="str">
         <x:v>work_rate</x:v>
@@ -42303,21 +42543,27 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E75" s="33" t="str">
-        <x:v>\dfrac{15}{4}</x:v>
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac</x:v>
       </x:c>
       <x:c r="F75" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G75" s="35" t="n">
+        <x:v>1.3192979580001065</x:v>
+      </x:c>
+      <x:c r="H75" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I75" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G75" s="35" t="n">
-        <x:v>6.176148500000011</x:v>
-      </x:c>
-      <x:c r="H75" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I75" s="31"/>
-      <x:c r="J75" s="31"/>
-      <x:c r="K75" s="31"/>
-      <x:c r="L75" s="31"/>
+      <x:c r="J75" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K75" s="33" t="str"/>
+      <x:c r="L75" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M75" s="31"/>
       <x:c r="N75" s="31"/>
       <x:c r="O75" s="31"/>
@@ -42326,10 +42572,10 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B76" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C76" s="33" t="str">
         <x:v>probability</x:v>
@@ -42338,21 +42584,27 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E76" s="33" t="str">
-        <x:v>\dfrac{1}{9}</x:v>
+        <x:v>'---</x:v>
       </x:c>
       <x:c r="F76" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G76" s="35" t="n">
+        <x:v>1.3131642920000104</x:v>
+      </x:c>
+      <x:c r="H76" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I76" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G76" s="35" t="n">
-        <x:v>4.10938950000002</x:v>
-      </x:c>
-      <x:c r="H76" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I76" s="31"/>
-      <x:c r="J76" s="31"/>
-      <x:c r="K76" s="31"/>
-      <x:c r="L76" s="31"/>
+      <x:c r="J76" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K76" s="33" t="str"/>
+      <x:c r="L76" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M76" s="31"/>
       <x:c r="N76" s="31"/>
       <x:c r="O76" s="31"/>
@@ -42361,10 +42613,10 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B77" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C77" s="33" t="str">
         <x:v>sequence</x:v>
@@ -42379,15 +42631,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G77" s="35" t="n">
-        <x:v>8.457965874999957</x:v>
+        <x:v>1.0978643329999613</x:v>
       </x:c>
       <x:c r="H77" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I77" s="31"/>
-      <x:c r="J77" s="31"/>
-      <x:c r="K77" s="31"/>
-      <x:c r="L77" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I77" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J77" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K77" s="33" t="str"/>
+      <x:c r="L77" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M77" s="31"/>
       <x:c r="N77" s="31"/>
       <x:c r="O77" s="31"/>
@@ -42396,10 +42654,10 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B78" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C78" s="33" t="str">
         <x:v>linear_word</x:v>
@@ -42414,15 +42672,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G78" s="35" t="n">
-        <x:v>4.77963704199999</x:v>
+        <x:v>1.0967079580000245</x:v>
       </x:c>
       <x:c r="H78" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I78" s="31"/>
-      <x:c r="J78" s="31"/>
-      <x:c r="K78" s="31"/>
-      <x:c r="L78" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I78" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J78" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K78" s="33" t="str"/>
+      <x:c r="L78" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M78" s="31"/>
       <x:c r="N78" s="31"/>
       <x:c r="O78" s="31"/>
@@ -42431,10 +42695,10 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B79" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C79" s="33" t="str">
         <x:v>reverse_discount</x:v>
@@ -42449,15 +42713,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G79" s="35" t="n">
-        <x:v>4.465110458999959</x:v>
+        <x:v>0.8887154999999893</x:v>
       </x:c>
       <x:c r="H79" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I79" s="31"/>
-      <x:c r="J79" s="31"/>
-      <x:c r="K79" s="31"/>
-      <x:c r="L79" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I79" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J79" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K79" s="33" t="str"/>
+      <x:c r="L79" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M79" s="31"/>
       <x:c r="N79" s="31"/>
       <x:c r="O79" s="31"/>
@@ -42466,10 +42736,10 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B80" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C80" s="33" t="str">
         <x:v>multiples</x:v>
@@ -42478,21 +42748,27 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E80" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>'- Common difference $ d</x:v>
       </x:c>
       <x:c r="F80" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G80" s="35" t="n">
+        <x:v>1.3256102499999542</x:v>
+      </x:c>
+      <x:c r="H80" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I80" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G80" s="35" t="n">
-        <x:v>4.0312850840000465</x:v>
-      </x:c>
-      <x:c r="H80" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I80" s="31"/>
-      <x:c r="J80" s="31"/>
-      <x:c r="K80" s="31"/>
-      <x:c r="L80" s="31"/>
+      <x:c r="J80" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K80" s="33" t="str"/>
+      <x:c r="L80" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M80" s="31"/>
       <x:c r="N80" s="31"/>
       <x:c r="O80" s="31"/>
@@ -42501,10 +42777,10 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B81" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C81" s="33" t="str">
         <x:v>rectangle</x:v>
@@ -42519,15 +42795,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G81" s="35" t="n">
-        <x:v>4.098184124999989</x:v>
+        <x:v>1.1687047079999502</x:v>
       </x:c>
       <x:c r="H81" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I81" s="31"/>
-      <x:c r="J81" s="31"/>
-      <x:c r="K81" s="31"/>
-      <x:c r="L81" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I81" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J81" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K81" s="33" t="str"/>
+      <x:c r="L81" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M81" s="31"/>
       <x:c r="N81" s="31"/>
       <x:c r="O81" s="31"/>
@@ -42536,10 +42818,10 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B82" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C82" s="33" t="str">
         <x:v>average</x:v>
@@ -42548,21 +42830,27 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E82" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>10 + 11 + 13 + 1</x:v>
       </x:c>
       <x:c r="F82" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G82" s="35" t="n">
+        <x:v>1.321005833000072</x:v>
+      </x:c>
+      <x:c r="H82" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I82" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G82" s="35" t="n">
-        <x:v>3.955258875000027</x:v>
-      </x:c>
-      <x:c r="H82" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I82" s="31"/>
-      <x:c r="J82" s="31"/>
-      <x:c r="K82" s="31"/>
-      <x:c r="L82" s="31"/>
+      <x:c r="J82" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K82" s="33" t="str"/>
+      <x:c r="L82" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M82" s="31"/>
       <x:c r="N82" s="31"/>
       <x:c r="O82" s="31"/>
@@ -42571,10 +42859,10 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B83" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C83" s="33" t="str">
         <x:v>combinations</x:v>
@@ -42583,21 +42871,27 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E83" s="33" t="str">
-        <x:v>15</x:v>
+        <x:v>\binom{6}{2} = \frac{6!</x:v>
       </x:c>
       <x:c r="F83" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G83" s="35" t="n">
+        <x:v>1.3201934169999276</x:v>
+      </x:c>
+      <x:c r="H83" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I83" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G83" s="35" t="n">
-        <x:v>6.499252583999976</x:v>
-      </x:c>
-      <x:c r="H83" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I83" s="31"/>
-      <x:c r="J83" s="31"/>
-      <x:c r="K83" s="31"/>
-      <x:c r="L83" s="31"/>
+      <x:c r="J83" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K83" s="33" t="str"/>
+      <x:c r="L83" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M83" s="31"/>
       <x:c r="N83" s="31"/>
       <x:c r="O83" s="31"/>
@@ -42606,10 +42900,10 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B84" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C84" s="33" t="str">
         <x:v>coins</x:v>
@@ -42618,21 +42912,27 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E84" s="33" t="str">
-        <x:v>\dfrac{3}{8}</x:v>
+        <x:v>'- $ p = \frac{1</x:v>
       </x:c>
       <x:c r="F84" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G84" s="35" t="n">
+        <x:v>1.3099095830000351</x:v>
+      </x:c>
+      <x:c r="H84" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I84" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G84" s="35" t="n">
-        <x:v>2.2782300830000395</x:v>
-      </x:c>
-      <x:c r="H84" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I84" s="31"/>
-      <x:c r="J84" s="31"/>
-      <x:c r="K84" s="31"/>
-      <x:c r="L84" s="31"/>
+      <x:c r="J84" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K84" s="33" t="str"/>
+      <x:c r="L84" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M84" s="31"/>
       <x:c r="N84" s="31"/>
       <x:c r="O84" s="31"/>
@@ -42641,10 +42941,10 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B85" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C85" s="33" t="str">
         <x:v>modular_small</x:v>
@@ -42659,15 +42959,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G85" s="35" t="n">
-        <x:v>12.253404416999956</x:v>
+        <x:v>1.1633975419999842</x:v>
       </x:c>
       <x:c r="H85" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I85" s="31"/>
-      <x:c r="J85" s="31"/>
-      <x:c r="K85" s="31"/>
-      <x:c r="L85" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I85" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J85" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K85" s="33" t="str"/>
+      <x:c r="L85" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M85" s="31"/>
       <x:c r="N85" s="31"/>
       <x:c r="O85" s="31"/>
@@ -42676,10 +42982,10 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B86" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Base</x:v>
       </x:c>
       <x:c r="C86" s="33" t="str">
         <x:v>syllogism</x:v>
@@ -42688,21 +42994,27 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E86" s="33" t="str">
-        <x:v>Yes, all bloops must be lazzies.</x:v>
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
       </x:c>
       <x:c r="F86" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="G86" s="35" t="n">
-        <x:v>4.511834166999961</x:v>
+        <x:v>1.2063080000000355</x:v>
       </x:c>
       <x:c r="H86" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I86" s="31"/>
-      <x:c r="J86" s="31"/>
-      <x:c r="K86" s="31"/>
-      <x:c r="L86" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I86" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J86" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K86" s="33" t="str"/>
+      <x:c r="L86" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M86" s="31"/>
       <x:c r="N86" s="31"/>
       <x:c r="O86" s="31"/>
@@ -42711,10 +43023,10 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B87" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C87" s="33" t="str">
         <x:v>algebra</x:v>
@@ -42723,21 +43035,27 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E87" s="33" t="str">
-        <x:v>\dfrac{25}{2}</x:v>
+        <x:v>x = \frac{2</x:v>
       </x:c>
       <x:c r="F87" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G87" s="35" t="n">
+        <x:v>3.089125250000052</x:v>
+      </x:c>
+      <x:c r="H87" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I87" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G87" s="35" t="n">
-        <x:v>16.656210082999962</x:v>
-      </x:c>
-      <x:c r="H87" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I87" s="31"/>
-      <x:c r="J87" s="31"/>
-      <x:c r="K87" s="31"/>
-      <x:c r="L87" s="31"/>
+      <x:c r="J87" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K87" s="33" t="str"/>
+      <x:c r="L87" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M87" s="31"/>
       <x:c r="N87" s="31"/>
       <x:c r="O87" s="31"/>
@@ -42746,10 +43064,10 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B88" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C88" s="33" t="str">
         <x:v>markup</x:v>
@@ -42758,21 +43076,27 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E88" s="33" t="str">
-        <x:v>96</x:v>
+        <x:v>= 1.00x \times 0.80 = 0.80x</x:v>
       </x:c>
       <x:c r="F88" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G88" s="35" t="n">
+        <x:v>3.095456208000087</x:v>
+      </x:c>
+      <x:c r="H88" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I88" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G88" s="35" t="n">
-        <x:v>12.64156225000005</x:v>
-      </x:c>
-      <x:c r="H88" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I88" s="31"/>
-      <x:c r="J88" s="31"/>
-      <x:c r="K88" s="31"/>
-      <x:c r="L88" s="31"/>
+      <x:c r="J88" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K88" s="33" t="str"/>
+      <x:c r="L88" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M88" s="31"/>
       <x:c r="N88" s="31"/>
       <x:c r="O88" s="31"/>
@@ -42781,10 +43105,10 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B89" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C89" s="33" t="str">
         <x:v>boxes</x:v>
@@ -42793,21 +43117,27 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E89" s="33" t="str">
-        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
+        <x:v>'- **Or</x:v>
       </x:c>
       <x:c r="F89" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G89" s="35" t="n">
+        <x:v>3.1302385419999155</x:v>
+      </x:c>
+      <x:c r="H89" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I89" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G89" s="35" t="n">
-        <x:v>19.97141316599999</x:v>
-      </x:c>
-      <x:c r="H89" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I89" s="31"/>
-      <x:c r="J89" s="31"/>
-      <x:c r="K89" s="31"/>
-      <x:c r="L89" s="31"/>
+      <x:c r="J89" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K89" s="33" t="str"/>
+      <x:c r="L89" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M89" s="31"/>
       <x:c r="N89" s="31"/>
       <x:c r="O89" s="31"/>
@@ -42816,10 +43146,10 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B90" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C90" s="33" t="str">
         <x:v>inclusion</x:v>
@@ -42828,21 +43158,27 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E90" s="33" t="str">
-        <x:v>80</x:v>
+        <x:v>'- $ |A| $: Numbers divisible by 3 from 1 to 2</x:v>
       </x:c>
       <x:c r="F90" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G90" s="35" t="n">
+        <x:v>3.0516290829998525</x:v>
+      </x:c>
+      <x:c r="H90" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I90" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G90" s="35" t="n">
-        <x:v>12.902716834000046</x:v>
-      </x:c>
-      <x:c r="H90" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I90" s="31"/>
-      <x:c r="J90" s="31"/>
-      <x:c r="K90" s="31"/>
-      <x:c r="L90" s="31"/>
+      <x:c r="J90" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K90" s="33" t="str"/>
+      <x:c r="L90" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M90" s="31"/>
       <x:c r="N90" s="31"/>
       <x:c r="O90" s="31"/>
@@ -42851,10 +43187,10 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B91" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C91" s="33" t="str">
         <x:v>modular</x:v>
@@ -42863,21 +43199,27 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E91" s="33" t="str">
-        <x:v>6</x:v>
+        <x:v>7^{103}</x:v>
       </x:c>
       <x:c r="F91" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G91" s="35" t="n">
+        <x:v>3.097941624999976</x:v>
+      </x:c>
+      <x:c r="H91" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I91" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G91" s="35" t="n">
-        <x:v>50.31506079099995</x:v>
-      </x:c>
-      <x:c r="H91" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I91" s="31"/>
-      <x:c r="J91" s="31"/>
-      <x:c r="K91" s="31"/>
-      <x:c r="L91" s="31"/>
+      <x:c r="J91" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K91" s="33" t="str"/>
+      <x:c r="L91" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M91" s="31"/>
       <x:c r="N91" s="31"/>
       <x:c r="O91" s="31"/>
@@ -42886,10 +43228,10 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B92" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C92" s="33" t="str">
         <x:v>work_rate</x:v>
@@ -42898,21 +43240,27 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E92" s="33" t="str">
-        <x:v>3.75</x:v>
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac{</x:v>
       </x:c>
       <x:c r="F92" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G92" s="35" t="n">
+        <x:v>3.054581416000019</x:v>
+      </x:c>
+      <x:c r="H92" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I92" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G92" s="35" t="n">
-        <x:v>33.462693083999966</x:v>
-      </x:c>
-      <x:c r="H92" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I92" s="31"/>
-      <x:c r="J92" s="31"/>
-      <x:c r="K92" s="31"/>
-      <x:c r="L92" s="31"/>
+      <x:c r="J92" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K92" s="33" t="str"/>
+      <x:c r="L92" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M92" s="31"/>
       <x:c r="N92" s="31"/>
       <x:c r="O92" s="31"/>
@@ -42921,10 +43269,10 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B93" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C93" s="33" t="str">
         <x:v>probability</x:v>
@@ -42933,21 +43281,27 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E93" s="33" t="str">
-        <x:v>\dfrac{1}{9}</x:v>
+        <x:v>$$</x:v>
       </x:c>
       <x:c r="F93" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G93" s="35" t="n">
+        <x:v>3.0579301660000056</x:v>
+      </x:c>
+      <x:c r="H93" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I93" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G93" s="35" t="n">
-        <x:v>7.085368707999919</x:v>
-      </x:c>
-      <x:c r="H93" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I93" s="31"/>
-      <x:c r="J93" s="31"/>
-      <x:c r="K93" s="31"/>
-      <x:c r="L93" s="31"/>
+      <x:c r="J93" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K93" s="33" t="str"/>
+      <x:c r="L93" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M93" s="31"/>
       <x:c r="N93" s="31"/>
       <x:c r="O93" s="31"/>
@@ -42956,10 +43310,10 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B94" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C94" s="33" t="str">
         <x:v>sequence</x:v>
@@ -42974,15 +43328,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G94" s="35" t="n">
-        <x:v>15.824353458000019</x:v>
+        <x:v>2.8091276249999737</x:v>
       </x:c>
       <x:c r="H94" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I94" s="31"/>
-      <x:c r="J94" s="31"/>
-      <x:c r="K94" s="31"/>
-      <x:c r="L94" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I94" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J94" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K94" s="33" t="str"/>
+      <x:c r="L94" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M94" s="31"/>
       <x:c r="N94" s="31"/>
       <x:c r="O94" s="31"/>
@@ -42991,10 +43351,10 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B95" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C95" s="33" t="str">
         <x:v>linear_word</x:v>
@@ -43009,15 +43369,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G95" s="35" t="n">
-        <x:v>8.149854707999907</x:v>
+        <x:v>2.622403499999791</x:v>
       </x:c>
       <x:c r="H95" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I95" s="31"/>
-      <x:c r="J95" s="31"/>
-      <x:c r="K95" s="31"/>
-      <x:c r="L95" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I95" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J95" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K95" s="33" t="str"/>
+      <x:c r="L95" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M95" s="31"/>
       <x:c r="N95" s="31"/>
       <x:c r="O95" s="31"/>
@@ -43026,10 +43392,10 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B96" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C96" s="33" t="str">
         <x:v>reverse_discount</x:v>
@@ -43044,15 +43410,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G96" s="35" t="n">
-        <x:v>6.157211500000017</x:v>
+        <x:v>2.9341864160001023</x:v>
       </x:c>
       <x:c r="H96" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I96" s="31"/>
-      <x:c r="J96" s="31"/>
-      <x:c r="K96" s="31"/>
-      <x:c r="L96" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I96" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J96" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K96" s="33" t="str"/>
+      <x:c r="L96" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M96" s="31"/>
       <x:c r="N96" s="31"/>
       <x:c r="O96" s="31"/>
@@ -43061,10 +43433,10 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B97" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C97" s="33" t="str">
         <x:v>multiples</x:v>
@@ -43073,21 +43445,27 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E97" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>'- First term:</x:v>
       </x:c>
       <x:c r="F97" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G97" s="35" t="n">
+        <x:v>3.4242983330000243</x:v>
+      </x:c>
+      <x:c r="H97" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I97" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G97" s="35" t="n">
-        <x:v>21.503388040999994</x:v>
-      </x:c>
-      <x:c r="H97" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I97" s="31"/>
-      <x:c r="J97" s="31"/>
-      <x:c r="K97" s="31"/>
-      <x:c r="L97" s="31"/>
+      <x:c r="J97" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K97" s="33" t="str"/>
+      <x:c r="L97" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M97" s="31"/>
       <x:c r="N97" s="31"/>
       <x:c r="O97" s="31"/>
@@ -43096,10 +43474,10 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B98" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C98" s="33" t="str">
         <x:v>rectangle</x:v>
@@ -43114,15 +43492,21 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G98" s="35" t="n">
-        <x:v>7.560139790999983</x:v>
+        <x:v>3.101650042000074</x:v>
       </x:c>
       <x:c r="H98" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I98" s="31"/>
-      <x:c r="J98" s="31"/>
-      <x:c r="K98" s="31"/>
-      <x:c r="L98" s="31"/>
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I98" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J98" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K98" s="33" t="str"/>
+      <x:c r="L98" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M98" s="31"/>
       <x:c r="N98" s="31"/>
       <x:c r="O98" s="31"/>
@@ -43131,10 +43515,10 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B99" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C99" s="33" t="str">
         <x:v>average</x:v>
@@ -43143,21 +43527,27 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E99" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>We are also given four of the numbers: 10, 11, 13, and</x:v>
       </x:c>
       <x:c r="F99" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G99" s="35" t="n">
+        <x:v>3.6057410830001118</x:v>
+      </x:c>
+      <x:c r="H99" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I99" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G99" s="35" t="n">
-        <x:v>8.231041165999955</x:v>
-      </x:c>
-      <x:c r="H99" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I99" s="31"/>
-      <x:c r="J99" s="31"/>
-      <x:c r="K99" s="31"/>
-      <x:c r="L99" s="31"/>
+      <x:c r="J99" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K99" s="33" t="str"/>
+      <x:c r="L99" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M99" s="31"/>
       <x:c r="N99" s="31"/>
       <x:c r="O99" s="31"/>
@@ -43166,10 +43556,10 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B100" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C100" s="33" t="str">
         <x:v>combinations</x:v>
@@ -43178,21 +43568,27 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E100" s="33" t="str">
-        <x:v>15</x:v>
+        <x:v>'- $6! = 7</x:v>
       </x:c>
       <x:c r="F100" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G100" s="35" t="n">
+        <x:v>3.55844941700002</x:v>
+      </x:c>
+      <x:c r="H100" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I100" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G100" s="35" t="n">
-        <x:v>30.73365029099989</x:v>
-      </x:c>
-      <x:c r="H100" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I100" s="31"/>
-      <x:c r="J100" s="31"/>
-      <x:c r="K100" s="31"/>
-      <x:c r="L100" s="31"/>
+      <x:c r="J100" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K100" s="33" t="str"/>
+      <x:c r="L100" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M100" s="31"/>
       <x:c r="N100" s="31"/>
       <x:c r="O100" s="31"/>
@@ -43201,10 +43597,10 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B101" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C101" s="33" t="str">
         <x:v>coins</x:v>
@@ -43213,21 +43609,27 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E101" s="33" t="str">
-        <x:v>\dfrac{3}{8}</x:v>
+        <x:v>$$</x:v>
       </x:c>
       <x:c r="F101" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G101" s="35" t="n">
+        <x:v>3.5426993330002006</x:v>
+      </x:c>
+      <x:c r="H101" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I101" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G101" s="35" t="n">
-        <x:v>11.049620875000073</x:v>
-      </x:c>
-      <x:c r="H101" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I101" s="31"/>
-      <x:c r="J101" s="31"/>
-      <x:c r="K101" s="31"/>
-      <x:c r="L101" s="31"/>
+      <x:c r="J101" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K101" s="33" t="str"/>
+      <x:c r="L101" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M101" s="31"/>
       <x:c r="N101" s="31"/>
       <x:c r="O101" s="31"/>
@@ -43236,10 +43638,10 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B102" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C102" s="33" t="str">
         <x:v>modular_small</x:v>
@@ -43248,21 +43650,27 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E102" s="33" t="str">
-        <x:v>All methods confirm that the remainder when</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F102" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G102" s="35" t="n">
+        <x:v>3.2748556660001213</x:v>
+      </x:c>
+      <x:c r="H102" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I102" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J102" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="G102" s="35" t="n">
-        <x:v>67.06586500000003</x:v>
-      </x:c>
-      <x:c r="H102" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I102" s="31"/>
-      <x:c r="J102" s="31"/>
-      <x:c r="K102" s="31"/>
-      <x:c r="L102" s="31"/>
+      <x:c r="K102" s="33" t="str"/>
+      <x:c r="L102" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M102" s="31"/>
       <x:c r="N102" s="31"/>
       <x:c r="O102" s="31"/>
@@ -43271,10 +43679,10 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B103" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C103" s="33" t="str">
         <x:v>syllogism</x:v>
@@ -43283,21 +43691,27 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E103" s="33" t="str">
-        <x:v>Yes, all bloops must be lazzies.</x:v>
+        <x:v>'- So, all bloops are</x:v>
       </x:c>
       <x:c r="F103" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G103" s="35" t="n">
+        <x:v>3.5789980419999665</x:v>
+      </x:c>
+      <x:c r="H103" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I103" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G103" s="35" t="n">
-        <x:v>8.902264708000075</x:v>
-      </x:c>
-      <x:c r="H103" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="I103" s="31"/>
-      <x:c r="J103" s="31"/>
-      <x:c r="K103" s="31"/>
-      <x:c r="L103" s="31"/>
+      <x:c r="J103" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K103" s="33" t="str"/>
+      <x:c r="L103" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
+      </x:c>
       <x:c r="M103" s="31"/>
       <x:c r="N103" s="31"/>
       <x:c r="O103" s="31"/>
@@ -43305,18 +43719,42 @@
       <x:c r="Q103" s="31"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="31"/>
-      <x:c r="B104" s="31"/>
-      <x:c r="C104" s="31"/>
-      <x:c r="D104" s="31"/>
-      <x:c r="E104" s="31"/>
-      <x:c r="F104" s="31"/>
-      <x:c r="G104" s="37"/>
-      <x:c r="H104" s="31"/>
-      <x:c r="I104" s="31"/>
-      <x:c r="J104" s="31"/>
-      <x:c r="K104" s="31"/>
-      <x:c r="L104" s="31"/>
+      <x:c r="A104" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B104" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C104" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D104" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E104" s="33" t="str">
+        <x:v>### **Step</x:v>
+      </x:c>
+      <x:c r="F104" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G104" s="35" t="n">
+        <x:v>3.921817082999951</x:v>
+      </x:c>
+      <x:c r="H104" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I104" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J104" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K104" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L104" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M104" s="31"/>
       <x:c r="N104" s="31"/>
       <x:c r="O104" s="31"/>
@@ -43324,18 +43762,42 @@
       <x:c r="Q104" s="31"/>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="31"/>
-      <x:c r="B105" s="31"/>
-      <x:c r="C105" s="31"/>
-      <x:c r="D105" s="31"/>
-      <x:c r="E105" s="31"/>
-      <x:c r="F105" s="31"/>
-      <x:c r="G105" s="37"/>
-      <x:c r="H105" s="31"/>
-      <x:c r="I105" s="31"/>
-      <x:c r="J105" s="31"/>
-      <x:c r="K105" s="31"/>
-      <x:c r="L105" s="31"/>
+      <x:c r="A105" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B105" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C105" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D105" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E105" s="33" t="str">
+        <x:v>### Step 2: Re-do the price changes</x:v>
+      </x:c>
+      <x:c r="F105" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G105" s="35" t="n">
+        <x:v>3.138619374999962</x:v>
+      </x:c>
+      <x:c r="H105" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I105" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J105" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K105" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L105" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M105" s="31"/>
       <x:c r="N105" s="31"/>
       <x:c r="O105" s="31"/>
@@ -43343,18 +43805,42 @@
       <x:c r="Q105" s="31"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="31"/>
-      <x:c r="B106" s="31"/>
-      <x:c r="C106" s="31"/>
-      <x:c r="D106" s="31"/>
-      <x:c r="E106" s="31"/>
-      <x:c r="F106" s="31"/>
-      <x:c r="G106" s="37"/>
-      <x:c r="H106" s="31"/>
-      <x:c r="I106" s="31"/>
-      <x:c r="J106" s="31"/>
-      <x:c r="K106" s="31"/>
-      <x:c r="L106" s="31"/>
+      <x:c r="A106" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B106" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C106" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D106" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E106" s="33" t="str">
+        <x:v>Now, the key is to figure out **which box is the only one that can contain the</x:v>
+      </x:c>
+      <x:c r="F106" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G106" s="35" t="n">
+        <x:v>3.320716624999932</x:v>
+      </x:c>
+      <x:c r="H106" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I106" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J106" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K106" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L106" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M106" s="31"/>
       <x:c r="N106" s="31"/>
       <x:c r="O106" s="31"/>
@@ -43362,18 +43848,42 @@
       <x:c r="Q106" s="31"/>
     </x:row>
     <x:row r="107">
-      <x:c r="A107" s="31"/>
-      <x:c r="B107" s="31"/>
-      <x:c r="C107" s="31"/>
-      <x:c r="D107" s="31"/>
-      <x:c r="E107" s="31"/>
-      <x:c r="F107" s="31"/>
-      <x:c r="G107" s="37"/>
-      <x:c r="H107" s="31"/>
-      <x:c r="I107" s="31"/>
-      <x:c r="J107" s="31"/>
-      <x:c r="K107" s="31"/>
-      <x:c r="L107" s="31"/>
+      <x:c r="A107" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B107" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C107" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D107" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E107" s="33" t="str">
+        <x:v>|A \cup B| - |C \cap (A \cup B</x:v>
+      </x:c>
+      <x:c r="F107" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G107" s="35" t="n">
+        <x:v>3.316836917000046</x:v>
+      </x:c>
+      <x:c r="H107" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I107" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J107" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K107" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L107" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M107" s="31"/>
       <x:c r="N107" s="31"/>
       <x:c r="O107" s="31"/>
@@ -43381,18 +43891,42 @@
       <x:c r="Q107" s="31"/>
     </x:row>
     <x:row r="108">
-      <x:c r="A108" s="31"/>
-      <x:c r="B108" s="31"/>
-      <x:c r="C108" s="31"/>
-      <x:c r="D108" s="31"/>
-      <x:c r="E108" s="31"/>
-      <x:c r="F108" s="31"/>
-      <x:c r="G108" s="37"/>
-      <x:c r="H108" s="31"/>
-      <x:c r="I108" s="31"/>
-      <x:c r="J108" s="31"/>
-      <x:c r="K108" s="31"/>
-      <x:c r="L108" s="31"/>
+      <x:c r="A108" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B108" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C108" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D108" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E108" s="33" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F108" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G108" s="35" t="n">
+        <x:v>3.184008416999859</x:v>
+      </x:c>
+      <x:c r="H108" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I108" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J108" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K108" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L108" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M108" s="31"/>
       <x:c r="N108" s="31"/>
       <x:c r="O108" s="31"/>
@@ -43400,18 +43934,42 @@
       <x:c r="Q108" s="31"/>
     </x:row>
     <x:row r="109">
-      <x:c r="A109" s="31"/>
-      <x:c r="B109" s="31"/>
-      <x:c r="C109" s="31"/>
-      <x:c r="D109" s="31"/>
-      <x:c r="E109" s="31"/>
-      <x:c r="F109" s="31"/>
-      <x:c r="G109" s="37"/>
-      <x:c r="H109" s="31"/>
-      <x:c r="I109" s="31"/>
-      <x:c r="J109" s="31"/>
-      <x:c r="K109" s="31"/>
-      <x:c r="L109" s="31"/>
+      <x:c r="A109" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B109" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C109" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D109" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E109" s="33" t="str">
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac{8</x:v>
+      </x:c>
+      <x:c r="F109" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G109" s="35" t="n">
+        <x:v>3.2122844169998643</x:v>
+      </x:c>
+      <x:c r="H109" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I109" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J109" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K109" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L109" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M109" s="31"/>
       <x:c r="N109" s="31"/>
       <x:c r="O109" s="31"/>
@@ -43419,18 +43977,42 @@
       <x:c r="Q109" s="31"/>
     </x:row>
     <x:row r="110">
-      <x:c r="A110" s="31"/>
-      <x:c r="B110" s="31"/>
-      <x:c r="C110" s="31"/>
-      <x:c r="D110" s="31"/>
-      <x:c r="E110" s="31"/>
-      <x:c r="F110" s="31"/>
-      <x:c r="G110" s="37"/>
-      <x:c r="H110" s="31"/>
-      <x:c r="I110" s="31"/>
-      <x:c r="J110" s="31"/>
-      <x:c r="K110" s="31"/>
-      <x:c r="L110" s="31"/>
+      <x:c r="A110" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B110" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C110" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D110" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E110" s="33" t="str">
+        <x:v>\frac{4}{36</x:v>
+      </x:c>
+      <x:c r="F110" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G110" s="35" t="n">
+        <x:v>3.1970770000000357</x:v>
+      </x:c>
+      <x:c r="H110" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I110" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J110" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K110" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L110" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M110" s="31"/>
       <x:c r="N110" s="31"/>
       <x:c r="O110" s="31"/>
@@ -43438,18 +44020,42 @@
       <x:c r="Q110" s="31"/>
     </x:row>
     <x:row r="111">
-      <x:c r="A111" s="31"/>
-      <x:c r="B111" s="31"/>
-      <x:c r="C111" s="31"/>
-      <x:c r="D111" s="31"/>
-      <x:c r="E111" s="31"/>
-      <x:c r="F111" s="31"/>
-      <x:c r="G111" s="37"/>
-      <x:c r="H111" s="31"/>
-      <x:c r="I111" s="31"/>
-      <x:c r="J111" s="31"/>
-      <x:c r="K111" s="31"/>
-      <x:c r="L111" s="31"/>
+      <x:c r="A111" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B111" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C111" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D111" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E111" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F111" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G111" s="35" t="n">
+        <x:v>2.9803552079999918</x:v>
+      </x:c>
+      <x:c r="H111" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I111" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J111" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K111" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L111" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M111" s="31"/>
       <x:c r="N111" s="31"/>
       <x:c r="O111" s="31"/>
@@ -43457,18 +44063,42 @@
       <x:c r="Q111" s="31"/>
     </x:row>
     <x:row r="112">
-      <x:c r="A112" s="31"/>
-      <x:c r="B112" s="31"/>
-      <x:c r="C112" s="31"/>
-      <x:c r="D112" s="31"/>
-      <x:c r="E112" s="31"/>
-      <x:c r="F112" s="31"/>
-      <x:c r="G112" s="37"/>
-      <x:c r="H112" s="31"/>
-      <x:c r="I112" s="31"/>
-      <x:c r="J112" s="31"/>
-      <x:c r="K112" s="31"/>
-      <x:c r="L112" s="31"/>
+      <x:c r="A112" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B112" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C112" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D112" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E112" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F112" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G112" s="35" t="n">
+        <x:v>2.7443987920000836</x:v>
+      </x:c>
+      <x:c r="H112" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I112" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J112" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K112" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L112" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M112" s="31"/>
       <x:c r="N112" s="31"/>
       <x:c r="O112" s="31"/>
@@ -43476,18 +44106,42 @@
       <x:c r="Q112" s="31"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="31"/>
-      <x:c r="B113" s="31"/>
-      <x:c r="C113" s="31"/>
-      <x:c r="D113" s="31"/>
-      <x:c r="E113" s="31"/>
-      <x:c r="F113" s="31"/>
-      <x:c r="G113" s="37"/>
-      <x:c r="H113" s="31"/>
-      <x:c r="I113" s="31"/>
-      <x:c r="J113" s="31"/>
-      <x:c r="K113" s="31"/>
-      <x:c r="L113" s="31"/>
+      <x:c r="A113" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B113" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C113" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D113" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E113" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F113" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G113" s="35" t="n">
+        <x:v>2.403762707999931</x:v>
+      </x:c>
+      <x:c r="H113" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I113" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J113" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K113" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L113" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M113" s="31"/>
       <x:c r="N113" s="31"/>
       <x:c r="O113" s="31"/>
@@ -43495,18 +44149,42 @@
       <x:c r="Q113" s="31"/>
     </x:row>
     <x:row r="114">
-      <x:c r="A114" s="31"/>
-      <x:c r="B114" s="31"/>
-      <x:c r="C114" s="31"/>
-      <x:c r="D114" s="31"/>
-      <x:c r="E114" s="31"/>
-      <x:c r="F114" s="31"/>
-      <x:c r="G114" s="37"/>
-      <x:c r="H114" s="31"/>
-      <x:c r="I114" s="31"/>
-      <x:c r="J114" s="31"/>
-      <x:c r="K114" s="31"/>
-      <x:c r="L114" s="31"/>
+      <x:c r="A114" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B114" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C114" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D114" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E114" s="33" t="str">
+        <x:v>4, 8, 12, 16,</x:v>
+      </x:c>
+      <x:c r="F114" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G114" s="35" t="n">
+        <x:v>3.1552308339998945</x:v>
+      </x:c>
+      <x:c r="H114" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I114" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J114" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K114" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L114" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M114" s="31"/>
       <x:c r="N114" s="31"/>
       <x:c r="O114" s="31"/>
@@ -43514,18 +44192,42 @@
       <x:c r="Q114" s="31"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="31"/>
-      <x:c r="B115" s="31"/>
-      <x:c r="C115" s="31"/>
-      <x:c r="D115" s="31"/>
-      <x:c r="E115" s="31"/>
-      <x:c r="F115" s="31"/>
-      <x:c r="G115" s="37"/>
-      <x:c r="H115" s="31"/>
-      <x:c r="I115" s="31"/>
-      <x:c r="J115" s="31"/>
-      <x:c r="K115" s="31"/>
-      <x:c r="L115" s="31"/>
+      <x:c r="A115" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B115" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C115" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D115" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E115" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F115" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G115" s="35" t="n">
+        <x:v>2.74628079099989</x:v>
+      </x:c>
+      <x:c r="H115" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I115" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J115" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K115" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L115" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M115" s="31"/>
       <x:c r="N115" s="31"/>
       <x:c r="O115" s="31"/>
@@ -43533,18 +44235,42 @@
       <x:c r="Q115" s="31"/>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" s="31"/>
-      <x:c r="B116" s="31"/>
-      <x:c r="C116" s="31"/>
-      <x:c r="D116" s="31"/>
-      <x:c r="E116" s="31"/>
-      <x:c r="F116" s="31"/>
-      <x:c r="G116" s="37"/>
-      <x:c r="H116" s="31"/>
-      <x:c r="I116" s="31"/>
-      <x:c r="J116" s="31"/>
-      <x:c r="K116" s="31"/>
-      <x:c r="L116" s="31"/>
+      <x:c r="A116" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B116" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C116" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D116" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E116" s="33" t="str">
+        <x:v>10 + 11 + 13 + 14</x:v>
+      </x:c>
+      <x:c r="F116" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G116" s="35" t="n">
+        <x:v>3.176684124999838</x:v>
+      </x:c>
+      <x:c r="H116" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I116" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J116" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K116" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L116" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M116" s="31"/>
       <x:c r="N116" s="31"/>
       <x:c r="O116" s="31"/>
@@ -43552,18 +44278,42 @@
       <x:c r="Q116" s="31"/>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" s="31"/>
-      <x:c r="B117" s="31"/>
-      <x:c r="C117" s="31"/>
-      <x:c r="D117" s="31"/>
-      <x:c r="E117" s="31"/>
-      <x:c r="F117" s="31"/>
-      <x:c r="G117" s="37"/>
-      <x:c r="H117" s="31"/>
-      <x:c r="I117" s="31"/>
-      <x:c r="J117" s="31"/>
-      <x:c r="K117" s="31"/>
-      <x:c r="L117" s="31"/>
+      <x:c r="A117" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B117" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C117" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D117" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E117" s="33" t="str">
+        <x:v>C(6, 2) = \frac{6 \times 5</x:v>
+      </x:c>
+      <x:c r="F117" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G117" s="35" t="n">
+        <x:v>3.192199166999899</x:v>
+      </x:c>
+      <x:c r="H117" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I117" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J117" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K117" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L117" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M117" s="31"/>
       <x:c r="N117" s="31"/>
       <x:c r="O117" s="31"/>
@@ -43571,18 +44321,42 @@
       <x:c r="Q117" s="31"/>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" s="31"/>
-      <x:c r="B118" s="31"/>
-      <x:c r="C118" s="31"/>
-      <x:c r="D118" s="31"/>
-      <x:c r="E118" s="31"/>
-      <x:c r="F118" s="31"/>
-      <x:c r="G118" s="37"/>
-      <x:c r="H118" s="31"/>
-      <x:c r="I118" s="31"/>
-      <x:c r="J118" s="31"/>
-      <x:c r="K118" s="31"/>
-      <x:c r="L118" s="31"/>
+      <x:c r="A118" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B118" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C118" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D118" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E118" s="33" t="str">
+        <x:v>'- $ p = \frac{1}{2}</x:v>
+      </x:c>
+      <x:c r="F118" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G118" s="35" t="n">
+        <x:v>3.329419375000043</x:v>
+      </x:c>
+      <x:c r="H118" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I118" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J118" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K118" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L118" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M118" s="31"/>
       <x:c r="N118" s="31"/>
       <x:c r="O118" s="31"/>
@@ -43590,18 +44364,42 @@
       <x:c r="Q118" s="31"/>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" s="31"/>
-      <x:c r="B119" s="31"/>
-      <x:c r="C119" s="31"/>
-      <x:c r="D119" s="31"/>
-      <x:c r="E119" s="31"/>
-      <x:c r="F119" s="31"/>
-      <x:c r="G119" s="37"/>
-      <x:c r="H119" s="31"/>
-      <x:c r="I119" s="31"/>
-      <x:c r="J119" s="31"/>
-      <x:c r="K119" s="31"/>
-      <x:c r="L119" s="31"/>
+      <x:c r="A119" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B119" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C119" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D119" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E119" s="33" t="str">
+        <x:v>'- $ 5^3 =</x:v>
+      </x:c>
+      <x:c r="F119" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G119" s="35" t="n">
+        <x:v>3.6277708340001027</x:v>
+      </x:c>
+      <x:c r="H119" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I119" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J119" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K119" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L119" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M119" s="31"/>
       <x:c r="N119" s="31"/>
       <x:c r="O119" s="31"/>
@@ -43609,18 +44407,42 @@
       <x:c r="Q119" s="31"/>
     </x:row>
     <x:row r="120">
-      <x:c r="A120" s="31"/>
-      <x:c r="B120" s="31"/>
-      <x:c r="C120" s="31"/>
-      <x:c r="D120" s="31"/>
-      <x:c r="E120" s="31"/>
-      <x:c r="F120" s="31"/>
-      <x:c r="G120" s="37"/>
-      <x:c r="H120" s="31"/>
-      <x:c r="I120" s="31"/>
-      <x:c r="J120" s="31"/>
-      <x:c r="K120" s="31"/>
-      <x:c r="L120" s="31"/>
+      <x:c r="A120" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B120" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C120" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D120" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E120" s="33" t="str">
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
+      </x:c>
+      <x:c r="F120" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G120" s="35" t="n">
+        <x:v>3.2941825000000335</x:v>
+      </x:c>
+      <x:c r="H120" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I120" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J120" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K120" s="33" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="L120" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
+      </x:c>
       <x:c r="M120" s="31"/>
       <x:c r="N120" s="31"/>
       <x:c r="O120" s="31"/>
@@ -43628,18 +44450,42 @@
       <x:c r="Q120" s="31"/>
     </x:row>
     <x:row r="121">
-      <x:c r="A121" s="31"/>
-      <x:c r="B121" s="31"/>
-      <x:c r="C121" s="31"/>
-      <x:c r="D121" s="31"/>
-      <x:c r="E121" s="31"/>
-      <x:c r="F121" s="31"/>
-      <x:c r="G121" s="37"/>
-      <x:c r="H121" s="31"/>
-      <x:c r="I121" s="31"/>
-      <x:c r="J121" s="31"/>
-      <x:c r="K121" s="31"/>
-      <x:c r="L121" s="31"/>
+      <x:c r="A121" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B121" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C121" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D121" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E121" s="33" t="str">
+        <x:v>### **Step 5: Divide both sides by 4</x:v>
+      </x:c>
+      <x:c r="F121" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G121" s="35" t="n">
+        <x:v>3.1032740420000664</x:v>
+      </x:c>
+      <x:c r="H121" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I121" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J121" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K121" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L121" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M121" s="31"/>
       <x:c r="N121" s="31"/>
       <x:c r="O121" s="31"/>
@@ -43647,18 +44493,42 @@
       <x:c r="Q121" s="31"/>
     </x:row>
     <x:row r="122">
-      <x:c r="A122" s="31"/>
-      <x:c r="B122" s="31"/>
-      <x:c r="C122" s="31"/>
-      <x:c r="D122" s="31"/>
-      <x:c r="E122" s="31"/>
-      <x:c r="F122" s="31"/>
-      <x:c r="G122" s="37"/>
-      <x:c r="H122" s="31"/>
-      <x:c r="I122" s="31"/>
-      <x:c r="J122" s="31"/>
-      <x:c r="K122" s="31"/>
-      <x:c r="L122" s="31"/>
+      <x:c r="A122" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B122" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C122" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D122" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E122" s="33" t="str">
+        <x:v>0.80x = 96</x:v>
+      </x:c>
+      <x:c r="F122" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G122" s="35" t="n">
+        <x:v>3.4190526249999493</x:v>
+      </x:c>
+      <x:c r="H122" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I122" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J122" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K122" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L122" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M122" s="31"/>
       <x:c r="N122" s="31"/>
       <x:c r="O122" s="31"/>
@@ -43666,18 +44536,42 @@
       <x:c r="Q122" s="31"/>
     </x:row>
     <x:row r="123">
-      <x:c r="A123" s="31"/>
-      <x:c r="B123" s="31"/>
-      <x:c r="C123" s="31"/>
-      <x:c r="D123" s="31"/>
-      <x:c r="E123" s="31"/>
-      <x:c r="F123" s="31"/>
-      <x:c r="G123" s="37"/>
-      <x:c r="H123" s="31"/>
-      <x:c r="I123" s="31"/>
-      <x:c r="J123" s="31"/>
-      <x:c r="K123" s="31"/>
-      <x:c r="L123" s="31"/>
+      <x:c r="A123" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B123" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C123" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D123" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E123" s="33" t="str">
+        <x:v>We are</x:v>
+      </x:c>
+      <x:c r="F123" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G123" s="35" t="n">
+        <x:v>3.2657574579998254</x:v>
+      </x:c>
+      <x:c r="H123" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I123" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J123" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K123" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L123" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M123" s="31"/>
       <x:c r="N123" s="31"/>
       <x:c r="O123" s="31"/>
@@ -43685,18 +44579,42 @@
       <x:c r="Q123" s="31"/>
     </x:row>
     <x:row r="124">
-      <x:c r="A124" s="31"/>
-      <x:c r="B124" s="31"/>
-      <x:c r="C124" s="31"/>
-      <x:c r="D124" s="31"/>
-      <x:c r="E124" s="31"/>
-      <x:c r="F124" s="31"/>
-      <x:c r="G124" s="37"/>
-      <x:c r="H124" s="31"/>
-      <x:c r="I124" s="31"/>
-      <x:c r="J124" s="31"/>
-      <x:c r="K124" s="31"/>
-      <x:c r="L124" s="31"/>
+      <x:c r="A124" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B124" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C124" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D124" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E124" s="33" t="str">
+        <x:v>'- $ |A \</x:v>
+      </x:c>
+      <x:c r="F124" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G124" s="35" t="n">
+        <x:v>3.2513477080001394</x:v>
+      </x:c>
+      <x:c r="H124" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I124" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J124" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K124" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L124" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M124" s="31"/>
       <x:c r="N124" s="31"/>
       <x:c r="O124" s="31"/>
@@ -43704,18 +44622,42 @@
       <x:c r="Q124" s="31"/>
     </x:row>
     <x:row r="125">
-      <x:c r="A125" s="31"/>
-      <x:c r="B125" s="31"/>
-      <x:c r="C125" s="31"/>
-      <x:c r="D125" s="31"/>
-      <x:c r="E125" s="31"/>
-      <x:c r="F125" s="31"/>
-      <x:c r="G125" s="37"/>
-      <x:c r="H125" s="31"/>
-      <x:c r="I125" s="31"/>
-      <x:c r="J125" s="31"/>
-      <x:c r="K125" s="31"/>
-      <x:c r="L125" s="31"/>
+      <x:c r="A125" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B125" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C125" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D125" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E125" s="33" t="str">
+        <x:v>7^{103} = 7^{12 \cdot 8 + 5} = (7^{12})^8 \</x:v>
+      </x:c>
+      <x:c r="F125" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G125" s="35" t="n">
+        <x:v>3.194940082999892</x:v>
+      </x:c>
+      <x:c r="H125" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I125" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J125" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K125" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L125" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M125" s="31"/>
       <x:c r="N125" s="31"/>
       <x:c r="O125" s="31"/>
@@ -43723,18 +44665,42 @@
       <x:c r="Q125" s="31"/>
     </x:row>
     <x:row r="126">
-      <x:c r="A126" s="31"/>
-      <x:c r="B126" s="31"/>
-      <x:c r="C126" s="31"/>
-      <x:c r="D126" s="31"/>
-      <x:c r="E126" s="31"/>
-      <x:c r="F126" s="31"/>
-      <x:c r="G126" s="37"/>
-      <x:c r="H126" s="31"/>
-      <x:c r="I126" s="31"/>
-      <x:c r="J126" s="31"/>
-      <x:c r="K126" s="31"/>
-      <x:c r="L126" s="31"/>
+      <x:c r="A126" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B126" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C126" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D126" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E126" s="33" t="str">
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30</x:v>
+      </x:c>
+      <x:c r="F126" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G126" s="35" t="n">
+        <x:v>3.2377627500000017</x:v>
+      </x:c>
+      <x:c r="H126" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I126" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J126" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K126" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L126" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M126" s="31"/>
       <x:c r="N126" s="31"/>
       <x:c r="O126" s="31"/>
@@ -43742,18 +44708,42 @@
       <x:c r="Q126" s="31"/>
     </x:row>
     <x:row r="127">
-      <x:c r="A127" s="31"/>
-      <x:c r="B127" s="31"/>
-      <x:c r="C127" s="31"/>
-      <x:c r="D127" s="31"/>
-      <x:c r="E127" s="31"/>
-      <x:c r="F127" s="31"/>
-      <x:c r="G127" s="37"/>
-      <x:c r="H127" s="31"/>
-      <x:c r="I127" s="31"/>
-      <x:c r="J127" s="31"/>
-      <x:c r="K127" s="31"/>
-      <x:c r="L127" s="31"/>
+      <x:c r="A127" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B127" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C127" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D127" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E127" s="33" t="str">
+        <x:v>###</x:v>
+      </x:c>
+      <x:c r="F127" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G127" s="35" t="n">
+        <x:v>3.141771791999872</x:v>
+      </x:c>
+      <x:c r="H127" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I127" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J127" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K127" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L127" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M127" s="31"/>
       <x:c r="N127" s="31"/>
       <x:c r="O127" s="31"/>
@@ -43761,18 +44751,42 @@
       <x:c r="Q127" s="31"/>
     </x:row>
     <x:row r="128">
-      <x:c r="A128" s="31"/>
-      <x:c r="B128" s="31"/>
-      <x:c r="C128" s="31"/>
-      <x:c r="D128" s="31"/>
-      <x:c r="E128" s="31"/>
-      <x:c r="F128" s="31"/>
-      <x:c r="G128" s="37"/>
-      <x:c r="H128" s="31"/>
-      <x:c r="I128" s="31"/>
-      <x:c r="J128" s="31"/>
-      <x:c r="K128" s="31"/>
-      <x:c r="L128" s="31"/>
+      <x:c r="A128" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B128" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C128" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D128" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E128" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F128" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G128" s="35" t="n">
+        <x:v>2.5774544580001475</x:v>
+      </x:c>
+      <x:c r="H128" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I128" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J128" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K128" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L128" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M128" s="31"/>
       <x:c r="N128" s="31"/>
       <x:c r="O128" s="31"/>
@@ -43780,18 +44794,42 @@
       <x:c r="Q128" s="31"/>
     </x:row>
     <x:row r="129">
-      <x:c r="A129" s="31"/>
-      <x:c r="B129" s="31"/>
-      <x:c r="C129" s="31"/>
-      <x:c r="D129" s="31"/>
-      <x:c r="E129" s="31"/>
-      <x:c r="F129" s="31"/>
-      <x:c r="G129" s="37"/>
-      <x:c r="H129" s="31"/>
-      <x:c r="I129" s="31"/>
-      <x:c r="J129" s="31"/>
-      <x:c r="K129" s="31"/>
-      <x:c r="L129" s="31"/>
+      <x:c r="A129" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B129" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C129" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D129" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E129" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F129" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G129" s="35" t="n">
+        <x:v>2.598009707999836</x:v>
+      </x:c>
+      <x:c r="H129" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I129" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J129" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K129" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L129" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M129" s="31"/>
       <x:c r="N129" s="31"/>
       <x:c r="O129" s="31"/>
@@ -43799,18 +44837,42 @@
       <x:c r="Q129" s="31"/>
     </x:row>
     <x:row r="130">
-      <x:c r="A130" s="31"/>
-      <x:c r="B130" s="31"/>
-      <x:c r="C130" s="31"/>
-      <x:c r="D130" s="31"/>
-      <x:c r="E130" s="31"/>
-      <x:c r="F130" s="31"/>
-      <x:c r="G130" s="37"/>
-      <x:c r="H130" s="31"/>
-      <x:c r="I130" s="31"/>
-      <x:c r="J130" s="31"/>
-      <x:c r="K130" s="31"/>
-      <x:c r="L130" s="31"/>
+      <x:c r="A130" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B130" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C130" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D130" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E130" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F130" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G130" s="35" t="n">
+        <x:v>2.1676251249998586</x:v>
+      </x:c>
+      <x:c r="H130" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I130" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J130" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K130" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L130" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M130" s="31"/>
       <x:c r="N130" s="31"/>
       <x:c r="O130" s="31"/>
@@ -43818,18 +44880,42 @@
       <x:c r="Q130" s="31"/>
     </x:row>
     <x:row r="131">
-      <x:c r="A131" s="31"/>
-      <x:c r="B131" s="31"/>
-      <x:c r="C131" s="31"/>
-      <x:c r="D131" s="31"/>
-      <x:c r="E131" s="31"/>
-      <x:c r="F131" s="31"/>
-      <x:c r="G131" s="37"/>
-      <x:c r="H131" s="31"/>
-      <x:c r="I131" s="31"/>
-      <x:c r="J131" s="31"/>
-      <x:c r="K131" s="31"/>
-      <x:c r="L131" s="31"/>
+      <x:c r="A131" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B131" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C131" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D131" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E131" s="33" t="str">
+        <x:v>We</x:v>
+      </x:c>
+      <x:c r="F131" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G131" s="35" t="n">
+        <x:v>3.1333857499998885</x:v>
+      </x:c>
+      <x:c r="H131" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I131" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J131" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K131" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L131" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M131" s="31"/>
       <x:c r="N131" s="31"/>
       <x:c r="O131" s="31"/>
@@ -43837,18 +44923,42 @@
       <x:c r="Q131" s="31"/>
     </x:row>
     <x:row r="132">
-      <x:c r="A132" s="31"/>
-      <x:c r="B132" s="31"/>
-      <x:c r="C132" s="31"/>
-      <x:c r="D132" s="31"/>
-      <x:c r="E132" s="31"/>
-      <x:c r="F132" s="31"/>
-      <x:c r="G132" s="37"/>
-      <x:c r="H132" s="31"/>
-      <x:c r="I132" s="31"/>
-      <x:c r="J132" s="31"/>
-      <x:c r="K132" s="31"/>
-      <x:c r="L132" s="31"/>
+      <x:c r="A132" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B132" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C132" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D132" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E132" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F132" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G132" s="35" t="n">
+        <x:v>2.8326213329999064</x:v>
+      </x:c>
+      <x:c r="H132" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I132" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J132" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K132" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L132" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M132" s="31"/>
       <x:c r="N132" s="31"/>
       <x:c r="O132" s="31"/>
@@ -43856,18 +44966,42 @@
       <x:c r="Q132" s="31"/>
     </x:row>
     <x:row r="133">
-      <x:c r="A133" s="31"/>
-      <x:c r="B133" s="31"/>
-      <x:c r="C133" s="31"/>
-      <x:c r="D133" s="31"/>
-      <x:c r="E133" s="31"/>
-      <x:c r="F133" s="31"/>
-      <x:c r="G133" s="37"/>
-      <x:c r="H133" s="31"/>
-      <x:c r="I133" s="31"/>
-      <x:c r="J133" s="31"/>
-      <x:c r="K133" s="31"/>
-      <x:c r="L133" s="31"/>
+      <x:c r="A133" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B133" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C133" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D133" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E133" s="33" t="str">
+        <x:v>10 + 11 + 13 + 1</x:v>
+      </x:c>
+      <x:c r="F133" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G133" s="35" t="n">
+        <x:v>3.117645125000081</x:v>
+      </x:c>
+      <x:c r="H133" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I133" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J133" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K133" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L133" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M133" s="31"/>
       <x:c r="N133" s="31"/>
       <x:c r="O133" s="31"/>
@@ -43875,18 +45009,42 @@
       <x:c r="Q133" s="31"/>
     </x:row>
     <x:row r="134">
-      <x:c r="A134" s="31"/>
-      <x:c r="B134" s="31"/>
-      <x:c r="C134" s="31"/>
-      <x:c r="D134" s="31"/>
-      <x:c r="E134" s="31"/>
-      <x:c r="F134" s="31"/>
-      <x:c r="G134" s="37"/>
-      <x:c r="H134" s="31"/>
-      <x:c r="I134" s="31"/>
-      <x:c r="J134" s="31"/>
-      <x:c r="K134" s="31"/>
-      <x:c r="L134" s="31"/>
+      <x:c r="A134" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B134" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C134" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D134" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E134" s="33" t="str">
+        <x:v>6! = 720, \quad 2! = 2</x:v>
+      </x:c>
+      <x:c r="F134" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G134" s="35" t="n">
+        <x:v>3.0924912499999664</x:v>
+      </x:c>
+      <x:c r="H134" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I134" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J134" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K134" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L134" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M134" s="31"/>
       <x:c r="N134" s="31"/>
       <x:c r="O134" s="31"/>
@@ -43894,18 +45052,42 @@
       <x:c r="Q134" s="31"/>
     </x:row>
     <x:row r="135">
-      <x:c r="A135" s="31"/>
-      <x:c r="B135" s="31"/>
-      <x:c r="C135" s="31"/>
-      <x:c r="D135" s="31"/>
-      <x:c r="E135" s="31"/>
-      <x:c r="F135" s="31"/>
-      <x:c r="G135" s="37"/>
-      <x:c r="H135" s="31"/>
-      <x:c r="I135" s="31"/>
-      <x:c r="J135" s="31"/>
-      <x:c r="K135" s="31"/>
-      <x:c r="L135" s="31"/>
+      <x:c r="A135" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B135" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C135" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D135" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E135" s="33" t="str">
+        <x:v>'- $ p = \frac{1}{2} $ (probability of success on</x:v>
+      </x:c>
+      <x:c r="F135" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G135" s="35" t="n">
+        <x:v>3.114008584000203</x:v>
+      </x:c>
+      <x:c r="H135" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I135" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J135" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K135" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L135" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M135" s="31"/>
       <x:c r="N135" s="31"/>
       <x:c r="O135" s="31"/>
@@ -43913,18 +45095,42 @@
       <x:c r="Q135" s="31"/>
     </x:row>
     <x:row r="136">
-      <x:c r="A136" s="31"/>
-      <x:c r="B136" s="31"/>
-      <x:c r="C136" s="31"/>
-      <x:c r="D136" s="31"/>
-      <x:c r="E136" s="31"/>
-      <x:c r="F136" s="31"/>
-      <x:c r="G136" s="37"/>
-      <x:c r="H136" s="31"/>
-      <x:c r="I136" s="31"/>
-      <x:c r="J136" s="31"/>
-      <x:c r="K136" s="31"/>
-      <x:c r="L136" s="31"/>
+      <x:c r="A136" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B136" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C136" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D136" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E136" s="33" t="str">
+        <x:v>'- $ 5^3 = 5^2 \times 5 = 4 \times</x:v>
+      </x:c>
+      <x:c r="F136" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G136" s="35" t="n">
+        <x:v>3.074636875000124</x:v>
+      </x:c>
+      <x:c r="H136" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I136" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J136" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K136" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L136" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M136" s="31"/>
       <x:c r="N136" s="31"/>
       <x:c r="O136" s="31"/>
@@ -43932,18 +45138,42 @@
       <x:c r="Q136" s="31"/>
     </x:row>
     <x:row r="137">
-      <x:c r="A137" s="31"/>
-      <x:c r="B137" s="31"/>
-      <x:c r="C137" s="31"/>
-      <x:c r="D137" s="31"/>
-      <x:c r="E137" s="31"/>
-      <x:c r="F137" s="31"/>
-      <x:c r="G137" s="37"/>
-      <x:c r="H137" s="31"/>
-      <x:c r="I137" s="31"/>
-      <x:c r="J137" s="31"/>
-      <x:c r="K137" s="31"/>
-      <x:c r="L137" s="31"/>
+      <x:c r="A137" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B137" s="33" t="str">
+        <x:v>Qwen-HRM</x:v>
+      </x:c>
+      <x:c r="C137" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D137" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E137" s="33" t="str">
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
+      </x:c>
+      <x:c r="F137" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G137" s="35" t="n">
+        <x:v>2.832200415999978</x:v>
+      </x:c>
+      <x:c r="H137" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I137" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J137" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K137" s="33" t="str">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="L137" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
+      </x:c>
       <x:c r="M137" s="31"/>
       <x:c r="N137" s="31"/>
       <x:c r="O137" s="31"/>
@@ -43951,18 +45181,34 @@
       <x:c r="Q137" s="31"/>
     </x:row>
     <x:row r="138">
-      <x:c r="A138" s="31"/>
-      <x:c r="B138" s="31"/>
-      <x:c r="C138" s="31"/>
-      <x:c r="D138" s="31"/>
-      <x:c r="E138" s="31"/>
-      <x:c r="F138" s="31"/>
-      <x:c r="G138" s="37"/>
-      <x:c r="H138" s="31"/>
-      <x:c r="I138" s="31"/>
-      <x:c r="J138" s="31"/>
-      <x:c r="K138" s="31"/>
-      <x:c r="L138" s="31"/>
+      <x:c r="A138" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B138" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C138" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D138" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E138" s="33" t="str">
+        <x:v>\dfrac{25}{2}</x:v>
+      </x:c>
+      <x:c r="F138" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G138" s="35" t="n">
+        <x:v>7.580443959000007</x:v>
+      </x:c>
+      <x:c r="H138" s="33" t="str"/>
+      <x:c r="I138" s="33" t="str"/>
+      <x:c r="J138" s="33" t="str"/>
+      <x:c r="K138" s="33" t="str"/>
+      <x:c r="L138" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M138" s="31"/>
       <x:c r="N138" s="31"/>
       <x:c r="O138" s="31"/>
@@ -43970,18 +45216,34 @@
       <x:c r="Q138" s="31"/>
     </x:row>
     <x:row r="139">
-      <x:c r="A139" s="31"/>
-      <x:c r="B139" s="31"/>
-      <x:c r="C139" s="31"/>
-      <x:c r="D139" s="31"/>
-      <x:c r="E139" s="31"/>
-      <x:c r="F139" s="31"/>
-      <x:c r="G139" s="37"/>
-      <x:c r="H139" s="31"/>
-      <x:c r="I139" s="31"/>
-      <x:c r="J139" s="31"/>
-      <x:c r="K139" s="31"/>
-      <x:c r="L139" s="31"/>
+      <x:c r="A139" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B139" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C139" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D139" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E139" s="33" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F139" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G139" s="35" t="n">
+        <x:v>6.407860625000012</x:v>
+      </x:c>
+      <x:c r="H139" s="33" t="str"/>
+      <x:c r="I139" s="33" t="str"/>
+      <x:c r="J139" s="33" t="str"/>
+      <x:c r="K139" s="33" t="str"/>
+      <x:c r="L139" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M139" s="31"/>
       <x:c r="N139" s="31"/>
       <x:c r="O139" s="31"/>
@@ -43989,18 +45251,34 @@
       <x:c r="Q139" s="31"/>
     </x:row>
     <x:row r="140">
-      <x:c r="A140" s="31"/>
-      <x:c r="B140" s="31"/>
-      <x:c r="C140" s="31"/>
-      <x:c r="D140" s="31"/>
-      <x:c r="E140" s="31"/>
-      <x:c r="F140" s="31"/>
-      <x:c r="G140" s="37"/>
-      <x:c r="H140" s="31"/>
-      <x:c r="I140" s="31"/>
-      <x:c r="J140" s="31"/>
-      <x:c r="K140" s="31"/>
-      <x:c r="L140" s="31"/>
+      <x:c r="A140" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B140" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C140" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D140" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E140" s="33" t="str">
+        <x:v>Mixed</x:v>
+      </x:c>
+      <x:c r="F140" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G140" s="35" t="n">
+        <x:v>6.2715228750000165</x:v>
+      </x:c>
+      <x:c r="H140" s="33" t="str"/>
+      <x:c r="I140" s="33" t="str"/>
+      <x:c r="J140" s="33" t="str"/>
+      <x:c r="K140" s="33" t="str"/>
+      <x:c r="L140" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M140" s="31"/>
       <x:c r="N140" s="31"/>
       <x:c r="O140" s="31"/>
@@ -44008,18 +45286,34 @@
       <x:c r="Q140" s="31"/>
     </x:row>
     <x:row r="141">
-      <x:c r="A141" s="31"/>
-      <x:c r="B141" s="31"/>
-      <x:c r="C141" s="31"/>
-      <x:c r="D141" s="31"/>
-      <x:c r="E141" s="31"/>
-      <x:c r="F141" s="31"/>
-      <x:c r="G141" s="37"/>
-      <x:c r="H141" s="31"/>
-      <x:c r="I141" s="31"/>
-      <x:c r="J141" s="31"/>
-      <x:c r="K141" s="31"/>
-      <x:c r="L141" s="31"/>
+      <x:c r="A141" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B141" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C141" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D141" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E141" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F141" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G141" s="35" t="n">
+        <x:v>4.775222624999998</x:v>
+      </x:c>
+      <x:c r="H141" s="33" t="str"/>
+      <x:c r="I141" s="33" t="str"/>
+      <x:c r="J141" s="33" t="str"/>
+      <x:c r="K141" s="33" t="str"/>
+      <x:c r="L141" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M141" s="31"/>
       <x:c r="N141" s="31"/>
       <x:c r="O141" s="31"/>
@@ -44027,18 +45321,34 @@
       <x:c r="Q141" s="31"/>
     </x:row>
     <x:row r="142">
-      <x:c r="A142" s="31"/>
-      <x:c r="B142" s="31"/>
-      <x:c r="C142" s="31"/>
-      <x:c r="D142" s="31"/>
-      <x:c r="E142" s="31"/>
-      <x:c r="F142" s="31"/>
-      <x:c r="G142" s="37"/>
-      <x:c r="H142" s="31"/>
-      <x:c r="I142" s="31"/>
-      <x:c r="J142" s="31"/>
-      <x:c r="K142" s="31"/>
-      <x:c r="L142" s="31"/>
+      <x:c r="A142" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B142" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C142" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D142" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E142" s="33" t="str">
+        <x:v>'- \(7^8 \equiv 9^2</x:v>
+      </x:c>
+      <x:c r="F142" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G142" s="35" t="n">
+        <x:v>14.03727679100001</x:v>
+      </x:c>
+      <x:c r="H142" s="33" t="str"/>
+      <x:c r="I142" s="33" t="str"/>
+      <x:c r="J142" s="33" t="str"/>
+      <x:c r="K142" s="33" t="str"/>
+      <x:c r="L142" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M142" s="31"/>
       <x:c r="N142" s="31"/>
       <x:c r="O142" s="31"/>
@@ -44046,18 +45356,34 @@
       <x:c r="Q142" s="31"/>
     </x:row>
     <x:row r="143">
-      <x:c r="A143" s="31"/>
-      <x:c r="B143" s="31"/>
-      <x:c r="C143" s="31"/>
-      <x:c r="D143" s="31"/>
-      <x:c r="E143" s="31"/>
-      <x:c r="F143" s="31"/>
-      <x:c r="G143" s="37"/>
-      <x:c r="H143" s="31"/>
-      <x:c r="I143" s="31"/>
-      <x:c r="J143" s="31"/>
-      <x:c r="K143" s="31"/>
-      <x:c r="L143" s="31"/>
+      <x:c r="A143" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B143" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C143" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D143" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E143" s="33" t="str">
+        <x:v>\dfrac{15}{4}</x:v>
+      </x:c>
+      <x:c r="F143" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G143" s="35" t="n">
+        <x:v>6.176148500000011</x:v>
+      </x:c>
+      <x:c r="H143" s="33" t="str"/>
+      <x:c r="I143" s="33" t="str"/>
+      <x:c r="J143" s="33" t="str"/>
+      <x:c r="K143" s="33" t="str"/>
+      <x:c r="L143" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M143" s="31"/>
       <x:c r="N143" s="31"/>
       <x:c r="O143" s="31"/>
@@ -44065,18 +45391,34 @@
       <x:c r="Q143" s="31"/>
     </x:row>
     <x:row r="144">
-      <x:c r="A144" s="31"/>
-      <x:c r="B144" s="31"/>
-      <x:c r="C144" s="31"/>
-      <x:c r="D144" s="31"/>
-      <x:c r="E144" s="31"/>
-      <x:c r="F144" s="31"/>
-      <x:c r="G144" s="37"/>
-      <x:c r="H144" s="31"/>
-      <x:c r="I144" s="31"/>
-      <x:c r="J144" s="31"/>
-      <x:c r="K144" s="31"/>
-      <x:c r="L144" s="31"/>
+      <x:c r="A144" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B144" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C144" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D144" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E144" s="33" t="str">
+        <x:v>\dfrac{1}{9}</x:v>
+      </x:c>
+      <x:c r="F144" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G144" s="35" t="n">
+        <x:v>4.10938950000002</x:v>
+      </x:c>
+      <x:c r="H144" s="33" t="str"/>
+      <x:c r="I144" s="33" t="str"/>
+      <x:c r="J144" s="33" t="str"/>
+      <x:c r="K144" s="33" t="str"/>
+      <x:c r="L144" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M144" s="31"/>
       <x:c r="N144" s="31"/>
       <x:c r="O144" s="31"/>
@@ -44084,18 +45426,34 @@
       <x:c r="Q144" s="31"/>
     </x:row>
     <x:row r="145">
-      <x:c r="A145" s="31"/>
-      <x:c r="B145" s="31"/>
-      <x:c r="C145" s="31"/>
-      <x:c r="D145" s="31"/>
-      <x:c r="E145" s="31"/>
-      <x:c r="F145" s="31"/>
-      <x:c r="G145" s="37"/>
-      <x:c r="H145" s="31"/>
-      <x:c r="I145" s="31"/>
-      <x:c r="J145" s="31"/>
-      <x:c r="K145" s="31"/>
-      <x:c r="L145" s="31"/>
+      <x:c r="A145" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B145" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C145" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D145" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E145" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F145" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G145" s="35" t="n">
+        <x:v>8.457965874999957</x:v>
+      </x:c>
+      <x:c r="H145" s="33" t="str"/>
+      <x:c r="I145" s="33" t="str"/>
+      <x:c r="J145" s="33" t="str"/>
+      <x:c r="K145" s="33" t="str"/>
+      <x:c r="L145" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M145" s="31"/>
       <x:c r="N145" s="31"/>
       <x:c r="O145" s="31"/>
@@ -44103,18 +45461,34 @@
       <x:c r="Q145" s="31"/>
     </x:row>
     <x:row r="146">
-      <x:c r="A146" s="31"/>
-      <x:c r="B146" s="31"/>
-      <x:c r="C146" s="31"/>
-      <x:c r="D146" s="31"/>
-      <x:c r="E146" s="31"/>
-      <x:c r="F146" s="31"/>
-      <x:c r="G146" s="37"/>
-      <x:c r="H146" s="31"/>
-      <x:c r="I146" s="31"/>
-      <x:c r="J146" s="31"/>
-      <x:c r="K146" s="31"/>
-      <x:c r="L146" s="31"/>
+      <x:c r="A146" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B146" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C146" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D146" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E146" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F146" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G146" s="35" t="n">
+        <x:v>4.77963704199999</x:v>
+      </x:c>
+      <x:c r="H146" s="33" t="str"/>
+      <x:c r="I146" s="33" t="str"/>
+      <x:c r="J146" s="33" t="str"/>
+      <x:c r="K146" s="33" t="str"/>
+      <x:c r="L146" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M146" s="31"/>
       <x:c r="N146" s="31"/>
       <x:c r="O146" s="31"/>
@@ -44122,18 +45496,34 @@
       <x:c r="Q146" s="31"/>
     </x:row>
     <x:row r="147">
-      <x:c r="A147" s="31"/>
-      <x:c r="B147" s="31"/>
-      <x:c r="C147" s="31"/>
-      <x:c r="D147" s="31"/>
-      <x:c r="E147" s="31"/>
-      <x:c r="F147" s="31"/>
-      <x:c r="G147" s="37"/>
-      <x:c r="H147" s="31"/>
-      <x:c r="I147" s="31"/>
-      <x:c r="J147" s="31"/>
-      <x:c r="K147" s="31"/>
-      <x:c r="L147" s="31"/>
+      <x:c r="A147" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B147" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C147" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D147" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E147" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F147" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G147" s="35" t="n">
+        <x:v>4.465110458999959</x:v>
+      </x:c>
+      <x:c r="H147" s="33" t="str"/>
+      <x:c r="I147" s="33" t="str"/>
+      <x:c r="J147" s="33" t="str"/>
+      <x:c r="K147" s="33" t="str"/>
+      <x:c r="L147" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M147" s="31"/>
       <x:c r="N147" s="31"/>
       <x:c r="O147" s="31"/>
@@ -44141,18 +45531,34 @@
       <x:c r="Q147" s="31"/>
     </x:row>
     <x:row r="148">
-      <x:c r="A148" s="31"/>
-      <x:c r="B148" s="31"/>
-      <x:c r="C148" s="31"/>
-      <x:c r="D148" s="31"/>
-      <x:c r="E148" s="31"/>
-      <x:c r="F148" s="31"/>
-      <x:c r="G148" s="37"/>
-      <x:c r="H148" s="31"/>
-      <x:c r="I148" s="31"/>
-      <x:c r="J148" s="31"/>
-      <x:c r="K148" s="31"/>
-      <x:c r="L148" s="31"/>
+      <x:c r="A148" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B148" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C148" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D148" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E148" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F148" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G148" s="35" t="n">
+        <x:v>4.0312850840000465</x:v>
+      </x:c>
+      <x:c r="H148" s="33" t="str"/>
+      <x:c r="I148" s="33" t="str"/>
+      <x:c r="J148" s="33" t="str"/>
+      <x:c r="K148" s="33" t="str"/>
+      <x:c r="L148" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M148" s="31"/>
       <x:c r="N148" s="31"/>
       <x:c r="O148" s="31"/>
@@ -44160,18 +45566,34 @@
       <x:c r="Q148" s="31"/>
     </x:row>
     <x:row r="149">
-      <x:c r="A149" s="31"/>
-      <x:c r="B149" s="31"/>
-      <x:c r="C149" s="31"/>
-      <x:c r="D149" s="31"/>
-      <x:c r="E149" s="31"/>
-      <x:c r="F149" s="31"/>
-      <x:c r="G149" s="37"/>
-      <x:c r="H149" s="31"/>
-      <x:c r="I149" s="31"/>
-      <x:c r="J149" s="31"/>
-      <x:c r="K149" s="31"/>
-      <x:c r="L149" s="31"/>
+      <x:c r="A149" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B149" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C149" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D149" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E149" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F149" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G149" s="35" t="n">
+        <x:v>4.098184124999989</x:v>
+      </x:c>
+      <x:c r="H149" s="33" t="str"/>
+      <x:c r="I149" s="33" t="str"/>
+      <x:c r="J149" s="33" t="str"/>
+      <x:c r="K149" s="33" t="str"/>
+      <x:c r="L149" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M149" s="31"/>
       <x:c r="N149" s="31"/>
       <x:c r="O149" s="31"/>
@@ -44179,18 +45601,34 @@
       <x:c r="Q149" s="31"/>
     </x:row>
     <x:row r="150">
-      <x:c r="A150" s="31"/>
-      <x:c r="B150" s="31"/>
-      <x:c r="C150" s="31"/>
-      <x:c r="D150" s="31"/>
-      <x:c r="E150" s="31"/>
-      <x:c r="F150" s="31"/>
-      <x:c r="G150" s="37"/>
-      <x:c r="H150" s="31"/>
-      <x:c r="I150" s="31"/>
-      <x:c r="J150" s="31"/>
-      <x:c r="K150" s="31"/>
-      <x:c r="L150" s="31"/>
+      <x:c r="A150" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B150" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C150" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D150" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E150" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F150" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G150" s="35" t="n">
+        <x:v>3.955258875000027</x:v>
+      </x:c>
+      <x:c r="H150" s="33" t="str"/>
+      <x:c r="I150" s="33" t="str"/>
+      <x:c r="J150" s="33" t="str"/>
+      <x:c r="K150" s="33" t="str"/>
+      <x:c r="L150" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M150" s="31"/>
       <x:c r="N150" s="31"/>
       <x:c r="O150" s="31"/>
@@ -44198,18 +45636,34 @@
       <x:c r="Q150" s="31"/>
     </x:row>
     <x:row r="151">
-      <x:c r="A151" s="31"/>
-      <x:c r="B151" s="31"/>
-      <x:c r="C151" s="31"/>
-      <x:c r="D151" s="31"/>
-      <x:c r="E151" s="31"/>
-      <x:c r="F151" s="31"/>
-      <x:c r="G151" s="37"/>
-      <x:c r="H151" s="31"/>
-      <x:c r="I151" s="31"/>
-      <x:c r="J151" s="31"/>
-      <x:c r="K151" s="31"/>
-      <x:c r="L151" s="31"/>
+      <x:c r="A151" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B151" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C151" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D151" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E151" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F151" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G151" s="35" t="n">
+        <x:v>6.499252583999976</x:v>
+      </x:c>
+      <x:c r="H151" s="33" t="str"/>
+      <x:c r="I151" s="33" t="str"/>
+      <x:c r="J151" s="33" t="str"/>
+      <x:c r="K151" s="33" t="str"/>
+      <x:c r="L151" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M151" s="31"/>
       <x:c r="N151" s="31"/>
       <x:c r="O151" s="31"/>
@@ -44217,18 +45671,34 @@
       <x:c r="Q151" s="31"/>
     </x:row>
     <x:row r="152">
-      <x:c r="A152" s="31"/>
-      <x:c r="B152" s="31"/>
-      <x:c r="C152" s="31"/>
-      <x:c r="D152" s="31"/>
-      <x:c r="E152" s="31"/>
-      <x:c r="F152" s="31"/>
-      <x:c r="G152" s="37"/>
-      <x:c r="H152" s="31"/>
-      <x:c r="I152" s="31"/>
-      <x:c r="J152" s="31"/>
-      <x:c r="K152" s="31"/>
-      <x:c r="L152" s="31"/>
+      <x:c r="A152" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B152" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C152" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D152" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E152" s="33" t="str">
+        <x:v>\dfrac{3}{8}</x:v>
+      </x:c>
+      <x:c r="F152" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G152" s="35" t="n">
+        <x:v>2.2782300830000395</x:v>
+      </x:c>
+      <x:c r="H152" s="33" t="str"/>
+      <x:c r="I152" s="33" t="str"/>
+      <x:c r="J152" s="33" t="str"/>
+      <x:c r="K152" s="33" t="str"/>
+      <x:c r="L152" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M152" s="31"/>
       <x:c r="N152" s="31"/>
       <x:c r="O152" s="31"/>
@@ -44236,18 +45706,34 @@
       <x:c r="Q152" s="31"/>
     </x:row>
     <x:row r="153">
-      <x:c r="A153" s="31"/>
-      <x:c r="B153" s="31"/>
-      <x:c r="C153" s="31"/>
-      <x:c r="D153" s="31"/>
-      <x:c r="E153" s="31"/>
-      <x:c r="F153" s="31"/>
-      <x:c r="G153" s="37"/>
-      <x:c r="H153" s="31"/>
-      <x:c r="I153" s="31"/>
-      <x:c r="J153" s="31"/>
-      <x:c r="K153" s="31"/>
-      <x:c r="L153" s="31"/>
+      <x:c r="A153" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B153" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C153" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D153" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E153" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F153" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G153" s="35" t="n">
+        <x:v>12.253404416999956</x:v>
+      </x:c>
+      <x:c r="H153" s="33" t="str"/>
+      <x:c r="I153" s="33" t="str"/>
+      <x:c r="J153" s="33" t="str"/>
+      <x:c r="K153" s="33" t="str"/>
+      <x:c r="L153" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M153" s="31"/>
       <x:c r="N153" s="31"/>
       <x:c r="O153" s="31"/>
@@ -44255,18 +45741,34 @@
       <x:c r="Q153" s="31"/>
     </x:row>
     <x:row r="154">
-      <x:c r="A154" s="31"/>
-      <x:c r="B154" s="31"/>
-      <x:c r="C154" s="31"/>
-      <x:c r="D154" s="31"/>
-      <x:c r="E154" s="31"/>
-      <x:c r="F154" s="31"/>
-      <x:c r="G154" s="37"/>
-      <x:c r="H154" s="31"/>
-      <x:c r="I154" s="31"/>
-      <x:c r="J154" s="31"/>
-      <x:c r="K154" s="31"/>
-      <x:c r="L154" s="31"/>
+      <x:c r="A154" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B154" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C154" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D154" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E154" s="33" t="str">
+        <x:v>Yes, all bloops must be lazzies.</x:v>
+      </x:c>
+      <x:c r="F154" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G154" s="35" t="n">
+        <x:v>4.511834166999961</x:v>
+      </x:c>
+      <x:c r="H154" s="33" t="str"/>
+      <x:c r="I154" s="33" t="str"/>
+      <x:c r="J154" s="33" t="str"/>
+      <x:c r="K154" s="33" t="str"/>
+      <x:c r="L154" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="M154" s="31"/>
       <x:c r="N154" s="31"/>
       <x:c r="O154" s="31"/>
@@ -44274,18 +45776,34 @@
       <x:c r="Q154" s="31"/>
     </x:row>
     <x:row r="155">
-      <x:c r="A155" s="31"/>
-      <x:c r="B155" s="31"/>
-      <x:c r="C155" s="31"/>
-      <x:c r="D155" s="31"/>
-      <x:c r="E155" s="31"/>
-      <x:c r="F155" s="31"/>
-      <x:c r="G155" s="37"/>
-      <x:c r="H155" s="31"/>
-      <x:c r="I155" s="31"/>
-      <x:c r="J155" s="31"/>
-      <x:c r="K155" s="31"/>
-      <x:c r="L155" s="31"/>
+      <x:c r="A155" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B155" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C155" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D155" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E155" s="33" t="str">
+        <x:v>\dfrac{25}{2}</x:v>
+      </x:c>
+      <x:c r="F155" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G155" s="35" t="n">
+        <x:v>16.656210082999962</x:v>
+      </x:c>
+      <x:c r="H155" s="33" t="str"/>
+      <x:c r="I155" s="33" t="str"/>
+      <x:c r="J155" s="33" t="str"/>
+      <x:c r="K155" s="33" t="str"/>
+      <x:c r="L155" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M155" s="31"/>
       <x:c r="N155" s="31"/>
       <x:c r="O155" s="31"/>
@@ -44293,18 +45811,34 @@
       <x:c r="Q155" s="31"/>
     </x:row>
     <x:row r="156">
-      <x:c r="A156" s="31"/>
-      <x:c r="B156" s="31"/>
-      <x:c r="C156" s="31"/>
-      <x:c r="D156" s="31"/>
-      <x:c r="E156" s="31"/>
-      <x:c r="F156" s="31"/>
-      <x:c r="G156" s="37"/>
-      <x:c r="H156" s="31"/>
-      <x:c r="I156" s="31"/>
-      <x:c r="J156" s="31"/>
-      <x:c r="K156" s="31"/>
-      <x:c r="L156" s="31"/>
+      <x:c r="A156" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B156" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C156" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D156" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E156" s="33" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F156" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G156" s="35" t="n">
+        <x:v>12.64156225000005</x:v>
+      </x:c>
+      <x:c r="H156" s="33" t="str"/>
+      <x:c r="I156" s="33" t="str"/>
+      <x:c r="J156" s="33" t="str"/>
+      <x:c r="K156" s="33" t="str"/>
+      <x:c r="L156" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M156" s="31"/>
       <x:c r="N156" s="31"/>
       <x:c r="O156" s="31"/>
@@ -44312,18 +45846,34 @@
       <x:c r="Q156" s="31"/>
     </x:row>
     <x:row r="157">
-      <x:c r="A157" s="31"/>
-      <x:c r="B157" s="31"/>
-      <x:c r="C157" s="31"/>
-      <x:c r="D157" s="31"/>
-      <x:c r="E157" s="31"/>
-      <x:c r="F157" s="31"/>
-      <x:c r="G157" s="37"/>
-      <x:c r="H157" s="31"/>
-      <x:c r="I157" s="31"/>
-      <x:c r="J157" s="31"/>
-      <x:c r="K157" s="31"/>
-      <x:c r="L157" s="31"/>
+      <x:c r="A157" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B157" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C157" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D157" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E157" s="33" t="str">
+        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
+      </x:c>
+      <x:c r="F157" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G157" s="35" t="n">
+        <x:v>19.97141316599999</x:v>
+      </x:c>
+      <x:c r="H157" s="33" t="str"/>
+      <x:c r="I157" s="33" t="str"/>
+      <x:c r="J157" s="33" t="str"/>
+      <x:c r="K157" s="33" t="str"/>
+      <x:c r="L157" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M157" s="31"/>
       <x:c r="N157" s="31"/>
       <x:c r="O157" s="31"/>
@@ -44331,18 +45881,34 @@
       <x:c r="Q157" s="31"/>
     </x:row>
     <x:row r="158">
-      <x:c r="A158" s="31"/>
-      <x:c r="B158" s="31"/>
-      <x:c r="C158" s="31"/>
-      <x:c r="D158" s="31"/>
-      <x:c r="E158" s="31"/>
-      <x:c r="F158" s="31"/>
-      <x:c r="G158" s="37"/>
-      <x:c r="H158" s="31"/>
-      <x:c r="I158" s="31"/>
-      <x:c r="J158" s="31"/>
-      <x:c r="K158" s="31"/>
-      <x:c r="L158" s="31"/>
+      <x:c r="A158" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B158" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C158" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D158" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E158" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F158" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G158" s="35" t="n">
+        <x:v>12.902716834000046</x:v>
+      </x:c>
+      <x:c r="H158" s="33" t="str"/>
+      <x:c r="I158" s="33" t="str"/>
+      <x:c r="J158" s="33" t="str"/>
+      <x:c r="K158" s="33" t="str"/>
+      <x:c r="L158" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M158" s="31"/>
       <x:c r="N158" s="31"/>
       <x:c r="O158" s="31"/>
@@ -44350,18 +45916,34 @@
       <x:c r="Q158" s="31"/>
     </x:row>
     <x:row r="159">
-      <x:c r="A159" s="31"/>
-      <x:c r="B159" s="31"/>
-      <x:c r="C159" s="31"/>
-      <x:c r="D159" s="31"/>
-      <x:c r="E159" s="31"/>
-      <x:c r="F159" s="31"/>
-      <x:c r="G159" s="37"/>
-      <x:c r="H159" s="31"/>
-      <x:c r="I159" s="31"/>
-      <x:c r="J159" s="31"/>
-      <x:c r="K159" s="31"/>
-      <x:c r="L159" s="31"/>
+      <x:c r="A159" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B159" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C159" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D159" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E159" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F159" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G159" s="35" t="n">
+        <x:v>50.31506079099995</x:v>
+      </x:c>
+      <x:c r="H159" s="33" t="str"/>
+      <x:c r="I159" s="33" t="str"/>
+      <x:c r="J159" s="33" t="str"/>
+      <x:c r="K159" s="33" t="str"/>
+      <x:c r="L159" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M159" s="31"/>
       <x:c r="N159" s="31"/>
       <x:c r="O159" s="31"/>
@@ -44369,18 +45951,34 @@
       <x:c r="Q159" s="31"/>
     </x:row>
     <x:row r="160">
-      <x:c r="A160" s="31"/>
-      <x:c r="B160" s="31"/>
-      <x:c r="C160" s="31"/>
-      <x:c r="D160" s="31"/>
-      <x:c r="E160" s="31"/>
-      <x:c r="F160" s="31"/>
-      <x:c r="G160" s="37"/>
-      <x:c r="H160" s="31"/>
-      <x:c r="I160" s="31"/>
-      <x:c r="J160" s="31"/>
-      <x:c r="K160" s="31"/>
-      <x:c r="L160" s="31"/>
+      <x:c r="A160" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B160" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C160" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D160" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E160" s="33" t="str">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="F160" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G160" s="35" t="n">
+        <x:v>33.462693083999966</x:v>
+      </x:c>
+      <x:c r="H160" s="33" t="str"/>
+      <x:c r="I160" s="33" t="str"/>
+      <x:c r="J160" s="33" t="str"/>
+      <x:c r="K160" s="33" t="str"/>
+      <x:c r="L160" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M160" s="31"/>
       <x:c r="N160" s="31"/>
       <x:c r="O160" s="31"/>
@@ -44388,18 +45986,34 @@
       <x:c r="Q160" s="31"/>
     </x:row>
     <x:row r="161">
-      <x:c r="A161" s="31"/>
-      <x:c r="B161" s="31"/>
-      <x:c r="C161" s="31"/>
-      <x:c r="D161" s="31"/>
-      <x:c r="E161" s="31"/>
-      <x:c r="F161" s="31"/>
-      <x:c r="G161" s="37"/>
-      <x:c r="H161" s="31"/>
-      <x:c r="I161" s="31"/>
-      <x:c r="J161" s="31"/>
-      <x:c r="K161" s="31"/>
-      <x:c r="L161" s="31"/>
+      <x:c r="A161" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B161" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C161" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D161" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E161" s="33" t="str">
+        <x:v>\dfrac{1}{9}</x:v>
+      </x:c>
+      <x:c r="F161" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G161" s="35" t="n">
+        <x:v>7.085368707999919</x:v>
+      </x:c>
+      <x:c r="H161" s="33" t="str"/>
+      <x:c r="I161" s="33" t="str"/>
+      <x:c r="J161" s="33" t="str"/>
+      <x:c r="K161" s="33" t="str"/>
+      <x:c r="L161" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M161" s="31"/>
       <x:c r="N161" s="31"/>
       <x:c r="O161" s="31"/>
@@ -44407,18 +46021,34 @@
       <x:c r="Q161" s="31"/>
     </x:row>
     <x:row r="162">
-      <x:c r="A162" s="31"/>
-      <x:c r="B162" s="31"/>
-      <x:c r="C162" s="31"/>
-      <x:c r="D162" s="31"/>
-      <x:c r="E162" s="31"/>
-      <x:c r="F162" s="31"/>
-      <x:c r="G162" s="37"/>
-      <x:c r="H162" s="31"/>
-      <x:c r="I162" s="31"/>
-      <x:c r="J162" s="31"/>
-      <x:c r="K162" s="31"/>
-      <x:c r="L162" s="31"/>
+      <x:c r="A162" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B162" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C162" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D162" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E162" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F162" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G162" s="35" t="n">
+        <x:v>15.824353458000019</x:v>
+      </x:c>
+      <x:c r="H162" s="33" t="str"/>
+      <x:c r="I162" s="33" t="str"/>
+      <x:c r="J162" s="33" t="str"/>
+      <x:c r="K162" s="33" t="str"/>
+      <x:c r="L162" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M162" s="31"/>
       <x:c r="N162" s="31"/>
       <x:c r="O162" s="31"/>
@@ -44426,18 +46056,34 @@
       <x:c r="Q162" s="31"/>
     </x:row>
     <x:row r="163">
-      <x:c r="A163" s="31"/>
-      <x:c r="B163" s="31"/>
-      <x:c r="C163" s="31"/>
-      <x:c r="D163" s="31"/>
-      <x:c r="E163" s="31"/>
-      <x:c r="F163" s="31"/>
-      <x:c r="G163" s="37"/>
-      <x:c r="H163" s="31"/>
-      <x:c r="I163" s="31"/>
-      <x:c r="J163" s="31"/>
-      <x:c r="K163" s="31"/>
-      <x:c r="L163" s="31"/>
+      <x:c r="A163" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B163" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C163" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D163" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E163" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F163" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G163" s="35" t="n">
+        <x:v>8.149854707999907</x:v>
+      </x:c>
+      <x:c r="H163" s="33" t="str"/>
+      <x:c r="I163" s="33" t="str"/>
+      <x:c r="J163" s="33" t="str"/>
+      <x:c r="K163" s="33" t="str"/>
+      <x:c r="L163" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M163" s="31"/>
       <x:c r="N163" s="31"/>
       <x:c r="O163" s="31"/>
@@ -44445,18 +46091,34 @@
       <x:c r="Q163" s="31"/>
     </x:row>
     <x:row r="164">
-      <x:c r="A164" s="31"/>
-      <x:c r="B164" s="31"/>
-      <x:c r="C164" s="31"/>
-      <x:c r="D164" s="31"/>
-      <x:c r="E164" s="31"/>
-      <x:c r="F164" s="31"/>
-      <x:c r="G164" s="37"/>
-      <x:c r="H164" s="31"/>
-      <x:c r="I164" s="31"/>
-      <x:c r="J164" s="31"/>
-      <x:c r="K164" s="31"/>
-      <x:c r="L164" s="31"/>
+      <x:c r="A164" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B164" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C164" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D164" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E164" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F164" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G164" s="35" t="n">
+        <x:v>6.157211500000017</x:v>
+      </x:c>
+      <x:c r="H164" s="33" t="str"/>
+      <x:c r="I164" s="33" t="str"/>
+      <x:c r="J164" s="33" t="str"/>
+      <x:c r="K164" s="33" t="str"/>
+      <x:c r="L164" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M164" s="31"/>
       <x:c r="N164" s="31"/>
       <x:c r="O164" s="31"/>
@@ -44464,18 +46126,34 @@
       <x:c r="Q164" s="31"/>
     </x:row>
     <x:row r="165">
-      <x:c r="A165" s="31"/>
-      <x:c r="B165" s="31"/>
-      <x:c r="C165" s="31"/>
-      <x:c r="D165" s="31"/>
-      <x:c r="E165" s="31"/>
-      <x:c r="F165" s="31"/>
-      <x:c r="G165" s="37"/>
-      <x:c r="H165" s="31"/>
-      <x:c r="I165" s="31"/>
-      <x:c r="J165" s="31"/>
-      <x:c r="K165" s="31"/>
-      <x:c r="L165" s="31"/>
+      <x:c r="A165" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B165" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C165" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D165" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E165" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F165" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G165" s="35" t="n">
+        <x:v>21.503388040999994</x:v>
+      </x:c>
+      <x:c r="H165" s="33" t="str"/>
+      <x:c r="I165" s="33" t="str"/>
+      <x:c r="J165" s="33" t="str"/>
+      <x:c r="K165" s="33" t="str"/>
+      <x:c r="L165" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M165" s="31"/>
       <x:c r="N165" s="31"/>
       <x:c r="O165" s="31"/>
@@ -44483,18 +46161,34 @@
       <x:c r="Q165" s="31"/>
     </x:row>
     <x:row r="166">
-      <x:c r="A166" s="31"/>
-      <x:c r="B166" s="31"/>
-      <x:c r="C166" s="31"/>
-      <x:c r="D166" s="31"/>
-      <x:c r="E166" s="31"/>
-      <x:c r="F166" s="31"/>
-      <x:c r="G166" s="37"/>
-      <x:c r="H166" s="31"/>
-      <x:c r="I166" s="31"/>
-      <x:c r="J166" s="31"/>
-      <x:c r="K166" s="31"/>
-      <x:c r="L166" s="31"/>
+      <x:c r="A166" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B166" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C166" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D166" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E166" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F166" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G166" s="35" t="n">
+        <x:v>7.560139790999983</x:v>
+      </x:c>
+      <x:c r="H166" s="33" t="str"/>
+      <x:c r="I166" s="33" t="str"/>
+      <x:c r="J166" s="33" t="str"/>
+      <x:c r="K166" s="33" t="str"/>
+      <x:c r="L166" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M166" s="31"/>
       <x:c r="N166" s="31"/>
       <x:c r="O166" s="31"/>
@@ -44502,18 +46196,34 @@
       <x:c r="Q166" s="31"/>
     </x:row>
     <x:row r="167">
-      <x:c r="A167" s="31"/>
-      <x:c r="B167" s="31"/>
-      <x:c r="C167" s="31"/>
-      <x:c r="D167" s="31"/>
-      <x:c r="E167" s="31"/>
-      <x:c r="F167" s="31"/>
-      <x:c r="G167" s="37"/>
-      <x:c r="H167" s="31"/>
-      <x:c r="I167" s="31"/>
-      <x:c r="J167" s="31"/>
-      <x:c r="K167" s="31"/>
-      <x:c r="L167" s="31"/>
+      <x:c r="A167" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B167" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C167" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D167" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E167" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F167" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G167" s="35" t="n">
+        <x:v>8.231041165999955</x:v>
+      </x:c>
+      <x:c r="H167" s="33" t="str"/>
+      <x:c r="I167" s="33" t="str"/>
+      <x:c r="J167" s="33" t="str"/>
+      <x:c r="K167" s="33" t="str"/>
+      <x:c r="L167" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M167" s="31"/>
       <x:c r="N167" s="31"/>
       <x:c r="O167" s="31"/>
@@ -44521,18 +46231,34 @@
       <x:c r="Q167" s="31"/>
     </x:row>
     <x:row r="168">
-      <x:c r="A168" s="31"/>
-      <x:c r="B168" s="31"/>
-      <x:c r="C168" s="31"/>
-      <x:c r="D168" s="31"/>
-      <x:c r="E168" s="31"/>
-      <x:c r="F168" s="31"/>
-      <x:c r="G168" s="37"/>
-      <x:c r="H168" s="31"/>
-      <x:c r="I168" s="31"/>
-      <x:c r="J168" s="31"/>
-      <x:c r="K168" s="31"/>
-      <x:c r="L168" s="31"/>
+      <x:c r="A168" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B168" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C168" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D168" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E168" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F168" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G168" s="35" t="n">
+        <x:v>30.73365029099989</x:v>
+      </x:c>
+      <x:c r="H168" s="33" t="str"/>
+      <x:c r="I168" s="33" t="str"/>
+      <x:c r="J168" s="33" t="str"/>
+      <x:c r="K168" s="33" t="str"/>
+      <x:c r="L168" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M168" s="31"/>
       <x:c r="N168" s="31"/>
       <x:c r="O168" s="31"/>
@@ -44540,18 +46266,34 @@
       <x:c r="Q168" s="31"/>
     </x:row>
     <x:row r="169">
-      <x:c r="A169" s="31"/>
-      <x:c r="B169" s="31"/>
-      <x:c r="C169" s="31"/>
-      <x:c r="D169" s="31"/>
-      <x:c r="E169" s="31"/>
-      <x:c r="F169" s="31"/>
-      <x:c r="G169" s="37"/>
-      <x:c r="H169" s="31"/>
-      <x:c r="I169" s="31"/>
-      <x:c r="J169" s="31"/>
-      <x:c r="K169" s="31"/>
-      <x:c r="L169" s="31"/>
+      <x:c r="A169" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B169" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C169" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D169" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E169" s="33" t="str">
+        <x:v>\dfrac{3}{8}</x:v>
+      </x:c>
+      <x:c r="F169" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G169" s="35" t="n">
+        <x:v>11.049620875000073</x:v>
+      </x:c>
+      <x:c r="H169" s="33" t="str"/>
+      <x:c r="I169" s="33" t="str"/>
+      <x:c r="J169" s="33" t="str"/>
+      <x:c r="K169" s="33" t="str"/>
+      <x:c r="L169" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M169" s="31"/>
       <x:c r="N169" s="31"/>
       <x:c r="O169" s="31"/>
@@ -44559,18 +46301,34 @@
       <x:c r="Q169" s="31"/>
     </x:row>
     <x:row r="170">
-      <x:c r="A170" s="31"/>
-      <x:c r="B170" s="31"/>
-      <x:c r="C170" s="31"/>
-      <x:c r="D170" s="31"/>
-      <x:c r="E170" s="31"/>
-      <x:c r="F170" s="31"/>
-      <x:c r="G170" s="37"/>
-      <x:c r="H170" s="31"/>
-      <x:c r="I170" s="31"/>
-      <x:c r="J170" s="31"/>
-      <x:c r="K170" s="31"/>
-      <x:c r="L170" s="31"/>
+      <x:c r="A170" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B170" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C170" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D170" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E170" s="33" t="str">
+        <x:v>All methods confirm that the remainder when</x:v>
+      </x:c>
+      <x:c r="F170" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G170" s="35" t="n">
+        <x:v>67.06586500000003</x:v>
+      </x:c>
+      <x:c r="H170" s="33" t="str"/>
+      <x:c r="I170" s="33" t="str"/>
+      <x:c r="J170" s="33" t="str"/>
+      <x:c r="K170" s="33" t="str"/>
+      <x:c r="L170" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M170" s="31"/>
       <x:c r="N170" s="31"/>
       <x:c r="O170" s="31"/>
@@ -44578,18 +46336,34 @@
       <x:c r="Q170" s="31"/>
     </x:row>
     <x:row r="171">
-      <x:c r="A171" s="31"/>
-      <x:c r="B171" s="31"/>
-      <x:c r="C171" s="31"/>
-      <x:c r="D171" s="31"/>
-      <x:c r="E171" s="31"/>
-      <x:c r="F171" s="31"/>
-      <x:c r="G171" s="37"/>
-      <x:c r="H171" s="31"/>
-      <x:c r="I171" s="31"/>
-      <x:c r="J171" s="31"/>
-      <x:c r="K171" s="31"/>
-      <x:c r="L171" s="31"/>
+      <x:c r="A171" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B171" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C171" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D171" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E171" s="33" t="str">
+        <x:v>Yes, all bloops must be lazzies.</x:v>
+      </x:c>
+      <x:c r="F171" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G171" s="35" t="n">
+        <x:v>8.902264708000075</x:v>
+      </x:c>
+      <x:c r="H171" s="33" t="str"/>
+      <x:c r="I171" s="33" t="str"/>
+      <x:c r="J171" s="33" t="str"/>
+      <x:c r="K171" s="33" t="str"/>
+      <x:c r="L171" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="M171" s="31"/>
       <x:c r="N171" s="31"/>
       <x:c r="O171" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R08085e55eaf64418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R5f17f2d6ec9942d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="Reea18092198148ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rdb45f27c4811498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R5261d6bffb54427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R470a2b0611b84815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R115ebbfbe3f54a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3fa16c7f16f442ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R8e9feec5e87a4dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R840d8c7890074c7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rc40f45fdb4984d2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R2a205f416a534ef8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="Re730bb69a1374e6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R6a2e93fa2058403c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -342,7 +342,7 @@
     <x:col min="6" max="6" width="11.65999984741211" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="41.599998474121094" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="42.939998626708984" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -888,29 +888,31 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B18" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C18" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
-      </x:c>
-      <x:c r="F18" s="33" t="str"/>
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="F18" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G18" s="35" t="n">
-        <x:v>104.68802758599998</x:v>
+        <x:v>49.364747375000206</x:v>
       </x:c>
       <x:c r="H18" s="35" t="n">
-        <x:v>6.158119269764704</x:v>
+        <x:v>2.9038086691176592</x:v>
       </x:c>
       <x:c r="I18" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
       <x:c r="J18" s="31"/>
       <x:c r="K18" s="31"/>
@@ -923,29 +925,31 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B19" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C19" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D19" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
-      </x:c>
-      <x:c r="F19" s="33" t="str"/>
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="F19" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G19" s="35" t="n">
-        <x:v>338.2124144539998</x:v>
+        <x:v>49.77078603999985</x:v>
       </x:c>
       <x:c r="H19" s="35" t="n">
-        <x:v>19.894847909058814</x:v>
+        <x:v>2.9276932964705793</x:v>
       </x:c>
       <x:c r="I19" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
       <x:c r="J19" s="31"/>
       <x:c r="K19" s="31"/>
@@ -957,15 +961,31 @@
       <x:c r="Q19" s="31"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="31"/>
-      <x:c r="B20" s="31"/>
-      <x:c r="C20" s="31"/>
-      <x:c r="D20" s="31"/>
-      <x:c r="E20" s="36"/>
-      <x:c r="F20" s="31"/>
-      <x:c r="G20" s="37"/>
-      <x:c r="H20" s="37"/>
-      <x:c r="I20" s="31"/>
+      <x:c r="A20" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B20" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C20" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D20" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E20" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F20" s="33" t="str"/>
+      <x:c r="G20" s="35" t="n">
+        <x:v>104.68802758599998</x:v>
+      </x:c>
+      <x:c r="H20" s="35" t="n">
+        <x:v>6.158119269764704</x:v>
+      </x:c>
+      <x:c r="I20" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="J20" s="31"/>
       <x:c r="K20" s="31"/>
       <x:c r="L20" s="31"/>
@@ -976,15 +996,31 @@
       <x:c r="Q20" s="31"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="31"/>
-      <x:c r="B21" s="31"/>
-      <x:c r="C21" s="31"/>
-      <x:c r="D21" s="31"/>
-      <x:c r="E21" s="36"/>
-      <x:c r="F21" s="31"/>
-      <x:c r="G21" s="37"/>
-      <x:c r="H21" s="37"/>
-      <x:c r="I21" s="31"/>
+      <x:c r="A21" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B21" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C21" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D21" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E21" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F21" s="33" t="str"/>
+      <x:c r="G21" s="35" t="n">
+        <x:v>338.2124144539998</x:v>
+      </x:c>
+      <x:c r="H21" s="35" t="n">
+        <x:v>19.894847909058814</x:v>
+      </x:c>
+      <x:c r="I21" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="J21" s="31"/>
       <x:c r="K21" s="31"/>
       <x:c r="L21" s="31"/>
@@ -33944,8 +33980,10 @@
     <x:col min="9" max="9" width="12.390000343322754" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="7.239999771118164" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="4.909999847412109" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="141.47000122070312" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="41.599998474121094" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="8.470000267028809" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="141.47000122070312" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="42.939998626708984" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -33983,13 +34021,17 @@
         <x:v>Blend</x:v>
       </x:c>
       <x:c r="L1" s="32" t="str">
+        <x:v>Fusion</x:v>
+      </x:c>
+      <x:c r="M1" s="32" t="str">
+        <x:v>Threshold</x:v>
+      </x:c>
+      <x:c r="N1" s="32" t="str">
         <x:v>Correct Cases</x:v>
       </x:c>
-      <x:c r="M1" s="32" t="str">
+      <x:c r="O1" s="32" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="N1" s="31"/>
-      <x:c r="O1" s="31"/>
       <x:c r="P1" s="31"/>
       <x:c r="Q1" s="31"/>
     </x:row>
@@ -34019,14 +34061,14 @@
       <x:c r="I2" s="33" t="str"/>
       <x:c r="J2" s="33" t="str"/>
       <x:c r="K2" s="33" t="str"/>
-      <x:c r="L2" s="33" t="str">
+      <x:c r="L2" s="33" t="str"/>
+      <x:c r="M2" s="33" t="str"/>
+      <x:c r="N2" s="33" t="str">
         <x:v>combinations</x:v>
       </x:c>
-      <x:c r="M2" s="33" t="str">
+      <x:c r="O2" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="N2" s="31"/>
-      <x:c r="O2" s="31"/>
       <x:c r="P2" s="31"/>
       <x:c r="Q2" s="31"/>
     </x:row>
@@ -34056,14 +34098,14 @@
       <x:c r="I3" s="33" t="str"/>
       <x:c r="J3" s="33" t="str"/>
       <x:c r="K3" s="33" t="str"/>
-      <x:c r="L3" s="33" t="str">
+      <x:c r="L3" s="33" t="str"/>
+      <x:c r="M3" s="33" t="str"/>
+      <x:c r="N3" s="33" t="str">
         <x:v>average, modular_small</x:v>
       </x:c>
-      <x:c r="M3" s="33" t="str">
+      <x:c r="O3" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="N3" s="31"/>
-      <x:c r="O3" s="31"/>
       <x:c r="P3" s="31"/>
       <x:c r="Q3" s="31"/>
     </x:row>
@@ -34093,14 +34135,14 @@
       <x:c r="I4" s="33" t="str"/>
       <x:c r="J4" s="33" t="str"/>
       <x:c r="K4" s="33" t="str"/>
-      <x:c r="L4" s="33" t="str">
+      <x:c r="L4" s="33" t="str"/>
+      <x:c r="M4" s="33" t="str"/>
+      <x:c r="N4" s="33" t="str">
         <x:v>boxes, probability, sequence, reverse_discount, average, coins</x:v>
       </x:c>
-      <x:c r="M4" s="33" t="str">
+      <x:c r="O4" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="N4" s="31"/>
-      <x:c r="O4" s="31"/>
       <x:c r="P4" s="31"/>
       <x:c r="Q4" s="31"/>
     </x:row>
@@ -34130,14 +34172,14 @@
       <x:c r="I5" s="33" t="str"/>
       <x:c r="J5" s="33" t="str"/>
       <x:c r="K5" s="33" t="str"/>
-      <x:c r="L5" s="33" t="str">
+      <x:c r="L5" s="33" t="str"/>
+      <x:c r="M5" s="33" t="str"/>
+      <x:c r="N5" s="33" t="str">
         <x:v>markup, boxes, probability, sequence, rectangle, coins</x:v>
       </x:c>
-      <x:c r="M5" s="33" t="str">
+      <x:c r="O5" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="N5" s="31"/>
-      <x:c r="O5" s="31"/>
       <x:c r="P5" s="31"/>
       <x:c r="Q5" s="31"/>
     </x:row>
@@ -34173,14 +34215,14 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K6" s="33" t="str"/>
-      <x:c r="L6" s="33" t="str">
+      <x:c r="L6" s="33" t="str"/>
+      <x:c r="M6" s="33" t="str"/>
+      <x:c r="N6" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
       </x:c>
-      <x:c r="M6" s="33" t="str">
+      <x:c r="O6" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="N6" s="31"/>
-      <x:c r="O6" s="31"/>
       <x:c r="P6" s="31"/>
       <x:c r="Q6" s="31"/>
     </x:row>
@@ -34216,14 +34258,14 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K7" s="33" t="str"/>
-      <x:c r="L7" s="33" t="str">
+      <x:c r="L7" s="33" t="str"/>
+      <x:c r="M7" s="33" t="str"/>
+      <x:c r="N7" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small</x:v>
       </x:c>
-      <x:c r="M7" s="33" t="str">
+      <x:c r="O7" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="N7" s="31"/>
-      <x:c r="O7" s="31"/>
       <x:c r="P7" s="31"/>
       <x:c r="Q7" s="31"/>
     </x:row>
@@ -34261,14 +34303,14 @@
       <x:c r="K8" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L8" s="33" t="str">
+      <x:c r="L8" s="33" t="str"/>
+      <x:c r="M8" s="33" t="str"/>
+      <x:c r="N8" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, syllogism</x:v>
       </x:c>
-      <x:c r="M8" s="33" t="str">
+      <x:c r="O8" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="N8" s="31"/>
-      <x:c r="O8" s="31"/>
       <x:c r="P8" s="31"/>
       <x:c r="Q8" s="31"/>
     </x:row>
@@ -34306,126 +34348,186 @@
       <x:c r="K9" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L9" s="33" t="str">
+      <x:c r="L9" s="33" t="str"/>
+      <x:c r="M9" s="33" t="str"/>
+      <x:c r="N9" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, syllogism</x:v>
       </x:c>
-      <x:c r="M9" s="33" t="str">
+      <x:c r="O9" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="N9" s="31"/>
-      <x:c r="O9" s="31"/>
       <x:c r="P9" s="31"/>
       <x:c r="Q9" s="31"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B10" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C10" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F10" s="35" t="n">
-        <x:v>104.68802758599998</x:v>
+        <x:v>49.364747375000206</x:v>
       </x:c>
       <x:c r="G10" s="35" t="n">
-        <x:v>6.158119269764704</x:v>
-      </x:c>
-      <x:c r="H10" s="33" t="str"/>
-      <x:c r="I10" s="33" t="str"/>
-      <x:c r="J10" s="33" t="str"/>
-      <x:c r="K10" s="33" t="str"/>
+        <x:v>2.9038086691176592</x:v>
+      </x:c>
+      <x:c r="H10" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I10" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J10" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K10" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L10" s="33" t="str">
-        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
+        <x:v>agreement_blend</x:v>
       </x:c>
       <x:c r="M10" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="N10" s="31"/>
-      <x:c r="O10" s="31"/>
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N10" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="O10" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="P10" s="31"/>
       <x:c r="Q10" s="31"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B11" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E11" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F11" s="35" t="n">
-        <x:v>338.2124144539998</x:v>
+        <x:v>49.77078603999985</x:v>
       </x:c>
       <x:c r="G11" s="35" t="n">
-        <x:v>19.894847909058814</x:v>
-      </x:c>
-      <x:c r="H11" s="33" t="str"/>
-      <x:c r="I11" s="33" t="str"/>
-      <x:c r="J11" s="33" t="str"/>
-      <x:c r="K11" s="33" t="str"/>
+        <x:v>2.9276932964705793</x:v>
+      </x:c>
+      <x:c r="H11" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I11" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J11" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K11" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L11" s="33" t="str">
-        <x:v>algebra, markup, boxes, inclusion, modular, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, syllogism</x:v>
+        <x:v>confidence_gate</x:v>
       </x:c>
       <x:c r="M11" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="N11" s="31"/>
-      <x:c r="O11" s="31"/>
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N11" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="O11" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="P11" s="31"/>
       <x:c r="Q11" s="31"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="31"/>
-      <x:c r="B12" s="31"/>
-      <x:c r="C12" s="31"/>
-      <x:c r="D12" s="31"/>
-      <x:c r="E12" s="36"/>
-      <x:c r="F12" s="37"/>
-      <x:c r="G12" s="37"/>
-      <x:c r="H12" s="31"/>
-      <x:c r="I12" s="31"/>
-      <x:c r="J12" s="31"/>
-      <x:c r="K12" s="31"/>
-      <x:c r="L12" s="31"/>
-      <x:c r="M12" s="31"/>
-      <x:c r="N12" s="31"/>
-      <x:c r="O12" s="31"/>
+      <x:c r="A12" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C12" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F12" s="35" t="n">
+        <x:v>104.68802758599998</x:v>
+      </x:c>
+      <x:c r="G12" s="35" t="n">
+        <x:v>6.158119269764704</x:v>
+      </x:c>
+      <x:c r="H12" s="33" t="str"/>
+      <x:c r="I12" s="33" t="str"/>
+      <x:c r="J12" s="33" t="str"/>
+      <x:c r="K12" s="33" t="str"/>
+      <x:c r="L12" s="33" t="str"/>
+      <x:c r="M12" s="33" t="str"/>
+      <x:c r="N12" s="33" t="str">
+        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="O12" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P12" s="31"/>
       <x:c r="Q12" s="31"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="31"/>
-      <x:c r="B13" s="31"/>
-      <x:c r="C13" s="31"/>
-      <x:c r="D13" s="31"/>
-      <x:c r="E13" s="36"/>
-      <x:c r="F13" s="37"/>
-      <x:c r="G13" s="37"/>
-      <x:c r="H13" s="31"/>
-      <x:c r="I13" s="31"/>
-      <x:c r="J13" s="31"/>
-      <x:c r="K13" s="31"/>
-      <x:c r="L13" s="31"/>
-      <x:c r="M13" s="31"/>
-      <x:c r="N13" s="31"/>
-      <x:c r="O13" s="31"/>
+      <x:c r="A13" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B13" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C13" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D13" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F13" s="35" t="n">
+        <x:v>338.2124144539998</x:v>
+      </x:c>
+      <x:c r="G13" s="35" t="n">
+        <x:v>19.894847909058814</x:v>
+      </x:c>
+      <x:c r="H13" s="33" t="str"/>
+      <x:c r="I13" s="33" t="str"/>
+      <x:c r="J13" s="33" t="str"/>
+      <x:c r="K13" s="33" t="str"/>
+      <x:c r="L13" s="33" t="str"/>
+      <x:c r="M13" s="33" t="str"/>
+      <x:c r="N13" s="33" t="str">
+        <x:v>algebra, markup, boxes, inclusion, modular, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, syllogism</x:v>
+      </x:c>
+      <x:c r="O13" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P13" s="31"/>
       <x:c r="Q13" s="31"/>
     </x:row>
@@ -39902,7 +40004,9 @@
     <x:col min="9" max="9" width="12.390000343322754" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="7.239999771118164" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="4.909999847412109" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="41.599998474121094" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="8.470000267028809" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="42.939998626708984" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -39940,10 +40044,14 @@
         <x:v>Blend</x:v>
       </x:c>
       <x:c r="L1" s="32" t="str">
+        <x:v>Fusion</x:v>
+      </x:c>
+      <x:c r="M1" s="32" t="str">
+        <x:v>Threshold</x:v>
+      </x:c>
+      <x:c r="N1" s="32" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="M1" s="31"/>
-      <x:c r="N1" s="31"/>
       <x:c r="O1" s="31"/>
       <x:c r="P1" s="31"/>
       <x:c r="Q1" s="31"/>
@@ -39974,11 +40082,11 @@
       <x:c r="I2" s="33" t="str"/>
       <x:c r="J2" s="33" t="str"/>
       <x:c r="K2" s="33" t="str"/>
-      <x:c r="L2" s="33" t="str">
+      <x:c r="L2" s="33" t="str"/>
+      <x:c r="M2" s="33" t="str"/>
+      <x:c r="N2" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M2" s="31"/>
-      <x:c r="N2" s="31"/>
       <x:c r="O2" s="31"/>
       <x:c r="P2" s="31"/>
       <x:c r="Q2" s="31"/>
@@ -40007,11 +40115,11 @@
       <x:c r="I3" s="33" t="str"/>
       <x:c r="J3" s="33" t="str"/>
       <x:c r="K3" s="33" t="str"/>
-      <x:c r="L3" s="33" t="str">
+      <x:c r="L3" s="33" t="str"/>
+      <x:c r="M3" s="33" t="str"/>
+      <x:c r="N3" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M3" s="31"/>
-      <x:c r="N3" s="31"/>
       <x:c r="O3" s="31"/>
       <x:c r="P3" s="31"/>
       <x:c r="Q3" s="31"/>
@@ -40042,11 +40150,11 @@
       <x:c r="I4" s="33" t="str"/>
       <x:c r="J4" s="33" t="str"/>
       <x:c r="K4" s="33" t="str"/>
-      <x:c r="L4" s="33" t="str">
+      <x:c r="L4" s="33" t="str"/>
+      <x:c r="M4" s="33" t="str"/>
+      <x:c r="N4" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M4" s="31"/>
-      <x:c r="N4" s="31"/>
       <x:c r="O4" s="31"/>
       <x:c r="P4" s="31"/>
       <x:c r="Q4" s="31"/>
@@ -40077,11 +40185,11 @@
       <x:c r="I5" s="33" t="str"/>
       <x:c r="J5" s="33" t="str"/>
       <x:c r="K5" s="33" t="str"/>
-      <x:c r="L5" s="33" t="str">
+      <x:c r="L5" s="33" t="str"/>
+      <x:c r="M5" s="33" t="str"/>
+      <x:c r="N5" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M5" s="31"/>
-      <x:c r="N5" s="31"/>
       <x:c r="O5" s="31"/>
       <x:c r="P5" s="31"/>
       <x:c r="Q5" s="31"/>
@@ -40112,11 +40220,11 @@
       <x:c r="I6" s="33" t="str"/>
       <x:c r="J6" s="33" t="str"/>
       <x:c r="K6" s="33" t="str"/>
-      <x:c r="L6" s="33" t="str">
+      <x:c r="L6" s="33" t="str"/>
+      <x:c r="M6" s="33" t="str"/>
+      <x:c r="N6" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M6" s="31"/>
-      <x:c r="N6" s="31"/>
       <x:c r="O6" s="31"/>
       <x:c r="P6" s="31"/>
       <x:c r="Q6" s="31"/>
@@ -40147,11 +40255,11 @@
       <x:c r="I7" s="33" t="str"/>
       <x:c r="J7" s="33" t="str"/>
       <x:c r="K7" s="33" t="str"/>
-      <x:c r="L7" s="33" t="str">
+      <x:c r="L7" s="33" t="str"/>
+      <x:c r="M7" s="33" t="str"/>
+      <x:c r="N7" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M7" s="31"/>
-      <x:c r="N7" s="31"/>
       <x:c r="O7" s="31"/>
       <x:c r="P7" s="31"/>
       <x:c r="Q7" s="31"/>
@@ -40182,11 +40290,11 @@
       <x:c r="I8" s="33" t="str"/>
       <x:c r="J8" s="33" t="str"/>
       <x:c r="K8" s="33" t="str"/>
-      <x:c r="L8" s="33" t="str">
+      <x:c r="L8" s="33" t="str"/>
+      <x:c r="M8" s="33" t="str"/>
+      <x:c r="N8" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M8" s="31"/>
-      <x:c r="N8" s="31"/>
       <x:c r="O8" s="31"/>
       <x:c r="P8" s="31"/>
       <x:c r="Q8" s="31"/>
@@ -40217,11 +40325,11 @@
       <x:c r="I9" s="33" t="str"/>
       <x:c r="J9" s="33" t="str"/>
       <x:c r="K9" s="33" t="str"/>
-      <x:c r="L9" s="33" t="str">
+      <x:c r="L9" s="33" t="str"/>
+      <x:c r="M9" s="33" t="str"/>
+      <x:c r="N9" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M9" s="31"/>
-      <x:c r="N9" s="31"/>
       <x:c r="O9" s="31"/>
       <x:c r="P9" s="31"/>
       <x:c r="Q9" s="31"/>
@@ -40252,11 +40360,11 @@
       <x:c r="I10" s="33" t="str"/>
       <x:c r="J10" s="33" t="str"/>
       <x:c r="K10" s="33" t="str"/>
-      <x:c r="L10" s="33" t="str">
+      <x:c r="L10" s="33" t="str"/>
+      <x:c r="M10" s="33" t="str"/>
+      <x:c r="N10" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M10" s="31"/>
-      <x:c r="N10" s="31"/>
       <x:c r="O10" s="31"/>
       <x:c r="P10" s="31"/>
       <x:c r="Q10" s="31"/>
@@ -40287,11 +40395,11 @@
       <x:c r="I11" s="33" t="str"/>
       <x:c r="J11" s="33" t="str"/>
       <x:c r="K11" s="33" t="str"/>
-      <x:c r="L11" s="33" t="str">
+      <x:c r="L11" s="33" t="str"/>
+      <x:c r="M11" s="33" t="str"/>
+      <x:c r="N11" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M11" s="31"/>
-      <x:c r="N11" s="31"/>
       <x:c r="O11" s="31"/>
       <x:c r="P11" s="31"/>
       <x:c r="Q11" s="31"/>
@@ -40322,11 +40430,11 @@
       <x:c r="I12" s="33" t="str"/>
       <x:c r="J12" s="33" t="str"/>
       <x:c r="K12" s="33" t="str"/>
-      <x:c r="L12" s="33" t="str">
+      <x:c r="L12" s="33" t="str"/>
+      <x:c r="M12" s="33" t="str"/>
+      <x:c r="N12" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M12" s="31"/>
-      <x:c r="N12" s="31"/>
       <x:c r="O12" s="31"/>
       <x:c r="P12" s="31"/>
       <x:c r="Q12" s="31"/>
@@ -40357,11 +40465,11 @@
       <x:c r="I13" s="33" t="str"/>
       <x:c r="J13" s="33" t="str"/>
       <x:c r="K13" s="33" t="str"/>
-      <x:c r="L13" s="33" t="str">
+      <x:c r="L13" s="33" t="str"/>
+      <x:c r="M13" s="33" t="str"/>
+      <x:c r="N13" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M13" s="31"/>
-      <x:c r="N13" s="31"/>
       <x:c r="O13" s="31"/>
       <x:c r="P13" s="31"/>
       <x:c r="Q13" s="31"/>
@@ -40392,11 +40500,11 @@
       <x:c r="I14" s="33" t="str"/>
       <x:c r="J14" s="33" t="str"/>
       <x:c r="K14" s="33" t="str"/>
-      <x:c r="L14" s="33" t="str">
+      <x:c r="L14" s="33" t="str"/>
+      <x:c r="M14" s="33" t="str"/>
+      <x:c r="N14" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M14" s="31"/>
-      <x:c r="N14" s="31"/>
       <x:c r="O14" s="31"/>
       <x:c r="P14" s="31"/>
       <x:c r="Q14" s="31"/>
@@ -40427,11 +40535,11 @@
       <x:c r="I15" s="33" t="str"/>
       <x:c r="J15" s="33" t="str"/>
       <x:c r="K15" s="33" t="str"/>
-      <x:c r="L15" s="33" t="str">
+      <x:c r="L15" s="33" t="str"/>
+      <x:c r="M15" s="33" t="str"/>
+      <x:c r="N15" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M15" s="31"/>
-      <x:c r="N15" s="31"/>
       <x:c r="O15" s="31"/>
       <x:c r="P15" s="31"/>
       <x:c r="Q15" s="31"/>
@@ -40462,11 +40570,11 @@
       <x:c r="I16" s="33" t="str"/>
       <x:c r="J16" s="33" t="str"/>
       <x:c r="K16" s="33" t="str"/>
-      <x:c r="L16" s="33" t="str">
+      <x:c r="L16" s="33" t="str"/>
+      <x:c r="M16" s="33" t="str"/>
+      <x:c r="N16" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M16" s="31"/>
-      <x:c r="N16" s="31"/>
       <x:c r="O16" s="31"/>
       <x:c r="P16" s="31"/>
       <x:c r="Q16" s="31"/>
@@ -40497,11 +40605,11 @@
       <x:c r="I17" s="33" t="str"/>
       <x:c r="J17" s="33" t="str"/>
       <x:c r="K17" s="33" t="str"/>
-      <x:c r="L17" s="33" t="str">
+      <x:c r="L17" s="33" t="str"/>
+      <x:c r="M17" s="33" t="str"/>
+      <x:c r="N17" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M17" s="31"/>
-      <x:c r="N17" s="31"/>
       <x:c r="O17" s="31"/>
       <x:c r="P17" s="31"/>
       <x:c r="Q17" s="31"/>
@@ -40532,11 +40640,11 @@
       <x:c r="I18" s="33" t="str"/>
       <x:c r="J18" s="33" t="str"/>
       <x:c r="K18" s="33" t="str"/>
-      <x:c r="L18" s="33" t="str">
+      <x:c r="L18" s="33" t="str"/>
+      <x:c r="M18" s="33" t="str"/>
+      <x:c r="N18" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="M18" s="31"/>
-      <x:c r="N18" s="31"/>
       <x:c r="O18" s="31"/>
       <x:c r="P18" s="31"/>
       <x:c r="Q18" s="31"/>
@@ -40567,11 +40675,11 @@
       <x:c r="I19" s="33" t="str"/>
       <x:c r="J19" s="33" t="str"/>
       <x:c r="K19" s="33" t="str"/>
-      <x:c r="L19" s="33" t="str">
+      <x:c r="L19" s="33" t="str"/>
+      <x:c r="M19" s="33" t="str"/>
+      <x:c r="N19" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M19" s="31"/>
-      <x:c r="N19" s="31"/>
       <x:c r="O19" s="31"/>
       <x:c r="P19" s="31"/>
       <x:c r="Q19" s="31"/>
@@ -40600,11 +40708,11 @@
       <x:c r="I20" s="33" t="str"/>
       <x:c r="J20" s="33" t="str"/>
       <x:c r="K20" s="33" t="str"/>
-      <x:c r="L20" s="33" t="str">
+      <x:c r="L20" s="33" t="str"/>
+      <x:c r="M20" s="33" t="str"/>
+      <x:c r="N20" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M20" s="31"/>
-      <x:c r="N20" s="31"/>
       <x:c r="O20" s="31"/>
       <x:c r="P20" s="31"/>
       <x:c r="Q20" s="31"/>
@@ -40635,11 +40743,11 @@
       <x:c r="I21" s="33" t="str"/>
       <x:c r="J21" s="33" t="str"/>
       <x:c r="K21" s="33" t="str"/>
-      <x:c r="L21" s="33" t="str">
+      <x:c r="L21" s="33" t="str"/>
+      <x:c r="M21" s="33" t="str"/>
+      <x:c r="N21" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M21" s="31"/>
-      <x:c r="N21" s="31"/>
       <x:c r="O21" s="31"/>
       <x:c r="P21" s="31"/>
       <x:c r="Q21" s="31"/>
@@ -40670,11 +40778,11 @@
       <x:c r="I22" s="33" t="str"/>
       <x:c r="J22" s="33" t="str"/>
       <x:c r="K22" s="33" t="str"/>
-      <x:c r="L22" s="33" t="str">
+      <x:c r="L22" s="33" t="str"/>
+      <x:c r="M22" s="33" t="str"/>
+      <x:c r="N22" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M22" s="31"/>
-      <x:c r="N22" s="31"/>
       <x:c r="O22" s="31"/>
       <x:c r="P22" s="31"/>
       <x:c r="Q22" s="31"/>
@@ -40705,11 +40813,11 @@
       <x:c r="I23" s="33" t="str"/>
       <x:c r="J23" s="33" t="str"/>
       <x:c r="K23" s="33" t="str"/>
-      <x:c r="L23" s="33" t="str">
+      <x:c r="L23" s="33" t="str"/>
+      <x:c r="M23" s="33" t="str"/>
+      <x:c r="N23" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M23" s="31"/>
-      <x:c r="N23" s="31"/>
       <x:c r="O23" s="31"/>
       <x:c r="P23" s="31"/>
       <x:c r="Q23" s="31"/>
@@ -40740,11 +40848,11 @@
       <x:c r="I24" s="33" t="str"/>
       <x:c r="J24" s="33" t="str"/>
       <x:c r="K24" s="33" t="str"/>
-      <x:c r="L24" s="33" t="str">
+      <x:c r="L24" s="33" t="str"/>
+      <x:c r="M24" s="33" t="str"/>
+      <x:c r="N24" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M24" s="31"/>
-      <x:c r="N24" s="31"/>
       <x:c r="O24" s="31"/>
       <x:c r="P24" s="31"/>
       <x:c r="Q24" s="31"/>
@@ -40775,11 +40883,11 @@
       <x:c r="I25" s="33" t="str"/>
       <x:c r="J25" s="33" t="str"/>
       <x:c r="K25" s="33" t="str"/>
-      <x:c r="L25" s="33" t="str">
+      <x:c r="L25" s="33" t="str"/>
+      <x:c r="M25" s="33" t="str"/>
+      <x:c r="N25" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M25" s="31"/>
-      <x:c r="N25" s="31"/>
       <x:c r="O25" s="31"/>
       <x:c r="P25" s="31"/>
       <x:c r="Q25" s="31"/>
@@ -40810,11 +40918,11 @@
       <x:c r="I26" s="33" t="str"/>
       <x:c r="J26" s="33" t="str"/>
       <x:c r="K26" s="33" t="str"/>
-      <x:c r="L26" s="33" t="str">
+      <x:c r="L26" s="33" t="str"/>
+      <x:c r="M26" s="33" t="str"/>
+      <x:c r="N26" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M26" s="31"/>
-      <x:c r="N26" s="31"/>
       <x:c r="O26" s="31"/>
       <x:c r="P26" s="31"/>
       <x:c r="Q26" s="31"/>
@@ -40845,11 +40953,11 @@
       <x:c r="I27" s="33" t="str"/>
       <x:c r="J27" s="33" t="str"/>
       <x:c r="K27" s="33" t="str"/>
-      <x:c r="L27" s="33" t="str">
+      <x:c r="L27" s="33" t="str"/>
+      <x:c r="M27" s="33" t="str"/>
+      <x:c r="N27" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M27" s="31"/>
-      <x:c r="N27" s="31"/>
       <x:c r="O27" s="31"/>
       <x:c r="P27" s="31"/>
       <x:c r="Q27" s="31"/>
@@ -40880,11 +40988,11 @@
       <x:c r="I28" s="33" t="str"/>
       <x:c r="J28" s="33" t="str"/>
       <x:c r="K28" s="33" t="str"/>
-      <x:c r="L28" s="33" t="str">
+      <x:c r="L28" s="33" t="str"/>
+      <x:c r="M28" s="33" t="str"/>
+      <x:c r="N28" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M28" s="31"/>
-      <x:c r="N28" s="31"/>
       <x:c r="O28" s="31"/>
       <x:c r="P28" s="31"/>
       <x:c r="Q28" s="31"/>
@@ -40915,11 +41023,11 @@
       <x:c r="I29" s="33" t="str"/>
       <x:c r="J29" s="33" t="str"/>
       <x:c r="K29" s="33" t="str"/>
-      <x:c r="L29" s="33" t="str">
+      <x:c r="L29" s="33" t="str"/>
+      <x:c r="M29" s="33" t="str"/>
+      <x:c r="N29" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M29" s="31"/>
-      <x:c r="N29" s="31"/>
       <x:c r="O29" s="31"/>
       <x:c r="P29" s="31"/>
       <x:c r="Q29" s="31"/>
@@ -40950,11 +41058,11 @@
       <x:c r="I30" s="33" t="str"/>
       <x:c r="J30" s="33" t="str"/>
       <x:c r="K30" s="33" t="str"/>
-      <x:c r="L30" s="33" t="str">
+      <x:c r="L30" s="33" t="str"/>
+      <x:c r="M30" s="33" t="str"/>
+      <x:c r="N30" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M30" s="31"/>
-      <x:c r="N30" s="31"/>
       <x:c r="O30" s="31"/>
       <x:c r="P30" s="31"/>
       <x:c r="Q30" s="31"/>
@@ -40985,11 +41093,11 @@
       <x:c r="I31" s="33" t="str"/>
       <x:c r="J31" s="33" t="str"/>
       <x:c r="K31" s="33" t="str"/>
-      <x:c r="L31" s="33" t="str">
+      <x:c r="L31" s="33" t="str"/>
+      <x:c r="M31" s="33" t="str"/>
+      <x:c r="N31" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M31" s="31"/>
-      <x:c r="N31" s="31"/>
       <x:c r="O31" s="31"/>
       <x:c r="P31" s="31"/>
       <x:c r="Q31" s="31"/>
@@ -41020,11 +41128,11 @@
       <x:c r="I32" s="33" t="str"/>
       <x:c r="J32" s="33" t="str"/>
       <x:c r="K32" s="33" t="str"/>
-      <x:c r="L32" s="33" t="str">
+      <x:c r="L32" s="33" t="str"/>
+      <x:c r="M32" s="33" t="str"/>
+      <x:c r="N32" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M32" s="31"/>
-      <x:c r="N32" s="31"/>
       <x:c r="O32" s="31"/>
       <x:c r="P32" s="31"/>
       <x:c r="Q32" s="31"/>
@@ -41055,11 +41163,11 @@
       <x:c r="I33" s="33" t="str"/>
       <x:c r="J33" s="33" t="str"/>
       <x:c r="K33" s="33" t="str"/>
-      <x:c r="L33" s="33" t="str">
+      <x:c r="L33" s="33" t="str"/>
+      <x:c r="M33" s="33" t="str"/>
+      <x:c r="N33" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M33" s="31"/>
-      <x:c r="N33" s="31"/>
       <x:c r="O33" s="31"/>
       <x:c r="P33" s="31"/>
       <x:c r="Q33" s="31"/>
@@ -41090,11 +41198,11 @@
       <x:c r="I34" s="33" t="str"/>
       <x:c r="J34" s="33" t="str"/>
       <x:c r="K34" s="33" t="str"/>
-      <x:c r="L34" s="33" t="str">
+      <x:c r="L34" s="33" t="str"/>
+      <x:c r="M34" s="33" t="str"/>
+      <x:c r="N34" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M34" s="31"/>
-      <x:c r="N34" s="31"/>
       <x:c r="O34" s="31"/>
       <x:c r="P34" s="31"/>
       <x:c r="Q34" s="31"/>
@@ -41125,11 +41233,11 @@
       <x:c r="I35" s="33" t="str"/>
       <x:c r="J35" s="33" t="str"/>
       <x:c r="K35" s="33" t="str"/>
-      <x:c r="L35" s="33" t="str">
+      <x:c r="L35" s="33" t="str"/>
+      <x:c r="M35" s="33" t="str"/>
+      <x:c r="N35" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M35" s="31"/>
-      <x:c r="N35" s="31"/>
       <x:c r="O35" s="31"/>
       <x:c r="P35" s="31"/>
       <x:c r="Q35" s="31"/>
@@ -41160,11 +41268,11 @@
       <x:c r="I36" s="33" t="str"/>
       <x:c r="J36" s="33" t="str"/>
       <x:c r="K36" s="33" t="str"/>
-      <x:c r="L36" s="33" t="str">
+      <x:c r="L36" s="33" t="str"/>
+      <x:c r="M36" s="33" t="str"/>
+      <x:c r="N36" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M36" s="31"/>
-      <x:c r="N36" s="31"/>
       <x:c r="O36" s="31"/>
       <x:c r="P36" s="31"/>
       <x:c r="Q36" s="31"/>
@@ -41195,11 +41303,11 @@
       <x:c r="I37" s="33" t="str"/>
       <x:c r="J37" s="33" t="str"/>
       <x:c r="K37" s="33" t="str"/>
-      <x:c r="L37" s="33" t="str">
+      <x:c r="L37" s="33" t="str"/>
+      <x:c r="M37" s="33" t="str"/>
+      <x:c r="N37" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M37" s="31"/>
-      <x:c r="N37" s="31"/>
       <x:c r="O37" s="31"/>
       <x:c r="P37" s="31"/>
       <x:c r="Q37" s="31"/>
@@ -41230,11 +41338,11 @@
       <x:c r="I38" s="33" t="str"/>
       <x:c r="J38" s="33" t="str"/>
       <x:c r="K38" s="33" t="str"/>
-      <x:c r="L38" s="33" t="str">
+      <x:c r="L38" s="33" t="str"/>
+      <x:c r="M38" s="33" t="str"/>
+      <x:c r="N38" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M38" s="31"/>
-      <x:c r="N38" s="31"/>
       <x:c r="O38" s="31"/>
       <x:c r="P38" s="31"/>
       <x:c r="Q38" s="31"/>
@@ -41265,11 +41373,11 @@
       <x:c r="I39" s="33" t="str"/>
       <x:c r="J39" s="33" t="str"/>
       <x:c r="K39" s="33" t="str"/>
-      <x:c r="L39" s="33" t="str">
+      <x:c r="L39" s="33" t="str"/>
+      <x:c r="M39" s="33" t="str"/>
+      <x:c r="N39" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M39" s="31"/>
-      <x:c r="N39" s="31"/>
       <x:c r="O39" s="31"/>
       <x:c r="P39" s="31"/>
       <x:c r="Q39" s="31"/>
@@ -41300,11 +41408,11 @@
       <x:c r="I40" s="33" t="str"/>
       <x:c r="J40" s="33" t="str"/>
       <x:c r="K40" s="33" t="str"/>
-      <x:c r="L40" s="33" t="str">
+      <x:c r="L40" s="33" t="str"/>
+      <x:c r="M40" s="33" t="str"/>
+      <x:c r="N40" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M40" s="31"/>
-      <x:c r="N40" s="31"/>
       <x:c r="O40" s="31"/>
       <x:c r="P40" s="31"/>
       <x:c r="Q40" s="31"/>
@@ -41335,11 +41443,11 @@
       <x:c r="I41" s="33" t="str"/>
       <x:c r="J41" s="33" t="str"/>
       <x:c r="K41" s="33" t="str"/>
-      <x:c r="L41" s="33" t="str">
+      <x:c r="L41" s="33" t="str"/>
+      <x:c r="M41" s="33" t="str"/>
+      <x:c r="N41" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M41" s="31"/>
-      <x:c r="N41" s="31"/>
       <x:c r="O41" s="31"/>
       <x:c r="P41" s="31"/>
       <x:c r="Q41" s="31"/>
@@ -41370,11 +41478,11 @@
       <x:c r="I42" s="33" t="str"/>
       <x:c r="J42" s="33" t="str"/>
       <x:c r="K42" s="33" t="str"/>
-      <x:c r="L42" s="33" t="str">
+      <x:c r="L42" s="33" t="str"/>
+      <x:c r="M42" s="33" t="str"/>
+      <x:c r="N42" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M42" s="31"/>
-      <x:c r="N42" s="31"/>
       <x:c r="O42" s="31"/>
       <x:c r="P42" s="31"/>
       <x:c r="Q42" s="31"/>
@@ -41405,11 +41513,11 @@
       <x:c r="I43" s="33" t="str"/>
       <x:c r="J43" s="33" t="str"/>
       <x:c r="K43" s="33" t="str"/>
-      <x:c r="L43" s="33" t="str">
+      <x:c r="L43" s="33" t="str"/>
+      <x:c r="M43" s="33" t="str"/>
+      <x:c r="N43" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M43" s="31"/>
-      <x:c r="N43" s="31"/>
       <x:c r="O43" s="31"/>
       <x:c r="P43" s="31"/>
       <x:c r="Q43" s="31"/>
@@ -41440,11 +41548,11 @@
       <x:c r="I44" s="33" t="str"/>
       <x:c r="J44" s="33" t="str"/>
       <x:c r="K44" s="33" t="str"/>
-      <x:c r="L44" s="33" t="str">
+      <x:c r="L44" s="33" t="str"/>
+      <x:c r="M44" s="33" t="str"/>
+      <x:c r="N44" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M44" s="31"/>
-      <x:c r="N44" s="31"/>
       <x:c r="O44" s="31"/>
       <x:c r="P44" s="31"/>
       <x:c r="Q44" s="31"/>
@@ -41475,11 +41583,11 @@
       <x:c r="I45" s="33" t="str"/>
       <x:c r="J45" s="33" t="str"/>
       <x:c r="K45" s="33" t="str"/>
-      <x:c r="L45" s="33" t="str">
+      <x:c r="L45" s="33" t="str"/>
+      <x:c r="M45" s="33" t="str"/>
+      <x:c r="N45" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M45" s="31"/>
-      <x:c r="N45" s="31"/>
       <x:c r="O45" s="31"/>
       <x:c r="P45" s="31"/>
       <x:c r="Q45" s="31"/>
@@ -41510,11 +41618,11 @@
       <x:c r="I46" s="33" t="str"/>
       <x:c r="J46" s="33" t="str"/>
       <x:c r="K46" s="33" t="str"/>
-      <x:c r="L46" s="33" t="str">
+      <x:c r="L46" s="33" t="str"/>
+      <x:c r="M46" s="33" t="str"/>
+      <x:c r="N46" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M46" s="31"/>
-      <x:c r="N46" s="31"/>
       <x:c r="O46" s="31"/>
       <x:c r="P46" s="31"/>
       <x:c r="Q46" s="31"/>
@@ -41545,11 +41653,11 @@
       <x:c r="I47" s="33" t="str"/>
       <x:c r="J47" s="33" t="str"/>
       <x:c r="K47" s="33" t="str"/>
-      <x:c r="L47" s="33" t="str">
+      <x:c r="L47" s="33" t="str"/>
+      <x:c r="M47" s="33" t="str"/>
+      <x:c r="N47" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M47" s="31"/>
-      <x:c r="N47" s="31"/>
       <x:c r="O47" s="31"/>
       <x:c r="P47" s="31"/>
       <x:c r="Q47" s="31"/>
@@ -41580,11 +41688,11 @@
       <x:c r="I48" s="33" t="str"/>
       <x:c r="J48" s="33" t="str"/>
       <x:c r="K48" s="33" t="str"/>
-      <x:c r="L48" s="33" t="str">
+      <x:c r="L48" s="33" t="str"/>
+      <x:c r="M48" s="33" t="str"/>
+      <x:c r="N48" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M48" s="31"/>
-      <x:c r="N48" s="31"/>
       <x:c r="O48" s="31"/>
       <x:c r="P48" s="31"/>
       <x:c r="Q48" s="31"/>
@@ -41615,11 +41723,11 @@
       <x:c r="I49" s="33" t="str"/>
       <x:c r="J49" s="33" t="str"/>
       <x:c r="K49" s="33" t="str"/>
-      <x:c r="L49" s="33" t="str">
+      <x:c r="L49" s="33" t="str"/>
+      <x:c r="M49" s="33" t="str"/>
+      <x:c r="N49" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M49" s="31"/>
-      <x:c r="N49" s="31"/>
       <x:c r="O49" s="31"/>
       <x:c r="P49" s="31"/>
       <x:c r="Q49" s="31"/>
@@ -41650,11 +41758,11 @@
       <x:c r="I50" s="33" t="str"/>
       <x:c r="J50" s="33" t="str"/>
       <x:c r="K50" s="33" t="str"/>
-      <x:c r="L50" s="33" t="str">
+      <x:c r="L50" s="33" t="str"/>
+      <x:c r="M50" s="33" t="str"/>
+      <x:c r="N50" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M50" s="31"/>
-      <x:c r="N50" s="31"/>
       <x:c r="O50" s="31"/>
       <x:c r="P50" s="31"/>
       <x:c r="Q50" s="31"/>
@@ -41685,11 +41793,11 @@
       <x:c r="I51" s="33" t="str"/>
       <x:c r="J51" s="33" t="str"/>
       <x:c r="K51" s="33" t="str"/>
-      <x:c r="L51" s="33" t="str">
+      <x:c r="L51" s="33" t="str"/>
+      <x:c r="M51" s="33" t="str"/>
+      <x:c r="N51" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M51" s="31"/>
-      <x:c r="N51" s="31"/>
       <x:c r="O51" s="31"/>
       <x:c r="P51" s="31"/>
       <x:c r="Q51" s="31"/>
@@ -41720,11 +41828,11 @@
       <x:c r="I52" s="33" t="str"/>
       <x:c r="J52" s="33" t="str"/>
       <x:c r="K52" s="33" t="str"/>
-      <x:c r="L52" s="33" t="str">
+      <x:c r="L52" s="33" t="str"/>
+      <x:c r="M52" s="33" t="str"/>
+      <x:c r="N52" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="M52" s="31"/>
-      <x:c r="N52" s="31"/>
       <x:c r="O52" s="31"/>
       <x:c r="P52" s="31"/>
       <x:c r="Q52" s="31"/>
@@ -41755,11 +41863,11 @@
       <x:c r="I53" s="33" t="str"/>
       <x:c r="J53" s="33" t="str"/>
       <x:c r="K53" s="33" t="str"/>
-      <x:c r="L53" s="33" t="str">
+      <x:c r="L53" s="33" t="str"/>
+      <x:c r="M53" s="33" t="str"/>
+      <x:c r="N53" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M53" s="31"/>
-      <x:c r="N53" s="31"/>
       <x:c r="O53" s="31"/>
       <x:c r="P53" s="31"/>
       <x:c r="Q53" s="31"/>
@@ -41790,11 +41898,11 @@
       <x:c r="I54" s="33" t="str"/>
       <x:c r="J54" s="33" t="str"/>
       <x:c r="K54" s="33" t="str"/>
-      <x:c r="L54" s="33" t="str">
+      <x:c r="L54" s="33" t="str"/>
+      <x:c r="M54" s="33" t="str"/>
+      <x:c r="N54" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M54" s="31"/>
-      <x:c r="N54" s="31"/>
       <x:c r="O54" s="31"/>
       <x:c r="P54" s="31"/>
       <x:c r="Q54" s="31"/>
@@ -41825,11 +41933,11 @@
       <x:c r="I55" s="33" t="str"/>
       <x:c r="J55" s="33" t="str"/>
       <x:c r="K55" s="33" t="str"/>
-      <x:c r="L55" s="33" t="str">
+      <x:c r="L55" s="33" t="str"/>
+      <x:c r="M55" s="33" t="str"/>
+      <x:c r="N55" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M55" s="31"/>
-      <x:c r="N55" s="31"/>
       <x:c r="O55" s="31"/>
       <x:c r="P55" s="31"/>
       <x:c r="Q55" s="31"/>
@@ -41860,11 +41968,11 @@
       <x:c r="I56" s="33" t="str"/>
       <x:c r="J56" s="33" t="str"/>
       <x:c r="K56" s="33" t="str"/>
-      <x:c r="L56" s="33" t="str">
+      <x:c r="L56" s="33" t="str"/>
+      <x:c r="M56" s="33" t="str"/>
+      <x:c r="N56" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M56" s="31"/>
-      <x:c r="N56" s="31"/>
       <x:c r="O56" s="31"/>
       <x:c r="P56" s="31"/>
       <x:c r="Q56" s="31"/>
@@ -41895,11 +42003,11 @@
       <x:c r="I57" s="33" t="str"/>
       <x:c r="J57" s="33" t="str"/>
       <x:c r="K57" s="33" t="str"/>
-      <x:c r="L57" s="33" t="str">
+      <x:c r="L57" s="33" t="str"/>
+      <x:c r="M57" s="33" t="str"/>
+      <x:c r="N57" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M57" s="31"/>
-      <x:c r="N57" s="31"/>
       <x:c r="O57" s="31"/>
       <x:c r="P57" s="31"/>
       <x:c r="Q57" s="31"/>
@@ -41930,11 +42038,11 @@
       <x:c r="I58" s="33" t="str"/>
       <x:c r="J58" s="33" t="str"/>
       <x:c r="K58" s="33" t="str"/>
-      <x:c r="L58" s="33" t="str">
+      <x:c r="L58" s="33" t="str"/>
+      <x:c r="M58" s="33" t="str"/>
+      <x:c r="N58" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M58" s="31"/>
-      <x:c r="N58" s="31"/>
       <x:c r="O58" s="31"/>
       <x:c r="P58" s="31"/>
       <x:c r="Q58" s="31"/>
@@ -41965,11 +42073,11 @@
       <x:c r="I59" s="33" t="str"/>
       <x:c r="J59" s="33" t="str"/>
       <x:c r="K59" s="33" t="str"/>
-      <x:c r="L59" s="33" t="str">
+      <x:c r="L59" s="33" t="str"/>
+      <x:c r="M59" s="33" t="str"/>
+      <x:c r="N59" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M59" s="31"/>
-      <x:c r="N59" s="31"/>
       <x:c r="O59" s="31"/>
       <x:c r="P59" s="31"/>
       <x:c r="Q59" s="31"/>
@@ -42000,11 +42108,11 @@
       <x:c r="I60" s="33" t="str"/>
       <x:c r="J60" s="33" t="str"/>
       <x:c r="K60" s="33" t="str"/>
-      <x:c r="L60" s="33" t="str">
+      <x:c r="L60" s="33" t="str"/>
+      <x:c r="M60" s="33" t="str"/>
+      <x:c r="N60" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M60" s="31"/>
-      <x:c r="N60" s="31"/>
       <x:c r="O60" s="31"/>
       <x:c r="P60" s="31"/>
       <x:c r="Q60" s="31"/>
@@ -42035,11 +42143,11 @@
       <x:c r="I61" s="33" t="str"/>
       <x:c r="J61" s="33" t="str"/>
       <x:c r="K61" s="33" t="str"/>
-      <x:c r="L61" s="33" t="str">
+      <x:c r="L61" s="33" t="str"/>
+      <x:c r="M61" s="33" t="str"/>
+      <x:c r="N61" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M61" s="31"/>
-      <x:c r="N61" s="31"/>
       <x:c r="O61" s="31"/>
       <x:c r="P61" s="31"/>
       <x:c r="Q61" s="31"/>
@@ -42070,11 +42178,11 @@
       <x:c r="I62" s="33" t="str"/>
       <x:c r="J62" s="33" t="str"/>
       <x:c r="K62" s="33" t="str"/>
-      <x:c r="L62" s="33" t="str">
+      <x:c r="L62" s="33" t="str"/>
+      <x:c r="M62" s="33" t="str"/>
+      <x:c r="N62" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M62" s="31"/>
-      <x:c r="N62" s="31"/>
       <x:c r="O62" s="31"/>
       <x:c r="P62" s="31"/>
       <x:c r="Q62" s="31"/>
@@ -42105,11 +42213,11 @@
       <x:c r="I63" s="33" t="str"/>
       <x:c r="J63" s="33" t="str"/>
       <x:c r="K63" s="33" t="str"/>
-      <x:c r="L63" s="33" t="str">
+      <x:c r="L63" s="33" t="str"/>
+      <x:c r="M63" s="33" t="str"/>
+      <x:c r="N63" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M63" s="31"/>
-      <x:c r="N63" s="31"/>
       <x:c r="O63" s="31"/>
       <x:c r="P63" s="31"/>
       <x:c r="Q63" s="31"/>
@@ -42140,11 +42248,11 @@
       <x:c r="I64" s="33" t="str"/>
       <x:c r="J64" s="33" t="str"/>
       <x:c r="K64" s="33" t="str"/>
-      <x:c r="L64" s="33" t="str">
+      <x:c r="L64" s="33" t="str"/>
+      <x:c r="M64" s="33" t="str"/>
+      <x:c r="N64" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M64" s="31"/>
-      <x:c r="N64" s="31"/>
       <x:c r="O64" s="31"/>
       <x:c r="P64" s="31"/>
       <x:c r="Q64" s="31"/>
@@ -42175,11 +42283,11 @@
       <x:c r="I65" s="33" t="str"/>
       <x:c r="J65" s="33" t="str"/>
       <x:c r="K65" s="33" t="str"/>
-      <x:c r="L65" s="33" t="str">
+      <x:c r="L65" s="33" t="str"/>
+      <x:c r="M65" s="33" t="str"/>
+      <x:c r="N65" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M65" s="31"/>
-      <x:c r="N65" s="31"/>
       <x:c r="O65" s="31"/>
       <x:c r="P65" s="31"/>
       <x:c r="Q65" s="31"/>
@@ -42210,11 +42318,11 @@
       <x:c r="I66" s="33" t="str"/>
       <x:c r="J66" s="33" t="str"/>
       <x:c r="K66" s="33" t="str"/>
-      <x:c r="L66" s="33" t="str">
+      <x:c r="L66" s="33" t="str"/>
+      <x:c r="M66" s="33" t="str"/>
+      <x:c r="N66" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M66" s="31"/>
-      <x:c r="N66" s="31"/>
       <x:c r="O66" s="31"/>
       <x:c r="P66" s="31"/>
       <x:c r="Q66" s="31"/>
@@ -42245,11 +42353,11 @@
       <x:c r="I67" s="33" t="str"/>
       <x:c r="J67" s="33" t="str"/>
       <x:c r="K67" s="33" t="str"/>
-      <x:c r="L67" s="33" t="str">
+      <x:c r="L67" s="33" t="str"/>
+      <x:c r="M67" s="33" t="str"/>
+      <x:c r="N67" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M67" s="31"/>
-      <x:c r="N67" s="31"/>
       <x:c r="O67" s="31"/>
       <x:c r="P67" s="31"/>
       <x:c r="Q67" s="31"/>
@@ -42280,11 +42388,11 @@
       <x:c r="I68" s="33" t="str"/>
       <x:c r="J68" s="33" t="str"/>
       <x:c r="K68" s="33" t="str"/>
-      <x:c r="L68" s="33" t="str">
+      <x:c r="L68" s="33" t="str"/>
+      <x:c r="M68" s="33" t="str"/>
+      <x:c r="N68" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M68" s="31"/>
-      <x:c r="N68" s="31"/>
       <x:c r="O68" s="31"/>
       <x:c r="P68" s="31"/>
       <x:c r="Q68" s="31"/>
@@ -42315,11 +42423,11 @@
       <x:c r="I69" s="33" t="str"/>
       <x:c r="J69" s="33" t="str"/>
       <x:c r="K69" s="33" t="str"/>
-      <x:c r="L69" s="33" t="str">
+      <x:c r="L69" s="33" t="str"/>
+      <x:c r="M69" s="33" t="str"/>
+      <x:c r="N69" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="M69" s="31"/>
-      <x:c r="N69" s="31"/>
       <x:c r="O69" s="31"/>
       <x:c r="P69" s="31"/>
       <x:c r="Q69" s="31"/>
@@ -42356,11 +42464,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K70" s="33" t="str"/>
-      <x:c r="L70" s="33" t="str">
+      <x:c r="L70" s="33" t="str"/>
+      <x:c r="M70" s="33" t="str"/>
+      <x:c r="N70" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M70" s="31"/>
-      <x:c r="N70" s="31"/>
       <x:c r="O70" s="31"/>
       <x:c r="P70" s="31"/>
       <x:c r="Q70" s="31"/>
@@ -42397,11 +42505,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K71" s="33" t="str"/>
-      <x:c r="L71" s="33" t="str">
+      <x:c r="L71" s="33" t="str"/>
+      <x:c r="M71" s="33" t="str"/>
+      <x:c r="N71" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M71" s="31"/>
-      <x:c r="N71" s="31"/>
       <x:c r="O71" s="31"/>
       <x:c r="P71" s="31"/>
       <x:c r="Q71" s="31"/>
@@ -42438,11 +42546,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K72" s="33" t="str"/>
-      <x:c r="L72" s="33" t="str">
+      <x:c r="L72" s="33" t="str"/>
+      <x:c r="M72" s="33" t="str"/>
+      <x:c r="N72" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M72" s="31"/>
-      <x:c r="N72" s="31"/>
       <x:c r="O72" s="31"/>
       <x:c r="P72" s="31"/>
       <x:c r="Q72" s="31"/>
@@ -42479,11 +42587,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K73" s="33" t="str"/>
-      <x:c r="L73" s="33" t="str">
+      <x:c r="L73" s="33" t="str"/>
+      <x:c r="M73" s="33" t="str"/>
+      <x:c r="N73" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M73" s="31"/>
-      <x:c r="N73" s="31"/>
       <x:c r="O73" s="31"/>
       <x:c r="P73" s="31"/>
       <x:c r="Q73" s="31"/>
@@ -42520,11 +42628,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K74" s="33" t="str"/>
-      <x:c r="L74" s="33" t="str">
+      <x:c r="L74" s="33" t="str"/>
+      <x:c r="M74" s="33" t="str"/>
+      <x:c r="N74" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M74" s="31"/>
-      <x:c r="N74" s="31"/>
       <x:c r="O74" s="31"/>
       <x:c r="P74" s="31"/>
       <x:c r="Q74" s="31"/>
@@ -42561,11 +42669,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K75" s="33" t="str"/>
-      <x:c r="L75" s="33" t="str">
+      <x:c r="L75" s="33" t="str"/>
+      <x:c r="M75" s="33" t="str"/>
+      <x:c r="N75" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M75" s="31"/>
-      <x:c r="N75" s="31"/>
       <x:c r="O75" s="31"/>
       <x:c r="P75" s="31"/>
       <x:c r="Q75" s="31"/>
@@ -42602,11 +42710,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K76" s="33" t="str"/>
-      <x:c r="L76" s="33" t="str">
+      <x:c r="L76" s="33" t="str"/>
+      <x:c r="M76" s="33" t="str"/>
+      <x:c r="N76" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M76" s="31"/>
-      <x:c r="N76" s="31"/>
       <x:c r="O76" s="31"/>
       <x:c r="P76" s="31"/>
       <x:c r="Q76" s="31"/>
@@ -42643,11 +42751,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K77" s="33" t="str"/>
-      <x:c r="L77" s="33" t="str">
+      <x:c r="L77" s="33" t="str"/>
+      <x:c r="M77" s="33" t="str"/>
+      <x:c r="N77" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M77" s="31"/>
-      <x:c r="N77" s="31"/>
       <x:c r="O77" s="31"/>
       <x:c r="P77" s="31"/>
       <x:c r="Q77" s="31"/>
@@ -42684,11 +42792,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K78" s="33" t="str"/>
-      <x:c r="L78" s="33" t="str">
+      <x:c r="L78" s="33" t="str"/>
+      <x:c r="M78" s="33" t="str"/>
+      <x:c r="N78" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M78" s="31"/>
-      <x:c r="N78" s="31"/>
       <x:c r="O78" s="31"/>
       <x:c r="P78" s="31"/>
       <x:c r="Q78" s="31"/>
@@ -42725,11 +42833,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K79" s="33" t="str"/>
-      <x:c r="L79" s="33" t="str">
+      <x:c r="L79" s="33" t="str"/>
+      <x:c r="M79" s="33" t="str"/>
+      <x:c r="N79" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M79" s="31"/>
-      <x:c r="N79" s="31"/>
       <x:c r="O79" s="31"/>
       <x:c r="P79" s="31"/>
       <x:c r="Q79" s="31"/>
@@ -42766,11 +42874,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K80" s="33" t="str"/>
-      <x:c r="L80" s="33" t="str">
+      <x:c r="L80" s="33" t="str"/>
+      <x:c r="M80" s="33" t="str"/>
+      <x:c r="N80" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M80" s="31"/>
-      <x:c r="N80" s="31"/>
       <x:c r="O80" s="31"/>
       <x:c r="P80" s="31"/>
       <x:c r="Q80" s="31"/>
@@ -42807,11 +42915,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K81" s="33" t="str"/>
-      <x:c r="L81" s="33" t="str">
+      <x:c r="L81" s="33" t="str"/>
+      <x:c r="M81" s="33" t="str"/>
+      <x:c r="N81" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M81" s="31"/>
-      <x:c r="N81" s="31"/>
       <x:c r="O81" s="31"/>
       <x:c r="P81" s="31"/>
       <x:c r="Q81" s="31"/>
@@ -42848,11 +42956,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K82" s="33" t="str"/>
-      <x:c r="L82" s="33" t="str">
+      <x:c r="L82" s="33" t="str"/>
+      <x:c r="M82" s="33" t="str"/>
+      <x:c r="N82" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M82" s="31"/>
-      <x:c r="N82" s="31"/>
       <x:c r="O82" s="31"/>
       <x:c r="P82" s="31"/>
       <x:c r="Q82" s="31"/>
@@ -42889,11 +42997,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K83" s="33" t="str"/>
-      <x:c r="L83" s="33" t="str">
+      <x:c r="L83" s="33" t="str"/>
+      <x:c r="M83" s="33" t="str"/>
+      <x:c r="N83" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M83" s="31"/>
-      <x:c r="N83" s="31"/>
       <x:c r="O83" s="31"/>
       <x:c r="P83" s="31"/>
       <x:c r="Q83" s="31"/>
@@ -42930,11 +43038,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K84" s="33" t="str"/>
-      <x:c r="L84" s="33" t="str">
+      <x:c r="L84" s="33" t="str"/>
+      <x:c r="M84" s="33" t="str"/>
+      <x:c r="N84" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M84" s="31"/>
-      <x:c r="N84" s="31"/>
       <x:c r="O84" s="31"/>
       <x:c r="P84" s="31"/>
       <x:c r="Q84" s="31"/>
@@ -42971,11 +43079,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K85" s="33" t="str"/>
-      <x:c r="L85" s="33" t="str">
+      <x:c r="L85" s="33" t="str"/>
+      <x:c r="M85" s="33" t="str"/>
+      <x:c r="N85" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M85" s="31"/>
-      <x:c r="N85" s="31"/>
       <x:c r="O85" s="31"/>
       <x:c r="P85" s="31"/>
       <x:c r="Q85" s="31"/>
@@ -43012,11 +43120,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K86" s="33" t="str"/>
-      <x:c r="L86" s="33" t="str">
+      <x:c r="L86" s="33" t="str"/>
+      <x:c r="M86" s="33" t="str"/>
+      <x:c r="N86" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M86" s="31"/>
-      <x:c r="N86" s="31"/>
       <x:c r="O86" s="31"/>
       <x:c r="P86" s="31"/>
       <x:c r="Q86" s="31"/>
@@ -43053,11 +43161,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K87" s="33" t="str"/>
-      <x:c r="L87" s="33" t="str">
+      <x:c r="L87" s="33" t="str"/>
+      <x:c r="M87" s="33" t="str"/>
+      <x:c r="N87" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M87" s="31"/>
-      <x:c r="N87" s="31"/>
       <x:c r="O87" s="31"/>
       <x:c r="P87" s="31"/>
       <x:c r="Q87" s="31"/>
@@ -43094,11 +43202,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K88" s="33" t="str"/>
-      <x:c r="L88" s="33" t="str">
+      <x:c r="L88" s="33" t="str"/>
+      <x:c r="M88" s="33" t="str"/>
+      <x:c r="N88" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M88" s="31"/>
-      <x:c r="N88" s="31"/>
       <x:c r="O88" s="31"/>
       <x:c r="P88" s="31"/>
       <x:c r="Q88" s="31"/>
@@ -43135,11 +43243,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K89" s="33" t="str"/>
-      <x:c r="L89" s="33" t="str">
+      <x:c r="L89" s="33" t="str"/>
+      <x:c r="M89" s="33" t="str"/>
+      <x:c r="N89" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M89" s="31"/>
-      <x:c r="N89" s="31"/>
       <x:c r="O89" s="31"/>
       <x:c r="P89" s="31"/>
       <x:c r="Q89" s="31"/>
@@ -43176,11 +43284,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K90" s="33" t="str"/>
-      <x:c r="L90" s="33" t="str">
+      <x:c r="L90" s="33" t="str"/>
+      <x:c r="M90" s="33" t="str"/>
+      <x:c r="N90" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M90" s="31"/>
-      <x:c r="N90" s="31"/>
       <x:c r="O90" s="31"/>
       <x:c r="P90" s="31"/>
       <x:c r="Q90" s="31"/>
@@ -43217,11 +43325,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K91" s="33" t="str"/>
-      <x:c r="L91" s="33" t="str">
+      <x:c r="L91" s="33" t="str"/>
+      <x:c r="M91" s="33" t="str"/>
+      <x:c r="N91" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M91" s="31"/>
-      <x:c r="N91" s="31"/>
       <x:c r="O91" s="31"/>
       <x:c r="P91" s="31"/>
       <x:c r="Q91" s="31"/>
@@ -43258,11 +43366,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K92" s="33" t="str"/>
-      <x:c r="L92" s="33" t="str">
+      <x:c r="L92" s="33" t="str"/>
+      <x:c r="M92" s="33" t="str"/>
+      <x:c r="N92" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M92" s="31"/>
-      <x:c r="N92" s="31"/>
       <x:c r="O92" s="31"/>
       <x:c r="P92" s="31"/>
       <x:c r="Q92" s="31"/>
@@ -43299,11 +43407,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K93" s="33" t="str"/>
-      <x:c r="L93" s="33" t="str">
+      <x:c r="L93" s="33" t="str"/>
+      <x:c r="M93" s="33" t="str"/>
+      <x:c r="N93" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M93" s="31"/>
-      <x:c r="N93" s="31"/>
       <x:c r="O93" s="31"/>
       <x:c r="P93" s="31"/>
       <x:c r="Q93" s="31"/>
@@ -43340,11 +43448,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K94" s="33" t="str"/>
-      <x:c r="L94" s="33" t="str">
+      <x:c r="L94" s="33" t="str"/>
+      <x:c r="M94" s="33" t="str"/>
+      <x:c r="N94" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M94" s="31"/>
-      <x:c r="N94" s="31"/>
       <x:c r="O94" s="31"/>
       <x:c r="P94" s="31"/>
       <x:c r="Q94" s="31"/>
@@ -43381,11 +43489,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K95" s="33" t="str"/>
-      <x:c r="L95" s="33" t="str">
+      <x:c r="L95" s="33" t="str"/>
+      <x:c r="M95" s="33" t="str"/>
+      <x:c r="N95" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M95" s="31"/>
-      <x:c r="N95" s="31"/>
       <x:c r="O95" s="31"/>
       <x:c r="P95" s="31"/>
       <x:c r="Q95" s="31"/>
@@ -43422,11 +43530,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K96" s="33" t="str"/>
-      <x:c r="L96" s="33" t="str">
+      <x:c r="L96" s="33" t="str"/>
+      <x:c r="M96" s="33" t="str"/>
+      <x:c r="N96" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M96" s="31"/>
-      <x:c r="N96" s="31"/>
       <x:c r="O96" s="31"/>
       <x:c r="P96" s="31"/>
       <x:c r="Q96" s="31"/>
@@ -43463,11 +43571,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K97" s="33" t="str"/>
-      <x:c r="L97" s="33" t="str">
+      <x:c r="L97" s="33" t="str"/>
+      <x:c r="M97" s="33" t="str"/>
+      <x:c r="N97" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M97" s="31"/>
-      <x:c r="N97" s="31"/>
       <x:c r="O97" s="31"/>
       <x:c r="P97" s="31"/>
       <x:c r="Q97" s="31"/>
@@ -43504,11 +43612,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K98" s="33" t="str"/>
-      <x:c r="L98" s="33" t="str">
+      <x:c r="L98" s="33" t="str"/>
+      <x:c r="M98" s="33" t="str"/>
+      <x:c r="N98" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M98" s="31"/>
-      <x:c r="N98" s="31"/>
       <x:c r="O98" s="31"/>
       <x:c r="P98" s="31"/>
       <x:c r="Q98" s="31"/>
@@ -43545,11 +43653,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K99" s="33" t="str"/>
-      <x:c r="L99" s="33" t="str">
+      <x:c r="L99" s="33" t="str"/>
+      <x:c r="M99" s="33" t="str"/>
+      <x:c r="N99" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M99" s="31"/>
-      <x:c r="N99" s="31"/>
       <x:c r="O99" s="31"/>
       <x:c r="P99" s="31"/>
       <x:c r="Q99" s="31"/>
@@ -43586,11 +43694,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K100" s="33" t="str"/>
-      <x:c r="L100" s="33" t="str">
+      <x:c r="L100" s="33" t="str"/>
+      <x:c r="M100" s="33" t="str"/>
+      <x:c r="N100" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M100" s="31"/>
-      <x:c r="N100" s="31"/>
       <x:c r="O100" s="31"/>
       <x:c r="P100" s="31"/>
       <x:c r="Q100" s="31"/>
@@ -43627,11 +43735,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K101" s="33" t="str"/>
-      <x:c r="L101" s="33" t="str">
+      <x:c r="L101" s="33" t="str"/>
+      <x:c r="M101" s="33" t="str"/>
+      <x:c r="N101" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M101" s="31"/>
-      <x:c r="N101" s="31"/>
       <x:c r="O101" s="31"/>
       <x:c r="P101" s="31"/>
       <x:c r="Q101" s="31"/>
@@ -43668,11 +43776,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K102" s="33" t="str"/>
-      <x:c r="L102" s="33" t="str">
+      <x:c r="L102" s="33" t="str"/>
+      <x:c r="M102" s="33" t="str"/>
+      <x:c r="N102" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M102" s="31"/>
-      <x:c r="N102" s="31"/>
       <x:c r="O102" s="31"/>
       <x:c r="P102" s="31"/>
       <x:c r="Q102" s="31"/>
@@ -43709,11 +43817,11 @@
         <x:v>False</x:v>
       </x:c>
       <x:c r="K103" s="33" t="str"/>
-      <x:c r="L103" s="33" t="str">
+      <x:c r="L103" s="33" t="str"/>
+      <x:c r="M103" s="33" t="str"/>
+      <x:c r="N103" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="M103" s="31"/>
-      <x:c r="N103" s="31"/>
       <x:c r="O103" s="31"/>
       <x:c r="P103" s="31"/>
       <x:c r="Q103" s="31"/>
@@ -43752,11 +43860,11 @@
       <x:c r="K104" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L104" s="33" t="str">
+      <x:c r="L104" s="33" t="str"/>
+      <x:c r="M104" s="33" t="str"/>
+      <x:c r="N104" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M104" s="31"/>
-      <x:c r="N104" s="31"/>
       <x:c r="O104" s="31"/>
       <x:c r="P104" s="31"/>
       <x:c r="Q104" s="31"/>
@@ -43795,11 +43903,11 @@
       <x:c r="K105" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L105" s="33" t="str">
+      <x:c r="L105" s="33" t="str"/>
+      <x:c r="M105" s="33" t="str"/>
+      <x:c r="N105" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M105" s="31"/>
-      <x:c r="N105" s="31"/>
       <x:c r="O105" s="31"/>
       <x:c r="P105" s="31"/>
       <x:c r="Q105" s="31"/>
@@ -43838,11 +43946,11 @@
       <x:c r="K106" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L106" s="33" t="str">
+      <x:c r="L106" s="33" t="str"/>
+      <x:c r="M106" s="33" t="str"/>
+      <x:c r="N106" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M106" s="31"/>
-      <x:c r="N106" s="31"/>
       <x:c r="O106" s="31"/>
       <x:c r="P106" s="31"/>
       <x:c r="Q106" s="31"/>
@@ -43881,11 +43989,11 @@
       <x:c r="K107" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L107" s="33" t="str">
+      <x:c r="L107" s="33" t="str"/>
+      <x:c r="M107" s="33" t="str"/>
+      <x:c r="N107" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M107" s="31"/>
-      <x:c r="N107" s="31"/>
       <x:c r="O107" s="31"/>
       <x:c r="P107" s="31"/>
       <x:c r="Q107" s="31"/>
@@ -43924,11 +44032,11 @@
       <x:c r="K108" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L108" s="33" t="str">
+      <x:c r="L108" s="33" t="str"/>
+      <x:c r="M108" s="33" t="str"/>
+      <x:c r="N108" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M108" s="31"/>
-      <x:c r="N108" s="31"/>
       <x:c r="O108" s="31"/>
       <x:c r="P108" s="31"/>
       <x:c r="Q108" s="31"/>
@@ -43967,11 +44075,11 @@
       <x:c r="K109" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L109" s="33" t="str">
+      <x:c r="L109" s="33" t="str"/>
+      <x:c r="M109" s="33" t="str"/>
+      <x:c r="N109" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M109" s="31"/>
-      <x:c r="N109" s="31"/>
       <x:c r="O109" s="31"/>
       <x:c r="P109" s="31"/>
       <x:c r="Q109" s="31"/>
@@ -44010,11 +44118,11 @@
       <x:c r="K110" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L110" s="33" t="str">
+      <x:c r="L110" s="33" t="str"/>
+      <x:c r="M110" s="33" t="str"/>
+      <x:c r="N110" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M110" s="31"/>
-      <x:c r="N110" s="31"/>
       <x:c r="O110" s="31"/>
       <x:c r="P110" s="31"/>
       <x:c r="Q110" s="31"/>
@@ -44053,11 +44161,11 @@
       <x:c r="K111" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L111" s="33" t="str">
+      <x:c r="L111" s="33" t="str"/>
+      <x:c r="M111" s="33" t="str"/>
+      <x:c r="N111" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M111" s="31"/>
-      <x:c r="N111" s="31"/>
       <x:c r="O111" s="31"/>
       <x:c r="P111" s="31"/>
       <x:c r="Q111" s="31"/>
@@ -44096,11 +44204,11 @@
       <x:c r="K112" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L112" s="33" t="str">
+      <x:c r="L112" s="33" t="str"/>
+      <x:c r="M112" s="33" t="str"/>
+      <x:c r="N112" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M112" s="31"/>
-      <x:c r="N112" s="31"/>
       <x:c r="O112" s="31"/>
       <x:c r="P112" s="31"/>
       <x:c r="Q112" s="31"/>
@@ -44139,11 +44247,11 @@
       <x:c r="K113" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L113" s="33" t="str">
+      <x:c r="L113" s="33" t="str"/>
+      <x:c r="M113" s="33" t="str"/>
+      <x:c r="N113" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M113" s="31"/>
-      <x:c r="N113" s="31"/>
       <x:c r="O113" s="31"/>
       <x:c r="P113" s="31"/>
       <x:c r="Q113" s="31"/>
@@ -44182,11 +44290,11 @@
       <x:c r="K114" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L114" s="33" t="str">
+      <x:c r="L114" s="33" t="str"/>
+      <x:c r="M114" s="33" t="str"/>
+      <x:c r="N114" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M114" s="31"/>
-      <x:c r="N114" s="31"/>
       <x:c r="O114" s="31"/>
       <x:c r="P114" s="31"/>
       <x:c r="Q114" s="31"/>
@@ -44225,11 +44333,11 @@
       <x:c r="K115" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L115" s="33" t="str">
+      <x:c r="L115" s="33" t="str"/>
+      <x:c r="M115" s="33" t="str"/>
+      <x:c r="N115" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M115" s="31"/>
-      <x:c r="N115" s="31"/>
       <x:c r="O115" s="31"/>
       <x:c r="P115" s="31"/>
       <x:c r="Q115" s="31"/>
@@ -44268,11 +44376,11 @@
       <x:c r="K116" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L116" s="33" t="str">
+      <x:c r="L116" s="33" t="str"/>
+      <x:c r="M116" s="33" t="str"/>
+      <x:c r="N116" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M116" s="31"/>
-      <x:c r="N116" s="31"/>
       <x:c r="O116" s="31"/>
       <x:c r="P116" s="31"/>
       <x:c r="Q116" s="31"/>
@@ -44311,11 +44419,11 @@
       <x:c r="K117" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L117" s="33" t="str">
+      <x:c r="L117" s="33" t="str"/>
+      <x:c r="M117" s="33" t="str"/>
+      <x:c r="N117" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M117" s="31"/>
-      <x:c r="N117" s="31"/>
       <x:c r="O117" s="31"/>
       <x:c r="P117" s="31"/>
       <x:c r="Q117" s="31"/>
@@ -44354,11 +44462,11 @@
       <x:c r="K118" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L118" s="33" t="str">
+      <x:c r="L118" s="33" t="str"/>
+      <x:c r="M118" s="33" t="str"/>
+      <x:c r="N118" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M118" s="31"/>
-      <x:c r="N118" s="31"/>
       <x:c r="O118" s="31"/>
       <x:c r="P118" s="31"/>
       <x:c r="Q118" s="31"/>
@@ -44397,11 +44505,11 @@
       <x:c r="K119" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L119" s="33" t="str">
+      <x:c r="L119" s="33" t="str"/>
+      <x:c r="M119" s="33" t="str"/>
+      <x:c r="N119" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M119" s="31"/>
-      <x:c r="N119" s="31"/>
       <x:c r="O119" s="31"/>
       <x:c r="P119" s="31"/>
       <x:c r="Q119" s="31"/>
@@ -44440,11 +44548,11 @@
       <x:c r="K120" s="33" t="str">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L120" s="33" t="str">
+      <x:c r="L120" s="33" t="str"/>
+      <x:c r="M120" s="33" t="str"/>
+      <x:c r="N120" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="M120" s="31"/>
-      <x:c r="N120" s="31"/>
       <x:c r="O120" s="31"/>
       <x:c r="P120" s="31"/>
       <x:c r="Q120" s="31"/>
@@ -44483,11 +44591,11 @@
       <x:c r="K121" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L121" s="33" t="str">
+      <x:c r="L121" s="33" t="str"/>
+      <x:c r="M121" s="33" t="str"/>
+      <x:c r="N121" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M121" s="31"/>
-      <x:c r="N121" s="31"/>
       <x:c r="O121" s="31"/>
       <x:c r="P121" s="31"/>
       <x:c r="Q121" s="31"/>
@@ -44526,11 +44634,11 @@
       <x:c r="K122" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L122" s="33" t="str">
+      <x:c r="L122" s="33" t="str"/>
+      <x:c r="M122" s="33" t="str"/>
+      <x:c r="N122" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M122" s="31"/>
-      <x:c r="N122" s="31"/>
       <x:c r="O122" s="31"/>
       <x:c r="P122" s="31"/>
       <x:c r="Q122" s="31"/>
@@ -44569,11 +44677,11 @@
       <x:c r="K123" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L123" s="33" t="str">
+      <x:c r="L123" s="33" t="str"/>
+      <x:c r="M123" s="33" t="str"/>
+      <x:c r="N123" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M123" s="31"/>
-      <x:c r="N123" s="31"/>
       <x:c r="O123" s="31"/>
       <x:c r="P123" s="31"/>
       <x:c r="Q123" s="31"/>
@@ -44612,11 +44720,11 @@
       <x:c r="K124" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L124" s="33" t="str">
+      <x:c r="L124" s="33" t="str"/>
+      <x:c r="M124" s="33" t="str"/>
+      <x:c r="N124" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M124" s="31"/>
-      <x:c r="N124" s="31"/>
       <x:c r="O124" s="31"/>
       <x:c r="P124" s="31"/>
       <x:c r="Q124" s="31"/>
@@ -44655,11 +44763,11 @@
       <x:c r="K125" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L125" s="33" t="str">
+      <x:c r="L125" s="33" t="str"/>
+      <x:c r="M125" s="33" t="str"/>
+      <x:c r="N125" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M125" s="31"/>
-      <x:c r="N125" s="31"/>
       <x:c r="O125" s="31"/>
       <x:c r="P125" s="31"/>
       <x:c r="Q125" s="31"/>
@@ -44698,11 +44806,11 @@
       <x:c r="K126" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L126" s="33" t="str">
+      <x:c r="L126" s="33" t="str"/>
+      <x:c r="M126" s="33" t="str"/>
+      <x:c r="N126" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M126" s="31"/>
-      <x:c r="N126" s="31"/>
       <x:c r="O126" s="31"/>
       <x:c r="P126" s="31"/>
       <x:c r="Q126" s="31"/>
@@ -44741,11 +44849,11 @@
       <x:c r="K127" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L127" s="33" t="str">
+      <x:c r="L127" s="33" t="str"/>
+      <x:c r="M127" s="33" t="str"/>
+      <x:c r="N127" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M127" s="31"/>
-      <x:c r="N127" s="31"/>
       <x:c r="O127" s="31"/>
       <x:c r="P127" s="31"/>
       <x:c r="Q127" s="31"/>
@@ -44784,11 +44892,11 @@
       <x:c r="K128" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L128" s="33" t="str">
+      <x:c r="L128" s="33" t="str"/>
+      <x:c r="M128" s="33" t="str"/>
+      <x:c r="N128" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M128" s="31"/>
-      <x:c r="N128" s="31"/>
       <x:c r="O128" s="31"/>
       <x:c r="P128" s="31"/>
       <x:c r="Q128" s="31"/>
@@ -44827,11 +44935,11 @@
       <x:c r="K129" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L129" s="33" t="str">
+      <x:c r="L129" s="33" t="str"/>
+      <x:c r="M129" s="33" t="str"/>
+      <x:c r="N129" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M129" s="31"/>
-      <x:c r="N129" s="31"/>
       <x:c r="O129" s="31"/>
       <x:c r="P129" s="31"/>
       <x:c r="Q129" s="31"/>
@@ -44870,11 +44978,11 @@
       <x:c r="K130" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L130" s="33" t="str">
+      <x:c r="L130" s="33" t="str"/>
+      <x:c r="M130" s="33" t="str"/>
+      <x:c r="N130" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M130" s="31"/>
-      <x:c r="N130" s="31"/>
       <x:c r="O130" s="31"/>
       <x:c r="P130" s="31"/>
       <x:c r="Q130" s="31"/>
@@ -44913,11 +45021,11 @@
       <x:c r="K131" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L131" s="33" t="str">
+      <x:c r="L131" s="33" t="str"/>
+      <x:c r="M131" s="33" t="str"/>
+      <x:c r="N131" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M131" s="31"/>
-      <x:c r="N131" s="31"/>
       <x:c r="O131" s="31"/>
       <x:c r="P131" s="31"/>
       <x:c r="Q131" s="31"/>
@@ -44956,11 +45064,11 @@
       <x:c r="K132" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L132" s="33" t="str">
+      <x:c r="L132" s="33" t="str"/>
+      <x:c r="M132" s="33" t="str"/>
+      <x:c r="N132" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M132" s="31"/>
-      <x:c r="N132" s="31"/>
       <x:c r="O132" s="31"/>
       <x:c r="P132" s="31"/>
       <x:c r="Q132" s="31"/>
@@ -44999,11 +45107,11 @@
       <x:c r="K133" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L133" s="33" t="str">
+      <x:c r="L133" s="33" t="str"/>
+      <x:c r="M133" s="33" t="str"/>
+      <x:c r="N133" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M133" s="31"/>
-      <x:c r="N133" s="31"/>
       <x:c r="O133" s="31"/>
       <x:c r="P133" s="31"/>
       <x:c r="Q133" s="31"/>
@@ -45042,11 +45150,11 @@
       <x:c r="K134" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L134" s="33" t="str">
+      <x:c r="L134" s="33" t="str"/>
+      <x:c r="M134" s="33" t="str"/>
+      <x:c r="N134" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M134" s="31"/>
-      <x:c r="N134" s="31"/>
       <x:c r="O134" s="31"/>
       <x:c r="P134" s="31"/>
       <x:c r="Q134" s="31"/>
@@ -45085,11 +45193,11 @@
       <x:c r="K135" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L135" s="33" t="str">
+      <x:c r="L135" s="33" t="str"/>
+      <x:c r="M135" s="33" t="str"/>
+      <x:c r="N135" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M135" s="31"/>
-      <x:c r="N135" s="31"/>
       <x:c r="O135" s="31"/>
       <x:c r="P135" s="31"/>
       <x:c r="Q135" s="31"/>
@@ -45128,11 +45236,11 @@
       <x:c r="K136" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L136" s="33" t="str">
+      <x:c r="L136" s="33" t="str"/>
+      <x:c r="M136" s="33" t="str"/>
+      <x:c r="N136" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M136" s="31"/>
-      <x:c r="N136" s="31"/>
       <x:c r="O136" s="31"/>
       <x:c r="P136" s="31"/>
       <x:c r="Q136" s="31"/>
@@ -45171,21 +45279,21 @@
       <x:c r="K137" s="33" t="str">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="L137" s="33" t="str">
+      <x:c r="L137" s="33" t="str"/>
+      <x:c r="M137" s="33" t="str"/>
+      <x:c r="N137" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="M137" s="31"/>
-      <x:c r="N137" s="31"/>
       <x:c r="O137" s="31"/>
       <x:c r="P137" s="31"/>
       <x:c r="Q137" s="31"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B138" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C138" s="33" t="str">
         <x:v>algebra</x:v>
@@ -45194,33 +45302,45 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E138" s="33" t="str">
-        <x:v>\dfrac{25}{2}</x:v>
+        <x:v>### **Step 5: Divide both sides by 4</x:v>
       </x:c>
       <x:c r="F138" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G138" s="35" t="n">
+        <x:v>3.1218744579998656</x:v>
+      </x:c>
+      <x:c r="H138" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I138" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G138" s="35" t="n">
-        <x:v>7.580443959000007</x:v>
-      </x:c>
-      <x:c r="H138" s="33" t="str"/>
-      <x:c r="I138" s="33" t="str"/>
-      <x:c r="J138" s="33" t="str"/>
-      <x:c r="K138" s="33" t="str"/>
+      <x:c r="J138" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K138" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L138" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M138" s="31"/>
-      <x:c r="N138" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M138" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N138" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O138" s="31"/>
       <x:c r="P138" s="31"/>
       <x:c r="Q138" s="31"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B139" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C139" s="33" t="str">
         <x:v>markup</x:v>
@@ -45229,33 +45349,45 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E139" s="33" t="str">
-        <x:v>96</x:v>
+        <x:v>0.80x = 96</x:v>
       </x:c>
       <x:c r="F139" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G139" s="35" t="n">
+        <x:v>3.058332124999879</x:v>
+      </x:c>
+      <x:c r="H139" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I139" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G139" s="35" t="n">
-        <x:v>6.407860625000012</x:v>
-      </x:c>
-      <x:c r="H139" s="33" t="str"/>
-      <x:c r="I139" s="33" t="str"/>
-      <x:c r="J139" s="33" t="str"/>
-      <x:c r="K139" s="33" t="str"/>
+      <x:c r="J139" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K139" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L139" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M139" s="31"/>
-      <x:c r="N139" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M139" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N139" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O139" s="31"/>
       <x:c r="P139" s="31"/>
       <x:c r="Q139" s="31"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B140" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C140" s="33" t="str">
         <x:v>boxes</x:v>
@@ -45264,33 +45396,45 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E140" s="33" t="str">
-        <x:v>Mixed</x:v>
+        <x:v>'- The</x:v>
       </x:c>
       <x:c r="F140" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G140" s="35" t="n">
+        <x:v>3.0432085830000233</x:v>
+      </x:c>
+      <x:c r="H140" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I140" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G140" s="35" t="n">
-        <x:v>6.2715228750000165</x:v>
-      </x:c>
-      <x:c r="H140" s="33" t="str"/>
-      <x:c r="I140" s="33" t="str"/>
-      <x:c r="J140" s="33" t="str"/>
-      <x:c r="K140" s="33" t="str"/>
+      <x:c r="J140" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K140" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L140" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M140" s="31"/>
-      <x:c r="N140" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M140" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N140" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O140" s="31"/>
       <x:c r="P140" s="31"/>
       <x:c r="Q140" s="31"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B141" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C141" s="33" t="str">
         <x:v>inclusion</x:v>
@@ -45299,33 +45443,45 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E141" s="33" t="str">
-        <x:v>80</x:v>
+        <x:v>|A \cup B| - |C| = |A</x:v>
       </x:c>
       <x:c r="F141" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G141" s="35" t="n">
+        <x:v>3.0949742910001987</x:v>
+      </x:c>
+      <x:c r="H141" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I141" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G141" s="35" t="n">
-        <x:v>4.775222624999998</x:v>
-      </x:c>
-      <x:c r="H141" s="33" t="str"/>
-      <x:c r="I141" s="33" t="str"/>
-      <x:c r="J141" s="33" t="str"/>
-      <x:c r="K141" s="33" t="str"/>
+      <x:c r="J141" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K141" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L141" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M141" s="31"/>
-      <x:c r="N141" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M141" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N141" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O141" s="31"/>
       <x:c r="P141" s="31"/>
       <x:c r="Q141" s="31"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B142" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C142" s="33" t="str">
         <x:v>modular</x:v>
@@ -45334,33 +45490,45 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E142" s="33" t="str">
-        <x:v>'- \(7^8 \equiv 9^2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F142" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
       <x:c r="G142" s="35" t="n">
-        <x:v>14.03727679100001</x:v>
-      </x:c>
-      <x:c r="H142" s="33" t="str"/>
-      <x:c r="I142" s="33" t="str"/>
-      <x:c r="J142" s="33" t="str"/>
-      <x:c r="K142" s="33" t="str"/>
+        <x:v>3.0811041660001592</x:v>
+      </x:c>
+      <x:c r="H142" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I142" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J142" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K142" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L142" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M142" s="31"/>
-      <x:c r="N142" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M142" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N142" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O142" s="31"/>
       <x:c r="P142" s="31"/>
       <x:c r="Q142" s="31"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B143" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C143" s="33" t="str">
         <x:v>work_rate</x:v>
@@ -45369,33 +45537,45 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E143" s="33" t="str">
-        <x:v>\dfrac{15}{4}</x:v>
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac</x:v>
       </x:c>
       <x:c r="F143" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G143" s="35" t="n">
+        <x:v>3.074097292000033</x:v>
+      </x:c>
+      <x:c r="H143" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I143" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G143" s="35" t="n">
-        <x:v>6.176148500000011</x:v>
-      </x:c>
-      <x:c r="H143" s="33" t="str"/>
-      <x:c r="I143" s="33" t="str"/>
-      <x:c r="J143" s="33" t="str"/>
-      <x:c r="K143" s="33" t="str"/>
+      <x:c r="J143" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K143" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L143" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M143" s="31"/>
-      <x:c r="N143" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M143" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N143" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O143" s="31"/>
       <x:c r="P143" s="31"/>
       <x:c r="Q143" s="31"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B144" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C144" s="33" t="str">
         <x:v>probability</x:v>
@@ -45404,33 +45584,45 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E144" s="33" t="str">
-        <x:v>\dfrac{1}{9}</x:v>
+        <x:v>'---</x:v>
       </x:c>
       <x:c r="F144" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G144" s="35" t="n">
+        <x:v>3.0731377500001145</x:v>
+      </x:c>
+      <x:c r="H144" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I144" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G144" s="35" t="n">
-        <x:v>4.10938950000002</x:v>
-      </x:c>
-      <x:c r="H144" s="33" t="str"/>
-      <x:c r="I144" s="33" t="str"/>
-      <x:c r="J144" s="33" t="str"/>
-      <x:c r="K144" s="33" t="str"/>
+      <x:c r="J144" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K144" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L144" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M144" s="31"/>
-      <x:c r="N144" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M144" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N144" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O144" s="31"/>
       <x:c r="P144" s="31"/>
       <x:c r="Q144" s="31"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B145" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C145" s="33" t="str">
         <x:v>sequence</x:v>
@@ -45445,27 +45637,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G145" s="35" t="n">
-        <x:v>8.457965874999957</x:v>
-      </x:c>
-      <x:c r="H145" s="33" t="str"/>
-      <x:c r="I145" s="33" t="str"/>
-      <x:c r="J145" s="33" t="str"/>
-      <x:c r="K145" s="33" t="str"/>
+        <x:v>2.5519006670001545</x:v>
+      </x:c>
+      <x:c r="H145" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I145" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J145" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K145" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L145" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M145" s="31"/>
-      <x:c r="N145" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M145" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N145" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O145" s="31"/>
       <x:c r="P145" s="31"/>
       <x:c r="Q145" s="31"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B146" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C146" s="33" t="str">
         <x:v>linear_word</x:v>
@@ -45480,27 +45684,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G146" s="35" t="n">
-        <x:v>4.77963704199999</x:v>
-      </x:c>
-      <x:c r="H146" s="33" t="str"/>
-      <x:c r="I146" s="33" t="str"/>
-      <x:c r="J146" s="33" t="str"/>
-      <x:c r="K146" s="33" t="str"/>
+        <x:v>2.5361337499998626</x:v>
+      </x:c>
+      <x:c r="H146" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I146" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J146" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K146" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L146" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M146" s="31"/>
-      <x:c r="N146" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M146" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N146" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O146" s="31"/>
       <x:c r="P146" s="31"/>
       <x:c r="Q146" s="31"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B147" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C147" s="33" t="str">
         <x:v>reverse_discount</x:v>
@@ -45515,27 +45731,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G147" s="35" t="n">
-        <x:v>4.465110458999959</x:v>
-      </x:c>
-      <x:c r="H147" s="33" t="str"/>
-      <x:c r="I147" s="33" t="str"/>
-      <x:c r="J147" s="33" t="str"/>
-      <x:c r="K147" s="33" t="str"/>
+        <x:v>2.1054682920000687</x:v>
+      </x:c>
+      <x:c r="H147" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I147" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J147" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K147" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L147" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M147" s="31"/>
-      <x:c r="N147" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M147" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N147" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O147" s="31"/>
       <x:c r="P147" s="31"/>
       <x:c r="Q147" s="31"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B148" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C148" s="33" t="str">
         <x:v>multiples</x:v>
@@ -45544,33 +45772,45 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E148" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>'- Common difference $ d</x:v>
       </x:c>
       <x:c r="F148" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G148" s="35" t="n">
+        <x:v>3.0762542079999093</x:v>
+      </x:c>
+      <x:c r="H148" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I148" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G148" s="35" t="n">
-        <x:v>4.0312850840000465</x:v>
-      </x:c>
-      <x:c r="H148" s="33" t="str"/>
-      <x:c r="I148" s="33" t="str"/>
-      <x:c r="J148" s="33" t="str"/>
-      <x:c r="K148" s="33" t="str"/>
+      <x:c r="J148" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K148" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L148" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M148" s="31"/>
-      <x:c r="N148" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M148" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N148" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O148" s="31"/>
       <x:c r="P148" s="31"/>
       <x:c r="Q148" s="31"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B149" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C149" s="33" t="str">
         <x:v>rectangle</x:v>
@@ -45585,27 +45825,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G149" s="35" t="n">
-        <x:v>4.098184124999989</x:v>
-      </x:c>
-      <x:c r="H149" s="33" t="str"/>
-      <x:c r="I149" s="33" t="str"/>
-      <x:c r="J149" s="33" t="str"/>
-      <x:c r="K149" s="33" t="str"/>
+        <x:v>2.7807854169998336</x:v>
+      </x:c>
+      <x:c r="H149" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I149" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J149" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K149" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L149" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M149" s="31"/>
-      <x:c r="N149" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M149" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N149" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O149" s="31"/>
       <x:c r="P149" s="31"/>
       <x:c r="Q149" s="31"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B150" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C150" s="33" t="str">
         <x:v>average</x:v>
@@ -45614,33 +45866,45 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E150" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>10 + 11 + 13 + 1</x:v>
       </x:c>
       <x:c r="F150" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G150" s="35" t="n">
+        <x:v>3.1336080000000948</x:v>
+      </x:c>
+      <x:c r="H150" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I150" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G150" s="35" t="n">
-        <x:v>3.955258875000027</x:v>
-      </x:c>
-      <x:c r="H150" s="33" t="str"/>
-      <x:c r="I150" s="33" t="str"/>
-      <x:c r="J150" s="33" t="str"/>
-      <x:c r="K150" s="33" t="str"/>
+      <x:c r="J150" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K150" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L150" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M150" s="31"/>
-      <x:c r="N150" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M150" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N150" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O150" s="31"/>
       <x:c r="P150" s="31"/>
       <x:c r="Q150" s="31"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B151" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C151" s="33" t="str">
         <x:v>combinations</x:v>
@@ -45649,33 +45913,45 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E151" s="33" t="str">
-        <x:v>15</x:v>
+        <x:v>\binom{6}{2} = \frac{6!</x:v>
       </x:c>
       <x:c r="F151" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G151" s="35" t="n">
+        <x:v>3.057753332999937</x:v>
+      </x:c>
+      <x:c r="H151" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I151" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G151" s="35" t="n">
-        <x:v>6.499252583999976</x:v>
-      </x:c>
-      <x:c r="H151" s="33" t="str"/>
-      <x:c r="I151" s="33" t="str"/>
-      <x:c r="J151" s="33" t="str"/>
-      <x:c r="K151" s="33" t="str"/>
+      <x:c r="J151" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K151" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L151" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M151" s="31"/>
-      <x:c r="N151" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M151" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N151" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O151" s="31"/>
       <x:c r="P151" s="31"/>
       <x:c r="Q151" s="31"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B152" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C152" s="33" t="str">
         <x:v>coins</x:v>
@@ -45684,33 +45960,45 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E152" s="33" t="str">
-        <x:v>\dfrac{3}{8}</x:v>
+        <x:v>'- $ p = \frac{1</x:v>
       </x:c>
       <x:c r="F152" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G152" s="35" t="n">
+        <x:v>3.0663049590000355</x:v>
+      </x:c>
+      <x:c r="H152" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I152" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G152" s="35" t="n">
-        <x:v>2.2782300830000395</x:v>
-      </x:c>
-      <x:c r="H152" s="33" t="str"/>
-      <x:c r="I152" s="33" t="str"/>
-      <x:c r="J152" s="33" t="str"/>
-      <x:c r="K152" s="33" t="str"/>
+      <x:c r="J152" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K152" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L152" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M152" s="31"/>
-      <x:c r="N152" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M152" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N152" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O152" s="31"/>
       <x:c r="P152" s="31"/>
       <x:c r="Q152" s="31"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B153" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C153" s="33" t="str">
         <x:v>modular_small</x:v>
@@ -45725,27 +46013,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G153" s="35" t="n">
-        <x:v>12.253404416999956</x:v>
-      </x:c>
-      <x:c r="H153" s="33" t="str"/>
-      <x:c r="I153" s="33" t="str"/>
-      <x:c r="J153" s="33" t="str"/>
-      <x:c r="K153" s="33" t="str"/>
+        <x:v>2.6720041670000683</x:v>
+      </x:c>
+      <x:c r="H153" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I153" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J153" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K153" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L153" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M153" s="31"/>
-      <x:c r="N153" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M153" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N153" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O153" s="31"/>
       <x:c r="P153" s="31"/>
       <x:c r="Q153" s="31"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B154" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C154" s="33" t="str">
         <x:v>syllogism</x:v>
@@ -45754,33 +46054,45 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E154" s="33" t="str">
-        <x:v>Yes, all bloops must be lazzies.</x:v>
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
       </x:c>
       <x:c r="F154" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="G154" s="35" t="n">
-        <x:v>4.511834166999961</x:v>
-      </x:c>
-      <x:c r="H154" s="33" t="str"/>
-      <x:c r="I154" s="33" t="str"/>
-      <x:c r="J154" s="33" t="str"/>
-      <x:c r="K154" s="33" t="str"/>
+        <x:v>2.8378059169999688</x:v>
+      </x:c>
+      <x:c r="H154" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I154" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J154" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K154" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L154" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M154" s="31"/>
-      <x:c r="N154" s="31"/>
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="M154" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N154" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
+      </x:c>
       <x:c r="O154" s="31"/>
       <x:c r="P154" s="31"/>
       <x:c r="Q154" s="31"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B155" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C155" s="33" t="str">
         <x:v>algebra</x:v>
@@ -45789,33 +46101,45 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E155" s="33" t="str">
-        <x:v>\dfrac{25}{2}</x:v>
+        <x:v>### **Step 5: Divide both sides by 4</x:v>
       </x:c>
       <x:c r="F155" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G155" s="35" t="n">
+        <x:v>3.162531209000008</x:v>
+      </x:c>
+      <x:c r="H155" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I155" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G155" s="35" t="n">
-        <x:v>16.656210082999962</x:v>
-      </x:c>
-      <x:c r="H155" s="33" t="str"/>
-      <x:c r="I155" s="33" t="str"/>
-      <x:c r="J155" s="33" t="str"/>
-      <x:c r="K155" s="33" t="str"/>
+      <x:c r="J155" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K155" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L155" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M155" s="31"/>
-      <x:c r="N155" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M155" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N155" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O155" s="31"/>
       <x:c r="P155" s="31"/>
       <x:c r="Q155" s="31"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B156" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C156" s="33" t="str">
         <x:v>markup</x:v>
@@ -45824,33 +46148,45 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E156" s="33" t="str">
-        <x:v>96</x:v>
+        <x:v>0.80x = 96</x:v>
       </x:c>
       <x:c r="F156" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G156" s="35" t="n">
+        <x:v>3.093509499999982</x:v>
+      </x:c>
+      <x:c r="H156" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I156" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G156" s="35" t="n">
-        <x:v>12.64156225000005</x:v>
-      </x:c>
-      <x:c r="H156" s="33" t="str"/>
-      <x:c r="I156" s="33" t="str"/>
-      <x:c r="J156" s="33" t="str"/>
-      <x:c r="K156" s="33" t="str"/>
+      <x:c r="J156" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K156" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L156" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M156" s="31"/>
-      <x:c r="N156" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M156" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N156" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O156" s="31"/>
       <x:c r="P156" s="31"/>
       <x:c r="Q156" s="31"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B157" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C157" s="33" t="str">
         <x:v>boxes</x:v>
@@ -45859,33 +46195,45 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E157" s="33" t="str">
-        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
+        <x:v>'- The</x:v>
       </x:c>
       <x:c r="F157" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G157" s="35" t="n">
+        <x:v>3.1344980419999047</x:v>
+      </x:c>
+      <x:c r="H157" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I157" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G157" s="35" t="n">
-        <x:v>19.97141316599999</x:v>
-      </x:c>
-      <x:c r="H157" s="33" t="str"/>
-      <x:c r="I157" s="33" t="str"/>
-      <x:c r="J157" s="33" t="str"/>
-      <x:c r="K157" s="33" t="str"/>
+      <x:c r="J157" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K157" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L157" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M157" s="31"/>
-      <x:c r="N157" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M157" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N157" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O157" s="31"/>
       <x:c r="P157" s="31"/>
       <x:c r="Q157" s="31"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B158" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C158" s="33" t="str">
         <x:v>inclusion</x:v>
@@ -45894,33 +46242,45 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E158" s="33" t="str">
-        <x:v>80</x:v>
+        <x:v>|A \cup B| - |C| = (|</x:v>
       </x:c>
       <x:c r="F158" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G158" s="35" t="n">
+        <x:v>3.1062752909999745</x:v>
+      </x:c>
+      <x:c r="H158" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I158" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G158" s="35" t="n">
-        <x:v>12.902716834000046</x:v>
-      </x:c>
-      <x:c r="H158" s="33" t="str"/>
-      <x:c r="I158" s="33" t="str"/>
-      <x:c r="J158" s="33" t="str"/>
-      <x:c r="K158" s="33" t="str"/>
+      <x:c r="J158" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K158" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L158" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M158" s="31"/>
-      <x:c r="N158" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M158" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N158" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O158" s="31"/>
       <x:c r="P158" s="31"/>
       <x:c r="Q158" s="31"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B159" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C159" s="33" t="str">
         <x:v>modular</x:v>
@@ -45929,33 +46289,45 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E159" s="33" t="str">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F159" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G159" s="35" t="n">
+        <x:v>3.0746571659999518</x:v>
+      </x:c>
+      <x:c r="H159" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I159" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G159" s="35" t="n">
-        <x:v>50.31506079099995</x:v>
-      </x:c>
-      <x:c r="H159" s="33" t="str"/>
-      <x:c r="I159" s="33" t="str"/>
-      <x:c r="J159" s="33" t="str"/>
-      <x:c r="K159" s="33" t="str"/>
+      <x:c r="J159" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K159" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L159" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M159" s="31"/>
-      <x:c r="N159" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M159" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N159" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O159" s="31"/>
       <x:c r="P159" s="31"/>
       <x:c r="Q159" s="31"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B160" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C160" s="33" t="str">
         <x:v>work_rate</x:v>
@@ -45964,33 +46336,45 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E160" s="33" t="str">
-        <x:v>3.75</x:v>
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac</x:v>
       </x:c>
       <x:c r="F160" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G160" s="35" t="n">
+        <x:v>3.078451958000187</x:v>
+      </x:c>
+      <x:c r="H160" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I160" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G160" s="35" t="n">
-        <x:v>33.462693083999966</x:v>
-      </x:c>
-      <x:c r="H160" s="33" t="str"/>
-      <x:c r="I160" s="33" t="str"/>
-      <x:c r="J160" s="33" t="str"/>
-      <x:c r="K160" s="33" t="str"/>
+      <x:c r="J160" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K160" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L160" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M160" s="31"/>
-      <x:c r="N160" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M160" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N160" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O160" s="31"/>
       <x:c r="P160" s="31"/>
       <x:c r="Q160" s="31"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B161" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C161" s="33" t="str">
         <x:v>probability</x:v>
@@ -45999,33 +46383,45 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E161" s="33" t="str">
-        <x:v>\dfrac{1}{9}</x:v>
+        <x:v>$$</x:v>
       </x:c>
       <x:c r="F161" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G161" s="35" t="n">
+        <x:v>3.091791457999989</x:v>
+      </x:c>
+      <x:c r="H161" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I161" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G161" s="35" t="n">
-        <x:v>7.085368707999919</x:v>
-      </x:c>
-      <x:c r="H161" s="33" t="str"/>
-      <x:c r="I161" s="33" t="str"/>
-      <x:c r="J161" s="33" t="str"/>
-      <x:c r="K161" s="33" t="str"/>
+      <x:c r="J161" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K161" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L161" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M161" s="31"/>
-      <x:c r="N161" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M161" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N161" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O161" s="31"/>
       <x:c r="P161" s="31"/>
       <x:c r="Q161" s="31"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B162" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C162" s="33" t="str">
         <x:v>sequence</x:v>
@@ -46040,27 +46436,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G162" s="35" t="n">
-        <x:v>15.824353458000019</x:v>
-      </x:c>
-      <x:c r="H162" s="33" t="str"/>
-      <x:c r="I162" s="33" t="str"/>
-      <x:c r="J162" s="33" t="str"/>
-      <x:c r="K162" s="33" t="str"/>
+        <x:v>2.5629934170001434</x:v>
+      </x:c>
+      <x:c r="H162" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I162" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J162" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K162" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L162" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M162" s="31"/>
-      <x:c r="N162" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M162" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N162" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O162" s="31"/>
       <x:c r="P162" s="31"/>
       <x:c r="Q162" s="31"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B163" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C163" s="33" t="str">
         <x:v>linear_word</x:v>
@@ -46075,27 +46483,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G163" s="35" t="n">
-        <x:v>8.149854707999907</x:v>
-      </x:c>
-      <x:c r="H163" s="33" t="str"/>
-      <x:c r="I163" s="33" t="str"/>
-      <x:c r="J163" s="33" t="str"/>
-      <x:c r="K163" s="33" t="str"/>
+        <x:v>2.5373730829999204</x:v>
+      </x:c>
+      <x:c r="H163" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I163" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J163" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L163" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M163" s="31"/>
-      <x:c r="N163" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M163" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N163" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O163" s="31"/>
       <x:c r="P163" s="31"/>
       <x:c r="Q163" s="31"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B164" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C164" s="33" t="str">
         <x:v>reverse_discount</x:v>
@@ -46110,27 +46530,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G164" s="35" t="n">
-        <x:v>6.157211500000017</x:v>
-      </x:c>
-      <x:c r="H164" s="33" t="str"/>
-      <x:c r="I164" s="33" t="str"/>
-      <x:c r="J164" s="33" t="str"/>
-      <x:c r="K164" s="33" t="str"/>
+        <x:v>2.0535927910000282</x:v>
+      </x:c>
+      <x:c r="H164" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I164" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J164" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K164" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L164" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M164" s="31"/>
-      <x:c r="N164" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M164" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N164" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O164" s="31"/>
       <x:c r="P164" s="31"/>
       <x:c r="Q164" s="31"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B165" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C165" s="33" t="str">
         <x:v>multiples</x:v>
@@ -46139,33 +46571,45 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E165" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>'- Common difference $ d</x:v>
       </x:c>
       <x:c r="F165" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G165" s="35" t="n">
+        <x:v>3.093794459000037</x:v>
+      </x:c>
+      <x:c r="H165" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I165" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G165" s="35" t="n">
-        <x:v>21.503388040999994</x:v>
-      </x:c>
-      <x:c r="H165" s="33" t="str"/>
-      <x:c r="I165" s="33" t="str"/>
-      <x:c r="J165" s="33" t="str"/>
-      <x:c r="K165" s="33" t="str"/>
+      <x:c r="J165" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K165" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L165" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M165" s="31"/>
-      <x:c r="N165" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M165" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N165" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O165" s="31"/>
       <x:c r="P165" s="31"/>
       <x:c r="Q165" s="31"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B166" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C166" s="33" t="str">
         <x:v>rectangle</x:v>
@@ -46180,27 +46624,39 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G166" s="35" t="n">
-        <x:v>7.560139790999983</x:v>
-      </x:c>
-      <x:c r="H166" s="33" t="str"/>
-      <x:c r="I166" s="33" t="str"/>
-      <x:c r="J166" s="33" t="str"/>
-      <x:c r="K166" s="33" t="str"/>
+        <x:v>2.743517082999915</x:v>
+      </x:c>
+      <x:c r="H166" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I166" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J166" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K166" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L166" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M166" s="31"/>
-      <x:c r="N166" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M166" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N166" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O166" s="31"/>
       <x:c r="P166" s="31"/>
       <x:c r="Q166" s="31"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B167" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C167" s="33" t="str">
         <x:v>average</x:v>
@@ -46209,33 +46665,45 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E167" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>10 + 11 + 13 + 1</x:v>
       </x:c>
       <x:c r="F167" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G167" s="35" t="n">
+        <x:v>3.138838832999909</x:v>
+      </x:c>
+      <x:c r="H167" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I167" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G167" s="35" t="n">
-        <x:v>8.231041165999955</x:v>
-      </x:c>
-      <x:c r="H167" s="33" t="str"/>
-      <x:c r="I167" s="33" t="str"/>
-      <x:c r="J167" s="33" t="str"/>
-      <x:c r="K167" s="33" t="str"/>
+      <x:c r="J167" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K167" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L167" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M167" s="31"/>
-      <x:c r="N167" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M167" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N167" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O167" s="31"/>
       <x:c r="P167" s="31"/>
       <x:c r="Q167" s="31"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B168" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C168" s="33" t="str">
         <x:v>combinations</x:v>
@@ -46244,33 +46712,45 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E168" s="33" t="str">
-        <x:v>15</x:v>
+        <x:v>\binom{6}{2} = \frac{6!</x:v>
       </x:c>
       <x:c r="F168" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G168" s="35" t="n">
+        <x:v>3.1032872079999834</x:v>
+      </x:c>
+      <x:c r="H168" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I168" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G168" s="35" t="n">
-        <x:v>30.73365029099989</x:v>
-      </x:c>
-      <x:c r="H168" s="33" t="str"/>
-      <x:c r="I168" s="33" t="str"/>
-      <x:c r="J168" s="33" t="str"/>
-      <x:c r="K168" s="33" t="str"/>
+      <x:c r="J168" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K168" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L168" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M168" s="31"/>
-      <x:c r="N168" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M168" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N168" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O168" s="31"/>
       <x:c r="P168" s="31"/>
       <x:c r="Q168" s="31"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B169" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C169" s="33" t="str">
         <x:v>coins</x:v>
@@ -46279,33 +46759,45 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E169" s="33" t="str">
-        <x:v>\dfrac{3}{8}</x:v>
+        <x:v>'- $</x:v>
       </x:c>
       <x:c r="F169" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G169" s="35" t="n">
+        <x:v>3.099425958999973</x:v>
+      </x:c>
+      <x:c r="H169" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I169" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G169" s="35" t="n">
-        <x:v>11.049620875000073</x:v>
-      </x:c>
-      <x:c r="H169" s="33" t="str"/>
-      <x:c r="I169" s="33" t="str"/>
-      <x:c r="J169" s="33" t="str"/>
-      <x:c r="K169" s="33" t="str"/>
+      <x:c r="J169" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K169" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L169" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M169" s="31"/>
-      <x:c r="N169" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M169" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N169" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O169" s="31"/>
       <x:c r="P169" s="31"/>
       <x:c r="Q169" s="31"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B170" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C170" s="33" t="str">
         <x:v>modular_small</x:v>
@@ -46314,33 +46806,45 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E170" s="33" t="str">
-        <x:v>All methods confirm that the remainder when</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F170" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G170" s="35" t="n">
+        <x:v>2.6710686670000996</x:v>
+      </x:c>
+      <x:c r="H170" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I170" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J170" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="G170" s="35" t="n">
-        <x:v>67.06586500000003</x:v>
-      </x:c>
-      <x:c r="H170" s="33" t="str"/>
-      <x:c r="I170" s="33" t="str"/>
-      <x:c r="J170" s="33" t="str"/>
-      <x:c r="K170" s="33" t="str"/>
+      <x:c r="K170" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L170" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M170" s="31"/>
-      <x:c r="N170" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M170" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N170" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O170" s="31"/>
       <x:c r="P170" s="31"/>
       <x:c r="Q170" s="31"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B171" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C171" s="33" t="str">
         <x:v>syllogism</x:v>
@@ -46349,669 +46853,1225 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E171" s="33" t="str">
-        <x:v>Yes, all bloops must be lazzies.</x:v>
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
       </x:c>
       <x:c r="F171" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="G171" s="35" t="n">
-        <x:v>8.902264708000075</x:v>
-      </x:c>
-      <x:c r="H171" s="33" t="str"/>
-      <x:c r="I171" s="33" t="str"/>
-      <x:c r="J171" s="33" t="str"/>
-      <x:c r="K171" s="33" t="str"/>
+        <x:v>3.0251799159998427</x:v>
+      </x:c>
+      <x:c r="H171" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I171" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J171" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K171" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
       <x:c r="L171" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="M171" s="31"/>
-      <x:c r="N171" s="31"/>
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M171" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N171" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
+      </x:c>
       <x:c r="O171" s="31"/>
       <x:c r="P171" s="31"/>
       <x:c r="Q171" s="31"/>
     </x:row>
     <x:row r="172">
-      <x:c r="A172" s="31"/>
-      <x:c r="B172" s="31"/>
-      <x:c r="C172" s="31"/>
-      <x:c r="D172" s="31"/>
-      <x:c r="E172" s="31"/>
-      <x:c r="F172" s="31"/>
-      <x:c r="G172" s="37"/>
-      <x:c r="H172" s="31"/>
-      <x:c r="I172" s="31"/>
-      <x:c r="J172" s="31"/>
-      <x:c r="K172" s="31"/>
-      <x:c r="L172" s="31"/>
-      <x:c r="M172" s="31"/>
-      <x:c r="N172" s="31"/>
+      <x:c r="A172" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B172" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C172" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D172" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E172" s="33" t="str">
+        <x:v>\dfrac{25}{2}</x:v>
+      </x:c>
+      <x:c r="F172" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G172" s="35" t="n">
+        <x:v>7.580443959000007</x:v>
+      </x:c>
+      <x:c r="H172" s="33" t="str"/>
+      <x:c r="I172" s="33" t="str"/>
+      <x:c r="J172" s="33" t="str"/>
+      <x:c r="K172" s="33" t="str"/>
+      <x:c r="L172" s="33" t="str"/>
+      <x:c r="M172" s="33" t="str"/>
+      <x:c r="N172" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O172" s="31"/>
       <x:c r="P172" s="31"/>
       <x:c r="Q172" s="31"/>
     </x:row>
     <x:row r="173">
-      <x:c r="A173" s="31"/>
-      <x:c r="B173" s="31"/>
-      <x:c r="C173" s="31"/>
-      <x:c r="D173" s="31"/>
-      <x:c r="E173" s="31"/>
-      <x:c r="F173" s="31"/>
-      <x:c r="G173" s="37"/>
-      <x:c r="H173" s="31"/>
-      <x:c r="I173" s="31"/>
-      <x:c r="J173" s="31"/>
-      <x:c r="K173" s="31"/>
-      <x:c r="L173" s="31"/>
-      <x:c r="M173" s="31"/>
-      <x:c r="N173" s="31"/>
+      <x:c r="A173" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B173" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C173" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D173" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E173" s="33" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F173" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G173" s="35" t="n">
+        <x:v>6.407860625000012</x:v>
+      </x:c>
+      <x:c r="H173" s="33" t="str"/>
+      <x:c r="I173" s="33" t="str"/>
+      <x:c r="J173" s="33" t="str"/>
+      <x:c r="K173" s="33" t="str"/>
+      <x:c r="L173" s="33" t="str"/>
+      <x:c r="M173" s="33" t="str"/>
+      <x:c r="N173" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O173" s="31"/>
       <x:c r="P173" s="31"/>
       <x:c r="Q173" s="31"/>
     </x:row>
     <x:row r="174">
-      <x:c r="A174" s="31"/>
-      <x:c r="B174" s="31"/>
-      <x:c r="C174" s="31"/>
-      <x:c r="D174" s="31"/>
-      <x:c r="E174" s="31"/>
-      <x:c r="F174" s="31"/>
-      <x:c r="G174" s="37"/>
-      <x:c r="H174" s="31"/>
-      <x:c r="I174" s="31"/>
-      <x:c r="J174" s="31"/>
-      <x:c r="K174" s="31"/>
-      <x:c r="L174" s="31"/>
-      <x:c r="M174" s="31"/>
-      <x:c r="N174" s="31"/>
+      <x:c r="A174" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B174" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C174" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D174" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E174" s="33" t="str">
+        <x:v>Mixed</x:v>
+      </x:c>
+      <x:c r="F174" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G174" s="35" t="n">
+        <x:v>6.2715228750000165</x:v>
+      </x:c>
+      <x:c r="H174" s="33" t="str"/>
+      <x:c r="I174" s="33" t="str"/>
+      <x:c r="J174" s="33" t="str"/>
+      <x:c r="K174" s="33" t="str"/>
+      <x:c r="L174" s="33" t="str"/>
+      <x:c r="M174" s="33" t="str"/>
+      <x:c r="N174" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O174" s="31"/>
       <x:c r="P174" s="31"/>
       <x:c r="Q174" s="31"/>
     </x:row>
     <x:row r="175">
-      <x:c r="A175" s="31"/>
-      <x:c r="B175" s="31"/>
-      <x:c r="C175" s="31"/>
-      <x:c r="D175" s="31"/>
-      <x:c r="E175" s="31"/>
-      <x:c r="F175" s="31"/>
-      <x:c r="G175" s="37"/>
-      <x:c r="H175" s="31"/>
-      <x:c r="I175" s="31"/>
-      <x:c r="J175" s="31"/>
-      <x:c r="K175" s="31"/>
-      <x:c r="L175" s="31"/>
-      <x:c r="M175" s="31"/>
-      <x:c r="N175" s="31"/>
+      <x:c r="A175" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B175" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C175" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D175" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E175" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F175" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G175" s="35" t="n">
+        <x:v>4.775222624999998</x:v>
+      </x:c>
+      <x:c r="H175" s="33" t="str"/>
+      <x:c r="I175" s="33" t="str"/>
+      <x:c r="J175" s="33" t="str"/>
+      <x:c r="K175" s="33" t="str"/>
+      <x:c r="L175" s="33" t="str"/>
+      <x:c r="M175" s="33" t="str"/>
+      <x:c r="N175" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O175" s="31"/>
       <x:c r="P175" s="31"/>
       <x:c r="Q175" s="31"/>
     </x:row>
     <x:row r="176">
-      <x:c r="A176" s="31"/>
-      <x:c r="B176" s="31"/>
-      <x:c r="C176" s="31"/>
-      <x:c r="D176" s="31"/>
-      <x:c r="E176" s="31"/>
-      <x:c r="F176" s="31"/>
-      <x:c r="G176" s="37"/>
-      <x:c r="H176" s="31"/>
-      <x:c r="I176" s="31"/>
-      <x:c r="J176" s="31"/>
-      <x:c r="K176" s="31"/>
-      <x:c r="L176" s="31"/>
-      <x:c r="M176" s="31"/>
-      <x:c r="N176" s="31"/>
+      <x:c r="A176" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B176" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C176" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D176" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E176" s="33" t="str">
+        <x:v>'- \(7^8 \equiv 9^2</x:v>
+      </x:c>
+      <x:c r="F176" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G176" s="35" t="n">
+        <x:v>14.03727679100001</x:v>
+      </x:c>
+      <x:c r="H176" s="33" t="str"/>
+      <x:c r="I176" s="33" t="str"/>
+      <x:c r="J176" s="33" t="str"/>
+      <x:c r="K176" s="33" t="str"/>
+      <x:c r="L176" s="33" t="str"/>
+      <x:c r="M176" s="33" t="str"/>
+      <x:c r="N176" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O176" s="31"/>
       <x:c r="P176" s="31"/>
       <x:c r="Q176" s="31"/>
     </x:row>
     <x:row r="177">
-      <x:c r="A177" s="31"/>
-      <x:c r="B177" s="31"/>
-      <x:c r="C177" s="31"/>
-      <x:c r="D177" s="31"/>
-      <x:c r="E177" s="31"/>
-      <x:c r="F177" s="31"/>
-      <x:c r="G177" s="37"/>
-      <x:c r="H177" s="31"/>
-      <x:c r="I177" s="31"/>
-      <x:c r="J177" s="31"/>
-      <x:c r="K177" s="31"/>
-      <x:c r="L177" s="31"/>
-      <x:c r="M177" s="31"/>
-      <x:c r="N177" s="31"/>
+      <x:c r="A177" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B177" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C177" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D177" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E177" s="33" t="str">
+        <x:v>\dfrac{15}{4}</x:v>
+      </x:c>
+      <x:c r="F177" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G177" s="35" t="n">
+        <x:v>6.176148500000011</x:v>
+      </x:c>
+      <x:c r="H177" s="33" t="str"/>
+      <x:c r="I177" s="33" t="str"/>
+      <x:c r="J177" s="33" t="str"/>
+      <x:c r="K177" s="33" t="str"/>
+      <x:c r="L177" s="33" t="str"/>
+      <x:c r="M177" s="33" t="str"/>
+      <x:c r="N177" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O177" s="31"/>
       <x:c r="P177" s="31"/>
       <x:c r="Q177" s="31"/>
     </x:row>
     <x:row r="178">
-      <x:c r="A178" s="31"/>
-      <x:c r="B178" s="31"/>
-      <x:c r="C178" s="31"/>
-      <x:c r="D178" s="31"/>
-      <x:c r="E178" s="31"/>
-      <x:c r="F178" s="31"/>
-      <x:c r="G178" s="37"/>
-      <x:c r="H178" s="31"/>
-      <x:c r="I178" s="31"/>
-      <x:c r="J178" s="31"/>
-      <x:c r="K178" s="31"/>
-      <x:c r="L178" s="31"/>
-      <x:c r="M178" s="31"/>
-      <x:c r="N178" s="31"/>
+      <x:c r="A178" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B178" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C178" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D178" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E178" s="33" t="str">
+        <x:v>\dfrac{1}{9}</x:v>
+      </x:c>
+      <x:c r="F178" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G178" s="35" t="n">
+        <x:v>4.10938950000002</x:v>
+      </x:c>
+      <x:c r="H178" s="33" t="str"/>
+      <x:c r="I178" s="33" t="str"/>
+      <x:c r="J178" s="33" t="str"/>
+      <x:c r="K178" s="33" t="str"/>
+      <x:c r="L178" s="33" t="str"/>
+      <x:c r="M178" s="33" t="str"/>
+      <x:c r="N178" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O178" s="31"/>
       <x:c r="P178" s="31"/>
       <x:c r="Q178" s="31"/>
     </x:row>
     <x:row r="179">
-      <x:c r="A179" s="31"/>
-      <x:c r="B179" s="31"/>
-      <x:c r="C179" s="31"/>
-      <x:c r="D179" s="31"/>
-      <x:c r="E179" s="31"/>
-      <x:c r="F179" s="31"/>
-      <x:c r="G179" s="37"/>
-      <x:c r="H179" s="31"/>
-      <x:c r="I179" s="31"/>
-      <x:c r="J179" s="31"/>
-      <x:c r="K179" s="31"/>
-      <x:c r="L179" s="31"/>
-      <x:c r="M179" s="31"/>
-      <x:c r="N179" s="31"/>
+      <x:c r="A179" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B179" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C179" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D179" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E179" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F179" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G179" s="35" t="n">
+        <x:v>8.457965874999957</x:v>
+      </x:c>
+      <x:c r="H179" s="33" t="str"/>
+      <x:c r="I179" s="33" t="str"/>
+      <x:c r="J179" s="33" t="str"/>
+      <x:c r="K179" s="33" t="str"/>
+      <x:c r="L179" s="33" t="str"/>
+      <x:c r="M179" s="33" t="str"/>
+      <x:c r="N179" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O179" s="31"/>
       <x:c r="P179" s="31"/>
       <x:c r="Q179" s="31"/>
     </x:row>
     <x:row r="180">
-      <x:c r="A180" s="31"/>
-      <x:c r="B180" s="31"/>
-      <x:c r="C180" s="31"/>
-      <x:c r="D180" s="31"/>
-      <x:c r="E180" s="31"/>
-      <x:c r="F180" s="31"/>
-      <x:c r="G180" s="37"/>
-      <x:c r="H180" s="31"/>
-      <x:c r="I180" s="31"/>
-      <x:c r="J180" s="31"/>
-      <x:c r="K180" s="31"/>
-      <x:c r="L180" s="31"/>
-      <x:c r="M180" s="31"/>
-      <x:c r="N180" s="31"/>
+      <x:c r="A180" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B180" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C180" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D180" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E180" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F180" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G180" s="35" t="n">
+        <x:v>4.77963704199999</x:v>
+      </x:c>
+      <x:c r="H180" s="33" t="str"/>
+      <x:c r="I180" s="33" t="str"/>
+      <x:c r="J180" s="33" t="str"/>
+      <x:c r="K180" s="33" t="str"/>
+      <x:c r="L180" s="33" t="str"/>
+      <x:c r="M180" s="33" t="str"/>
+      <x:c r="N180" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O180" s="31"/>
       <x:c r="P180" s="31"/>
       <x:c r="Q180" s="31"/>
     </x:row>
     <x:row r="181">
-      <x:c r="A181" s="31"/>
-      <x:c r="B181" s="31"/>
-      <x:c r="C181" s="31"/>
-      <x:c r="D181" s="31"/>
-      <x:c r="E181" s="31"/>
-      <x:c r="F181" s="31"/>
-      <x:c r="G181" s="37"/>
-      <x:c r="H181" s="31"/>
-      <x:c r="I181" s="31"/>
-      <x:c r="J181" s="31"/>
-      <x:c r="K181" s="31"/>
-      <x:c r="L181" s="31"/>
-      <x:c r="M181" s="31"/>
-      <x:c r="N181" s="31"/>
+      <x:c r="A181" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B181" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C181" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D181" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E181" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F181" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G181" s="35" t="n">
+        <x:v>4.465110458999959</x:v>
+      </x:c>
+      <x:c r="H181" s="33" t="str"/>
+      <x:c r="I181" s="33" t="str"/>
+      <x:c r="J181" s="33" t="str"/>
+      <x:c r="K181" s="33" t="str"/>
+      <x:c r="L181" s="33" t="str"/>
+      <x:c r="M181" s="33" t="str"/>
+      <x:c r="N181" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O181" s="31"/>
       <x:c r="P181" s="31"/>
       <x:c r="Q181" s="31"/>
     </x:row>
     <x:row r="182">
-      <x:c r="A182" s="31"/>
-      <x:c r="B182" s="31"/>
-      <x:c r="C182" s="31"/>
-      <x:c r="D182" s="31"/>
-      <x:c r="E182" s="31"/>
-      <x:c r="F182" s="31"/>
-      <x:c r="G182" s="37"/>
-      <x:c r="H182" s="31"/>
-      <x:c r="I182" s="31"/>
-      <x:c r="J182" s="31"/>
-      <x:c r="K182" s="31"/>
-      <x:c r="L182" s="31"/>
-      <x:c r="M182" s="31"/>
-      <x:c r="N182" s="31"/>
+      <x:c r="A182" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B182" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C182" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D182" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E182" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F182" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G182" s="35" t="n">
+        <x:v>4.0312850840000465</x:v>
+      </x:c>
+      <x:c r="H182" s="33" t="str"/>
+      <x:c r="I182" s="33" t="str"/>
+      <x:c r="J182" s="33" t="str"/>
+      <x:c r="K182" s="33" t="str"/>
+      <x:c r="L182" s="33" t="str"/>
+      <x:c r="M182" s="33" t="str"/>
+      <x:c r="N182" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O182" s="31"/>
       <x:c r="P182" s="31"/>
       <x:c r="Q182" s="31"/>
     </x:row>
     <x:row r="183">
-      <x:c r="A183" s="31"/>
-      <x:c r="B183" s="31"/>
-      <x:c r="C183" s="31"/>
-      <x:c r="D183" s="31"/>
-      <x:c r="E183" s="31"/>
-      <x:c r="F183" s="31"/>
-      <x:c r="G183" s="37"/>
-      <x:c r="H183" s="31"/>
-      <x:c r="I183" s="31"/>
-      <x:c r="J183" s="31"/>
-      <x:c r="K183" s="31"/>
-      <x:c r="L183" s="31"/>
-      <x:c r="M183" s="31"/>
-      <x:c r="N183" s="31"/>
+      <x:c r="A183" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B183" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C183" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D183" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E183" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F183" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G183" s="35" t="n">
+        <x:v>4.098184124999989</x:v>
+      </x:c>
+      <x:c r="H183" s="33" t="str"/>
+      <x:c r="I183" s="33" t="str"/>
+      <x:c r="J183" s="33" t="str"/>
+      <x:c r="K183" s="33" t="str"/>
+      <x:c r="L183" s="33" t="str"/>
+      <x:c r="M183" s="33" t="str"/>
+      <x:c r="N183" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O183" s="31"/>
       <x:c r="P183" s="31"/>
       <x:c r="Q183" s="31"/>
     </x:row>
     <x:row r="184">
-      <x:c r="A184" s="31"/>
-      <x:c r="B184" s="31"/>
-      <x:c r="C184" s="31"/>
-      <x:c r="D184" s="31"/>
-      <x:c r="E184" s="31"/>
-      <x:c r="F184" s="31"/>
-      <x:c r="G184" s="37"/>
-      <x:c r="H184" s="31"/>
-      <x:c r="I184" s="31"/>
-      <x:c r="J184" s="31"/>
-      <x:c r="K184" s="31"/>
-      <x:c r="L184" s="31"/>
-      <x:c r="M184" s="31"/>
-      <x:c r="N184" s="31"/>
+      <x:c r="A184" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B184" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C184" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D184" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E184" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F184" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G184" s="35" t="n">
+        <x:v>3.955258875000027</x:v>
+      </x:c>
+      <x:c r="H184" s="33" t="str"/>
+      <x:c r="I184" s="33" t="str"/>
+      <x:c r="J184" s="33" t="str"/>
+      <x:c r="K184" s="33" t="str"/>
+      <x:c r="L184" s="33" t="str"/>
+      <x:c r="M184" s="33" t="str"/>
+      <x:c r="N184" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O184" s="31"/>
       <x:c r="P184" s="31"/>
       <x:c r="Q184" s="31"/>
     </x:row>
     <x:row r="185">
-      <x:c r="A185" s="31"/>
-      <x:c r="B185" s="31"/>
-      <x:c r="C185" s="31"/>
-      <x:c r="D185" s="31"/>
-      <x:c r="E185" s="31"/>
-      <x:c r="F185" s="31"/>
-      <x:c r="G185" s="37"/>
-      <x:c r="H185" s="31"/>
-      <x:c r="I185" s="31"/>
-      <x:c r="J185" s="31"/>
-      <x:c r="K185" s="31"/>
-      <x:c r="L185" s="31"/>
-      <x:c r="M185" s="31"/>
-      <x:c r="N185" s="31"/>
+      <x:c r="A185" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B185" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C185" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D185" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E185" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F185" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G185" s="35" t="n">
+        <x:v>6.499252583999976</x:v>
+      </x:c>
+      <x:c r="H185" s="33" t="str"/>
+      <x:c r="I185" s="33" t="str"/>
+      <x:c r="J185" s="33" t="str"/>
+      <x:c r="K185" s="33" t="str"/>
+      <x:c r="L185" s="33" t="str"/>
+      <x:c r="M185" s="33" t="str"/>
+      <x:c r="N185" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O185" s="31"/>
       <x:c r="P185" s="31"/>
       <x:c r="Q185" s="31"/>
     </x:row>
     <x:row r="186">
-      <x:c r="A186" s="31"/>
-      <x:c r="B186" s="31"/>
-      <x:c r="C186" s="31"/>
-      <x:c r="D186" s="31"/>
-      <x:c r="E186" s="31"/>
-      <x:c r="F186" s="31"/>
-      <x:c r="G186" s="37"/>
-      <x:c r="H186" s="31"/>
-      <x:c r="I186" s="31"/>
-      <x:c r="J186" s="31"/>
-      <x:c r="K186" s="31"/>
-      <x:c r="L186" s="31"/>
-      <x:c r="M186" s="31"/>
-      <x:c r="N186" s="31"/>
+      <x:c r="A186" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B186" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C186" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D186" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E186" s="33" t="str">
+        <x:v>\dfrac{3}{8}</x:v>
+      </x:c>
+      <x:c r="F186" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G186" s="35" t="n">
+        <x:v>2.2782300830000395</x:v>
+      </x:c>
+      <x:c r="H186" s="33" t="str"/>
+      <x:c r="I186" s="33" t="str"/>
+      <x:c r="J186" s="33" t="str"/>
+      <x:c r="K186" s="33" t="str"/>
+      <x:c r="L186" s="33" t="str"/>
+      <x:c r="M186" s="33" t="str"/>
+      <x:c r="N186" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O186" s="31"/>
       <x:c r="P186" s="31"/>
       <x:c r="Q186" s="31"/>
     </x:row>
     <x:row r="187">
-      <x:c r="A187" s="31"/>
-      <x:c r="B187" s="31"/>
-      <x:c r="C187" s="31"/>
-      <x:c r="D187" s="31"/>
-      <x:c r="E187" s="31"/>
-      <x:c r="F187" s="31"/>
-      <x:c r="G187" s="37"/>
-      <x:c r="H187" s="31"/>
-      <x:c r="I187" s="31"/>
-      <x:c r="J187" s="31"/>
-      <x:c r="K187" s="31"/>
-      <x:c r="L187" s="31"/>
-      <x:c r="M187" s="31"/>
-      <x:c r="N187" s="31"/>
+      <x:c r="A187" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B187" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C187" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D187" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E187" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F187" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G187" s="35" t="n">
+        <x:v>12.253404416999956</x:v>
+      </x:c>
+      <x:c r="H187" s="33" t="str"/>
+      <x:c r="I187" s="33" t="str"/>
+      <x:c r="J187" s="33" t="str"/>
+      <x:c r="K187" s="33" t="str"/>
+      <x:c r="L187" s="33" t="str"/>
+      <x:c r="M187" s="33" t="str"/>
+      <x:c r="N187" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O187" s="31"/>
       <x:c r="P187" s="31"/>
       <x:c r="Q187" s="31"/>
     </x:row>
     <x:row r="188">
-      <x:c r="A188" s="31"/>
-      <x:c r="B188" s="31"/>
-      <x:c r="C188" s="31"/>
-      <x:c r="D188" s="31"/>
-      <x:c r="E188" s="31"/>
-      <x:c r="F188" s="31"/>
-      <x:c r="G188" s="37"/>
-      <x:c r="H188" s="31"/>
-      <x:c r="I188" s="31"/>
-      <x:c r="J188" s="31"/>
-      <x:c r="K188" s="31"/>
-      <x:c r="L188" s="31"/>
-      <x:c r="M188" s="31"/>
-      <x:c r="N188" s="31"/>
+      <x:c r="A188" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B188" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C188" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D188" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E188" s="33" t="str">
+        <x:v>Yes, all bloops must be lazzies.</x:v>
+      </x:c>
+      <x:c r="F188" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G188" s="35" t="n">
+        <x:v>4.511834166999961</x:v>
+      </x:c>
+      <x:c r="H188" s="33" t="str"/>
+      <x:c r="I188" s="33" t="str"/>
+      <x:c r="J188" s="33" t="str"/>
+      <x:c r="K188" s="33" t="str"/>
+      <x:c r="L188" s="33" t="str"/>
+      <x:c r="M188" s="33" t="str"/>
+      <x:c r="N188" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="O188" s="31"/>
       <x:c r="P188" s="31"/>
       <x:c r="Q188" s="31"/>
     </x:row>
     <x:row r="189">
-      <x:c r="A189" s="31"/>
-      <x:c r="B189" s="31"/>
-      <x:c r="C189" s="31"/>
-      <x:c r="D189" s="31"/>
-      <x:c r="E189" s="31"/>
-      <x:c r="F189" s="31"/>
-      <x:c r="G189" s="37"/>
-      <x:c r="H189" s="31"/>
-      <x:c r="I189" s="31"/>
-      <x:c r="J189" s="31"/>
-      <x:c r="K189" s="31"/>
-      <x:c r="L189" s="31"/>
-      <x:c r="M189" s="31"/>
-      <x:c r="N189" s="31"/>
+      <x:c r="A189" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B189" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C189" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D189" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E189" s="33" t="str">
+        <x:v>\dfrac{25}{2}</x:v>
+      </x:c>
+      <x:c r="F189" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G189" s="35" t="n">
+        <x:v>16.656210082999962</x:v>
+      </x:c>
+      <x:c r="H189" s="33" t="str"/>
+      <x:c r="I189" s="33" t="str"/>
+      <x:c r="J189" s="33" t="str"/>
+      <x:c r="K189" s="33" t="str"/>
+      <x:c r="L189" s="33" t="str"/>
+      <x:c r="M189" s="33" t="str"/>
+      <x:c r="N189" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O189" s="31"/>
       <x:c r="P189" s="31"/>
       <x:c r="Q189" s="31"/>
     </x:row>
     <x:row r="190">
-      <x:c r="A190" s="31"/>
-      <x:c r="B190" s="31"/>
-      <x:c r="C190" s="31"/>
-      <x:c r="D190" s="31"/>
-      <x:c r="E190" s="31"/>
-      <x:c r="F190" s="31"/>
-      <x:c r="G190" s="37"/>
-      <x:c r="H190" s="31"/>
-      <x:c r="I190" s="31"/>
-      <x:c r="J190" s="31"/>
-      <x:c r="K190" s="31"/>
-      <x:c r="L190" s="31"/>
-      <x:c r="M190" s="31"/>
-      <x:c r="N190" s="31"/>
+      <x:c r="A190" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B190" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C190" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D190" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E190" s="33" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F190" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G190" s="35" t="n">
+        <x:v>12.64156225000005</x:v>
+      </x:c>
+      <x:c r="H190" s="33" t="str"/>
+      <x:c r="I190" s="33" t="str"/>
+      <x:c r="J190" s="33" t="str"/>
+      <x:c r="K190" s="33" t="str"/>
+      <x:c r="L190" s="33" t="str"/>
+      <x:c r="M190" s="33" t="str"/>
+      <x:c r="N190" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O190" s="31"/>
       <x:c r="P190" s="31"/>
       <x:c r="Q190" s="31"/>
     </x:row>
     <x:row r="191">
-      <x:c r="A191" s="31"/>
-      <x:c r="B191" s="31"/>
-      <x:c r="C191" s="31"/>
-      <x:c r="D191" s="31"/>
-      <x:c r="E191" s="31"/>
-      <x:c r="F191" s="31"/>
-      <x:c r="G191" s="37"/>
-      <x:c r="H191" s="31"/>
-      <x:c r="I191" s="31"/>
-      <x:c r="J191" s="31"/>
-      <x:c r="K191" s="31"/>
-      <x:c r="L191" s="31"/>
-      <x:c r="M191" s="31"/>
-      <x:c r="N191" s="31"/>
+      <x:c r="A191" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B191" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C191" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D191" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E191" s="33" t="str">
+        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
+      </x:c>
+      <x:c r="F191" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G191" s="35" t="n">
+        <x:v>19.97141316599999</x:v>
+      </x:c>
+      <x:c r="H191" s="33" t="str"/>
+      <x:c r="I191" s="33" t="str"/>
+      <x:c r="J191" s="33" t="str"/>
+      <x:c r="K191" s="33" t="str"/>
+      <x:c r="L191" s="33" t="str"/>
+      <x:c r="M191" s="33" t="str"/>
+      <x:c r="N191" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O191" s="31"/>
       <x:c r="P191" s="31"/>
       <x:c r="Q191" s="31"/>
     </x:row>
     <x:row r="192">
-      <x:c r="A192" s="31"/>
-      <x:c r="B192" s="31"/>
-      <x:c r="C192" s="31"/>
-      <x:c r="D192" s="31"/>
-      <x:c r="E192" s="31"/>
-      <x:c r="F192" s="31"/>
-      <x:c r="G192" s="37"/>
-      <x:c r="H192" s="31"/>
-      <x:c r="I192" s="31"/>
-      <x:c r="J192" s="31"/>
-      <x:c r="K192" s="31"/>
-      <x:c r="L192" s="31"/>
-      <x:c r="M192" s="31"/>
-      <x:c r="N192" s="31"/>
+      <x:c r="A192" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B192" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C192" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D192" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E192" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F192" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G192" s="35" t="n">
+        <x:v>12.902716834000046</x:v>
+      </x:c>
+      <x:c r="H192" s="33" t="str"/>
+      <x:c r="I192" s="33" t="str"/>
+      <x:c r="J192" s="33" t="str"/>
+      <x:c r="K192" s="33" t="str"/>
+      <x:c r="L192" s="33" t="str"/>
+      <x:c r="M192" s="33" t="str"/>
+      <x:c r="N192" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O192" s="31"/>
       <x:c r="P192" s="31"/>
       <x:c r="Q192" s="31"/>
     </x:row>
     <x:row r="193">
-      <x:c r="A193" s="31"/>
-      <x:c r="B193" s="31"/>
-      <x:c r="C193" s="31"/>
-      <x:c r="D193" s="31"/>
-      <x:c r="E193" s="31"/>
-      <x:c r="F193" s="31"/>
-      <x:c r="G193" s="37"/>
-      <x:c r="H193" s="31"/>
-      <x:c r="I193" s="31"/>
-      <x:c r="J193" s="31"/>
-      <x:c r="K193" s="31"/>
-      <x:c r="L193" s="31"/>
-      <x:c r="M193" s="31"/>
-      <x:c r="N193" s="31"/>
+      <x:c r="A193" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B193" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C193" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D193" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E193" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F193" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G193" s="35" t="n">
+        <x:v>50.31506079099995</x:v>
+      </x:c>
+      <x:c r="H193" s="33" t="str"/>
+      <x:c r="I193" s="33" t="str"/>
+      <x:c r="J193" s="33" t="str"/>
+      <x:c r="K193" s="33" t="str"/>
+      <x:c r="L193" s="33" t="str"/>
+      <x:c r="M193" s="33" t="str"/>
+      <x:c r="N193" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O193" s="31"/>
       <x:c r="P193" s="31"/>
       <x:c r="Q193" s="31"/>
     </x:row>
     <x:row r="194">
-      <x:c r="A194" s="31"/>
-      <x:c r="B194" s="31"/>
-      <x:c r="C194" s="31"/>
-      <x:c r="D194" s="31"/>
-      <x:c r="E194" s="31"/>
-      <x:c r="F194" s="31"/>
-      <x:c r="G194" s="37"/>
-      <x:c r="H194" s="31"/>
-      <x:c r="I194" s="31"/>
-      <x:c r="J194" s="31"/>
-      <x:c r="K194" s="31"/>
-      <x:c r="L194" s="31"/>
-      <x:c r="M194" s="31"/>
-      <x:c r="N194" s="31"/>
+      <x:c r="A194" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B194" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C194" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D194" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E194" s="33" t="str">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="F194" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G194" s="35" t="n">
+        <x:v>33.462693083999966</x:v>
+      </x:c>
+      <x:c r="H194" s="33" t="str"/>
+      <x:c r="I194" s="33" t="str"/>
+      <x:c r="J194" s="33" t="str"/>
+      <x:c r="K194" s="33" t="str"/>
+      <x:c r="L194" s="33" t="str"/>
+      <x:c r="M194" s="33" t="str"/>
+      <x:c r="N194" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O194" s="31"/>
       <x:c r="P194" s="31"/>
       <x:c r="Q194" s="31"/>
     </x:row>
     <x:row r="195">
-      <x:c r="A195" s="31"/>
-      <x:c r="B195" s="31"/>
-      <x:c r="C195" s="31"/>
-      <x:c r="D195" s="31"/>
-      <x:c r="E195" s="31"/>
-      <x:c r="F195" s="31"/>
-      <x:c r="G195" s="37"/>
-      <x:c r="H195" s="31"/>
-      <x:c r="I195" s="31"/>
-      <x:c r="J195" s="31"/>
-      <x:c r="K195" s="31"/>
-      <x:c r="L195" s="31"/>
-      <x:c r="M195" s="31"/>
-      <x:c r="N195" s="31"/>
+      <x:c r="A195" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B195" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C195" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D195" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E195" s="33" t="str">
+        <x:v>\dfrac{1}{9}</x:v>
+      </x:c>
+      <x:c r="F195" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G195" s="35" t="n">
+        <x:v>7.085368707999919</x:v>
+      </x:c>
+      <x:c r="H195" s="33" t="str"/>
+      <x:c r="I195" s="33" t="str"/>
+      <x:c r="J195" s="33" t="str"/>
+      <x:c r="K195" s="33" t="str"/>
+      <x:c r="L195" s="33" t="str"/>
+      <x:c r="M195" s="33" t="str"/>
+      <x:c r="N195" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O195" s="31"/>
       <x:c r="P195" s="31"/>
       <x:c r="Q195" s="31"/>
     </x:row>
     <x:row r="196">
-      <x:c r="A196" s="31"/>
-      <x:c r="B196" s="31"/>
-      <x:c r="C196" s="31"/>
-      <x:c r="D196" s="31"/>
-      <x:c r="E196" s="31"/>
-      <x:c r="F196" s="31"/>
-      <x:c r="G196" s="37"/>
-      <x:c r="H196" s="31"/>
-      <x:c r="I196" s="31"/>
-      <x:c r="J196" s="31"/>
-      <x:c r="K196" s="31"/>
-      <x:c r="L196" s="31"/>
-      <x:c r="M196" s="31"/>
-      <x:c r="N196" s="31"/>
+      <x:c r="A196" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B196" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C196" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D196" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E196" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F196" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G196" s="35" t="n">
+        <x:v>15.824353458000019</x:v>
+      </x:c>
+      <x:c r="H196" s="33" t="str"/>
+      <x:c r="I196" s="33" t="str"/>
+      <x:c r="J196" s="33" t="str"/>
+      <x:c r="K196" s="33" t="str"/>
+      <x:c r="L196" s="33" t="str"/>
+      <x:c r="M196" s="33" t="str"/>
+      <x:c r="N196" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O196" s="31"/>
       <x:c r="P196" s="31"/>
       <x:c r="Q196" s="31"/>
     </x:row>
     <x:row r="197">
-      <x:c r="A197" s="31"/>
-      <x:c r="B197" s="31"/>
-      <x:c r="C197" s="31"/>
-      <x:c r="D197" s="31"/>
-      <x:c r="E197" s="31"/>
-      <x:c r="F197" s="31"/>
-      <x:c r="G197" s="37"/>
-      <x:c r="H197" s="31"/>
-      <x:c r="I197" s="31"/>
-      <x:c r="J197" s="31"/>
-      <x:c r="K197" s="31"/>
-      <x:c r="L197" s="31"/>
-      <x:c r="M197" s="31"/>
-      <x:c r="N197" s="31"/>
+      <x:c r="A197" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B197" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C197" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D197" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E197" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F197" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G197" s="35" t="n">
+        <x:v>8.149854707999907</x:v>
+      </x:c>
+      <x:c r="H197" s="33" t="str"/>
+      <x:c r="I197" s="33" t="str"/>
+      <x:c r="J197" s="33" t="str"/>
+      <x:c r="K197" s="33" t="str"/>
+      <x:c r="L197" s="33" t="str"/>
+      <x:c r="M197" s="33" t="str"/>
+      <x:c r="N197" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O197" s="31"/>
       <x:c r="P197" s="31"/>
       <x:c r="Q197" s="31"/>
     </x:row>
     <x:row r="198">
-      <x:c r="A198" s="31"/>
-      <x:c r="B198" s="31"/>
-      <x:c r="C198" s="31"/>
-      <x:c r="D198" s="31"/>
-      <x:c r="E198" s="31"/>
-      <x:c r="F198" s="31"/>
-      <x:c r="G198" s="37"/>
-      <x:c r="H198" s="31"/>
-      <x:c r="I198" s="31"/>
-      <x:c r="J198" s="31"/>
-      <x:c r="K198" s="31"/>
-      <x:c r="L198" s="31"/>
-      <x:c r="M198" s="31"/>
-      <x:c r="N198" s="31"/>
+      <x:c r="A198" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B198" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C198" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D198" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E198" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F198" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G198" s="35" t="n">
+        <x:v>6.157211500000017</x:v>
+      </x:c>
+      <x:c r="H198" s="33" t="str"/>
+      <x:c r="I198" s="33" t="str"/>
+      <x:c r="J198" s="33" t="str"/>
+      <x:c r="K198" s="33" t="str"/>
+      <x:c r="L198" s="33" t="str"/>
+      <x:c r="M198" s="33" t="str"/>
+      <x:c r="N198" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O198" s="31"/>
       <x:c r="P198" s="31"/>
       <x:c r="Q198" s="31"/>
     </x:row>
     <x:row r="199">
-      <x:c r="A199" s="31"/>
-      <x:c r="B199" s="31"/>
-      <x:c r="C199" s="31"/>
-      <x:c r="D199" s="31"/>
-      <x:c r="E199" s="31"/>
-      <x:c r="F199" s="31"/>
-      <x:c r="G199" s="37"/>
-      <x:c r="H199" s="31"/>
-      <x:c r="I199" s="31"/>
-      <x:c r="J199" s="31"/>
-      <x:c r="K199" s="31"/>
-      <x:c r="L199" s="31"/>
-      <x:c r="M199" s="31"/>
-      <x:c r="N199" s="31"/>
+      <x:c r="A199" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B199" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C199" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D199" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E199" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F199" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G199" s="35" t="n">
+        <x:v>21.503388040999994</x:v>
+      </x:c>
+      <x:c r="H199" s="33" t="str"/>
+      <x:c r="I199" s="33" t="str"/>
+      <x:c r="J199" s="33" t="str"/>
+      <x:c r="K199" s="33" t="str"/>
+      <x:c r="L199" s="33" t="str"/>
+      <x:c r="M199" s="33" t="str"/>
+      <x:c r="N199" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O199" s="31"/>
       <x:c r="P199" s="31"/>
       <x:c r="Q199" s="31"/>
     </x:row>
     <x:row r="200">
-      <x:c r="A200" s="31"/>
-      <x:c r="B200" s="31"/>
-      <x:c r="C200" s="31"/>
-      <x:c r="D200" s="31"/>
-      <x:c r="E200" s="31"/>
-      <x:c r="F200" s="31"/>
-      <x:c r="G200" s="37"/>
-      <x:c r="H200" s="31"/>
-      <x:c r="I200" s="31"/>
-      <x:c r="J200" s="31"/>
-      <x:c r="K200" s="31"/>
-      <x:c r="L200" s="31"/>
-      <x:c r="M200" s="31"/>
-      <x:c r="N200" s="31"/>
+      <x:c r="A200" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B200" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C200" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D200" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E200" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F200" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G200" s="35" t="n">
+        <x:v>7.560139790999983</x:v>
+      </x:c>
+      <x:c r="H200" s="33" t="str"/>
+      <x:c r="I200" s="33" t="str"/>
+      <x:c r="J200" s="33" t="str"/>
+      <x:c r="K200" s="33" t="str"/>
+      <x:c r="L200" s="33" t="str"/>
+      <x:c r="M200" s="33" t="str"/>
+      <x:c r="N200" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O200" s="31"/>
       <x:c r="P200" s="31"/>
       <x:c r="Q200" s="31"/>
     </x:row>
     <x:row r="201">
-      <x:c r="A201" s="31"/>
-      <x:c r="B201" s="31"/>
-      <x:c r="C201" s="31"/>
-      <x:c r="D201" s="31"/>
-      <x:c r="E201" s="31"/>
-      <x:c r="F201" s="31"/>
-      <x:c r="G201" s="37"/>
-      <x:c r="H201" s="31"/>
-      <x:c r="I201" s="31"/>
-      <x:c r="J201" s="31"/>
-      <x:c r="K201" s="31"/>
-      <x:c r="L201" s="31"/>
-      <x:c r="M201" s="31"/>
-      <x:c r="N201" s="31"/>
+      <x:c r="A201" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B201" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C201" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D201" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E201" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F201" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G201" s="35" t="n">
+        <x:v>8.231041165999955</x:v>
+      </x:c>
+      <x:c r="H201" s="33" t="str"/>
+      <x:c r="I201" s="33" t="str"/>
+      <x:c r="J201" s="33" t="str"/>
+      <x:c r="K201" s="33" t="str"/>
+      <x:c r="L201" s="33" t="str"/>
+      <x:c r="M201" s="33" t="str"/>
+      <x:c r="N201" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O201" s="31"/>
       <x:c r="P201" s="31"/>
       <x:c r="Q201" s="31"/>
     </x:row>
     <x:row r="202">
-      <x:c r="A202" s="31"/>
-      <x:c r="B202" s="31"/>
-      <x:c r="C202" s="31"/>
-      <x:c r="D202" s="31"/>
-      <x:c r="E202" s="31"/>
-      <x:c r="F202" s="31"/>
-      <x:c r="G202" s="37"/>
-      <x:c r="H202" s="31"/>
-      <x:c r="I202" s="31"/>
-      <x:c r="J202" s="31"/>
-      <x:c r="K202" s="31"/>
-      <x:c r="L202" s="31"/>
-      <x:c r="M202" s="31"/>
-      <x:c r="N202" s="31"/>
+      <x:c r="A202" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B202" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C202" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D202" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E202" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F202" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G202" s="35" t="n">
+        <x:v>30.73365029099989</x:v>
+      </x:c>
+      <x:c r="H202" s="33" t="str"/>
+      <x:c r="I202" s="33" t="str"/>
+      <x:c r="J202" s="33" t="str"/>
+      <x:c r="K202" s="33" t="str"/>
+      <x:c r="L202" s="33" t="str"/>
+      <x:c r="M202" s="33" t="str"/>
+      <x:c r="N202" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O202" s="31"/>
       <x:c r="P202" s="31"/>
       <x:c r="Q202" s="31"/>
     </x:row>
     <x:row r="203">
-      <x:c r="A203" s="31"/>
-      <x:c r="B203" s="31"/>
-      <x:c r="C203" s="31"/>
-      <x:c r="D203" s="31"/>
-      <x:c r="E203" s="31"/>
-      <x:c r="F203" s="31"/>
-      <x:c r="G203" s="37"/>
-      <x:c r="H203" s="31"/>
-      <x:c r="I203" s="31"/>
-      <x:c r="J203" s="31"/>
-      <x:c r="K203" s="31"/>
-      <x:c r="L203" s="31"/>
-      <x:c r="M203" s="31"/>
-      <x:c r="N203" s="31"/>
+      <x:c r="A203" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B203" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C203" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D203" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E203" s="33" t="str">
+        <x:v>\dfrac{3}{8}</x:v>
+      </x:c>
+      <x:c r="F203" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G203" s="35" t="n">
+        <x:v>11.049620875000073</x:v>
+      </x:c>
+      <x:c r="H203" s="33" t="str"/>
+      <x:c r="I203" s="33" t="str"/>
+      <x:c r="J203" s="33" t="str"/>
+      <x:c r="K203" s="33" t="str"/>
+      <x:c r="L203" s="33" t="str"/>
+      <x:c r="M203" s="33" t="str"/>
+      <x:c r="N203" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O203" s="31"/>
       <x:c r="P203" s="31"/>
       <x:c r="Q203" s="31"/>
     </x:row>
     <x:row r="204">
-      <x:c r="A204" s="31"/>
-      <x:c r="B204" s="31"/>
-      <x:c r="C204" s="31"/>
-      <x:c r="D204" s="31"/>
-      <x:c r="E204" s="31"/>
-      <x:c r="F204" s="31"/>
-      <x:c r="G204" s="37"/>
-      <x:c r="H204" s="31"/>
-      <x:c r="I204" s="31"/>
-      <x:c r="J204" s="31"/>
-      <x:c r="K204" s="31"/>
-      <x:c r="L204" s="31"/>
-      <x:c r="M204" s="31"/>
-      <x:c r="N204" s="31"/>
+      <x:c r="A204" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B204" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C204" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D204" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E204" s="33" t="str">
+        <x:v>All methods confirm that the remainder when</x:v>
+      </x:c>
+      <x:c r="F204" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G204" s="35" t="n">
+        <x:v>67.06586500000003</x:v>
+      </x:c>
+      <x:c r="H204" s="33" t="str"/>
+      <x:c r="I204" s="33" t="str"/>
+      <x:c r="J204" s="33" t="str"/>
+      <x:c r="K204" s="33" t="str"/>
+      <x:c r="L204" s="33" t="str"/>
+      <x:c r="M204" s="33" t="str"/>
+      <x:c r="N204" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O204" s="31"/>
       <x:c r="P204" s="31"/>
       <x:c r="Q204" s="31"/>
     </x:row>
     <x:row r="205">
-      <x:c r="A205" s="31"/>
-      <x:c r="B205" s="31"/>
-      <x:c r="C205" s="31"/>
-      <x:c r="D205" s="31"/>
-      <x:c r="E205" s="31"/>
-      <x:c r="F205" s="31"/>
-      <x:c r="G205" s="37"/>
-      <x:c r="H205" s="31"/>
-      <x:c r="I205" s="31"/>
-      <x:c r="J205" s="31"/>
-      <x:c r="K205" s="31"/>
-      <x:c r="L205" s="31"/>
-      <x:c r="M205" s="31"/>
-      <x:c r="N205" s="31"/>
+      <x:c r="A205" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B205" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C205" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D205" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E205" s="33" t="str">
+        <x:v>Yes, all bloops must be lazzies.</x:v>
+      </x:c>
+      <x:c r="F205" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G205" s="35" t="n">
+        <x:v>8.902264708000075</x:v>
+      </x:c>
+      <x:c r="H205" s="33" t="str"/>
+      <x:c r="I205" s="33" t="str"/>
+      <x:c r="J205" s="33" t="str"/>
+      <x:c r="K205" s="33" t="str"/>
+      <x:c r="L205" s="33" t="str"/>
+      <x:c r="M205" s="33" t="str"/>
+      <x:c r="N205" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="O205" s="31"/>
       <x:c r="P205" s="31"/>
       <x:c r="Q205" s="31"/>
@@ -48831,7 +49891,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="150.17999267578125" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="150.6699981689453" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -48951,10 +50011,10 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="41" t="str">
-        <x:v>HRM-Text comparison</x:v>
+        <x:v>Qwen chat exact</x:v>
       </x:c>
       <x:c r="B6" s="41" t="str">
-        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
+        <x:v>On Qwen3-1.7B chat-template boxed runs, fixed blend scores 5/17 while agreement_blend and confidence_gate recover the 6/17 base score. Use gated fusion for open-ended generation.</x:v>
       </x:c>
       <x:c r="C6" s="31"/>
       <x:c r="D6" s="31"/>
@@ -48974,10 +50034,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41" t="str">
-        <x:v>Cost</x:v>
+        <x:v>HRM-Text comparison</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
+        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="31"/>
@@ -48997,10 +50057,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="41" t="str">
-        <x:v>Correction</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="B8" s="41" t="str">
-        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
+        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
       </x:c>
       <x:c r="C8" s="31"/>
       <x:c r="D8" s="31"/>
@@ -49020,10 +50080,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="41" t="str">
-        <x:v>Interpretation</x:v>
+        <x:v>Correction</x:v>
       </x:c>
       <x:c r="B9" s="41" t="str">
-        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
+        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
       </x:c>
       <x:c r="C9" s="31"/>
       <x:c r="D9" s="31"/>
@@ -49043,10 +50103,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="41" t="str">
-        <x:v>Fusion finding</x:v>
+        <x:v>Interpretation</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
-        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
+        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
       </x:c>
       <x:c r="C10" s="31"/>
       <x:c r="D10" s="31"/>
@@ -49066,10 +50126,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="41" t="str">
-        <x:v>Next</x:v>
+        <x:v>Fusion finding</x:v>
       </x:c>
       <x:c r="B11" s="41" t="str">
-        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
       </x:c>
       <x:c r="C11" s="31"/>
       <x:c r="D11" s="31"/>
@@ -49088,8 +50148,12 @@
       <x:c r="Q11" s="31"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="31"/>
-      <x:c r="B12" s="31"/>
+      <x:c r="A12" s="41" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="B12" s="41" t="str">
+        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+      </x:c>
       <x:c r="C12" s="31"/>
       <x:c r="D12" s="31"/>
       <x:c r="E12" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3fa16c7f16f442ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R8e9feec5e87a4dbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R840d8c7890074c7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rc40f45fdb4984d2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R2a205f416a534ef8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="Re730bb69a1374e6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" r:id="R6a2e93fa2058403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R97639377aca2415c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="Rbc0c7b08881447cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R40a4a6b7cd534859"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rdcdfeb4589164a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="Rd0f97212282e43db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R2e6e5a9e5dcb4fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R1d21cfee99e04b45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" r:id="Rde30761b90f345c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -49890,6 +49891,5904 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="6.010000228881836" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.229999542236328" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4.909999847412109" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="4.050000190734863" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12.390000343322754" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="45.029998779296875" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="33.9900016784668" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="32" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>Verifier</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>Scoring</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
+        <x:v>Fusion</x:v>
+      </x:c>
+      <x:c r="E1" s="32" t="str">
+        <x:v>Blend</x:v>
+      </x:c>
+      <x:c r="F1" s="32" t="str">
+        <x:v>Correct</x:v>
+      </x:c>
+      <x:c r="G1" s="32" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="H1" s="32" t="str">
+        <x:v>Accuracy</x:v>
+      </x:c>
+      <x:c r="I1" s="32" t="str">
+        <x:v>Chat Template</x:v>
+      </x:c>
+      <x:c r="J1" s="32" t="str">
+        <x:v>Correct Cases</x:v>
+      </x:c>
+      <x:c r="K1" s="32" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="L1" s="31"/>
+      <x:c r="M1" s="31"/>
+      <x:c r="N1" s="31"/>
+      <x:c r="O1" s="31"/>
+      <x:c r="P1" s="31"/>
+      <x:c r="Q1" s="31"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B2" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="C2" s="33" t="str">
+        <x:v>yesno</x:v>
+      </x:c>
+      <x:c r="D2" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E2" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F2" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H2" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I2" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J2" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="K2" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
+      </x:c>
+      <x:c r="L2" s="31"/>
+      <x:c r="M2" s="31"/>
+      <x:c r="N2" s="31"/>
+      <x:c r="O2" s="31"/>
+      <x:c r="P2" s="31"/>
+      <x:c r="Q2" s="31"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B3" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="C3" s="33" t="str">
+        <x:v>yesno</x:v>
+      </x:c>
+      <x:c r="D3" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E3" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F3" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G3" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H3" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I3" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J3" s="33" t="str">
+        <x:v>boxes, probability, sequence, reverse_discount, average</x:v>
+      </x:c>
+      <x:c r="K3" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base.csv</x:v>
+      </x:c>
+      <x:c r="L3" s="31"/>
+      <x:c r="M3" s="31"/>
+      <x:c r="N3" s="31"/>
+      <x:c r="O3" s="31"/>
+      <x:c r="P3" s="31"/>
+      <x:c r="Q3" s="31"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>hrm</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="str">
+        <x:v>yesno</x:v>
+      </x:c>
+      <x:c r="D4" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E4" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F4" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G4" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H4" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I4" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J4" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="K4" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
+      </x:c>
+      <x:c r="L4" s="31"/>
+      <x:c r="M4" s="31"/>
+      <x:c r="N4" s="31"/>
+      <x:c r="O4" s="31"/>
+      <x:c r="P4" s="31"/>
+      <x:c r="Q4" s="31"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B5" s="33" t="str">
+        <x:v>hrm</x:v>
+      </x:c>
+      <x:c r="C5" s="33" t="str">
+        <x:v>yesno</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E5" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F5" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G5" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H5" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I5" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J5" s="33" t="str">
+        <x:v>boxes, probability, sequence, reverse_discount, average</x:v>
+      </x:c>
+      <x:c r="K5" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base.csv</x:v>
+      </x:c>
+      <x:c r="L5" s="31"/>
+      <x:c r="M5" s="31"/>
+      <x:c r="N5" s="31"/>
+      <x:c r="O5" s="31"/>
+      <x:c r="P5" s="31"/>
+      <x:c r="Q5" s="31"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="str">
+        <x:v>answer_likelihood</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F6" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G6" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H6" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I6" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J6" s="33" t="str">
+        <x:v>markup, probability, coins, markup, probability, coins</x:v>
+      </x:c>
+      <x:c r="K6" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
+      </x:c>
+      <x:c r="L6" s="31"/>
+      <x:c r="M6" s="31"/>
+      <x:c r="N6" s="31"/>
+      <x:c r="O6" s="31"/>
+      <x:c r="P6" s="31"/>
+      <x:c r="Q6" s="31"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B7" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="C7" s="33" t="str">
+        <x:v>answer_likelihood</x:v>
+      </x:c>
+      <x:c r="D7" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E7" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F7" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I7" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J7" s="33" t="str">
+        <x:v>boxes, sequence, average, boxes, average</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base.csv</x:v>
+      </x:c>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="31"/>
+      <x:c r="N7" s="31"/>
+      <x:c r="O7" s="31"/>
+      <x:c r="P7" s="31"/>
+      <x:c r="Q7" s="31"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="str">
+        <x:v>answer_likelihood</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="E8" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H8" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="I8" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="K8" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
+      </x:c>
+      <x:c r="L8" s="31"/>
+      <x:c r="M8" s="31"/>
+      <x:c r="N8" s="31"/>
+      <x:c r="O8" s="31"/>
+      <x:c r="P8" s="31"/>
+      <x:c r="Q8" s="31"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="31"/>
+      <x:c r="B9" s="31"/>
+      <x:c r="C9" s="31"/>
+      <x:c r="D9" s="31"/>
+      <x:c r="E9" s="31"/>
+      <x:c r="F9" s="31"/>
+      <x:c r="G9" s="31"/>
+      <x:c r="H9" s="36"/>
+      <x:c r="I9" s="31"/>
+      <x:c r="J9" s="31"/>
+      <x:c r="K9" s="31"/>
+      <x:c r="L9" s="31"/>
+      <x:c r="M9" s="31"/>
+      <x:c r="N9" s="31"/>
+      <x:c r="O9" s="31"/>
+      <x:c r="P9" s="31"/>
+      <x:c r="Q9" s="31"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="31"/>
+      <x:c r="B10" s="31"/>
+      <x:c r="C10" s="31"/>
+      <x:c r="D10" s="31"/>
+      <x:c r="E10" s="31"/>
+      <x:c r="F10" s="31"/>
+      <x:c r="G10" s="31"/>
+      <x:c r="H10" s="36"/>
+      <x:c r="I10" s="31"/>
+      <x:c r="J10" s="31"/>
+      <x:c r="K10" s="31"/>
+      <x:c r="L10" s="31"/>
+      <x:c r="M10" s="31"/>
+      <x:c r="N10" s="31"/>
+      <x:c r="O10" s="31"/>
+      <x:c r="P10" s="31"/>
+      <x:c r="Q10" s="31"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="31"/>
+      <x:c r="B11" s="31"/>
+      <x:c r="C11" s="31"/>
+      <x:c r="D11" s="31"/>
+      <x:c r="E11" s="31"/>
+      <x:c r="F11" s="31"/>
+      <x:c r="G11" s="31"/>
+      <x:c r="H11" s="36"/>
+      <x:c r="I11" s="31"/>
+      <x:c r="J11" s="31"/>
+      <x:c r="K11" s="31"/>
+      <x:c r="L11" s="31"/>
+      <x:c r="M11" s="31"/>
+      <x:c r="N11" s="31"/>
+      <x:c r="O11" s="31"/>
+      <x:c r="P11" s="31"/>
+      <x:c r="Q11" s="31"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31"/>
+      <x:c r="B12" s="31"/>
+      <x:c r="C12" s="31"/>
+      <x:c r="D12" s="31"/>
+      <x:c r="E12" s="31"/>
+      <x:c r="F12" s="31"/>
+      <x:c r="G12" s="31"/>
+      <x:c r="H12" s="36"/>
+      <x:c r="I12" s="31"/>
+      <x:c r="J12" s="31"/>
+      <x:c r="K12" s="31"/>
+      <x:c r="L12" s="31"/>
+      <x:c r="M12" s="31"/>
+      <x:c r="N12" s="31"/>
+      <x:c r="O12" s="31"/>
+      <x:c r="P12" s="31"/>
+      <x:c r="Q12" s="31"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="31"/>
+      <x:c r="B13" s="31"/>
+      <x:c r="C13" s="31"/>
+      <x:c r="D13" s="31"/>
+      <x:c r="E13" s="31"/>
+      <x:c r="F13" s="31"/>
+      <x:c r="G13" s="31"/>
+      <x:c r="H13" s="36"/>
+      <x:c r="I13" s="31"/>
+      <x:c r="J13" s="31"/>
+      <x:c r="K13" s="31"/>
+      <x:c r="L13" s="31"/>
+      <x:c r="M13" s="31"/>
+      <x:c r="N13" s="31"/>
+      <x:c r="O13" s="31"/>
+      <x:c r="P13" s="31"/>
+      <x:c r="Q13" s="31"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="31"/>
+      <x:c r="B14" s="31"/>
+      <x:c r="C14" s="31"/>
+      <x:c r="D14" s="31"/>
+      <x:c r="E14" s="31"/>
+      <x:c r="F14" s="31"/>
+      <x:c r="G14" s="31"/>
+      <x:c r="H14" s="36"/>
+      <x:c r="I14" s="31"/>
+      <x:c r="J14" s="31"/>
+      <x:c r="K14" s="31"/>
+      <x:c r="L14" s="31"/>
+      <x:c r="M14" s="31"/>
+      <x:c r="N14" s="31"/>
+      <x:c r="O14" s="31"/>
+      <x:c r="P14" s="31"/>
+      <x:c r="Q14" s="31"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="31"/>
+      <x:c r="B15" s="31"/>
+      <x:c r="C15" s="31"/>
+      <x:c r="D15" s="31"/>
+      <x:c r="E15" s="31"/>
+      <x:c r="F15" s="31"/>
+      <x:c r="G15" s="31"/>
+      <x:c r="H15" s="36"/>
+      <x:c r="I15" s="31"/>
+      <x:c r="J15" s="31"/>
+      <x:c r="K15" s="31"/>
+      <x:c r="L15" s="31"/>
+      <x:c r="M15" s="31"/>
+      <x:c r="N15" s="31"/>
+      <x:c r="O15" s="31"/>
+      <x:c r="P15" s="31"/>
+      <x:c r="Q15" s="31"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="31"/>
+      <x:c r="B16" s="31"/>
+      <x:c r="C16" s="31"/>
+      <x:c r="D16" s="31"/>
+      <x:c r="E16" s="31"/>
+      <x:c r="F16" s="31"/>
+      <x:c r="G16" s="31"/>
+      <x:c r="H16" s="36"/>
+      <x:c r="I16" s="31"/>
+      <x:c r="J16" s="31"/>
+      <x:c r="K16" s="31"/>
+      <x:c r="L16" s="31"/>
+      <x:c r="M16" s="31"/>
+      <x:c r="N16" s="31"/>
+      <x:c r="O16" s="31"/>
+      <x:c r="P16" s="31"/>
+      <x:c r="Q16" s="31"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="31"/>
+      <x:c r="B17" s="31"/>
+      <x:c r="C17" s="31"/>
+      <x:c r="D17" s="31"/>
+      <x:c r="E17" s="31"/>
+      <x:c r="F17" s="31"/>
+      <x:c r="G17" s="31"/>
+      <x:c r="H17" s="36"/>
+      <x:c r="I17" s="31"/>
+      <x:c r="J17" s="31"/>
+      <x:c r="K17" s="31"/>
+      <x:c r="L17" s="31"/>
+      <x:c r="M17" s="31"/>
+      <x:c r="N17" s="31"/>
+      <x:c r="O17" s="31"/>
+      <x:c r="P17" s="31"/>
+      <x:c r="Q17" s="31"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
+      <x:c r="G18" s="31"/>
+      <x:c r="H18" s="36"/>
+      <x:c r="I18" s="31"/>
+      <x:c r="J18" s="31"/>
+      <x:c r="K18" s="31"/>
+      <x:c r="L18" s="31"/>
+      <x:c r="M18" s="31"/>
+      <x:c r="N18" s="31"/>
+      <x:c r="O18" s="31"/>
+      <x:c r="P18" s="31"/>
+      <x:c r="Q18" s="31"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31"/>
+      <x:c r="B19" s="31"/>
+      <x:c r="C19" s="31"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="31"/>
+      <x:c r="F19" s="31"/>
+      <x:c r="G19" s="31"/>
+      <x:c r="H19" s="36"/>
+      <x:c r="I19" s="31"/>
+      <x:c r="J19" s="31"/>
+      <x:c r="K19" s="31"/>
+      <x:c r="L19" s="31"/>
+      <x:c r="M19" s="31"/>
+      <x:c r="N19" s="31"/>
+      <x:c r="O19" s="31"/>
+      <x:c r="P19" s="31"/>
+      <x:c r="Q19" s="31"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31"/>
+      <x:c r="B20" s="31"/>
+      <x:c r="C20" s="31"/>
+      <x:c r="D20" s="31"/>
+      <x:c r="E20" s="31"/>
+      <x:c r="F20" s="31"/>
+      <x:c r="G20" s="31"/>
+      <x:c r="H20" s="36"/>
+      <x:c r="I20" s="31"/>
+      <x:c r="J20" s="31"/>
+      <x:c r="K20" s="31"/>
+      <x:c r="L20" s="31"/>
+      <x:c r="M20" s="31"/>
+      <x:c r="N20" s="31"/>
+      <x:c r="O20" s="31"/>
+      <x:c r="P20" s="31"/>
+      <x:c r="Q20" s="31"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31"/>
+      <x:c r="B21" s="31"/>
+      <x:c r="C21" s="31"/>
+      <x:c r="D21" s="31"/>
+      <x:c r="E21" s="31"/>
+      <x:c r="F21" s="31"/>
+      <x:c r="G21" s="31"/>
+      <x:c r="H21" s="36"/>
+      <x:c r="I21" s="31"/>
+      <x:c r="J21" s="31"/>
+      <x:c r="K21" s="31"/>
+      <x:c r="L21" s="31"/>
+      <x:c r="M21" s="31"/>
+      <x:c r="N21" s="31"/>
+      <x:c r="O21" s="31"/>
+      <x:c r="P21" s="31"/>
+      <x:c r="Q21" s="31"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31"/>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+      <x:c r="F22" s="31"/>
+      <x:c r="G22" s="31"/>
+      <x:c r="H22" s="36"/>
+      <x:c r="I22" s="31"/>
+      <x:c r="J22" s="31"/>
+      <x:c r="K22" s="31"/>
+      <x:c r="L22" s="31"/>
+      <x:c r="M22" s="31"/>
+      <x:c r="N22" s="31"/>
+      <x:c r="O22" s="31"/>
+      <x:c r="P22" s="31"/>
+      <x:c r="Q22" s="31"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31"/>
+      <x:c r="B23" s="31"/>
+      <x:c r="C23" s="31"/>
+      <x:c r="D23" s="31"/>
+      <x:c r="E23" s="31"/>
+      <x:c r="F23" s="31"/>
+      <x:c r="G23" s="31"/>
+      <x:c r="H23" s="36"/>
+      <x:c r="I23" s="31"/>
+      <x:c r="J23" s="31"/>
+      <x:c r="K23" s="31"/>
+      <x:c r="L23" s="31"/>
+      <x:c r="M23" s="31"/>
+      <x:c r="N23" s="31"/>
+      <x:c r="O23" s="31"/>
+      <x:c r="P23" s="31"/>
+      <x:c r="Q23" s="31"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="31"/>
+      <x:c r="B24" s="31"/>
+      <x:c r="C24" s="31"/>
+      <x:c r="D24" s="31"/>
+      <x:c r="E24" s="31"/>
+      <x:c r="F24" s="31"/>
+      <x:c r="G24" s="31"/>
+      <x:c r="H24" s="36"/>
+      <x:c r="I24" s="31"/>
+      <x:c r="J24" s="31"/>
+      <x:c r="K24" s="31"/>
+      <x:c r="L24" s="31"/>
+      <x:c r="M24" s="31"/>
+      <x:c r="N24" s="31"/>
+      <x:c r="O24" s="31"/>
+      <x:c r="P24" s="31"/>
+      <x:c r="Q24" s="31"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31"/>
+      <x:c r="B25" s="31"/>
+      <x:c r="C25" s="31"/>
+      <x:c r="D25" s="31"/>
+      <x:c r="E25" s="31"/>
+      <x:c r="F25" s="31"/>
+      <x:c r="G25" s="31"/>
+      <x:c r="H25" s="36"/>
+      <x:c r="I25" s="31"/>
+      <x:c r="J25" s="31"/>
+      <x:c r="K25" s="31"/>
+      <x:c r="L25" s="31"/>
+      <x:c r="M25" s="31"/>
+      <x:c r="N25" s="31"/>
+      <x:c r="O25" s="31"/>
+      <x:c r="P25" s="31"/>
+      <x:c r="Q25" s="31"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31"/>
+      <x:c r="B26" s="31"/>
+      <x:c r="C26" s="31"/>
+      <x:c r="D26" s="31"/>
+      <x:c r="E26" s="31"/>
+      <x:c r="F26" s="31"/>
+      <x:c r="G26" s="31"/>
+      <x:c r="H26" s="36"/>
+      <x:c r="I26" s="31"/>
+      <x:c r="J26" s="31"/>
+      <x:c r="K26" s="31"/>
+      <x:c r="L26" s="31"/>
+      <x:c r="M26" s="31"/>
+      <x:c r="N26" s="31"/>
+      <x:c r="O26" s="31"/>
+      <x:c r="P26" s="31"/>
+      <x:c r="Q26" s="31"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+      <x:c r="F27" s="31"/>
+      <x:c r="G27" s="31"/>
+      <x:c r="H27" s="36"/>
+      <x:c r="I27" s="31"/>
+      <x:c r="J27" s="31"/>
+      <x:c r="K27" s="31"/>
+      <x:c r="L27" s="31"/>
+      <x:c r="M27" s="31"/>
+      <x:c r="N27" s="31"/>
+      <x:c r="O27" s="31"/>
+      <x:c r="P27" s="31"/>
+      <x:c r="Q27" s="31"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="31"/>
+      <x:c r="B28" s="31"/>
+      <x:c r="C28" s="31"/>
+      <x:c r="D28" s="31"/>
+      <x:c r="E28" s="31"/>
+      <x:c r="F28" s="31"/>
+      <x:c r="G28" s="31"/>
+      <x:c r="H28" s="36"/>
+      <x:c r="I28" s="31"/>
+      <x:c r="J28" s="31"/>
+      <x:c r="K28" s="31"/>
+      <x:c r="L28" s="31"/>
+      <x:c r="M28" s="31"/>
+      <x:c r="N28" s="31"/>
+      <x:c r="O28" s="31"/>
+      <x:c r="P28" s="31"/>
+      <x:c r="Q28" s="31"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="31"/>
+      <x:c r="B29" s="31"/>
+      <x:c r="C29" s="31"/>
+      <x:c r="D29" s="31"/>
+      <x:c r="E29" s="31"/>
+      <x:c r="F29" s="31"/>
+      <x:c r="G29" s="31"/>
+      <x:c r="H29" s="36"/>
+      <x:c r="I29" s="31"/>
+      <x:c r="J29" s="31"/>
+      <x:c r="K29" s="31"/>
+      <x:c r="L29" s="31"/>
+      <x:c r="M29" s="31"/>
+      <x:c r="N29" s="31"/>
+      <x:c r="O29" s="31"/>
+      <x:c r="P29" s="31"/>
+      <x:c r="Q29" s="31"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31"/>
+      <x:c r="B30" s="31"/>
+      <x:c r="C30" s="31"/>
+      <x:c r="D30" s="31"/>
+      <x:c r="E30" s="31"/>
+      <x:c r="F30" s="31"/>
+      <x:c r="G30" s="31"/>
+      <x:c r="H30" s="36"/>
+      <x:c r="I30" s="31"/>
+      <x:c r="J30" s="31"/>
+      <x:c r="K30" s="31"/>
+      <x:c r="L30" s="31"/>
+      <x:c r="M30" s="31"/>
+      <x:c r="N30" s="31"/>
+      <x:c r="O30" s="31"/>
+      <x:c r="P30" s="31"/>
+      <x:c r="Q30" s="31"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31"/>
+      <x:c r="B31" s="31"/>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
+      <x:c r="E31" s="31"/>
+      <x:c r="F31" s="31"/>
+      <x:c r="G31" s="31"/>
+      <x:c r="H31" s="36"/>
+      <x:c r="I31" s="31"/>
+      <x:c r="J31" s="31"/>
+      <x:c r="K31" s="31"/>
+      <x:c r="L31" s="31"/>
+      <x:c r="M31" s="31"/>
+      <x:c r="N31" s="31"/>
+      <x:c r="O31" s="31"/>
+      <x:c r="P31" s="31"/>
+      <x:c r="Q31" s="31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="31"/>
+      <x:c r="B32" s="31"/>
+      <x:c r="C32" s="31"/>
+      <x:c r="D32" s="31"/>
+      <x:c r="E32" s="31"/>
+      <x:c r="F32" s="31"/>
+      <x:c r="G32" s="31"/>
+      <x:c r="H32" s="36"/>
+      <x:c r="I32" s="31"/>
+      <x:c r="J32" s="31"/>
+      <x:c r="K32" s="31"/>
+      <x:c r="L32" s="31"/>
+      <x:c r="M32" s="31"/>
+      <x:c r="N32" s="31"/>
+      <x:c r="O32" s="31"/>
+      <x:c r="P32" s="31"/>
+      <x:c r="Q32" s="31"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31"/>
+      <x:c r="B33" s="31"/>
+      <x:c r="C33" s="31"/>
+      <x:c r="D33" s="31"/>
+      <x:c r="E33" s="31"/>
+      <x:c r="F33" s="31"/>
+      <x:c r="G33" s="31"/>
+      <x:c r="H33" s="36"/>
+      <x:c r="I33" s="31"/>
+      <x:c r="J33" s="31"/>
+      <x:c r="K33" s="31"/>
+      <x:c r="L33" s="31"/>
+      <x:c r="M33" s="31"/>
+      <x:c r="N33" s="31"/>
+      <x:c r="O33" s="31"/>
+      <x:c r="P33" s="31"/>
+      <x:c r="Q33" s="31"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="31"/>
+      <x:c r="B34" s="31"/>
+      <x:c r="C34" s="31"/>
+      <x:c r="D34" s="31"/>
+      <x:c r="E34" s="31"/>
+      <x:c r="F34" s="31"/>
+      <x:c r="G34" s="31"/>
+      <x:c r="H34" s="36"/>
+      <x:c r="I34" s="31"/>
+      <x:c r="J34" s="31"/>
+      <x:c r="K34" s="31"/>
+      <x:c r="L34" s="31"/>
+      <x:c r="M34" s="31"/>
+      <x:c r="N34" s="31"/>
+      <x:c r="O34" s="31"/>
+      <x:c r="P34" s="31"/>
+      <x:c r="Q34" s="31"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31"/>
+      <x:c r="B35" s="31"/>
+      <x:c r="C35" s="31"/>
+      <x:c r="D35" s="31"/>
+      <x:c r="E35" s="31"/>
+      <x:c r="F35" s="31"/>
+      <x:c r="G35" s="31"/>
+      <x:c r="H35" s="36"/>
+      <x:c r="I35" s="31"/>
+      <x:c r="J35" s="31"/>
+      <x:c r="K35" s="31"/>
+      <x:c r="L35" s="31"/>
+      <x:c r="M35" s="31"/>
+      <x:c r="N35" s="31"/>
+      <x:c r="O35" s="31"/>
+      <x:c r="P35" s="31"/>
+      <x:c r="Q35" s="31"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31"/>
+      <x:c r="B36" s="31"/>
+      <x:c r="C36" s="31"/>
+      <x:c r="D36" s="31"/>
+      <x:c r="E36" s="31"/>
+      <x:c r="F36" s="31"/>
+      <x:c r="G36" s="31"/>
+      <x:c r="H36" s="36"/>
+      <x:c r="I36" s="31"/>
+      <x:c r="J36" s="31"/>
+      <x:c r="K36" s="31"/>
+      <x:c r="L36" s="31"/>
+      <x:c r="M36" s="31"/>
+      <x:c r="N36" s="31"/>
+      <x:c r="O36" s="31"/>
+      <x:c r="P36" s="31"/>
+      <x:c r="Q36" s="31"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="31"/>
+      <x:c r="B37" s="31"/>
+      <x:c r="C37" s="31"/>
+      <x:c r="D37" s="31"/>
+      <x:c r="E37" s="31"/>
+      <x:c r="F37" s="31"/>
+      <x:c r="G37" s="31"/>
+      <x:c r="H37" s="36"/>
+      <x:c r="I37" s="31"/>
+      <x:c r="J37" s="31"/>
+      <x:c r="K37" s="31"/>
+      <x:c r="L37" s="31"/>
+      <x:c r="M37" s="31"/>
+      <x:c r="N37" s="31"/>
+      <x:c r="O37" s="31"/>
+      <x:c r="P37" s="31"/>
+      <x:c r="Q37" s="31"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31"/>
+      <x:c r="B38" s="31"/>
+      <x:c r="C38" s="31"/>
+      <x:c r="D38" s="31"/>
+      <x:c r="E38" s="31"/>
+      <x:c r="F38" s="31"/>
+      <x:c r="G38" s="31"/>
+      <x:c r="H38" s="36"/>
+      <x:c r="I38" s="31"/>
+      <x:c r="J38" s="31"/>
+      <x:c r="K38" s="31"/>
+      <x:c r="L38" s="31"/>
+      <x:c r="M38" s="31"/>
+      <x:c r="N38" s="31"/>
+      <x:c r="O38" s="31"/>
+      <x:c r="P38" s="31"/>
+      <x:c r="Q38" s="31"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31"/>
+      <x:c r="B39" s="31"/>
+      <x:c r="C39" s="31"/>
+      <x:c r="D39" s="31"/>
+      <x:c r="E39" s="31"/>
+      <x:c r="F39" s="31"/>
+      <x:c r="G39" s="31"/>
+      <x:c r="H39" s="36"/>
+      <x:c r="I39" s="31"/>
+      <x:c r="J39" s="31"/>
+      <x:c r="K39" s="31"/>
+      <x:c r="L39" s="31"/>
+      <x:c r="M39" s="31"/>
+      <x:c r="N39" s="31"/>
+      <x:c r="O39" s="31"/>
+      <x:c r="P39" s="31"/>
+      <x:c r="Q39" s="31"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31"/>
+      <x:c r="B40" s="31"/>
+      <x:c r="C40" s="31"/>
+      <x:c r="D40" s="31"/>
+      <x:c r="E40" s="31"/>
+      <x:c r="F40" s="31"/>
+      <x:c r="G40" s="31"/>
+      <x:c r="H40" s="36"/>
+      <x:c r="I40" s="31"/>
+      <x:c r="J40" s="31"/>
+      <x:c r="K40" s="31"/>
+      <x:c r="L40" s="31"/>
+      <x:c r="M40" s="31"/>
+      <x:c r="N40" s="31"/>
+      <x:c r="O40" s="31"/>
+      <x:c r="P40" s="31"/>
+      <x:c r="Q40" s="31"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31"/>
+      <x:c r="B41" s="31"/>
+      <x:c r="C41" s="31"/>
+      <x:c r="D41" s="31"/>
+      <x:c r="E41" s="31"/>
+      <x:c r="F41" s="31"/>
+      <x:c r="G41" s="31"/>
+      <x:c r="H41" s="36"/>
+      <x:c r="I41" s="31"/>
+      <x:c r="J41" s="31"/>
+      <x:c r="K41" s="31"/>
+      <x:c r="L41" s="31"/>
+      <x:c r="M41" s="31"/>
+      <x:c r="N41" s="31"/>
+      <x:c r="O41" s="31"/>
+      <x:c r="P41" s="31"/>
+      <x:c r="Q41" s="31"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31"/>
+      <x:c r="B42" s="31"/>
+      <x:c r="C42" s="31"/>
+      <x:c r="D42" s="31"/>
+      <x:c r="E42" s="31"/>
+      <x:c r="F42" s="31"/>
+      <x:c r="G42" s="31"/>
+      <x:c r="H42" s="36"/>
+      <x:c r="I42" s="31"/>
+      <x:c r="J42" s="31"/>
+      <x:c r="K42" s="31"/>
+      <x:c r="L42" s="31"/>
+      <x:c r="M42" s="31"/>
+      <x:c r="N42" s="31"/>
+      <x:c r="O42" s="31"/>
+      <x:c r="P42" s="31"/>
+      <x:c r="Q42" s="31"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31"/>
+      <x:c r="B43" s="31"/>
+      <x:c r="C43" s="31"/>
+      <x:c r="D43" s="31"/>
+      <x:c r="E43" s="31"/>
+      <x:c r="F43" s="31"/>
+      <x:c r="G43" s="31"/>
+      <x:c r="H43" s="36"/>
+      <x:c r="I43" s="31"/>
+      <x:c r="J43" s="31"/>
+      <x:c r="K43" s="31"/>
+      <x:c r="L43" s="31"/>
+      <x:c r="M43" s="31"/>
+      <x:c r="N43" s="31"/>
+      <x:c r="O43" s="31"/>
+      <x:c r="P43" s="31"/>
+      <x:c r="Q43" s="31"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31"/>
+      <x:c r="B44" s="31"/>
+      <x:c r="C44" s="31"/>
+      <x:c r="D44" s="31"/>
+      <x:c r="E44" s="31"/>
+      <x:c r="F44" s="31"/>
+      <x:c r="G44" s="31"/>
+      <x:c r="H44" s="36"/>
+      <x:c r="I44" s="31"/>
+      <x:c r="J44" s="31"/>
+      <x:c r="K44" s="31"/>
+      <x:c r="L44" s="31"/>
+      <x:c r="M44" s="31"/>
+      <x:c r="N44" s="31"/>
+      <x:c r="O44" s="31"/>
+      <x:c r="P44" s="31"/>
+      <x:c r="Q44" s="31"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31"/>
+      <x:c r="B45" s="31"/>
+      <x:c r="C45" s="31"/>
+      <x:c r="D45" s="31"/>
+      <x:c r="E45" s="31"/>
+      <x:c r="F45" s="31"/>
+      <x:c r="G45" s="31"/>
+      <x:c r="H45" s="36"/>
+      <x:c r="I45" s="31"/>
+      <x:c r="J45" s="31"/>
+      <x:c r="K45" s="31"/>
+      <x:c r="L45" s="31"/>
+      <x:c r="M45" s="31"/>
+      <x:c r="N45" s="31"/>
+      <x:c r="O45" s="31"/>
+      <x:c r="P45" s="31"/>
+      <x:c r="Q45" s="31"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31"/>
+      <x:c r="B46" s="31"/>
+      <x:c r="C46" s="31"/>
+      <x:c r="D46" s="31"/>
+      <x:c r="E46" s="31"/>
+      <x:c r="F46" s="31"/>
+      <x:c r="G46" s="31"/>
+      <x:c r="H46" s="36"/>
+      <x:c r="I46" s="31"/>
+      <x:c r="J46" s="31"/>
+      <x:c r="K46" s="31"/>
+      <x:c r="L46" s="31"/>
+      <x:c r="M46" s="31"/>
+      <x:c r="N46" s="31"/>
+      <x:c r="O46" s="31"/>
+      <x:c r="P46" s="31"/>
+      <x:c r="Q46" s="31"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31"/>
+      <x:c r="B47" s="31"/>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31"/>
+      <x:c r="E47" s="31"/>
+      <x:c r="F47" s="31"/>
+      <x:c r="G47" s="31"/>
+      <x:c r="H47" s="36"/>
+      <x:c r="I47" s="31"/>
+      <x:c r="J47" s="31"/>
+      <x:c r="K47" s="31"/>
+      <x:c r="L47" s="31"/>
+      <x:c r="M47" s="31"/>
+      <x:c r="N47" s="31"/>
+      <x:c r="O47" s="31"/>
+      <x:c r="P47" s="31"/>
+      <x:c r="Q47" s="31"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31"/>
+      <x:c r="B48" s="31"/>
+      <x:c r="C48" s="31"/>
+      <x:c r="D48" s="31"/>
+      <x:c r="E48" s="31"/>
+      <x:c r="F48" s="31"/>
+      <x:c r="G48" s="31"/>
+      <x:c r="H48" s="36"/>
+      <x:c r="I48" s="31"/>
+      <x:c r="J48" s="31"/>
+      <x:c r="K48" s="31"/>
+      <x:c r="L48" s="31"/>
+      <x:c r="M48" s="31"/>
+      <x:c r="N48" s="31"/>
+      <x:c r="O48" s="31"/>
+      <x:c r="P48" s="31"/>
+      <x:c r="Q48" s="31"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31"/>
+      <x:c r="B49" s="31"/>
+      <x:c r="C49" s="31"/>
+      <x:c r="D49" s="31"/>
+      <x:c r="E49" s="31"/>
+      <x:c r="F49" s="31"/>
+      <x:c r="G49" s="31"/>
+      <x:c r="H49" s="36"/>
+      <x:c r="I49" s="31"/>
+      <x:c r="J49" s="31"/>
+      <x:c r="K49" s="31"/>
+      <x:c r="L49" s="31"/>
+      <x:c r="M49" s="31"/>
+      <x:c r="N49" s="31"/>
+      <x:c r="O49" s="31"/>
+      <x:c r="P49" s="31"/>
+      <x:c r="Q49" s="31"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31"/>
+      <x:c r="B50" s="31"/>
+      <x:c r="C50" s="31"/>
+      <x:c r="D50" s="31"/>
+      <x:c r="E50" s="31"/>
+      <x:c r="F50" s="31"/>
+      <x:c r="G50" s="31"/>
+      <x:c r="H50" s="36"/>
+      <x:c r="I50" s="31"/>
+      <x:c r="J50" s="31"/>
+      <x:c r="K50" s="31"/>
+      <x:c r="L50" s="31"/>
+      <x:c r="M50" s="31"/>
+      <x:c r="N50" s="31"/>
+      <x:c r="O50" s="31"/>
+      <x:c r="P50" s="31"/>
+      <x:c r="Q50" s="31"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31"/>
+      <x:c r="B51" s="31"/>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31"/>
+      <x:c r="E51" s="31"/>
+      <x:c r="F51" s="31"/>
+      <x:c r="G51" s="31"/>
+      <x:c r="H51" s="31"/>
+      <x:c r="I51" s="31"/>
+      <x:c r="J51" s="31"/>
+      <x:c r="K51" s="31"/>
+      <x:c r="L51" s="31"/>
+      <x:c r="M51" s="31"/>
+      <x:c r="N51" s="31"/>
+      <x:c r="O51" s="31"/>
+      <x:c r="P51" s="31"/>
+      <x:c r="Q51" s="31"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31"/>
+      <x:c r="B52" s="31"/>
+      <x:c r="C52" s="31"/>
+      <x:c r="D52" s="31"/>
+      <x:c r="E52" s="31"/>
+      <x:c r="F52" s="31"/>
+      <x:c r="G52" s="31"/>
+      <x:c r="H52" s="31"/>
+      <x:c r="I52" s="31"/>
+      <x:c r="J52" s="31"/>
+      <x:c r="K52" s="31"/>
+      <x:c r="L52" s="31"/>
+      <x:c r="M52" s="31"/>
+      <x:c r="N52" s="31"/>
+      <x:c r="O52" s="31"/>
+      <x:c r="P52" s="31"/>
+      <x:c r="Q52" s="31"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31"/>
+      <x:c r="B53" s="31"/>
+      <x:c r="C53" s="31"/>
+      <x:c r="D53" s="31"/>
+      <x:c r="E53" s="31"/>
+      <x:c r="F53" s="31"/>
+      <x:c r="G53" s="31"/>
+      <x:c r="H53" s="31"/>
+      <x:c r="I53" s="31"/>
+      <x:c r="J53" s="31"/>
+      <x:c r="K53" s="31"/>
+      <x:c r="L53" s="31"/>
+      <x:c r="M53" s="31"/>
+      <x:c r="N53" s="31"/>
+      <x:c r="O53" s="31"/>
+      <x:c r="P53" s="31"/>
+      <x:c r="Q53" s="31"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31"/>
+      <x:c r="B54" s="31"/>
+      <x:c r="C54" s="31"/>
+      <x:c r="D54" s="31"/>
+      <x:c r="E54" s="31"/>
+      <x:c r="F54" s="31"/>
+      <x:c r="G54" s="31"/>
+      <x:c r="H54" s="31"/>
+      <x:c r="I54" s="31"/>
+      <x:c r="J54" s="31"/>
+      <x:c r="K54" s="31"/>
+      <x:c r="L54" s="31"/>
+      <x:c r="M54" s="31"/>
+      <x:c r="N54" s="31"/>
+      <x:c r="O54" s="31"/>
+      <x:c r="P54" s="31"/>
+      <x:c r="Q54" s="31"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31"/>
+      <x:c r="B55" s="31"/>
+      <x:c r="C55" s="31"/>
+      <x:c r="D55" s="31"/>
+      <x:c r="E55" s="31"/>
+      <x:c r="F55" s="31"/>
+      <x:c r="G55" s="31"/>
+      <x:c r="H55" s="31"/>
+      <x:c r="I55" s="31"/>
+      <x:c r="J55" s="31"/>
+      <x:c r="K55" s="31"/>
+      <x:c r="L55" s="31"/>
+      <x:c r="M55" s="31"/>
+      <x:c r="N55" s="31"/>
+      <x:c r="O55" s="31"/>
+      <x:c r="P55" s="31"/>
+      <x:c r="Q55" s="31"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31"/>
+      <x:c r="B56" s="31"/>
+      <x:c r="C56" s="31"/>
+      <x:c r="D56" s="31"/>
+      <x:c r="E56" s="31"/>
+      <x:c r="F56" s="31"/>
+      <x:c r="G56" s="31"/>
+      <x:c r="H56" s="31"/>
+      <x:c r="I56" s="31"/>
+      <x:c r="J56" s="31"/>
+      <x:c r="K56" s="31"/>
+      <x:c r="L56" s="31"/>
+      <x:c r="M56" s="31"/>
+      <x:c r="N56" s="31"/>
+      <x:c r="O56" s="31"/>
+      <x:c r="P56" s="31"/>
+      <x:c r="Q56" s="31"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="31"/>
+      <x:c r="B57" s="31"/>
+      <x:c r="C57" s="31"/>
+      <x:c r="D57" s="31"/>
+      <x:c r="E57" s="31"/>
+      <x:c r="F57" s="31"/>
+      <x:c r="G57" s="31"/>
+      <x:c r="H57" s="31"/>
+      <x:c r="I57" s="31"/>
+      <x:c r="J57" s="31"/>
+      <x:c r="K57" s="31"/>
+      <x:c r="L57" s="31"/>
+      <x:c r="M57" s="31"/>
+      <x:c r="N57" s="31"/>
+      <x:c r="O57" s="31"/>
+      <x:c r="P57" s="31"/>
+      <x:c r="Q57" s="31"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="31"/>
+      <x:c r="B58" s="31"/>
+      <x:c r="C58" s="31"/>
+      <x:c r="D58" s="31"/>
+      <x:c r="E58" s="31"/>
+      <x:c r="F58" s="31"/>
+      <x:c r="G58" s="31"/>
+      <x:c r="H58" s="31"/>
+      <x:c r="I58" s="31"/>
+      <x:c r="J58" s="31"/>
+      <x:c r="K58" s="31"/>
+      <x:c r="L58" s="31"/>
+      <x:c r="M58" s="31"/>
+      <x:c r="N58" s="31"/>
+      <x:c r="O58" s="31"/>
+      <x:c r="P58" s="31"/>
+      <x:c r="Q58" s="31"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="31"/>
+      <x:c r="B59" s="31"/>
+      <x:c r="C59" s="31"/>
+      <x:c r="D59" s="31"/>
+      <x:c r="E59" s="31"/>
+      <x:c r="F59" s="31"/>
+      <x:c r="G59" s="31"/>
+      <x:c r="H59" s="31"/>
+      <x:c r="I59" s="31"/>
+      <x:c r="J59" s="31"/>
+      <x:c r="K59" s="31"/>
+      <x:c r="L59" s="31"/>
+      <x:c r="M59" s="31"/>
+      <x:c r="N59" s="31"/>
+      <x:c r="O59" s="31"/>
+      <x:c r="P59" s="31"/>
+      <x:c r="Q59" s="31"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="31"/>
+      <x:c r="B60" s="31"/>
+      <x:c r="C60" s="31"/>
+      <x:c r="D60" s="31"/>
+      <x:c r="E60" s="31"/>
+      <x:c r="F60" s="31"/>
+      <x:c r="G60" s="31"/>
+      <x:c r="H60" s="31"/>
+      <x:c r="I60" s="31"/>
+      <x:c r="J60" s="31"/>
+      <x:c r="K60" s="31"/>
+      <x:c r="L60" s="31"/>
+      <x:c r="M60" s="31"/>
+      <x:c r="N60" s="31"/>
+      <x:c r="O60" s="31"/>
+      <x:c r="P60" s="31"/>
+      <x:c r="Q60" s="31"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="31"/>
+      <x:c r="B61" s="31"/>
+      <x:c r="C61" s="31"/>
+      <x:c r="D61" s="31"/>
+      <x:c r="E61" s="31"/>
+      <x:c r="F61" s="31"/>
+      <x:c r="G61" s="31"/>
+      <x:c r="H61" s="31"/>
+      <x:c r="I61" s="31"/>
+      <x:c r="J61" s="31"/>
+      <x:c r="K61" s="31"/>
+      <x:c r="L61" s="31"/>
+      <x:c r="M61" s="31"/>
+      <x:c r="N61" s="31"/>
+      <x:c r="O61" s="31"/>
+      <x:c r="P61" s="31"/>
+      <x:c r="Q61" s="31"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="31"/>
+      <x:c r="B62" s="31"/>
+      <x:c r="C62" s="31"/>
+      <x:c r="D62" s="31"/>
+      <x:c r="E62" s="31"/>
+      <x:c r="F62" s="31"/>
+      <x:c r="G62" s="31"/>
+      <x:c r="H62" s="31"/>
+      <x:c r="I62" s="31"/>
+      <x:c r="J62" s="31"/>
+      <x:c r="K62" s="31"/>
+      <x:c r="L62" s="31"/>
+      <x:c r="M62" s="31"/>
+      <x:c r="N62" s="31"/>
+      <x:c r="O62" s="31"/>
+      <x:c r="P62" s="31"/>
+      <x:c r="Q62" s="31"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="31"/>
+      <x:c r="B63" s="31"/>
+      <x:c r="C63" s="31"/>
+      <x:c r="D63" s="31"/>
+      <x:c r="E63" s="31"/>
+      <x:c r="F63" s="31"/>
+      <x:c r="G63" s="31"/>
+      <x:c r="H63" s="31"/>
+      <x:c r="I63" s="31"/>
+      <x:c r="J63" s="31"/>
+      <x:c r="K63" s="31"/>
+      <x:c r="L63" s="31"/>
+      <x:c r="M63" s="31"/>
+      <x:c r="N63" s="31"/>
+      <x:c r="O63" s="31"/>
+      <x:c r="P63" s="31"/>
+      <x:c r="Q63" s="31"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="31"/>
+      <x:c r="B64" s="31"/>
+      <x:c r="C64" s="31"/>
+      <x:c r="D64" s="31"/>
+      <x:c r="E64" s="31"/>
+      <x:c r="F64" s="31"/>
+      <x:c r="G64" s="31"/>
+      <x:c r="H64" s="31"/>
+      <x:c r="I64" s="31"/>
+      <x:c r="J64" s="31"/>
+      <x:c r="K64" s="31"/>
+      <x:c r="L64" s="31"/>
+      <x:c r="M64" s="31"/>
+      <x:c r="N64" s="31"/>
+      <x:c r="O64" s="31"/>
+      <x:c r="P64" s="31"/>
+      <x:c r="Q64" s="31"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="31"/>
+      <x:c r="B65" s="31"/>
+      <x:c r="C65" s="31"/>
+      <x:c r="D65" s="31"/>
+      <x:c r="E65" s="31"/>
+      <x:c r="F65" s="31"/>
+      <x:c r="G65" s="31"/>
+      <x:c r="H65" s="31"/>
+      <x:c r="I65" s="31"/>
+      <x:c r="J65" s="31"/>
+      <x:c r="K65" s="31"/>
+      <x:c r="L65" s="31"/>
+      <x:c r="M65" s="31"/>
+      <x:c r="N65" s="31"/>
+      <x:c r="O65" s="31"/>
+      <x:c r="P65" s="31"/>
+      <x:c r="Q65" s="31"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="31"/>
+      <x:c r="B66" s="31"/>
+      <x:c r="C66" s="31"/>
+      <x:c r="D66" s="31"/>
+      <x:c r="E66" s="31"/>
+      <x:c r="F66" s="31"/>
+      <x:c r="G66" s="31"/>
+      <x:c r="H66" s="31"/>
+      <x:c r="I66" s="31"/>
+      <x:c r="J66" s="31"/>
+      <x:c r="K66" s="31"/>
+      <x:c r="L66" s="31"/>
+      <x:c r="M66" s="31"/>
+      <x:c r="N66" s="31"/>
+      <x:c r="O66" s="31"/>
+      <x:c r="P66" s="31"/>
+      <x:c r="Q66" s="31"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="31"/>
+      <x:c r="B67" s="31"/>
+      <x:c r="C67" s="31"/>
+      <x:c r="D67" s="31"/>
+      <x:c r="E67" s="31"/>
+      <x:c r="F67" s="31"/>
+      <x:c r="G67" s="31"/>
+      <x:c r="H67" s="31"/>
+      <x:c r="I67" s="31"/>
+      <x:c r="J67" s="31"/>
+      <x:c r="K67" s="31"/>
+      <x:c r="L67" s="31"/>
+      <x:c r="M67" s="31"/>
+      <x:c r="N67" s="31"/>
+      <x:c r="O67" s="31"/>
+      <x:c r="P67" s="31"/>
+      <x:c r="Q67" s="31"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="31"/>
+      <x:c r="B68" s="31"/>
+      <x:c r="C68" s="31"/>
+      <x:c r="D68" s="31"/>
+      <x:c r="E68" s="31"/>
+      <x:c r="F68" s="31"/>
+      <x:c r="G68" s="31"/>
+      <x:c r="H68" s="31"/>
+      <x:c r="I68" s="31"/>
+      <x:c r="J68" s="31"/>
+      <x:c r="K68" s="31"/>
+      <x:c r="L68" s="31"/>
+      <x:c r="M68" s="31"/>
+      <x:c r="N68" s="31"/>
+      <x:c r="O68" s="31"/>
+      <x:c r="P68" s="31"/>
+      <x:c r="Q68" s="31"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="31"/>
+      <x:c r="B69" s="31"/>
+      <x:c r="C69" s="31"/>
+      <x:c r="D69" s="31"/>
+      <x:c r="E69" s="31"/>
+      <x:c r="F69" s="31"/>
+      <x:c r="G69" s="31"/>
+      <x:c r="H69" s="31"/>
+      <x:c r="I69" s="31"/>
+      <x:c r="J69" s="31"/>
+      <x:c r="K69" s="31"/>
+      <x:c r="L69" s="31"/>
+      <x:c r="M69" s="31"/>
+      <x:c r="N69" s="31"/>
+      <x:c r="O69" s="31"/>
+      <x:c r="P69" s="31"/>
+      <x:c r="Q69" s="31"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="31"/>
+      <x:c r="B70" s="31"/>
+      <x:c r="C70" s="31"/>
+      <x:c r="D70" s="31"/>
+      <x:c r="E70" s="31"/>
+      <x:c r="F70" s="31"/>
+      <x:c r="G70" s="31"/>
+      <x:c r="H70" s="31"/>
+      <x:c r="I70" s="31"/>
+      <x:c r="J70" s="31"/>
+      <x:c r="K70" s="31"/>
+      <x:c r="L70" s="31"/>
+      <x:c r="M70" s="31"/>
+      <x:c r="N70" s="31"/>
+      <x:c r="O70" s="31"/>
+      <x:c r="P70" s="31"/>
+      <x:c r="Q70" s="31"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="31"/>
+      <x:c r="B71" s="31"/>
+      <x:c r="C71" s="31"/>
+      <x:c r="D71" s="31"/>
+      <x:c r="E71" s="31"/>
+      <x:c r="F71" s="31"/>
+      <x:c r="G71" s="31"/>
+      <x:c r="H71" s="31"/>
+      <x:c r="I71" s="31"/>
+      <x:c r="J71" s="31"/>
+      <x:c r="K71" s="31"/>
+      <x:c r="L71" s="31"/>
+      <x:c r="M71" s="31"/>
+      <x:c r="N71" s="31"/>
+      <x:c r="O71" s="31"/>
+      <x:c r="P71" s="31"/>
+      <x:c r="Q71" s="31"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="31"/>
+      <x:c r="B72" s="31"/>
+      <x:c r="C72" s="31"/>
+      <x:c r="D72" s="31"/>
+      <x:c r="E72" s="31"/>
+      <x:c r="F72" s="31"/>
+      <x:c r="G72" s="31"/>
+      <x:c r="H72" s="31"/>
+      <x:c r="I72" s="31"/>
+      <x:c r="J72" s="31"/>
+      <x:c r="K72" s="31"/>
+      <x:c r="L72" s="31"/>
+      <x:c r="M72" s="31"/>
+      <x:c r="N72" s="31"/>
+      <x:c r="O72" s="31"/>
+      <x:c r="P72" s="31"/>
+      <x:c r="Q72" s="31"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="31"/>
+      <x:c r="B73" s="31"/>
+      <x:c r="C73" s="31"/>
+      <x:c r="D73" s="31"/>
+      <x:c r="E73" s="31"/>
+      <x:c r="F73" s="31"/>
+      <x:c r="G73" s="31"/>
+      <x:c r="H73" s="31"/>
+      <x:c r="I73" s="31"/>
+      <x:c r="J73" s="31"/>
+      <x:c r="K73" s="31"/>
+      <x:c r="L73" s="31"/>
+      <x:c r="M73" s="31"/>
+      <x:c r="N73" s="31"/>
+      <x:c r="O73" s="31"/>
+      <x:c r="P73" s="31"/>
+      <x:c r="Q73" s="31"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="31"/>
+      <x:c r="B74" s="31"/>
+      <x:c r="C74" s="31"/>
+      <x:c r="D74" s="31"/>
+      <x:c r="E74" s="31"/>
+      <x:c r="F74" s="31"/>
+      <x:c r="G74" s="31"/>
+      <x:c r="H74" s="31"/>
+      <x:c r="I74" s="31"/>
+      <x:c r="J74" s="31"/>
+      <x:c r="K74" s="31"/>
+      <x:c r="L74" s="31"/>
+      <x:c r="M74" s="31"/>
+      <x:c r="N74" s="31"/>
+      <x:c r="O74" s="31"/>
+      <x:c r="P74" s="31"/>
+      <x:c r="Q74" s="31"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="31"/>
+      <x:c r="B75" s="31"/>
+      <x:c r="C75" s="31"/>
+      <x:c r="D75" s="31"/>
+      <x:c r="E75" s="31"/>
+      <x:c r="F75" s="31"/>
+      <x:c r="G75" s="31"/>
+      <x:c r="H75" s="31"/>
+      <x:c r="I75" s="31"/>
+      <x:c r="J75" s="31"/>
+      <x:c r="K75" s="31"/>
+      <x:c r="L75" s="31"/>
+      <x:c r="M75" s="31"/>
+      <x:c r="N75" s="31"/>
+      <x:c r="O75" s="31"/>
+      <x:c r="P75" s="31"/>
+      <x:c r="Q75" s="31"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="31"/>
+      <x:c r="B76" s="31"/>
+      <x:c r="C76" s="31"/>
+      <x:c r="D76" s="31"/>
+      <x:c r="E76" s="31"/>
+      <x:c r="F76" s="31"/>
+      <x:c r="G76" s="31"/>
+      <x:c r="H76" s="31"/>
+      <x:c r="I76" s="31"/>
+      <x:c r="J76" s="31"/>
+      <x:c r="K76" s="31"/>
+      <x:c r="L76" s="31"/>
+      <x:c r="M76" s="31"/>
+      <x:c r="N76" s="31"/>
+      <x:c r="O76" s="31"/>
+      <x:c r="P76" s="31"/>
+      <x:c r="Q76" s="31"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="31"/>
+      <x:c r="B77" s="31"/>
+      <x:c r="C77" s="31"/>
+      <x:c r="D77" s="31"/>
+      <x:c r="E77" s="31"/>
+      <x:c r="F77" s="31"/>
+      <x:c r="G77" s="31"/>
+      <x:c r="H77" s="31"/>
+      <x:c r="I77" s="31"/>
+      <x:c r="J77" s="31"/>
+      <x:c r="K77" s="31"/>
+      <x:c r="L77" s="31"/>
+      <x:c r="M77" s="31"/>
+      <x:c r="N77" s="31"/>
+      <x:c r="O77" s="31"/>
+      <x:c r="P77" s="31"/>
+      <x:c r="Q77" s="31"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="31"/>
+      <x:c r="B78" s="31"/>
+      <x:c r="C78" s="31"/>
+      <x:c r="D78" s="31"/>
+      <x:c r="E78" s="31"/>
+      <x:c r="F78" s="31"/>
+      <x:c r="G78" s="31"/>
+      <x:c r="H78" s="31"/>
+      <x:c r="I78" s="31"/>
+      <x:c r="J78" s="31"/>
+      <x:c r="K78" s="31"/>
+      <x:c r="L78" s="31"/>
+      <x:c r="M78" s="31"/>
+      <x:c r="N78" s="31"/>
+      <x:c r="O78" s="31"/>
+      <x:c r="P78" s="31"/>
+      <x:c r="Q78" s="31"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="31"/>
+      <x:c r="B79" s="31"/>
+      <x:c r="C79" s="31"/>
+      <x:c r="D79" s="31"/>
+      <x:c r="E79" s="31"/>
+      <x:c r="F79" s="31"/>
+      <x:c r="G79" s="31"/>
+      <x:c r="H79" s="31"/>
+      <x:c r="I79" s="31"/>
+      <x:c r="J79" s="31"/>
+      <x:c r="K79" s="31"/>
+      <x:c r="L79" s="31"/>
+      <x:c r="M79" s="31"/>
+      <x:c r="N79" s="31"/>
+      <x:c r="O79" s="31"/>
+      <x:c r="P79" s="31"/>
+      <x:c r="Q79" s="31"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="31"/>
+      <x:c r="B80" s="31"/>
+      <x:c r="C80" s="31"/>
+      <x:c r="D80" s="31"/>
+      <x:c r="E80" s="31"/>
+      <x:c r="F80" s="31"/>
+      <x:c r="G80" s="31"/>
+      <x:c r="H80" s="31"/>
+      <x:c r="I80" s="31"/>
+      <x:c r="J80" s="31"/>
+      <x:c r="K80" s="31"/>
+      <x:c r="L80" s="31"/>
+      <x:c r="M80" s="31"/>
+      <x:c r="N80" s="31"/>
+      <x:c r="O80" s="31"/>
+      <x:c r="P80" s="31"/>
+      <x:c r="Q80" s="31"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="31"/>
+      <x:c r="B81" s="31"/>
+      <x:c r="C81" s="31"/>
+      <x:c r="D81" s="31"/>
+      <x:c r="E81" s="31"/>
+      <x:c r="F81" s="31"/>
+      <x:c r="G81" s="31"/>
+      <x:c r="H81" s="31"/>
+      <x:c r="I81" s="31"/>
+      <x:c r="J81" s="31"/>
+      <x:c r="K81" s="31"/>
+      <x:c r="L81" s="31"/>
+      <x:c r="M81" s="31"/>
+      <x:c r="N81" s="31"/>
+      <x:c r="O81" s="31"/>
+      <x:c r="P81" s="31"/>
+      <x:c r="Q81" s="31"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="31"/>
+      <x:c r="B82" s="31"/>
+      <x:c r="C82" s="31"/>
+      <x:c r="D82" s="31"/>
+      <x:c r="E82" s="31"/>
+      <x:c r="F82" s="31"/>
+      <x:c r="G82" s="31"/>
+      <x:c r="H82" s="31"/>
+      <x:c r="I82" s="31"/>
+      <x:c r="J82" s="31"/>
+      <x:c r="K82" s="31"/>
+      <x:c r="L82" s="31"/>
+      <x:c r="M82" s="31"/>
+      <x:c r="N82" s="31"/>
+      <x:c r="O82" s="31"/>
+      <x:c r="P82" s="31"/>
+      <x:c r="Q82" s="31"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="31"/>
+      <x:c r="B83" s="31"/>
+      <x:c r="C83" s="31"/>
+      <x:c r="D83" s="31"/>
+      <x:c r="E83" s="31"/>
+      <x:c r="F83" s="31"/>
+      <x:c r="G83" s="31"/>
+      <x:c r="H83" s="31"/>
+      <x:c r="I83" s="31"/>
+      <x:c r="J83" s="31"/>
+      <x:c r="K83" s="31"/>
+      <x:c r="L83" s="31"/>
+      <x:c r="M83" s="31"/>
+      <x:c r="N83" s="31"/>
+      <x:c r="O83" s="31"/>
+      <x:c r="P83" s="31"/>
+      <x:c r="Q83" s="31"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="31"/>
+      <x:c r="B84" s="31"/>
+      <x:c r="C84" s="31"/>
+      <x:c r="D84" s="31"/>
+      <x:c r="E84" s="31"/>
+      <x:c r="F84" s="31"/>
+      <x:c r="G84" s="31"/>
+      <x:c r="H84" s="31"/>
+      <x:c r="I84" s="31"/>
+      <x:c r="J84" s="31"/>
+      <x:c r="K84" s="31"/>
+      <x:c r="L84" s="31"/>
+      <x:c r="M84" s="31"/>
+      <x:c r="N84" s="31"/>
+      <x:c r="O84" s="31"/>
+      <x:c r="P84" s="31"/>
+      <x:c r="Q84" s="31"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="31"/>
+      <x:c r="B85" s="31"/>
+      <x:c r="C85" s="31"/>
+      <x:c r="D85" s="31"/>
+      <x:c r="E85" s="31"/>
+      <x:c r="F85" s="31"/>
+      <x:c r="G85" s="31"/>
+      <x:c r="H85" s="31"/>
+      <x:c r="I85" s="31"/>
+      <x:c r="J85" s="31"/>
+      <x:c r="K85" s="31"/>
+      <x:c r="L85" s="31"/>
+      <x:c r="M85" s="31"/>
+      <x:c r="N85" s="31"/>
+      <x:c r="O85" s="31"/>
+      <x:c r="P85" s="31"/>
+      <x:c r="Q85" s="31"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="31"/>
+      <x:c r="B86" s="31"/>
+      <x:c r="C86" s="31"/>
+      <x:c r="D86" s="31"/>
+      <x:c r="E86" s="31"/>
+      <x:c r="F86" s="31"/>
+      <x:c r="G86" s="31"/>
+      <x:c r="H86" s="31"/>
+      <x:c r="I86" s="31"/>
+      <x:c r="J86" s="31"/>
+      <x:c r="K86" s="31"/>
+      <x:c r="L86" s="31"/>
+      <x:c r="M86" s="31"/>
+      <x:c r="N86" s="31"/>
+      <x:c r="O86" s="31"/>
+      <x:c r="P86" s="31"/>
+      <x:c r="Q86" s="31"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="31"/>
+      <x:c r="B87" s="31"/>
+      <x:c r="C87" s="31"/>
+      <x:c r="D87" s="31"/>
+      <x:c r="E87" s="31"/>
+      <x:c r="F87" s="31"/>
+      <x:c r="G87" s="31"/>
+      <x:c r="H87" s="31"/>
+      <x:c r="I87" s="31"/>
+      <x:c r="J87" s="31"/>
+      <x:c r="K87" s="31"/>
+      <x:c r="L87" s="31"/>
+      <x:c r="M87" s="31"/>
+      <x:c r="N87" s="31"/>
+      <x:c r="O87" s="31"/>
+      <x:c r="P87" s="31"/>
+      <x:c r="Q87" s="31"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="31"/>
+      <x:c r="B88" s="31"/>
+      <x:c r="C88" s="31"/>
+      <x:c r="D88" s="31"/>
+      <x:c r="E88" s="31"/>
+      <x:c r="F88" s="31"/>
+      <x:c r="G88" s="31"/>
+      <x:c r="H88" s="31"/>
+      <x:c r="I88" s="31"/>
+      <x:c r="J88" s="31"/>
+      <x:c r="K88" s="31"/>
+      <x:c r="L88" s="31"/>
+      <x:c r="M88" s="31"/>
+      <x:c r="N88" s="31"/>
+      <x:c r="O88" s="31"/>
+      <x:c r="P88" s="31"/>
+      <x:c r="Q88" s="31"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="31"/>
+      <x:c r="B89" s="31"/>
+      <x:c r="C89" s="31"/>
+      <x:c r="D89" s="31"/>
+      <x:c r="E89" s="31"/>
+      <x:c r="F89" s="31"/>
+      <x:c r="G89" s="31"/>
+      <x:c r="H89" s="31"/>
+      <x:c r="I89" s="31"/>
+      <x:c r="J89" s="31"/>
+      <x:c r="K89" s="31"/>
+      <x:c r="L89" s="31"/>
+      <x:c r="M89" s="31"/>
+      <x:c r="N89" s="31"/>
+      <x:c r="O89" s="31"/>
+      <x:c r="P89" s="31"/>
+      <x:c r="Q89" s="31"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="31"/>
+      <x:c r="B90" s="31"/>
+      <x:c r="C90" s="31"/>
+      <x:c r="D90" s="31"/>
+      <x:c r="E90" s="31"/>
+      <x:c r="F90" s="31"/>
+      <x:c r="G90" s="31"/>
+      <x:c r="H90" s="31"/>
+      <x:c r="I90" s="31"/>
+      <x:c r="J90" s="31"/>
+      <x:c r="K90" s="31"/>
+      <x:c r="L90" s="31"/>
+      <x:c r="M90" s="31"/>
+      <x:c r="N90" s="31"/>
+      <x:c r="O90" s="31"/>
+      <x:c r="P90" s="31"/>
+      <x:c r="Q90" s="31"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="31"/>
+      <x:c r="B91" s="31"/>
+      <x:c r="C91" s="31"/>
+      <x:c r="D91" s="31"/>
+      <x:c r="E91" s="31"/>
+      <x:c r="F91" s="31"/>
+      <x:c r="G91" s="31"/>
+      <x:c r="H91" s="31"/>
+      <x:c r="I91" s="31"/>
+      <x:c r="J91" s="31"/>
+      <x:c r="K91" s="31"/>
+      <x:c r="L91" s="31"/>
+      <x:c r="M91" s="31"/>
+      <x:c r="N91" s="31"/>
+      <x:c r="O91" s="31"/>
+      <x:c r="P91" s="31"/>
+      <x:c r="Q91" s="31"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="31"/>
+      <x:c r="B92" s="31"/>
+      <x:c r="C92" s="31"/>
+      <x:c r="D92" s="31"/>
+      <x:c r="E92" s="31"/>
+      <x:c r="F92" s="31"/>
+      <x:c r="G92" s="31"/>
+      <x:c r="H92" s="31"/>
+      <x:c r="I92" s="31"/>
+      <x:c r="J92" s="31"/>
+      <x:c r="K92" s="31"/>
+      <x:c r="L92" s="31"/>
+      <x:c r="M92" s="31"/>
+      <x:c r="N92" s="31"/>
+      <x:c r="O92" s="31"/>
+      <x:c r="P92" s="31"/>
+      <x:c r="Q92" s="31"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="31"/>
+      <x:c r="B93" s="31"/>
+      <x:c r="C93" s="31"/>
+      <x:c r="D93" s="31"/>
+      <x:c r="E93" s="31"/>
+      <x:c r="F93" s="31"/>
+      <x:c r="G93" s="31"/>
+      <x:c r="H93" s="31"/>
+      <x:c r="I93" s="31"/>
+      <x:c r="J93" s="31"/>
+      <x:c r="K93" s="31"/>
+      <x:c r="L93" s="31"/>
+      <x:c r="M93" s="31"/>
+      <x:c r="N93" s="31"/>
+      <x:c r="O93" s="31"/>
+      <x:c r="P93" s="31"/>
+      <x:c r="Q93" s="31"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="31"/>
+      <x:c r="B94" s="31"/>
+      <x:c r="C94" s="31"/>
+      <x:c r="D94" s="31"/>
+      <x:c r="E94" s="31"/>
+      <x:c r="F94" s="31"/>
+      <x:c r="G94" s="31"/>
+      <x:c r="H94" s="31"/>
+      <x:c r="I94" s="31"/>
+      <x:c r="J94" s="31"/>
+      <x:c r="K94" s="31"/>
+      <x:c r="L94" s="31"/>
+      <x:c r="M94" s="31"/>
+      <x:c r="N94" s="31"/>
+      <x:c r="O94" s="31"/>
+      <x:c r="P94" s="31"/>
+      <x:c r="Q94" s="31"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="31"/>
+      <x:c r="B95" s="31"/>
+      <x:c r="C95" s="31"/>
+      <x:c r="D95" s="31"/>
+      <x:c r="E95" s="31"/>
+      <x:c r="F95" s="31"/>
+      <x:c r="G95" s="31"/>
+      <x:c r="H95" s="31"/>
+      <x:c r="I95" s="31"/>
+      <x:c r="J95" s="31"/>
+      <x:c r="K95" s="31"/>
+      <x:c r="L95" s="31"/>
+      <x:c r="M95" s="31"/>
+      <x:c r="N95" s="31"/>
+      <x:c r="O95" s="31"/>
+      <x:c r="P95" s="31"/>
+      <x:c r="Q95" s="31"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="31"/>
+      <x:c r="B96" s="31"/>
+      <x:c r="C96" s="31"/>
+      <x:c r="D96" s="31"/>
+      <x:c r="E96" s="31"/>
+      <x:c r="F96" s="31"/>
+      <x:c r="G96" s="31"/>
+      <x:c r="H96" s="31"/>
+      <x:c r="I96" s="31"/>
+      <x:c r="J96" s="31"/>
+      <x:c r="K96" s="31"/>
+      <x:c r="L96" s="31"/>
+      <x:c r="M96" s="31"/>
+      <x:c r="N96" s="31"/>
+      <x:c r="O96" s="31"/>
+      <x:c r="P96" s="31"/>
+      <x:c r="Q96" s="31"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="31"/>
+      <x:c r="B97" s="31"/>
+      <x:c r="C97" s="31"/>
+      <x:c r="D97" s="31"/>
+      <x:c r="E97" s="31"/>
+      <x:c r="F97" s="31"/>
+      <x:c r="G97" s="31"/>
+      <x:c r="H97" s="31"/>
+      <x:c r="I97" s="31"/>
+      <x:c r="J97" s="31"/>
+      <x:c r="K97" s="31"/>
+      <x:c r="L97" s="31"/>
+      <x:c r="M97" s="31"/>
+      <x:c r="N97" s="31"/>
+      <x:c r="O97" s="31"/>
+      <x:c r="P97" s="31"/>
+      <x:c r="Q97" s="31"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="31"/>
+      <x:c r="B98" s="31"/>
+      <x:c r="C98" s="31"/>
+      <x:c r="D98" s="31"/>
+      <x:c r="E98" s="31"/>
+      <x:c r="F98" s="31"/>
+      <x:c r="G98" s="31"/>
+      <x:c r="H98" s="31"/>
+      <x:c r="I98" s="31"/>
+      <x:c r="J98" s="31"/>
+      <x:c r="K98" s="31"/>
+      <x:c r="L98" s="31"/>
+      <x:c r="M98" s="31"/>
+      <x:c r="N98" s="31"/>
+      <x:c r="O98" s="31"/>
+      <x:c r="P98" s="31"/>
+      <x:c r="Q98" s="31"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="31"/>
+      <x:c r="B99" s="31"/>
+      <x:c r="C99" s="31"/>
+      <x:c r="D99" s="31"/>
+      <x:c r="E99" s="31"/>
+      <x:c r="F99" s="31"/>
+      <x:c r="G99" s="31"/>
+      <x:c r="H99" s="31"/>
+      <x:c r="I99" s="31"/>
+      <x:c r="J99" s="31"/>
+      <x:c r="K99" s="31"/>
+      <x:c r="L99" s="31"/>
+      <x:c r="M99" s="31"/>
+      <x:c r="N99" s="31"/>
+      <x:c r="O99" s="31"/>
+      <x:c r="P99" s="31"/>
+      <x:c r="Q99" s="31"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="31"/>
+      <x:c r="B100" s="31"/>
+      <x:c r="C100" s="31"/>
+      <x:c r="D100" s="31"/>
+      <x:c r="E100" s="31"/>
+      <x:c r="F100" s="31"/>
+      <x:c r="G100" s="31"/>
+      <x:c r="H100" s="31"/>
+      <x:c r="I100" s="31"/>
+      <x:c r="J100" s="31"/>
+      <x:c r="K100" s="31"/>
+      <x:c r="L100" s="31"/>
+      <x:c r="M100" s="31"/>
+      <x:c r="N100" s="31"/>
+      <x:c r="O100" s="31"/>
+      <x:c r="P100" s="31"/>
+      <x:c r="Q100" s="31"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="31"/>
+      <x:c r="B101" s="31"/>
+      <x:c r="C101" s="31"/>
+      <x:c r="D101" s="31"/>
+      <x:c r="E101" s="31"/>
+      <x:c r="F101" s="31"/>
+      <x:c r="G101" s="31"/>
+      <x:c r="H101" s="31"/>
+      <x:c r="I101" s="31"/>
+      <x:c r="J101" s="31"/>
+      <x:c r="K101" s="31"/>
+      <x:c r="L101" s="31"/>
+      <x:c r="M101" s="31"/>
+      <x:c r="N101" s="31"/>
+      <x:c r="O101" s="31"/>
+      <x:c r="P101" s="31"/>
+      <x:c r="Q101" s="31"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="31"/>
+      <x:c r="B102" s="31"/>
+      <x:c r="C102" s="31"/>
+      <x:c r="D102" s="31"/>
+      <x:c r="E102" s="31"/>
+      <x:c r="F102" s="31"/>
+      <x:c r="G102" s="31"/>
+      <x:c r="H102" s="31"/>
+      <x:c r="I102" s="31"/>
+      <x:c r="J102" s="31"/>
+      <x:c r="K102" s="31"/>
+      <x:c r="L102" s="31"/>
+      <x:c r="M102" s="31"/>
+      <x:c r="N102" s="31"/>
+      <x:c r="O102" s="31"/>
+      <x:c r="P102" s="31"/>
+      <x:c r="Q102" s="31"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="31"/>
+      <x:c r="B103" s="31"/>
+      <x:c r="C103" s="31"/>
+      <x:c r="D103" s="31"/>
+      <x:c r="E103" s="31"/>
+      <x:c r="F103" s="31"/>
+      <x:c r="G103" s="31"/>
+      <x:c r="H103" s="31"/>
+      <x:c r="I103" s="31"/>
+      <x:c r="J103" s="31"/>
+      <x:c r="K103" s="31"/>
+      <x:c r="L103" s="31"/>
+      <x:c r="M103" s="31"/>
+      <x:c r="N103" s="31"/>
+      <x:c r="O103" s="31"/>
+      <x:c r="P103" s="31"/>
+      <x:c r="Q103" s="31"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="31"/>
+      <x:c r="B104" s="31"/>
+      <x:c r="C104" s="31"/>
+      <x:c r="D104" s="31"/>
+      <x:c r="E104" s="31"/>
+      <x:c r="F104" s="31"/>
+      <x:c r="G104" s="31"/>
+      <x:c r="H104" s="31"/>
+      <x:c r="I104" s="31"/>
+      <x:c r="J104" s="31"/>
+      <x:c r="K104" s="31"/>
+      <x:c r="L104" s="31"/>
+      <x:c r="M104" s="31"/>
+      <x:c r="N104" s="31"/>
+      <x:c r="O104" s="31"/>
+      <x:c r="P104" s="31"/>
+      <x:c r="Q104" s="31"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="31"/>
+      <x:c r="B105" s="31"/>
+      <x:c r="C105" s="31"/>
+      <x:c r="D105" s="31"/>
+      <x:c r="E105" s="31"/>
+      <x:c r="F105" s="31"/>
+      <x:c r="G105" s="31"/>
+      <x:c r="H105" s="31"/>
+      <x:c r="I105" s="31"/>
+      <x:c r="J105" s="31"/>
+      <x:c r="K105" s="31"/>
+      <x:c r="L105" s="31"/>
+      <x:c r="M105" s="31"/>
+      <x:c r="N105" s="31"/>
+      <x:c r="O105" s="31"/>
+      <x:c r="P105" s="31"/>
+      <x:c r="Q105" s="31"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="31"/>
+      <x:c r="B106" s="31"/>
+      <x:c r="C106" s="31"/>
+      <x:c r="D106" s="31"/>
+      <x:c r="E106" s="31"/>
+      <x:c r="F106" s="31"/>
+      <x:c r="G106" s="31"/>
+      <x:c r="H106" s="31"/>
+      <x:c r="I106" s="31"/>
+      <x:c r="J106" s="31"/>
+      <x:c r="K106" s="31"/>
+      <x:c r="L106" s="31"/>
+      <x:c r="M106" s="31"/>
+      <x:c r="N106" s="31"/>
+      <x:c r="O106" s="31"/>
+      <x:c r="P106" s="31"/>
+      <x:c r="Q106" s="31"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="31"/>
+      <x:c r="B107" s="31"/>
+      <x:c r="C107" s="31"/>
+      <x:c r="D107" s="31"/>
+      <x:c r="E107" s="31"/>
+      <x:c r="F107" s="31"/>
+      <x:c r="G107" s="31"/>
+      <x:c r="H107" s="31"/>
+      <x:c r="I107" s="31"/>
+      <x:c r="J107" s="31"/>
+      <x:c r="K107" s="31"/>
+      <x:c r="L107" s="31"/>
+      <x:c r="M107" s="31"/>
+      <x:c r="N107" s="31"/>
+      <x:c r="O107" s="31"/>
+      <x:c r="P107" s="31"/>
+      <x:c r="Q107" s="31"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="31"/>
+      <x:c r="B108" s="31"/>
+      <x:c r="C108" s="31"/>
+      <x:c r="D108" s="31"/>
+      <x:c r="E108" s="31"/>
+      <x:c r="F108" s="31"/>
+      <x:c r="G108" s="31"/>
+      <x:c r="H108" s="31"/>
+      <x:c r="I108" s="31"/>
+      <x:c r="J108" s="31"/>
+      <x:c r="K108" s="31"/>
+      <x:c r="L108" s="31"/>
+      <x:c r="M108" s="31"/>
+      <x:c r="N108" s="31"/>
+      <x:c r="O108" s="31"/>
+      <x:c r="P108" s="31"/>
+      <x:c r="Q108" s="31"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="31"/>
+      <x:c r="B109" s="31"/>
+      <x:c r="C109" s="31"/>
+      <x:c r="D109" s="31"/>
+      <x:c r="E109" s="31"/>
+      <x:c r="F109" s="31"/>
+      <x:c r="G109" s="31"/>
+      <x:c r="H109" s="31"/>
+      <x:c r="I109" s="31"/>
+      <x:c r="J109" s="31"/>
+      <x:c r="K109" s="31"/>
+      <x:c r="L109" s="31"/>
+      <x:c r="M109" s="31"/>
+      <x:c r="N109" s="31"/>
+      <x:c r="O109" s="31"/>
+      <x:c r="P109" s="31"/>
+      <x:c r="Q109" s="31"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="31"/>
+      <x:c r="B110" s="31"/>
+      <x:c r="C110" s="31"/>
+      <x:c r="D110" s="31"/>
+      <x:c r="E110" s="31"/>
+      <x:c r="F110" s="31"/>
+      <x:c r="G110" s="31"/>
+      <x:c r="H110" s="31"/>
+      <x:c r="I110" s="31"/>
+      <x:c r="J110" s="31"/>
+      <x:c r="K110" s="31"/>
+      <x:c r="L110" s="31"/>
+      <x:c r="M110" s="31"/>
+      <x:c r="N110" s="31"/>
+      <x:c r="O110" s="31"/>
+      <x:c r="P110" s="31"/>
+      <x:c r="Q110" s="31"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="31"/>
+      <x:c r="B111" s="31"/>
+      <x:c r="C111" s="31"/>
+      <x:c r="D111" s="31"/>
+      <x:c r="E111" s="31"/>
+      <x:c r="F111" s="31"/>
+      <x:c r="G111" s="31"/>
+      <x:c r="H111" s="31"/>
+      <x:c r="I111" s="31"/>
+      <x:c r="J111" s="31"/>
+      <x:c r="K111" s="31"/>
+      <x:c r="L111" s="31"/>
+      <x:c r="M111" s="31"/>
+      <x:c r="N111" s="31"/>
+      <x:c r="O111" s="31"/>
+      <x:c r="P111" s="31"/>
+      <x:c r="Q111" s="31"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="31"/>
+      <x:c r="B112" s="31"/>
+      <x:c r="C112" s="31"/>
+      <x:c r="D112" s="31"/>
+      <x:c r="E112" s="31"/>
+      <x:c r="F112" s="31"/>
+      <x:c r="G112" s="31"/>
+      <x:c r="H112" s="31"/>
+      <x:c r="I112" s="31"/>
+      <x:c r="J112" s="31"/>
+      <x:c r="K112" s="31"/>
+      <x:c r="L112" s="31"/>
+      <x:c r="M112" s="31"/>
+      <x:c r="N112" s="31"/>
+      <x:c r="O112" s="31"/>
+      <x:c r="P112" s="31"/>
+      <x:c r="Q112" s="31"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="31"/>
+      <x:c r="B113" s="31"/>
+      <x:c r="C113" s="31"/>
+      <x:c r="D113" s="31"/>
+      <x:c r="E113" s="31"/>
+      <x:c r="F113" s="31"/>
+      <x:c r="G113" s="31"/>
+      <x:c r="H113" s="31"/>
+      <x:c r="I113" s="31"/>
+      <x:c r="J113" s="31"/>
+      <x:c r="K113" s="31"/>
+      <x:c r="L113" s="31"/>
+      <x:c r="M113" s="31"/>
+      <x:c r="N113" s="31"/>
+      <x:c r="O113" s="31"/>
+      <x:c r="P113" s="31"/>
+      <x:c r="Q113" s="31"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="31"/>
+      <x:c r="B114" s="31"/>
+      <x:c r="C114" s="31"/>
+      <x:c r="D114" s="31"/>
+      <x:c r="E114" s="31"/>
+      <x:c r="F114" s="31"/>
+      <x:c r="G114" s="31"/>
+      <x:c r="H114" s="31"/>
+      <x:c r="I114" s="31"/>
+      <x:c r="J114" s="31"/>
+      <x:c r="K114" s="31"/>
+      <x:c r="L114" s="31"/>
+      <x:c r="M114" s="31"/>
+      <x:c r="N114" s="31"/>
+      <x:c r="O114" s="31"/>
+      <x:c r="P114" s="31"/>
+      <x:c r="Q114" s="31"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="31"/>
+      <x:c r="B115" s="31"/>
+      <x:c r="C115" s="31"/>
+      <x:c r="D115" s="31"/>
+      <x:c r="E115" s="31"/>
+      <x:c r="F115" s="31"/>
+      <x:c r="G115" s="31"/>
+      <x:c r="H115" s="31"/>
+      <x:c r="I115" s="31"/>
+      <x:c r="J115" s="31"/>
+      <x:c r="K115" s="31"/>
+      <x:c r="L115" s="31"/>
+      <x:c r="M115" s="31"/>
+      <x:c r="N115" s="31"/>
+      <x:c r="O115" s="31"/>
+      <x:c r="P115" s="31"/>
+      <x:c r="Q115" s="31"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="31"/>
+      <x:c r="B116" s="31"/>
+      <x:c r="C116" s="31"/>
+      <x:c r="D116" s="31"/>
+      <x:c r="E116" s="31"/>
+      <x:c r="F116" s="31"/>
+      <x:c r="G116" s="31"/>
+      <x:c r="H116" s="31"/>
+      <x:c r="I116" s="31"/>
+      <x:c r="J116" s="31"/>
+      <x:c r="K116" s="31"/>
+      <x:c r="L116" s="31"/>
+      <x:c r="M116" s="31"/>
+      <x:c r="N116" s="31"/>
+      <x:c r="O116" s="31"/>
+      <x:c r="P116" s="31"/>
+      <x:c r="Q116" s="31"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="31"/>
+      <x:c r="B117" s="31"/>
+      <x:c r="C117" s="31"/>
+      <x:c r="D117" s="31"/>
+      <x:c r="E117" s="31"/>
+      <x:c r="F117" s="31"/>
+      <x:c r="G117" s="31"/>
+      <x:c r="H117" s="31"/>
+      <x:c r="I117" s="31"/>
+      <x:c r="J117" s="31"/>
+      <x:c r="K117" s="31"/>
+      <x:c r="L117" s="31"/>
+      <x:c r="M117" s="31"/>
+      <x:c r="N117" s="31"/>
+      <x:c r="O117" s="31"/>
+      <x:c r="P117" s="31"/>
+      <x:c r="Q117" s="31"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="31"/>
+      <x:c r="B118" s="31"/>
+      <x:c r="C118" s="31"/>
+      <x:c r="D118" s="31"/>
+      <x:c r="E118" s="31"/>
+      <x:c r="F118" s="31"/>
+      <x:c r="G118" s="31"/>
+      <x:c r="H118" s="31"/>
+      <x:c r="I118" s="31"/>
+      <x:c r="J118" s="31"/>
+      <x:c r="K118" s="31"/>
+      <x:c r="L118" s="31"/>
+      <x:c r="M118" s="31"/>
+      <x:c r="N118" s="31"/>
+      <x:c r="O118" s="31"/>
+      <x:c r="P118" s="31"/>
+      <x:c r="Q118" s="31"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="31"/>
+      <x:c r="B119" s="31"/>
+      <x:c r="C119" s="31"/>
+      <x:c r="D119" s="31"/>
+      <x:c r="E119" s="31"/>
+      <x:c r="F119" s="31"/>
+      <x:c r="G119" s="31"/>
+      <x:c r="H119" s="31"/>
+      <x:c r="I119" s="31"/>
+      <x:c r="J119" s="31"/>
+      <x:c r="K119" s="31"/>
+      <x:c r="L119" s="31"/>
+      <x:c r="M119" s="31"/>
+      <x:c r="N119" s="31"/>
+      <x:c r="O119" s="31"/>
+      <x:c r="P119" s="31"/>
+      <x:c r="Q119" s="31"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="31"/>
+      <x:c r="B120" s="31"/>
+      <x:c r="C120" s="31"/>
+      <x:c r="D120" s="31"/>
+      <x:c r="E120" s="31"/>
+      <x:c r="F120" s="31"/>
+      <x:c r="G120" s="31"/>
+      <x:c r="H120" s="31"/>
+      <x:c r="I120" s="31"/>
+      <x:c r="J120" s="31"/>
+      <x:c r="K120" s="31"/>
+      <x:c r="L120" s="31"/>
+      <x:c r="M120" s="31"/>
+      <x:c r="N120" s="31"/>
+      <x:c r="O120" s="31"/>
+      <x:c r="P120" s="31"/>
+      <x:c r="Q120" s="31"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="31"/>
+      <x:c r="B121" s="31"/>
+      <x:c r="C121" s="31"/>
+      <x:c r="D121" s="31"/>
+      <x:c r="E121" s="31"/>
+      <x:c r="F121" s="31"/>
+      <x:c r="G121" s="31"/>
+      <x:c r="H121" s="31"/>
+      <x:c r="I121" s="31"/>
+      <x:c r="J121" s="31"/>
+      <x:c r="K121" s="31"/>
+      <x:c r="L121" s="31"/>
+      <x:c r="M121" s="31"/>
+      <x:c r="N121" s="31"/>
+      <x:c r="O121" s="31"/>
+      <x:c r="P121" s="31"/>
+      <x:c r="Q121" s="31"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="31"/>
+      <x:c r="B122" s="31"/>
+      <x:c r="C122" s="31"/>
+      <x:c r="D122" s="31"/>
+      <x:c r="E122" s="31"/>
+      <x:c r="F122" s="31"/>
+      <x:c r="G122" s="31"/>
+      <x:c r="H122" s="31"/>
+      <x:c r="I122" s="31"/>
+      <x:c r="J122" s="31"/>
+      <x:c r="K122" s="31"/>
+      <x:c r="L122" s="31"/>
+      <x:c r="M122" s="31"/>
+      <x:c r="N122" s="31"/>
+      <x:c r="O122" s="31"/>
+      <x:c r="P122" s="31"/>
+      <x:c r="Q122" s="31"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="31"/>
+      <x:c r="B123" s="31"/>
+      <x:c r="C123" s="31"/>
+      <x:c r="D123" s="31"/>
+      <x:c r="E123" s="31"/>
+      <x:c r="F123" s="31"/>
+      <x:c r="G123" s="31"/>
+      <x:c r="H123" s="31"/>
+      <x:c r="I123" s="31"/>
+      <x:c r="J123" s="31"/>
+      <x:c r="K123" s="31"/>
+      <x:c r="L123" s="31"/>
+      <x:c r="M123" s="31"/>
+      <x:c r="N123" s="31"/>
+      <x:c r="O123" s="31"/>
+      <x:c r="P123" s="31"/>
+      <x:c r="Q123" s="31"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="31"/>
+      <x:c r="B124" s="31"/>
+      <x:c r="C124" s="31"/>
+      <x:c r="D124" s="31"/>
+      <x:c r="E124" s="31"/>
+      <x:c r="F124" s="31"/>
+      <x:c r="G124" s="31"/>
+      <x:c r="H124" s="31"/>
+      <x:c r="I124" s="31"/>
+      <x:c r="J124" s="31"/>
+      <x:c r="K124" s="31"/>
+      <x:c r="L124" s="31"/>
+      <x:c r="M124" s="31"/>
+      <x:c r="N124" s="31"/>
+      <x:c r="O124" s="31"/>
+      <x:c r="P124" s="31"/>
+      <x:c r="Q124" s="31"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="31"/>
+      <x:c r="B125" s="31"/>
+      <x:c r="C125" s="31"/>
+      <x:c r="D125" s="31"/>
+      <x:c r="E125" s="31"/>
+      <x:c r="F125" s="31"/>
+      <x:c r="G125" s="31"/>
+      <x:c r="H125" s="31"/>
+      <x:c r="I125" s="31"/>
+      <x:c r="J125" s="31"/>
+      <x:c r="K125" s="31"/>
+      <x:c r="L125" s="31"/>
+      <x:c r="M125" s="31"/>
+      <x:c r="N125" s="31"/>
+      <x:c r="O125" s="31"/>
+      <x:c r="P125" s="31"/>
+      <x:c r="Q125" s="31"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="31"/>
+      <x:c r="B126" s="31"/>
+      <x:c r="C126" s="31"/>
+      <x:c r="D126" s="31"/>
+      <x:c r="E126" s="31"/>
+      <x:c r="F126" s="31"/>
+      <x:c r="G126" s="31"/>
+      <x:c r="H126" s="31"/>
+      <x:c r="I126" s="31"/>
+      <x:c r="J126" s="31"/>
+      <x:c r="K126" s="31"/>
+      <x:c r="L126" s="31"/>
+      <x:c r="M126" s="31"/>
+      <x:c r="N126" s="31"/>
+      <x:c r="O126" s="31"/>
+      <x:c r="P126" s="31"/>
+      <x:c r="Q126" s="31"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="31"/>
+      <x:c r="B127" s="31"/>
+      <x:c r="C127" s="31"/>
+      <x:c r="D127" s="31"/>
+      <x:c r="E127" s="31"/>
+      <x:c r="F127" s="31"/>
+      <x:c r="G127" s="31"/>
+      <x:c r="H127" s="31"/>
+      <x:c r="I127" s="31"/>
+      <x:c r="J127" s="31"/>
+      <x:c r="K127" s="31"/>
+      <x:c r="L127" s="31"/>
+      <x:c r="M127" s="31"/>
+      <x:c r="N127" s="31"/>
+      <x:c r="O127" s="31"/>
+      <x:c r="P127" s="31"/>
+      <x:c r="Q127" s="31"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="31"/>
+      <x:c r="B128" s="31"/>
+      <x:c r="C128" s="31"/>
+      <x:c r="D128" s="31"/>
+      <x:c r="E128" s="31"/>
+      <x:c r="F128" s="31"/>
+      <x:c r="G128" s="31"/>
+      <x:c r="H128" s="31"/>
+      <x:c r="I128" s="31"/>
+      <x:c r="J128" s="31"/>
+      <x:c r="K128" s="31"/>
+      <x:c r="L128" s="31"/>
+      <x:c r="M128" s="31"/>
+      <x:c r="N128" s="31"/>
+      <x:c r="O128" s="31"/>
+      <x:c r="P128" s="31"/>
+      <x:c r="Q128" s="31"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="31"/>
+      <x:c r="B129" s="31"/>
+      <x:c r="C129" s="31"/>
+      <x:c r="D129" s="31"/>
+      <x:c r="E129" s="31"/>
+      <x:c r="F129" s="31"/>
+      <x:c r="G129" s="31"/>
+      <x:c r="H129" s="31"/>
+      <x:c r="I129" s="31"/>
+      <x:c r="J129" s="31"/>
+      <x:c r="K129" s="31"/>
+      <x:c r="L129" s="31"/>
+      <x:c r="M129" s="31"/>
+      <x:c r="N129" s="31"/>
+      <x:c r="O129" s="31"/>
+      <x:c r="P129" s="31"/>
+      <x:c r="Q129" s="31"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="31"/>
+      <x:c r="B130" s="31"/>
+      <x:c r="C130" s="31"/>
+      <x:c r="D130" s="31"/>
+      <x:c r="E130" s="31"/>
+      <x:c r="F130" s="31"/>
+      <x:c r="G130" s="31"/>
+      <x:c r="H130" s="31"/>
+      <x:c r="I130" s="31"/>
+      <x:c r="J130" s="31"/>
+      <x:c r="K130" s="31"/>
+      <x:c r="L130" s="31"/>
+      <x:c r="M130" s="31"/>
+      <x:c r="N130" s="31"/>
+      <x:c r="O130" s="31"/>
+      <x:c r="P130" s="31"/>
+      <x:c r="Q130" s="31"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="31"/>
+      <x:c r="B131" s="31"/>
+      <x:c r="C131" s="31"/>
+      <x:c r="D131" s="31"/>
+      <x:c r="E131" s="31"/>
+      <x:c r="F131" s="31"/>
+      <x:c r="G131" s="31"/>
+      <x:c r="H131" s="31"/>
+      <x:c r="I131" s="31"/>
+      <x:c r="J131" s="31"/>
+      <x:c r="K131" s="31"/>
+      <x:c r="L131" s="31"/>
+      <x:c r="M131" s="31"/>
+      <x:c r="N131" s="31"/>
+      <x:c r="O131" s="31"/>
+      <x:c r="P131" s="31"/>
+      <x:c r="Q131" s="31"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="31"/>
+      <x:c r="B132" s="31"/>
+      <x:c r="C132" s="31"/>
+      <x:c r="D132" s="31"/>
+      <x:c r="E132" s="31"/>
+      <x:c r="F132" s="31"/>
+      <x:c r="G132" s="31"/>
+      <x:c r="H132" s="31"/>
+      <x:c r="I132" s="31"/>
+      <x:c r="J132" s="31"/>
+      <x:c r="K132" s="31"/>
+      <x:c r="L132" s="31"/>
+      <x:c r="M132" s="31"/>
+      <x:c r="N132" s="31"/>
+      <x:c r="O132" s="31"/>
+      <x:c r="P132" s="31"/>
+      <x:c r="Q132" s="31"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="31"/>
+      <x:c r="B133" s="31"/>
+      <x:c r="C133" s="31"/>
+      <x:c r="D133" s="31"/>
+      <x:c r="E133" s="31"/>
+      <x:c r="F133" s="31"/>
+      <x:c r="G133" s="31"/>
+      <x:c r="H133" s="31"/>
+      <x:c r="I133" s="31"/>
+      <x:c r="J133" s="31"/>
+      <x:c r="K133" s="31"/>
+      <x:c r="L133" s="31"/>
+      <x:c r="M133" s="31"/>
+      <x:c r="N133" s="31"/>
+      <x:c r="O133" s="31"/>
+      <x:c r="P133" s="31"/>
+      <x:c r="Q133" s="31"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="31"/>
+      <x:c r="B134" s="31"/>
+      <x:c r="C134" s="31"/>
+      <x:c r="D134" s="31"/>
+      <x:c r="E134" s="31"/>
+      <x:c r="F134" s="31"/>
+      <x:c r="G134" s="31"/>
+      <x:c r="H134" s="31"/>
+      <x:c r="I134" s="31"/>
+      <x:c r="J134" s="31"/>
+      <x:c r="K134" s="31"/>
+      <x:c r="L134" s="31"/>
+      <x:c r="M134" s="31"/>
+      <x:c r="N134" s="31"/>
+      <x:c r="O134" s="31"/>
+      <x:c r="P134" s="31"/>
+      <x:c r="Q134" s="31"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="31"/>
+      <x:c r="B135" s="31"/>
+      <x:c r="C135" s="31"/>
+      <x:c r="D135" s="31"/>
+      <x:c r="E135" s="31"/>
+      <x:c r="F135" s="31"/>
+      <x:c r="G135" s="31"/>
+      <x:c r="H135" s="31"/>
+      <x:c r="I135" s="31"/>
+      <x:c r="J135" s="31"/>
+      <x:c r="K135" s="31"/>
+      <x:c r="L135" s="31"/>
+      <x:c r="M135" s="31"/>
+      <x:c r="N135" s="31"/>
+      <x:c r="O135" s="31"/>
+      <x:c r="P135" s="31"/>
+      <x:c r="Q135" s="31"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="31"/>
+      <x:c r="B136" s="31"/>
+      <x:c r="C136" s="31"/>
+      <x:c r="D136" s="31"/>
+      <x:c r="E136" s="31"/>
+      <x:c r="F136" s="31"/>
+      <x:c r="G136" s="31"/>
+      <x:c r="H136" s="31"/>
+      <x:c r="I136" s="31"/>
+      <x:c r="J136" s="31"/>
+      <x:c r="K136" s="31"/>
+      <x:c r="L136" s="31"/>
+      <x:c r="M136" s="31"/>
+      <x:c r="N136" s="31"/>
+      <x:c r="O136" s="31"/>
+      <x:c r="P136" s="31"/>
+      <x:c r="Q136" s="31"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="31"/>
+      <x:c r="B137" s="31"/>
+      <x:c r="C137" s="31"/>
+      <x:c r="D137" s="31"/>
+      <x:c r="E137" s="31"/>
+      <x:c r="F137" s="31"/>
+      <x:c r="G137" s="31"/>
+      <x:c r="H137" s="31"/>
+      <x:c r="I137" s="31"/>
+      <x:c r="J137" s="31"/>
+      <x:c r="K137" s="31"/>
+      <x:c r="L137" s="31"/>
+      <x:c r="M137" s="31"/>
+      <x:c r="N137" s="31"/>
+      <x:c r="O137" s="31"/>
+      <x:c r="P137" s="31"/>
+      <x:c r="Q137" s="31"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="31"/>
+      <x:c r="B138" s="31"/>
+      <x:c r="C138" s="31"/>
+      <x:c r="D138" s="31"/>
+      <x:c r="E138" s="31"/>
+      <x:c r="F138" s="31"/>
+      <x:c r="G138" s="31"/>
+      <x:c r="H138" s="31"/>
+      <x:c r="I138" s="31"/>
+      <x:c r="J138" s="31"/>
+      <x:c r="K138" s="31"/>
+      <x:c r="L138" s="31"/>
+      <x:c r="M138" s="31"/>
+      <x:c r="N138" s="31"/>
+      <x:c r="O138" s="31"/>
+      <x:c r="P138" s="31"/>
+      <x:c r="Q138" s="31"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="31"/>
+      <x:c r="B139" s="31"/>
+      <x:c r="C139" s="31"/>
+      <x:c r="D139" s="31"/>
+      <x:c r="E139" s="31"/>
+      <x:c r="F139" s="31"/>
+      <x:c r="G139" s="31"/>
+      <x:c r="H139" s="31"/>
+      <x:c r="I139" s="31"/>
+      <x:c r="J139" s="31"/>
+      <x:c r="K139" s="31"/>
+      <x:c r="L139" s="31"/>
+      <x:c r="M139" s="31"/>
+      <x:c r="N139" s="31"/>
+      <x:c r="O139" s="31"/>
+      <x:c r="P139" s="31"/>
+      <x:c r="Q139" s="31"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="31"/>
+      <x:c r="B140" s="31"/>
+      <x:c r="C140" s="31"/>
+      <x:c r="D140" s="31"/>
+      <x:c r="E140" s="31"/>
+      <x:c r="F140" s="31"/>
+      <x:c r="G140" s="31"/>
+      <x:c r="H140" s="31"/>
+      <x:c r="I140" s="31"/>
+      <x:c r="J140" s="31"/>
+      <x:c r="K140" s="31"/>
+      <x:c r="L140" s="31"/>
+      <x:c r="M140" s="31"/>
+      <x:c r="N140" s="31"/>
+      <x:c r="O140" s="31"/>
+      <x:c r="P140" s="31"/>
+      <x:c r="Q140" s="31"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="31"/>
+      <x:c r="B141" s="31"/>
+      <x:c r="C141" s="31"/>
+      <x:c r="D141" s="31"/>
+      <x:c r="E141" s="31"/>
+      <x:c r="F141" s="31"/>
+      <x:c r="G141" s="31"/>
+      <x:c r="H141" s="31"/>
+      <x:c r="I141" s="31"/>
+      <x:c r="J141" s="31"/>
+      <x:c r="K141" s="31"/>
+      <x:c r="L141" s="31"/>
+      <x:c r="M141" s="31"/>
+      <x:c r="N141" s="31"/>
+      <x:c r="O141" s="31"/>
+      <x:c r="P141" s="31"/>
+      <x:c r="Q141" s="31"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="31"/>
+      <x:c r="B142" s="31"/>
+      <x:c r="C142" s="31"/>
+      <x:c r="D142" s="31"/>
+      <x:c r="E142" s="31"/>
+      <x:c r="F142" s="31"/>
+      <x:c r="G142" s="31"/>
+      <x:c r="H142" s="31"/>
+      <x:c r="I142" s="31"/>
+      <x:c r="J142" s="31"/>
+      <x:c r="K142" s="31"/>
+      <x:c r="L142" s="31"/>
+      <x:c r="M142" s="31"/>
+      <x:c r="N142" s="31"/>
+      <x:c r="O142" s="31"/>
+      <x:c r="P142" s="31"/>
+      <x:c r="Q142" s="31"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="31"/>
+      <x:c r="B143" s="31"/>
+      <x:c r="C143" s="31"/>
+      <x:c r="D143" s="31"/>
+      <x:c r="E143" s="31"/>
+      <x:c r="F143" s="31"/>
+      <x:c r="G143" s="31"/>
+      <x:c r="H143" s="31"/>
+      <x:c r="I143" s="31"/>
+      <x:c r="J143" s="31"/>
+      <x:c r="K143" s="31"/>
+      <x:c r="L143" s="31"/>
+      <x:c r="M143" s="31"/>
+      <x:c r="N143" s="31"/>
+      <x:c r="O143" s="31"/>
+      <x:c r="P143" s="31"/>
+      <x:c r="Q143" s="31"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="31"/>
+      <x:c r="B144" s="31"/>
+      <x:c r="C144" s="31"/>
+      <x:c r="D144" s="31"/>
+      <x:c r="E144" s="31"/>
+      <x:c r="F144" s="31"/>
+      <x:c r="G144" s="31"/>
+      <x:c r="H144" s="31"/>
+      <x:c r="I144" s="31"/>
+      <x:c r="J144" s="31"/>
+      <x:c r="K144" s="31"/>
+      <x:c r="L144" s="31"/>
+      <x:c r="M144" s="31"/>
+      <x:c r="N144" s="31"/>
+      <x:c r="O144" s="31"/>
+      <x:c r="P144" s="31"/>
+      <x:c r="Q144" s="31"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="31"/>
+      <x:c r="B145" s="31"/>
+      <x:c r="C145" s="31"/>
+      <x:c r="D145" s="31"/>
+      <x:c r="E145" s="31"/>
+      <x:c r="F145" s="31"/>
+      <x:c r="G145" s="31"/>
+      <x:c r="H145" s="31"/>
+      <x:c r="I145" s="31"/>
+      <x:c r="J145" s="31"/>
+      <x:c r="K145" s="31"/>
+      <x:c r="L145" s="31"/>
+      <x:c r="M145" s="31"/>
+      <x:c r="N145" s="31"/>
+      <x:c r="O145" s="31"/>
+      <x:c r="P145" s="31"/>
+      <x:c r="Q145" s="31"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="31"/>
+      <x:c r="B146" s="31"/>
+      <x:c r="C146" s="31"/>
+      <x:c r="D146" s="31"/>
+      <x:c r="E146" s="31"/>
+      <x:c r="F146" s="31"/>
+      <x:c r="G146" s="31"/>
+      <x:c r="H146" s="31"/>
+      <x:c r="I146" s="31"/>
+      <x:c r="J146" s="31"/>
+      <x:c r="K146" s="31"/>
+      <x:c r="L146" s="31"/>
+      <x:c r="M146" s="31"/>
+      <x:c r="N146" s="31"/>
+      <x:c r="O146" s="31"/>
+      <x:c r="P146" s="31"/>
+      <x:c r="Q146" s="31"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="31"/>
+      <x:c r="B147" s="31"/>
+      <x:c r="C147" s="31"/>
+      <x:c r="D147" s="31"/>
+      <x:c r="E147" s="31"/>
+      <x:c r="F147" s="31"/>
+      <x:c r="G147" s="31"/>
+      <x:c r="H147" s="31"/>
+      <x:c r="I147" s="31"/>
+      <x:c r="J147" s="31"/>
+      <x:c r="K147" s="31"/>
+      <x:c r="L147" s="31"/>
+      <x:c r="M147" s="31"/>
+      <x:c r="N147" s="31"/>
+      <x:c r="O147" s="31"/>
+      <x:c r="P147" s="31"/>
+      <x:c r="Q147" s="31"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="31"/>
+      <x:c r="B148" s="31"/>
+      <x:c r="C148" s="31"/>
+      <x:c r="D148" s="31"/>
+      <x:c r="E148" s="31"/>
+      <x:c r="F148" s="31"/>
+      <x:c r="G148" s="31"/>
+      <x:c r="H148" s="31"/>
+      <x:c r="I148" s="31"/>
+      <x:c r="J148" s="31"/>
+      <x:c r="K148" s="31"/>
+      <x:c r="L148" s="31"/>
+      <x:c r="M148" s="31"/>
+      <x:c r="N148" s="31"/>
+      <x:c r="O148" s="31"/>
+      <x:c r="P148" s="31"/>
+      <x:c r="Q148" s="31"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="31"/>
+      <x:c r="B149" s="31"/>
+      <x:c r="C149" s="31"/>
+      <x:c r="D149" s="31"/>
+      <x:c r="E149" s="31"/>
+      <x:c r="F149" s="31"/>
+      <x:c r="G149" s="31"/>
+      <x:c r="H149" s="31"/>
+      <x:c r="I149" s="31"/>
+      <x:c r="J149" s="31"/>
+      <x:c r="K149" s="31"/>
+      <x:c r="L149" s="31"/>
+      <x:c r="M149" s="31"/>
+      <x:c r="N149" s="31"/>
+      <x:c r="O149" s="31"/>
+      <x:c r="P149" s="31"/>
+      <x:c r="Q149" s="31"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="31"/>
+      <x:c r="B150" s="31"/>
+      <x:c r="C150" s="31"/>
+      <x:c r="D150" s="31"/>
+      <x:c r="E150" s="31"/>
+      <x:c r="F150" s="31"/>
+      <x:c r="G150" s="31"/>
+      <x:c r="H150" s="31"/>
+      <x:c r="I150" s="31"/>
+      <x:c r="J150" s="31"/>
+      <x:c r="K150" s="31"/>
+      <x:c r="L150" s="31"/>
+      <x:c r="M150" s="31"/>
+      <x:c r="N150" s="31"/>
+      <x:c r="O150" s="31"/>
+      <x:c r="P150" s="31"/>
+      <x:c r="Q150" s="31"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="31"/>
+      <x:c r="B151" s="31"/>
+      <x:c r="C151" s="31"/>
+      <x:c r="D151" s="31"/>
+      <x:c r="E151" s="31"/>
+      <x:c r="F151" s="31"/>
+      <x:c r="G151" s="31"/>
+      <x:c r="H151" s="31"/>
+      <x:c r="I151" s="31"/>
+      <x:c r="J151" s="31"/>
+      <x:c r="K151" s="31"/>
+      <x:c r="L151" s="31"/>
+      <x:c r="M151" s="31"/>
+      <x:c r="N151" s="31"/>
+      <x:c r="O151" s="31"/>
+      <x:c r="P151" s="31"/>
+      <x:c r="Q151" s="31"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="31"/>
+      <x:c r="B152" s="31"/>
+      <x:c r="C152" s="31"/>
+      <x:c r="D152" s="31"/>
+      <x:c r="E152" s="31"/>
+      <x:c r="F152" s="31"/>
+      <x:c r="G152" s="31"/>
+      <x:c r="H152" s="31"/>
+      <x:c r="I152" s="31"/>
+      <x:c r="J152" s="31"/>
+      <x:c r="K152" s="31"/>
+      <x:c r="L152" s="31"/>
+      <x:c r="M152" s="31"/>
+      <x:c r="N152" s="31"/>
+      <x:c r="O152" s="31"/>
+      <x:c r="P152" s="31"/>
+      <x:c r="Q152" s="31"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="31"/>
+      <x:c r="B153" s="31"/>
+      <x:c r="C153" s="31"/>
+      <x:c r="D153" s="31"/>
+      <x:c r="E153" s="31"/>
+      <x:c r="F153" s="31"/>
+      <x:c r="G153" s="31"/>
+      <x:c r="H153" s="31"/>
+      <x:c r="I153" s="31"/>
+      <x:c r="J153" s="31"/>
+      <x:c r="K153" s="31"/>
+      <x:c r="L153" s="31"/>
+      <x:c r="M153" s="31"/>
+      <x:c r="N153" s="31"/>
+      <x:c r="O153" s="31"/>
+      <x:c r="P153" s="31"/>
+      <x:c r="Q153" s="31"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="31"/>
+      <x:c r="B154" s="31"/>
+      <x:c r="C154" s="31"/>
+      <x:c r="D154" s="31"/>
+      <x:c r="E154" s="31"/>
+      <x:c r="F154" s="31"/>
+      <x:c r="G154" s="31"/>
+      <x:c r="H154" s="31"/>
+      <x:c r="I154" s="31"/>
+      <x:c r="J154" s="31"/>
+      <x:c r="K154" s="31"/>
+      <x:c r="L154" s="31"/>
+      <x:c r="M154" s="31"/>
+      <x:c r="N154" s="31"/>
+      <x:c r="O154" s="31"/>
+      <x:c r="P154" s="31"/>
+      <x:c r="Q154" s="31"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="31"/>
+      <x:c r="B155" s="31"/>
+      <x:c r="C155" s="31"/>
+      <x:c r="D155" s="31"/>
+      <x:c r="E155" s="31"/>
+      <x:c r="F155" s="31"/>
+      <x:c r="G155" s="31"/>
+      <x:c r="H155" s="31"/>
+      <x:c r="I155" s="31"/>
+      <x:c r="J155" s="31"/>
+      <x:c r="K155" s="31"/>
+      <x:c r="L155" s="31"/>
+      <x:c r="M155" s="31"/>
+      <x:c r="N155" s="31"/>
+      <x:c r="O155" s="31"/>
+      <x:c r="P155" s="31"/>
+      <x:c r="Q155" s="31"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="31"/>
+      <x:c r="B156" s="31"/>
+      <x:c r="C156" s="31"/>
+      <x:c r="D156" s="31"/>
+      <x:c r="E156" s="31"/>
+      <x:c r="F156" s="31"/>
+      <x:c r="G156" s="31"/>
+      <x:c r="H156" s="31"/>
+      <x:c r="I156" s="31"/>
+      <x:c r="J156" s="31"/>
+      <x:c r="K156" s="31"/>
+      <x:c r="L156" s="31"/>
+      <x:c r="M156" s="31"/>
+      <x:c r="N156" s="31"/>
+      <x:c r="O156" s="31"/>
+      <x:c r="P156" s="31"/>
+      <x:c r="Q156" s="31"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="31"/>
+      <x:c r="B157" s="31"/>
+      <x:c r="C157" s="31"/>
+      <x:c r="D157" s="31"/>
+      <x:c r="E157" s="31"/>
+      <x:c r="F157" s="31"/>
+      <x:c r="G157" s="31"/>
+      <x:c r="H157" s="31"/>
+      <x:c r="I157" s="31"/>
+      <x:c r="J157" s="31"/>
+      <x:c r="K157" s="31"/>
+      <x:c r="L157" s="31"/>
+      <x:c r="M157" s="31"/>
+      <x:c r="N157" s="31"/>
+      <x:c r="O157" s="31"/>
+      <x:c r="P157" s="31"/>
+      <x:c r="Q157" s="31"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="31"/>
+      <x:c r="B158" s="31"/>
+      <x:c r="C158" s="31"/>
+      <x:c r="D158" s="31"/>
+      <x:c r="E158" s="31"/>
+      <x:c r="F158" s="31"/>
+      <x:c r="G158" s="31"/>
+      <x:c r="H158" s="31"/>
+      <x:c r="I158" s="31"/>
+      <x:c r="J158" s="31"/>
+      <x:c r="K158" s="31"/>
+      <x:c r="L158" s="31"/>
+      <x:c r="M158" s="31"/>
+      <x:c r="N158" s="31"/>
+      <x:c r="O158" s="31"/>
+      <x:c r="P158" s="31"/>
+      <x:c r="Q158" s="31"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="31"/>
+      <x:c r="B159" s="31"/>
+      <x:c r="C159" s="31"/>
+      <x:c r="D159" s="31"/>
+      <x:c r="E159" s="31"/>
+      <x:c r="F159" s="31"/>
+      <x:c r="G159" s="31"/>
+      <x:c r="H159" s="31"/>
+      <x:c r="I159" s="31"/>
+      <x:c r="J159" s="31"/>
+      <x:c r="K159" s="31"/>
+      <x:c r="L159" s="31"/>
+      <x:c r="M159" s="31"/>
+      <x:c r="N159" s="31"/>
+      <x:c r="O159" s="31"/>
+      <x:c r="P159" s="31"/>
+      <x:c r="Q159" s="31"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="31"/>
+      <x:c r="B160" s="31"/>
+      <x:c r="C160" s="31"/>
+      <x:c r="D160" s="31"/>
+      <x:c r="E160" s="31"/>
+      <x:c r="F160" s="31"/>
+      <x:c r="G160" s="31"/>
+      <x:c r="H160" s="31"/>
+      <x:c r="I160" s="31"/>
+      <x:c r="J160" s="31"/>
+      <x:c r="K160" s="31"/>
+      <x:c r="L160" s="31"/>
+      <x:c r="M160" s="31"/>
+      <x:c r="N160" s="31"/>
+      <x:c r="O160" s="31"/>
+      <x:c r="P160" s="31"/>
+      <x:c r="Q160" s="31"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="31"/>
+      <x:c r="B161" s="31"/>
+      <x:c r="C161" s="31"/>
+      <x:c r="D161" s="31"/>
+      <x:c r="E161" s="31"/>
+      <x:c r="F161" s="31"/>
+      <x:c r="G161" s="31"/>
+      <x:c r="H161" s="31"/>
+      <x:c r="I161" s="31"/>
+      <x:c r="J161" s="31"/>
+      <x:c r="K161" s="31"/>
+      <x:c r="L161" s="31"/>
+      <x:c r="M161" s="31"/>
+      <x:c r="N161" s="31"/>
+      <x:c r="O161" s="31"/>
+      <x:c r="P161" s="31"/>
+      <x:c r="Q161" s="31"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="31"/>
+      <x:c r="B162" s="31"/>
+      <x:c r="C162" s="31"/>
+      <x:c r="D162" s="31"/>
+      <x:c r="E162" s="31"/>
+      <x:c r="F162" s="31"/>
+      <x:c r="G162" s="31"/>
+      <x:c r="H162" s="31"/>
+      <x:c r="I162" s="31"/>
+      <x:c r="J162" s="31"/>
+      <x:c r="K162" s="31"/>
+      <x:c r="L162" s="31"/>
+      <x:c r="M162" s="31"/>
+      <x:c r="N162" s="31"/>
+      <x:c r="O162" s="31"/>
+      <x:c r="P162" s="31"/>
+      <x:c r="Q162" s="31"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="31"/>
+      <x:c r="B163" s="31"/>
+      <x:c r="C163" s="31"/>
+      <x:c r="D163" s="31"/>
+      <x:c r="E163" s="31"/>
+      <x:c r="F163" s="31"/>
+      <x:c r="G163" s="31"/>
+      <x:c r="H163" s="31"/>
+      <x:c r="I163" s="31"/>
+      <x:c r="J163" s="31"/>
+      <x:c r="K163" s="31"/>
+      <x:c r="L163" s="31"/>
+      <x:c r="M163" s="31"/>
+      <x:c r="N163" s="31"/>
+      <x:c r="O163" s="31"/>
+      <x:c r="P163" s="31"/>
+      <x:c r="Q163" s="31"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="31"/>
+      <x:c r="B164" s="31"/>
+      <x:c r="C164" s="31"/>
+      <x:c r="D164" s="31"/>
+      <x:c r="E164" s="31"/>
+      <x:c r="F164" s="31"/>
+      <x:c r="G164" s="31"/>
+      <x:c r="H164" s="31"/>
+      <x:c r="I164" s="31"/>
+      <x:c r="J164" s="31"/>
+      <x:c r="K164" s="31"/>
+      <x:c r="L164" s="31"/>
+      <x:c r="M164" s="31"/>
+      <x:c r="N164" s="31"/>
+      <x:c r="O164" s="31"/>
+      <x:c r="P164" s="31"/>
+      <x:c r="Q164" s="31"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="31"/>
+      <x:c r="B165" s="31"/>
+      <x:c r="C165" s="31"/>
+      <x:c r="D165" s="31"/>
+      <x:c r="E165" s="31"/>
+      <x:c r="F165" s="31"/>
+      <x:c r="G165" s="31"/>
+      <x:c r="H165" s="31"/>
+      <x:c r="I165" s="31"/>
+      <x:c r="J165" s="31"/>
+      <x:c r="K165" s="31"/>
+      <x:c r="L165" s="31"/>
+      <x:c r="M165" s="31"/>
+      <x:c r="N165" s="31"/>
+      <x:c r="O165" s="31"/>
+      <x:c r="P165" s="31"/>
+      <x:c r="Q165" s="31"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="31"/>
+      <x:c r="B166" s="31"/>
+      <x:c r="C166" s="31"/>
+      <x:c r="D166" s="31"/>
+      <x:c r="E166" s="31"/>
+      <x:c r="F166" s="31"/>
+      <x:c r="G166" s="31"/>
+      <x:c r="H166" s="31"/>
+      <x:c r="I166" s="31"/>
+      <x:c r="J166" s="31"/>
+      <x:c r="K166" s="31"/>
+      <x:c r="L166" s="31"/>
+      <x:c r="M166" s="31"/>
+      <x:c r="N166" s="31"/>
+      <x:c r="O166" s="31"/>
+      <x:c r="P166" s="31"/>
+      <x:c r="Q166" s="31"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="31"/>
+      <x:c r="B167" s="31"/>
+      <x:c r="C167" s="31"/>
+      <x:c r="D167" s="31"/>
+      <x:c r="E167" s="31"/>
+      <x:c r="F167" s="31"/>
+      <x:c r="G167" s="31"/>
+      <x:c r="H167" s="31"/>
+      <x:c r="I167" s="31"/>
+      <x:c r="J167" s="31"/>
+      <x:c r="K167" s="31"/>
+      <x:c r="L167" s="31"/>
+      <x:c r="M167" s="31"/>
+      <x:c r="N167" s="31"/>
+      <x:c r="O167" s="31"/>
+      <x:c r="P167" s="31"/>
+      <x:c r="Q167" s="31"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="31"/>
+      <x:c r="B168" s="31"/>
+      <x:c r="C168" s="31"/>
+      <x:c r="D168" s="31"/>
+      <x:c r="E168" s="31"/>
+      <x:c r="F168" s="31"/>
+      <x:c r="G168" s="31"/>
+      <x:c r="H168" s="31"/>
+      <x:c r="I168" s="31"/>
+      <x:c r="J168" s="31"/>
+      <x:c r="K168" s="31"/>
+      <x:c r="L168" s="31"/>
+      <x:c r="M168" s="31"/>
+      <x:c r="N168" s="31"/>
+      <x:c r="O168" s="31"/>
+      <x:c r="P168" s="31"/>
+      <x:c r="Q168" s="31"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="31"/>
+      <x:c r="B169" s="31"/>
+      <x:c r="C169" s="31"/>
+      <x:c r="D169" s="31"/>
+      <x:c r="E169" s="31"/>
+      <x:c r="F169" s="31"/>
+      <x:c r="G169" s="31"/>
+      <x:c r="H169" s="31"/>
+      <x:c r="I169" s="31"/>
+      <x:c r="J169" s="31"/>
+      <x:c r="K169" s="31"/>
+      <x:c r="L169" s="31"/>
+      <x:c r="M169" s="31"/>
+      <x:c r="N169" s="31"/>
+      <x:c r="O169" s="31"/>
+      <x:c r="P169" s="31"/>
+      <x:c r="Q169" s="31"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="31"/>
+      <x:c r="B170" s="31"/>
+      <x:c r="C170" s="31"/>
+      <x:c r="D170" s="31"/>
+      <x:c r="E170" s="31"/>
+      <x:c r="F170" s="31"/>
+      <x:c r="G170" s="31"/>
+      <x:c r="H170" s="31"/>
+      <x:c r="I170" s="31"/>
+      <x:c r="J170" s="31"/>
+      <x:c r="K170" s="31"/>
+      <x:c r="L170" s="31"/>
+      <x:c r="M170" s="31"/>
+      <x:c r="N170" s="31"/>
+      <x:c r="O170" s="31"/>
+      <x:c r="P170" s="31"/>
+      <x:c r="Q170" s="31"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="31"/>
+      <x:c r="B171" s="31"/>
+      <x:c r="C171" s="31"/>
+      <x:c r="D171" s="31"/>
+      <x:c r="E171" s="31"/>
+      <x:c r="F171" s="31"/>
+      <x:c r="G171" s="31"/>
+      <x:c r="H171" s="31"/>
+      <x:c r="I171" s="31"/>
+      <x:c r="J171" s="31"/>
+      <x:c r="K171" s="31"/>
+      <x:c r="L171" s="31"/>
+      <x:c r="M171" s="31"/>
+      <x:c r="N171" s="31"/>
+      <x:c r="O171" s="31"/>
+      <x:c r="P171" s="31"/>
+      <x:c r="Q171" s="31"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="31"/>
+      <x:c r="B172" s="31"/>
+      <x:c r="C172" s="31"/>
+      <x:c r="D172" s="31"/>
+      <x:c r="E172" s="31"/>
+      <x:c r="F172" s="31"/>
+      <x:c r="G172" s="31"/>
+      <x:c r="H172" s="31"/>
+      <x:c r="I172" s="31"/>
+      <x:c r="J172" s="31"/>
+      <x:c r="K172" s="31"/>
+      <x:c r="L172" s="31"/>
+      <x:c r="M172" s="31"/>
+      <x:c r="N172" s="31"/>
+      <x:c r="O172" s="31"/>
+      <x:c r="P172" s="31"/>
+      <x:c r="Q172" s="31"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="31"/>
+      <x:c r="B173" s="31"/>
+      <x:c r="C173" s="31"/>
+      <x:c r="D173" s="31"/>
+      <x:c r="E173" s="31"/>
+      <x:c r="F173" s="31"/>
+      <x:c r="G173" s="31"/>
+      <x:c r="H173" s="31"/>
+      <x:c r="I173" s="31"/>
+      <x:c r="J173" s="31"/>
+      <x:c r="K173" s="31"/>
+      <x:c r="L173" s="31"/>
+      <x:c r="M173" s="31"/>
+      <x:c r="N173" s="31"/>
+      <x:c r="O173" s="31"/>
+      <x:c r="P173" s="31"/>
+      <x:c r="Q173" s="31"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="31"/>
+      <x:c r="B174" s="31"/>
+      <x:c r="C174" s="31"/>
+      <x:c r="D174" s="31"/>
+      <x:c r="E174" s="31"/>
+      <x:c r="F174" s="31"/>
+      <x:c r="G174" s="31"/>
+      <x:c r="H174" s="31"/>
+      <x:c r="I174" s="31"/>
+      <x:c r="J174" s="31"/>
+      <x:c r="K174" s="31"/>
+      <x:c r="L174" s="31"/>
+      <x:c r="M174" s="31"/>
+      <x:c r="N174" s="31"/>
+      <x:c r="O174" s="31"/>
+      <x:c r="P174" s="31"/>
+      <x:c r="Q174" s="31"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="31"/>
+      <x:c r="B175" s="31"/>
+      <x:c r="C175" s="31"/>
+      <x:c r="D175" s="31"/>
+      <x:c r="E175" s="31"/>
+      <x:c r="F175" s="31"/>
+      <x:c r="G175" s="31"/>
+      <x:c r="H175" s="31"/>
+      <x:c r="I175" s="31"/>
+      <x:c r="J175" s="31"/>
+      <x:c r="K175" s="31"/>
+      <x:c r="L175" s="31"/>
+      <x:c r="M175" s="31"/>
+      <x:c r="N175" s="31"/>
+      <x:c r="O175" s="31"/>
+      <x:c r="P175" s="31"/>
+      <x:c r="Q175" s="31"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="31"/>
+      <x:c r="B176" s="31"/>
+      <x:c r="C176" s="31"/>
+      <x:c r="D176" s="31"/>
+      <x:c r="E176" s="31"/>
+      <x:c r="F176" s="31"/>
+      <x:c r="G176" s="31"/>
+      <x:c r="H176" s="31"/>
+      <x:c r="I176" s="31"/>
+      <x:c r="J176" s="31"/>
+      <x:c r="K176" s="31"/>
+      <x:c r="L176" s="31"/>
+      <x:c r="M176" s="31"/>
+      <x:c r="N176" s="31"/>
+      <x:c r="O176" s="31"/>
+      <x:c r="P176" s="31"/>
+      <x:c r="Q176" s="31"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="31"/>
+      <x:c r="B177" s="31"/>
+      <x:c r="C177" s="31"/>
+      <x:c r="D177" s="31"/>
+      <x:c r="E177" s="31"/>
+      <x:c r="F177" s="31"/>
+      <x:c r="G177" s="31"/>
+      <x:c r="H177" s="31"/>
+      <x:c r="I177" s="31"/>
+      <x:c r="J177" s="31"/>
+      <x:c r="K177" s="31"/>
+      <x:c r="L177" s="31"/>
+      <x:c r="M177" s="31"/>
+      <x:c r="N177" s="31"/>
+      <x:c r="O177" s="31"/>
+      <x:c r="P177" s="31"/>
+      <x:c r="Q177" s="31"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="31"/>
+      <x:c r="B178" s="31"/>
+      <x:c r="C178" s="31"/>
+      <x:c r="D178" s="31"/>
+      <x:c r="E178" s="31"/>
+      <x:c r="F178" s="31"/>
+      <x:c r="G178" s="31"/>
+      <x:c r="H178" s="31"/>
+      <x:c r="I178" s="31"/>
+      <x:c r="J178" s="31"/>
+      <x:c r="K178" s="31"/>
+      <x:c r="L178" s="31"/>
+      <x:c r="M178" s="31"/>
+      <x:c r="N178" s="31"/>
+      <x:c r="O178" s="31"/>
+      <x:c r="P178" s="31"/>
+      <x:c r="Q178" s="31"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="31"/>
+      <x:c r="B179" s="31"/>
+      <x:c r="C179" s="31"/>
+      <x:c r="D179" s="31"/>
+      <x:c r="E179" s="31"/>
+      <x:c r="F179" s="31"/>
+      <x:c r="G179" s="31"/>
+      <x:c r="H179" s="31"/>
+      <x:c r="I179" s="31"/>
+      <x:c r="J179" s="31"/>
+      <x:c r="K179" s="31"/>
+      <x:c r="L179" s="31"/>
+      <x:c r="M179" s="31"/>
+      <x:c r="N179" s="31"/>
+      <x:c r="O179" s="31"/>
+      <x:c r="P179" s="31"/>
+      <x:c r="Q179" s="31"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="31"/>
+      <x:c r="B180" s="31"/>
+      <x:c r="C180" s="31"/>
+      <x:c r="D180" s="31"/>
+      <x:c r="E180" s="31"/>
+      <x:c r="F180" s="31"/>
+      <x:c r="G180" s="31"/>
+      <x:c r="H180" s="31"/>
+      <x:c r="I180" s="31"/>
+      <x:c r="J180" s="31"/>
+      <x:c r="K180" s="31"/>
+      <x:c r="L180" s="31"/>
+      <x:c r="M180" s="31"/>
+      <x:c r="N180" s="31"/>
+      <x:c r="O180" s="31"/>
+      <x:c r="P180" s="31"/>
+      <x:c r="Q180" s="31"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="31"/>
+      <x:c r="B181" s="31"/>
+      <x:c r="C181" s="31"/>
+      <x:c r="D181" s="31"/>
+      <x:c r="E181" s="31"/>
+      <x:c r="F181" s="31"/>
+      <x:c r="G181" s="31"/>
+      <x:c r="H181" s="31"/>
+      <x:c r="I181" s="31"/>
+      <x:c r="J181" s="31"/>
+      <x:c r="K181" s="31"/>
+      <x:c r="L181" s="31"/>
+      <x:c r="M181" s="31"/>
+      <x:c r="N181" s="31"/>
+      <x:c r="O181" s="31"/>
+      <x:c r="P181" s="31"/>
+      <x:c r="Q181" s="31"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31"/>
+      <x:c r="B182" s="31"/>
+      <x:c r="C182" s="31"/>
+      <x:c r="D182" s="31"/>
+      <x:c r="E182" s="31"/>
+      <x:c r="F182" s="31"/>
+      <x:c r="G182" s="31"/>
+      <x:c r="H182" s="31"/>
+      <x:c r="I182" s="31"/>
+      <x:c r="J182" s="31"/>
+      <x:c r="K182" s="31"/>
+      <x:c r="L182" s="31"/>
+      <x:c r="M182" s="31"/>
+      <x:c r="N182" s="31"/>
+      <x:c r="O182" s="31"/>
+      <x:c r="P182" s="31"/>
+      <x:c r="Q182" s="31"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31"/>
+      <x:c r="B183" s="31"/>
+      <x:c r="C183" s="31"/>
+      <x:c r="D183" s="31"/>
+      <x:c r="E183" s="31"/>
+      <x:c r="F183" s="31"/>
+      <x:c r="G183" s="31"/>
+      <x:c r="H183" s="31"/>
+      <x:c r="I183" s="31"/>
+      <x:c r="J183" s="31"/>
+      <x:c r="K183" s="31"/>
+      <x:c r="L183" s="31"/>
+      <x:c r="M183" s="31"/>
+      <x:c r="N183" s="31"/>
+      <x:c r="O183" s="31"/>
+      <x:c r="P183" s="31"/>
+      <x:c r="Q183" s="31"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31"/>
+      <x:c r="B184" s="31"/>
+      <x:c r="C184" s="31"/>
+      <x:c r="D184" s="31"/>
+      <x:c r="E184" s="31"/>
+      <x:c r="F184" s="31"/>
+      <x:c r="G184" s="31"/>
+      <x:c r="H184" s="31"/>
+      <x:c r="I184" s="31"/>
+      <x:c r="J184" s="31"/>
+      <x:c r="K184" s="31"/>
+      <x:c r="L184" s="31"/>
+      <x:c r="M184" s="31"/>
+      <x:c r="N184" s="31"/>
+      <x:c r="O184" s="31"/>
+      <x:c r="P184" s="31"/>
+      <x:c r="Q184" s="31"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31"/>
+      <x:c r="B185" s="31"/>
+      <x:c r="C185" s="31"/>
+      <x:c r="D185" s="31"/>
+      <x:c r="E185" s="31"/>
+      <x:c r="F185" s="31"/>
+      <x:c r="G185" s="31"/>
+      <x:c r="H185" s="31"/>
+      <x:c r="I185" s="31"/>
+      <x:c r="J185" s="31"/>
+      <x:c r="K185" s="31"/>
+      <x:c r="L185" s="31"/>
+      <x:c r="M185" s="31"/>
+      <x:c r="N185" s="31"/>
+      <x:c r="O185" s="31"/>
+      <x:c r="P185" s="31"/>
+      <x:c r="Q185" s="31"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31"/>
+      <x:c r="B186" s="31"/>
+      <x:c r="C186" s="31"/>
+      <x:c r="D186" s="31"/>
+      <x:c r="E186" s="31"/>
+      <x:c r="F186" s="31"/>
+      <x:c r="G186" s="31"/>
+      <x:c r="H186" s="31"/>
+      <x:c r="I186" s="31"/>
+      <x:c r="J186" s="31"/>
+      <x:c r="K186" s="31"/>
+      <x:c r="L186" s="31"/>
+      <x:c r="M186" s="31"/>
+      <x:c r="N186" s="31"/>
+      <x:c r="O186" s="31"/>
+      <x:c r="P186" s="31"/>
+      <x:c r="Q186" s="31"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31"/>
+      <x:c r="B187" s="31"/>
+      <x:c r="C187" s="31"/>
+      <x:c r="D187" s="31"/>
+      <x:c r="E187" s="31"/>
+      <x:c r="F187" s="31"/>
+      <x:c r="G187" s="31"/>
+      <x:c r="H187" s="31"/>
+      <x:c r="I187" s="31"/>
+      <x:c r="J187" s="31"/>
+      <x:c r="K187" s="31"/>
+      <x:c r="L187" s="31"/>
+      <x:c r="M187" s="31"/>
+      <x:c r="N187" s="31"/>
+      <x:c r="O187" s="31"/>
+      <x:c r="P187" s="31"/>
+      <x:c r="Q187" s="31"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31"/>
+      <x:c r="B188" s="31"/>
+      <x:c r="C188" s="31"/>
+      <x:c r="D188" s="31"/>
+      <x:c r="E188" s="31"/>
+      <x:c r="F188" s="31"/>
+      <x:c r="G188" s="31"/>
+      <x:c r="H188" s="31"/>
+      <x:c r="I188" s="31"/>
+      <x:c r="J188" s="31"/>
+      <x:c r="K188" s="31"/>
+      <x:c r="L188" s="31"/>
+      <x:c r="M188" s="31"/>
+      <x:c r="N188" s="31"/>
+      <x:c r="O188" s="31"/>
+      <x:c r="P188" s="31"/>
+      <x:c r="Q188" s="31"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31"/>
+      <x:c r="B189" s="31"/>
+      <x:c r="C189" s="31"/>
+      <x:c r="D189" s="31"/>
+      <x:c r="E189" s="31"/>
+      <x:c r="F189" s="31"/>
+      <x:c r="G189" s="31"/>
+      <x:c r="H189" s="31"/>
+      <x:c r="I189" s="31"/>
+      <x:c r="J189" s="31"/>
+      <x:c r="K189" s="31"/>
+      <x:c r="L189" s="31"/>
+      <x:c r="M189" s="31"/>
+      <x:c r="N189" s="31"/>
+      <x:c r="O189" s="31"/>
+      <x:c r="P189" s="31"/>
+      <x:c r="Q189" s="31"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31"/>
+      <x:c r="B190" s="31"/>
+      <x:c r="C190" s="31"/>
+      <x:c r="D190" s="31"/>
+      <x:c r="E190" s="31"/>
+      <x:c r="F190" s="31"/>
+      <x:c r="G190" s="31"/>
+      <x:c r="H190" s="31"/>
+      <x:c r="I190" s="31"/>
+      <x:c r="J190" s="31"/>
+      <x:c r="K190" s="31"/>
+      <x:c r="L190" s="31"/>
+      <x:c r="M190" s="31"/>
+      <x:c r="N190" s="31"/>
+      <x:c r="O190" s="31"/>
+      <x:c r="P190" s="31"/>
+      <x:c r="Q190" s="31"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="31"/>
+      <x:c r="B191" s="31"/>
+      <x:c r="C191" s="31"/>
+      <x:c r="D191" s="31"/>
+      <x:c r="E191" s="31"/>
+      <x:c r="F191" s="31"/>
+      <x:c r="G191" s="31"/>
+      <x:c r="H191" s="31"/>
+      <x:c r="I191" s="31"/>
+      <x:c r="J191" s="31"/>
+      <x:c r="K191" s="31"/>
+      <x:c r="L191" s="31"/>
+      <x:c r="M191" s="31"/>
+      <x:c r="N191" s="31"/>
+      <x:c r="O191" s="31"/>
+      <x:c r="P191" s="31"/>
+      <x:c r="Q191" s="31"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31"/>
+      <x:c r="B192" s="31"/>
+      <x:c r="C192" s="31"/>
+      <x:c r="D192" s="31"/>
+      <x:c r="E192" s="31"/>
+      <x:c r="F192" s="31"/>
+      <x:c r="G192" s="31"/>
+      <x:c r="H192" s="31"/>
+      <x:c r="I192" s="31"/>
+      <x:c r="J192" s="31"/>
+      <x:c r="K192" s="31"/>
+      <x:c r="L192" s="31"/>
+      <x:c r="M192" s="31"/>
+      <x:c r="N192" s="31"/>
+      <x:c r="O192" s="31"/>
+      <x:c r="P192" s="31"/>
+      <x:c r="Q192" s="31"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31"/>
+      <x:c r="B193" s="31"/>
+      <x:c r="C193" s="31"/>
+      <x:c r="D193" s="31"/>
+      <x:c r="E193" s="31"/>
+      <x:c r="F193" s="31"/>
+      <x:c r="G193" s="31"/>
+      <x:c r="H193" s="31"/>
+      <x:c r="I193" s="31"/>
+      <x:c r="J193" s="31"/>
+      <x:c r="K193" s="31"/>
+      <x:c r="L193" s="31"/>
+      <x:c r="M193" s="31"/>
+      <x:c r="N193" s="31"/>
+      <x:c r="O193" s="31"/>
+      <x:c r="P193" s="31"/>
+      <x:c r="Q193" s="31"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31"/>
+      <x:c r="B194" s="31"/>
+      <x:c r="C194" s="31"/>
+      <x:c r="D194" s="31"/>
+      <x:c r="E194" s="31"/>
+      <x:c r="F194" s="31"/>
+      <x:c r="G194" s="31"/>
+      <x:c r="H194" s="31"/>
+      <x:c r="I194" s="31"/>
+      <x:c r="J194" s="31"/>
+      <x:c r="K194" s="31"/>
+      <x:c r="L194" s="31"/>
+      <x:c r="M194" s="31"/>
+      <x:c r="N194" s="31"/>
+      <x:c r="O194" s="31"/>
+      <x:c r="P194" s="31"/>
+      <x:c r="Q194" s="31"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31"/>
+      <x:c r="B195" s="31"/>
+      <x:c r="C195" s="31"/>
+      <x:c r="D195" s="31"/>
+      <x:c r="E195" s="31"/>
+      <x:c r="F195" s="31"/>
+      <x:c r="G195" s="31"/>
+      <x:c r="H195" s="31"/>
+      <x:c r="I195" s="31"/>
+      <x:c r="J195" s="31"/>
+      <x:c r="K195" s="31"/>
+      <x:c r="L195" s="31"/>
+      <x:c r="M195" s="31"/>
+      <x:c r="N195" s="31"/>
+      <x:c r="O195" s="31"/>
+      <x:c r="P195" s="31"/>
+      <x:c r="Q195" s="31"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="31"/>
+      <x:c r="B196" s="31"/>
+      <x:c r="C196" s="31"/>
+      <x:c r="D196" s="31"/>
+      <x:c r="E196" s="31"/>
+      <x:c r="F196" s="31"/>
+      <x:c r="G196" s="31"/>
+      <x:c r="H196" s="31"/>
+      <x:c r="I196" s="31"/>
+      <x:c r="J196" s="31"/>
+      <x:c r="K196" s="31"/>
+      <x:c r="L196" s="31"/>
+      <x:c r="M196" s="31"/>
+      <x:c r="N196" s="31"/>
+      <x:c r="O196" s="31"/>
+      <x:c r="P196" s="31"/>
+      <x:c r="Q196" s="31"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="31"/>
+      <x:c r="B197" s="31"/>
+      <x:c r="C197" s="31"/>
+      <x:c r="D197" s="31"/>
+      <x:c r="E197" s="31"/>
+      <x:c r="F197" s="31"/>
+      <x:c r="G197" s="31"/>
+      <x:c r="H197" s="31"/>
+      <x:c r="I197" s="31"/>
+      <x:c r="J197" s="31"/>
+      <x:c r="K197" s="31"/>
+      <x:c r="L197" s="31"/>
+      <x:c r="M197" s="31"/>
+      <x:c r="N197" s="31"/>
+      <x:c r="O197" s="31"/>
+      <x:c r="P197" s="31"/>
+      <x:c r="Q197" s="31"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="31"/>
+      <x:c r="B198" s="31"/>
+      <x:c r="C198" s="31"/>
+      <x:c r="D198" s="31"/>
+      <x:c r="E198" s="31"/>
+      <x:c r="F198" s="31"/>
+      <x:c r="G198" s="31"/>
+      <x:c r="H198" s="31"/>
+      <x:c r="I198" s="31"/>
+      <x:c r="J198" s="31"/>
+      <x:c r="K198" s="31"/>
+      <x:c r="L198" s="31"/>
+      <x:c r="M198" s="31"/>
+      <x:c r="N198" s="31"/>
+      <x:c r="O198" s="31"/>
+      <x:c r="P198" s="31"/>
+      <x:c r="Q198" s="31"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="31"/>
+      <x:c r="B199" s="31"/>
+      <x:c r="C199" s="31"/>
+      <x:c r="D199" s="31"/>
+      <x:c r="E199" s="31"/>
+      <x:c r="F199" s="31"/>
+      <x:c r="G199" s="31"/>
+      <x:c r="H199" s="31"/>
+      <x:c r="I199" s="31"/>
+      <x:c r="J199" s="31"/>
+      <x:c r="K199" s="31"/>
+      <x:c r="L199" s="31"/>
+      <x:c r="M199" s="31"/>
+      <x:c r="N199" s="31"/>
+      <x:c r="O199" s="31"/>
+      <x:c r="P199" s="31"/>
+      <x:c r="Q199" s="31"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="31"/>
+      <x:c r="B200" s="31"/>
+      <x:c r="C200" s="31"/>
+      <x:c r="D200" s="31"/>
+      <x:c r="E200" s="31"/>
+      <x:c r="F200" s="31"/>
+      <x:c r="G200" s="31"/>
+      <x:c r="H200" s="31"/>
+      <x:c r="I200" s="31"/>
+      <x:c r="J200" s="31"/>
+      <x:c r="K200" s="31"/>
+      <x:c r="L200" s="31"/>
+      <x:c r="M200" s="31"/>
+      <x:c r="N200" s="31"/>
+      <x:c r="O200" s="31"/>
+      <x:c r="P200" s="31"/>
+      <x:c r="Q200" s="31"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="31"/>
+      <x:c r="B201" s="31"/>
+      <x:c r="C201" s="31"/>
+      <x:c r="D201" s="31"/>
+      <x:c r="E201" s="31"/>
+      <x:c r="F201" s="31"/>
+      <x:c r="G201" s="31"/>
+      <x:c r="H201" s="31"/>
+      <x:c r="I201" s="31"/>
+      <x:c r="J201" s="31"/>
+      <x:c r="K201" s="31"/>
+      <x:c r="L201" s="31"/>
+      <x:c r="M201" s="31"/>
+      <x:c r="N201" s="31"/>
+      <x:c r="O201" s="31"/>
+      <x:c r="P201" s="31"/>
+      <x:c r="Q201" s="31"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="31"/>
+      <x:c r="B202" s="31"/>
+      <x:c r="C202" s="31"/>
+      <x:c r="D202" s="31"/>
+      <x:c r="E202" s="31"/>
+      <x:c r="F202" s="31"/>
+      <x:c r="G202" s="31"/>
+      <x:c r="H202" s="31"/>
+      <x:c r="I202" s="31"/>
+      <x:c r="J202" s="31"/>
+      <x:c r="K202" s="31"/>
+      <x:c r="L202" s="31"/>
+      <x:c r="M202" s="31"/>
+      <x:c r="N202" s="31"/>
+      <x:c r="O202" s="31"/>
+      <x:c r="P202" s="31"/>
+      <x:c r="Q202" s="31"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="31"/>
+      <x:c r="B203" s="31"/>
+      <x:c r="C203" s="31"/>
+      <x:c r="D203" s="31"/>
+      <x:c r="E203" s="31"/>
+      <x:c r="F203" s="31"/>
+      <x:c r="G203" s="31"/>
+      <x:c r="H203" s="31"/>
+      <x:c r="I203" s="31"/>
+      <x:c r="J203" s="31"/>
+      <x:c r="K203" s="31"/>
+      <x:c r="L203" s="31"/>
+      <x:c r="M203" s="31"/>
+      <x:c r="N203" s="31"/>
+      <x:c r="O203" s="31"/>
+      <x:c r="P203" s="31"/>
+      <x:c r="Q203" s="31"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="31"/>
+      <x:c r="B204" s="31"/>
+      <x:c r="C204" s="31"/>
+      <x:c r="D204" s="31"/>
+      <x:c r="E204" s="31"/>
+      <x:c r="F204" s="31"/>
+      <x:c r="G204" s="31"/>
+      <x:c r="H204" s="31"/>
+      <x:c r="I204" s="31"/>
+      <x:c r="J204" s="31"/>
+      <x:c r="K204" s="31"/>
+      <x:c r="L204" s="31"/>
+      <x:c r="M204" s="31"/>
+      <x:c r="N204" s="31"/>
+      <x:c r="O204" s="31"/>
+      <x:c r="P204" s="31"/>
+      <x:c r="Q204" s="31"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="31"/>
+      <x:c r="B205" s="31"/>
+      <x:c r="C205" s="31"/>
+      <x:c r="D205" s="31"/>
+      <x:c r="E205" s="31"/>
+      <x:c r="F205" s="31"/>
+      <x:c r="G205" s="31"/>
+      <x:c r="H205" s="31"/>
+      <x:c r="I205" s="31"/>
+      <x:c r="J205" s="31"/>
+      <x:c r="K205" s="31"/>
+      <x:c r="L205" s="31"/>
+      <x:c r="M205" s="31"/>
+      <x:c r="N205" s="31"/>
+      <x:c r="O205" s="31"/>
+      <x:c r="P205" s="31"/>
+      <x:c r="Q205" s="31"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="31"/>
+      <x:c r="B206" s="31"/>
+      <x:c r="C206" s="31"/>
+      <x:c r="D206" s="31"/>
+      <x:c r="E206" s="31"/>
+      <x:c r="F206" s="31"/>
+      <x:c r="G206" s="31"/>
+      <x:c r="H206" s="31"/>
+      <x:c r="I206" s="31"/>
+      <x:c r="J206" s="31"/>
+      <x:c r="K206" s="31"/>
+      <x:c r="L206" s="31"/>
+      <x:c r="M206" s="31"/>
+      <x:c r="N206" s="31"/>
+      <x:c r="O206" s="31"/>
+      <x:c r="P206" s="31"/>
+      <x:c r="Q206" s="31"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="31"/>
+      <x:c r="B207" s="31"/>
+      <x:c r="C207" s="31"/>
+      <x:c r="D207" s="31"/>
+      <x:c r="E207" s="31"/>
+      <x:c r="F207" s="31"/>
+      <x:c r="G207" s="31"/>
+      <x:c r="H207" s="31"/>
+      <x:c r="I207" s="31"/>
+      <x:c r="J207" s="31"/>
+      <x:c r="K207" s="31"/>
+      <x:c r="L207" s="31"/>
+      <x:c r="M207" s="31"/>
+      <x:c r="N207" s="31"/>
+      <x:c r="O207" s="31"/>
+      <x:c r="P207" s="31"/>
+      <x:c r="Q207" s="31"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="31"/>
+      <x:c r="B208" s="31"/>
+      <x:c r="C208" s="31"/>
+      <x:c r="D208" s="31"/>
+      <x:c r="E208" s="31"/>
+      <x:c r="F208" s="31"/>
+      <x:c r="G208" s="31"/>
+      <x:c r="H208" s="31"/>
+      <x:c r="I208" s="31"/>
+      <x:c r="J208" s="31"/>
+      <x:c r="K208" s="31"/>
+      <x:c r="L208" s="31"/>
+      <x:c r="M208" s="31"/>
+      <x:c r="N208" s="31"/>
+      <x:c r="O208" s="31"/>
+      <x:c r="P208" s="31"/>
+      <x:c r="Q208" s="31"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="31"/>
+      <x:c r="B209" s="31"/>
+      <x:c r="C209" s="31"/>
+      <x:c r="D209" s="31"/>
+      <x:c r="E209" s="31"/>
+      <x:c r="F209" s="31"/>
+      <x:c r="G209" s="31"/>
+      <x:c r="H209" s="31"/>
+      <x:c r="I209" s="31"/>
+      <x:c r="J209" s="31"/>
+      <x:c r="K209" s="31"/>
+      <x:c r="L209" s="31"/>
+      <x:c r="M209" s="31"/>
+      <x:c r="N209" s="31"/>
+      <x:c r="O209" s="31"/>
+      <x:c r="P209" s="31"/>
+      <x:c r="Q209" s="31"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="31"/>
+      <x:c r="B210" s="31"/>
+      <x:c r="C210" s="31"/>
+      <x:c r="D210" s="31"/>
+      <x:c r="E210" s="31"/>
+      <x:c r="F210" s="31"/>
+      <x:c r="G210" s="31"/>
+      <x:c r="H210" s="31"/>
+      <x:c r="I210" s="31"/>
+      <x:c r="J210" s="31"/>
+      <x:c r="K210" s="31"/>
+      <x:c r="L210" s="31"/>
+      <x:c r="M210" s="31"/>
+      <x:c r="N210" s="31"/>
+      <x:c r="O210" s="31"/>
+      <x:c r="P210" s="31"/>
+      <x:c r="Q210" s="31"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="31"/>
+      <x:c r="B211" s="31"/>
+      <x:c r="C211" s="31"/>
+      <x:c r="D211" s="31"/>
+      <x:c r="E211" s="31"/>
+      <x:c r="F211" s="31"/>
+      <x:c r="G211" s="31"/>
+      <x:c r="H211" s="31"/>
+      <x:c r="I211" s="31"/>
+      <x:c r="J211" s="31"/>
+      <x:c r="K211" s="31"/>
+      <x:c r="L211" s="31"/>
+      <x:c r="M211" s="31"/>
+      <x:c r="N211" s="31"/>
+      <x:c r="O211" s="31"/>
+      <x:c r="P211" s="31"/>
+      <x:c r="Q211" s="31"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31"/>
+      <x:c r="B212" s="31"/>
+      <x:c r="C212" s="31"/>
+      <x:c r="D212" s="31"/>
+      <x:c r="E212" s="31"/>
+      <x:c r="F212" s="31"/>
+      <x:c r="G212" s="31"/>
+      <x:c r="H212" s="31"/>
+      <x:c r="I212" s="31"/>
+      <x:c r="J212" s="31"/>
+      <x:c r="K212" s="31"/>
+      <x:c r="L212" s="31"/>
+      <x:c r="M212" s="31"/>
+      <x:c r="N212" s="31"/>
+      <x:c r="O212" s="31"/>
+      <x:c r="P212" s="31"/>
+      <x:c r="Q212" s="31"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31"/>
+      <x:c r="B213" s="31"/>
+      <x:c r="C213" s="31"/>
+      <x:c r="D213" s="31"/>
+      <x:c r="E213" s="31"/>
+      <x:c r="F213" s="31"/>
+      <x:c r="G213" s="31"/>
+      <x:c r="H213" s="31"/>
+      <x:c r="I213" s="31"/>
+      <x:c r="J213" s="31"/>
+      <x:c r="K213" s="31"/>
+      <x:c r="L213" s="31"/>
+      <x:c r="M213" s="31"/>
+      <x:c r="N213" s="31"/>
+      <x:c r="O213" s="31"/>
+      <x:c r="P213" s="31"/>
+      <x:c r="Q213" s="31"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31"/>
+      <x:c r="B214" s="31"/>
+      <x:c r="C214" s="31"/>
+      <x:c r="D214" s="31"/>
+      <x:c r="E214" s="31"/>
+      <x:c r="F214" s="31"/>
+      <x:c r="G214" s="31"/>
+      <x:c r="H214" s="31"/>
+      <x:c r="I214" s="31"/>
+      <x:c r="J214" s="31"/>
+      <x:c r="K214" s="31"/>
+      <x:c r="L214" s="31"/>
+      <x:c r="M214" s="31"/>
+      <x:c r="N214" s="31"/>
+      <x:c r="O214" s="31"/>
+      <x:c r="P214" s="31"/>
+      <x:c r="Q214" s="31"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31"/>
+      <x:c r="B215" s="31"/>
+      <x:c r="C215" s="31"/>
+      <x:c r="D215" s="31"/>
+      <x:c r="E215" s="31"/>
+      <x:c r="F215" s="31"/>
+      <x:c r="G215" s="31"/>
+      <x:c r="H215" s="31"/>
+      <x:c r="I215" s="31"/>
+      <x:c r="J215" s="31"/>
+      <x:c r="K215" s="31"/>
+      <x:c r="L215" s="31"/>
+      <x:c r="M215" s="31"/>
+      <x:c r="N215" s="31"/>
+      <x:c r="O215" s="31"/>
+      <x:c r="P215" s="31"/>
+      <x:c r="Q215" s="31"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="31"/>
+      <x:c r="B216" s="31"/>
+      <x:c r="C216" s="31"/>
+      <x:c r="D216" s="31"/>
+      <x:c r="E216" s="31"/>
+      <x:c r="F216" s="31"/>
+      <x:c r="G216" s="31"/>
+      <x:c r="H216" s="31"/>
+      <x:c r="I216" s="31"/>
+      <x:c r="J216" s="31"/>
+      <x:c r="K216" s="31"/>
+      <x:c r="L216" s="31"/>
+      <x:c r="M216" s="31"/>
+      <x:c r="N216" s="31"/>
+      <x:c r="O216" s="31"/>
+      <x:c r="P216" s="31"/>
+      <x:c r="Q216" s="31"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31"/>
+      <x:c r="B217" s="31"/>
+      <x:c r="C217" s="31"/>
+      <x:c r="D217" s="31"/>
+      <x:c r="E217" s="31"/>
+      <x:c r="F217" s="31"/>
+      <x:c r="G217" s="31"/>
+      <x:c r="H217" s="31"/>
+      <x:c r="I217" s="31"/>
+      <x:c r="J217" s="31"/>
+      <x:c r="K217" s="31"/>
+      <x:c r="L217" s="31"/>
+      <x:c r="M217" s="31"/>
+      <x:c r="N217" s="31"/>
+      <x:c r="O217" s="31"/>
+      <x:c r="P217" s="31"/>
+      <x:c r="Q217" s="31"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31"/>
+      <x:c r="B218" s="31"/>
+      <x:c r="C218" s="31"/>
+      <x:c r="D218" s="31"/>
+      <x:c r="E218" s="31"/>
+      <x:c r="F218" s="31"/>
+      <x:c r="G218" s="31"/>
+      <x:c r="H218" s="31"/>
+      <x:c r="I218" s="31"/>
+      <x:c r="J218" s="31"/>
+      <x:c r="K218" s="31"/>
+      <x:c r="L218" s="31"/>
+      <x:c r="M218" s="31"/>
+      <x:c r="N218" s="31"/>
+      <x:c r="O218" s="31"/>
+      <x:c r="P218" s="31"/>
+      <x:c r="Q218" s="31"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31"/>
+      <x:c r="B219" s="31"/>
+      <x:c r="C219" s="31"/>
+      <x:c r="D219" s="31"/>
+      <x:c r="E219" s="31"/>
+      <x:c r="F219" s="31"/>
+      <x:c r="G219" s="31"/>
+      <x:c r="H219" s="31"/>
+      <x:c r="I219" s="31"/>
+      <x:c r="J219" s="31"/>
+      <x:c r="K219" s="31"/>
+      <x:c r="L219" s="31"/>
+      <x:c r="M219" s="31"/>
+      <x:c r="N219" s="31"/>
+      <x:c r="O219" s="31"/>
+      <x:c r="P219" s="31"/>
+      <x:c r="Q219" s="31"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31"/>
+      <x:c r="B220" s="31"/>
+      <x:c r="C220" s="31"/>
+      <x:c r="D220" s="31"/>
+      <x:c r="E220" s="31"/>
+      <x:c r="F220" s="31"/>
+      <x:c r="G220" s="31"/>
+      <x:c r="H220" s="31"/>
+      <x:c r="I220" s="31"/>
+      <x:c r="J220" s="31"/>
+      <x:c r="K220" s="31"/>
+      <x:c r="L220" s="31"/>
+      <x:c r="M220" s="31"/>
+      <x:c r="N220" s="31"/>
+      <x:c r="O220" s="31"/>
+      <x:c r="P220" s="31"/>
+      <x:c r="Q220" s="31"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31"/>
+      <x:c r="B221" s="31"/>
+      <x:c r="C221" s="31"/>
+      <x:c r="D221" s="31"/>
+      <x:c r="E221" s="31"/>
+      <x:c r="F221" s="31"/>
+      <x:c r="G221" s="31"/>
+      <x:c r="H221" s="31"/>
+      <x:c r="I221" s="31"/>
+      <x:c r="J221" s="31"/>
+      <x:c r="K221" s="31"/>
+      <x:c r="L221" s="31"/>
+      <x:c r="M221" s="31"/>
+      <x:c r="N221" s="31"/>
+      <x:c r="O221" s="31"/>
+      <x:c r="P221" s="31"/>
+      <x:c r="Q221" s="31"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31"/>
+      <x:c r="B222" s="31"/>
+      <x:c r="C222" s="31"/>
+      <x:c r="D222" s="31"/>
+      <x:c r="E222" s="31"/>
+      <x:c r="F222" s="31"/>
+      <x:c r="G222" s="31"/>
+      <x:c r="H222" s="31"/>
+      <x:c r="I222" s="31"/>
+      <x:c r="J222" s="31"/>
+      <x:c r="K222" s="31"/>
+      <x:c r="L222" s="31"/>
+      <x:c r="M222" s="31"/>
+      <x:c r="N222" s="31"/>
+      <x:c r="O222" s="31"/>
+      <x:c r="P222" s="31"/>
+      <x:c r="Q222" s="31"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31"/>
+      <x:c r="B223" s="31"/>
+      <x:c r="C223" s="31"/>
+      <x:c r="D223" s="31"/>
+      <x:c r="E223" s="31"/>
+      <x:c r="F223" s="31"/>
+      <x:c r="G223" s="31"/>
+      <x:c r="H223" s="31"/>
+      <x:c r="I223" s="31"/>
+      <x:c r="J223" s="31"/>
+      <x:c r="K223" s="31"/>
+      <x:c r="L223" s="31"/>
+      <x:c r="M223" s="31"/>
+      <x:c r="N223" s="31"/>
+      <x:c r="O223" s="31"/>
+      <x:c r="P223" s="31"/>
+      <x:c r="Q223" s="31"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31"/>
+      <x:c r="B224" s="31"/>
+      <x:c r="C224" s="31"/>
+      <x:c r="D224" s="31"/>
+      <x:c r="E224" s="31"/>
+      <x:c r="F224" s="31"/>
+      <x:c r="G224" s="31"/>
+      <x:c r="H224" s="31"/>
+      <x:c r="I224" s="31"/>
+      <x:c r="J224" s="31"/>
+      <x:c r="K224" s="31"/>
+      <x:c r="L224" s="31"/>
+      <x:c r="M224" s="31"/>
+      <x:c r="N224" s="31"/>
+      <x:c r="O224" s="31"/>
+      <x:c r="P224" s="31"/>
+      <x:c r="Q224" s="31"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="31"/>
+      <x:c r="B225" s="31"/>
+      <x:c r="C225" s="31"/>
+      <x:c r="D225" s="31"/>
+      <x:c r="E225" s="31"/>
+      <x:c r="F225" s="31"/>
+      <x:c r="G225" s="31"/>
+      <x:c r="H225" s="31"/>
+      <x:c r="I225" s="31"/>
+      <x:c r="J225" s="31"/>
+      <x:c r="K225" s="31"/>
+      <x:c r="L225" s="31"/>
+      <x:c r="M225" s="31"/>
+      <x:c r="N225" s="31"/>
+      <x:c r="O225" s="31"/>
+      <x:c r="P225" s="31"/>
+      <x:c r="Q225" s="31"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31"/>
+      <x:c r="B226" s="31"/>
+      <x:c r="C226" s="31"/>
+      <x:c r="D226" s="31"/>
+      <x:c r="E226" s="31"/>
+      <x:c r="F226" s="31"/>
+      <x:c r="G226" s="31"/>
+      <x:c r="H226" s="31"/>
+      <x:c r="I226" s="31"/>
+      <x:c r="J226" s="31"/>
+      <x:c r="K226" s="31"/>
+      <x:c r="L226" s="31"/>
+      <x:c r="M226" s="31"/>
+      <x:c r="N226" s="31"/>
+      <x:c r="O226" s="31"/>
+      <x:c r="P226" s="31"/>
+      <x:c r="Q226" s="31"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31"/>
+      <x:c r="B227" s="31"/>
+      <x:c r="C227" s="31"/>
+      <x:c r="D227" s="31"/>
+      <x:c r="E227" s="31"/>
+      <x:c r="F227" s="31"/>
+      <x:c r="G227" s="31"/>
+      <x:c r="H227" s="31"/>
+      <x:c r="I227" s="31"/>
+      <x:c r="J227" s="31"/>
+      <x:c r="K227" s="31"/>
+      <x:c r="L227" s="31"/>
+      <x:c r="M227" s="31"/>
+      <x:c r="N227" s="31"/>
+      <x:c r="O227" s="31"/>
+      <x:c r="P227" s="31"/>
+      <x:c r="Q227" s="31"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="31"/>
+      <x:c r="B228" s="31"/>
+      <x:c r="C228" s="31"/>
+      <x:c r="D228" s="31"/>
+      <x:c r="E228" s="31"/>
+      <x:c r="F228" s="31"/>
+      <x:c r="G228" s="31"/>
+      <x:c r="H228" s="31"/>
+      <x:c r="I228" s="31"/>
+      <x:c r="J228" s="31"/>
+      <x:c r="K228" s="31"/>
+      <x:c r="L228" s="31"/>
+      <x:c r="M228" s="31"/>
+      <x:c r="N228" s="31"/>
+      <x:c r="O228" s="31"/>
+      <x:c r="P228" s="31"/>
+      <x:c r="Q228" s="31"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="31"/>
+      <x:c r="B229" s="31"/>
+      <x:c r="C229" s="31"/>
+      <x:c r="D229" s="31"/>
+      <x:c r="E229" s="31"/>
+      <x:c r="F229" s="31"/>
+      <x:c r="G229" s="31"/>
+      <x:c r="H229" s="31"/>
+      <x:c r="I229" s="31"/>
+      <x:c r="J229" s="31"/>
+      <x:c r="K229" s="31"/>
+      <x:c r="L229" s="31"/>
+      <x:c r="M229" s="31"/>
+      <x:c r="N229" s="31"/>
+      <x:c r="O229" s="31"/>
+      <x:c r="P229" s="31"/>
+      <x:c r="Q229" s="31"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="31"/>
+      <x:c r="B230" s="31"/>
+      <x:c r="C230" s="31"/>
+      <x:c r="D230" s="31"/>
+      <x:c r="E230" s="31"/>
+      <x:c r="F230" s="31"/>
+      <x:c r="G230" s="31"/>
+      <x:c r="H230" s="31"/>
+      <x:c r="I230" s="31"/>
+      <x:c r="J230" s="31"/>
+      <x:c r="K230" s="31"/>
+      <x:c r="L230" s="31"/>
+      <x:c r="M230" s="31"/>
+      <x:c r="N230" s="31"/>
+      <x:c r="O230" s="31"/>
+      <x:c r="P230" s="31"/>
+      <x:c r="Q230" s="31"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="31"/>
+      <x:c r="B231" s="31"/>
+      <x:c r="C231" s="31"/>
+      <x:c r="D231" s="31"/>
+      <x:c r="E231" s="31"/>
+      <x:c r="F231" s="31"/>
+      <x:c r="G231" s="31"/>
+      <x:c r="H231" s="31"/>
+      <x:c r="I231" s="31"/>
+      <x:c r="J231" s="31"/>
+      <x:c r="K231" s="31"/>
+      <x:c r="L231" s="31"/>
+      <x:c r="M231" s="31"/>
+      <x:c r="N231" s="31"/>
+      <x:c r="O231" s="31"/>
+      <x:c r="P231" s="31"/>
+      <x:c r="Q231" s="31"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="31"/>
+      <x:c r="B232" s="31"/>
+      <x:c r="C232" s="31"/>
+      <x:c r="D232" s="31"/>
+      <x:c r="E232" s="31"/>
+      <x:c r="F232" s="31"/>
+      <x:c r="G232" s="31"/>
+      <x:c r="H232" s="31"/>
+      <x:c r="I232" s="31"/>
+      <x:c r="J232" s="31"/>
+      <x:c r="K232" s="31"/>
+      <x:c r="L232" s="31"/>
+      <x:c r="M232" s="31"/>
+      <x:c r="N232" s="31"/>
+      <x:c r="O232" s="31"/>
+      <x:c r="P232" s="31"/>
+      <x:c r="Q232" s="31"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="31"/>
+      <x:c r="B233" s="31"/>
+      <x:c r="C233" s="31"/>
+      <x:c r="D233" s="31"/>
+      <x:c r="E233" s="31"/>
+      <x:c r="F233" s="31"/>
+      <x:c r="G233" s="31"/>
+      <x:c r="H233" s="31"/>
+      <x:c r="I233" s="31"/>
+      <x:c r="J233" s="31"/>
+      <x:c r="K233" s="31"/>
+      <x:c r="L233" s="31"/>
+      <x:c r="M233" s="31"/>
+      <x:c r="N233" s="31"/>
+      <x:c r="O233" s="31"/>
+      <x:c r="P233" s="31"/>
+      <x:c r="Q233" s="31"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31"/>
+      <x:c r="B234" s="31"/>
+      <x:c r="C234" s="31"/>
+      <x:c r="D234" s="31"/>
+      <x:c r="E234" s="31"/>
+      <x:c r="F234" s="31"/>
+      <x:c r="G234" s="31"/>
+      <x:c r="H234" s="31"/>
+      <x:c r="I234" s="31"/>
+      <x:c r="J234" s="31"/>
+      <x:c r="K234" s="31"/>
+      <x:c r="L234" s="31"/>
+      <x:c r="M234" s="31"/>
+      <x:c r="N234" s="31"/>
+      <x:c r="O234" s="31"/>
+      <x:c r="P234" s="31"/>
+      <x:c r="Q234" s="31"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="31"/>
+      <x:c r="B235" s="31"/>
+      <x:c r="C235" s="31"/>
+      <x:c r="D235" s="31"/>
+      <x:c r="E235" s="31"/>
+      <x:c r="F235" s="31"/>
+      <x:c r="G235" s="31"/>
+      <x:c r="H235" s="31"/>
+      <x:c r="I235" s="31"/>
+      <x:c r="J235" s="31"/>
+      <x:c r="K235" s="31"/>
+      <x:c r="L235" s="31"/>
+      <x:c r="M235" s="31"/>
+      <x:c r="N235" s="31"/>
+      <x:c r="O235" s="31"/>
+      <x:c r="P235" s="31"/>
+      <x:c r="Q235" s="31"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31"/>
+      <x:c r="B236" s="31"/>
+      <x:c r="C236" s="31"/>
+      <x:c r="D236" s="31"/>
+      <x:c r="E236" s="31"/>
+      <x:c r="F236" s="31"/>
+      <x:c r="G236" s="31"/>
+      <x:c r="H236" s="31"/>
+      <x:c r="I236" s="31"/>
+      <x:c r="J236" s="31"/>
+      <x:c r="K236" s="31"/>
+      <x:c r="L236" s="31"/>
+      <x:c r="M236" s="31"/>
+      <x:c r="N236" s="31"/>
+      <x:c r="O236" s="31"/>
+      <x:c r="P236" s="31"/>
+      <x:c r="Q236" s="31"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31"/>
+      <x:c r="B237" s="31"/>
+      <x:c r="C237" s="31"/>
+      <x:c r="D237" s="31"/>
+      <x:c r="E237" s="31"/>
+      <x:c r="F237" s="31"/>
+      <x:c r="G237" s="31"/>
+      <x:c r="H237" s="31"/>
+      <x:c r="I237" s="31"/>
+      <x:c r="J237" s="31"/>
+      <x:c r="K237" s="31"/>
+      <x:c r="L237" s="31"/>
+      <x:c r="M237" s="31"/>
+      <x:c r="N237" s="31"/>
+      <x:c r="O237" s="31"/>
+      <x:c r="P237" s="31"/>
+      <x:c r="Q237" s="31"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="31"/>
+      <x:c r="B238" s="31"/>
+      <x:c r="C238" s="31"/>
+      <x:c r="D238" s="31"/>
+      <x:c r="E238" s="31"/>
+      <x:c r="F238" s="31"/>
+      <x:c r="G238" s="31"/>
+      <x:c r="H238" s="31"/>
+      <x:c r="I238" s="31"/>
+      <x:c r="J238" s="31"/>
+      <x:c r="K238" s="31"/>
+      <x:c r="L238" s="31"/>
+      <x:c r="M238" s="31"/>
+      <x:c r="N238" s="31"/>
+      <x:c r="O238" s="31"/>
+      <x:c r="P238" s="31"/>
+      <x:c r="Q238" s="31"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="31"/>
+      <x:c r="B239" s="31"/>
+      <x:c r="C239" s="31"/>
+      <x:c r="D239" s="31"/>
+      <x:c r="E239" s="31"/>
+      <x:c r="F239" s="31"/>
+      <x:c r="G239" s="31"/>
+      <x:c r="H239" s="31"/>
+      <x:c r="I239" s="31"/>
+      <x:c r="J239" s="31"/>
+      <x:c r="K239" s="31"/>
+      <x:c r="L239" s="31"/>
+      <x:c r="M239" s="31"/>
+      <x:c r="N239" s="31"/>
+      <x:c r="O239" s="31"/>
+      <x:c r="P239" s="31"/>
+      <x:c r="Q239" s="31"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="31"/>
+      <x:c r="B240" s="31"/>
+      <x:c r="C240" s="31"/>
+      <x:c r="D240" s="31"/>
+      <x:c r="E240" s="31"/>
+      <x:c r="F240" s="31"/>
+      <x:c r="G240" s="31"/>
+      <x:c r="H240" s="31"/>
+      <x:c r="I240" s="31"/>
+      <x:c r="J240" s="31"/>
+      <x:c r="K240" s="31"/>
+      <x:c r="L240" s="31"/>
+      <x:c r="M240" s="31"/>
+      <x:c r="N240" s="31"/>
+      <x:c r="O240" s="31"/>
+      <x:c r="P240" s="31"/>
+      <x:c r="Q240" s="31"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="31"/>
+      <x:c r="B241" s="31"/>
+      <x:c r="C241" s="31"/>
+      <x:c r="D241" s="31"/>
+      <x:c r="E241" s="31"/>
+      <x:c r="F241" s="31"/>
+      <x:c r="G241" s="31"/>
+      <x:c r="H241" s="31"/>
+      <x:c r="I241" s="31"/>
+      <x:c r="J241" s="31"/>
+      <x:c r="K241" s="31"/>
+      <x:c r="L241" s="31"/>
+      <x:c r="M241" s="31"/>
+      <x:c r="N241" s="31"/>
+      <x:c r="O241" s="31"/>
+      <x:c r="P241" s="31"/>
+      <x:c r="Q241" s="31"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="31"/>
+      <x:c r="B242" s="31"/>
+      <x:c r="C242" s="31"/>
+      <x:c r="D242" s="31"/>
+      <x:c r="E242" s="31"/>
+      <x:c r="F242" s="31"/>
+      <x:c r="G242" s="31"/>
+      <x:c r="H242" s="31"/>
+      <x:c r="I242" s="31"/>
+      <x:c r="J242" s="31"/>
+      <x:c r="K242" s="31"/>
+      <x:c r="L242" s="31"/>
+      <x:c r="M242" s="31"/>
+      <x:c r="N242" s="31"/>
+      <x:c r="O242" s="31"/>
+      <x:c r="P242" s="31"/>
+      <x:c r="Q242" s="31"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="31"/>
+      <x:c r="B243" s="31"/>
+      <x:c r="C243" s="31"/>
+      <x:c r="D243" s="31"/>
+      <x:c r="E243" s="31"/>
+      <x:c r="F243" s="31"/>
+      <x:c r="G243" s="31"/>
+      <x:c r="H243" s="31"/>
+      <x:c r="I243" s="31"/>
+      <x:c r="J243" s="31"/>
+      <x:c r="K243" s="31"/>
+      <x:c r="L243" s="31"/>
+      <x:c r="M243" s="31"/>
+      <x:c r="N243" s="31"/>
+      <x:c r="O243" s="31"/>
+      <x:c r="P243" s="31"/>
+      <x:c r="Q243" s="31"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="31"/>
+      <x:c r="B244" s="31"/>
+      <x:c r="C244" s="31"/>
+      <x:c r="D244" s="31"/>
+      <x:c r="E244" s="31"/>
+      <x:c r="F244" s="31"/>
+      <x:c r="G244" s="31"/>
+      <x:c r="H244" s="31"/>
+      <x:c r="I244" s="31"/>
+      <x:c r="J244" s="31"/>
+      <x:c r="K244" s="31"/>
+      <x:c r="L244" s="31"/>
+      <x:c r="M244" s="31"/>
+      <x:c r="N244" s="31"/>
+      <x:c r="O244" s="31"/>
+      <x:c r="P244" s="31"/>
+      <x:c r="Q244" s="31"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="31"/>
+      <x:c r="B245" s="31"/>
+      <x:c r="C245" s="31"/>
+      <x:c r="D245" s="31"/>
+      <x:c r="E245" s="31"/>
+      <x:c r="F245" s="31"/>
+      <x:c r="G245" s="31"/>
+      <x:c r="H245" s="31"/>
+      <x:c r="I245" s="31"/>
+      <x:c r="J245" s="31"/>
+      <x:c r="K245" s="31"/>
+      <x:c r="L245" s="31"/>
+      <x:c r="M245" s="31"/>
+      <x:c r="N245" s="31"/>
+      <x:c r="O245" s="31"/>
+      <x:c r="P245" s="31"/>
+      <x:c r="Q245" s="31"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="31"/>
+      <x:c r="B246" s="31"/>
+      <x:c r="C246" s="31"/>
+      <x:c r="D246" s="31"/>
+      <x:c r="E246" s="31"/>
+      <x:c r="F246" s="31"/>
+      <x:c r="G246" s="31"/>
+      <x:c r="H246" s="31"/>
+      <x:c r="I246" s="31"/>
+      <x:c r="J246" s="31"/>
+      <x:c r="K246" s="31"/>
+      <x:c r="L246" s="31"/>
+      <x:c r="M246" s="31"/>
+      <x:c r="N246" s="31"/>
+      <x:c r="O246" s="31"/>
+      <x:c r="P246" s="31"/>
+      <x:c r="Q246" s="31"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="31"/>
+      <x:c r="B247" s="31"/>
+      <x:c r="C247" s="31"/>
+      <x:c r="D247" s="31"/>
+      <x:c r="E247" s="31"/>
+      <x:c r="F247" s="31"/>
+      <x:c r="G247" s="31"/>
+      <x:c r="H247" s="31"/>
+      <x:c r="I247" s="31"/>
+      <x:c r="J247" s="31"/>
+      <x:c r="K247" s="31"/>
+      <x:c r="L247" s="31"/>
+      <x:c r="M247" s="31"/>
+      <x:c r="N247" s="31"/>
+      <x:c r="O247" s="31"/>
+      <x:c r="P247" s="31"/>
+      <x:c r="Q247" s="31"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="31"/>
+      <x:c r="B248" s="31"/>
+      <x:c r="C248" s="31"/>
+      <x:c r="D248" s="31"/>
+      <x:c r="E248" s="31"/>
+      <x:c r="F248" s="31"/>
+      <x:c r="G248" s="31"/>
+      <x:c r="H248" s="31"/>
+      <x:c r="I248" s="31"/>
+      <x:c r="J248" s="31"/>
+      <x:c r="K248" s="31"/>
+      <x:c r="L248" s="31"/>
+      <x:c r="M248" s="31"/>
+      <x:c r="N248" s="31"/>
+      <x:c r="O248" s="31"/>
+      <x:c r="P248" s="31"/>
+      <x:c r="Q248" s="31"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="31"/>
+      <x:c r="B249" s="31"/>
+      <x:c r="C249" s="31"/>
+      <x:c r="D249" s="31"/>
+      <x:c r="E249" s="31"/>
+      <x:c r="F249" s="31"/>
+      <x:c r="G249" s="31"/>
+      <x:c r="H249" s="31"/>
+      <x:c r="I249" s="31"/>
+      <x:c r="J249" s="31"/>
+      <x:c r="K249" s="31"/>
+      <x:c r="L249" s="31"/>
+      <x:c r="M249" s="31"/>
+      <x:c r="N249" s="31"/>
+      <x:c r="O249" s="31"/>
+      <x:c r="P249" s="31"/>
+      <x:c r="Q249" s="31"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="31"/>
+      <x:c r="B250" s="31"/>
+      <x:c r="C250" s="31"/>
+      <x:c r="D250" s="31"/>
+      <x:c r="E250" s="31"/>
+      <x:c r="F250" s="31"/>
+      <x:c r="G250" s="31"/>
+      <x:c r="H250" s="31"/>
+      <x:c r="I250" s="31"/>
+      <x:c r="J250" s="31"/>
+      <x:c r="K250" s="31"/>
+      <x:c r="L250" s="31"/>
+      <x:c r="M250" s="31"/>
+      <x:c r="N250" s="31"/>
+      <x:c r="O250" s="31"/>
+      <x:c r="P250" s="31"/>
+      <x:c r="Q250" s="31"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="31"/>
+      <x:c r="B251" s="31"/>
+      <x:c r="C251" s="31"/>
+      <x:c r="D251" s="31"/>
+      <x:c r="E251" s="31"/>
+      <x:c r="F251" s="31"/>
+      <x:c r="G251" s="31"/>
+      <x:c r="H251" s="31"/>
+      <x:c r="I251" s="31"/>
+      <x:c r="J251" s="31"/>
+      <x:c r="K251" s="31"/>
+      <x:c r="L251" s="31"/>
+      <x:c r="M251" s="31"/>
+      <x:c r="N251" s="31"/>
+      <x:c r="O251" s="31"/>
+      <x:c r="P251" s="31"/>
+      <x:c r="Q251" s="31"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="31"/>
+      <x:c r="B252" s="31"/>
+      <x:c r="C252" s="31"/>
+      <x:c r="D252" s="31"/>
+      <x:c r="E252" s="31"/>
+      <x:c r="F252" s="31"/>
+      <x:c r="G252" s="31"/>
+      <x:c r="H252" s="31"/>
+      <x:c r="I252" s="31"/>
+      <x:c r="J252" s="31"/>
+      <x:c r="K252" s="31"/>
+      <x:c r="L252" s="31"/>
+      <x:c r="M252" s="31"/>
+      <x:c r="N252" s="31"/>
+      <x:c r="O252" s="31"/>
+      <x:c r="P252" s="31"/>
+      <x:c r="Q252" s="31"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="31"/>
+      <x:c r="B253" s="31"/>
+      <x:c r="C253" s="31"/>
+      <x:c r="D253" s="31"/>
+      <x:c r="E253" s="31"/>
+      <x:c r="F253" s="31"/>
+      <x:c r="G253" s="31"/>
+      <x:c r="H253" s="31"/>
+      <x:c r="I253" s="31"/>
+      <x:c r="J253" s="31"/>
+      <x:c r="K253" s="31"/>
+      <x:c r="L253" s="31"/>
+      <x:c r="M253" s="31"/>
+      <x:c r="N253" s="31"/>
+      <x:c r="O253" s="31"/>
+      <x:c r="P253" s="31"/>
+      <x:c r="Q253" s="31"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="31"/>
+      <x:c r="B254" s="31"/>
+      <x:c r="C254" s="31"/>
+      <x:c r="D254" s="31"/>
+      <x:c r="E254" s="31"/>
+      <x:c r="F254" s="31"/>
+      <x:c r="G254" s="31"/>
+      <x:c r="H254" s="31"/>
+      <x:c r="I254" s="31"/>
+      <x:c r="J254" s="31"/>
+      <x:c r="K254" s="31"/>
+      <x:c r="L254" s="31"/>
+      <x:c r="M254" s="31"/>
+      <x:c r="N254" s="31"/>
+      <x:c r="O254" s="31"/>
+      <x:c r="P254" s="31"/>
+      <x:c r="Q254" s="31"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="31"/>
+      <x:c r="B255" s="31"/>
+      <x:c r="C255" s="31"/>
+      <x:c r="D255" s="31"/>
+      <x:c r="E255" s="31"/>
+      <x:c r="F255" s="31"/>
+      <x:c r="G255" s="31"/>
+      <x:c r="H255" s="31"/>
+      <x:c r="I255" s="31"/>
+      <x:c r="J255" s="31"/>
+      <x:c r="K255" s="31"/>
+      <x:c r="L255" s="31"/>
+      <x:c r="M255" s="31"/>
+      <x:c r="N255" s="31"/>
+      <x:c r="O255" s="31"/>
+      <x:c r="P255" s="31"/>
+      <x:c r="Q255" s="31"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="31"/>
+      <x:c r="B256" s="31"/>
+      <x:c r="C256" s="31"/>
+      <x:c r="D256" s="31"/>
+      <x:c r="E256" s="31"/>
+      <x:c r="F256" s="31"/>
+      <x:c r="G256" s="31"/>
+      <x:c r="H256" s="31"/>
+      <x:c r="I256" s="31"/>
+      <x:c r="J256" s="31"/>
+      <x:c r="K256" s="31"/>
+      <x:c r="L256" s="31"/>
+      <x:c r="M256" s="31"/>
+      <x:c r="N256" s="31"/>
+      <x:c r="O256" s="31"/>
+      <x:c r="P256" s="31"/>
+      <x:c r="Q256" s="31"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="31"/>
+      <x:c r="B257" s="31"/>
+      <x:c r="C257" s="31"/>
+      <x:c r="D257" s="31"/>
+      <x:c r="E257" s="31"/>
+      <x:c r="F257" s="31"/>
+      <x:c r="G257" s="31"/>
+      <x:c r="H257" s="31"/>
+      <x:c r="I257" s="31"/>
+      <x:c r="J257" s="31"/>
+      <x:c r="K257" s="31"/>
+      <x:c r="L257" s="31"/>
+      <x:c r="M257" s="31"/>
+      <x:c r="N257" s="31"/>
+      <x:c r="O257" s="31"/>
+      <x:c r="P257" s="31"/>
+      <x:c r="Q257" s="31"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="31"/>
+      <x:c r="B258" s="31"/>
+      <x:c r="C258" s="31"/>
+      <x:c r="D258" s="31"/>
+      <x:c r="E258" s="31"/>
+      <x:c r="F258" s="31"/>
+      <x:c r="G258" s="31"/>
+      <x:c r="H258" s="31"/>
+      <x:c r="I258" s="31"/>
+      <x:c r="J258" s="31"/>
+      <x:c r="K258" s="31"/>
+      <x:c r="L258" s="31"/>
+      <x:c r="M258" s="31"/>
+      <x:c r="N258" s="31"/>
+      <x:c r="O258" s="31"/>
+      <x:c r="P258" s="31"/>
+      <x:c r="Q258" s="31"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="31"/>
+      <x:c r="B259" s="31"/>
+      <x:c r="C259" s="31"/>
+      <x:c r="D259" s="31"/>
+      <x:c r="E259" s="31"/>
+      <x:c r="F259" s="31"/>
+      <x:c r="G259" s="31"/>
+      <x:c r="H259" s="31"/>
+      <x:c r="I259" s="31"/>
+      <x:c r="J259" s="31"/>
+      <x:c r="K259" s="31"/>
+      <x:c r="L259" s="31"/>
+      <x:c r="M259" s="31"/>
+      <x:c r="N259" s="31"/>
+      <x:c r="O259" s="31"/>
+      <x:c r="P259" s="31"/>
+      <x:c r="Q259" s="31"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="31"/>
+      <x:c r="B260" s="31"/>
+      <x:c r="C260" s="31"/>
+      <x:c r="D260" s="31"/>
+      <x:c r="E260" s="31"/>
+      <x:c r="F260" s="31"/>
+      <x:c r="G260" s="31"/>
+      <x:c r="H260" s="31"/>
+      <x:c r="I260" s="31"/>
+      <x:c r="J260" s="31"/>
+      <x:c r="K260" s="31"/>
+      <x:c r="L260" s="31"/>
+      <x:c r="M260" s="31"/>
+      <x:c r="N260" s="31"/>
+      <x:c r="O260" s="31"/>
+      <x:c r="P260" s="31"/>
+      <x:c r="Q260" s="31"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="31"/>
+      <x:c r="B261" s="31"/>
+      <x:c r="C261" s="31"/>
+      <x:c r="D261" s="31"/>
+      <x:c r="E261" s="31"/>
+      <x:c r="F261" s="31"/>
+      <x:c r="G261" s="31"/>
+      <x:c r="H261" s="31"/>
+      <x:c r="I261" s="31"/>
+      <x:c r="J261" s="31"/>
+      <x:c r="K261" s="31"/>
+      <x:c r="L261" s="31"/>
+      <x:c r="M261" s="31"/>
+      <x:c r="N261" s="31"/>
+      <x:c r="O261" s="31"/>
+      <x:c r="P261" s="31"/>
+      <x:c r="Q261" s="31"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="31"/>
+      <x:c r="B262" s="31"/>
+      <x:c r="C262" s="31"/>
+      <x:c r="D262" s="31"/>
+      <x:c r="E262" s="31"/>
+      <x:c r="F262" s="31"/>
+      <x:c r="G262" s="31"/>
+      <x:c r="H262" s="31"/>
+      <x:c r="I262" s="31"/>
+      <x:c r="J262" s="31"/>
+      <x:c r="K262" s="31"/>
+      <x:c r="L262" s="31"/>
+      <x:c r="M262" s="31"/>
+      <x:c r="N262" s="31"/>
+      <x:c r="O262" s="31"/>
+      <x:c r="P262" s="31"/>
+      <x:c r="Q262" s="31"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="31"/>
+      <x:c r="B263" s="31"/>
+      <x:c r="C263" s="31"/>
+      <x:c r="D263" s="31"/>
+      <x:c r="E263" s="31"/>
+      <x:c r="F263" s="31"/>
+      <x:c r="G263" s="31"/>
+      <x:c r="H263" s="31"/>
+      <x:c r="I263" s="31"/>
+      <x:c r="J263" s="31"/>
+      <x:c r="K263" s="31"/>
+      <x:c r="L263" s="31"/>
+      <x:c r="M263" s="31"/>
+      <x:c r="N263" s="31"/>
+      <x:c r="O263" s="31"/>
+      <x:c r="P263" s="31"/>
+      <x:c r="Q263" s="31"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="31"/>
+      <x:c r="B264" s="31"/>
+      <x:c r="C264" s="31"/>
+      <x:c r="D264" s="31"/>
+      <x:c r="E264" s="31"/>
+      <x:c r="F264" s="31"/>
+      <x:c r="G264" s="31"/>
+      <x:c r="H264" s="31"/>
+      <x:c r="I264" s="31"/>
+      <x:c r="J264" s="31"/>
+      <x:c r="K264" s="31"/>
+      <x:c r="L264" s="31"/>
+      <x:c r="M264" s="31"/>
+      <x:c r="N264" s="31"/>
+      <x:c r="O264" s="31"/>
+      <x:c r="P264" s="31"/>
+      <x:c r="Q264" s="31"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="31"/>
+      <x:c r="B265" s="31"/>
+      <x:c r="C265" s="31"/>
+      <x:c r="D265" s="31"/>
+      <x:c r="E265" s="31"/>
+      <x:c r="F265" s="31"/>
+      <x:c r="G265" s="31"/>
+      <x:c r="H265" s="31"/>
+      <x:c r="I265" s="31"/>
+      <x:c r="J265" s="31"/>
+      <x:c r="K265" s="31"/>
+      <x:c r="L265" s="31"/>
+      <x:c r="M265" s="31"/>
+      <x:c r="N265" s="31"/>
+      <x:c r="O265" s="31"/>
+      <x:c r="P265" s="31"/>
+      <x:c r="Q265" s="31"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="31"/>
+      <x:c r="B266" s="31"/>
+      <x:c r="C266" s="31"/>
+      <x:c r="D266" s="31"/>
+      <x:c r="E266" s="31"/>
+      <x:c r="F266" s="31"/>
+      <x:c r="G266" s="31"/>
+      <x:c r="H266" s="31"/>
+      <x:c r="I266" s="31"/>
+      <x:c r="J266" s="31"/>
+      <x:c r="K266" s="31"/>
+      <x:c r="L266" s="31"/>
+      <x:c r="M266" s="31"/>
+      <x:c r="N266" s="31"/>
+      <x:c r="O266" s="31"/>
+      <x:c r="P266" s="31"/>
+      <x:c r="Q266" s="31"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="31"/>
+      <x:c r="B267" s="31"/>
+      <x:c r="C267" s="31"/>
+      <x:c r="D267" s="31"/>
+      <x:c r="E267" s="31"/>
+      <x:c r="F267" s="31"/>
+      <x:c r="G267" s="31"/>
+      <x:c r="H267" s="31"/>
+      <x:c r="I267" s="31"/>
+      <x:c r="J267" s="31"/>
+      <x:c r="K267" s="31"/>
+      <x:c r="L267" s="31"/>
+      <x:c r="M267" s="31"/>
+      <x:c r="N267" s="31"/>
+      <x:c r="O267" s="31"/>
+      <x:c r="P267" s="31"/>
+      <x:c r="Q267" s="31"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="31"/>
+      <x:c r="B268" s="31"/>
+      <x:c r="C268" s="31"/>
+      <x:c r="D268" s="31"/>
+      <x:c r="E268" s="31"/>
+      <x:c r="F268" s="31"/>
+      <x:c r="G268" s="31"/>
+      <x:c r="H268" s="31"/>
+      <x:c r="I268" s="31"/>
+      <x:c r="J268" s="31"/>
+      <x:c r="K268" s="31"/>
+      <x:c r="L268" s="31"/>
+      <x:c r="M268" s="31"/>
+      <x:c r="N268" s="31"/>
+      <x:c r="O268" s="31"/>
+      <x:c r="P268" s="31"/>
+      <x:c r="Q268" s="31"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="31"/>
+      <x:c r="B269" s="31"/>
+      <x:c r="C269" s="31"/>
+      <x:c r="D269" s="31"/>
+      <x:c r="E269" s="31"/>
+      <x:c r="F269" s="31"/>
+      <x:c r="G269" s="31"/>
+      <x:c r="H269" s="31"/>
+      <x:c r="I269" s="31"/>
+      <x:c r="J269" s="31"/>
+      <x:c r="K269" s="31"/>
+      <x:c r="L269" s="31"/>
+      <x:c r="M269" s="31"/>
+      <x:c r="N269" s="31"/>
+      <x:c r="O269" s="31"/>
+      <x:c r="P269" s="31"/>
+      <x:c r="Q269" s="31"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="31"/>
+      <x:c r="B270" s="31"/>
+      <x:c r="C270" s="31"/>
+      <x:c r="D270" s="31"/>
+      <x:c r="E270" s="31"/>
+      <x:c r="F270" s="31"/>
+      <x:c r="G270" s="31"/>
+      <x:c r="H270" s="31"/>
+      <x:c r="I270" s="31"/>
+      <x:c r="J270" s="31"/>
+      <x:c r="K270" s="31"/>
+      <x:c r="L270" s="31"/>
+      <x:c r="M270" s="31"/>
+      <x:c r="N270" s="31"/>
+      <x:c r="O270" s="31"/>
+      <x:c r="P270" s="31"/>
+      <x:c r="Q270" s="31"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="31"/>
+      <x:c r="B271" s="31"/>
+      <x:c r="C271" s="31"/>
+      <x:c r="D271" s="31"/>
+      <x:c r="E271" s="31"/>
+      <x:c r="F271" s="31"/>
+      <x:c r="G271" s="31"/>
+      <x:c r="H271" s="31"/>
+      <x:c r="I271" s="31"/>
+      <x:c r="J271" s="31"/>
+      <x:c r="K271" s="31"/>
+      <x:c r="L271" s="31"/>
+      <x:c r="M271" s="31"/>
+      <x:c r="N271" s="31"/>
+      <x:c r="O271" s="31"/>
+      <x:c r="P271" s="31"/>
+      <x:c r="Q271" s="31"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="31"/>
+      <x:c r="B272" s="31"/>
+      <x:c r="C272" s="31"/>
+      <x:c r="D272" s="31"/>
+      <x:c r="E272" s="31"/>
+      <x:c r="F272" s="31"/>
+      <x:c r="G272" s="31"/>
+      <x:c r="H272" s="31"/>
+      <x:c r="I272" s="31"/>
+      <x:c r="J272" s="31"/>
+      <x:c r="K272" s="31"/>
+      <x:c r="L272" s="31"/>
+      <x:c r="M272" s="31"/>
+      <x:c r="N272" s="31"/>
+      <x:c r="O272" s="31"/>
+      <x:c r="P272" s="31"/>
+      <x:c r="Q272" s="31"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="31"/>
+      <x:c r="B273" s="31"/>
+      <x:c r="C273" s="31"/>
+      <x:c r="D273" s="31"/>
+      <x:c r="E273" s="31"/>
+      <x:c r="F273" s="31"/>
+      <x:c r="G273" s="31"/>
+      <x:c r="H273" s="31"/>
+      <x:c r="I273" s="31"/>
+      <x:c r="J273" s="31"/>
+      <x:c r="K273" s="31"/>
+      <x:c r="L273" s="31"/>
+      <x:c r="M273" s="31"/>
+      <x:c r="N273" s="31"/>
+      <x:c r="O273" s="31"/>
+      <x:c r="P273" s="31"/>
+      <x:c r="Q273" s="31"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="31"/>
+      <x:c r="B274" s="31"/>
+      <x:c r="C274" s="31"/>
+      <x:c r="D274" s="31"/>
+      <x:c r="E274" s="31"/>
+      <x:c r="F274" s="31"/>
+      <x:c r="G274" s="31"/>
+      <x:c r="H274" s="31"/>
+      <x:c r="I274" s="31"/>
+      <x:c r="J274" s="31"/>
+      <x:c r="K274" s="31"/>
+      <x:c r="L274" s="31"/>
+      <x:c r="M274" s="31"/>
+      <x:c r="N274" s="31"/>
+      <x:c r="O274" s="31"/>
+      <x:c r="P274" s="31"/>
+      <x:c r="Q274" s="31"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="31"/>
+      <x:c r="B275" s="31"/>
+      <x:c r="C275" s="31"/>
+      <x:c r="D275" s="31"/>
+      <x:c r="E275" s="31"/>
+      <x:c r="F275" s="31"/>
+      <x:c r="G275" s="31"/>
+      <x:c r="H275" s="31"/>
+      <x:c r="I275" s="31"/>
+      <x:c r="J275" s="31"/>
+      <x:c r="K275" s="31"/>
+      <x:c r="L275" s="31"/>
+      <x:c r="M275" s="31"/>
+      <x:c r="N275" s="31"/>
+      <x:c r="O275" s="31"/>
+      <x:c r="P275" s="31"/>
+      <x:c r="Q275" s="31"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="31"/>
+      <x:c r="B276" s="31"/>
+      <x:c r="C276" s="31"/>
+      <x:c r="D276" s="31"/>
+      <x:c r="E276" s="31"/>
+      <x:c r="F276" s="31"/>
+      <x:c r="G276" s="31"/>
+      <x:c r="H276" s="31"/>
+      <x:c r="I276" s="31"/>
+      <x:c r="J276" s="31"/>
+      <x:c r="K276" s="31"/>
+      <x:c r="L276" s="31"/>
+      <x:c r="M276" s="31"/>
+      <x:c r="N276" s="31"/>
+      <x:c r="O276" s="31"/>
+      <x:c r="P276" s="31"/>
+      <x:c r="Q276" s="31"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="31"/>
+      <x:c r="B277" s="31"/>
+      <x:c r="C277" s="31"/>
+      <x:c r="D277" s="31"/>
+      <x:c r="E277" s="31"/>
+      <x:c r="F277" s="31"/>
+      <x:c r="G277" s="31"/>
+      <x:c r="H277" s="31"/>
+      <x:c r="I277" s="31"/>
+      <x:c r="J277" s="31"/>
+      <x:c r="K277" s="31"/>
+      <x:c r="L277" s="31"/>
+      <x:c r="M277" s="31"/>
+      <x:c r="N277" s="31"/>
+      <x:c r="O277" s="31"/>
+      <x:c r="P277" s="31"/>
+      <x:c r="Q277" s="31"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="31"/>
+      <x:c r="B278" s="31"/>
+      <x:c r="C278" s="31"/>
+      <x:c r="D278" s="31"/>
+      <x:c r="E278" s="31"/>
+      <x:c r="F278" s="31"/>
+      <x:c r="G278" s="31"/>
+      <x:c r="H278" s="31"/>
+      <x:c r="I278" s="31"/>
+      <x:c r="J278" s="31"/>
+      <x:c r="K278" s="31"/>
+      <x:c r="L278" s="31"/>
+      <x:c r="M278" s="31"/>
+      <x:c r="N278" s="31"/>
+      <x:c r="O278" s="31"/>
+      <x:c r="P278" s="31"/>
+      <x:c r="Q278" s="31"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="31"/>
+      <x:c r="B279" s="31"/>
+      <x:c r="C279" s="31"/>
+      <x:c r="D279" s="31"/>
+      <x:c r="E279" s="31"/>
+      <x:c r="F279" s="31"/>
+      <x:c r="G279" s="31"/>
+      <x:c r="H279" s="31"/>
+      <x:c r="I279" s="31"/>
+      <x:c r="J279" s="31"/>
+      <x:c r="K279" s="31"/>
+      <x:c r="L279" s="31"/>
+      <x:c r="M279" s="31"/>
+      <x:c r="N279" s="31"/>
+      <x:c r="O279" s="31"/>
+      <x:c r="P279" s="31"/>
+      <x:c r="Q279" s="31"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="31"/>
+      <x:c r="B280" s="31"/>
+      <x:c r="C280" s="31"/>
+      <x:c r="D280" s="31"/>
+      <x:c r="E280" s="31"/>
+      <x:c r="F280" s="31"/>
+      <x:c r="G280" s="31"/>
+      <x:c r="H280" s="31"/>
+      <x:c r="I280" s="31"/>
+      <x:c r="J280" s="31"/>
+      <x:c r="K280" s="31"/>
+      <x:c r="L280" s="31"/>
+      <x:c r="M280" s="31"/>
+      <x:c r="N280" s="31"/>
+      <x:c r="O280" s="31"/>
+      <x:c r="P280" s="31"/>
+      <x:c r="Q280" s="31"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="31"/>
+      <x:c r="B281" s="31"/>
+      <x:c r="C281" s="31"/>
+      <x:c r="D281" s="31"/>
+      <x:c r="E281" s="31"/>
+      <x:c r="F281" s="31"/>
+      <x:c r="G281" s="31"/>
+      <x:c r="H281" s="31"/>
+      <x:c r="I281" s="31"/>
+      <x:c r="J281" s="31"/>
+      <x:c r="K281" s="31"/>
+      <x:c r="L281" s="31"/>
+      <x:c r="M281" s="31"/>
+      <x:c r="N281" s="31"/>
+      <x:c r="O281" s="31"/>
+      <x:c r="P281" s="31"/>
+      <x:c r="Q281" s="31"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="31"/>
+      <x:c r="B282" s="31"/>
+      <x:c r="C282" s="31"/>
+      <x:c r="D282" s="31"/>
+      <x:c r="E282" s="31"/>
+      <x:c r="F282" s="31"/>
+      <x:c r="G282" s="31"/>
+      <x:c r="H282" s="31"/>
+      <x:c r="I282" s="31"/>
+      <x:c r="J282" s="31"/>
+      <x:c r="K282" s="31"/>
+      <x:c r="L282" s="31"/>
+      <x:c r="M282" s="31"/>
+      <x:c r="N282" s="31"/>
+      <x:c r="O282" s="31"/>
+      <x:c r="P282" s="31"/>
+      <x:c r="Q282" s="31"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="31"/>
+      <x:c r="B283" s="31"/>
+      <x:c r="C283" s="31"/>
+      <x:c r="D283" s="31"/>
+      <x:c r="E283" s="31"/>
+      <x:c r="F283" s="31"/>
+      <x:c r="G283" s="31"/>
+      <x:c r="H283" s="31"/>
+      <x:c r="I283" s="31"/>
+      <x:c r="J283" s="31"/>
+      <x:c r="K283" s="31"/>
+      <x:c r="L283" s="31"/>
+      <x:c r="M283" s="31"/>
+      <x:c r="N283" s="31"/>
+      <x:c r="O283" s="31"/>
+      <x:c r="P283" s="31"/>
+      <x:c r="Q283" s="31"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="31"/>
+      <x:c r="B284" s="31"/>
+      <x:c r="C284" s="31"/>
+      <x:c r="D284" s="31"/>
+      <x:c r="E284" s="31"/>
+      <x:c r="F284" s="31"/>
+      <x:c r="G284" s="31"/>
+      <x:c r="H284" s="31"/>
+      <x:c r="I284" s="31"/>
+      <x:c r="J284" s="31"/>
+      <x:c r="K284" s="31"/>
+      <x:c r="L284" s="31"/>
+      <x:c r="M284" s="31"/>
+      <x:c r="N284" s="31"/>
+      <x:c r="O284" s="31"/>
+      <x:c r="P284" s="31"/>
+      <x:c r="Q284" s="31"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="31"/>
+      <x:c r="B285" s="31"/>
+      <x:c r="C285" s="31"/>
+      <x:c r="D285" s="31"/>
+      <x:c r="E285" s="31"/>
+      <x:c r="F285" s="31"/>
+      <x:c r="G285" s="31"/>
+      <x:c r="H285" s="31"/>
+      <x:c r="I285" s="31"/>
+      <x:c r="J285" s="31"/>
+      <x:c r="K285" s="31"/>
+      <x:c r="L285" s="31"/>
+      <x:c r="M285" s="31"/>
+      <x:c r="N285" s="31"/>
+      <x:c r="O285" s="31"/>
+      <x:c r="P285" s="31"/>
+      <x:c r="Q285" s="31"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="31"/>
+      <x:c r="B286" s="31"/>
+      <x:c r="C286" s="31"/>
+      <x:c r="D286" s="31"/>
+      <x:c r="E286" s="31"/>
+      <x:c r="F286" s="31"/>
+      <x:c r="G286" s="31"/>
+      <x:c r="H286" s="31"/>
+      <x:c r="I286" s="31"/>
+      <x:c r="J286" s="31"/>
+      <x:c r="K286" s="31"/>
+      <x:c r="L286" s="31"/>
+      <x:c r="M286" s="31"/>
+      <x:c r="N286" s="31"/>
+      <x:c r="O286" s="31"/>
+      <x:c r="P286" s="31"/>
+      <x:c r="Q286" s="31"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="31"/>
+      <x:c r="B287" s="31"/>
+      <x:c r="C287" s="31"/>
+      <x:c r="D287" s="31"/>
+      <x:c r="E287" s="31"/>
+      <x:c r="F287" s="31"/>
+      <x:c r="G287" s="31"/>
+      <x:c r="H287" s="31"/>
+      <x:c r="I287" s="31"/>
+      <x:c r="J287" s="31"/>
+      <x:c r="K287" s="31"/>
+      <x:c r="L287" s="31"/>
+      <x:c r="M287" s="31"/>
+      <x:c r="N287" s="31"/>
+      <x:c r="O287" s="31"/>
+      <x:c r="P287" s="31"/>
+      <x:c r="Q287" s="31"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="31"/>
+      <x:c r="B288" s="31"/>
+      <x:c r="C288" s="31"/>
+      <x:c r="D288" s="31"/>
+      <x:c r="E288" s="31"/>
+      <x:c r="F288" s="31"/>
+      <x:c r="G288" s="31"/>
+      <x:c r="H288" s="31"/>
+      <x:c r="I288" s="31"/>
+      <x:c r="J288" s="31"/>
+      <x:c r="K288" s="31"/>
+      <x:c r="L288" s="31"/>
+      <x:c r="M288" s="31"/>
+      <x:c r="N288" s="31"/>
+      <x:c r="O288" s="31"/>
+      <x:c r="P288" s="31"/>
+      <x:c r="Q288" s="31"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="31"/>
+      <x:c r="B289" s="31"/>
+      <x:c r="C289" s="31"/>
+      <x:c r="D289" s="31"/>
+      <x:c r="E289" s="31"/>
+      <x:c r="F289" s="31"/>
+      <x:c r="G289" s="31"/>
+      <x:c r="H289" s="31"/>
+      <x:c r="I289" s="31"/>
+      <x:c r="J289" s="31"/>
+      <x:c r="K289" s="31"/>
+      <x:c r="L289" s="31"/>
+      <x:c r="M289" s="31"/>
+      <x:c r="N289" s="31"/>
+      <x:c r="O289" s="31"/>
+      <x:c r="P289" s="31"/>
+      <x:c r="Q289" s="31"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="31"/>
+      <x:c r="B290" s="31"/>
+      <x:c r="C290" s="31"/>
+      <x:c r="D290" s="31"/>
+      <x:c r="E290" s="31"/>
+      <x:c r="F290" s="31"/>
+      <x:c r="G290" s="31"/>
+      <x:c r="H290" s="31"/>
+      <x:c r="I290" s="31"/>
+      <x:c r="J290" s="31"/>
+      <x:c r="K290" s="31"/>
+      <x:c r="L290" s="31"/>
+      <x:c r="M290" s="31"/>
+      <x:c r="N290" s="31"/>
+      <x:c r="O290" s="31"/>
+      <x:c r="P290" s="31"/>
+      <x:c r="Q290" s="31"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="31"/>
+      <x:c r="B291" s="31"/>
+      <x:c r="C291" s="31"/>
+      <x:c r="D291" s="31"/>
+      <x:c r="E291" s="31"/>
+      <x:c r="F291" s="31"/>
+      <x:c r="G291" s="31"/>
+      <x:c r="H291" s="31"/>
+      <x:c r="I291" s="31"/>
+      <x:c r="J291" s="31"/>
+      <x:c r="K291" s="31"/>
+      <x:c r="L291" s="31"/>
+      <x:c r="M291" s="31"/>
+      <x:c r="N291" s="31"/>
+      <x:c r="O291" s="31"/>
+      <x:c r="P291" s="31"/>
+      <x:c r="Q291" s="31"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="31"/>
+      <x:c r="B292" s="31"/>
+      <x:c r="C292" s="31"/>
+      <x:c r="D292" s="31"/>
+      <x:c r="E292" s="31"/>
+      <x:c r="F292" s="31"/>
+      <x:c r="G292" s="31"/>
+      <x:c r="H292" s="31"/>
+      <x:c r="I292" s="31"/>
+      <x:c r="J292" s="31"/>
+      <x:c r="K292" s="31"/>
+      <x:c r="L292" s="31"/>
+      <x:c r="M292" s="31"/>
+      <x:c r="N292" s="31"/>
+      <x:c r="O292" s="31"/>
+      <x:c r="P292" s="31"/>
+      <x:c r="Q292" s="31"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="31"/>
+      <x:c r="B293" s="31"/>
+      <x:c r="C293" s="31"/>
+      <x:c r="D293" s="31"/>
+      <x:c r="E293" s="31"/>
+      <x:c r="F293" s="31"/>
+      <x:c r="G293" s="31"/>
+      <x:c r="H293" s="31"/>
+      <x:c r="I293" s="31"/>
+      <x:c r="J293" s="31"/>
+      <x:c r="K293" s="31"/>
+      <x:c r="L293" s="31"/>
+      <x:c r="M293" s="31"/>
+      <x:c r="N293" s="31"/>
+      <x:c r="O293" s="31"/>
+      <x:c r="P293" s="31"/>
+      <x:c r="Q293" s="31"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="31"/>
+      <x:c r="B294" s="31"/>
+      <x:c r="C294" s="31"/>
+      <x:c r="D294" s="31"/>
+      <x:c r="E294" s="31"/>
+      <x:c r="F294" s="31"/>
+      <x:c r="G294" s="31"/>
+      <x:c r="H294" s="31"/>
+      <x:c r="I294" s="31"/>
+      <x:c r="J294" s="31"/>
+      <x:c r="K294" s="31"/>
+      <x:c r="L294" s="31"/>
+      <x:c r="M294" s="31"/>
+      <x:c r="N294" s="31"/>
+      <x:c r="O294" s="31"/>
+      <x:c r="P294" s="31"/>
+      <x:c r="Q294" s="31"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="31"/>
+      <x:c r="B295" s="31"/>
+      <x:c r="C295" s="31"/>
+      <x:c r="D295" s="31"/>
+      <x:c r="E295" s="31"/>
+      <x:c r="F295" s="31"/>
+      <x:c r="G295" s="31"/>
+      <x:c r="H295" s="31"/>
+      <x:c r="I295" s="31"/>
+      <x:c r="J295" s="31"/>
+      <x:c r="K295" s="31"/>
+      <x:c r="L295" s="31"/>
+      <x:c r="M295" s="31"/>
+      <x:c r="N295" s="31"/>
+      <x:c r="O295" s="31"/>
+      <x:c r="P295" s="31"/>
+      <x:c r="Q295" s="31"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="31"/>
+      <x:c r="B296" s="31"/>
+      <x:c r="C296" s="31"/>
+      <x:c r="D296" s="31"/>
+      <x:c r="E296" s="31"/>
+      <x:c r="F296" s="31"/>
+      <x:c r="G296" s="31"/>
+      <x:c r="H296" s="31"/>
+      <x:c r="I296" s="31"/>
+      <x:c r="J296" s="31"/>
+      <x:c r="K296" s="31"/>
+      <x:c r="L296" s="31"/>
+      <x:c r="M296" s="31"/>
+      <x:c r="N296" s="31"/>
+      <x:c r="O296" s="31"/>
+      <x:c r="P296" s="31"/>
+      <x:c r="Q296" s="31"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="31"/>
+      <x:c r="B297" s="31"/>
+      <x:c r="C297" s="31"/>
+      <x:c r="D297" s="31"/>
+      <x:c r="E297" s="31"/>
+      <x:c r="F297" s="31"/>
+      <x:c r="G297" s="31"/>
+      <x:c r="H297" s="31"/>
+      <x:c r="I297" s="31"/>
+      <x:c r="J297" s="31"/>
+      <x:c r="K297" s="31"/>
+      <x:c r="L297" s="31"/>
+      <x:c r="M297" s="31"/>
+      <x:c r="N297" s="31"/>
+      <x:c r="O297" s="31"/>
+      <x:c r="P297" s="31"/>
+      <x:c r="Q297" s="31"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="31"/>
+      <x:c r="B298" s="31"/>
+      <x:c r="C298" s="31"/>
+      <x:c r="D298" s="31"/>
+      <x:c r="E298" s="31"/>
+      <x:c r="F298" s="31"/>
+      <x:c r="G298" s="31"/>
+      <x:c r="H298" s="31"/>
+      <x:c r="I298" s="31"/>
+      <x:c r="J298" s="31"/>
+      <x:c r="K298" s="31"/>
+      <x:c r="L298" s="31"/>
+      <x:c r="M298" s="31"/>
+      <x:c r="N298" s="31"/>
+      <x:c r="O298" s="31"/>
+      <x:c r="P298" s="31"/>
+      <x:c r="Q298" s="31"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="31"/>
+      <x:c r="B299" s="31"/>
+      <x:c r="C299" s="31"/>
+      <x:c r="D299" s="31"/>
+      <x:c r="E299" s="31"/>
+      <x:c r="F299" s="31"/>
+      <x:c r="G299" s="31"/>
+      <x:c r="H299" s="31"/>
+      <x:c r="I299" s="31"/>
+      <x:c r="J299" s="31"/>
+      <x:c r="K299" s="31"/>
+      <x:c r="L299" s="31"/>
+      <x:c r="M299" s="31"/>
+      <x:c r="N299" s="31"/>
+      <x:c r="O299" s="31"/>
+      <x:c r="P299" s="31"/>
+      <x:c r="Q299" s="31"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="31"/>
+      <x:c r="B300" s="31"/>
+      <x:c r="C300" s="31"/>
+      <x:c r="D300" s="31"/>
+      <x:c r="E300" s="31"/>
+      <x:c r="F300" s="31"/>
+      <x:c r="G300" s="31"/>
+      <x:c r="H300" s="31"/>
+      <x:c r="I300" s="31"/>
+      <x:c r="J300" s="31"/>
+      <x:c r="K300" s="31"/>
+      <x:c r="L300" s="31"/>
+      <x:c r="M300" s="31"/>
+      <x:c r="N300" s="31"/>
+      <x:c r="O300" s="31"/>
+      <x:c r="P300" s="31"/>
+      <x:c r="Q300" s="31"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="150.6699981689453" hidden="0" customWidth="1"/>
   </x:cols>
@@ -50034,10 +55933,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41" t="str">
-        <x:v>HRM-Text comparison</x:v>
+        <x:v>Candidate rerank</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
+        <x:v>Saved-output candidate reranking found an 11/17 oracle union across raw/chat candidates, but naive yes/no and answer-likelihood rerankers selected only 6/17. Need a stronger verifier.</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="31"/>
@@ -50057,10 +55956,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="41" t="str">
-        <x:v>Cost</x:v>
+        <x:v>HRM-Text comparison</x:v>
       </x:c>
       <x:c r="B8" s="41" t="str">
-        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
+        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
       </x:c>
       <x:c r="C8" s="31"/>
       <x:c r="D8" s="31"/>
@@ -50080,10 +55979,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="41" t="str">
-        <x:v>Correction</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="B9" s="41" t="str">
-        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
+        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
       </x:c>
       <x:c r="C9" s="31"/>
       <x:c r="D9" s="31"/>
@@ -50103,10 +56002,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="41" t="str">
-        <x:v>Interpretation</x:v>
+        <x:v>Correction</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
-        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
+        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
       </x:c>
       <x:c r="C10" s="31"/>
       <x:c r="D10" s="31"/>
@@ -50126,10 +56025,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="41" t="str">
-        <x:v>Fusion finding</x:v>
+        <x:v>Interpretation</x:v>
       </x:c>
       <x:c r="B11" s="41" t="str">
-        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
+        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
       </x:c>
       <x:c r="C11" s="31"/>
       <x:c r="D11" s="31"/>
@@ -50149,10 +56048,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="41" t="str">
-        <x:v>Next</x:v>
+        <x:v>Fusion finding</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
-        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
       </x:c>
       <x:c r="C12" s="31"/>
       <x:c r="D12" s="31"/>
@@ -50171,8 +56070,12 @@
       <x:c r="Q12" s="31"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="31"/>
-      <x:c r="B13" s="31"/>
+      <x:c r="A13" s="41" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="B13" s="41" t="str">
+        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+      </x:c>
       <x:c r="C13" s="31"/>
       <x:c r="D13" s="31"/>
       <x:c r="E13" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R97639377aca2415c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="Rbc0c7b08881447cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R40a4a6b7cd534859"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rdcdfeb4589164a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="Rd0f97212282e43db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R2e6e5a9e5dcb4fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R1d21cfee99e04b45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" r:id="Rde30761b90f345c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4dcd6149bf304bf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R825037734988427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R7643abae0e2140f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="R6eea31d6cbe74055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R8075d1c4b2e24b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="Rdfa30bcb6d554c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R2b708adf3b1643dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" r:id="R0dfe31c3abcc4e26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -343,7 +343,7 @@
     <x:col min="6" max="6" width="11.65999984741211" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="42.939998626708984" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="47.119998931884766" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -963,29 +963,31 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B20" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C20" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D20" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E20" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
-      </x:c>
-      <x:c r="F20" s="33" t="str"/>
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="F20" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G20" s="35" t="n">
-        <x:v>104.68802758599998</x:v>
+        <x:v>32.70797237700026</x:v>
       </x:c>
       <x:c r="H20" s="35" t="n">
-        <x:v>6.158119269764704</x:v>
+        <x:v>1.9239983751176624</x:v>
       </x:c>
       <x:c r="I20" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
       </x:c>
       <x:c r="J20" s="31"/>
       <x:c r="K20" s="31"/>
@@ -998,29 +1000,31 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B21" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C21" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D21" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E21" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
-      </x:c>
-      <x:c r="F21" s="33" t="str"/>
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="F21" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G21" s="35" t="n">
-        <x:v>338.2124144539998</x:v>
+        <x:v>32.75521304199992</x:v>
       </x:c>
       <x:c r="H21" s="35" t="n">
-        <x:v>19.894847909058814</x:v>
+        <x:v>1.9267772377647014</x:v>
       </x:c>
       <x:c r="I21" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
       </x:c>
       <x:c r="J21" s="31"/>
       <x:c r="K21" s="31"/>
@@ -1032,15 +1036,31 @@
       <x:c r="Q21" s="31"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="31"/>
-      <x:c r="B22" s="31"/>
-      <x:c r="C22" s="31"/>
-      <x:c r="D22" s="31"/>
-      <x:c r="E22" s="36"/>
-      <x:c r="F22" s="31"/>
-      <x:c r="G22" s="37"/>
-      <x:c r="H22" s="37"/>
-      <x:c r="I22" s="31"/>
+      <x:c r="A22" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B22" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C22" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D22" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E22" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F22" s="33" t="str"/>
+      <x:c r="G22" s="35" t="n">
+        <x:v>104.68802758599998</x:v>
+      </x:c>
+      <x:c r="H22" s="35" t="n">
+        <x:v>6.158119269764704</x:v>
+      </x:c>
+      <x:c r="I22" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="J22" s="31"/>
       <x:c r="K22" s="31"/>
       <x:c r="L22" s="31"/>
@@ -1051,15 +1071,31 @@
       <x:c r="Q22" s="31"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="31"/>
-      <x:c r="B23" s="31"/>
-      <x:c r="C23" s="31"/>
-      <x:c r="D23" s="31"/>
-      <x:c r="E23" s="36"/>
-      <x:c r="F23" s="31"/>
-      <x:c r="G23" s="37"/>
-      <x:c r="H23" s="37"/>
-      <x:c r="I23" s="31"/>
+      <x:c r="A23" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B23" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C23" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D23" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E23" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F23" s="33" t="str"/>
+      <x:c r="G23" s="35" t="n">
+        <x:v>338.2124144539998</x:v>
+      </x:c>
+      <x:c r="H23" s="35" t="n">
+        <x:v>19.894847909058814</x:v>
+      </x:c>
+      <x:c r="I23" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="J23" s="31"/>
       <x:c r="K23" s="31"/>
       <x:c r="L23" s="31"/>
@@ -33983,8 +34019,9 @@
     <x:col min="11" max="11" width="4.909999847412109" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="13.869999885559082" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="8.470000267028809" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="141.47000122070312" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="42.939998626708984" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26.260000228881836" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="141.47000122070312" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="47.119998931884766" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -34028,12 +34065,14 @@
         <x:v>Threshold</x:v>
       </x:c>
       <x:c r="N1" s="32" t="str">
+        <x:v>Fusion After</x:v>
+      </x:c>
+      <x:c r="O1" s="32" t="str">
         <x:v>Correct Cases</x:v>
       </x:c>
-      <x:c r="O1" s="32" t="str">
+      <x:c r="P1" s="32" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="P1" s="31"/>
       <x:c r="Q1" s="31"/>
     </x:row>
     <x:row r="2">
@@ -34064,13 +34103,13 @@
       <x:c r="K2" s="33" t="str"/>
       <x:c r="L2" s="33" t="str"/>
       <x:c r="M2" s="33" t="str"/>
-      <x:c r="N2" s="33" t="str">
+      <x:c r="N2" s="33" t="str"/>
+      <x:c r="O2" s="33" t="str">
         <x:v>combinations</x:v>
       </x:c>
-      <x:c r="O2" s="33" t="str">
+      <x:c r="P2" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="P2" s="31"/>
       <x:c r="Q2" s="31"/>
     </x:row>
     <x:row r="3">
@@ -34101,13 +34140,13 @@
       <x:c r="K3" s="33" t="str"/>
       <x:c r="L3" s="33" t="str"/>
       <x:c r="M3" s="33" t="str"/>
-      <x:c r="N3" s="33" t="str">
+      <x:c r="N3" s="33" t="str"/>
+      <x:c r="O3" s="33" t="str">
         <x:v>average, modular_small</x:v>
       </x:c>
-      <x:c r="O3" s="33" t="str">
+      <x:c r="P3" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="P3" s="31"/>
       <x:c r="Q3" s="31"/>
     </x:row>
     <x:row r="4">
@@ -34138,13 +34177,13 @@
       <x:c r="K4" s="33" t="str"/>
       <x:c r="L4" s="33" t="str"/>
       <x:c r="M4" s="33" t="str"/>
-      <x:c r="N4" s="33" t="str">
+      <x:c r="N4" s="33" t="str"/>
+      <x:c r="O4" s="33" t="str">
         <x:v>boxes, probability, sequence, reverse_discount, average, coins</x:v>
       </x:c>
-      <x:c r="O4" s="33" t="str">
+      <x:c r="P4" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="P4" s="31"/>
       <x:c r="Q4" s="31"/>
     </x:row>
     <x:row r="5">
@@ -34175,13 +34214,13 @@
       <x:c r="K5" s="33" t="str"/>
       <x:c r="L5" s="33" t="str"/>
       <x:c r="M5" s="33" t="str"/>
-      <x:c r="N5" s="33" t="str">
+      <x:c r="N5" s="33" t="str"/>
+      <x:c r="O5" s="33" t="str">
         <x:v>markup, boxes, probability, sequence, rectangle, coins</x:v>
       </x:c>
-      <x:c r="O5" s="33" t="str">
+      <x:c r="P5" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="P5" s="31"/>
       <x:c r="Q5" s="31"/>
     </x:row>
     <x:row r="6">
@@ -34218,13 +34257,13 @@
       <x:c r="K6" s="33" t="str"/>
       <x:c r="L6" s="33" t="str"/>
       <x:c r="M6" s="33" t="str"/>
-      <x:c r="N6" s="33" t="str">
+      <x:c r="N6" s="33" t="str"/>
+      <x:c r="O6" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
       </x:c>
-      <x:c r="O6" s="33" t="str">
+      <x:c r="P6" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="P6" s="31"/>
       <x:c r="Q6" s="31"/>
     </x:row>
     <x:row r="7">
@@ -34261,13 +34300,13 @@
       <x:c r="K7" s="33" t="str"/>
       <x:c r="L7" s="33" t="str"/>
       <x:c r="M7" s="33" t="str"/>
-      <x:c r="N7" s="33" t="str">
+      <x:c r="N7" s="33" t="str"/>
+      <x:c r="O7" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small</x:v>
       </x:c>
-      <x:c r="O7" s="33" t="str">
+      <x:c r="P7" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="P7" s="31"/>
       <x:c r="Q7" s="31"/>
     </x:row>
     <x:row r="8">
@@ -34306,13 +34345,13 @@
       </x:c>
       <x:c r="L8" s="33" t="str"/>
       <x:c r="M8" s="33" t="str"/>
-      <x:c r="N8" s="33" t="str">
+      <x:c r="N8" s="33" t="str"/>
+      <x:c r="O8" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, syllogism</x:v>
       </x:c>
-      <x:c r="O8" s="33" t="str">
+      <x:c r="P8" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="P8" s="31"/>
       <x:c r="Q8" s="31"/>
     </x:row>
     <x:row r="9">
@@ -34351,13 +34390,13 @@
       </x:c>
       <x:c r="L9" s="33" t="str"/>
       <x:c r="M9" s="33" t="str"/>
-      <x:c r="N9" s="33" t="str">
+      <x:c r="N9" s="33" t="str"/>
+      <x:c r="O9" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, syllogism</x:v>
       </x:c>
-      <x:c r="O9" s="33" t="str">
+      <x:c r="P9" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="P9" s="31"/>
       <x:c r="Q9" s="31"/>
     </x:row>
     <x:row r="10">
@@ -34400,13 +34439,13 @@
       <x:c r="M10" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N10" s="33" t="str">
+      <x:c r="N10" s="33" t="str"/>
+      <x:c r="O10" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
       </x:c>
-      <x:c r="O10" s="33" t="str">
+      <x:c r="P10" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="P10" s="31"/>
       <x:c r="Q10" s="31"/>
     </x:row>
     <x:row r="11">
@@ -34449,125 +34488,189 @@
       <x:c r="M11" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N11" s="33" t="str">
+      <x:c r="N11" s="33" t="str"/>
+      <x:c r="O11" s="33" t="str">
         <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
       </x:c>
-      <x:c r="O11" s="33" t="str">
+      <x:c r="P11" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="P11" s="31"/>
       <x:c r="Q11" s="31"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B12" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E12" s="34" t="n">
-        <x:v>0.9411764705882353</x:v>
+        <x:v>0.35294117647058826</x:v>
       </x:c>
       <x:c r="F12" s="35" t="n">
-        <x:v>104.68802758599998</x:v>
+        <x:v>32.70797237700026</x:v>
       </x:c>
       <x:c r="G12" s="35" t="n">
-        <x:v>6.158119269764704</x:v>
-      </x:c>
-      <x:c r="H12" s="33" t="str"/>
-      <x:c r="I12" s="33" t="str"/>
-      <x:c r="J12" s="33" t="str"/>
-      <x:c r="K12" s="33" t="str"/>
-      <x:c r="L12" s="33" t="str"/>
-      <x:c r="M12" s="33" t="str"/>
+        <x:v>1.9239983751176624</x:v>
+      </x:c>
+      <x:c r="H12" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I12" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J12" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K12" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L12" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M12" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N12" s="33" t="str">
-        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
+        <x:v>\boxed|Final Answer|final answer</x:v>
       </x:c>
       <x:c r="O12" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="P12" s="31"/>
+        <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="P12" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="Q12" s="31"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B13" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D13" s="33" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E13" s="34" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="F13" s="35" t="n">
+        <x:v>32.75521304199992</x:v>
+      </x:c>
+      <x:c r="G13" s="35" t="n">
+        <x:v>1.9267772377647014</x:v>
+      </x:c>
+      <x:c r="H13" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I13" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J13" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K13" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L13" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M13" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="N13" s="33" t="str">
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O13" s="33" t="str">
+        <x:v>sequence, linear_word, reverse_discount, rectangle, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="P13" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
+      <x:c r="Q13" s="31"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C14" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="n">
         <x:v>0.9411764705882353</x:v>
       </x:c>
-      <x:c r="F13" s="35" t="n">
+      <x:c r="F14" s="35" t="n">
+        <x:v>104.68802758599998</x:v>
+      </x:c>
+      <x:c r="G14" s="35" t="n">
+        <x:v>6.158119269764704</x:v>
+      </x:c>
+      <x:c r="H14" s="33" t="str"/>
+      <x:c r="I14" s="33" t="str"/>
+      <x:c r="J14" s="33" t="str"/>
+      <x:c r="K14" s="33" t="str"/>
+      <x:c r="L14" s="33" t="str"/>
+      <x:c r="M14" s="33" t="str"/>
+      <x:c r="N14" s="33" t="str"/>
+      <x:c r="O14" s="33" t="str">
+        <x:v>algebra, markup, boxes, inclusion, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, modular_small, syllogism</x:v>
+      </x:c>
+      <x:c r="P14" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
+      <x:c r="Q14" s="31"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B15" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C15" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D15" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="34" t="n">
+        <x:v>0.9411764705882353</x:v>
+      </x:c>
+      <x:c r="F15" s="35" t="n">
         <x:v>338.2124144539998</x:v>
       </x:c>
-      <x:c r="G13" s="35" t="n">
+      <x:c r="G15" s="35" t="n">
         <x:v>19.894847909058814</x:v>
       </x:c>
-      <x:c r="H13" s="33" t="str"/>
-      <x:c r="I13" s="33" t="str"/>
-      <x:c r="J13" s="33" t="str"/>
-      <x:c r="K13" s="33" t="str"/>
-      <x:c r="L13" s="33" t="str"/>
-      <x:c r="M13" s="33" t="str"/>
-      <x:c r="N13" s="33" t="str">
+      <x:c r="H15" s="33" t="str"/>
+      <x:c r="I15" s="33" t="str"/>
+      <x:c r="J15" s="33" t="str"/>
+      <x:c r="K15" s="33" t="str"/>
+      <x:c r="L15" s="33" t="str"/>
+      <x:c r="M15" s="33" t="str"/>
+      <x:c r="N15" s="33" t="str"/>
+      <x:c r="O15" s="33" t="str">
         <x:v>algebra, markup, boxes, inclusion, modular, work_rate, probability, sequence, linear_word, reverse_discount, multiples, rectangle, average, combinations, coins, syllogism</x:v>
       </x:c>
-      <x:c r="O13" s="33" t="str">
+      <x:c r="P15" s="33" t="str">
         <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
       </x:c>
-      <x:c r="P13" s="31"/>
-      <x:c r="Q13" s="31"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="31"/>
-      <x:c r="B14" s="31"/>
-      <x:c r="C14" s="31"/>
-      <x:c r="D14" s="31"/>
-      <x:c r="E14" s="36"/>
-      <x:c r="F14" s="37"/>
-      <x:c r="G14" s="37"/>
-      <x:c r="H14" s="31"/>
-      <x:c r="I14" s="31"/>
-      <x:c r="J14" s="31"/>
-      <x:c r="K14" s="31"/>
-      <x:c r="L14" s="31"/>
-      <x:c r="M14" s="31"/>
-      <x:c r="N14" s="31"/>
-      <x:c r="O14" s="31"/>
-      <x:c r="P14" s="31"/>
-      <x:c r="Q14" s="31"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="31"/>
-      <x:c r="B15" s="31"/>
-      <x:c r="C15" s="31"/>
-      <x:c r="D15" s="31"/>
-      <x:c r="E15" s="36"/>
-      <x:c r="F15" s="37"/>
-      <x:c r="G15" s="37"/>
-      <x:c r="H15" s="31"/>
-      <x:c r="I15" s="31"/>
-      <x:c r="J15" s="31"/>
-      <x:c r="K15" s="31"/>
-      <x:c r="L15" s="31"/>
-      <x:c r="M15" s="31"/>
-      <x:c r="N15" s="31"/>
-      <x:c r="O15" s="31"/>
-      <x:c r="P15" s="31"/>
       <x:c r="Q15" s="31"/>
     </x:row>
     <x:row r="16">
@@ -40007,7 +40110,8 @@
     <x:col min="11" max="11" width="4.909999847412109" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="13.869999885559082" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="8.470000267028809" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="42.939998626708984" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="26.260000228881836" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="47.119998931884766" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -40051,9 +40155,11 @@
         <x:v>Threshold</x:v>
       </x:c>
       <x:c r="N1" s="32" t="str">
+        <x:v>Fusion After</x:v>
+      </x:c>
+      <x:c r="O1" s="32" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="O1" s="31"/>
       <x:c r="P1" s="31"/>
       <x:c r="Q1" s="31"/>
     </x:row>
@@ -40085,10 +40191,10 @@
       <x:c r="K2" s="33" t="str"/>
       <x:c r="L2" s="33" t="str"/>
       <x:c r="M2" s="33" t="str"/>
-      <x:c r="N2" s="33" t="str">
+      <x:c r="N2" s="33" t="str"/>
+      <x:c r="O2" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O2" s="31"/>
       <x:c r="P2" s="31"/>
       <x:c r="Q2" s="31"/>
     </x:row>
@@ -40118,10 +40224,10 @@
       <x:c r="K3" s="33" t="str"/>
       <x:c r="L3" s="33" t="str"/>
       <x:c r="M3" s="33" t="str"/>
-      <x:c r="N3" s="33" t="str">
+      <x:c r="N3" s="33" t="str"/>
+      <x:c r="O3" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O3" s="31"/>
       <x:c r="P3" s="31"/>
       <x:c r="Q3" s="31"/>
     </x:row>
@@ -40153,10 +40259,10 @@
       <x:c r="K4" s="33" t="str"/>
       <x:c r="L4" s="33" t="str"/>
       <x:c r="M4" s="33" t="str"/>
-      <x:c r="N4" s="33" t="str">
+      <x:c r="N4" s="33" t="str"/>
+      <x:c r="O4" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O4" s="31"/>
       <x:c r="P4" s="31"/>
       <x:c r="Q4" s="31"/>
     </x:row>
@@ -40188,10 +40294,10 @@
       <x:c r="K5" s="33" t="str"/>
       <x:c r="L5" s="33" t="str"/>
       <x:c r="M5" s="33" t="str"/>
-      <x:c r="N5" s="33" t="str">
+      <x:c r="N5" s="33" t="str"/>
+      <x:c r="O5" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O5" s="31"/>
       <x:c r="P5" s="31"/>
       <x:c r="Q5" s="31"/>
     </x:row>
@@ -40223,10 +40329,10 @@
       <x:c r="K6" s="33" t="str"/>
       <x:c r="L6" s="33" t="str"/>
       <x:c r="M6" s="33" t="str"/>
-      <x:c r="N6" s="33" t="str">
+      <x:c r="N6" s="33" t="str"/>
+      <x:c r="O6" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O6" s="31"/>
       <x:c r="P6" s="31"/>
       <x:c r="Q6" s="31"/>
     </x:row>
@@ -40258,10 +40364,10 @@
       <x:c r="K7" s="33" t="str"/>
       <x:c r="L7" s="33" t="str"/>
       <x:c r="M7" s="33" t="str"/>
-      <x:c r="N7" s="33" t="str">
+      <x:c r="N7" s="33" t="str"/>
+      <x:c r="O7" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O7" s="31"/>
       <x:c r="P7" s="31"/>
       <x:c r="Q7" s="31"/>
     </x:row>
@@ -40293,10 +40399,10 @@
       <x:c r="K8" s="33" t="str"/>
       <x:c r="L8" s="33" t="str"/>
       <x:c r="M8" s="33" t="str"/>
-      <x:c r="N8" s="33" t="str">
+      <x:c r="N8" s="33" t="str"/>
+      <x:c r="O8" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O8" s="31"/>
       <x:c r="P8" s="31"/>
       <x:c r="Q8" s="31"/>
     </x:row>
@@ -40328,10 +40434,10 @@
       <x:c r="K9" s="33" t="str"/>
       <x:c r="L9" s="33" t="str"/>
       <x:c r="M9" s="33" t="str"/>
-      <x:c r="N9" s="33" t="str">
+      <x:c r="N9" s="33" t="str"/>
+      <x:c r="O9" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O9" s="31"/>
       <x:c r="P9" s="31"/>
       <x:c r="Q9" s="31"/>
     </x:row>
@@ -40363,10 +40469,10 @@
       <x:c r="K10" s="33" t="str"/>
       <x:c r="L10" s="33" t="str"/>
       <x:c r="M10" s="33" t="str"/>
-      <x:c r="N10" s="33" t="str">
+      <x:c r="N10" s="33" t="str"/>
+      <x:c r="O10" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O10" s="31"/>
       <x:c r="P10" s="31"/>
       <x:c r="Q10" s="31"/>
     </x:row>
@@ -40398,10 +40504,10 @@
       <x:c r="K11" s="33" t="str"/>
       <x:c r="L11" s="33" t="str"/>
       <x:c r="M11" s="33" t="str"/>
-      <x:c r="N11" s="33" t="str">
+      <x:c r="N11" s="33" t="str"/>
+      <x:c r="O11" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O11" s="31"/>
       <x:c r="P11" s="31"/>
       <x:c r="Q11" s="31"/>
     </x:row>
@@ -40433,10 +40539,10 @@
       <x:c r="K12" s="33" t="str"/>
       <x:c r="L12" s="33" t="str"/>
       <x:c r="M12" s="33" t="str"/>
-      <x:c r="N12" s="33" t="str">
+      <x:c r="N12" s="33" t="str"/>
+      <x:c r="O12" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O12" s="31"/>
       <x:c r="P12" s="31"/>
       <x:c r="Q12" s="31"/>
     </x:row>
@@ -40468,10 +40574,10 @@
       <x:c r="K13" s="33" t="str"/>
       <x:c r="L13" s="33" t="str"/>
       <x:c r="M13" s="33" t="str"/>
-      <x:c r="N13" s="33" t="str">
+      <x:c r="N13" s="33" t="str"/>
+      <x:c r="O13" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O13" s="31"/>
       <x:c r="P13" s="31"/>
       <x:c r="Q13" s="31"/>
     </x:row>
@@ -40503,10 +40609,10 @@
       <x:c r="K14" s="33" t="str"/>
       <x:c r="L14" s="33" t="str"/>
       <x:c r="M14" s="33" t="str"/>
-      <x:c r="N14" s="33" t="str">
+      <x:c r="N14" s="33" t="str"/>
+      <x:c r="O14" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O14" s="31"/>
       <x:c r="P14" s="31"/>
       <x:c r="Q14" s="31"/>
     </x:row>
@@ -40538,10 +40644,10 @@
       <x:c r="K15" s="33" t="str"/>
       <x:c r="L15" s="33" t="str"/>
       <x:c r="M15" s="33" t="str"/>
-      <x:c r="N15" s="33" t="str">
+      <x:c r="N15" s="33" t="str"/>
+      <x:c r="O15" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O15" s="31"/>
       <x:c r="P15" s="31"/>
       <x:c r="Q15" s="31"/>
     </x:row>
@@ -40573,10 +40679,10 @@
       <x:c r="K16" s="33" t="str"/>
       <x:c r="L16" s="33" t="str"/>
       <x:c r="M16" s="33" t="str"/>
-      <x:c r="N16" s="33" t="str">
+      <x:c r="N16" s="33" t="str"/>
+      <x:c r="O16" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O16" s="31"/>
       <x:c r="P16" s="31"/>
       <x:c r="Q16" s="31"/>
     </x:row>
@@ -40608,10 +40714,10 @@
       <x:c r="K17" s="33" t="str"/>
       <x:c r="L17" s="33" t="str"/>
       <x:c r="M17" s="33" t="str"/>
-      <x:c r="N17" s="33" t="str">
+      <x:c r="N17" s="33" t="str"/>
+      <x:c r="O17" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O17" s="31"/>
       <x:c r="P17" s="31"/>
       <x:c r="Q17" s="31"/>
     </x:row>
@@ -40643,10 +40749,10 @@
       <x:c r="K18" s="33" t="str"/>
       <x:c r="L18" s="33" t="str"/>
       <x:c r="M18" s="33" t="str"/>
-      <x:c r="N18" s="33" t="str">
+      <x:c r="N18" s="33" t="str"/>
+      <x:c r="O18" s="33" t="str">
         <x:v>exact_qwen3_0_6b_base.csv</x:v>
       </x:c>
-      <x:c r="O18" s="31"/>
       <x:c r="P18" s="31"/>
       <x:c r="Q18" s="31"/>
     </x:row>
@@ -40678,10 +40784,10 @@
       <x:c r="K19" s="33" t="str"/>
       <x:c r="L19" s="33" t="str"/>
       <x:c r="M19" s="33" t="str"/>
-      <x:c r="N19" s="33" t="str">
+      <x:c r="N19" s="33" t="str"/>
+      <x:c r="O19" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O19" s="31"/>
       <x:c r="P19" s="31"/>
       <x:c r="Q19" s="31"/>
     </x:row>
@@ -40711,10 +40817,10 @@
       <x:c r="K20" s="33" t="str"/>
       <x:c r="L20" s="33" t="str"/>
       <x:c r="M20" s="33" t="str"/>
-      <x:c r="N20" s="33" t="str">
+      <x:c r="N20" s="33" t="str"/>
+      <x:c r="O20" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O20" s="31"/>
       <x:c r="P20" s="31"/>
       <x:c r="Q20" s="31"/>
     </x:row>
@@ -40746,10 +40852,10 @@
       <x:c r="K21" s="33" t="str"/>
       <x:c r="L21" s="33" t="str"/>
       <x:c r="M21" s="33" t="str"/>
-      <x:c r="N21" s="33" t="str">
+      <x:c r="N21" s="33" t="str"/>
+      <x:c r="O21" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O21" s="31"/>
       <x:c r="P21" s="31"/>
       <x:c r="Q21" s="31"/>
     </x:row>
@@ -40781,10 +40887,10 @@
       <x:c r="K22" s="33" t="str"/>
       <x:c r="L22" s="33" t="str"/>
       <x:c r="M22" s="33" t="str"/>
-      <x:c r="N22" s="33" t="str">
+      <x:c r="N22" s="33" t="str"/>
+      <x:c r="O22" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O22" s="31"/>
       <x:c r="P22" s="31"/>
       <x:c r="Q22" s="31"/>
     </x:row>
@@ -40816,10 +40922,10 @@
       <x:c r="K23" s="33" t="str"/>
       <x:c r="L23" s="33" t="str"/>
       <x:c r="M23" s="33" t="str"/>
-      <x:c r="N23" s="33" t="str">
+      <x:c r="N23" s="33" t="str"/>
+      <x:c r="O23" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O23" s="31"/>
       <x:c r="P23" s="31"/>
       <x:c r="Q23" s="31"/>
     </x:row>
@@ -40851,10 +40957,10 @@
       <x:c r="K24" s="33" t="str"/>
       <x:c r="L24" s="33" t="str"/>
       <x:c r="M24" s="33" t="str"/>
-      <x:c r="N24" s="33" t="str">
+      <x:c r="N24" s="33" t="str"/>
+      <x:c r="O24" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O24" s="31"/>
       <x:c r="P24" s="31"/>
       <x:c r="Q24" s="31"/>
     </x:row>
@@ -40886,10 +40992,10 @@
       <x:c r="K25" s="33" t="str"/>
       <x:c r="L25" s="33" t="str"/>
       <x:c r="M25" s="33" t="str"/>
-      <x:c r="N25" s="33" t="str">
+      <x:c r="N25" s="33" t="str"/>
+      <x:c r="O25" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O25" s="31"/>
       <x:c r="P25" s="31"/>
       <x:c r="Q25" s="31"/>
     </x:row>
@@ -40921,10 +41027,10 @@
       <x:c r="K26" s="33" t="str"/>
       <x:c r="L26" s="33" t="str"/>
       <x:c r="M26" s="33" t="str"/>
-      <x:c r="N26" s="33" t="str">
+      <x:c r="N26" s="33" t="str"/>
+      <x:c r="O26" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O26" s="31"/>
       <x:c r="P26" s="31"/>
       <x:c r="Q26" s="31"/>
     </x:row>
@@ -40956,10 +41062,10 @@
       <x:c r="K27" s="33" t="str"/>
       <x:c r="L27" s="33" t="str"/>
       <x:c r="M27" s="33" t="str"/>
-      <x:c r="N27" s="33" t="str">
+      <x:c r="N27" s="33" t="str"/>
+      <x:c r="O27" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O27" s="31"/>
       <x:c r="P27" s="31"/>
       <x:c r="Q27" s="31"/>
     </x:row>
@@ -40991,10 +41097,10 @@
       <x:c r="K28" s="33" t="str"/>
       <x:c r="L28" s="33" t="str"/>
       <x:c r="M28" s="33" t="str"/>
-      <x:c r="N28" s="33" t="str">
+      <x:c r="N28" s="33" t="str"/>
+      <x:c r="O28" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O28" s="31"/>
       <x:c r="P28" s="31"/>
       <x:c r="Q28" s="31"/>
     </x:row>
@@ -41026,10 +41132,10 @@
       <x:c r="K29" s="33" t="str"/>
       <x:c r="L29" s="33" t="str"/>
       <x:c r="M29" s="33" t="str"/>
-      <x:c r="N29" s="33" t="str">
+      <x:c r="N29" s="33" t="str"/>
+      <x:c r="O29" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O29" s="31"/>
       <x:c r="P29" s="31"/>
       <x:c r="Q29" s="31"/>
     </x:row>
@@ -41061,10 +41167,10 @@
       <x:c r="K30" s="33" t="str"/>
       <x:c r="L30" s="33" t="str"/>
       <x:c r="M30" s="33" t="str"/>
-      <x:c r="N30" s="33" t="str">
+      <x:c r="N30" s="33" t="str"/>
+      <x:c r="O30" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O30" s="31"/>
       <x:c r="P30" s="31"/>
       <x:c r="Q30" s="31"/>
     </x:row>
@@ -41096,10 +41202,10 @@
       <x:c r="K31" s="33" t="str"/>
       <x:c r="L31" s="33" t="str"/>
       <x:c r="M31" s="33" t="str"/>
-      <x:c r="N31" s="33" t="str">
+      <x:c r="N31" s="33" t="str"/>
+      <x:c r="O31" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O31" s="31"/>
       <x:c r="P31" s="31"/>
       <x:c r="Q31" s="31"/>
     </x:row>
@@ -41131,10 +41237,10 @@
       <x:c r="K32" s="33" t="str"/>
       <x:c r="L32" s="33" t="str"/>
       <x:c r="M32" s="33" t="str"/>
-      <x:c r="N32" s="33" t="str">
+      <x:c r="N32" s="33" t="str"/>
+      <x:c r="O32" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O32" s="31"/>
       <x:c r="P32" s="31"/>
       <x:c r="Q32" s="31"/>
     </x:row>
@@ -41166,10 +41272,10 @@
       <x:c r="K33" s="33" t="str"/>
       <x:c r="L33" s="33" t="str"/>
       <x:c r="M33" s="33" t="str"/>
-      <x:c r="N33" s="33" t="str">
+      <x:c r="N33" s="33" t="str"/>
+      <x:c r="O33" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O33" s="31"/>
       <x:c r="P33" s="31"/>
       <x:c r="Q33" s="31"/>
     </x:row>
@@ -41201,10 +41307,10 @@
       <x:c r="K34" s="33" t="str"/>
       <x:c r="L34" s="33" t="str"/>
       <x:c r="M34" s="33" t="str"/>
-      <x:c r="N34" s="33" t="str">
+      <x:c r="N34" s="33" t="str"/>
+      <x:c r="O34" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O34" s="31"/>
       <x:c r="P34" s="31"/>
       <x:c r="Q34" s="31"/>
     </x:row>
@@ -41236,10 +41342,10 @@
       <x:c r="K35" s="33" t="str"/>
       <x:c r="L35" s="33" t="str"/>
       <x:c r="M35" s="33" t="str"/>
-      <x:c r="N35" s="33" t="str">
+      <x:c r="N35" s="33" t="str"/>
+      <x:c r="O35" s="33" t="str">
         <x:v>exact_qwen3_0_6b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O35" s="31"/>
       <x:c r="P35" s="31"/>
       <x:c r="Q35" s="31"/>
     </x:row>
@@ -41271,10 +41377,10 @@
       <x:c r="K36" s="33" t="str"/>
       <x:c r="L36" s="33" t="str"/>
       <x:c r="M36" s="33" t="str"/>
-      <x:c r="N36" s="33" t="str">
+      <x:c r="N36" s="33" t="str"/>
+      <x:c r="O36" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O36" s="31"/>
       <x:c r="P36" s="31"/>
       <x:c r="Q36" s="31"/>
     </x:row>
@@ -41306,10 +41412,10 @@
       <x:c r="K37" s="33" t="str"/>
       <x:c r="L37" s="33" t="str"/>
       <x:c r="M37" s="33" t="str"/>
-      <x:c r="N37" s="33" t="str">
+      <x:c r="N37" s="33" t="str"/>
+      <x:c r="O37" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O37" s="31"/>
       <x:c r="P37" s="31"/>
       <x:c r="Q37" s="31"/>
     </x:row>
@@ -41341,10 +41447,10 @@
       <x:c r="K38" s="33" t="str"/>
       <x:c r="L38" s="33" t="str"/>
       <x:c r="M38" s="33" t="str"/>
-      <x:c r="N38" s="33" t="str">
+      <x:c r="N38" s="33" t="str"/>
+      <x:c r="O38" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O38" s="31"/>
       <x:c r="P38" s="31"/>
       <x:c r="Q38" s="31"/>
     </x:row>
@@ -41376,10 +41482,10 @@
       <x:c r="K39" s="33" t="str"/>
       <x:c r="L39" s="33" t="str"/>
       <x:c r="M39" s="33" t="str"/>
-      <x:c r="N39" s="33" t="str">
+      <x:c r="N39" s="33" t="str"/>
+      <x:c r="O39" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O39" s="31"/>
       <x:c r="P39" s="31"/>
       <x:c r="Q39" s="31"/>
     </x:row>
@@ -41411,10 +41517,10 @@
       <x:c r="K40" s="33" t="str"/>
       <x:c r="L40" s="33" t="str"/>
       <x:c r="M40" s="33" t="str"/>
-      <x:c r="N40" s="33" t="str">
+      <x:c r="N40" s="33" t="str"/>
+      <x:c r="O40" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O40" s="31"/>
       <x:c r="P40" s="31"/>
       <x:c r="Q40" s="31"/>
     </x:row>
@@ -41446,10 +41552,10 @@
       <x:c r="K41" s="33" t="str"/>
       <x:c r="L41" s="33" t="str"/>
       <x:c r="M41" s="33" t="str"/>
-      <x:c r="N41" s="33" t="str">
+      <x:c r="N41" s="33" t="str"/>
+      <x:c r="O41" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O41" s="31"/>
       <x:c r="P41" s="31"/>
       <x:c r="Q41" s="31"/>
     </x:row>
@@ -41481,10 +41587,10 @@
       <x:c r="K42" s="33" t="str"/>
       <x:c r="L42" s="33" t="str"/>
       <x:c r="M42" s="33" t="str"/>
-      <x:c r="N42" s="33" t="str">
+      <x:c r="N42" s="33" t="str"/>
+      <x:c r="O42" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O42" s="31"/>
       <x:c r="P42" s="31"/>
       <x:c r="Q42" s="31"/>
     </x:row>
@@ -41516,10 +41622,10 @@
       <x:c r="K43" s="33" t="str"/>
       <x:c r="L43" s="33" t="str"/>
       <x:c r="M43" s="33" t="str"/>
-      <x:c r="N43" s="33" t="str">
+      <x:c r="N43" s="33" t="str"/>
+      <x:c r="O43" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O43" s="31"/>
       <x:c r="P43" s="31"/>
       <x:c r="Q43" s="31"/>
     </x:row>
@@ -41551,10 +41657,10 @@
       <x:c r="K44" s="33" t="str"/>
       <x:c r="L44" s="33" t="str"/>
       <x:c r="M44" s="33" t="str"/>
-      <x:c r="N44" s="33" t="str">
+      <x:c r="N44" s="33" t="str"/>
+      <x:c r="O44" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O44" s="31"/>
       <x:c r="P44" s="31"/>
       <x:c r="Q44" s="31"/>
     </x:row>
@@ -41586,10 +41692,10 @@
       <x:c r="K45" s="33" t="str"/>
       <x:c r="L45" s="33" t="str"/>
       <x:c r="M45" s="33" t="str"/>
-      <x:c r="N45" s="33" t="str">
+      <x:c r="N45" s="33" t="str"/>
+      <x:c r="O45" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O45" s="31"/>
       <x:c r="P45" s="31"/>
       <x:c r="Q45" s="31"/>
     </x:row>
@@ -41621,10 +41727,10 @@
       <x:c r="K46" s="33" t="str"/>
       <x:c r="L46" s="33" t="str"/>
       <x:c r="M46" s="33" t="str"/>
-      <x:c r="N46" s="33" t="str">
+      <x:c r="N46" s="33" t="str"/>
+      <x:c r="O46" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O46" s="31"/>
       <x:c r="P46" s="31"/>
       <x:c r="Q46" s="31"/>
     </x:row>
@@ -41656,10 +41762,10 @@
       <x:c r="K47" s="33" t="str"/>
       <x:c r="L47" s="33" t="str"/>
       <x:c r="M47" s="33" t="str"/>
-      <x:c r="N47" s="33" t="str">
+      <x:c r="N47" s="33" t="str"/>
+      <x:c r="O47" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O47" s="31"/>
       <x:c r="P47" s="31"/>
       <x:c r="Q47" s="31"/>
     </x:row>
@@ -41691,10 +41797,10 @@
       <x:c r="K48" s="33" t="str"/>
       <x:c r="L48" s="33" t="str"/>
       <x:c r="M48" s="33" t="str"/>
-      <x:c r="N48" s="33" t="str">
+      <x:c r="N48" s="33" t="str"/>
+      <x:c r="O48" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O48" s="31"/>
       <x:c r="P48" s="31"/>
       <x:c r="Q48" s="31"/>
     </x:row>
@@ -41726,10 +41832,10 @@
       <x:c r="K49" s="33" t="str"/>
       <x:c r="L49" s="33" t="str"/>
       <x:c r="M49" s="33" t="str"/>
-      <x:c r="N49" s="33" t="str">
+      <x:c r="N49" s="33" t="str"/>
+      <x:c r="O49" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O49" s="31"/>
       <x:c r="P49" s="31"/>
       <x:c r="Q49" s="31"/>
     </x:row>
@@ -41761,10 +41867,10 @@
       <x:c r="K50" s="33" t="str"/>
       <x:c r="L50" s="33" t="str"/>
       <x:c r="M50" s="33" t="str"/>
-      <x:c r="N50" s="33" t="str">
+      <x:c r="N50" s="33" t="str"/>
+      <x:c r="O50" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O50" s="31"/>
       <x:c r="P50" s="31"/>
       <x:c r="Q50" s="31"/>
     </x:row>
@@ -41796,10 +41902,10 @@
       <x:c r="K51" s="33" t="str"/>
       <x:c r="L51" s="33" t="str"/>
       <x:c r="M51" s="33" t="str"/>
-      <x:c r="N51" s="33" t="str">
+      <x:c r="N51" s="33" t="str"/>
+      <x:c r="O51" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O51" s="31"/>
       <x:c r="P51" s="31"/>
       <x:c r="Q51" s="31"/>
     </x:row>
@@ -41831,10 +41937,10 @@
       <x:c r="K52" s="33" t="str"/>
       <x:c r="L52" s="33" t="str"/>
       <x:c r="M52" s="33" t="str"/>
-      <x:c r="N52" s="33" t="str">
+      <x:c r="N52" s="33" t="str"/>
+      <x:c r="O52" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base.csv</x:v>
       </x:c>
-      <x:c r="O52" s="31"/>
       <x:c r="P52" s="31"/>
       <x:c r="Q52" s="31"/>
     </x:row>
@@ -41866,10 +41972,10 @@
       <x:c r="K53" s="33" t="str"/>
       <x:c r="L53" s="33" t="str"/>
       <x:c r="M53" s="33" t="str"/>
-      <x:c r="N53" s="33" t="str">
+      <x:c r="N53" s="33" t="str"/>
+      <x:c r="O53" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O53" s="31"/>
       <x:c r="P53" s="31"/>
       <x:c r="Q53" s="31"/>
     </x:row>
@@ -41901,10 +42007,10 @@
       <x:c r="K54" s="33" t="str"/>
       <x:c r="L54" s="33" t="str"/>
       <x:c r="M54" s="33" t="str"/>
-      <x:c r="N54" s="33" t="str">
+      <x:c r="N54" s="33" t="str"/>
+      <x:c r="O54" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O54" s="31"/>
       <x:c r="P54" s="31"/>
       <x:c r="Q54" s="31"/>
     </x:row>
@@ -41936,10 +42042,10 @@
       <x:c r="K55" s="33" t="str"/>
       <x:c r="L55" s="33" t="str"/>
       <x:c r="M55" s="33" t="str"/>
-      <x:c r="N55" s="33" t="str">
+      <x:c r="N55" s="33" t="str"/>
+      <x:c r="O55" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O55" s="31"/>
       <x:c r="P55" s="31"/>
       <x:c r="Q55" s="31"/>
     </x:row>
@@ -41971,10 +42077,10 @@
       <x:c r="K56" s="33" t="str"/>
       <x:c r="L56" s="33" t="str"/>
       <x:c r="M56" s="33" t="str"/>
-      <x:c r="N56" s="33" t="str">
+      <x:c r="N56" s="33" t="str"/>
+      <x:c r="O56" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O56" s="31"/>
       <x:c r="P56" s="31"/>
       <x:c r="Q56" s="31"/>
     </x:row>
@@ -42006,10 +42112,10 @@
       <x:c r="K57" s="33" t="str"/>
       <x:c r="L57" s="33" t="str"/>
       <x:c r="M57" s="33" t="str"/>
-      <x:c r="N57" s="33" t="str">
+      <x:c r="N57" s="33" t="str"/>
+      <x:c r="O57" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O57" s="31"/>
       <x:c r="P57" s="31"/>
       <x:c r="Q57" s="31"/>
     </x:row>
@@ -42041,10 +42147,10 @@
       <x:c r="K58" s="33" t="str"/>
       <x:c r="L58" s="33" t="str"/>
       <x:c r="M58" s="33" t="str"/>
-      <x:c r="N58" s="33" t="str">
+      <x:c r="N58" s="33" t="str"/>
+      <x:c r="O58" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O58" s="31"/>
       <x:c r="P58" s="31"/>
       <x:c r="Q58" s="31"/>
     </x:row>
@@ -42076,10 +42182,10 @@
       <x:c r="K59" s="33" t="str"/>
       <x:c r="L59" s="33" t="str"/>
       <x:c r="M59" s="33" t="str"/>
-      <x:c r="N59" s="33" t="str">
+      <x:c r="N59" s="33" t="str"/>
+      <x:c r="O59" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O59" s="31"/>
       <x:c r="P59" s="31"/>
       <x:c r="Q59" s="31"/>
     </x:row>
@@ -42111,10 +42217,10 @@
       <x:c r="K60" s="33" t="str"/>
       <x:c r="L60" s="33" t="str"/>
       <x:c r="M60" s="33" t="str"/>
-      <x:c r="N60" s="33" t="str">
+      <x:c r="N60" s="33" t="str"/>
+      <x:c r="O60" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O60" s="31"/>
       <x:c r="P60" s="31"/>
       <x:c r="Q60" s="31"/>
     </x:row>
@@ -42146,10 +42252,10 @@
       <x:c r="K61" s="33" t="str"/>
       <x:c r="L61" s="33" t="str"/>
       <x:c r="M61" s="33" t="str"/>
-      <x:c r="N61" s="33" t="str">
+      <x:c r="N61" s="33" t="str"/>
+      <x:c r="O61" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O61" s="31"/>
       <x:c r="P61" s="31"/>
       <x:c r="Q61" s="31"/>
     </x:row>
@@ -42181,10 +42287,10 @@
       <x:c r="K62" s="33" t="str"/>
       <x:c r="L62" s="33" t="str"/>
       <x:c r="M62" s="33" t="str"/>
-      <x:c r="N62" s="33" t="str">
+      <x:c r="N62" s="33" t="str"/>
+      <x:c r="O62" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O62" s="31"/>
       <x:c r="P62" s="31"/>
       <x:c r="Q62" s="31"/>
     </x:row>
@@ -42216,10 +42322,10 @@
       <x:c r="K63" s="33" t="str"/>
       <x:c r="L63" s="33" t="str"/>
       <x:c r="M63" s="33" t="str"/>
-      <x:c r="N63" s="33" t="str">
+      <x:c r="N63" s="33" t="str"/>
+      <x:c r="O63" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O63" s="31"/>
       <x:c r="P63" s="31"/>
       <x:c r="Q63" s="31"/>
     </x:row>
@@ -42251,10 +42357,10 @@
       <x:c r="K64" s="33" t="str"/>
       <x:c r="L64" s="33" t="str"/>
       <x:c r="M64" s="33" t="str"/>
-      <x:c r="N64" s="33" t="str">
+      <x:c r="N64" s="33" t="str"/>
+      <x:c r="O64" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O64" s="31"/>
       <x:c r="P64" s="31"/>
       <x:c r="Q64" s="31"/>
     </x:row>
@@ -42286,10 +42392,10 @@
       <x:c r="K65" s="33" t="str"/>
       <x:c r="L65" s="33" t="str"/>
       <x:c r="M65" s="33" t="str"/>
-      <x:c r="N65" s="33" t="str">
+      <x:c r="N65" s="33" t="str"/>
+      <x:c r="O65" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O65" s="31"/>
       <x:c r="P65" s="31"/>
       <x:c r="Q65" s="31"/>
     </x:row>
@@ -42321,10 +42427,10 @@
       <x:c r="K66" s="33" t="str"/>
       <x:c r="L66" s="33" t="str"/>
       <x:c r="M66" s="33" t="str"/>
-      <x:c r="N66" s="33" t="str">
+      <x:c r="N66" s="33" t="str"/>
+      <x:c r="O66" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O66" s="31"/>
       <x:c r="P66" s="31"/>
       <x:c r="Q66" s="31"/>
     </x:row>
@@ -42356,10 +42462,10 @@
       <x:c r="K67" s="33" t="str"/>
       <x:c r="L67" s="33" t="str"/>
       <x:c r="M67" s="33" t="str"/>
-      <x:c r="N67" s="33" t="str">
+      <x:c r="N67" s="33" t="str"/>
+      <x:c r="O67" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O67" s="31"/>
       <x:c r="P67" s="31"/>
       <x:c r="Q67" s="31"/>
     </x:row>
@@ -42391,10 +42497,10 @@
       <x:c r="K68" s="33" t="str"/>
       <x:c r="L68" s="33" t="str"/>
       <x:c r="M68" s="33" t="str"/>
-      <x:c r="N68" s="33" t="str">
+      <x:c r="N68" s="33" t="str"/>
+      <x:c r="O68" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O68" s="31"/>
       <x:c r="P68" s="31"/>
       <x:c r="Q68" s="31"/>
     </x:row>
@@ -42426,10 +42532,10 @@
       <x:c r="K69" s="33" t="str"/>
       <x:c r="L69" s="33" t="str"/>
       <x:c r="M69" s="33" t="str"/>
-      <x:c r="N69" s="33" t="str">
+      <x:c r="N69" s="33" t="str"/>
+      <x:c r="O69" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm.csv</x:v>
       </x:c>
-      <x:c r="O69" s="31"/>
       <x:c r="P69" s="31"/>
       <x:c r="Q69" s="31"/>
     </x:row>
@@ -42467,10 +42573,10 @@
       <x:c r="K70" s="33" t="str"/>
       <x:c r="L70" s="33" t="str"/>
       <x:c r="M70" s="33" t="str"/>
-      <x:c r="N70" s="33" t="str">
+      <x:c r="N70" s="33" t="str"/>
+      <x:c r="O70" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O70" s="31"/>
       <x:c r="P70" s="31"/>
       <x:c r="Q70" s="31"/>
     </x:row>
@@ -42508,10 +42614,10 @@
       <x:c r="K71" s="33" t="str"/>
       <x:c r="L71" s="33" t="str"/>
       <x:c r="M71" s="33" t="str"/>
-      <x:c r="N71" s="33" t="str">
+      <x:c r="N71" s="33" t="str"/>
+      <x:c r="O71" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O71" s="31"/>
       <x:c r="P71" s="31"/>
       <x:c r="Q71" s="31"/>
     </x:row>
@@ -42549,10 +42655,10 @@
       <x:c r="K72" s="33" t="str"/>
       <x:c r="L72" s="33" t="str"/>
       <x:c r="M72" s="33" t="str"/>
-      <x:c r="N72" s="33" t="str">
+      <x:c r="N72" s="33" t="str"/>
+      <x:c r="O72" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O72" s="31"/>
       <x:c r="P72" s="31"/>
       <x:c r="Q72" s="31"/>
     </x:row>
@@ -42590,10 +42696,10 @@
       <x:c r="K73" s="33" t="str"/>
       <x:c r="L73" s="33" t="str"/>
       <x:c r="M73" s="33" t="str"/>
-      <x:c r="N73" s="33" t="str">
+      <x:c r="N73" s="33" t="str"/>
+      <x:c r="O73" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O73" s="31"/>
       <x:c r="P73" s="31"/>
       <x:c r="Q73" s="31"/>
     </x:row>
@@ -42631,10 +42737,10 @@
       <x:c r="K74" s="33" t="str"/>
       <x:c r="L74" s="33" t="str"/>
       <x:c r="M74" s="33" t="str"/>
-      <x:c r="N74" s="33" t="str">
+      <x:c r="N74" s="33" t="str"/>
+      <x:c r="O74" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O74" s="31"/>
       <x:c r="P74" s="31"/>
       <x:c r="Q74" s="31"/>
     </x:row>
@@ -42672,10 +42778,10 @@
       <x:c r="K75" s="33" t="str"/>
       <x:c r="L75" s="33" t="str"/>
       <x:c r="M75" s="33" t="str"/>
-      <x:c r="N75" s="33" t="str">
+      <x:c r="N75" s="33" t="str"/>
+      <x:c r="O75" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O75" s="31"/>
       <x:c r="P75" s="31"/>
       <x:c r="Q75" s="31"/>
     </x:row>
@@ -42713,10 +42819,10 @@
       <x:c r="K76" s="33" t="str"/>
       <x:c r="L76" s="33" t="str"/>
       <x:c r="M76" s="33" t="str"/>
-      <x:c r="N76" s="33" t="str">
+      <x:c r="N76" s="33" t="str"/>
+      <x:c r="O76" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O76" s="31"/>
       <x:c r="P76" s="31"/>
       <x:c r="Q76" s="31"/>
     </x:row>
@@ -42754,10 +42860,10 @@
       <x:c r="K77" s="33" t="str"/>
       <x:c r="L77" s="33" t="str"/>
       <x:c r="M77" s="33" t="str"/>
-      <x:c r="N77" s="33" t="str">
+      <x:c r="N77" s="33" t="str"/>
+      <x:c r="O77" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O77" s="31"/>
       <x:c r="P77" s="31"/>
       <x:c r="Q77" s="31"/>
     </x:row>
@@ -42795,10 +42901,10 @@
       <x:c r="K78" s="33" t="str"/>
       <x:c r="L78" s="33" t="str"/>
       <x:c r="M78" s="33" t="str"/>
-      <x:c r="N78" s="33" t="str">
+      <x:c r="N78" s="33" t="str"/>
+      <x:c r="O78" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O78" s="31"/>
       <x:c r="P78" s="31"/>
       <x:c r="Q78" s="31"/>
     </x:row>
@@ -42836,10 +42942,10 @@
       <x:c r="K79" s="33" t="str"/>
       <x:c r="L79" s="33" t="str"/>
       <x:c r="M79" s="33" t="str"/>
-      <x:c r="N79" s="33" t="str">
+      <x:c r="N79" s="33" t="str"/>
+      <x:c r="O79" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O79" s="31"/>
       <x:c r="P79" s="31"/>
       <x:c r="Q79" s="31"/>
     </x:row>
@@ -42877,10 +42983,10 @@
       <x:c r="K80" s="33" t="str"/>
       <x:c r="L80" s="33" t="str"/>
       <x:c r="M80" s="33" t="str"/>
-      <x:c r="N80" s="33" t="str">
+      <x:c r="N80" s="33" t="str"/>
+      <x:c r="O80" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O80" s="31"/>
       <x:c r="P80" s="31"/>
       <x:c r="Q80" s="31"/>
     </x:row>
@@ -42918,10 +43024,10 @@
       <x:c r="K81" s="33" t="str"/>
       <x:c r="L81" s="33" t="str"/>
       <x:c r="M81" s="33" t="str"/>
-      <x:c r="N81" s="33" t="str">
+      <x:c r="N81" s="33" t="str"/>
+      <x:c r="O81" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O81" s="31"/>
       <x:c r="P81" s="31"/>
       <x:c r="Q81" s="31"/>
     </x:row>
@@ -42959,10 +43065,10 @@
       <x:c r="K82" s="33" t="str"/>
       <x:c r="L82" s="33" t="str"/>
       <x:c r="M82" s="33" t="str"/>
-      <x:c r="N82" s="33" t="str">
+      <x:c r="N82" s="33" t="str"/>
+      <x:c r="O82" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O82" s="31"/>
       <x:c r="P82" s="31"/>
       <x:c r="Q82" s="31"/>
     </x:row>
@@ -43000,10 +43106,10 @@
       <x:c r="K83" s="33" t="str"/>
       <x:c r="L83" s="33" t="str"/>
       <x:c r="M83" s="33" t="str"/>
-      <x:c r="N83" s="33" t="str">
+      <x:c r="N83" s="33" t="str"/>
+      <x:c r="O83" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O83" s="31"/>
       <x:c r="P83" s="31"/>
       <x:c r="Q83" s="31"/>
     </x:row>
@@ -43041,10 +43147,10 @@
       <x:c r="K84" s="33" t="str"/>
       <x:c r="L84" s="33" t="str"/>
       <x:c r="M84" s="33" t="str"/>
-      <x:c r="N84" s="33" t="str">
+      <x:c r="N84" s="33" t="str"/>
+      <x:c r="O84" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O84" s="31"/>
       <x:c r="P84" s="31"/>
       <x:c r="Q84" s="31"/>
     </x:row>
@@ -43082,10 +43188,10 @@
       <x:c r="K85" s="33" t="str"/>
       <x:c r="L85" s="33" t="str"/>
       <x:c r="M85" s="33" t="str"/>
-      <x:c r="N85" s="33" t="str">
+      <x:c r="N85" s="33" t="str"/>
+      <x:c r="O85" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O85" s="31"/>
       <x:c r="P85" s="31"/>
       <x:c r="Q85" s="31"/>
     </x:row>
@@ -43123,10 +43229,10 @@
       <x:c r="K86" s="33" t="str"/>
       <x:c r="L86" s="33" t="str"/>
       <x:c r="M86" s="33" t="str"/>
-      <x:c r="N86" s="33" t="str">
+      <x:c r="N86" s="33" t="str"/>
+      <x:c r="O86" s="33" t="str">
         <x:v>exact_qwen3_1_7b_base_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O86" s="31"/>
       <x:c r="P86" s="31"/>
       <x:c r="Q86" s="31"/>
     </x:row>
@@ -43164,10 +43270,10 @@
       <x:c r="K87" s="33" t="str"/>
       <x:c r="L87" s="33" t="str"/>
       <x:c r="M87" s="33" t="str"/>
-      <x:c r="N87" s="33" t="str">
+      <x:c r="N87" s="33" t="str"/>
+      <x:c r="O87" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O87" s="31"/>
       <x:c r="P87" s="31"/>
       <x:c r="Q87" s="31"/>
     </x:row>
@@ -43205,10 +43311,10 @@
       <x:c r="K88" s="33" t="str"/>
       <x:c r="L88" s="33" t="str"/>
       <x:c r="M88" s="33" t="str"/>
-      <x:c r="N88" s="33" t="str">
+      <x:c r="N88" s="33" t="str"/>
+      <x:c r="O88" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O88" s="31"/>
       <x:c r="P88" s="31"/>
       <x:c r="Q88" s="31"/>
     </x:row>
@@ -43246,10 +43352,10 @@
       <x:c r="K89" s="33" t="str"/>
       <x:c r="L89" s="33" t="str"/>
       <x:c r="M89" s="33" t="str"/>
-      <x:c r="N89" s="33" t="str">
+      <x:c r="N89" s="33" t="str"/>
+      <x:c r="O89" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O89" s="31"/>
       <x:c r="P89" s="31"/>
       <x:c r="Q89" s="31"/>
     </x:row>
@@ -43287,10 +43393,10 @@
       <x:c r="K90" s="33" t="str"/>
       <x:c r="L90" s="33" t="str"/>
       <x:c r="M90" s="33" t="str"/>
-      <x:c r="N90" s="33" t="str">
+      <x:c r="N90" s="33" t="str"/>
+      <x:c r="O90" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O90" s="31"/>
       <x:c r="P90" s="31"/>
       <x:c r="Q90" s="31"/>
     </x:row>
@@ -43328,10 +43434,10 @@
       <x:c r="K91" s="33" t="str"/>
       <x:c r="L91" s="33" t="str"/>
       <x:c r="M91" s="33" t="str"/>
-      <x:c r="N91" s="33" t="str">
+      <x:c r="N91" s="33" t="str"/>
+      <x:c r="O91" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O91" s="31"/>
       <x:c r="P91" s="31"/>
       <x:c r="Q91" s="31"/>
     </x:row>
@@ -43369,10 +43475,10 @@
       <x:c r="K92" s="33" t="str"/>
       <x:c r="L92" s="33" t="str"/>
       <x:c r="M92" s="33" t="str"/>
-      <x:c r="N92" s="33" t="str">
+      <x:c r="N92" s="33" t="str"/>
+      <x:c r="O92" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O92" s="31"/>
       <x:c r="P92" s="31"/>
       <x:c r="Q92" s="31"/>
     </x:row>
@@ -43410,10 +43516,10 @@
       <x:c r="K93" s="33" t="str"/>
       <x:c r="L93" s="33" t="str"/>
       <x:c r="M93" s="33" t="str"/>
-      <x:c r="N93" s="33" t="str">
+      <x:c r="N93" s="33" t="str"/>
+      <x:c r="O93" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O93" s="31"/>
       <x:c r="P93" s="31"/>
       <x:c r="Q93" s="31"/>
     </x:row>
@@ -43451,10 +43557,10 @@
       <x:c r="K94" s="33" t="str"/>
       <x:c r="L94" s="33" t="str"/>
       <x:c r="M94" s="33" t="str"/>
-      <x:c r="N94" s="33" t="str">
+      <x:c r="N94" s="33" t="str"/>
+      <x:c r="O94" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O94" s="31"/>
       <x:c r="P94" s="31"/>
       <x:c r="Q94" s="31"/>
     </x:row>
@@ -43492,10 +43598,10 @@
       <x:c r="K95" s="33" t="str"/>
       <x:c r="L95" s="33" t="str"/>
       <x:c r="M95" s="33" t="str"/>
-      <x:c r="N95" s="33" t="str">
+      <x:c r="N95" s="33" t="str"/>
+      <x:c r="O95" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O95" s="31"/>
       <x:c r="P95" s="31"/>
       <x:c r="Q95" s="31"/>
     </x:row>
@@ -43533,10 +43639,10 @@
       <x:c r="K96" s="33" t="str"/>
       <x:c r="L96" s="33" t="str"/>
       <x:c r="M96" s="33" t="str"/>
-      <x:c r="N96" s="33" t="str">
+      <x:c r="N96" s="33" t="str"/>
+      <x:c r="O96" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O96" s="31"/>
       <x:c r="P96" s="31"/>
       <x:c r="Q96" s="31"/>
     </x:row>
@@ -43574,10 +43680,10 @@
       <x:c r="K97" s="33" t="str"/>
       <x:c r="L97" s="33" t="str"/>
       <x:c r="M97" s="33" t="str"/>
-      <x:c r="N97" s="33" t="str">
+      <x:c r="N97" s="33" t="str"/>
+      <x:c r="O97" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O97" s="31"/>
       <x:c r="P97" s="31"/>
       <x:c r="Q97" s="31"/>
     </x:row>
@@ -43615,10 +43721,10 @@
       <x:c r="K98" s="33" t="str"/>
       <x:c r="L98" s="33" t="str"/>
       <x:c r="M98" s="33" t="str"/>
-      <x:c r="N98" s="33" t="str">
+      <x:c r="N98" s="33" t="str"/>
+      <x:c r="O98" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O98" s="31"/>
       <x:c r="P98" s="31"/>
       <x:c r="Q98" s="31"/>
     </x:row>
@@ -43656,10 +43762,10 @@
       <x:c r="K99" s="33" t="str"/>
       <x:c r="L99" s="33" t="str"/>
       <x:c r="M99" s="33" t="str"/>
-      <x:c r="N99" s="33" t="str">
+      <x:c r="N99" s="33" t="str"/>
+      <x:c r="O99" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O99" s="31"/>
       <x:c r="P99" s="31"/>
       <x:c r="Q99" s="31"/>
     </x:row>
@@ -43697,10 +43803,10 @@
       <x:c r="K100" s="33" t="str"/>
       <x:c r="L100" s="33" t="str"/>
       <x:c r="M100" s="33" t="str"/>
-      <x:c r="N100" s="33" t="str">
+      <x:c r="N100" s="33" t="str"/>
+      <x:c r="O100" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O100" s="31"/>
       <x:c r="P100" s="31"/>
       <x:c r="Q100" s="31"/>
     </x:row>
@@ -43738,10 +43844,10 @@
       <x:c r="K101" s="33" t="str"/>
       <x:c r="L101" s="33" t="str"/>
       <x:c r="M101" s="33" t="str"/>
-      <x:c r="N101" s="33" t="str">
+      <x:c r="N101" s="33" t="str"/>
+      <x:c r="O101" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O101" s="31"/>
       <x:c r="P101" s="31"/>
       <x:c r="Q101" s="31"/>
     </x:row>
@@ -43779,10 +43885,10 @@
       <x:c r="K102" s="33" t="str"/>
       <x:c r="L102" s="33" t="str"/>
       <x:c r="M102" s="33" t="str"/>
-      <x:c r="N102" s="33" t="str">
+      <x:c r="N102" s="33" t="str"/>
+      <x:c r="O102" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O102" s="31"/>
       <x:c r="P102" s="31"/>
       <x:c r="Q102" s="31"/>
     </x:row>
@@ -43820,10 +43926,10 @@
       <x:c r="K103" s="33" t="str"/>
       <x:c r="L103" s="33" t="str"/>
       <x:c r="M103" s="33" t="str"/>
-      <x:c r="N103" s="33" t="str">
+      <x:c r="N103" s="33" t="str"/>
+      <x:c r="O103" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed.csv</x:v>
       </x:c>
-      <x:c r="O103" s="31"/>
       <x:c r="P103" s="31"/>
       <x:c r="Q103" s="31"/>
     </x:row>
@@ -43863,10 +43969,10 @@
       </x:c>
       <x:c r="L104" s="33" t="str"/>
       <x:c r="M104" s="33" t="str"/>
-      <x:c r="N104" s="33" t="str">
+      <x:c r="N104" s="33" t="str"/>
+      <x:c r="O104" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O104" s="31"/>
       <x:c r="P104" s="31"/>
       <x:c r="Q104" s="31"/>
     </x:row>
@@ -43906,10 +44012,10 @@
       </x:c>
       <x:c r="L105" s="33" t="str"/>
       <x:c r="M105" s="33" t="str"/>
-      <x:c r="N105" s="33" t="str">
+      <x:c r="N105" s="33" t="str"/>
+      <x:c r="O105" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O105" s="31"/>
       <x:c r="P105" s="31"/>
       <x:c r="Q105" s="31"/>
     </x:row>
@@ -43949,10 +44055,10 @@
       </x:c>
       <x:c r="L106" s="33" t="str"/>
       <x:c r="M106" s="33" t="str"/>
-      <x:c r="N106" s="33" t="str">
+      <x:c r="N106" s="33" t="str"/>
+      <x:c r="O106" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O106" s="31"/>
       <x:c r="P106" s="31"/>
       <x:c r="Q106" s="31"/>
     </x:row>
@@ -43992,10 +44098,10 @@
       </x:c>
       <x:c r="L107" s="33" t="str"/>
       <x:c r="M107" s="33" t="str"/>
-      <x:c r="N107" s="33" t="str">
+      <x:c r="N107" s="33" t="str"/>
+      <x:c r="O107" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O107" s="31"/>
       <x:c r="P107" s="31"/>
       <x:c r="Q107" s="31"/>
     </x:row>
@@ -44035,10 +44141,10 @@
       </x:c>
       <x:c r="L108" s="33" t="str"/>
       <x:c r="M108" s="33" t="str"/>
-      <x:c r="N108" s="33" t="str">
+      <x:c r="N108" s="33" t="str"/>
+      <x:c r="O108" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O108" s="31"/>
       <x:c r="P108" s="31"/>
       <x:c r="Q108" s="31"/>
     </x:row>
@@ -44078,10 +44184,10 @@
       </x:c>
       <x:c r="L109" s="33" t="str"/>
       <x:c r="M109" s="33" t="str"/>
-      <x:c r="N109" s="33" t="str">
+      <x:c r="N109" s="33" t="str"/>
+      <x:c r="O109" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O109" s="31"/>
       <x:c r="P109" s="31"/>
       <x:c r="Q109" s="31"/>
     </x:row>
@@ -44121,10 +44227,10 @@
       </x:c>
       <x:c r="L110" s="33" t="str"/>
       <x:c r="M110" s="33" t="str"/>
-      <x:c r="N110" s="33" t="str">
+      <x:c r="N110" s="33" t="str"/>
+      <x:c r="O110" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O110" s="31"/>
       <x:c r="P110" s="31"/>
       <x:c r="Q110" s="31"/>
     </x:row>
@@ -44164,10 +44270,10 @@
       </x:c>
       <x:c r="L111" s="33" t="str"/>
       <x:c r="M111" s="33" t="str"/>
-      <x:c r="N111" s="33" t="str">
+      <x:c r="N111" s="33" t="str"/>
+      <x:c r="O111" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O111" s="31"/>
       <x:c r="P111" s="31"/>
       <x:c r="Q111" s="31"/>
     </x:row>
@@ -44207,10 +44313,10 @@
       </x:c>
       <x:c r="L112" s="33" t="str"/>
       <x:c r="M112" s="33" t="str"/>
-      <x:c r="N112" s="33" t="str">
+      <x:c r="N112" s="33" t="str"/>
+      <x:c r="O112" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O112" s="31"/>
       <x:c r="P112" s="31"/>
       <x:c r="Q112" s="31"/>
     </x:row>
@@ -44250,10 +44356,10 @@
       </x:c>
       <x:c r="L113" s="33" t="str"/>
       <x:c r="M113" s="33" t="str"/>
-      <x:c r="N113" s="33" t="str">
+      <x:c r="N113" s="33" t="str"/>
+      <x:c r="O113" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O113" s="31"/>
       <x:c r="P113" s="31"/>
       <x:c r="Q113" s="31"/>
     </x:row>
@@ -44293,10 +44399,10 @@
       </x:c>
       <x:c r="L114" s="33" t="str"/>
       <x:c r="M114" s="33" t="str"/>
-      <x:c r="N114" s="33" t="str">
+      <x:c r="N114" s="33" t="str"/>
+      <x:c r="O114" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O114" s="31"/>
       <x:c r="P114" s="31"/>
       <x:c r="Q114" s="31"/>
     </x:row>
@@ -44336,10 +44442,10 @@
       </x:c>
       <x:c r="L115" s="33" t="str"/>
       <x:c r="M115" s="33" t="str"/>
-      <x:c r="N115" s="33" t="str">
+      <x:c r="N115" s="33" t="str"/>
+      <x:c r="O115" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O115" s="31"/>
       <x:c r="P115" s="31"/>
       <x:c r="Q115" s="31"/>
     </x:row>
@@ -44379,10 +44485,10 @@
       </x:c>
       <x:c r="L116" s="33" t="str"/>
       <x:c r="M116" s="33" t="str"/>
-      <x:c r="N116" s="33" t="str">
+      <x:c r="N116" s="33" t="str"/>
+      <x:c r="O116" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O116" s="31"/>
       <x:c r="P116" s="31"/>
       <x:c r="Q116" s="31"/>
     </x:row>
@@ -44422,10 +44528,10 @@
       </x:c>
       <x:c r="L117" s="33" t="str"/>
       <x:c r="M117" s="33" t="str"/>
-      <x:c r="N117" s="33" t="str">
+      <x:c r="N117" s="33" t="str"/>
+      <x:c r="O117" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O117" s="31"/>
       <x:c r="P117" s="31"/>
       <x:c r="Q117" s="31"/>
     </x:row>
@@ -44465,10 +44571,10 @@
       </x:c>
       <x:c r="L118" s="33" t="str"/>
       <x:c r="M118" s="33" t="str"/>
-      <x:c r="N118" s="33" t="str">
+      <x:c r="N118" s="33" t="str"/>
+      <x:c r="O118" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O118" s="31"/>
       <x:c r="P118" s="31"/>
       <x:c r="Q118" s="31"/>
     </x:row>
@@ -44508,10 +44614,10 @@
       </x:c>
       <x:c r="L119" s="33" t="str"/>
       <x:c r="M119" s="33" t="str"/>
-      <x:c r="N119" s="33" t="str">
+      <x:c r="N119" s="33" t="str"/>
+      <x:c r="O119" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O119" s="31"/>
       <x:c r="P119" s="31"/>
       <x:c r="Q119" s="31"/>
     </x:row>
@@ -44551,10 +44657,10 @@
       </x:c>
       <x:c r="L120" s="33" t="str"/>
       <x:c r="M120" s="33" t="str"/>
-      <x:c r="N120" s="33" t="str">
+      <x:c r="N120" s="33" t="str"/>
+      <x:c r="O120" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend01.csv</x:v>
       </x:c>
-      <x:c r="O120" s="31"/>
       <x:c r="P120" s="31"/>
       <x:c r="Q120" s="31"/>
     </x:row>
@@ -44594,10 +44700,10 @@
       </x:c>
       <x:c r="L121" s="33" t="str"/>
       <x:c r="M121" s="33" t="str"/>
-      <x:c r="N121" s="33" t="str">
+      <x:c r="N121" s="33" t="str"/>
+      <x:c r="O121" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O121" s="31"/>
       <x:c r="P121" s="31"/>
       <x:c r="Q121" s="31"/>
     </x:row>
@@ -44637,10 +44743,10 @@
       </x:c>
       <x:c r="L122" s="33" t="str"/>
       <x:c r="M122" s="33" t="str"/>
-      <x:c r="N122" s="33" t="str">
+      <x:c r="N122" s="33" t="str"/>
+      <x:c r="O122" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O122" s="31"/>
       <x:c r="P122" s="31"/>
       <x:c r="Q122" s="31"/>
     </x:row>
@@ -44680,10 +44786,10 @@
       </x:c>
       <x:c r="L123" s="33" t="str"/>
       <x:c r="M123" s="33" t="str"/>
-      <x:c r="N123" s="33" t="str">
+      <x:c r="N123" s="33" t="str"/>
+      <x:c r="O123" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O123" s="31"/>
       <x:c r="P123" s="31"/>
       <x:c r="Q123" s="31"/>
     </x:row>
@@ -44723,10 +44829,10 @@
       </x:c>
       <x:c r="L124" s="33" t="str"/>
       <x:c r="M124" s="33" t="str"/>
-      <x:c r="N124" s="33" t="str">
+      <x:c r="N124" s="33" t="str"/>
+      <x:c r="O124" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O124" s="31"/>
       <x:c r="P124" s="31"/>
       <x:c r="Q124" s="31"/>
     </x:row>
@@ -44766,10 +44872,10 @@
       </x:c>
       <x:c r="L125" s="33" t="str"/>
       <x:c r="M125" s="33" t="str"/>
-      <x:c r="N125" s="33" t="str">
+      <x:c r="N125" s="33" t="str"/>
+      <x:c r="O125" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O125" s="31"/>
       <x:c r="P125" s="31"/>
       <x:c r="Q125" s="31"/>
     </x:row>
@@ -44809,10 +44915,10 @@
       </x:c>
       <x:c r="L126" s="33" t="str"/>
       <x:c r="M126" s="33" t="str"/>
-      <x:c r="N126" s="33" t="str">
+      <x:c r="N126" s="33" t="str"/>
+      <x:c r="O126" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O126" s="31"/>
       <x:c r="P126" s="31"/>
       <x:c r="Q126" s="31"/>
     </x:row>
@@ -44852,10 +44958,10 @@
       </x:c>
       <x:c r="L127" s="33" t="str"/>
       <x:c r="M127" s="33" t="str"/>
-      <x:c r="N127" s="33" t="str">
+      <x:c r="N127" s="33" t="str"/>
+      <x:c r="O127" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O127" s="31"/>
       <x:c r="P127" s="31"/>
       <x:c r="Q127" s="31"/>
     </x:row>
@@ -44895,10 +45001,10 @@
       </x:c>
       <x:c r="L128" s="33" t="str"/>
       <x:c r="M128" s="33" t="str"/>
-      <x:c r="N128" s="33" t="str">
+      <x:c r="N128" s="33" t="str"/>
+      <x:c r="O128" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O128" s="31"/>
       <x:c r="P128" s="31"/>
       <x:c r="Q128" s="31"/>
     </x:row>
@@ -44938,10 +45044,10 @@
       </x:c>
       <x:c r="L129" s="33" t="str"/>
       <x:c r="M129" s="33" t="str"/>
-      <x:c r="N129" s="33" t="str">
+      <x:c r="N129" s="33" t="str"/>
+      <x:c r="O129" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O129" s="31"/>
       <x:c r="P129" s="31"/>
       <x:c r="Q129" s="31"/>
     </x:row>
@@ -44981,10 +45087,10 @@
       </x:c>
       <x:c r="L130" s="33" t="str"/>
       <x:c r="M130" s="33" t="str"/>
-      <x:c r="N130" s="33" t="str">
+      <x:c r="N130" s="33" t="str"/>
+      <x:c r="O130" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O130" s="31"/>
       <x:c r="P130" s="31"/>
       <x:c r="Q130" s="31"/>
     </x:row>
@@ -45024,10 +45130,10 @@
       </x:c>
       <x:c r="L131" s="33" t="str"/>
       <x:c r="M131" s="33" t="str"/>
-      <x:c r="N131" s="33" t="str">
+      <x:c r="N131" s="33" t="str"/>
+      <x:c r="O131" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O131" s="31"/>
       <x:c r="P131" s="31"/>
       <x:c r="Q131" s="31"/>
     </x:row>
@@ -45067,10 +45173,10 @@
       </x:c>
       <x:c r="L132" s="33" t="str"/>
       <x:c r="M132" s="33" t="str"/>
-      <x:c r="N132" s="33" t="str">
+      <x:c r="N132" s="33" t="str"/>
+      <x:c r="O132" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O132" s="31"/>
       <x:c r="P132" s="31"/>
       <x:c r="Q132" s="31"/>
     </x:row>
@@ -45110,10 +45216,10 @@
       </x:c>
       <x:c r="L133" s="33" t="str"/>
       <x:c r="M133" s="33" t="str"/>
-      <x:c r="N133" s="33" t="str">
+      <x:c r="N133" s="33" t="str"/>
+      <x:c r="O133" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O133" s="31"/>
       <x:c r="P133" s="31"/>
       <x:c r="Q133" s="31"/>
     </x:row>
@@ -45153,10 +45259,10 @@
       </x:c>
       <x:c r="L134" s="33" t="str"/>
       <x:c r="M134" s="33" t="str"/>
-      <x:c r="N134" s="33" t="str">
+      <x:c r="N134" s="33" t="str"/>
+      <x:c r="O134" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O134" s="31"/>
       <x:c r="P134" s="31"/>
       <x:c r="Q134" s="31"/>
     </x:row>
@@ -45196,10 +45302,10 @@
       </x:c>
       <x:c r="L135" s="33" t="str"/>
       <x:c r="M135" s="33" t="str"/>
-      <x:c r="N135" s="33" t="str">
+      <x:c r="N135" s="33" t="str"/>
+      <x:c r="O135" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O135" s="31"/>
       <x:c r="P135" s="31"/>
       <x:c r="Q135" s="31"/>
     </x:row>
@@ -45239,10 +45345,10 @@
       </x:c>
       <x:c r="L136" s="33" t="str"/>
       <x:c r="M136" s="33" t="str"/>
-      <x:c r="N136" s="33" t="str">
+      <x:c r="N136" s="33" t="str"/>
+      <x:c r="O136" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O136" s="31"/>
       <x:c r="P136" s="31"/>
       <x:c r="Q136" s="31"/>
     </x:row>
@@ -45282,10 +45388,10 @@
       </x:c>
       <x:c r="L137" s="33" t="str"/>
       <x:c r="M137" s="33" t="str"/>
-      <x:c r="N137" s="33" t="str">
+      <x:c r="N137" s="33" t="str"/>
+      <x:c r="O137" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_blend005.csv</x:v>
       </x:c>
-      <x:c r="O137" s="31"/>
       <x:c r="P137" s="31"/>
       <x:c r="Q137" s="31"/>
     </x:row>
@@ -45329,10 +45435,10 @@
       <x:c r="M138" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N138" s="33" t="str">
+      <x:c r="N138" s="33" t="str"/>
+      <x:c r="O138" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O138" s="31"/>
       <x:c r="P138" s="31"/>
       <x:c r="Q138" s="31"/>
     </x:row>
@@ -45376,10 +45482,10 @@
       <x:c r="M139" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N139" s="33" t="str">
+      <x:c r="N139" s="33" t="str"/>
+      <x:c r="O139" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O139" s="31"/>
       <x:c r="P139" s="31"/>
       <x:c r="Q139" s="31"/>
     </x:row>
@@ -45423,10 +45529,10 @@
       <x:c r="M140" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N140" s="33" t="str">
+      <x:c r="N140" s="33" t="str"/>
+      <x:c r="O140" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O140" s="31"/>
       <x:c r="P140" s="31"/>
       <x:c r="Q140" s="31"/>
     </x:row>
@@ -45470,10 +45576,10 @@
       <x:c r="M141" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N141" s="33" t="str">
+      <x:c r="N141" s="33" t="str"/>
+      <x:c r="O141" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O141" s="31"/>
       <x:c r="P141" s="31"/>
       <x:c r="Q141" s="31"/>
     </x:row>
@@ -45517,10 +45623,10 @@
       <x:c r="M142" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N142" s="33" t="str">
+      <x:c r="N142" s="33" t="str"/>
+      <x:c r="O142" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O142" s="31"/>
       <x:c r="P142" s="31"/>
       <x:c r="Q142" s="31"/>
     </x:row>
@@ -45564,10 +45670,10 @@
       <x:c r="M143" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N143" s="33" t="str">
+      <x:c r="N143" s="33" t="str"/>
+      <x:c r="O143" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O143" s="31"/>
       <x:c r="P143" s="31"/>
       <x:c r="Q143" s="31"/>
     </x:row>
@@ -45611,10 +45717,10 @@
       <x:c r="M144" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N144" s="33" t="str">
+      <x:c r="N144" s="33" t="str"/>
+      <x:c r="O144" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O144" s="31"/>
       <x:c r="P144" s="31"/>
       <x:c r="Q144" s="31"/>
     </x:row>
@@ -45658,10 +45764,10 @@
       <x:c r="M145" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N145" s="33" t="str">
+      <x:c r="N145" s="33" t="str"/>
+      <x:c r="O145" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O145" s="31"/>
       <x:c r="P145" s="31"/>
       <x:c r="Q145" s="31"/>
     </x:row>
@@ -45705,10 +45811,10 @@
       <x:c r="M146" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N146" s="33" t="str">
+      <x:c r="N146" s="33" t="str"/>
+      <x:c r="O146" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O146" s="31"/>
       <x:c r="P146" s="31"/>
       <x:c r="Q146" s="31"/>
     </x:row>
@@ -45752,10 +45858,10 @@
       <x:c r="M147" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N147" s="33" t="str">
+      <x:c r="N147" s="33" t="str"/>
+      <x:c r="O147" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O147" s="31"/>
       <x:c r="P147" s="31"/>
       <x:c r="Q147" s="31"/>
     </x:row>
@@ -45799,10 +45905,10 @@
       <x:c r="M148" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N148" s="33" t="str">
+      <x:c r="N148" s="33" t="str"/>
+      <x:c r="O148" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O148" s="31"/>
       <x:c r="P148" s="31"/>
       <x:c r="Q148" s="31"/>
     </x:row>
@@ -45846,10 +45952,10 @@
       <x:c r="M149" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N149" s="33" t="str">
+      <x:c r="N149" s="33" t="str"/>
+      <x:c r="O149" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O149" s="31"/>
       <x:c r="P149" s="31"/>
       <x:c r="Q149" s="31"/>
     </x:row>
@@ -45893,10 +45999,10 @@
       <x:c r="M150" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N150" s="33" t="str">
+      <x:c r="N150" s="33" t="str"/>
+      <x:c r="O150" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O150" s="31"/>
       <x:c r="P150" s="31"/>
       <x:c r="Q150" s="31"/>
     </x:row>
@@ -45940,10 +46046,10 @@
       <x:c r="M151" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N151" s="33" t="str">
+      <x:c r="N151" s="33" t="str"/>
+      <x:c r="O151" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O151" s="31"/>
       <x:c r="P151" s="31"/>
       <x:c r="Q151" s="31"/>
     </x:row>
@@ -45987,10 +46093,10 @@
       <x:c r="M152" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N152" s="33" t="str">
+      <x:c r="N152" s="33" t="str"/>
+      <x:c r="O152" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O152" s="31"/>
       <x:c r="P152" s="31"/>
       <x:c r="Q152" s="31"/>
     </x:row>
@@ -46034,10 +46140,10 @@
       <x:c r="M153" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N153" s="33" t="str">
+      <x:c r="N153" s="33" t="str"/>
+      <x:c r="O153" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O153" s="31"/>
       <x:c r="P153" s="31"/>
       <x:c r="Q153" s="31"/>
     </x:row>
@@ -46081,10 +46187,10 @@
       <x:c r="M154" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N154" s="33" t="str">
+      <x:c r="N154" s="33" t="str"/>
+      <x:c r="O154" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_agreement.csv</x:v>
       </x:c>
-      <x:c r="O154" s="31"/>
       <x:c r="P154" s="31"/>
       <x:c r="Q154" s="31"/>
     </x:row>
@@ -46128,10 +46234,10 @@
       <x:c r="M155" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N155" s="33" t="str">
+      <x:c r="N155" s="33" t="str"/>
+      <x:c r="O155" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O155" s="31"/>
       <x:c r="P155" s="31"/>
       <x:c r="Q155" s="31"/>
     </x:row>
@@ -46175,10 +46281,10 @@
       <x:c r="M156" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N156" s="33" t="str">
+      <x:c r="N156" s="33" t="str"/>
+      <x:c r="O156" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O156" s="31"/>
       <x:c r="P156" s="31"/>
       <x:c r="Q156" s="31"/>
     </x:row>
@@ -46222,10 +46328,10 @@
       <x:c r="M157" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N157" s="33" t="str">
+      <x:c r="N157" s="33" t="str"/>
+      <x:c r="O157" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O157" s="31"/>
       <x:c r="P157" s="31"/>
       <x:c r="Q157" s="31"/>
     </x:row>
@@ -46269,10 +46375,10 @@
       <x:c r="M158" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N158" s="33" t="str">
+      <x:c r="N158" s="33" t="str"/>
+      <x:c r="O158" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O158" s="31"/>
       <x:c r="P158" s="31"/>
       <x:c r="Q158" s="31"/>
     </x:row>
@@ -46316,10 +46422,10 @@
       <x:c r="M159" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N159" s="33" t="str">
+      <x:c r="N159" s="33" t="str"/>
+      <x:c r="O159" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O159" s="31"/>
       <x:c r="P159" s="31"/>
       <x:c r="Q159" s="31"/>
     </x:row>
@@ -46363,10 +46469,10 @@
       <x:c r="M160" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N160" s="33" t="str">
+      <x:c r="N160" s="33" t="str"/>
+      <x:c r="O160" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O160" s="31"/>
       <x:c r="P160" s="31"/>
       <x:c r="Q160" s="31"/>
     </x:row>
@@ -46410,10 +46516,10 @@
       <x:c r="M161" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N161" s="33" t="str">
+      <x:c r="N161" s="33" t="str"/>
+      <x:c r="O161" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O161" s="31"/>
       <x:c r="P161" s="31"/>
       <x:c r="Q161" s="31"/>
     </x:row>
@@ -46457,10 +46563,10 @@
       <x:c r="M162" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N162" s="33" t="str">
+      <x:c r="N162" s="33" t="str"/>
+      <x:c r="O162" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O162" s="31"/>
       <x:c r="P162" s="31"/>
       <x:c r="Q162" s="31"/>
     </x:row>
@@ -46504,10 +46610,10 @@
       <x:c r="M163" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N163" s="33" t="str">
+      <x:c r="N163" s="33" t="str"/>
+      <x:c r="O163" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O163" s="31"/>
       <x:c r="P163" s="31"/>
       <x:c r="Q163" s="31"/>
     </x:row>
@@ -46551,10 +46657,10 @@
       <x:c r="M164" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N164" s="33" t="str">
+      <x:c r="N164" s="33" t="str"/>
+      <x:c r="O164" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O164" s="31"/>
       <x:c r="P164" s="31"/>
       <x:c r="Q164" s="31"/>
     </x:row>
@@ -46598,10 +46704,10 @@
       <x:c r="M165" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N165" s="33" t="str">
+      <x:c r="N165" s="33" t="str"/>
+      <x:c r="O165" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O165" s="31"/>
       <x:c r="P165" s="31"/>
       <x:c r="Q165" s="31"/>
     </x:row>
@@ -46645,10 +46751,10 @@
       <x:c r="M166" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N166" s="33" t="str">
+      <x:c r="N166" s="33" t="str"/>
+      <x:c r="O166" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O166" s="31"/>
       <x:c r="P166" s="31"/>
       <x:c r="Q166" s="31"/>
     </x:row>
@@ -46692,10 +46798,10 @@
       <x:c r="M167" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N167" s="33" t="str">
+      <x:c r="N167" s="33" t="str"/>
+      <x:c r="O167" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O167" s="31"/>
       <x:c r="P167" s="31"/>
       <x:c r="Q167" s="31"/>
     </x:row>
@@ -46739,10 +46845,10 @@
       <x:c r="M168" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N168" s="33" t="str">
+      <x:c r="N168" s="33" t="str"/>
+      <x:c r="O168" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O168" s="31"/>
       <x:c r="P168" s="31"/>
       <x:c r="Q168" s="31"/>
     </x:row>
@@ -46786,10 +46892,10 @@
       <x:c r="M169" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N169" s="33" t="str">
+      <x:c r="N169" s="33" t="str"/>
+      <x:c r="O169" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O169" s="31"/>
       <x:c r="P169" s="31"/>
       <x:c r="Q169" s="31"/>
     </x:row>
@@ -46833,10 +46939,10 @@
       <x:c r="M170" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N170" s="33" t="str">
+      <x:c r="N170" s="33" t="str"/>
+      <x:c r="O170" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O170" s="31"/>
       <x:c r="P170" s="31"/>
       <x:c r="Q170" s="31"/>
     </x:row>
@@ -46880,19 +46986,19 @@
       <x:c r="M171" s="33" t="str">
         <x:v>0.0</x:v>
       </x:c>
-      <x:c r="N171" s="33" t="str">
+      <x:c r="N171" s="33" t="str"/>
+      <x:c r="O171" s="33" t="str">
         <x:v>exact_qwen3_1_7b_hrm_chat_boxed_confidence.csv</x:v>
       </x:c>
-      <x:c r="O171" s="31"/>
       <x:c r="P171" s="31"/>
       <x:c r="Q171" s="31"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B172" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C172" s="33" t="str">
         <x:v>algebra</x:v>
@@ -46901,33 +47007,47 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E172" s="33" t="str">
-        <x:v>\dfrac{25}{2}</x:v>
+        <x:v>### **Step 5: Divide both sides by 4</x:v>
       </x:c>
       <x:c r="F172" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G172" s="35" t="n">
+        <x:v>1.6133804589999272</x:v>
+      </x:c>
+      <x:c r="H172" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I172" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G172" s="35" t="n">
-        <x:v>7.580443959000007</x:v>
-      </x:c>
-      <x:c r="H172" s="33" t="str"/>
-      <x:c r="I172" s="33" t="str"/>
-      <x:c r="J172" s="33" t="str"/>
-      <x:c r="K172" s="33" t="str"/>
-      <x:c r="L172" s="33" t="str"/>
-      <x:c r="M172" s="33" t="str"/>
+      <x:c r="J172" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K172" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L172" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M172" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N172" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O172" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O172" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P172" s="31"/>
       <x:c r="Q172" s="31"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B173" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C173" s="33" t="str">
         <x:v>markup</x:v>
@@ -46936,33 +47056,47 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E173" s="33" t="str">
-        <x:v>96</x:v>
+        <x:v>0.80x = 96</x:v>
       </x:c>
       <x:c r="F173" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G173" s="35" t="n">
+        <x:v>1.5982287920001</x:v>
+      </x:c>
+      <x:c r="H173" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I173" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G173" s="35" t="n">
-        <x:v>6.407860625000012</x:v>
-      </x:c>
-      <x:c r="H173" s="33" t="str"/>
-      <x:c r="I173" s="33" t="str"/>
-      <x:c r="J173" s="33" t="str"/>
-      <x:c r="K173" s="33" t="str"/>
-      <x:c r="L173" s="33" t="str"/>
-      <x:c r="M173" s="33" t="str"/>
+      <x:c r="J173" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K173" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L173" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M173" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N173" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O173" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O173" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P173" s="31"/>
       <x:c r="Q173" s="31"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B174" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C174" s="33" t="str">
         <x:v>boxes</x:v>
@@ -46971,33 +47105,47 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E174" s="33" t="str">
-        <x:v>Mixed</x:v>
+        <x:v>'- The</x:v>
       </x:c>
       <x:c r="F174" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G174" s="35" t="n">
+        <x:v>1.5920459159997336</x:v>
+      </x:c>
+      <x:c r="H174" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I174" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G174" s="35" t="n">
-        <x:v>6.2715228750000165</x:v>
-      </x:c>
-      <x:c r="H174" s="33" t="str"/>
-      <x:c r="I174" s="33" t="str"/>
-      <x:c r="J174" s="33" t="str"/>
-      <x:c r="K174" s="33" t="str"/>
-      <x:c r="L174" s="33" t="str"/>
-      <x:c r="M174" s="33" t="str"/>
+      <x:c r="J174" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K174" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L174" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M174" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N174" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O174" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O174" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P174" s="31"/>
       <x:c r="Q174" s="31"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B175" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C175" s="33" t="str">
         <x:v>inclusion</x:v>
@@ -47006,33 +47154,47 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E175" s="33" t="str">
-        <x:v>80</x:v>
+        <x:v>|A \cup B| - |C| = |A</x:v>
       </x:c>
       <x:c r="F175" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G175" s="35" t="n">
+        <x:v>1.5861215420000008</x:v>
+      </x:c>
+      <x:c r="H175" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I175" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G175" s="35" t="n">
-        <x:v>4.775222624999998</x:v>
-      </x:c>
-      <x:c r="H175" s="33" t="str"/>
-      <x:c r="I175" s="33" t="str"/>
-      <x:c r="J175" s="33" t="str"/>
-      <x:c r="K175" s="33" t="str"/>
-      <x:c r="L175" s="33" t="str"/>
-      <x:c r="M175" s="33" t="str"/>
+      <x:c r="J175" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K175" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L175" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M175" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N175" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O175" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O175" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P175" s="31"/>
       <x:c r="Q175" s="31"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B176" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C176" s="33" t="str">
         <x:v>modular</x:v>
@@ -47041,33 +47203,47 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E176" s="33" t="str">
-        <x:v>'- \(7^8 \equiv 9^2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F176" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
       <x:c r="G176" s="35" t="n">
-        <x:v>14.03727679100001</x:v>
-      </x:c>
-      <x:c r="H176" s="33" t="str"/>
-      <x:c r="I176" s="33" t="str"/>
-      <x:c r="J176" s="33" t="str"/>
-      <x:c r="K176" s="33" t="str"/>
-      <x:c r="L176" s="33" t="str"/>
-      <x:c r="M176" s="33" t="str"/>
+        <x:v>1.8240370000003168</x:v>
+      </x:c>
+      <x:c r="H176" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I176" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J176" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K176" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L176" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M176" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N176" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O176" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O176" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P176" s="31"/>
       <x:c r="Q176" s="31"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B177" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C177" s="33" t="str">
         <x:v>work_rate</x:v>
@@ -47076,33 +47252,47 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E177" s="33" t="str">
-        <x:v>\dfrac{15}{4}</x:v>
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac</x:v>
       </x:c>
       <x:c r="F177" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G177" s="35" t="n">
+        <x:v>1.6387322920004408</x:v>
+      </x:c>
+      <x:c r="H177" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I177" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G177" s="35" t="n">
-        <x:v>6.176148500000011</x:v>
-      </x:c>
-      <x:c r="H177" s="33" t="str"/>
-      <x:c r="I177" s="33" t="str"/>
-      <x:c r="J177" s="33" t="str"/>
-      <x:c r="K177" s="33" t="str"/>
-      <x:c r="L177" s="33" t="str"/>
-      <x:c r="M177" s="33" t="str"/>
+      <x:c r="J177" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K177" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L177" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M177" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N177" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O177" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O177" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P177" s="31"/>
       <x:c r="Q177" s="31"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B178" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C178" s="33" t="str">
         <x:v>probability</x:v>
@@ -47111,33 +47301,47 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E178" s="33" t="str">
-        <x:v>\dfrac{1}{9}</x:v>
+        <x:v>'---</x:v>
       </x:c>
       <x:c r="F178" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G178" s="35" t="n">
+        <x:v>1.5750748750001549</x:v>
+      </x:c>
+      <x:c r="H178" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I178" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G178" s="35" t="n">
-        <x:v>4.10938950000002</x:v>
-      </x:c>
-      <x:c r="H178" s="33" t="str"/>
-      <x:c r="I178" s="33" t="str"/>
-      <x:c r="J178" s="33" t="str"/>
-      <x:c r="K178" s="33" t="str"/>
-      <x:c r="L178" s="33" t="str"/>
-      <x:c r="M178" s="33" t="str"/>
+      <x:c r="J178" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K178" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L178" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M178" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N178" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O178" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O178" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P178" s="31"/>
       <x:c r="Q178" s="31"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B179" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C179" s="33" t="str">
         <x:v>sequence</x:v>
@@ -47152,27 +47356,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G179" s="35" t="n">
-        <x:v>8.457965874999957</x:v>
-      </x:c>
-      <x:c r="H179" s="33" t="str"/>
-      <x:c r="I179" s="33" t="str"/>
-      <x:c r="J179" s="33" t="str"/>
-      <x:c r="K179" s="33" t="str"/>
-      <x:c r="L179" s="33" t="str"/>
-      <x:c r="M179" s="33" t="str"/>
+        <x:v>2.30137729199987</x:v>
+      </x:c>
+      <x:c r="H179" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I179" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J179" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K179" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L179" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M179" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N179" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O179" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O179" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P179" s="31"/>
       <x:c r="Q179" s="31"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B180" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C180" s="33" t="str">
         <x:v>linear_word</x:v>
@@ -47187,27 +47405,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G180" s="35" t="n">
-        <x:v>4.77963704199999</x:v>
-      </x:c>
-      <x:c r="H180" s="33" t="str"/>
-      <x:c r="I180" s="33" t="str"/>
-      <x:c r="J180" s="33" t="str"/>
-      <x:c r="K180" s="33" t="str"/>
-      <x:c r="L180" s="33" t="str"/>
-      <x:c r="M180" s="33" t="str"/>
+        <x:v>2.373712792000333</x:v>
+      </x:c>
+      <x:c r="H180" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I180" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J180" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K180" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L180" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M180" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N180" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O180" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O180" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P180" s="31"/>
       <x:c r="Q180" s="31"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B181" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C181" s="33" t="str">
         <x:v>reverse_discount</x:v>
@@ -47222,27 +47454,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G181" s="35" t="n">
-        <x:v>4.465110458999959</x:v>
-      </x:c>
-      <x:c r="H181" s="33" t="str"/>
-      <x:c r="I181" s="33" t="str"/>
-      <x:c r="J181" s="33" t="str"/>
-      <x:c r="K181" s="33" t="str"/>
-      <x:c r="L181" s="33" t="str"/>
-      <x:c r="M181" s="33" t="str"/>
+        <x:v>2.2699117910001405</x:v>
+      </x:c>
+      <x:c r="H181" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I181" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J181" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K181" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L181" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M181" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N181" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O181" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O181" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P181" s="31"/>
       <x:c r="Q181" s="31"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B182" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C182" s="33" t="str">
         <x:v>multiples</x:v>
@@ -47251,33 +47497,47 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E182" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>'- Common difference $ d</x:v>
       </x:c>
       <x:c r="F182" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G182" s="35" t="n">
+        <x:v>1.8648728749999464</x:v>
+      </x:c>
+      <x:c r="H182" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I182" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G182" s="35" t="n">
-        <x:v>4.0312850840000465</x:v>
-      </x:c>
-      <x:c r="H182" s="33" t="str"/>
-      <x:c r="I182" s="33" t="str"/>
-      <x:c r="J182" s="33" t="str"/>
-      <x:c r="K182" s="33" t="str"/>
-      <x:c r="L182" s="33" t="str"/>
-      <x:c r="M182" s="33" t="str"/>
+      <x:c r="J182" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K182" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L182" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M182" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N182" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O182" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O182" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P182" s="31"/>
       <x:c r="Q182" s="31"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B183" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C183" s="33" t="str">
         <x:v>rectangle</x:v>
@@ -47292,27 +47552,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G183" s="35" t="n">
-        <x:v>4.098184124999989</x:v>
-      </x:c>
-      <x:c r="H183" s="33" t="str"/>
-      <x:c r="I183" s="33" t="str"/>
-      <x:c r="J183" s="33" t="str"/>
-      <x:c r="K183" s="33" t="str"/>
-      <x:c r="L183" s="33" t="str"/>
-      <x:c r="M183" s="33" t="str"/>
+        <x:v>2.7604973749998862</x:v>
+      </x:c>
+      <x:c r="H183" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I183" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J183" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K183" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L183" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M183" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N183" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O183" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O183" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P183" s="31"/>
       <x:c r="Q183" s="31"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B184" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C184" s="33" t="str">
         <x:v>average</x:v>
@@ -47321,33 +47595,47 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E184" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>10 + 11 + 13 + 1</x:v>
       </x:c>
       <x:c r="F184" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G184" s="35" t="n">
+        <x:v>1.5941838749999988</x:v>
+      </x:c>
+      <x:c r="H184" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I184" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G184" s="35" t="n">
-        <x:v>3.955258875000027</x:v>
-      </x:c>
-      <x:c r="H184" s="33" t="str"/>
-      <x:c r="I184" s="33" t="str"/>
-      <x:c r="J184" s="33" t="str"/>
-      <x:c r="K184" s="33" t="str"/>
-      <x:c r="L184" s="33" t="str"/>
-      <x:c r="M184" s="33" t="str"/>
+      <x:c r="J184" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K184" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L184" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M184" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N184" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O184" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O184" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P184" s="31"/>
       <x:c r="Q184" s="31"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B185" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C185" s="33" t="str">
         <x:v>combinations</x:v>
@@ -47356,33 +47644,47 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E185" s="33" t="str">
-        <x:v>15</x:v>
+        <x:v>\binom{6}{2} = \frac{6!</x:v>
       </x:c>
       <x:c r="F185" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G185" s="35" t="n">
+        <x:v>1.585441124999761</x:v>
+      </x:c>
+      <x:c r="H185" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I185" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G185" s="35" t="n">
-        <x:v>6.499252583999976</x:v>
-      </x:c>
-      <x:c r="H185" s="33" t="str"/>
-      <x:c r="I185" s="33" t="str"/>
-      <x:c r="J185" s="33" t="str"/>
-      <x:c r="K185" s="33" t="str"/>
-      <x:c r="L185" s="33" t="str"/>
-      <x:c r="M185" s="33" t="str"/>
+      <x:c r="J185" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K185" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L185" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M185" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N185" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O185" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O185" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P185" s="31"/>
       <x:c r="Q185" s="31"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B186" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C186" s="33" t="str">
         <x:v>coins</x:v>
@@ -47391,33 +47693,47 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E186" s="33" t="str">
-        <x:v>\dfrac{3}{8}</x:v>
+        <x:v>'- $ p = \frac{1</x:v>
       </x:c>
       <x:c r="F186" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G186" s="35" t="n">
+        <x:v>1.5954377919997569</x:v>
+      </x:c>
+      <x:c r="H186" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I186" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G186" s="35" t="n">
-        <x:v>2.2782300830000395</x:v>
-      </x:c>
-      <x:c r="H186" s="33" t="str"/>
-      <x:c r="I186" s="33" t="str"/>
-      <x:c r="J186" s="33" t="str"/>
-      <x:c r="K186" s="33" t="str"/>
-      <x:c r="L186" s="33" t="str"/>
-      <x:c r="M186" s="33" t="str"/>
+      <x:c r="J186" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K186" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L186" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M186" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N186" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O186" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O186" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P186" s="31"/>
       <x:c r="Q186" s="31"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B187" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C187" s="33" t="str">
         <x:v>modular_small</x:v>
@@ -47432,27 +47748,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G187" s="35" t="n">
-        <x:v>12.253404416999956</x:v>
-      </x:c>
-      <x:c r="H187" s="33" t="str"/>
-      <x:c r="I187" s="33" t="str"/>
-      <x:c r="J187" s="33" t="str"/>
-      <x:c r="K187" s="33" t="str"/>
-      <x:c r="L187" s="33" t="str"/>
-      <x:c r="M187" s="33" t="str"/>
+        <x:v>2.3947960420000527</x:v>
+      </x:c>
+      <x:c r="H187" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I187" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J187" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K187" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L187" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M187" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N187" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O187" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O187" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P187" s="31"/>
       <x:c r="Q187" s="31"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="33" t="str">
-        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B188" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C188" s="33" t="str">
         <x:v>syllogism</x:v>
@@ -47461,33 +47791,47 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E188" s="33" t="str">
-        <x:v>Yes, all bloops must be lazzies.</x:v>
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
       </x:c>
       <x:c r="F188" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="G188" s="35" t="n">
-        <x:v>4.511834166999961</x:v>
-      </x:c>
-      <x:c r="H188" s="33" t="str"/>
-      <x:c r="I188" s="33" t="str"/>
-      <x:c r="J188" s="33" t="str"/>
-      <x:c r="K188" s="33" t="str"/>
-      <x:c r="L188" s="33" t="str"/>
-      <x:c r="M188" s="33" t="str"/>
+        <x:v>2.5401205419998405</x:v>
+      </x:c>
+      <x:c r="H188" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I188" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J188" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K188" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L188" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="M188" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N188" s="33" t="str">
-        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O188" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O188" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_blend.csv</x:v>
+      </x:c>
       <x:c r="P188" s="31"/>
       <x:c r="Q188" s="31"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B189" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C189" s="33" t="str">
         <x:v>algebra</x:v>
@@ -47496,33 +47840,47 @@
         <x:v>12.5|25/2</x:v>
       </x:c>
       <x:c r="E189" s="33" t="str">
-        <x:v>\dfrac{25}{2}</x:v>
+        <x:v>### **Step 5: Divide both sides by 4</x:v>
       </x:c>
       <x:c r="F189" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G189" s="35" t="n">
+        <x:v>1.6393786670000736</x:v>
+      </x:c>
+      <x:c r="H189" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I189" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G189" s="35" t="n">
-        <x:v>16.656210082999962</x:v>
-      </x:c>
-      <x:c r="H189" s="33" t="str"/>
-      <x:c r="I189" s="33" t="str"/>
-      <x:c r="J189" s="33" t="str"/>
-      <x:c r="K189" s="33" t="str"/>
-      <x:c r="L189" s="33" t="str"/>
-      <x:c r="M189" s="33" t="str"/>
+      <x:c r="J189" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K189" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L189" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M189" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N189" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O189" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O189" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P189" s="31"/>
       <x:c r="Q189" s="31"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B190" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C190" s="33" t="str">
         <x:v>markup</x:v>
@@ -47531,33 +47889,47 @@
         <x:v>96|$96</x:v>
       </x:c>
       <x:c r="E190" s="33" t="str">
-        <x:v>96</x:v>
+        <x:v>0.80x = 96</x:v>
       </x:c>
       <x:c r="F190" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G190" s="35" t="n">
+        <x:v>1.7484442089998993</x:v>
+      </x:c>
+      <x:c r="H190" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I190" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G190" s="35" t="n">
-        <x:v>12.64156225000005</x:v>
-      </x:c>
-      <x:c r="H190" s="33" t="str"/>
-      <x:c r="I190" s="33" t="str"/>
-      <x:c r="J190" s="33" t="str"/>
-      <x:c r="K190" s="33" t="str"/>
-      <x:c r="L190" s="33" t="str"/>
-      <x:c r="M190" s="33" t="str"/>
+      <x:c r="J190" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K190" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L190" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M190" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N190" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O190" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O190" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P190" s="31"/>
       <x:c r="Q190" s="31"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B191" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C191" s="33" t="str">
         <x:v>boxes</x:v>
@@ -47566,33 +47938,47 @@
         <x:v>mixed|Mixed</x:v>
       </x:c>
       <x:c r="E191" s="33" t="str">
-        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
+        <x:v>'- The</x:v>
       </x:c>
       <x:c r="F191" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G191" s="35" t="n">
+        <x:v>1.5794739999996636</x:v>
+      </x:c>
+      <x:c r="H191" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I191" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G191" s="35" t="n">
-        <x:v>19.97141316599999</x:v>
-      </x:c>
-      <x:c r="H191" s="33" t="str"/>
-      <x:c r="I191" s="33" t="str"/>
-      <x:c r="J191" s="33" t="str"/>
-      <x:c r="K191" s="33" t="str"/>
-      <x:c r="L191" s="33" t="str"/>
-      <x:c r="M191" s="33" t="str"/>
+      <x:c r="J191" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K191" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L191" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M191" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N191" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O191" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O191" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P191" s="31"/>
       <x:c r="Q191" s="31"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B192" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C192" s="33" t="str">
         <x:v>inclusion</x:v>
@@ -47601,33 +47987,47 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="E192" s="33" t="str">
-        <x:v>80</x:v>
+        <x:v>|A \cup B| - |C| = |A</x:v>
       </x:c>
       <x:c r="F192" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G192" s="35" t="n">
+        <x:v>1.700776415999826</x:v>
+      </x:c>
+      <x:c r="H192" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I192" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G192" s="35" t="n">
-        <x:v>12.902716834000046</x:v>
-      </x:c>
-      <x:c r="H192" s="33" t="str"/>
-      <x:c r="I192" s="33" t="str"/>
-      <x:c r="J192" s="33" t="str"/>
-      <x:c r="K192" s="33" t="str"/>
-      <x:c r="L192" s="33" t="str"/>
-      <x:c r="M192" s="33" t="str"/>
+      <x:c r="J192" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K192" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L192" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M192" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N192" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O192" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O192" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P192" s="31"/>
       <x:c r="Q192" s="31"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B193" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C193" s="33" t="str">
         <x:v>modular</x:v>
@@ -47636,33 +48036,47 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="E193" s="33" t="str">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F193" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G193" s="35" t="n">
+        <x:v>1.612958209000226</x:v>
+      </x:c>
+      <x:c r="H193" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I193" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G193" s="35" t="n">
-        <x:v>50.31506079099995</x:v>
-      </x:c>
-      <x:c r="H193" s="33" t="str"/>
-      <x:c r="I193" s="33" t="str"/>
-      <x:c r="J193" s="33" t="str"/>
-      <x:c r="K193" s="33" t="str"/>
-      <x:c r="L193" s="33" t="str"/>
-      <x:c r="M193" s="33" t="str"/>
+      <x:c r="J193" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K193" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L193" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M193" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N193" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O193" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O193" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P193" s="31"/>
       <x:c r="Q193" s="31"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B194" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C194" s="33" t="str">
         <x:v>work_rate</x:v>
@@ -47671,33 +48085,47 @@
         <x:v>3.75|15/4</x:v>
       </x:c>
       <x:c r="E194" s="33" t="str">
-        <x:v>3.75</x:v>
+        <x:v>\text{Combined rate} = \frac{5}{30} + \frac{3}{30} = \frac</x:v>
       </x:c>
       <x:c r="F194" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G194" s="35" t="n">
+        <x:v>1.685121583000182</x:v>
+      </x:c>
+      <x:c r="H194" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I194" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G194" s="35" t="n">
-        <x:v>33.462693083999966</x:v>
-      </x:c>
-      <x:c r="H194" s="33" t="str"/>
-      <x:c r="I194" s="33" t="str"/>
-      <x:c r="J194" s="33" t="str"/>
-      <x:c r="K194" s="33" t="str"/>
-      <x:c r="L194" s="33" t="str"/>
-      <x:c r="M194" s="33" t="str"/>
+      <x:c r="J194" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K194" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L194" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M194" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N194" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O194" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O194" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P194" s="31"/>
       <x:c r="Q194" s="31"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B195" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C195" s="33" t="str">
         <x:v>probability</x:v>
@@ -47706,33 +48134,47 @@
         <x:v>1/9</x:v>
       </x:c>
       <x:c r="E195" s="33" t="str">
-        <x:v>\dfrac{1}{9}</x:v>
+        <x:v>'---</x:v>
       </x:c>
       <x:c r="F195" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G195" s="35" t="n">
+        <x:v>1.6234770000000935</x:v>
+      </x:c>
+      <x:c r="H195" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I195" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G195" s="35" t="n">
-        <x:v>7.085368707999919</x:v>
-      </x:c>
-      <x:c r="H195" s="33" t="str"/>
-      <x:c r="I195" s="33" t="str"/>
-      <x:c r="J195" s="33" t="str"/>
-      <x:c r="K195" s="33" t="str"/>
-      <x:c r="L195" s="33" t="str"/>
-      <x:c r="M195" s="33" t="str"/>
+      <x:c r="J195" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K195" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L195" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M195" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N195" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O195" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O195" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P195" s="31"/>
       <x:c r="Q195" s="31"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B196" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C196" s="33" t="str">
         <x:v>sequence</x:v>
@@ -47747,27 +48189,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G196" s="35" t="n">
-        <x:v>15.824353458000019</x:v>
-      </x:c>
-      <x:c r="H196" s="33" t="str"/>
-      <x:c r="I196" s="33" t="str"/>
-      <x:c r="J196" s="33" t="str"/>
-      <x:c r="K196" s="33" t="str"/>
-      <x:c r="L196" s="33" t="str"/>
-      <x:c r="M196" s="33" t="str"/>
+        <x:v>2.336924958000054</x:v>
+      </x:c>
+      <x:c r="H196" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I196" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J196" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K196" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L196" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M196" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N196" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O196" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O196" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P196" s="31"/>
       <x:c r="Q196" s="31"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B197" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C197" s="33" t="str">
         <x:v>linear_word</x:v>
@@ -47782,27 +48238,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G197" s="35" t="n">
-        <x:v>8.149854707999907</x:v>
-      </x:c>
-      <x:c r="H197" s="33" t="str"/>
-      <x:c r="I197" s="33" t="str"/>
-      <x:c r="J197" s="33" t="str"/>
-      <x:c r="K197" s="33" t="str"/>
-      <x:c r="L197" s="33" t="str"/>
-      <x:c r="M197" s="33" t="str"/>
+        <x:v>2.393144915999983</x:v>
+      </x:c>
+      <x:c r="H197" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I197" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J197" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K197" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L197" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M197" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N197" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O197" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O197" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P197" s="31"/>
       <x:c r="Q197" s="31"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B198" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C198" s="33" t="str">
         <x:v>reverse_discount</x:v>
@@ -47817,27 +48287,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G198" s="35" t="n">
-        <x:v>6.157211500000017</x:v>
-      </x:c>
-      <x:c r="H198" s="33" t="str"/>
-      <x:c r="I198" s="33" t="str"/>
-      <x:c r="J198" s="33" t="str"/>
-      <x:c r="K198" s="33" t="str"/>
-      <x:c r="L198" s="33" t="str"/>
-      <x:c r="M198" s="33" t="str"/>
+        <x:v>1.8850382499999796</x:v>
+      </x:c>
+      <x:c r="H198" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I198" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J198" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K198" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L198" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M198" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N198" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O198" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O198" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P198" s="31"/>
       <x:c r="Q198" s="31"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B199" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C199" s="33" t="str">
         <x:v>multiples</x:v>
@@ -47846,33 +48330,47 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E199" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>'- Common difference $ d</x:v>
       </x:c>
       <x:c r="F199" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G199" s="35" t="n">
+        <x:v>1.627677124999991</x:v>
+      </x:c>
+      <x:c r="H199" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I199" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G199" s="35" t="n">
-        <x:v>21.503388040999994</x:v>
-      </x:c>
-      <x:c r="H199" s="33" t="str"/>
-      <x:c r="I199" s="33" t="str"/>
-      <x:c r="J199" s="33" t="str"/>
-      <x:c r="K199" s="33" t="str"/>
-      <x:c r="L199" s="33" t="str"/>
-      <x:c r="M199" s="33" t="str"/>
+      <x:c r="J199" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K199" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L199" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M199" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N199" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O199" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O199" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P199" s="31"/>
       <x:c r="Q199" s="31"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B200" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C200" s="33" t="str">
         <x:v>rectangle</x:v>
@@ -47887,27 +48385,41 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="G200" s="35" t="n">
-        <x:v>7.560139790999983</x:v>
-      </x:c>
-      <x:c r="H200" s="33" t="str"/>
-      <x:c r="I200" s="33" t="str"/>
-      <x:c r="J200" s="33" t="str"/>
-      <x:c r="K200" s="33" t="str"/>
-      <x:c r="L200" s="33" t="str"/>
-      <x:c r="M200" s="33" t="str"/>
+        <x:v>2.4977514590000283</x:v>
+      </x:c>
+      <x:c r="H200" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I200" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J200" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K200" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L200" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M200" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N200" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O200" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O200" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P200" s="31"/>
       <x:c r="Q200" s="31"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B201" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C201" s="33" t="str">
         <x:v>average</x:v>
@@ -47916,33 +48428,47 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E201" s="33" t="str">
-        <x:v>12</x:v>
+        <x:v>10 + 11 + 13 + 1</x:v>
       </x:c>
       <x:c r="F201" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G201" s="35" t="n">
+        <x:v>1.7288417499999014</x:v>
+      </x:c>
+      <x:c r="H201" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I201" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G201" s="35" t="n">
-        <x:v>8.231041165999955</x:v>
-      </x:c>
-      <x:c r="H201" s="33" t="str"/>
-      <x:c r="I201" s="33" t="str"/>
-      <x:c r="J201" s="33" t="str"/>
-      <x:c r="K201" s="33" t="str"/>
-      <x:c r="L201" s="33" t="str"/>
-      <x:c r="M201" s="33" t="str"/>
+      <x:c r="J201" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K201" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L201" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M201" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N201" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O201" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O201" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P201" s="31"/>
       <x:c r="Q201" s="31"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B202" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C202" s="33" t="str">
         <x:v>combinations</x:v>
@@ -47951,33 +48477,47 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E202" s="33" t="str">
-        <x:v>15</x:v>
+        <x:v>\binom{6}{2} = \frac{6!</x:v>
       </x:c>
       <x:c r="F202" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G202" s="35" t="n">
+        <x:v>1.7333646669999325</x:v>
+      </x:c>
+      <x:c r="H202" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I202" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G202" s="35" t="n">
-        <x:v>30.73365029099989</x:v>
-      </x:c>
-      <x:c r="H202" s="33" t="str"/>
-      <x:c r="I202" s="33" t="str"/>
-      <x:c r="J202" s="33" t="str"/>
-      <x:c r="K202" s="33" t="str"/>
-      <x:c r="L202" s="33" t="str"/>
-      <x:c r="M202" s="33" t="str"/>
+      <x:c r="J202" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K202" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L202" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M202" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N202" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O202" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O202" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P202" s="31"/>
       <x:c r="Q202" s="31"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B203" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C203" s="33" t="str">
         <x:v>coins</x:v>
@@ -47986,33 +48526,47 @@
         <x:v>3/8</x:v>
       </x:c>
       <x:c r="E203" s="33" t="str">
-        <x:v>\dfrac{3}{8}</x:v>
+        <x:v>'- $ p = \frac{1</x:v>
       </x:c>
       <x:c r="F203" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G203" s="35" t="n">
+        <x:v>1.948383541000112</x:v>
+      </x:c>
+      <x:c r="H203" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I203" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
-      <x:c r="G203" s="35" t="n">
-        <x:v>11.049620875000073</x:v>
-      </x:c>
-      <x:c r="H203" s="33" t="str"/>
-      <x:c r="I203" s="33" t="str"/>
-      <x:c r="J203" s="33" t="str"/>
-      <x:c r="K203" s="33" t="str"/>
-      <x:c r="L203" s="33" t="str"/>
-      <x:c r="M203" s="33" t="str"/>
+      <x:c r="J203" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K203" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L203" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M203" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N203" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O203" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O203" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P203" s="31"/>
       <x:c r="Q203" s="31"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B204" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C204" s="33" t="str">
         <x:v>modular_small</x:v>
@@ -48021,33 +48575,47 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E204" s="33" t="str">
-        <x:v>All methods confirm that the remainder when</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F204" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G204" s="35" t="n">
+        <x:v>2.474032250000164</x:v>
+      </x:c>
+      <x:c r="H204" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I204" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J204" s="33" t="str">
         <x:v>False</x:v>
       </x:c>
-      <x:c r="G204" s="35" t="n">
-        <x:v>67.06586500000003</x:v>
-      </x:c>
-      <x:c r="H204" s="33" t="str"/>
-      <x:c r="I204" s="33" t="str"/>
-      <x:c r="J204" s="33" t="str"/>
-      <x:c r="K204" s="33" t="str"/>
-      <x:c r="L204" s="33" t="str"/>
-      <x:c r="M204" s="33" t="str"/>
+      <x:c r="K204" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L204" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M204" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N204" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O204" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O204" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P204" s="31"/>
       <x:c r="Q204" s="31"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="33" t="str">
-        <x:v>HRM-Text-1B MLX BF16</x:v>
+        <x:v>Qwen3-1.7B-4bit</x:v>
       </x:c>
       <x:c r="B205" s="33" t="str">
-        <x:v>HRM-Text</x:v>
+        <x:v>Qwen-HRM</x:v>
       </x:c>
       <x:c r="C205" s="33" t="str">
         <x:v>syllogism</x:v>
@@ -48056,670 +48624,1228 @@
         <x:v>yes</x:v>
       </x:c>
       <x:c r="E205" s="33" t="str">
-        <x:v>Yes, all bloops must be lazzies.</x:v>
+        <x:v>\text{Yes, all bloops must be lazzies.}</x:v>
       </x:c>
       <x:c r="F205" s="33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="G205" s="35" t="n">
-        <x:v>8.902264708000075</x:v>
-      </x:c>
-      <x:c r="H205" s="33" t="str"/>
-      <x:c r="I205" s="33" t="str"/>
-      <x:c r="J205" s="33" t="str"/>
-      <x:c r="K205" s="33" t="str"/>
-      <x:c r="L205" s="33" t="str"/>
-      <x:c r="M205" s="33" t="str"/>
+        <x:v>2.540424041999813</x:v>
+      </x:c>
+      <x:c r="H205" s="33" t="str">
+        <x:v>boxed</x:v>
+      </x:c>
+      <x:c r="I205" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="J205" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="K205" s="33" t="str">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="L205" s="33" t="str">
+        <x:v>confidence_gate</x:v>
+      </x:c>
+      <x:c r="M205" s="33" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
       <x:c r="N205" s="33" t="str">
-        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
-      </x:c>
-      <x:c r="O205" s="31"/>
+        <x:v>\boxed|Final Answer|final answer</x:v>
+      </x:c>
+      <x:c r="O205" s="33" t="str">
+        <x:v>exact_qwen3_1_7b_hrm_chat_boxed_final_confidence.csv</x:v>
+      </x:c>
       <x:c r="P205" s="31"/>
       <x:c r="Q205" s="31"/>
     </x:row>
     <x:row r="206">
-      <x:c r="A206" s="31"/>
-      <x:c r="B206" s="31"/>
-      <x:c r="C206" s="31"/>
-      <x:c r="D206" s="31"/>
-      <x:c r="E206" s="31"/>
-      <x:c r="F206" s="31"/>
-      <x:c r="G206" s="37"/>
-      <x:c r="H206" s="31"/>
-      <x:c r="I206" s="31"/>
-      <x:c r="J206" s="31"/>
-      <x:c r="K206" s="31"/>
-      <x:c r="L206" s="31"/>
-      <x:c r="M206" s="31"/>
-      <x:c r="N206" s="31"/>
-      <x:c r="O206" s="31"/>
+      <x:c r="A206" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B206" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C206" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D206" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E206" s="33" t="str">
+        <x:v>\dfrac{25}{2}</x:v>
+      </x:c>
+      <x:c r="F206" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G206" s="35" t="n">
+        <x:v>7.580443959000007</x:v>
+      </x:c>
+      <x:c r="H206" s="33" t="str"/>
+      <x:c r="I206" s="33" t="str"/>
+      <x:c r="J206" s="33" t="str"/>
+      <x:c r="K206" s="33" t="str"/>
+      <x:c r="L206" s="33" t="str"/>
+      <x:c r="M206" s="33" t="str"/>
+      <x:c r="N206" s="33" t="str"/>
+      <x:c r="O206" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P206" s="31"/>
       <x:c r="Q206" s="31"/>
     </x:row>
     <x:row r="207">
-      <x:c r="A207" s="31"/>
-      <x:c r="B207" s="31"/>
-      <x:c r="C207" s="31"/>
-      <x:c r="D207" s="31"/>
-      <x:c r="E207" s="31"/>
-      <x:c r="F207" s="31"/>
-      <x:c r="G207" s="37"/>
-      <x:c r="H207" s="31"/>
-      <x:c r="I207" s="31"/>
-      <x:c r="J207" s="31"/>
-      <x:c r="K207" s="31"/>
-      <x:c r="L207" s="31"/>
-      <x:c r="M207" s="31"/>
-      <x:c r="N207" s="31"/>
-      <x:c r="O207" s="31"/>
+      <x:c r="A207" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B207" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C207" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D207" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E207" s="33" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F207" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G207" s="35" t="n">
+        <x:v>6.407860625000012</x:v>
+      </x:c>
+      <x:c r="H207" s="33" t="str"/>
+      <x:c r="I207" s="33" t="str"/>
+      <x:c r="J207" s="33" t="str"/>
+      <x:c r="K207" s="33" t="str"/>
+      <x:c r="L207" s="33" t="str"/>
+      <x:c r="M207" s="33" t="str"/>
+      <x:c r="N207" s="33" t="str"/>
+      <x:c r="O207" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P207" s="31"/>
       <x:c r="Q207" s="31"/>
     </x:row>
     <x:row r="208">
-      <x:c r="A208" s="31"/>
-      <x:c r="B208" s="31"/>
-      <x:c r="C208" s="31"/>
-      <x:c r="D208" s="31"/>
-      <x:c r="E208" s="31"/>
-      <x:c r="F208" s="31"/>
-      <x:c r="G208" s="37"/>
-      <x:c r="H208" s="31"/>
-      <x:c r="I208" s="31"/>
-      <x:c r="J208" s="31"/>
-      <x:c r="K208" s="31"/>
-      <x:c r="L208" s="31"/>
-      <x:c r="M208" s="31"/>
-      <x:c r="N208" s="31"/>
-      <x:c r="O208" s="31"/>
+      <x:c r="A208" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B208" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C208" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D208" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E208" s="33" t="str">
+        <x:v>Mixed</x:v>
+      </x:c>
+      <x:c r="F208" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G208" s="35" t="n">
+        <x:v>6.2715228750000165</x:v>
+      </x:c>
+      <x:c r="H208" s="33" t="str"/>
+      <x:c r="I208" s="33" t="str"/>
+      <x:c r="J208" s="33" t="str"/>
+      <x:c r="K208" s="33" t="str"/>
+      <x:c r="L208" s="33" t="str"/>
+      <x:c r="M208" s="33" t="str"/>
+      <x:c r="N208" s="33" t="str"/>
+      <x:c r="O208" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P208" s="31"/>
       <x:c r="Q208" s="31"/>
     </x:row>
     <x:row r="209">
-      <x:c r="A209" s="31"/>
-      <x:c r="B209" s="31"/>
-      <x:c r="C209" s="31"/>
-      <x:c r="D209" s="31"/>
-      <x:c r="E209" s="31"/>
-      <x:c r="F209" s="31"/>
-      <x:c r="G209" s="37"/>
-      <x:c r="H209" s="31"/>
-      <x:c r="I209" s="31"/>
-      <x:c r="J209" s="31"/>
-      <x:c r="K209" s="31"/>
-      <x:c r="L209" s="31"/>
-      <x:c r="M209" s="31"/>
-      <x:c r="N209" s="31"/>
-      <x:c r="O209" s="31"/>
+      <x:c r="A209" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B209" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C209" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D209" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E209" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F209" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G209" s="35" t="n">
+        <x:v>4.775222624999998</x:v>
+      </x:c>
+      <x:c r="H209" s="33" t="str"/>
+      <x:c r="I209" s="33" t="str"/>
+      <x:c r="J209" s="33" t="str"/>
+      <x:c r="K209" s="33" t="str"/>
+      <x:c r="L209" s="33" t="str"/>
+      <x:c r="M209" s="33" t="str"/>
+      <x:c r="N209" s="33" t="str"/>
+      <x:c r="O209" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P209" s="31"/>
       <x:c r="Q209" s="31"/>
     </x:row>
     <x:row r="210">
-      <x:c r="A210" s="31"/>
-      <x:c r="B210" s="31"/>
-      <x:c r="C210" s="31"/>
-      <x:c r="D210" s="31"/>
-      <x:c r="E210" s="31"/>
-      <x:c r="F210" s="31"/>
-      <x:c r="G210" s="37"/>
-      <x:c r="H210" s="31"/>
-      <x:c r="I210" s="31"/>
-      <x:c r="J210" s="31"/>
-      <x:c r="K210" s="31"/>
-      <x:c r="L210" s="31"/>
-      <x:c r="M210" s="31"/>
-      <x:c r="N210" s="31"/>
-      <x:c r="O210" s="31"/>
+      <x:c r="A210" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B210" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C210" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D210" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E210" s="33" t="str">
+        <x:v>'- \(7^8 \equiv 9^2</x:v>
+      </x:c>
+      <x:c r="F210" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G210" s="35" t="n">
+        <x:v>14.03727679100001</x:v>
+      </x:c>
+      <x:c r="H210" s="33" t="str"/>
+      <x:c r="I210" s="33" t="str"/>
+      <x:c r="J210" s="33" t="str"/>
+      <x:c r="K210" s="33" t="str"/>
+      <x:c r="L210" s="33" t="str"/>
+      <x:c r="M210" s="33" t="str"/>
+      <x:c r="N210" s="33" t="str"/>
+      <x:c r="O210" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P210" s="31"/>
       <x:c r="Q210" s="31"/>
     </x:row>
     <x:row r="211">
-      <x:c r="A211" s="31"/>
-      <x:c r="B211" s="31"/>
-      <x:c r="C211" s="31"/>
-      <x:c r="D211" s="31"/>
-      <x:c r="E211" s="31"/>
-      <x:c r="F211" s="31"/>
-      <x:c r="G211" s="37"/>
-      <x:c r="H211" s="31"/>
-      <x:c r="I211" s="31"/>
-      <x:c r="J211" s="31"/>
-      <x:c r="K211" s="31"/>
-      <x:c r="L211" s="31"/>
-      <x:c r="M211" s="31"/>
-      <x:c r="N211" s="31"/>
-      <x:c r="O211" s="31"/>
+      <x:c r="A211" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B211" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C211" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D211" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E211" s="33" t="str">
+        <x:v>\dfrac{15}{4}</x:v>
+      </x:c>
+      <x:c r="F211" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G211" s="35" t="n">
+        <x:v>6.176148500000011</x:v>
+      </x:c>
+      <x:c r="H211" s="33" t="str"/>
+      <x:c r="I211" s="33" t="str"/>
+      <x:c r="J211" s="33" t="str"/>
+      <x:c r="K211" s="33" t="str"/>
+      <x:c r="L211" s="33" t="str"/>
+      <x:c r="M211" s="33" t="str"/>
+      <x:c r="N211" s="33" t="str"/>
+      <x:c r="O211" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P211" s="31"/>
       <x:c r="Q211" s="31"/>
     </x:row>
     <x:row r="212">
-      <x:c r="A212" s="31"/>
-      <x:c r="B212" s="31"/>
-      <x:c r="C212" s="31"/>
-      <x:c r="D212" s="31"/>
-      <x:c r="E212" s="31"/>
-      <x:c r="F212" s="31"/>
-      <x:c r="G212" s="37"/>
-      <x:c r="H212" s="31"/>
-      <x:c r="I212" s="31"/>
-      <x:c r="J212" s="31"/>
-      <x:c r="K212" s="31"/>
-      <x:c r="L212" s="31"/>
-      <x:c r="M212" s="31"/>
-      <x:c r="N212" s="31"/>
-      <x:c r="O212" s="31"/>
+      <x:c r="A212" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B212" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C212" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D212" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E212" s="33" t="str">
+        <x:v>\dfrac{1}{9}</x:v>
+      </x:c>
+      <x:c r="F212" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G212" s="35" t="n">
+        <x:v>4.10938950000002</x:v>
+      </x:c>
+      <x:c r="H212" s="33" t="str"/>
+      <x:c r="I212" s="33" t="str"/>
+      <x:c r="J212" s="33" t="str"/>
+      <x:c r="K212" s="33" t="str"/>
+      <x:c r="L212" s="33" t="str"/>
+      <x:c r="M212" s="33" t="str"/>
+      <x:c r="N212" s="33" t="str"/>
+      <x:c r="O212" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P212" s="31"/>
       <x:c r="Q212" s="31"/>
     </x:row>
     <x:row r="213">
-      <x:c r="A213" s="31"/>
-      <x:c r="B213" s="31"/>
-      <x:c r="C213" s="31"/>
-      <x:c r="D213" s="31"/>
-      <x:c r="E213" s="31"/>
-      <x:c r="F213" s="31"/>
-      <x:c r="G213" s="37"/>
-      <x:c r="H213" s="31"/>
-      <x:c r="I213" s="31"/>
-      <x:c r="J213" s="31"/>
-      <x:c r="K213" s="31"/>
-      <x:c r="L213" s="31"/>
-      <x:c r="M213" s="31"/>
-      <x:c r="N213" s="31"/>
-      <x:c r="O213" s="31"/>
+      <x:c r="A213" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B213" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C213" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D213" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E213" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F213" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G213" s="35" t="n">
+        <x:v>8.457965874999957</x:v>
+      </x:c>
+      <x:c r="H213" s="33" t="str"/>
+      <x:c r="I213" s="33" t="str"/>
+      <x:c r="J213" s="33" t="str"/>
+      <x:c r="K213" s="33" t="str"/>
+      <x:c r="L213" s="33" t="str"/>
+      <x:c r="M213" s="33" t="str"/>
+      <x:c r="N213" s="33" t="str"/>
+      <x:c r="O213" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P213" s="31"/>
       <x:c r="Q213" s="31"/>
     </x:row>
     <x:row r="214">
-      <x:c r="A214" s="31"/>
-      <x:c r="B214" s="31"/>
-      <x:c r="C214" s="31"/>
-      <x:c r="D214" s="31"/>
-      <x:c r="E214" s="31"/>
-      <x:c r="F214" s="31"/>
-      <x:c r="G214" s="37"/>
-      <x:c r="H214" s="31"/>
-      <x:c r="I214" s="31"/>
-      <x:c r="J214" s="31"/>
-      <x:c r="K214" s="31"/>
-      <x:c r="L214" s="31"/>
-      <x:c r="M214" s="31"/>
-      <x:c r="N214" s="31"/>
-      <x:c r="O214" s="31"/>
+      <x:c r="A214" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B214" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C214" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D214" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E214" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F214" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G214" s="35" t="n">
+        <x:v>4.77963704199999</x:v>
+      </x:c>
+      <x:c r="H214" s="33" t="str"/>
+      <x:c r="I214" s="33" t="str"/>
+      <x:c r="J214" s="33" t="str"/>
+      <x:c r="K214" s="33" t="str"/>
+      <x:c r="L214" s="33" t="str"/>
+      <x:c r="M214" s="33" t="str"/>
+      <x:c r="N214" s="33" t="str"/>
+      <x:c r="O214" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P214" s="31"/>
       <x:c r="Q214" s="31"/>
     </x:row>
     <x:row r="215">
-      <x:c r="A215" s="31"/>
-      <x:c r="B215" s="31"/>
-      <x:c r="C215" s="31"/>
-      <x:c r="D215" s="31"/>
-      <x:c r="E215" s="31"/>
-      <x:c r="F215" s="31"/>
-      <x:c r="G215" s="37"/>
-      <x:c r="H215" s="31"/>
-      <x:c r="I215" s="31"/>
-      <x:c r="J215" s="31"/>
-      <x:c r="K215" s="31"/>
-      <x:c r="L215" s="31"/>
-      <x:c r="M215" s="31"/>
-      <x:c r="N215" s="31"/>
-      <x:c r="O215" s="31"/>
+      <x:c r="A215" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B215" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C215" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D215" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E215" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F215" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G215" s="35" t="n">
+        <x:v>4.465110458999959</x:v>
+      </x:c>
+      <x:c r="H215" s="33" t="str"/>
+      <x:c r="I215" s="33" t="str"/>
+      <x:c r="J215" s="33" t="str"/>
+      <x:c r="K215" s="33" t="str"/>
+      <x:c r="L215" s="33" t="str"/>
+      <x:c r="M215" s="33" t="str"/>
+      <x:c r="N215" s="33" t="str"/>
+      <x:c r="O215" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P215" s="31"/>
       <x:c r="Q215" s="31"/>
     </x:row>
     <x:row r="216">
-      <x:c r="A216" s="31"/>
-      <x:c r="B216" s="31"/>
-      <x:c r="C216" s="31"/>
-      <x:c r="D216" s="31"/>
-      <x:c r="E216" s="31"/>
-      <x:c r="F216" s="31"/>
-      <x:c r="G216" s="37"/>
-      <x:c r="H216" s="31"/>
-      <x:c r="I216" s="31"/>
-      <x:c r="J216" s="31"/>
-      <x:c r="K216" s="31"/>
-      <x:c r="L216" s="31"/>
-      <x:c r="M216" s="31"/>
-      <x:c r="N216" s="31"/>
-      <x:c r="O216" s="31"/>
+      <x:c r="A216" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B216" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C216" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D216" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E216" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F216" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G216" s="35" t="n">
+        <x:v>4.0312850840000465</x:v>
+      </x:c>
+      <x:c r="H216" s="33" t="str"/>
+      <x:c r="I216" s="33" t="str"/>
+      <x:c r="J216" s="33" t="str"/>
+      <x:c r="K216" s="33" t="str"/>
+      <x:c r="L216" s="33" t="str"/>
+      <x:c r="M216" s="33" t="str"/>
+      <x:c r="N216" s="33" t="str"/>
+      <x:c r="O216" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P216" s="31"/>
       <x:c r="Q216" s="31"/>
     </x:row>
     <x:row r="217">
-      <x:c r="A217" s="31"/>
-      <x:c r="B217" s="31"/>
-      <x:c r="C217" s="31"/>
-      <x:c r="D217" s="31"/>
-      <x:c r="E217" s="31"/>
-      <x:c r="F217" s="31"/>
-      <x:c r="G217" s="37"/>
-      <x:c r="H217" s="31"/>
-      <x:c r="I217" s="31"/>
-      <x:c r="J217" s="31"/>
-      <x:c r="K217" s="31"/>
-      <x:c r="L217" s="31"/>
-      <x:c r="M217" s="31"/>
-      <x:c r="N217" s="31"/>
-      <x:c r="O217" s="31"/>
+      <x:c r="A217" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B217" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C217" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D217" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E217" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F217" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G217" s="35" t="n">
+        <x:v>4.098184124999989</x:v>
+      </x:c>
+      <x:c r="H217" s="33" t="str"/>
+      <x:c r="I217" s="33" t="str"/>
+      <x:c r="J217" s="33" t="str"/>
+      <x:c r="K217" s="33" t="str"/>
+      <x:c r="L217" s="33" t="str"/>
+      <x:c r="M217" s="33" t="str"/>
+      <x:c r="N217" s="33" t="str"/>
+      <x:c r="O217" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P217" s="31"/>
       <x:c r="Q217" s="31"/>
     </x:row>
     <x:row r="218">
-      <x:c r="A218" s="31"/>
-      <x:c r="B218" s="31"/>
-      <x:c r="C218" s="31"/>
-      <x:c r="D218" s="31"/>
-      <x:c r="E218" s="31"/>
-      <x:c r="F218" s="31"/>
-      <x:c r="G218" s="37"/>
-      <x:c r="H218" s="31"/>
-      <x:c r="I218" s="31"/>
-      <x:c r="J218" s="31"/>
-      <x:c r="K218" s="31"/>
-      <x:c r="L218" s="31"/>
-      <x:c r="M218" s="31"/>
-      <x:c r="N218" s="31"/>
-      <x:c r="O218" s="31"/>
+      <x:c r="A218" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B218" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C218" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D218" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E218" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F218" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G218" s="35" t="n">
+        <x:v>3.955258875000027</x:v>
+      </x:c>
+      <x:c r="H218" s="33" t="str"/>
+      <x:c r="I218" s="33" t="str"/>
+      <x:c r="J218" s="33" t="str"/>
+      <x:c r="K218" s="33" t="str"/>
+      <x:c r="L218" s="33" t="str"/>
+      <x:c r="M218" s="33" t="str"/>
+      <x:c r="N218" s="33" t="str"/>
+      <x:c r="O218" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P218" s="31"/>
       <x:c r="Q218" s="31"/>
     </x:row>
     <x:row r="219">
-      <x:c r="A219" s="31"/>
-      <x:c r="B219" s="31"/>
-      <x:c r="C219" s="31"/>
-      <x:c r="D219" s="31"/>
-      <x:c r="E219" s="31"/>
-      <x:c r="F219" s="31"/>
-      <x:c r="G219" s="37"/>
-      <x:c r="H219" s="31"/>
-      <x:c r="I219" s="31"/>
-      <x:c r="J219" s="31"/>
-      <x:c r="K219" s="31"/>
-      <x:c r="L219" s="31"/>
-      <x:c r="M219" s="31"/>
-      <x:c r="N219" s="31"/>
-      <x:c r="O219" s="31"/>
+      <x:c r="A219" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B219" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C219" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D219" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E219" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F219" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G219" s="35" t="n">
+        <x:v>6.499252583999976</x:v>
+      </x:c>
+      <x:c r="H219" s="33" t="str"/>
+      <x:c r="I219" s="33" t="str"/>
+      <x:c r="J219" s="33" t="str"/>
+      <x:c r="K219" s="33" t="str"/>
+      <x:c r="L219" s="33" t="str"/>
+      <x:c r="M219" s="33" t="str"/>
+      <x:c r="N219" s="33" t="str"/>
+      <x:c r="O219" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P219" s="31"/>
       <x:c r="Q219" s="31"/>
     </x:row>
     <x:row r="220">
-      <x:c r="A220" s="31"/>
-      <x:c r="B220" s="31"/>
-      <x:c r="C220" s="31"/>
-      <x:c r="D220" s="31"/>
-      <x:c r="E220" s="31"/>
-      <x:c r="F220" s="31"/>
-      <x:c r="G220" s="37"/>
-      <x:c r="H220" s="31"/>
-      <x:c r="I220" s="31"/>
-      <x:c r="J220" s="31"/>
-      <x:c r="K220" s="31"/>
-      <x:c r="L220" s="31"/>
-      <x:c r="M220" s="31"/>
-      <x:c r="N220" s="31"/>
-      <x:c r="O220" s="31"/>
+      <x:c r="A220" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B220" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C220" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D220" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E220" s="33" t="str">
+        <x:v>\dfrac{3}{8}</x:v>
+      </x:c>
+      <x:c r="F220" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G220" s="35" t="n">
+        <x:v>2.2782300830000395</x:v>
+      </x:c>
+      <x:c r="H220" s="33" t="str"/>
+      <x:c r="I220" s="33" t="str"/>
+      <x:c r="J220" s="33" t="str"/>
+      <x:c r="K220" s="33" t="str"/>
+      <x:c r="L220" s="33" t="str"/>
+      <x:c r="M220" s="33" t="str"/>
+      <x:c r="N220" s="33" t="str"/>
+      <x:c r="O220" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P220" s="31"/>
       <x:c r="Q220" s="31"/>
     </x:row>
     <x:row r="221">
-      <x:c r="A221" s="31"/>
-      <x:c r="B221" s="31"/>
-      <x:c r="C221" s="31"/>
-      <x:c r="D221" s="31"/>
-      <x:c r="E221" s="31"/>
-      <x:c r="F221" s="31"/>
-      <x:c r="G221" s="37"/>
-      <x:c r="H221" s="31"/>
-      <x:c r="I221" s="31"/>
-      <x:c r="J221" s="31"/>
-      <x:c r="K221" s="31"/>
-      <x:c r="L221" s="31"/>
-      <x:c r="M221" s="31"/>
-      <x:c r="N221" s="31"/>
-      <x:c r="O221" s="31"/>
+      <x:c r="A221" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B221" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C221" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D221" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E221" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F221" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G221" s="35" t="n">
+        <x:v>12.253404416999956</x:v>
+      </x:c>
+      <x:c r="H221" s="33" t="str"/>
+      <x:c r="I221" s="33" t="str"/>
+      <x:c r="J221" s="33" t="str"/>
+      <x:c r="K221" s="33" t="str"/>
+      <x:c r="L221" s="33" t="str"/>
+      <x:c r="M221" s="33" t="str"/>
+      <x:c r="N221" s="33" t="str"/>
+      <x:c r="O221" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P221" s="31"/>
       <x:c r="Q221" s="31"/>
     </x:row>
     <x:row r="222">
-      <x:c r="A222" s="31"/>
-      <x:c r="B222" s="31"/>
-      <x:c r="C222" s="31"/>
-      <x:c r="D222" s="31"/>
-      <x:c r="E222" s="31"/>
-      <x:c r="F222" s="31"/>
-      <x:c r="G222" s="37"/>
-      <x:c r="H222" s="31"/>
-      <x:c r="I222" s="31"/>
-      <x:c r="J222" s="31"/>
-      <x:c r="K222" s="31"/>
-      <x:c r="L222" s="31"/>
-      <x:c r="M222" s="31"/>
-      <x:c r="N222" s="31"/>
-      <x:c r="O222" s="31"/>
+      <x:c r="A222" s="33" t="str">
+        <x:v>HRM-Text-1B MLX 4-bit</x:v>
+      </x:c>
+      <x:c r="B222" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C222" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D222" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E222" s="33" t="str">
+        <x:v>Yes, all bloops must be lazzies.</x:v>
+      </x:c>
+      <x:c r="F222" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G222" s="35" t="n">
+        <x:v>4.511834166999961</x:v>
+      </x:c>
+      <x:c r="H222" s="33" t="str"/>
+      <x:c r="I222" s="33" t="str"/>
+      <x:c r="J222" s="33" t="str"/>
+      <x:c r="K222" s="33" t="str"/>
+      <x:c r="L222" s="33" t="str"/>
+      <x:c r="M222" s="33" t="str"/>
+      <x:c r="N222" s="33" t="str"/>
+      <x:c r="O222" s="33" t="str">
+        <x:v>exact_hrm_text_1b_4bit_corrected.csv</x:v>
+      </x:c>
       <x:c r="P222" s="31"/>
       <x:c r="Q222" s="31"/>
     </x:row>
     <x:row r="223">
-      <x:c r="A223" s="31"/>
-      <x:c r="B223" s="31"/>
-      <x:c r="C223" s="31"/>
-      <x:c r="D223" s="31"/>
-      <x:c r="E223" s="31"/>
-      <x:c r="F223" s="31"/>
-      <x:c r="G223" s="37"/>
-      <x:c r="H223" s="31"/>
-      <x:c r="I223" s="31"/>
-      <x:c r="J223" s="31"/>
-      <x:c r="K223" s="31"/>
-      <x:c r="L223" s="31"/>
-      <x:c r="M223" s="31"/>
-      <x:c r="N223" s="31"/>
-      <x:c r="O223" s="31"/>
+      <x:c r="A223" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B223" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C223" s="33" t="str">
+        <x:v>algebra</x:v>
+      </x:c>
+      <x:c r="D223" s="33" t="str">
+        <x:v>12.5|25/2</x:v>
+      </x:c>
+      <x:c r="E223" s="33" t="str">
+        <x:v>\dfrac{25}{2}</x:v>
+      </x:c>
+      <x:c r="F223" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G223" s="35" t="n">
+        <x:v>16.656210082999962</x:v>
+      </x:c>
+      <x:c r="H223" s="33" t="str"/>
+      <x:c r="I223" s="33" t="str"/>
+      <x:c r="J223" s="33" t="str"/>
+      <x:c r="K223" s="33" t="str"/>
+      <x:c r="L223" s="33" t="str"/>
+      <x:c r="M223" s="33" t="str"/>
+      <x:c r="N223" s="33" t="str"/>
+      <x:c r="O223" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P223" s="31"/>
       <x:c r="Q223" s="31"/>
     </x:row>
     <x:row r="224">
-      <x:c r="A224" s="31"/>
-      <x:c r="B224" s="31"/>
-      <x:c r="C224" s="31"/>
-      <x:c r="D224" s="31"/>
-      <x:c r="E224" s="31"/>
-      <x:c r="F224" s="31"/>
-      <x:c r="G224" s="37"/>
-      <x:c r="H224" s="31"/>
-      <x:c r="I224" s="31"/>
-      <x:c r="J224" s="31"/>
-      <x:c r="K224" s="31"/>
-      <x:c r="L224" s="31"/>
-      <x:c r="M224" s="31"/>
-      <x:c r="N224" s="31"/>
-      <x:c r="O224" s="31"/>
+      <x:c r="A224" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B224" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C224" s="33" t="str">
+        <x:v>markup</x:v>
+      </x:c>
+      <x:c r="D224" s="33" t="str">
+        <x:v>96|$96</x:v>
+      </x:c>
+      <x:c r="E224" s="33" t="str">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="F224" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G224" s="35" t="n">
+        <x:v>12.64156225000005</x:v>
+      </x:c>
+      <x:c r="H224" s="33" t="str"/>
+      <x:c r="I224" s="33" t="str"/>
+      <x:c r="J224" s="33" t="str"/>
+      <x:c r="K224" s="33" t="str"/>
+      <x:c r="L224" s="33" t="str"/>
+      <x:c r="M224" s="33" t="str"/>
+      <x:c r="N224" s="33" t="str"/>
+      <x:c r="O224" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P224" s="31"/>
       <x:c r="Q224" s="31"/>
     </x:row>
     <x:row r="225">
-      <x:c r="A225" s="31"/>
-      <x:c r="B225" s="31"/>
-      <x:c r="C225" s="31"/>
-      <x:c r="D225" s="31"/>
-      <x:c r="E225" s="31"/>
-      <x:c r="F225" s="31"/>
-      <x:c r="G225" s="37"/>
-      <x:c r="H225" s="31"/>
-      <x:c r="I225" s="31"/>
-      <x:c r="J225" s="31"/>
-      <x:c r="K225" s="31"/>
-      <x:c r="L225" s="31"/>
-      <x:c r="M225" s="31"/>
-      <x:c r="N225" s="31"/>
-      <x:c r="O225" s="31"/>
+      <x:c r="A225" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B225" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C225" s="33" t="str">
+        <x:v>boxes</x:v>
+      </x:c>
+      <x:c r="D225" s="33" t="str">
+        <x:v>mixed|Mixed</x:v>
+      </x:c>
+      <x:c r="E225" s="33" t="str">
+        <x:v>**Final Answer**: The fruit is drawn from the **Mixed** box.</x:v>
+      </x:c>
+      <x:c r="F225" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G225" s="35" t="n">
+        <x:v>19.97141316599999</x:v>
+      </x:c>
+      <x:c r="H225" s="33" t="str"/>
+      <x:c r="I225" s="33" t="str"/>
+      <x:c r="J225" s="33" t="str"/>
+      <x:c r="K225" s="33" t="str"/>
+      <x:c r="L225" s="33" t="str"/>
+      <x:c r="M225" s="33" t="str"/>
+      <x:c r="N225" s="33" t="str"/>
+      <x:c r="O225" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P225" s="31"/>
       <x:c r="Q225" s="31"/>
     </x:row>
     <x:row r="226">
-      <x:c r="A226" s="31"/>
-      <x:c r="B226" s="31"/>
-      <x:c r="C226" s="31"/>
-      <x:c r="D226" s="31"/>
-      <x:c r="E226" s="31"/>
-      <x:c r="F226" s="31"/>
-      <x:c r="G226" s="37"/>
-      <x:c r="H226" s="31"/>
-      <x:c r="I226" s="31"/>
-      <x:c r="J226" s="31"/>
-      <x:c r="K226" s="31"/>
-      <x:c r="L226" s="31"/>
-      <x:c r="M226" s="31"/>
-      <x:c r="N226" s="31"/>
-      <x:c r="O226" s="31"/>
+      <x:c r="A226" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B226" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C226" s="33" t="str">
+        <x:v>inclusion</x:v>
+      </x:c>
+      <x:c r="D226" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E226" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F226" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G226" s="35" t="n">
+        <x:v>12.902716834000046</x:v>
+      </x:c>
+      <x:c r="H226" s="33" t="str"/>
+      <x:c r="I226" s="33" t="str"/>
+      <x:c r="J226" s="33" t="str"/>
+      <x:c r="K226" s="33" t="str"/>
+      <x:c r="L226" s="33" t="str"/>
+      <x:c r="M226" s="33" t="str"/>
+      <x:c r="N226" s="33" t="str"/>
+      <x:c r="O226" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P226" s="31"/>
       <x:c r="Q226" s="31"/>
     </x:row>
     <x:row r="227">
-      <x:c r="A227" s="31"/>
-      <x:c r="B227" s="31"/>
-      <x:c r="C227" s="31"/>
-      <x:c r="D227" s="31"/>
-      <x:c r="E227" s="31"/>
-      <x:c r="F227" s="31"/>
-      <x:c r="G227" s="37"/>
-      <x:c r="H227" s="31"/>
-      <x:c r="I227" s="31"/>
-      <x:c r="J227" s="31"/>
-      <x:c r="K227" s="31"/>
-      <x:c r="L227" s="31"/>
-      <x:c r="M227" s="31"/>
-      <x:c r="N227" s="31"/>
-      <x:c r="O227" s="31"/>
+      <x:c r="A227" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B227" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C227" s="33" t="str">
+        <x:v>modular</x:v>
+      </x:c>
+      <x:c r="D227" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E227" s="33" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F227" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G227" s="35" t="n">
+        <x:v>50.31506079099995</x:v>
+      </x:c>
+      <x:c r="H227" s="33" t="str"/>
+      <x:c r="I227" s="33" t="str"/>
+      <x:c r="J227" s="33" t="str"/>
+      <x:c r="K227" s="33" t="str"/>
+      <x:c r="L227" s="33" t="str"/>
+      <x:c r="M227" s="33" t="str"/>
+      <x:c r="N227" s="33" t="str"/>
+      <x:c r="O227" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P227" s="31"/>
       <x:c r="Q227" s="31"/>
     </x:row>
     <x:row r="228">
-      <x:c r="A228" s="31"/>
-      <x:c r="B228" s="31"/>
-      <x:c r="C228" s="31"/>
-      <x:c r="D228" s="31"/>
-      <x:c r="E228" s="31"/>
-      <x:c r="F228" s="31"/>
-      <x:c r="G228" s="37"/>
-      <x:c r="H228" s="31"/>
-      <x:c r="I228" s="31"/>
-      <x:c r="J228" s="31"/>
-      <x:c r="K228" s="31"/>
-      <x:c r="L228" s="31"/>
-      <x:c r="M228" s="31"/>
-      <x:c r="N228" s="31"/>
-      <x:c r="O228" s="31"/>
+      <x:c r="A228" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B228" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C228" s="33" t="str">
+        <x:v>work_rate</x:v>
+      </x:c>
+      <x:c r="D228" s="33" t="str">
+        <x:v>3.75|15/4</x:v>
+      </x:c>
+      <x:c r="E228" s="33" t="str">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="F228" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G228" s="35" t="n">
+        <x:v>33.462693083999966</x:v>
+      </x:c>
+      <x:c r="H228" s="33" t="str"/>
+      <x:c r="I228" s="33" t="str"/>
+      <x:c r="J228" s="33" t="str"/>
+      <x:c r="K228" s="33" t="str"/>
+      <x:c r="L228" s="33" t="str"/>
+      <x:c r="M228" s="33" t="str"/>
+      <x:c r="N228" s="33" t="str"/>
+      <x:c r="O228" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P228" s="31"/>
       <x:c r="Q228" s="31"/>
     </x:row>
     <x:row r="229">
-      <x:c r="A229" s="31"/>
-      <x:c r="B229" s="31"/>
-      <x:c r="C229" s="31"/>
-      <x:c r="D229" s="31"/>
-      <x:c r="E229" s="31"/>
-      <x:c r="F229" s="31"/>
-      <x:c r="G229" s="37"/>
-      <x:c r="H229" s="31"/>
-      <x:c r="I229" s="31"/>
-      <x:c r="J229" s="31"/>
-      <x:c r="K229" s="31"/>
-      <x:c r="L229" s="31"/>
-      <x:c r="M229" s="31"/>
-      <x:c r="N229" s="31"/>
-      <x:c r="O229" s="31"/>
+      <x:c r="A229" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B229" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C229" s="33" t="str">
+        <x:v>probability</x:v>
+      </x:c>
+      <x:c r="D229" s="33" t="str">
+        <x:v>1/9</x:v>
+      </x:c>
+      <x:c r="E229" s="33" t="str">
+        <x:v>\dfrac{1}{9}</x:v>
+      </x:c>
+      <x:c r="F229" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G229" s="35" t="n">
+        <x:v>7.085368707999919</x:v>
+      </x:c>
+      <x:c r="H229" s="33" t="str"/>
+      <x:c r="I229" s="33" t="str"/>
+      <x:c r="J229" s="33" t="str"/>
+      <x:c r="K229" s="33" t="str"/>
+      <x:c r="L229" s="33" t="str"/>
+      <x:c r="M229" s="33" t="str"/>
+      <x:c r="N229" s="33" t="str"/>
+      <x:c r="O229" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P229" s="31"/>
       <x:c r="Q229" s="31"/>
     </x:row>
     <x:row r="230">
-      <x:c r="A230" s="31"/>
-      <x:c r="B230" s="31"/>
-      <x:c r="C230" s="31"/>
-      <x:c r="D230" s="31"/>
-      <x:c r="E230" s="31"/>
-      <x:c r="F230" s="31"/>
-      <x:c r="G230" s="37"/>
-      <x:c r="H230" s="31"/>
-      <x:c r="I230" s="31"/>
-      <x:c r="J230" s="31"/>
-      <x:c r="K230" s="31"/>
-      <x:c r="L230" s="31"/>
-      <x:c r="M230" s="31"/>
-      <x:c r="N230" s="31"/>
-      <x:c r="O230" s="31"/>
+      <x:c r="A230" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B230" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C230" s="33" t="str">
+        <x:v>sequence</x:v>
+      </x:c>
+      <x:c r="D230" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E230" s="33" t="str">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F230" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G230" s="35" t="n">
+        <x:v>15.824353458000019</x:v>
+      </x:c>
+      <x:c r="H230" s="33" t="str"/>
+      <x:c r="I230" s="33" t="str"/>
+      <x:c r="J230" s="33" t="str"/>
+      <x:c r="K230" s="33" t="str"/>
+      <x:c r="L230" s="33" t="str"/>
+      <x:c r="M230" s="33" t="str"/>
+      <x:c r="N230" s="33" t="str"/>
+      <x:c r="O230" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P230" s="31"/>
       <x:c r="Q230" s="31"/>
     </x:row>
     <x:row r="231">
-      <x:c r="A231" s="31"/>
-      <x:c r="B231" s="31"/>
-      <x:c r="C231" s="31"/>
-      <x:c r="D231" s="31"/>
-      <x:c r="E231" s="31"/>
-      <x:c r="F231" s="31"/>
-      <x:c r="G231" s="37"/>
-      <x:c r="H231" s="31"/>
-      <x:c r="I231" s="31"/>
-      <x:c r="J231" s="31"/>
-      <x:c r="K231" s="31"/>
-      <x:c r="L231" s="31"/>
-      <x:c r="M231" s="31"/>
-      <x:c r="N231" s="31"/>
-      <x:c r="O231" s="31"/>
+      <x:c r="A231" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B231" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C231" s="33" t="str">
+        <x:v>linear_word</x:v>
+      </x:c>
+      <x:c r="D231" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E231" s="33" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F231" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G231" s="35" t="n">
+        <x:v>8.149854707999907</x:v>
+      </x:c>
+      <x:c r="H231" s="33" t="str"/>
+      <x:c r="I231" s="33" t="str"/>
+      <x:c r="J231" s="33" t="str"/>
+      <x:c r="K231" s="33" t="str"/>
+      <x:c r="L231" s="33" t="str"/>
+      <x:c r="M231" s="33" t="str"/>
+      <x:c r="N231" s="33" t="str"/>
+      <x:c r="O231" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P231" s="31"/>
       <x:c r="Q231" s="31"/>
     </x:row>
     <x:row r="232">
-      <x:c r="A232" s="31"/>
-      <x:c r="B232" s="31"/>
-      <x:c r="C232" s="31"/>
-      <x:c r="D232" s="31"/>
-      <x:c r="E232" s="31"/>
-      <x:c r="F232" s="31"/>
-      <x:c r="G232" s="37"/>
-      <x:c r="H232" s="31"/>
-      <x:c r="I232" s="31"/>
-      <x:c r="J232" s="31"/>
-      <x:c r="K232" s="31"/>
-      <x:c r="L232" s="31"/>
-      <x:c r="M232" s="31"/>
-      <x:c r="N232" s="31"/>
-      <x:c r="O232" s="31"/>
+      <x:c r="A232" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B232" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C232" s="33" t="str">
+        <x:v>reverse_discount</x:v>
+      </x:c>
+      <x:c r="D232" s="33" t="str">
+        <x:v>80|$80</x:v>
+      </x:c>
+      <x:c r="E232" s="33" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F232" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G232" s="35" t="n">
+        <x:v>6.157211500000017</x:v>
+      </x:c>
+      <x:c r="H232" s="33" t="str"/>
+      <x:c r="I232" s="33" t="str"/>
+      <x:c r="J232" s="33" t="str"/>
+      <x:c r="K232" s="33" t="str"/>
+      <x:c r="L232" s="33" t="str"/>
+      <x:c r="M232" s="33" t="str"/>
+      <x:c r="N232" s="33" t="str"/>
+      <x:c r="O232" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P232" s="31"/>
       <x:c r="Q232" s="31"/>
     </x:row>
     <x:row r="233">
-      <x:c r="A233" s="31"/>
-      <x:c r="B233" s="31"/>
-      <x:c r="C233" s="31"/>
-      <x:c r="D233" s="31"/>
-      <x:c r="E233" s="31"/>
-      <x:c r="F233" s="31"/>
-      <x:c r="G233" s="37"/>
-      <x:c r="H233" s="31"/>
-      <x:c r="I233" s="31"/>
-      <x:c r="J233" s="31"/>
-      <x:c r="K233" s="31"/>
-      <x:c r="L233" s="31"/>
-      <x:c r="M233" s="31"/>
-      <x:c r="N233" s="31"/>
-      <x:c r="O233" s="31"/>
+      <x:c r="A233" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B233" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C233" s="33" t="str">
+        <x:v>multiples</x:v>
+      </x:c>
+      <x:c r="D233" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E233" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F233" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G233" s="35" t="n">
+        <x:v>21.503388040999994</x:v>
+      </x:c>
+      <x:c r="H233" s="33" t="str"/>
+      <x:c r="I233" s="33" t="str"/>
+      <x:c r="J233" s="33" t="str"/>
+      <x:c r="K233" s="33" t="str"/>
+      <x:c r="L233" s="33" t="str"/>
+      <x:c r="M233" s="33" t="str"/>
+      <x:c r="N233" s="33" t="str"/>
+      <x:c r="O233" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P233" s="31"/>
       <x:c r="Q233" s="31"/>
     </x:row>
     <x:row r="234">
-      <x:c r="A234" s="31"/>
-      <x:c r="B234" s="31"/>
-      <x:c r="C234" s="31"/>
-      <x:c r="D234" s="31"/>
-      <x:c r="E234" s="31"/>
-      <x:c r="F234" s="31"/>
-      <x:c r="G234" s="37"/>
-      <x:c r="H234" s="31"/>
-      <x:c r="I234" s="31"/>
-      <x:c r="J234" s="31"/>
-      <x:c r="K234" s="31"/>
-      <x:c r="L234" s="31"/>
-      <x:c r="M234" s="31"/>
-      <x:c r="N234" s="31"/>
-      <x:c r="O234" s="31"/>
+      <x:c r="A234" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B234" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C234" s="33" t="str">
+        <x:v>rectangle</x:v>
+      </x:c>
+      <x:c r="D234" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E234" s="33" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F234" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G234" s="35" t="n">
+        <x:v>7.560139790999983</x:v>
+      </x:c>
+      <x:c r="H234" s="33" t="str"/>
+      <x:c r="I234" s="33" t="str"/>
+      <x:c r="J234" s="33" t="str"/>
+      <x:c r="K234" s="33" t="str"/>
+      <x:c r="L234" s="33" t="str"/>
+      <x:c r="M234" s="33" t="str"/>
+      <x:c r="N234" s="33" t="str"/>
+      <x:c r="O234" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P234" s="31"/>
       <x:c r="Q234" s="31"/>
     </x:row>
     <x:row r="235">
-      <x:c r="A235" s="31"/>
-      <x:c r="B235" s="31"/>
-      <x:c r="C235" s="31"/>
-      <x:c r="D235" s="31"/>
-      <x:c r="E235" s="31"/>
-      <x:c r="F235" s="31"/>
-      <x:c r="G235" s="37"/>
-      <x:c r="H235" s="31"/>
-      <x:c r="I235" s="31"/>
-      <x:c r="J235" s="31"/>
-      <x:c r="K235" s="31"/>
-      <x:c r="L235" s="31"/>
-      <x:c r="M235" s="31"/>
-      <x:c r="N235" s="31"/>
-      <x:c r="O235" s="31"/>
+      <x:c r="A235" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B235" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C235" s="33" t="str">
+        <x:v>average</x:v>
+      </x:c>
+      <x:c r="D235" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E235" s="33" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F235" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G235" s="35" t="n">
+        <x:v>8.231041165999955</x:v>
+      </x:c>
+      <x:c r="H235" s="33" t="str"/>
+      <x:c r="I235" s="33" t="str"/>
+      <x:c r="J235" s="33" t="str"/>
+      <x:c r="K235" s="33" t="str"/>
+      <x:c r="L235" s="33" t="str"/>
+      <x:c r="M235" s="33" t="str"/>
+      <x:c r="N235" s="33" t="str"/>
+      <x:c r="O235" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P235" s="31"/>
       <x:c r="Q235" s="31"/>
     </x:row>
     <x:row r="236">
-      <x:c r="A236" s="31"/>
-      <x:c r="B236" s="31"/>
-      <x:c r="C236" s="31"/>
-      <x:c r="D236" s="31"/>
-      <x:c r="E236" s="31"/>
-      <x:c r="F236" s="31"/>
-      <x:c r="G236" s="37"/>
-      <x:c r="H236" s="31"/>
-      <x:c r="I236" s="31"/>
-      <x:c r="J236" s="31"/>
-      <x:c r="K236" s="31"/>
-      <x:c r="L236" s="31"/>
-      <x:c r="M236" s="31"/>
-      <x:c r="N236" s="31"/>
-      <x:c r="O236" s="31"/>
+      <x:c r="A236" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B236" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C236" s="33" t="str">
+        <x:v>combinations</x:v>
+      </x:c>
+      <x:c r="D236" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E236" s="33" t="str">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F236" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G236" s="35" t="n">
+        <x:v>30.73365029099989</x:v>
+      </x:c>
+      <x:c r="H236" s="33" t="str"/>
+      <x:c r="I236" s="33" t="str"/>
+      <x:c r="J236" s="33" t="str"/>
+      <x:c r="K236" s="33" t="str"/>
+      <x:c r="L236" s="33" t="str"/>
+      <x:c r="M236" s="33" t="str"/>
+      <x:c r="N236" s="33" t="str"/>
+      <x:c r="O236" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P236" s="31"/>
       <x:c r="Q236" s="31"/>
     </x:row>
     <x:row r="237">
-      <x:c r="A237" s="31"/>
-      <x:c r="B237" s="31"/>
-      <x:c r="C237" s="31"/>
-      <x:c r="D237" s="31"/>
-      <x:c r="E237" s="31"/>
-      <x:c r="F237" s="31"/>
-      <x:c r="G237" s="37"/>
-      <x:c r="H237" s="31"/>
-      <x:c r="I237" s="31"/>
-      <x:c r="J237" s="31"/>
-      <x:c r="K237" s="31"/>
-      <x:c r="L237" s="31"/>
-      <x:c r="M237" s="31"/>
-      <x:c r="N237" s="31"/>
-      <x:c r="O237" s="31"/>
+      <x:c r="A237" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B237" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C237" s="33" t="str">
+        <x:v>coins</x:v>
+      </x:c>
+      <x:c r="D237" s="33" t="str">
+        <x:v>3/8</x:v>
+      </x:c>
+      <x:c r="E237" s="33" t="str">
+        <x:v>\dfrac{3}{8}</x:v>
+      </x:c>
+      <x:c r="F237" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G237" s="35" t="n">
+        <x:v>11.049620875000073</x:v>
+      </x:c>
+      <x:c r="H237" s="33" t="str"/>
+      <x:c r="I237" s="33" t="str"/>
+      <x:c r="J237" s="33" t="str"/>
+      <x:c r="K237" s="33" t="str"/>
+      <x:c r="L237" s="33" t="str"/>
+      <x:c r="M237" s="33" t="str"/>
+      <x:c r="N237" s="33" t="str"/>
+      <x:c r="O237" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P237" s="31"/>
       <x:c r="Q237" s="31"/>
     </x:row>
     <x:row r="238">
-      <x:c r="A238" s="31"/>
-      <x:c r="B238" s="31"/>
-      <x:c r="C238" s="31"/>
-      <x:c r="D238" s="31"/>
-      <x:c r="E238" s="31"/>
-      <x:c r="F238" s="31"/>
-      <x:c r="G238" s="37"/>
-      <x:c r="H238" s="31"/>
-      <x:c r="I238" s="31"/>
-      <x:c r="J238" s="31"/>
-      <x:c r="K238" s="31"/>
-      <x:c r="L238" s="31"/>
-      <x:c r="M238" s="31"/>
-      <x:c r="N238" s="31"/>
-      <x:c r="O238" s="31"/>
+      <x:c r="A238" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B238" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C238" s="33" t="str">
+        <x:v>modular_small</x:v>
+      </x:c>
+      <x:c r="D238" s="33" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E238" s="33" t="str">
+        <x:v>All methods confirm that the remainder when</x:v>
+      </x:c>
+      <x:c r="F238" s="33" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="G238" s="35" t="n">
+        <x:v>67.06586500000003</x:v>
+      </x:c>
+      <x:c r="H238" s="33" t="str"/>
+      <x:c r="I238" s="33" t="str"/>
+      <x:c r="J238" s="33" t="str"/>
+      <x:c r="K238" s="33" t="str"/>
+      <x:c r="L238" s="33" t="str"/>
+      <x:c r="M238" s="33" t="str"/>
+      <x:c r="N238" s="33" t="str"/>
+      <x:c r="O238" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P238" s="31"/>
       <x:c r="Q238" s="31"/>
     </x:row>
     <x:row r="239">
-      <x:c r="A239" s="31"/>
-      <x:c r="B239" s="31"/>
-      <x:c r="C239" s="31"/>
-      <x:c r="D239" s="31"/>
-      <x:c r="E239" s="31"/>
-      <x:c r="F239" s="31"/>
-      <x:c r="G239" s="37"/>
-      <x:c r="H239" s="31"/>
-      <x:c r="I239" s="31"/>
-      <x:c r="J239" s="31"/>
-      <x:c r="K239" s="31"/>
-      <x:c r="L239" s="31"/>
-      <x:c r="M239" s="31"/>
-      <x:c r="N239" s="31"/>
-      <x:c r="O239" s="31"/>
+      <x:c r="A239" s="33" t="str">
+        <x:v>HRM-Text-1B MLX BF16</x:v>
+      </x:c>
+      <x:c r="B239" s="33" t="str">
+        <x:v>HRM-Text</x:v>
+      </x:c>
+      <x:c r="C239" s="33" t="str">
+        <x:v>syllogism</x:v>
+      </x:c>
+      <x:c r="D239" s="33" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="E239" s="33" t="str">
+        <x:v>Yes, all bloops must be lazzies.</x:v>
+      </x:c>
+      <x:c r="F239" s="33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="G239" s="35" t="n">
+        <x:v>8.902264708000075</x:v>
+      </x:c>
+      <x:c r="H239" s="33" t="str"/>
+      <x:c r="I239" s="33" t="str"/>
+      <x:c r="J239" s="33" t="str"/>
+      <x:c r="K239" s="33" t="str"/>
+      <x:c r="L239" s="33" t="str"/>
+      <x:c r="M239" s="33" t="str"/>
+      <x:c r="N239" s="33" t="str"/>
+      <x:c r="O239" s="33" t="str">
+        <x:v>exact_hrm_text_1b_bf16_corrected.csv</x:v>
+      </x:c>
       <x:c r="P239" s="31"/>
       <x:c r="Q239" s="31"/>
     </x:row>
@@ -55933,10 +57059,10 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41" t="str">
-        <x:v>Candidate rerank</x:v>
+        <x:v>Delayed fusion</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>Saved-output candidate reranking found an 11/17 oracle union across raw/chat candidates, but naive yes/no and answer-likelihood rerankers selected only 6/17. Need a stronger verifier.</x:v>
+        <x:v>Final-answer-triggered HRM fusion also recovers the 6/17 base score on Qwen3-1.7B chat-template boxed runs. It is safer than full-sequence fixed blending but still not above base.</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="31"/>
@@ -55956,10 +57082,10 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="41" t="str">
-        <x:v>HRM-Text comparison</x:v>
+        <x:v>Candidate rerank</x:v>
       </x:c>
       <x:c r="B8" s="41" t="str">
-        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
+        <x:v>Saved-output candidate reranking found an 11/17 oracle union across raw/chat candidates, but naive yes/no and answer-likelihood rerankers selected only 6/17. Need a stronger verifier.</x:v>
       </x:c>
       <x:c r="C8" s="31"/>
       <x:c r="D8" s="31"/>
@@ -55979,10 +57105,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="41" t="str">
-        <x:v>Cost</x:v>
+        <x:v>HRM-Text comparison</x:v>
       </x:c>
       <x:c r="B9" s="41" t="str">
-        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
+        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
       </x:c>
       <x:c r="C9" s="31"/>
       <x:c r="D9" s="31"/>
@@ -56002,10 +57128,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="41" t="str">
-        <x:v>Correction</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
-        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
+        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
       </x:c>
       <x:c r="C10" s="31"/>
       <x:c r="D10" s="31"/>
@@ -56025,10 +57151,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="41" t="str">
-        <x:v>Interpretation</x:v>
+        <x:v>Correction</x:v>
       </x:c>
       <x:c r="B11" s="41" t="str">
-        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
+        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
       </x:c>
       <x:c r="C11" s="31"/>
       <x:c r="D11" s="31"/>
@@ -56048,10 +57174,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="41" t="str">
-        <x:v>Fusion finding</x:v>
+        <x:v>Interpretation</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
-        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
+        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
       </x:c>
       <x:c r="C12" s="31"/>
       <x:c r="D12" s="31"/>
@@ -56071,10 +57197,10 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="41" t="str">
-        <x:v>Next</x:v>
+        <x:v>Fusion finding</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
-        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
       </x:c>
       <x:c r="C13" s="31"/>
       <x:c r="D13" s="31"/>
@@ -56093,8 +57219,12 @@
       <x:c r="Q13" s="31"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="31"/>
-      <x:c r="B14" s="31"/>
+      <x:c r="A14" s="41" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="B14" s="41" t="str">
+        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+      </x:c>
       <x:c r="C14" s="31"/>
       <x:c r="D14" s="31"/>
       <x:c r="E14" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4dcd6149bf304bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R825037734988427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R7643abae0e2140f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="R6eea31d6cbe74055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R8075d1c4b2e24b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="Rdfa30bcb6d554c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R2b708adf3b1643dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="8" r:id="R0dfe31c3abcc4e26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5ea8e0be52154fe2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R4e0962bfe8f64468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R22ea8a6a15f848f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rec4894bd3c114b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R32a330b52c304f0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R79e54b233ded419a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R8c7f475fd7af43c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARC Runs" sheetId="8" r:id="Rc1acf40dc848486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" r:id="Rac6afbdc9add40da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56915,6 +56916,5816 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.610000133514404" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="4.789999961853027" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4.909999847412109" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="4.050000190734863" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="7.980000019073486" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="40.97999954223633" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="32" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>Split</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>Limit</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
+        <x:v>Mode</x:v>
+      </x:c>
+      <x:c r="E1" s="32" t="str">
+        <x:v>Fusion</x:v>
+      </x:c>
+      <x:c r="F1" s="32" t="str">
+        <x:v>Blend</x:v>
+      </x:c>
+      <x:c r="G1" s="32" t="str">
+        <x:v>Correct</x:v>
+      </x:c>
+      <x:c r="H1" s="32" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="I1" s="32" t="str">
+        <x:v>Accuracy</x:v>
+      </x:c>
+      <x:c r="J1" s="32" t="str">
+        <x:v>Elapsed s</x:v>
+      </x:c>
+      <x:c r="K1" s="32" t="str">
+        <x:v>Source</x:v>
+      </x:c>
+      <x:c r="L1" s="31"/>
+      <x:c r="M1" s="31"/>
+      <x:c r="N1" s="31"/>
+      <x:c r="O1" s="31"/>
+      <x:c r="P1" s="31"/>
+      <x:c r="Q1" s="31"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B2" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C2" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D2" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="E2" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F2" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="33" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H2" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I2" s="34" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="J2" s="35" t="n">
+        <x:v>7.229978584000037</x:v>
+      </x:c>
+      <x:c r="K2" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_base_validation50.csv</x:v>
+      </x:c>
+      <x:c r="L2" s="31"/>
+      <x:c r="M2" s="31"/>
+      <x:c r="N2" s="31"/>
+      <x:c r="O2" s="31"/>
+      <x:c r="P2" s="31"/>
+      <x:c r="Q2" s="31"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B3" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C3" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D3" s="33" t="str">
+        <x:v>hrm</x:v>
+      </x:c>
+      <x:c r="E3" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F3" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="G3" s="33" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H3" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I3" s="34" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="J3" s="35" t="n">
+        <x:v>20.041542333000052</x:v>
+      </x:c>
+      <x:c r="K3" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_hrm_validation50.csv</x:v>
+      </x:c>
+      <x:c r="L3" s="31"/>
+      <x:c r="M3" s="31"/>
+      <x:c r="N3" s="31"/>
+      <x:c r="O3" s="31"/>
+      <x:c r="P3" s="31"/>
+      <x:c r="Q3" s="31"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D4" s="33" t="str">
+        <x:v>hrm</x:v>
+      </x:c>
+      <x:c r="E4" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="F4" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="G4" s="33" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H4" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I4" s="34" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="J4" s="35" t="n">
+        <x:v>20.54996462500003</x:v>
+      </x:c>
+      <x:c r="K4" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_hrm_agreement_validation50.csv</x:v>
+      </x:c>
+      <x:c r="L4" s="31"/>
+      <x:c r="M4" s="31"/>
+      <x:c r="N4" s="31"/>
+      <x:c r="O4" s="31"/>
+      <x:c r="P4" s="31"/>
+      <x:c r="Q4" s="31"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="31"/>
+      <x:c r="B5" s="31"/>
+      <x:c r="C5" s="31"/>
+      <x:c r="D5" s="31"/>
+      <x:c r="E5" s="31"/>
+      <x:c r="F5" s="31"/>
+      <x:c r="G5" s="31"/>
+      <x:c r="H5" s="31"/>
+      <x:c r="I5" s="36"/>
+      <x:c r="J5" s="37"/>
+      <x:c r="K5" s="31"/>
+      <x:c r="L5" s="31"/>
+      <x:c r="M5" s="31"/>
+      <x:c r="N5" s="31"/>
+      <x:c r="O5" s="31"/>
+      <x:c r="P5" s="31"/>
+      <x:c r="Q5" s="31"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="31"/>
+      <x:c r="B6" s="31"/>
+      <x:c r="C6" s="31"/>
+      <x:c r="D6" s="31"/>
+      <x:c r="E6" s="31"/>
+      <x:c r="F6" s="31"/>
+      <x:c r="G6" s="31"/>
+      <x:c r="H6" s="31"/>
+      <x:c r="I6" s="36"/>
+      <x:c r="J6" s="37"/>
+      <x:c r="K6" s="31"/>
+      <x:c r="L6" s="31"/>
+      <x:c r="M6" s="31"/>
+      <x:c r="N6" s="31"/>
+      <x:c r="O6" s="31"/>
+      <x:c r="P6" s="31"/>
+      <x:c r="Q6" s="31"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="31"/>
+      <x:c r="B7" s="31"/>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="31"/>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="31"/>
+      <x:c r="H7" s="31"/>
+      <x:c r="I7" s="36"/>
+      <x:c r="J7" s="37"/>
+      <x:c r="K7" s="31"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="31"/>
+      <x:c r="N7" s="31"/>
+      <x:c r="O7" s="31"/>
+      <x:c r="P7" s="31"/>
+      <x:c r="Q7" s="31"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="31"/>
+      <x:c r="B8" s="31"/>
+      <x:c r="C8" s="31"/>
+      <x:c r="D8" s="31"/>
+      <x:c r="E8" s="31"/>
+      <x:c r="F8" s="31"/>
+      <x:c r="G8" s="31"/>
+      <x:c r="H8" s="31"/>
+      <x:c r="I8" s="36"/>
+      <x:c r="J8" s="37"/>
+      <x:c r="K8" s="31"/>
+      <x:c r="L8" s="31"/>
+      <x:c r="M8" s="31"/>
+      <x:c r="N8" s="31"/>
+      <x:c r="O8" s="31"/>
+      <x:c r="P8" s="31"/>
+      <x:c r="Q8" s="31"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="31"/>
+      <x:c r="B9" s="31"/>
+      <x:c r="C9" s="31"/>
+      <x:c r="D9" s="31"/>
+      <x:c r="E9" s="31"/>
+      <x:c r="F9" s="31"/>
+      <x:c r="G9" s="31"/>
+      <x:c r="H9" s="31"/>
+      <x:c r="I9" s="36"/>
+      <x:c r="J9" s="37"/>
+      <x:c r="K9" s="31"/>
+      <x:c r="L9" s="31"/>
+      <x:c r="M9" s="31"/>
+      <x:c r="N9" s="31"/>
+      <x:c r="O9" s="31"/>
+      <x:c r="P9" s="31"/>
+      <x:c r="Q9" s="31"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="31"/>
+      <x:c r="B10" s="31"/>
+      <x:c r="C10" s="31"/>
+      <x:c r="D10" s="31"/>
+      <x:c r="E10" s="31"/>
+      <x:c r="F10" s="31"/>
+      <x:c r="G10" s="31"/>
+      <x:c r="H10" s="31"/>
+      <x:c r="I10" s="36"/>
+      <x:c r="J10" s="37"/>
+      <x:c r="K10" s="31"/>
+      <x:c r="L10" s="31"/>
+      <x:c r="M10" s="31"/>
+      <x:c r="N10" s="31"/>
+      <x:c r="O10" s="31"/>
+      <x:c r="P10" s="31"/>
+      <x:c r="Q10" s="31"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="31"/>
+      <x:c r="B11" s="31"/>
+      <x:c r="C11" s="31"/>
+      <x:c r="D11" s="31"/>
+      <x:c r="E11" s="31"/>
+      <x:c r="F11" s="31"/>
+      <x:c r="G11" s="31"/>
+      <x:c r="H11" s="31"/>
+      <x:c r="I11" s="36"/>
+      <x:c r="J11" s="37"/>
+      <x:c r="K11" s="31"/>
+      <x:c r="L11" s="31"/>
+      <x:c r="M11" s="31"/>
+      <x:c r="N11" s="31"/>
+      <x:c r="O11" s="31"/>
+      <x:c r="P11" s="31"/>
+      <x:c r="Q11" s="31"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="31"/>
+      <x:c r="B12" s="31"/>
+      <x:c r="C12" s="31"/>
+      <x:c r="D12" s="31"/>
+      <x:c r="E12" s="31"/>
+      <x:c r="F12" s="31"/>
+      <x:c r="G12" s="31"/>
+      <x:c r="H12" s="31"/>
+      <x:c r="I12" s="36"/>
+      <x:c r="J12" s="37"/>
+      <x:c r="K12" s="31"/>
+      <x:c r="L12" s="31"/>
+      <x:c r="M12" s="31"/>
+      <x:c r="N12" s="31"/>
+      <x:c r="O12" s="31"/>
+      <x:c r="P12" s="31"/>
+      <x:c r="Q12" s="31"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="31"/>
+      <x:c r="B13" s="31"/>
+      <x:c r="C13" s="31"/>
+      <x:c r="D13" s="31"/>
+      <x:c r="E13" s="31"/>
+      <x:c r="F13" s="31"/>
+      <x:c r="G13" s="31"/>
+      <x:c r="H13" s="31"/>
+      <x:c r="I13" s="36"/>
+      <x:c r="J13" s="37"/>
+      <x:c r="K13" s="31"/>
+      <x:c r="L13" s="31"/>
+      <x:c r="M13" s="31"/>
+      <x:c r="N13" s="31"/>
+      <x:c r="O13" s="31"/>
+      <x:c r="P13" s="31"/>
+      <x:c r="Q13" s="31"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="31"/>
+      <x:c r="B14" s="31"/>
+      <x:c r="C14" s="31"/>
+      <x:c r="D14" s="31"/>
+      <x:c r="E14" s="31"/>
+      <x:c r="F14" s="31"/>
+      <x:c r="G14" s="31"/>
+      <x:c r="H14" s="31"/>
+      <x:c r="I14" s="36"/>
+      <x:c r="J14" s="37"/>
+      <x:c r="K14" s="31"/>
+      <x:c r="L14" s="31"/>
+      <x:c r="M14" s="31"/>
+      <x:c r="N14" s="31"/>
+      <x:c r="O14" s="31"/>
+      <x:c r="P14" s="31"/>
+      <x:c r="Q14" s="31"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="31"/>
+      <x:c r="B15" s="31"/>
+      <x:c r="C15" s="31"/>
+      <x:c r="D15" s="31"/>
+      <x:c r="E15" s="31"/>
+      <x:c r="F15" s="31"/>
+      <x:c r="G15" s="31"/>
+      <x:c r="H15" s="31"/>
+      <x:c r="I15" s="36"/>
+      <x:c r="J15" s="37"/>
+      <x:c r="K15" s="31"/>
+      <x:c r="L15" s="31"/>
+      <x:c r="M15" s="31"/>
+      <x:c r="N15" s="31"/>
+      <x:c r="O15" s="31"/>
+      <x:c r="P15" s="31"/>
+      <x:c r="Q15" s="31"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="31"/>
+      <x:c r="B16" s="31"/>
+      <x:c r="C16" s="31"/>
+      <x:c r="D16" s="31"/>
+      <x:c r="E16" s="31"/>
+      <x:c r="F16" s="31"/>
+      <x:c r="G16" s="31"/>
+      <x:c r="H16" s="31"/>
+      <x:c r="I16" s="36"/>
+      <x:c r="J16" s="37"/>
+      <x:c r="K16" s="31"/>
+      <x:c r="L16" s="31"/>
+      <x:c r="M16" s="31"/>
+      <x:c r="N16" s="31"/>
+      <x:c r="O16" s="31"/>
+      <x:c r="P16" s="31"/>
+      <x:c r="Q16" s="31"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="31"/>
+      <x:c r="B17" s="31"/>
+      <x:c r="C17" s="31"/>
+      <x:c r="D17" s="31"/>
+      <x:c r="E17" s="31"/>
+      <x:c r="F17" s="31"/>
+      <x:c r="G17" s="31"/>
+      <x:c r="H17" s="31"/>
+      <x:c r="I17" s="36"/>
+      <x:c r="J17" s="37"/>
+      <x:c r="K17" s="31"/>
+      <x:c r="L17" s="31"/>
+      <x:c r="M17" s="31"/>
+      <x:c r="N17" s="31"/>
+      <x:c r="O17" s="31"/>
+      <x:c r="P17" s="31"/>
+      <x:c r="Q17" s="31"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
+      <x:c r="G18" s="31"/>
+      <x:c r="H18" s="31"/>
+      <x:c r="I18" s="36"/>
+      <x:c r="J18" s="37"/>
+      <x:c r="K18" s="31"/>
+      <x:c r="L18" s="31"/>
+      <x:c r="M18" s="31"/>
+      <x:c r="N18" s="31"/>
+      <x:c r="O18" s="31"/>
+      <x:c r="P18" s="31"/>
+      <x:c r="Q18" s="31"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31"/>
+      <x:c r="B19" s="31"/>
+      <x:c r="C19" s="31"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="31"/>
+      <x:c r="F19" s="31"/>
+      <x:c r="G19" s="31"/>
+      <x:c r="H19" s="31"/>
+      <x:c r="I19" s="36"/>
+      <x:c r="J19" s="37"/>
+      <x:c r="K19" s="31"/>
+      <x:c r="L19" s="31"/>
+      <x:c r="M19" s="31"/>
+      <x:c r="N19" s="31"/>
+      <x:c r="O19" s="31"/>
+      <x:c r="P19" s="31"/>
+      <x:c r="Q19" s="31"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31"/>
+      <x:c r="B20" s="31"/>
+      <x:c r="C20" s="31"/>
+      <x:c r="D20" s="31"/>
+      <x:c r="E20" s="31"/>
+      <x:c r="F20" s="31"/>
+      <x:c r="G20" s="31"/>
+      <x:c r="H20" s="31"/>
+      <x:c r="I20" s="36"/>
+      <x:c r="J20" s="37"/>
+      <x:c r="K20" s="31"/>
+      <x:c r="L20" s="31"/>
+      <x:c r="M20" s="31"/>
+      <x:c r="N20" s="31"/>
+      <x:c r="O20" s="31"/>
+      <x:c r="P20" s="31"/>
+      <x:c r="Q20" s="31"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31"/>
+      <x:c r="B21" s="31"/>
+      <x:c r="C21" s="31"/>
+      <x:c r="D21" s="31"/>
+      <x:c r="E21" s="31"/>
+      <x:c r="F21" s="31"/>
+      <x:c r="G21" s="31"/>
+      <x:c r="H21" s="31"/>
+      <x:c r="I21" s="36"/>
+      <x:c r="J21" s="37"/>
+      <x:c r="K21" s="31"/>
+      <x:c r="L21" s="31"/>
+      <x:c r="M21" s="31"/>
+      <x:c r="N21" s="31"/>
+      <x:c r="O21" s="31"/>
+      <x:c r="P21" s="31"/>
+      <x:c r="Q21" s="31"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31"/>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+      <x:c r="F22" s="31"/>
+      <x:c r="G22" s="31"/>
+      <x:c r="H22" s="31"/>
+      <x:c r="I22" s="36"/>
+      <x:c r="J22" s="37"/>
+      <x:c r="K22" s="31"/>
+      <x:c r="L22" s="31"/>
+      <x:c r="M22" s="31"/>
+      <x:c r="N22" s="31"/>
+      <x:c r="O22" s="31"/>
+      <x:c r="P22" s="31"/>
+      <x:c r="Q22" s="31"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31"/>
+      <x:c r="B23" s="31"/>
+      <x:c r="C23" s="31"/>
+      <x:c r="D23" s="31"/>
+      <x:c r="E23" s="31"/>
+      <x:c r="F23" s="31"/>
+      <x:c r="G23" s="31"/>
+      <x:c r="H23" s="31"/>
+      <x:c r="I23" s="36"/>
+      <x:c r="J23" s="37"/>
+      <x:c r="K23" s="31"/>
+      <x:c r="L23" s="31"/>
+      <x:c r="M23" s="31"/>
+      <x:c r="N23" s="31"/>
+      <x:c r="O23" s="31"/>
+      <x:c r="P23" s="31"/>
+      <x:c r="Q23" s="31"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="31"/>
+      <x:c r="B24" s="31"/>
+      <x:c r="C24" s="31"/>
+      <x:c r="D24" s="31"/>
+      <x:c r="E24" s="31"/>
+      <x:c r="F24" s="31"/>
+      <x:c r="G24" s="31"/>
+      <x:c r="H24" s="31"/>
+      <x:c r="I24" s="36"/>
+      <x:c r="J24" s="37"/>
+      <x:c r="K24" s="31"/>
+      <x:c r="L24" s="31"/>
+      <x:c r="M24" s="31"/>
+      <x:c r="N24" s="31"/>
+      <x:c r="O24" s="31"/>
+      <x:c r="P24" s="31"/>
+      <x:c r="Q24" s="31"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31"/>
+      <x:c r="B25" s="31"/>
+      <x:c r="C25" s="31"/>
+      <x:c r="D25" s="31"/>
+      <x:c r="E25" s="31"/>
+      <x:c r="F25" s="31"/>
+      <x:c r="G25" s="31"/>
+      <x:c r="H25" s="31"/>
+      <x:c r="I25" s="36"/>
+      <x:c r="J25" s="37"/>
+      <x:c r="K25" s="31"/>
+      <x:c r="L25" s="31"/>
+      <x:c r="M25" s="31"/>
+      <x:c r="N25" s="31"/>
+      <x:c r="O25" s="31"/>
+      <x:c r="P25" s="31"/>
+      <x:c r="Q25" s="31"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31"/>
+      <x:c r="B26" s="31"/>
+      <x:c r="C26" s="31"/>
+      <x:c r="D26" s="31"/>
+      <x:c r="E26" s="31"/>
+      <x:c r="F26" s="31"/>
+      <x:c r="G26" s="31"/>
+      <x:c r="H26" s="31"/>
+      <x:c r="I26" s="36"/>
+      <x:c r="J26" s="37"/>
+      <x:c r="K26" s="31"/>
+      <x:c r="L26" s="31"/>
+      <x:c r="M26" s="31"/>
+      <x:c r="N26" s="31"/>
+      <x:c r="O26" s="31"/>
+      <x:c r="P26" s="31"/>
+      <x:c r="Q26" s="31"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+      <x:c r="F27" s="31"/>
+      <x:c r="G27" s="31"/>
+      <x:c r="H27" s="31"/>
+      <x:c r="I27" s="36"/>
+      <x:c r="J27" s="37"/>
+      <x:c r="K27" s="31"/>
+      <x:c r="L27" s="31"/>
+      <x:c r="M27" s="31"/>
+      <x:c r="N27" s="31"/>
+      <x:c r="O27" s="31"/>
+      <x:c r="P27" s="31"/>
+      <x:c r="Q27" s="31"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="31"/>
+      <x:c r="B28" s="31"/>
+      <x:c r="C28" s="31"/>
+      <x:c r="D28" s="31"/>
+      <x:c r="E28" s="31"/>
+      <x:c r="F28" s="31"/>
+      <x:c r="G28" s="31"/>
+      <x:c r="H28" s="31"/>
+      <x:c r="I28" s="36"/>
+      <x:c r="J28" s="37"/>
+      <x:c r="K28" s="31"/>
+      <x:c r="L28" s="31"/>
+      <x:c r="M28" s="31"/>
+      <x:c r="N28" s="31"/>
+      <x:c r="O28" s="31"/>
+      <x:c r="P28" s="31"/>
+      <x:c r="Q28" s="31"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="31"/>
+      <x:c r="B29" s="31"/>
+      <x:c r="C29" s="31"/>
+      <x:c r="D29" s="31"/>
+      <x:c r="E29" s="31"/>
+      <x:c r="F29" s="31"/>
+      <x:c r="G29" s="31"/>
+      <x:c r="H29" s="31"/>
+      <x:c r="I29" s="36"/>
+      <x:c r="J29" s="37"/>
+      <x:c r="K29" s="31"/>
+      <x:c r="L29" s="31"/>
+      <x:c r="M29" s="31"/>
+      <x:c r="N29" s="31"/>
+      <x:c r="O29" s="31"/>
+      <x:c r="P29" s="31"/>
+      <x:c r="Q29" s="31"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31"/>
+      <x:c r="B30" s="31"/>
+      <x:c r="C30" s="31"/>
+      <x:c r="D30" s="31"/>
+      <x:c r="E30" s="31"/>
+      <x:c r="F30" s="31"/>
+      <x:c r="G30" s="31"/>
+      <x:c r="H30" s="31"/>
+      <x:c r="I30" s="36"/>
+      <x:c r="J30" s="37"/>
+      <x:c r="K30" s="31"/>
+      <x:c r="L30" s="31"/>
+      <x:c r="M30" s="31"/>
+      <x:c r="N30" s="31"/>
+      <x:c r="O30" s="31"/>
+      <x:c r="P30" s="31"/>
+      <x:c r="Q30" s="31"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31"/>
+      <x:c r="B31" s="31"/>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
+      <x:c r="E31" s="31"/>
+      <x:c r="F31" s="31"/>
+      <x:c r="G31" s="31"/>
+      <x:c r="H31" s="31"/>
+      <x:c r="I31" s="36"/>
+      <x:c r="J31" s="37"/>
+      <x:c r="K31" s="31"/>
+      <x:c r="L31" s="31"/>
+      <x:c r="M31" s="31"/>
+      <x:c r="N31" s="31"/>
+      <x:c r="O31" s="31"/>
+      <x:c r="P31" s="31"/>
+      <x:c r="Q31" s="31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="31"/>
+      <x:c r="B32" s="31"/>
+      <x:c r="C32" s="31"/>
+      <x:c r="D32" s="31"/>
+      <x:c r="E32" s="31"/>
+      <x:c r="F32" s="31"/>
+      <x:c r="G32" s="31"/>
+      <x:c r="H32" s="31"/>
+      <x:c r="I32" s="36"/>
+      <x:c r="J32" s="37"/>
+      <x:c r="K32" s="31"/>
+      <x:c r="L32" s="31"/>
+      <x:c r="M32" s="31"/>
+      <x:c r="N32" s="31"/>
+      <x:c r="O32" s="31"/>
+      <x:c r="P32" s="31"/>
+      <x:c r="Q32" s="31"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31"/>
+      <x:c r="B33" s="31"/>
+      <x:c r="C33" s="31"/>
+      <x:c r="D33" s="31"/>
+      <x:c r="E33" s="31"/>
+      <x:c r="F33" s="31"/>
+      <x:c r="G33" s="31"/>
+      <x:c r="H33" s="31"/>
+      <x:c r="I33" s="36"/>
+      <x:c r="J33" s="37"/>
+      <x:c r="K33" s="31"/>
+      <x:c r="L33" s="31"/>
+      <x:c r="M33" s="31"/>
+      <x:c r="N33" s="31"/>
+      <x:c r="O33" s="31"/>
+      <x:c r="P33" s="31"/>
+      <x:c r="Q33" s="31"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="31"/>
+      <x:c r="B34" s="31"/>
+      <x:c r="C34" s="31"/>
+      <x:c r="D34" s="31"/>
+      <x:c r="E34" s="31"/>
+      <x:c r="F34" s="31"/>
+      <x:c r="G34" s="31"/>
+      <x:c r="H34" s="31"/>
+      <x:c r="I34" s="36"/>
+      <x:c r="J34" s="37"/>
+      <x:c r="K34" s="31"/>
+      <x:c r="L34" s="31"/>
+      <x:c r="M34" s="31"/>
+      <x:c r="N34" s="31"/>
+      <x:c r="O34" s="31"/>
+      <x:c r="P34" s="31"/>
+      <x:c r="Q34" s="31"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31"/>
+      <x:c r="B35" s="31"/>
+      <x:c r="C35" s="31"/>
+      <x:c r="D35" s="31"/>
+      <x:c r="E35" s="31"/>
+      <x:c r="F35" s="31"/>
+      <x:c r="G35" s="31"/>
+      <x:c r="H35" s="31"/>
+      <x:c r="I35" s="36"/>
+      <x:c r="J35" s="37"/>
+      <x:c r="K35" s="31"/>
+      <x:c r="L35" s="31"/>
+      <x:c r="M35" s="31"/>
+      <x:c r="N35" s="31"/>
+      <x:c r="O35" s="31"/>
+      <x:c r="P35" s="31"/>
+      <x:c r="Q35" s="31"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31"/>
+      <x:c r="B36" s="31"/>
+      <x:c r="C36" s="31"/>
+      <x:c r="D36" s="31"/>
+      <x:c r="E36" s="31"/>
+      <x:c r="F36" s="31"/>
+      <x:c r="G36" s="31"/>
+      <x:c r="H36" s="31"/>
+      <x:c r="I36" s="36"/>
+      <x:c r="J36" s="37"/>
+      <x:c r="K36" s="31"/>
+      <x:c r="L36" s="31"/>
+      <x:c r="M36" s="31"/>
+      <x:c r="N36" s="31"/>
+      <x:c r="O36" s="31"/>
+      <x:c r="P36" s="31"/>
+      <x:c r="Q36" s="31"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="31"/>
+      <x:c r="B37" s="31"/>
+      <x:c r="C37" s="31"/>
+      <x:c r="D37" s="31"/>
+      <x:c r="E37" s="31"/>
+      <x:c r="F37" s="31"/>
+      <x:c r="G37" s="31"/>
+      <x:c r="H37" s="31"/>
+      <x:c r="I37" s="36"/>
+      <x:c r="J37" s="37"/>
+      <x:c r="K37" s="31"/>
+      <x:c r="L37" s="31"/>
+      <x:c r="M37" s="31"/>
+      <x:c r="N37" s="31"/>
+      <x:c r="O37" s="31"/>
+      <x:c r="P37" s="31"/>
+      <x:c r="Q37" s="31"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31"/>
+      <x:c r="B38" s="31"/>
+      <x:c r="C38" s="31"/>
+      <x:c r="D38" s="31"/>
+      <x:c r="E38" s="31"/>
+      <x:c r="F38" s="31"/>
+      <x:c r="G38" s="31"/>
+      <x:c r="H38" s="31"/>
+      <x:c r="I38" s="36"/>
+      <x:c r="J38" s="37"/>
+      <x:c r="K38" s="31"/>
+      <x:c r="L38" s="31"/>
+      <x:c r="M38" s="31"/>
+      <x:c r="N38" s="31"/>
+      <x:c r="O38" s="31"/>
+      <x:c r="P38" s="31"/>
+      <x:c r="Q38" s="31"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31"/>
+      <x:c r="B39" s="31"/>
+      <x:c r="C39" s="31"/>
+      <x:c r="D39" s="31"/>
+      <x:c r="E39" s="31"/>
+      <x:c r="F39" s="31"/>
+      <x:c r="G39" s="31"/>
+      <x:c r="H39" s="31"/>
+      <x:c r="I39" s="36"/>
+      <x:c r="J39" s="37"/>
+      <x:c r="K39" s="31"/>
+      <x:c r="L39" s="31"/>
+      <x:c r="M39" s="31"/>
+      <x:c r="N39" s="31"/>
+      <x:c r="O39" s="31"/>
+      <x:c r="P39" s="31"/>
+      <x:c r="Q39" s="31"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31"/>
+      <x:c r="B40" s="31"/>
+      <x:c r="C40" s="31"/>
+      <x:c r="D40" s="31"/>
+      <x:c r="E40" s="31"/>
+      <x:c r="F40" s="31"/>
+      <x:c r="G40" s="31"/>
+      <x:c r="H40" s="31"/>
+      <x:c r="I40" s="36"/>
+      <x:c r="J40" s="37"/>
+      <x:c r="K40" s="31"/>
+      <x:c r="L40" s="31"/>
+      <x:c r="M40" s="31"/>
+      <x:c r="N40" s="31"/>
+      <x:c r="O40" s="31"/>
+      <x:c r="P40" s="31"/>
+      <x:c r="Q40" s="31"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31"/>
+      <x:c r="B41" s="31"/>
+      <x:c r="C41" s="31"/>
+      <x:c r="D41" s="31"/>
+      <x:c r="E41" s="31"/>
+      <x:c r="F41" s="31"/>
+      <x:c r="G41" s="31"/>
+      <x:c r="H41" s="31"/>
+      <x:c r="I41" s="36"/>
+      <x:c r="J41" s="37"/>
+      <x:c r="K41" s="31"/>
+      <x:c r="L41" s="31"/>
+      <x:c r="M41" s="31"/>
+      <x:c r="N41" s="31"/>
+      <x:c r="O41" s="31"/>
+      <x:c r="P41" s="31"/>
+      <x:c r="Q41" s="31"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31"/>
+      <x:c r="B42" s="31"/>
+      <x:c r="C42" s="31"/>
+      <x:c r="D42" s="31"/>
+      <x:c r="E42" s="31"/>
+      <x:c r="F42" s="31"/>
+      <x:c r="G42" s="31"/>
+      <x:c r="H42" s="31"/>
+      <x:c r="I42" s="36"/>
+      <x:c r="J42" s="37"/>
+      <x:c r="K42" s="31"/>
+      <x:c r="L42" s="31"/>
+      <x:c r="M42" s="31"/>
+      <x:c r="N42" s="31"/>
+      <x:c r="O42" s="31"/>
+      <x:c r="P42" s="31"/>
+      <x:c r="Q42" s="31"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31"/>
+      <x:c r="B43" s="31"/>
+      <x:c r="C43" s="31"/>
+      <x:c r="D43" s="31"/>
+      <x:c r="E43" s="31"/>
+      <x:c r="F43" s="31"/>
+      <x:c r="G43" s="31"/>
+      <x:c r="H43" s="31"/>
+      <x:c r="I43" s="36"/>
+      <x:c r="J43" s="37"/>
+      <x:c r="K43" s="31"/>
+      <x:c r="L43" s="31"/>
+      <x:c r="M43" s="31"/>
+      <x:c r="N43" s="31"/>
+      <x:c r="O43" s="31"/>
+      <x:c r="P43" s="31"/>
+      <x:c r="Q43" s="31"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31"/>
+      <x:c r="B44" s="31"/>
+      <x:c r="C44" s="31"/>
+      <x:c r="D44" s="31"/>
+      <x:c r="E44" s="31"/>
+      <x:c r="F44" s="31"/>
+      <x:c r="G44" s="31"/>
+      <x:c r="H44" s="31"/>
+      <x:c r="I44" s="36"/>
+      <x:c r="J44" s="37"/>
+      <x:c r="K44" s="31"/>
+      <x:c r="L44" s="31"/>
+      <x:c r="M44" s="31"/>
+      <x:c r="N44" s="31"/>
+      <x:c r="O44" s="31"/>
+      <x:c r="P44" s="31"/>
+      <x:c r="Q44" s="31"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31"/>
+      <x:c r="B45" s="31"/>
+      <x:c r="C45" s="31"/>
+      <x:c r="D45" s="31"/>
+      <x:c r="E45" s="31"/>
+      <x:c r="F45" s="31"/>
+      <x:c r="G45" s="31"/>
+      <x:c r="H45" s="31"/>
+      <x:c r="I45" s="36"/>
+      <x:c r="J45" s="37"/>
+      <x:c r="K45" s="31"/>
+      <x:c r="L45" s="31"/>
+      <x:c r="M45" s="31"/>
+      <x:c r="N45" s="31"/>
+      <x:c r="O45" s="31"/>
+      <x:c r="P45" s="31"/>
+      <x:c r="Q45" s="31"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31"/>
+      <x:c r="B46" s="31"/>
+      <x:c r="C46" s="31"/>
+      <x:c r="D46" s="31"/>
+      <x:c r="E46" s="31"/>
+      <x:c r="F46" s="31"/>
+      <x:c r="G46" s="31"/>
+      <x:c r="H46" s="31"/>
+      <x:c r="I46" s="36"/>
+      <x:c r="J46" s="37"/>
+      <x:c r="K46" s="31"/>
+      <x:c r="L46" s="31"/>
+      <x:c r="M46" s="31"/>
+      <x:c r="N46" s="31"/>
+      <x:c r="O46" s="31"/>
+      <x:c r="P46" s="31"/>
+      <x:c r="Q46" s="31"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31"/>
+      <x:c r="B47" s="31"/>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31"/>
+      <x:c r="E47" s="31"/>
+      <x:c r="F47" s="31"/>
+      <x:c r="G47" s="31"/>
+      <x:c r="H47" s="31"/>
+      <x:c r="I47" s="36"/>
+      <x:c r="J47" s="37"/>
+      <x:c r="K47" s="31"/>
+      <x:c r="L47" s="31"/>
+      <x:c r="M47" s="31"/>
+      <x:c r="N47" s="31"/>
+      <x:c r="O47" s="31"/>
+      <x:c r="P47" s="31"/>
+      <x:c r="Q47" s="31"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31"/>
+      <x:c r="B48" s="31"/>
+      <x:c r="C48" s="31"/>
+      <x:c r="D48" s="31"/>
+      <x:c r="E48" s="31"/>
+      <x:c r="F48" s="31"/>
+      <x:c r="G48" s="31"/>
+      <x:c r="H48" s="31"/>
+      <x:c r="I48" s="36"/>
+      <x:c r="J48" s="37"/>
+      <x:c r="K48" s="31"/>
+      <x:c r="L48" s="31"/>
+      <x:c r="M48" s="31"/>
+      <x:c r="N48" s="31"/>
+      <x:c r="O48" s="31"/>
+      <x:c r="P48" s="31"/>
+      <x:c r="Q48" s="31"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31"/>
+      <x:c r="B49" s="31"/>
+      <x:c r="C49" s="31"/>
+      <x:c r="D49" s="31"/>
+      <x:c r="E49" s="31"/>
+      <x:c r="F49" s="31"/>
+      <x:c r="G49" s="31"/>
+      <x:c r="H49" s="31"/>
+      <x:c r="I49" s="36"/>
+      <x:c r="J49" s="37"/>
+      <x:c r="K49" s="31"/>
+      <x:c r="L49" s="31"/>
+      <x:c r="M49" s="31"/>
+      <x:c r="N49" s="31"/>
+      <x:c r="O49" s="31"/>
+      <x:c r="P49" s="31"/>
+      <x:c r="Q49" s="31"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31"/>
+      <x:c r="B50" s="31"/>
+      <x:c r="C50" s="31"/>
+      <x:c r="D50" s="31"/>
+      <x:c r="E50" s="31"/>
+      <x:c r="F50" s="31"/>
+      <x:c r="G50" s="31"/>
+      <x:c r="H50" s="31"/>
+      <x:c r="I50" s="36"/>
+      <x:c r="J50" s="37"/>
+      <x:c r="K50" s="31"/>
+      <x:c r="L50" s="31"/>
+      <x:c r="M50" s="31"/>
+      <x:c r="N50" s="31"/>
+      <x:c r="O50" s="31"/>
+      <x:c r="P50" s="31"/>
+      <x:c r="Q50" s="31"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31"/>
+      <x:c r="B51" s="31"/>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31"/>
+      <x:c r="E51" s="31"/>
+      <x:c r="F51" s="31"/>
+      <x:c r="G51" s="31"/>
+      <x:c r="H51" s="31"/>
+      <x:c r="I51" s="31"/>
+      <x:c r="J51" s="31"/>
+      <x:c r="K51" s="31"/>
+      <x:c r="L51" s="31"/>
+      <x:c r="M51" s="31"/>
+      <x:c r="N51" s="31"/>
+      <x:c r="O51" s="31"/>
+      <x:c r="P51" s="31"/>
+      <x:c r="Q51" s="31"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31"/>
+      <x:c r="B52" s="31"/>
+      <x:c r="C52" s="31"/>
+      <x:c r="D52" s="31"/>
+      <x:c r="E52" s="31"/>
+      <x:c r="F52" s="31"/>
+      <x:c r="G52" s="31"/>
+      <x:c r="H52" s="31"/>
+      <x:c r="I52" s="31"/>
+      <x:c r="J52" s="31"/>
+      <x:c r="K52" s="31"/>
+      <x:c r="L52" s="31"/>
+      <x:c r="M52" s="31"/>
+      <x:c r="N52" s="31"/>
+      <x:c r="O52" s="31"/>
+      <x:c r="P52" s="31"/>
+      <x:c r="Q52" s="31"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31"/>
+      <x:c r="B53" s="31"/>
+      <x:c r="C53" s="31"/>
+      <x:c r="D53" s="31"/>
+      <x:c r="E53" s="31"/>
+      <x:c r="F53" s="31"/>
+      <x:c r="G53" s="31"/>
+      <x:c r="H53" s="31"/>
+      <x:c r="I53" s="31"/>
+      <x:c r="J53" s="31"/>
+      <x:c r="K53" s="31"/>
+      <x:c r="L53" s="31"/>
+      <x:c r="M53" s="31"/>
+      <x:c r="N53" s="31"/>
+      <x:c r="O53" s="31"/>
+      <x:c r="P53" s="31"/>
+      <x:c r="Q53" s="31"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31"/>
+      <x:c r="B54" s="31"/>
+      <x:c r="C54" s="31"/>
+      <x:c r="D54" s="31"/>
+      <x:c r="E54" s="31"/>
+      <x:c r="F54" s="31"/>
+      <x:c r="G54" s="31"/>
+      <x:c r="H54" s="31"/>
+      <x:c r="I54" s="31"/>
+      <x:c r="J54" s="31"/>
+      <x:c r="K54" s="31"/>
+      <x:c r="L54" s="31"/>
+      <x:c r="M54" s="31"/>
+      <x:c r="N54" s="31"/>
+      <x:c r="O54" s="31"/>
+      <x:c r="P54" s="31"/>
+      <x:c r="Q54" s="31"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31"/>
+      <x:c r="B55" s="31"/>
+      <x:c r="C55" s="31"/>
+      <x:c r="D55" s="31"/>
+      <x:c r="E55" s="31"/>
+      <x:c r="F55" s="31"/>
+      <x:c r="G55" s="31"/>
+      <x:c r="H55" s="31"/>
+      <x:c r="I55" s="31"/>
+      <x:c r="J55" s="31"/>
+      <x:c r="K55" s="31"/>
+      <x:c r="L55" s="31"/>
+      <x:c r="M55" s="31"/>
+      <x:c r="N55" s="31"/>
+      <x:c r="O55" s="31"/>
+      <x:c r="P55" s="31"/>
+      <x:c r="Q55" s="31"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31"/>
+      <x:c r="B56" s="31"/>
+      <x:c r="C56" s="31"/>
+      <x:c r="D56" s="31"/>
+      <x:c r="E56" s="31"/>
+      <x:c r="F56" s="31"/>
+      <x:c r="G56" s="31"/>
+      <x:c r="H56" s="31"/>
+      <x:c r="I56" s="31"/>
+      <x:c r="J56" s="31"/>
+      <x:c r="K56" s="31"/>
+      <x:c r="L56" s="31"/>
+      <x:c r="M56" s="31"/>
+      <x:c r="N56" s="31"/>
+      <x:c r="O56" s="31"/>
+      <x:c r="P56" s="31"/>
+      <x:c r="Q56" s="31"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="31"/>
+      <x:c r="B57" s="31"/>
+      <x:c r="C57" s="31"/>
+      <x:c r="D57" s="31"/>
+      <x:c r="E57" s="31"/>
+      <x:c r="F57" s="31"/>
+      <x:c r="G57" s="31"/>
+      <x:c r="H57" s="31"/>
+      <x:c r="I57" s="31"/>
+      <x:c r="J57" s="31"/>
+      <x:c r="K57" s="31"/>
+      <x:c r="L57" s="31"/>
+      <x:c r="M57" s="31"/>
+      <x:c r="N57" s="31"/>
+      <x:c r="O57" s="31"/>
+      <x:c r="P57" s="31"/>
+      <x:c r="Q57" s="31"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="31"/>
+      <x:c r="B58" s="31"/>
+      <x:c r="C58" s="31"/>
+      <x:c r="D58" s="31"/>
+      <x:c r="E58" s="31"/>
+      <x:c r="F58" s="31"/>
+      <x:c r="G58" s="31"/>
+      <x:c r="H58" s="31"/>
+      <x:c r="I58" s="31"/>
+      <x:c r="J58" s="31"/>
+      <x:c r="K58" s="31"/>
+      <x:c r="L58" s="31"/>
+      <x:c r="M58" s="31"/>
+      <x:c r="N58" s="31"/>
+      <x:c r="O58" s="31"/>
+      <x:c r="P58" s="31"/>
+      <x:c r="Q58" s="31"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="31"/>
+      <x:c r="B59" s="31"/>
+      <x:c r="C59" s="31"/>
+      <x:c r="D59" s="31"/>
+      <x:c r="E59" s="31"/>
+      <x:c r="F59" s="31"/>
+      <x:c r="G59" s="31"/>
+      <x:c r="H59" s="31"/>
+      <x:c r="I59" s="31"/>
+      <x:c r="J59" s="31"/>
+      <x:c r="K59" s="31"/>
+      <x:c r="L59" s="31"/>
+      <x:c r="M59" s="31"/>
+      <x:c r="N59" s="31"/>
+      <x:c r="O59" s="31"/>
+      <x:c r="P59" s="31"/>
+      <x:c r="Q59" s="31"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="31"/>
+      <x:c r="B60" s="31"/>
+      <x:c r="C60" s="31"/>
+      <x:c r="D60" s="31"/>
+      <x:c r="E60" s="31"/>
+      <x:c r="F60" s="31"/>
+      <x:c r="G60" s="31"/>
+      <x:c r="H60" s="31"/>
+      <x:c r="I60" s="31"/>
+      <x:c r="J60" s="31"/>
+      <x:c r="K60" s="31"/>
+      <x:c r="L60" s="31"/>
+      <x:c r="M60" s="31"/>
+      <x:c r="N60" s="31"/>
+      <x:c r="O60" s="31"/>
+      <x:c r="P60" s="31"/>
+      <x:c r="Q60" s="31"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="31"/>
+      <x:c r="B61" s="31"/>
+      <x:c r="C61" s="31"/>
+      <x:c r="D61" s="31"/>
+      <x:c r="E61" s="31"/>
+      <x:c r="F61" s="31"/>
+      <x:c r="G61" s="31"/>
+      <x:c r="H61" s="31"/>
+      <x:c r="I61" s="31"/>
+      <x:c r="J61" s="31"/>
+      <x:c r="K61" s="31"/>
+      <x:c r="L61" s="31"/>
+      <x:c r="M61" s="31"/>
+      <x:c r="N61" s="31"/>
+      <x:c r="O61" s="31"/>
+      <x:c r="P61" s="31"/>
+      <x:c r="Q61" s="31"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="31"/>
+      <x:c r="B62" s="31"/>
+      <x:c r="C62" s="31"/>
+      <x:c r="D62" s="31"/>
+      <x:c r="E62" s="31"/>
+      <x:c r="F62" s="31"/>
+      <x:c r="G62" s="31"/>
+      <x:c r="H62" s="31"/>
+      <x:c r="I62" s="31"/>
+      <x:c r="J62" s="31"/>
+      <x:c r="K62" s="31"/>
+      <x:c r="L62" s="31"/>
+      <x:c r="M62" s="31"/>
+      <x:c r="N62" s="31"/>
+      <x:c r="O62" s="31"/>
+      <x:c r="P62" s="31"/>
+      <x:c r="Q62" s="31"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="31"/>
+      <x:c r="B63" s="31"/>
+      <x:c r="C63" s="31"/>
+      <x:c r="D63" s="31"/>
+      <x:c r="E63" s="31"/>
+      <x:c r="F63" s="31"/>
+      <x:c r="G63" s="31"/>
+      <x:c r="H63" s="31"/>
+      <x:c r="I63" s="31"/>
+      <x:c r="J63" s="31"/>
+      <x:c r="K63" s="31"/>
+      <x:c r="L63" s="31"/>
+      <x:c r="M63" s="31"/>
+      <x:c r="N63" s="31"/>
+      <x:c r="O63" s="31"/>
+      <x:c r="P63" s="31"/>
+      <x:c r="Q63" s="31"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="31"/>
+      <x:c r="B64" s="31"/>
+      <x:c r="C64" s="31"/>
+      <x:c r="D64" s="31"/>
+      <x:c r="E64" s="31"/>
+      <x:c r="F64" s="31"/>
+      <x:c r="G64" s="31"/>
+      <x:c r="H64" s="31"/>
+      <x:c r="I64" s="31"/>
+      <x:c r="J64" s="31"/>
+      <x:c r="K64" s="31"/>
+      <x:c r="L64" s="31"/>
+      <x:c r="M64" s="31"/>
+      <x:c r="N64" s="31"/>
+      <x:c r="O64" s="31"/>
+      <x:c r="P64" s="31"/>
+      <x:c r="Q64" s="31"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="31"/>
+      <x:c r="B65" s="31"/>
+      <x:c r="C65" s="31"/>
+      <x:c r="D65" s="31"/>
+      <x:c r="E65" s="31"/>
+      <x:c r="F65" s="31"/>
+      <x:c r="G65" s="31"/>
+      <x:c r="H65" s="31"/>
+      <x:c r="I65" s="31"/>
+      <x:c r="J65" s="31"/>
+      <x:c r="K65" s="31"/>
+      <x:c r="L65" s="31"/>
+      <x:c r="M65" s="31"/>
+      <x:c r="N65" s="31"/>
+      <x:c r="O65" s="31"/>
+      <x:c r="P65" s="31"/>
+      <x:c r="Q65" s="31"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="31"/>
+      <x:c r="B66" s="31"/>
+      <x:c r="C66" s="31"/>
+      <x:c r="D66" s="31"/>
+      <x:c r="E66" s="31"/>
+      <x:c r="F66" s="31"/>
+      <x:c r="G66" s="31"/>
+      <x:c r="H66" s="31"/>
+      <x:c r="I66" s="31"/>
+      <x:c r="J66" s="31"/>
+      <x:c r="K66" s="31"/>
+      <x:c r="L66" s="31"/>
+      <x:c r="M66" s="31"/>
+      <x:c r="N66" s="31"/>
+      <x:c r="O66" s="31"/>
+      <x:c r="P66" s="31"/>
+      <x:c r="Q66" s="31"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="31"/>
+      <x:c r="B67" s="31"/>
+      <x:c r="C67" s="31"/>
+      <x:c r="D67" s="31"/>
+      <x:c r="E67" s="31"/>
+      <x:c r="F67" s="31"/>
+      <x:c r="G67" s="31"/>
+      <x:c r="H67" s="31"/>
+      <x:c r="I67" s="31"/>
+      <x:c r="J67" s="31"/>
+      <x:c r="K67" s="31"/>
+      <x:c r="L67" s="31"/>
+      <x:c r="M67" s="31"/>
+      <x:c r="N67" s="31"/>
+      <x:c r="O67" s="31"/>
+      <x:c r="P67" s="31"/>
+      <x:c r="Q67" s="31"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="31"/>
+      <x:c r="B68" s="31"/>
+      <x:c r="C68" s="31"/>
+      <x:c r="D68" s="31"/>
+      <x:c r="E68" s="31"/>
+      <x:c r="F68" s="31"/>
+      <x:c r="G68" s="31"/>
+      <x:c r="H68" s="31"/>
+      <x:c r="I68" s="31"/>
+      <x:c r="J68" s="31"/>
+      <x:c r="K68" s="31"/>
+      <x:c r="L68" s="31"/>
+      <x:c r="M68" s="31"/>
+      <x:c r="N68" s="31"/>
+      <x:c r="O68" s="31"/>
+      <x:c r="P68" s="31"/>
+      <x:c r="Q68" s="31"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="31"/>
+      <x:c r="B69" s="31"/>
+      <x:c r="C69" s="31"/>
+      <x:c r="D69" s="31"/>
+      <x:c r="E69" s="31"/>
+      <x:c r="F69" s="31"/>
+      <x:c r="G69" s="31"/>
+      <x:c r="H69" s="31"/>
+      <x:c r="I69" s="31"/>
+      <x:c r="J69" s="31"/>
+      <x:c r="K69" s="31"/>
+      <x:c r="L69" s="31"/>
+      <x:c r="M69" s="31"/>
+      <x:c r="N69" s="31"/>
+      <x:c r="O69" s="31"/>
+      <x:c r="P69" s="31"/>
+      <x:c r="Q69" s="31"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="31"/>
+      <x:c r="B70" s="31"/>
+      <x:c r="C70" s="31"/>
+      <x:c r="D70" s="31"/>
+      <x:c r="E70" s="31"/>
+      <x:c r="F70" s="31"/>
+      <x:c r="G70" s="31"/>
+      <x:c r="H70" s="31"/>
+      <x:c r="I70" s="31"/>
+      <x:c r="J70" s="31"/>
+      <x:c r="K70" s="31"/>
+      <x:c r="L70" s="31"/>
+      <x:c r="M70" s="31"/>
+      <x:c r="N70" s="31"/>
+      <x:c r="O70" s="31"/>
+      <x:c r="P70" s="31"/>
+      <x:c r="Q70" s="31"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="31"/>
+      <x:c r="B71" s="31"/>
+      <x:c r="C71" s="31"/>
+      <x:c r="D71" s="31"/>
+      <x:c r="E71" s="31"/>
+      <x:c r="F71" s="31"/>
+      <x:c r="G71" s="31"/>
+      <x:c r="H71" s="31"/>
+      <x:c r="I71" s="31"/>
+      <x:c r="J71" s="31"/>
+      <x:c r="K71" s="31"/>
+      <x:c r="L71" s="31"/>
+      <x:c r="M71" s="31"/>
+      <x:c r="N71" s="31"/>
+      <x:c r="O71" s="31"/>
+      <x:c r="P71" s="31"/>
+      <x:c r="Q71" s="31"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="31"/>
+      <x:c r="B72" s="31"/>
+      <x:c r="C72" s="31"/>
+      <x:c r="D72" s="31"/>
+      <x:c r="E72" s="31"/>
+      <x:c r="F72" s="31"/>
+      <x:c r="G72" s="31"/>
+      <x:c r="H72" s="31"/>
+      <x:c r="I72" s="31"/>
+      <x:c r="J72" s="31"/>
+      <x:c r="K72" s="31"/>
+      <x:c r="L72" s="31"/>
+      <x:c r="M72" s="31"/>
+      <x:c r="N72" s="31"/>
+      <x:c r="O72" s="31"/>
+      <x:c r="P72" s="31"/>
+      <x:c r="Q72" s="31"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="31"/>
+      <x:c r="B73" s="31"/>
+      <x:c r="C73" s="31"/>
+      <x:c r="D73" s="31"/>
+      <x:c r="E73" s="31"/>
+      <x:c r="F73" s="31"/>
+      <x:c r="G73" s="31"/>
+      <x:c r="H73" s="31"/>
+      <x:c r="I73" s="31"/>
+      <x:c r="J73" s="31"/>
+      <x:c r="K73" s="31"/>
+      <x:c r="L73" s="31"/>
+      <x:c r="M73" s="31"/>
+      <x:c r="N73" s="31"/>
+      <x:c r="O73" s="31"/>
+      <x:c r="P73" s="31"/>
+      <x:c r="Q73" s="31"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="31"/>
+      <x:c r="B74" s="31"/>
+      <x:c r="C74" s="31"/>
+      <x:c r="D74" s="31"/>
+      <x:c r="E74" s="31"/>
+      <x:c r="F74" s="31"/>
+      <x:c r="G74" s="31"/>
+      <x:c r="H74" s="31"/>
+      <x:c r="I74" s="31"/>
+      <x:c r="J74" s="31"/>
+      <x:c r="K74" s="31"/>
+      <x:c r="L74" s="31"/>
+      <x:c r="M74" s="31"/>
+      <x:c r="N74" s="31"/>
+      <x:c r="O74" s="31"/>
+      <x:c r="P74" s="31"/>
+      <x:c r="Q74" s="31"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="31"/>
+      <x:c r="B75" s="31"/>
+      <x:c r="C75" s="31"/>
+      <x:c r="D75" s="31"/>
+      <x:c r="E75" s="31"/>
+      <x:c r="F75" s="31"/>
+      <x:c r="G75" s="31"/>
+      <x:c r="H75" s="31"/>
+      <x:c r="I75" s="31"/>
+      <x:c r="J75" s="31"/>
+      <x:c r="K75" s="31"/>
+      <x:c r="L75" s="31"/>
+      <x:c r="M75" s="31"/>
+      <x:c r="N75" s="31"/>
+      <x:c r="O75" s="31"/>
+      <x:c r="P75" s="31"/>
+      <x:c r="Q75" s="31"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="31"/>
+      <x:c r="B76" s="31"/>
+      <x:c r="C76" s="31"/>
+      <x:c r="D76" s="31"/>
+      <x:c r="E76" s="31"/>
+      <x:c r="F76" s="31"/>
+      <x:c r="G76" s="31"/>
+      <x:c r="H76" s="31"/>
+      <x:c r="I76" s="31"/>
+      <x:c r="J76" s="31"/>
+      <x:c r="K76" s="31"/>
+      <x:c r="L76" s="31"/>
+      <x:c r="M76" s="31"/>
+      <x:c r="N76" s="31"/>
+      <x:c r="O76" s="31"/>
+      <x:c r="P76" s="31"/>
+      <x:c r="Q76" s="31"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="31"/>
+      <x:c r="B77" s="31"/>
+      <x:c r="C77" s="31"/>
+      <x:c r="D77" s="31"/>
+      <x:c r="E77" s="31"/>
+      <x:c r="F77" s="31"/>
+      <x:c r="G77" s="31"/>
+      <x:c r="H77" s="31"/>
+      <x:c r="I77" s="31"/>
+      <x:c r="J77" s="31"/>
+      <x:c r="K77" s="31"/>
+      <x:c r="L77" s="31"/>
+      <x:c r="M77" s="31"/>
+      <x:c r="N77" s="31"/>
+      <x:c r="O77" s="31"/>
+      <x:c r="P77" s="31"/>
+      <x:c r="Q77" s="31"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="31"/>
+      <x:c r="B78" s="31"/>
+      <x:c r="C78" s="31"/>
+      <x:c r="D78" s="31"/>
+      <x:c r="E78" s="31"/>
+      <x:c r="F78" s="31"/>
+      <x:c r="G78" s="31"/>
+      <x:c r="H78" s="31"/>
+      <x:c r="I78" s="31"/>
+      <x:c r="J78" s="31"/>
+      <x:c r="K78" s="31"/>
+      <x:c r="L78" s="31"/>
+      <x:c r="M78" s="31"/>
+      <x:c r="N78" s="31"/>
+      <x:c r="O78" s="31"/>
+      <x:c r="P78" s="31"/>
+      <x:c r="Q78" s="31"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="31"/>
+      <x:c r="B79" s="31"/>
+      <x:c r="C79" s="31"/>
+      <x:c r="D79" s="31"/>
+      <x:c r="E79" s="31"/>
+      <x:c r="F79" s="31"/>
+      <x:c r="G79" s="31"/>
+      <x:c r="H79" s="31"/>
+      <x:c r="I79" s="31"/>
+      <x:c r="J79" s="31"/>
+      <x:c r="K79" s="31"/>
+      <x:c r="L79" s="31"/>
+      <x:c r="M79" s="31"/>
+      <x:c r="N79" s="31"/>
+      <x:c r="O79" s="31"/>
+      <x:c r="P79" s="31"/>
+      <x:c r="Q79" s="31"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="31"/>
+      <x:c r="B80" s="31"/>
+      <x:c r="C80" s="31"/>
+      <x:c r="D80" s="31"/>
+      <x:c r="E80" s="31"/>
+      <x:c r="F80" s="31"/>
+      <x:c r="G80" s="31"/>
+      <x:c r="H80" s="31"/>
+      <x:c r="I80" s="31"/>
+      <x:c r="J80" s="31"/>
+      <x:c r="K80" s="31"/>
+      <x:c r="L80" s="31"/>
+      <x:c r="M80" s="31"/>
+      <x:c r="N80" s="31"/>
+      <x:c r="O80" s="31"/>
+      <x:c r="P80" s="31"/>
+      <x:c r="Q80" s="31"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="31"/>
+      <x:c r="B81" s="31"/>
+      <x:c r="C81" s="31"/>
+      <x:c r="D81" s="31"/>
+      <x:c r="E81" s="31"/>
+      <x:c r="F81" s="31"/>
+      <x:c r="G81" s="31"/>
+      <x:c r="H81" s="31"/>
+      <x:c r="I81" s="31"/>
+      <x:c r="J81" s="31"/>
+      <x:c r="K81" s="31"/>
+      <x:c r="L81" s="31"/>
+      <x:c r="M81" s="31"/>
+      <x:c r="N81" s="31"/>
+      <x:c r="O81" s="31"/>
+      <x:c r="P81" s="31"/>
+      <x:c r="Q81" s="31"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="31"/>
+      <x:c r="B82" s="31"/>
+      <x:c r="C82" s="31"/>
+      <x:c r="D82" s="31"/>
+      <x:c r="E82" s="31"/>
+      <x:c r="F82" s="31"/>
+      <x:c r="G82" s="31"/>
+      <x:c r="H82" s="31"/>
+      <x:c r="I82" s="31"/>
+      <x:c r="J82" s="31"/>
+      <x:c r="K82" s="31"/>
+      <x:c r="L82" s="31"/>
+      <x:c r="M82" s="31"/>
+      <x:c r="N82" s="31"/>
+      <x:c r="O82" s="31"/>
+      <x:c r="P82" s="31"/>
+      <x:c r="Q82" s="31"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="31"/>
+      <x:c r="B83" s="31"/>
+      <x:c r="C83" s="31"/>
+      <x:c r="D83" s="31"/>
+      <x:c r="E83" s="31"/>
+      <x:c r="F83" s="31"/>
+      <x:c r="G83" s="31"/>
+      <x:c r="H83" s="31"/>
+      <x:c r="I83" s="31"/>
+      <x:c r="J83" s="31"/>
+      <x:c r="K83" s="31"/>
+      <x:c r="L83" s="31"/>
+      <x:c r="M83" s="31"/>
+      <x:c r="N83" s="31"/>
+      <x:c r="O83" s="31"/>
+      <x:c r="P83" s="31"/>
+      <x:c r="Q83" s="31"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="31"/>
+      <x:c r="B84" s="31"/>
+      <x:c r="C84" s="31"/>
+      <x:c r="D84" s="31"/>
+      <x:c r="E84" s="31"/>
+      <x:c r="F84" s="31"/>
+      <x:c r="G84" s="31"/>
+      <x:c r="H84" s="31"/>
+      <x:c r="I84" s="31"/>
+      <x:c r="J84" s="31"/>
+      <x:c r="K84" s="31"/>
+      <x:c r="L84" s="31"/>
+      <x:c r="M84" s="31"/>
+      <x:c r="N84" s="31"/>
+      <x:c r="O84" s="31"/>
+      <x:c r="P84" s="31"/>
+      <x:c r="Q84" s="31"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="31"/>
+      <x:c r="B85" s="31"/>
+      <x:c r="C85" s="31"/>
+      <x:c r="D85" s="31"/>
+      <x:c r="E85" s="31"/>
+      <x:c r="F85" s="31"/>
+      <x:c r="G85" s="31"/>
+      <x:c r="H85" s="31"/>
+      <x:c r="I85" s="31"/>
+      <x:c r="J85" s="31"/>
+      <x:c r="K85" s="31"/>
+      <x:c r="L85" s="31"/>
+      <x:c r="M85" s="31"/>
+      <x:c r="N85" s="31"/>
+      <x:c r="O85" s="31"/>
+      <x:c r="P85" s="31"/>
+      <x:c r="Q85" s="31"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="31"/>
+      <x:c r="B86" s="31"/>
+      <x:c r="C86" s="31"/>
+      <x:c r="D86" s="31"/>
+      <x:c r="E86" s="31"/>
+      <x:c r="F86" s="31"/>
+      <x:c r="G86" s="31"/>
+      <x:c r="H86" s="31"/>
+      <x:c r="I86" s="31"/>
+      <x:c r="J86" s="31"/>
+      <x:c r="K86" s="31"/>
+      <x:c r="L86" s="31"/>
+      <x:c r="M86" s="31"/>
+      <x:c r="N86" s="31"/>
+      <x:c r="O86" s="31"/>
+      <x:c r="P86" s="31"/>
+      <x:c r="Q86" s="31"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="31"/>
+      <x:c r="B87" s="31"/>
+      <x:c r="C87" s="31"/>
+      <x:c r="D87" s="31"/>
+      <x:c r="E87" s="31"/>
+      <x:c r="F87" s="31"/>
+      <x:c r="G87" s="31"/>
+      <x:c r="H87" s="31"/>
+      <x:c r="I87" s="31"/>
+      <x:c r="J87" s="31"/>
+      <x:c r="K87" s="31"/>
+      <x:c r="L87" s="31"/>
+      <x:c r="M87" s="31"/>
+      <x:c r="N87" s="31"/>
+      <x:c r="O87" s="31"/>
+      <x:c r="P87" s="31"/>
+      <x:c r="Q87" s="31"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="31"/>
+      <x:c r="B88" s="31"/>
+      <x:c r="C88" s="31"/>
+      <x:c r="D88" s="31"/>
+      <x:c r="E88" s="31"/>
+      <x:c r="F88" s="31"/>
+      <x:c r="G88" s="31"/>
+      <x:c r="H88" s="31"/>
+      <x:c r="I88" s="31"/>
+      <x:c r="J88" s="31"/>
+      <x:c r="K88" s="31"/>
+      <x:c r="L88" s="31"/>
+      <x:c r="M88" s="31"/>
+      <x:c r="N88" s="31"/>
+      <x:c r="O88" s="31"/>
+      <x:c r="P88" s="31"/>
+      <x:c r="Q88" s="31"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="31"/>
+      <x:c r="B89" s="31"/>
+      <x:c r="C89" s="31"/>
+      <x:c r="D89" s="31"/>
+      <x:c r="E89" s="31"/>
+      <x:c r="F89" s="31"/>
+      <x:c r="G89" s="31"/>
+      <x:c r="H89" s="31"/>
+      <x:c r="I89" s="31"/>
+      <x:c r="J89" s="31"/>
+      <x:c r="K89" s="31"/>
+      <x:c r="L89" s="31"/>
+      <x:c r="M89" s="31"/>
+      <x:c r="N89" s="31"/>
+      <x:c r="O89" s="31"/>
+      <x:c r="P89" s="31"/>
+      <x:c r="Q89" s="31"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="31"/>
+      <x:c r="B90" s="31"/>
+      <x:c r="C90" s="31"/>
+      <x:c r="D90" s="31"/>
+      <x:c r="E90" s="31"/>
+      <x:c r="F90" s="31"/>
+      <x:c r="G90" s="31"/>
+      <x:c r="H90" s="31"/>
+      <x:c r="I90" s="31"/>
+      <x:c r="J90" s="31"/>
+      <x:c r="K90" s="31"/>
+      <x:c r="L90" s="31"/>
+      <x:c r="M90" s="31"/>
+      <x:c r="N90" s="31"/>
+      <x:c r="O90" s="31"/>
+      <x:c r="P90" s="31"/>
+      <x:c r="Q90" s="31"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="31"/>
+      <x:c r="B91" s="31"/>
+      <x:c r="C91" s="31"/>
+      <x:c r="D91" s="31"/>
+      <x:c r="E91" s="31"/>
+      <x:c r="F91" s="31"/>
+      <x:c r="G91" s="31"/>
+      <x:c r="H91" s="31"/>
+      <x:c r="I91" s="31"/>
+      <x:c r="J91" s="31"/>
+      <x:c r="K91" s="31"/>
+      <x:c r="L91" s="31"/>
+      <x:c r="M91" s="31"/>
+      <x:c r="N91" s="31"/>
+      <x:c r="O91" s="31"/>
+      <x:c r="P91" s="31"/>
+      <x:c r="Q91" s="31"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="31"/>
+      <x:c r="B92" s="31"/>
+      <x:c r="C92" s="31"/>
+      <x:c r="D92" s="31"/>
+      <x:c r="E92" s="31"/>
+      <x:c r="F92" s="31"/>
+      <x:c r="G92" s="31"/>
+      <x:c r="H92" s="31"/>
+      <x:c r="I92" s="31"/>
+      <x:c r="J92" s="31"/>
+      <x:c r="K92" s="31"/>
+      <x:c r="L92" s="31"/>
+      <x:c r="M92" s="31"/>
+      <x:c r="N92" s="31"/>
+      <x:c r="O92" s="31"/>
+      <x:c r="P92" s="31"/>
+      <x:c r="Q92" s="31"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="31"/>
+      <x:c r="B93" s="31"/>
+      <x:c r="C93" s="31"/>
+      <x:c r="D93" s="31"/>
+      <x:c r="E93" s="31"/>
+      <x:c r="F93" s="31"/>
+      <x:c r="G93" s="31"/>
+      <x:c r="H93" s="31"/>
+      <x:c r="I93" s="31"/>
+      <x:c r="J93" s="31"/>
+      <x:c r="K93" s="31"/>
+      <x:c r="L93" s="31"/>
+      <x:c r="M93" s="31"/>
+      <x:c r="N93" s="31"/>
+      <x:c r="O93" s="31"/>
+      <x:c r="P93" s="31"/>
+      <x:c r="Q93" s="31"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="31"/>
+      <x:c r="B94" s="31"/>
+      <x:c r="C94" s="31"/>
+      <x:c r="D94" s="31"/>
+      <x:c r="E94" s="31"/>
+      <x:c r="F94" s="31"/>
+      <x:c r="G94" s="31"/>
+      <x:c r="H94" s="31"/>
+      <x:c r="I94" s="31"/>
+      <x:c r="J94" s="31"/>
+      <x:c r="K94" s="31"/>
+      <x:c r="L94" s="31"/>
+      <x:c r="M94" s="31"/>
+      <x:c r="N94" s="31"/>
+      <x:c r="O94" s="31"/>
+      <x:c r="P94" s="31"/>
+      <x:c r="Q94" s="31"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="31"/>
+      <x:c r="B95" s="31"/>
+      <x:c r="C95" s="31"/>
+      <x:c r="D95" s="31"/>
+      <x:c r="E95" s="31"/>
+      <x:c r="F95" s="31"/>
+      <x:c r="G95" s="31"/>
+      <x:c r="H95" s="31"/>
+      <x:c r="I95" s="31"/>
+      <x:c r="J95" s="31"/>
+      <x:c r="K95" s="31"/>
+      <x:c r="L95" s="31"/>
+      <x:c r="M95" s="31"/>
+      <x:c r="N95" s="31"/>
+      <x:c r="O95" s="31"/>
+      <x:c r="P95" s="31"/>
+      <x:c r="Q95" s="31"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="31"/>
+      <x:c r="B96" s="31"/>
+      <x:c r="C96" s="31"/>
+      <x:c r="D96" s="31"/>
+      <x:c r="E96" s="31"/>
+      <x:c r="F96" s="31"/>
+      <x:c r="G96" s="31"/>
+      <x:c r="H96" s="31"/>
+      <x:c r="I96" s="31"/>
+      <x:c r="J96" s="31"/>
+      <x:c r="K96" s="31"/>
+      <x:c r="L96" s="31"/>
+      <x:c r="M96" s="31"/>
+      <x:c r="N96" s="31"/>
+      <x:c r="O96" s="31"/>
+      <x:c r="P96" s="31"/>
+      <x:c r="Q96" s="31"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="31"/>
+      <x:c r="B97" s="31"/>
+      <x:c r="C97" s="31"/>
+      <x:c r="D97" s="31"/>
+      <x:c r="E97" s="31"/>
+      <x:c r="F97" s="31"/>
+      <x:c r="G97" s="31"/>
+      <x:c r="H97" s="31"/>
+      <x:c r="I97" s="31"/>
+      <x:c r="J97" s="31"/>
+      <x:c r="K97" s="31"/>
+      <x:c r="L97" s="31"/>
+      <x:c r="M97" s="31"/>
+      <x:c r="N97" s="31"/>
+      <x:c r="O97" s="31"/>
+      <x:c r="P97" s="31"/>
+      <x:c r="Q97" s="31"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="31"/>
+      <x:c r="B98" s="31"/>
+      <x:c r="C98" s="31"/>
+      <x:c r="D98" s="31"/>
+      <x:c r="E98" s="31"/>
+      <x:c r="F98" s="31"/>
+      <x:c r="G98" s="31"/>
+      <x:c r="H98" s="31"/>
+      <x:c r="I98" s="31"/>
+      <x:c r="J98" s="31"/>
+      <x:c r="K98" s="31"/>
+      <x:c r="L98" s="31"/>
+      <x:c r="M98" s="31"/>
+      <x:c r="N98" s="31"/>
+      <x:c r="O98" s="31"/>
+      <x:c r="P98" s="31"/>
+      <x:c r="Q98" s="31"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="31"/>
+      <x:c r="B99" s="31"/>
+      <x:c r="C99" s="31"/>
+      <x:c r="D99" s="31"/>
+      <x:c r="E99" s="31"/>
+      <x:c r="F99" s="31"/>
+      <x:c r="G99" s="31"/>
+      <x:c r="H99" s="31"/>
+      <x:c r="I99" s="31"/>
+      <x:c r="J99" s="31"/>
+      <x:c r="K99" s="31"/>
+      <x:c r="L99" s="31"/>
+      <x:c r="M99" s="31"/>
+      <x:c r="N99" s="31"/>
+      <x:c r="O99" s="31"/>
+      <x:c r="P99" s="31"/>
+      <x:c r="Q99" s="31"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="31"/>
+      <x:c r="B100" s="31"/>
+      <x:c r="C100" s="31"/>
+      <x:c r="D100" s="31"/>
+      <x:c r="E100" s="31"/>
+      <x:c r="F100" s="31"/>
+      <x:c r="G100" s="31"/>
+      <x:c r="H100" s="31"/>
+      <x:c r="I100" s="31"/>
+      <x:c r="J100" s="31"/>
+      <x:c r="K100" s="31"/>
+      <x:c r="L100" s="31"/>
+      <x:c r="M100" s="31"/>
+      <x:c r="N100" s="31"/>
+      <x:c r="O100" s="31"/>
+      <x:c r="P100" s="31"/>
+      <x:c r="Q100" s="31"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="31"/>
+      <x:c r="B101" s="31"/>
+      <x:c r="C101" s="31"/>
+      <x:c r="D101" s="31"/>
+      <x:c r="E101" s="31"/>
+      <x:c r="F101" s="31"/>
+      <x:c r="G101" s="31"/>
+      <x:c r="H101" s="31"/>
+      <x:c r="I101" s="31"/>
+      <x:c r="J101" s="31"/>
+      <x:c r="K101" s="31"/>
+      <x:c r="L101" s="31"/>
+      <x:c r="M101" s="31"/>
+      <x:c r="N101" s="31"/>
+      <x:c r="O101" s="31"/>
+      <x:c r="P101" s="31"/>
+      <x:c r="Q101" s="31"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="31"/>
+      <x:c r="B102" s="31"/>
+      <x:c r="C102" s="31"/>
+      <x:c r="D102" s="31"/>
+      <x:c r="E102" s="31"/>
+      <x:c r="F102" s="31"/>
+      <x:c r="G102" s="31"/>
+      <x:c r="H102" s="31"/>
+      <x:c r="I102" s="31"/>
+      <x:c r="J102" s="31"/>
+      <x:c r="K102" s="31"/>
+      <x:c r="L102" s="31"/>
+      <x:c r="M102" s="31"/>
+      <x:c r="N102" s="31"/>
+      <x:c r="O102" s="31"/>
+      <x:c r="P102" s="31"/>
+      <x:c r="Q102" s="31"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="31"/>
+      <x:c r="B103" s="31"/>
+      <x:c r="C103" s="31"/>
+      <x:c r="D103" s="31"/>
+      <x:c r="E103" s="31"/>
+      <x:c r="F103" s="31"/>
+      <x:c r="G103" s="31"/>
+      <x:c r="H103" s="31"/>
+      <x:c r="I103" s="31"/>
+      <x:c r="J103" s="31"/>
+      <x:c r="K103" s="31"/>
+      <x:c r="L103" s="31"/>
+      <x:c r="M103" s="31"/>
+      <x:c r="N103" s="31"/>
+      <x:c r="O103" s="31"/>
+      <x:c r="P103" s="31"/>
+      <x:c r="Q103" s="31"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="31"/>
+      <x:c r="B104" s="31"/>
+      <x:c r="C104" s="31"/>
+      <x:c r="D104" s="31"/>
+      <x:c r="E104" s="31"/>
+      <x:c r="F104" s="31"/>
+      <x:c r="G104" s="31"/>
+      <x:c r="H104" s="31"/>
+      <x:c r="I104" s="31"/>
+      <x:c r="J104" s="31"/>
+      <x:c r="K104" s="31"/>
+      <x:c r="L104" s="31"/>
+      <x:c r="M104" s="31"/>
+      <x:c r="N104" s="31"/>
+      <x:c r="O104" s="31"/>
+      <x:c r="P104" s="31"/>
+      <x:c r="Q104" s="31"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="31"/>
+      <x:c r="B105" s="31"/>
+      <x:c r="C105" s="31"/>
+      <x:c r="D105" s="31"/>
+      <x:c r="E105" s="31"/>
+      <x:c r="F105" s="31"/>
+      <x:c r="G105" s="31"/>
+      <x:c r="H105" s="31"/>
+      <x:c r="I105" s="31"/>
+      <x:c r="J105" s="31"/>
+      <x:c r="K105" s="31"/>
+      <x:c r="L105" s="31"/>
+      <x:c r="M105" s="31"/>
+      <x:c r="N105" s="31"/>
+      <x:c r="O105" s="31"/>
+      <x:c r="P105" s="31"/>
+      <x:c r="Q105" s="31"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="31"/>
+      <x:c r="B106" s="31"/>
+      <x:c r="C106" s="31"/>
+      <x:c r="D106" s="31"/>
+      <x:c r="E106" s="31"/>
+      <x:c r="F106" s="31"/>
+      <x:c r="G106" s="31"/>
+      <x:c r="H106" s="31"/>
+      <x:c r="I106" s="31"/>
+      <x:c r="J106" s="31"/>
+      <x:c r="K106" s="31"/>
+      <x:c r="L106" s="31"/>
+      <x:c r="M106" s="31"/>
+      <x:c r="N106" s="31"/>
+      <x:c r="O106" s="31"/>
+      <x:c r="P106" s="31"/>
+      <x:c r="Q106" s="31"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="31"/>
+      <x:c r="B107" s="31"/>
+      <x:c r="C107" s="31"/>
+      <x:c r="D107" s="31"/>
+      <x:c r="E107" s="31"/>
+      <x:c r="F107" s="31"/>
+      <x:c r="G107" s="31"/>
+      <x:c r="H107" s="31"/>
+      <x:c r="I107" s="31"/>
+      <x:c r="J107" s="31"/>
+      <x:c r="K107" s="31"/>
+      <x:c r="L107" s="31"/>
+      <x:c r="M107" s="31"/>
+      <x:c r="N107" s="31"/>
+      <x:c r="O107" s="31"/>
+      <x:c r="P107" s="31"/>
+      <x:c r="Q107" s="31"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="31"/>
+      <x:c r="B108" s="31"/>
+      <x:c r="C108" s="31"/>
+      <x:c r="D108" s="31"/>
+      <x:c r="E108" s="31"/>
+      <x:c r="F108" s="31"/>
+      <x:c r="G108" s="31"/>
+      <x:c r="H108" s="31"/>
+      <x:c r="I108" s="31"/>
+      <x:c r="J108" s="31"/>
+      <x:c r="K108" s="31"/>
+      <x:c r="L108" s="31"/>
+      <x:c r="M108" s="31"/>
+      <x:c r="N108" s="31"/>
+      <x:c r="O108" s="31"/>
+      <x:c r="P108" s="31"/>
+      <x:c r="Q108" s="31"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="31"/>
+      <x:c r="B109" s="31"/>
+      <x:c r="C109" s="31"/>
+      <x:c r="D109" s="31"/>
+      <x:c r="E109" s="31"/>
+      <x:c r="F109" s="31"/>
+      <x:c r="G109" s="31"/>
+      <x:c r="H109" s="31"/>
+      <x:c r="I109" s="31"/>
+      <x:c r="J109" s="31"/>
+      <x:c r="K109" s="31"/>
+      <x:c r="L109" s="31"/>
+      <x:c r="M109" s="31"/>
+      <x:c r="N109" s="31"/>
+      <x:c r="O109" s="31"/>
+      <x:c r="P109" s="31"/>
+      <x:c r="Q109" s="31"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="31"/>
+      <x:c r="B110" s="31"/>
+      <x:c r="C110" s="31"/>
+      <x:c r="D110" s="31"/>
+      <x:c r="E110" s="31"/>
+      <x:c r="F110" s="31"/>
+      <x:c r="G110" s="31"/>
+      <x:c r="H110" s="31"/>
+      <x:c r="I110" s="31"/>
+      <x:c r="J110" s="31"/>
+      <x:c r="K110" s="31"/>
+      <x:c r="L110" s="31"/>
+      <x:c r="M110" s="31"/>
+      <x:c r="N110" s="31"/>
+      <x:c r="O110" s="31"/>
+      <x:c r="P110" s="31"/>
+      <x:c r="Q110" s="31"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="31"/>
+      <x:c r="B111" s="31"/>
+      <x:c r="C111" s="31"/>
+      <x:c r="D111" s="31"/>
+      <x:c r="E111" s="31"/>
+      <x:c r="F111" s="31"/>
+      <x:c r="G111" s="31"/>
+      <x:c r="H111" s="31"/>
+      <x:c r="I111" s="31"/>
+      <x:c r="J111" s="31"/>
+      <x:c r="K111" s="31"/>
+      <x:c r="L111" s="31"/>
+      <x:c r="M111" s="31"/>
+      <x:c r="N111" s="31"/>
+      <x:c r="O111" s="31"/>
+      <x:c r="P111" s="31"/>
+      <x:c r="Q111" s="31"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="31"/>
+      <x:c r="B112" s="31"/>
+      <x:c r="C112" s="31"/>
+      <x:c r="D112" s="31"/>
+      <x:c r="E112" s="31"/>
+      <x:c r="F112" s="31"/>
+      <x:c r="G112" s="31"/>
+      <x:c r="H112" s="31"/>
+      <x:c r="I112" s="31"/>
+      <x:c r="J112" s="31"/>
+      <x:c r="K112" s="31"/>
+      <x:c r="L112" s="31"/>
+      <x:c r="M112" s="31"/>
+      <x:c r="N112" s="31"/>
+      <x:c r="O112" s="31"/>
+      <x:c r="P112" s="31"/>
+      <x:c r="Q112" s="31"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="31"/>
+      <x:c r="B113" s="31"/>
+      <x:c r="C113" s="31"/>
+      <x:c r="D113" s="31"/>
+      <x:c r="E113" s="31"/>
+      <x:c r="F113" s="31"/>
+      <x:c r="G113" s="31"/>
+      <x:c r="H113" s="31"/>
+      <x:c r="I113" s="31"/>
+      <x:c r="J113" s="31"/>
+      <x:c r="K113" s="31"/>
+      <x:c r="L113" s="31"/>
+      <x:c r="M113" s="31"/>
+      <x:c r="N113" s="31"/>
+      <x:c r="O113" s="31"/>
+      <x:c r="P113" s="31"/>
+      <x:c r="Q113" s="31"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="31"/>
+      <x:c r="B114" s="31"/>
+      <x:c r="C114" s="31"/>
+      <x:c r="D114" s="31"/>
+      <x:c r="E114" s="31"/>
+      <x:c r="F114" s="31"/>
+      <x:c r="G114" s="31"/>
+      <x:c r="H114" s="31"/>
+      <x:c r="I114" s="31"/>
+      <x:c r="J114" s="31"/>
+      <x:c r="K114" s="31"/>
+      <x:c r="L114" s="31"/>
+      <x:c r="M114" s="31"/>
+      <x:c r="N114" s="31"/>
+      <x:c r="O114" s="31"/>
+      <x:c r="P114" s="31"/>
+      <x:c r="Q114" s="31"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="31"/>
+      <x:c r="B115" s="31"/>
+      <x:c r="C115" s="31"/>
+      <x:c r="D115" s="31"/>
+      <x:c r="E115" s="31"/>
+      <x:c r="F115" s="31"/>
+      <x:c r="G115" s="31"/>
+      <x:c r="H115" s="31"/>
+      <x:c r="I115" s="31"/>
+      <x:c r="J115" s="31"/>
+      <x:c r="K115" s="31"/>
+      <x:c r="L115" s="31"/>
+      <x:c r="M115" s="31"/>
+      <x:c r="N115" s="31"/>
+      <x:c r="O115" s="31"/>
+      <x:c r="P115" s="31"/>
+      <x:c r="Q115" s="31"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="31"/>
+      <x:c r="B116" s="31"/>
+      <x:c r="C116" s="31"/>
+      <x:c r="D116" s="31"/>
+      <x:c r="E116" s="31"/>
+      <x:c r="F116" s="31"/>
+      <x:c r="G116" s="31"/>
+      <x:c r="H116" s="31"/>
+      <x:c r="I116" s="31"/>
+      <x:c r="J116" s="31"/>
+      <x:c r="K116" s="31"/>
+      <x:c r="L116" s="31"/>
+      <x:c r="M116" s="31"/>
+      <x:c r="N116" s="31"/>
+      <x:c r="O116" s="31"/>
+      <x:c r="P116" s="31"/>
+      <x:c r="Q116" s="31"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="31"/>
+      <x:c r="B117" s="31"/>
+      <x:c r="C117" s="31"/>
+      <x:c r="D117" s="31"/>
+      <x:c r="E117" s="31"/>
+      <x:c r="F117" s="31"/>
+      <x:c r="G117" s="31"/>
+      <x:c r="H117" s="31"/>
+      <x:c r="I117" s="31"/>
+      <x:c r="J117" s="31"/>
+      <x:c r="K117" s="31"/>
+      <x:c r="L117" s="31"/>
+      <x:c r="M117" s="31"/>
+      <x:c r="N117" s="31"/>
+      <x:c r="O117" s="31"/>
+      <x:c r="P117" s="31"/>
+      <x:c r="Q117" s="31"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="31"/>
+      <x:c r="B118" s="31"/>
+      <x:c r="C118" s="31"/>
+      <x:c r="D118" s="31"/>
+      <x:c r="E118" s="31"/>
+      <x:c r="F118" s="31"/>
+      <x:c r="G118" s="31"/>
+      <x:c r="H118" s="31"/>
+      <x:c r="I118" s="31"/>
+      <x:c r="J118" s="31"/>
+      <x:c r="K118" s="31"/>
+      <x:c r="L118" s="31"/>
+      <x:c r="M118" s="31"/>
+      <x:c r="N118" s="31"/>
+      <x:c r="O118" s="31"/>
+      <x:c r="P118" s="31"/>
+      <x:c r="Q118" s="31"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="31"/>
+      <x:c r="B119" s="31"/>
+      <x:c r="C119" s="31"/>
+      <x:c r="D119" s="31"/>
+      <x:c r="E119" s="31"/>
+      <x:c r="F119" s="31"/>
+      <x:c r="G119" s="31"/>
+      <x:c r="H119" s="31"/>
+      <x:c r="I119" s="31"/>
+      <x:c r="J119" s="31"/>
+      <x:c r="K119" s="31"/>
+      <x:c r="L119" s="31"/>
+      <x:c r="M119" s="31"/>
+      <x:c r="N119" s="31"/>
+      <x:c r="O119" s="31"/>
+      <x:c r="P119" s="31"/>
+      <x:c r="Q119" s="31"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="31"/>
+      <x:c r="B120" s="31"/>
+      <x:c r="C120" s="31"/>
+      <x:c r="D120" s="31"/>
+      <x:c r="E120" s="31"/>
+      <x:c r="F120" s="31"/>
+      <x:c r="G120" s="31"/>
+      <x:c r="H120" s="31"/>
+      <x:c r="I120" s="31"/>
+      <x:c r="J120" s="31"/>
+      <x:c r="K120" s="31"/>
+      <x:c r="L120" s="31"/>
+      <x:c r="M120" s="31"/>
+      <x:c r="N120" s="31"/>
+      <x:c r="O120" s="31"/>
+      <x:c r="P120" s="31"/>
+      <x:c r="Q120" s="31"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="31"/>
+      <x:c r="B121" s="31"/>
+      <x:c r="C121" s="31"/>
+      <x:c r="D121" s="31"/>
+      <x:c r="E121" s="31"/>
+      <x:c r="F121" s="31"/>
+      <x:c r="G121" s="31"/>
+      <x:c r="H121" s="31"/>
+      <x:c r="I121" s="31"/>
+      <x:c r="J121" s="31"/>
+      <x:c r="K121" s="31"/>
+      <x:c r="L121" s="31"/>
+      <x:c r="M121" s="31"/>
+      <x:c r="N121" s="31"/>
+      <x:c r="O121" s="31"/>
+      <x:c r="P121" s="31"/>
+      <x:c r="Q121" s="31"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="31"/>
+      <x:c r="B122" s="31"/>
+      <x:c r="C122" s="31"/>
+      <x:c r="D122" s="31"/>
+      <x:c r="E122" s="31"/>
+      <x:c r="F122" s="31"/>
+      <x:c r="G122" s="31"/>
+      <x:c r="H122" s="31"/>
+      <x:c r="I122" s="31"/>
+      <x:c r="J122" s="31"/>
+      <x:c r="K122" s="31"/>
+      <x:c r="L122" s="31"/>
+      <x:c r="M122" s="31"/>
+      <x:c r="N122" s="31"/>
+      <x:c r="O122" s="31"/>
+      <x:c r="P122" s="31"/>
+      <x:c r="Q122" s="31"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="31"/>
+      <x:c r="B123" s="31"/>
+      <x:c r="C123" s="31"/>
+      <x:c r="D123" s="31"/>
+      <x:c r="E123" s="31"/>
+      <x:c r="F123" s="31"/>
+      <x:c r="G123" s="31"/>
+      <x:c r="H123" s="31"/>
+      <x:c r="I123" s="31"/>
+      <x:c r="J123" s="31"/>
+      <x:c r="K123" s="31"/>
+      <x:c r="L123" s="31"/>
+      <x:c r="M123" s="31"/>
+      <x:c r="N123" s="31"/>
+      <x:c r="O123" s="31"/>
+      <x:c r="P123" s="31"/>
+      <x:c r="Q123" s="31"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="31"/>
+      <x:c r="B124" s="31"/>
+      <x:c r="C124" s="31"/>
+      <x:c r="D124" s="31"/>
+      <x:c r="E124" s="31"/>
+      <x:c r="F124" s="31"/>
+      <x:c r="G124" s="31"/>
+      <x:c r="H124" s="31"/>
+      <x:c r="I124" s="31"/>
+      <x:c r="J124" s="31"/>
+      <x:c r="K124" s="31"/>
+      <x:c r="L124" s="31"/>
+      <x:c r="M124" s="31"/>
+      <x:c r="N124" s="31"/>
+      <x:c r="O124" s="31"/>
+      <x:c r="P124" s="31"/>
+      <x:c r="Q124" s="31"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="31"/>
+      <x:c r="B125" s="31"/>
+      <x:c r="C125" s="31"/>
+      <x:c r="D125" s="31"/>
+      <x:c r="E125" s="31"/>
+      <x:c r="F125" s="31"/>
+      <x:c r="G125" s="31"/>
+      <x:c r="H125" s="31"/>
+      <x:c r="I125" s="31"/>
+      <x:c r="J125" s="31"/>
+      <x:c r="K125" s="31"/>
+      <x:c r="L125" s="31"/>
+      <x:c r="M125" s="31"/>
+      <x:c r="N125" s="31"/>
+      <x:c r="O125" s="31"/>
+      <x:c r="P125" s="31"/>
+      <x:c r="Q125" s="31"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="31"/>
+      <x:c r="B126" s="31"/>
+      <x:c r="C126" s="31"/>
+      <x:c r="D126" s="31"/>
+      <x:c r="E126" s="31"/>
+      <x:c r="F126" s="31"/>
+      <x:c r="G126" s="31"/>
+      <x:c r="H126" s="31"/>
+      <x:c r="I126" s="31"/>
+      <x:c r="J126" s="31"/>
+      <x:c r="K126" s="31"/>
+      <x:c r="L126" s="31"/>
+      <x:c r="M126" s="31"/>
+      <x:c r="N126" s="31"/>
+      <x:c r="O126" s="31"/>
+      <x:c r="P126" s="31"/>
+      <x:c r="Q126" s="31"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="31"/>
+      <x:c r="B127" s="31"/>
+      <x:c r="C127" s="31"/>
+      <x:c r="D127" s="31"/>
+      <x:c r="E127" s="31"/>
+      <x:c r="F127" s="31"/>
+      <x:c r="G127" s="31"/>
+      <x:c r="H127" s="31"/>
+      <x:c r="I127" s="31"/>
+      <x:c r="J127" s="31"/>
+      <x:c r="K127" s="31"/>
+      <x:c r="L127" s="31"/>
+      <x:c r="M127" s="31"/>
+      <x:c r="N127" s="31"/>
+      <x:c r="O127" s="31"/>
+      <x:c r="P127" s="31"/>
+      <x:c r="Q127" s="31"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="31"/>
+      <x:c r="B128" s="31"/>
+      <x:c r="C128" s="31"/>
+      <x:c r="D128" s="31"/>
+      <x:c r="E128" s="31"/>
+      <x:c r="F128" s="31"/>
+      <x:c r="G128" s="31"/>
+      <x:c r="H128" s="31"/>
+      <x:c r="I128" s="31"/>
+      <x:c r="J128" s="31"/>
+      <x:c r="K128" s="31"/>
+      <x:c r="L128" s="31"/>
+      <x:c r="M128" s="31"/>
+      <x:c r="N128" s="31"/>
+      <x:c r="O128" s="31"/>
+      <x:c r="P128" s="31"/>
+      <x:c r="Q128" s="31"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="31"/>
+      <x:c r="B129" s="31"/>
+      <x:c r="C129" s="31"/>
+      <x:c r="D129" s="31"/>
+      <x:c r="E129" s="31"/>
+      <x:c r="F129" s="31"/>
+      <x:c r="G129" s="31"/>
+      <x:c r="H129" s="31"/>
+      <x:c r="I129" s="31"/>
+      <x:c r="J129" s="31"/>
+      <x:c r="K129" s="31"/>
+      <x:c r="L129" s="31"/>
+      <x:c r="M129" s="31"/>
+      <x:c r="N129" s="31"/>
+      <x:c r="O129" s="31"/>
+      <x:c r="P129" s="31"/>
+      <x:c r="Q129" s="31"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="31"/>
+      <x:c r="B130" s="31"/>
+      <x:c r="C130" s="31"/>
+      <x:c r="D130" s="31"/>
+      <x:c r="E130" s="31"/>
+      <x:c r="F130" s="31"/>
+      <x:c r="G130" s="31"/>
+      <x:c r="H130" s="31"/>
+      <x:c r="I130" s="31"/>
+      <x:c r="J130" s="31"/>
+      <x:c r="K130" s="31"/>
+      <x:c r="L130" s="31"/>
+      <x:c r="M130" s="31"/>
+      <x:c r="N130" s="31"/>
+      <x:c r="O130" s="31"/>
+      <x:c r="P130" s="31"/>
+      <x:c r="Q130" s="31"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="31"/>
+      <x:c r="B131" s="31"/>
+      <x:c r="C131" s="31"/>
+      <x:c r="D131" s="31"/>
+      <x:c r="E131" s="31"/>
+      <x:c r="F131" s="31"/>
+      <x:c r="G131" s="31"/>
+      <x:c r="H131" s="31"/>
+      <x:c r="I131" s="31"/>
+      <x:c r="J131" s="31"/>
+      <x:c r="K131" s="31"/>
+      <x:c r="L131" s="31"/>
+      <x:c r="M131" s="31"/>
+      <x:c r="N131" s="31"/>
+      <x:c r="O131" s="31"/>
+      <x:c r="P131" s="31"/>
+      <x:c r="Q131" s="31"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="31"/>
+      <x:c r="B132" s="31"/>
+      <x:c r="C132" s="31"/>
+      <x:c r="D132" s="31"/>
+      <x:c r="E132" s="31"/>
+      <x:c r="F132" s="31"/>
+      <x:c r="G132" s="31"/>
+      <x:c r="H132" s="31"/>
+      <x:c r="I132" s="31"/>
+      <x:c r="J132" s="31"/>
+      <x:c r="K132" s="31"/>
+      <x:c r="L132" s="31"/>
+      <x:c r="M132" s="31"/>
+      <x:c r="N132" s="31"/>
+      <x:c r="O132" s="31"/>
+      <x:c r="P132" s="31"/>
+      <x:c r="Q132" s="31"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="31"/>
+      <x:c r="B133" s="31"/>
+      <x:c r="C133" s="31"/>
+      <x:c r="D133" s="31"/>
+      <x:c r="E133" s="31"/>
+      <x:c r="F133" s="31"/>
+      <x:c r="G133" s="31"/>
+      <x:c r="H133" s="31"/>
+      <x:c r="I133" s="31"/>
+      <x:c r="J133" s="31"/>
+      <x:c r="K133" s="31"/>
+      <x:c r="L133" s="31"/>
+      <x:c r="M133" s="31"/>
+      <x:c r="N133" s="31"/>
+      <x:c r="O133" s="31"/>
+      <x:c r="P133" s="31"/>
+      <x:c r="Q133" s="31"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="31"/>
+      <x:c r="B134" s="31"/>
+      <x:c r="C134" s="31"/>
+      <x:c r="D134" s="31"/>
+      <x:c r="E134" s="31"/>
+      <x:c r="F134" s="31"/>
+      <x:c r="G134" s="31"/>
+      <x:c r="H134" s="31"/>
+      <x:c r="I134" s="31"/>
+      <x:c r="J134" s="31"/>
+      <x:c r="K134" s="31"/>
+      <x:c r="L134" s="31"/>
+      <x:c r="M134" s="31"/>
+      <x:c r="N134" s="31"/>
+      <x:c r="O134" s="31"/>
+      <x:c r="P134" s="31"/>
+      <x:c r="Q134" s="31"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="31"/>
+      <x:c r="B135" s="31"/>
+      <x:c r="C135" s="31"/>
+      <x:c r="D135" s="31"/>
+      <x:c r="E135" s="31"/>
+      <x:c r="F135" s="31"/>
+      <x:c r="G135" s="31"/>
+      <x:c r="H135" s="31"/>
+      <x:c r="I135" s="31"/>
+      <x:c r="J135" s="31"/>
+      <x:c r="K135" s="31"/>
+      <x:c r="L135" s="31"/>
+      <x:c r="M135" s="31"/>
+      <x:c r="N135" s="31"/>
+      <x:c r="O135" s="31"/>
+      <x:c r="P135" s="31"/>
+      <x:c r="Q135" s="31"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="31"/>
+      <x:c r="B136" s="31"/>
+      <x:c r="C136" s="31"/>
+      <x:c r="D136" s="31"/>
+      <x:c r="E136" s="31"/>
+      <x:c r="F136" s="31"/>
+      <x:c r="G136" s="31"/>
+      <x:c r="H136" s="31"/>
+      <x:c r="I136" s="31"/>
+      <x:c r="J136" s="31"/>
+      <x:c r="K136" s="31"/>
+      <x:c r="L136" s="31"/>
+      <x:c r="M136" s="31"/>
+      <x:c r="N136" s="31"/>
+      <x:c r="O136" s="31"/>
+      <x:c r="P136" s="31"/>
+      <x:c r="Q136" s="31"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="31"/>
+      <x:c r="B137" s="31"/>
+      <x:c r="C137" s="31"/>
+      <x:c r="D137" s="31"/>
+      <x:c r="E137" s="31"/>
+      <x:c r="F137" s="31"/>
+      <x:c r="G137" s="31"/>
+      <x:c r="H137" s="31"/>
+      <x:c r="I137" s="31"/>
+      <x:c r="J137" s="31"/>
+      <x:c r="K137" s="31"/>
+      <x:c r="L137" s="31"/>
+      <x:c r="M137" s="31"/>
+      <x:c r="N137" s="31"/>
+      <x:c r="O137" s="31"/>
+      <x:c r="P137" s="31"/>
+      <x:c r="Q137" s="31"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="31"/>
+      <x:c r="B138" s="31"/>
+      <x:c r="C138" s="31"/>
+      <x:c r="D138" s="31"/>
+      <x:c r="E138" s="31"/>
+      <x:c r="F138" s="31"/>
+      <x:c r="G138" s="31"/>
+      <x:c r="H138" s="31"/>
+      <x:c r="I138" s="31"/>
+      <x:c r="J138" s="31"/>
+      <x:c r="K138" s="31"/>
+      <x:c r="L138" s="31"/>
+      <x:c r="M138" s="31"/>
+      <x:c r="N138" s="31"/>
+      <x:c r="O138" s="31"/>
+      <x:c r="P138" s="31"/>
+      <x:c r="Q138" s="31"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="31"/>
+      <x:c r="B139" s="31"/>
+      <x:c r="C139" s="31"/>
+      <x:c r="D139" s="31"/>
+      <x:c r="E139" s="31"/>
+      <x:c r="F139" s="31"/>
+      <x:c r="G139" s="31"/>
+      <x:c r="H139" s="31"/>
+      <x:c r="I139" s="31"/>
+      <x:c r="J139" s="31"/>
+      <x:c r="K139" s="31"/>
+      <x:c r="L139" s="31"/>
+      <x:c r="M139" s="31"/>
+      <x:c r="N139" s="31"/>
+      <x:c r="O139" s="31"/>
+      <x:c r="P139" s="31"/>
+      <x:c r="Q139" s="31"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="31"/>
+      <x:c r="B140" s="31"/>
+      <x:c r="C140" s="31"/>
+      <x:c r="D140" s="31"/>
+      <x:c r="E140" s="31"/>
+      <x:c r="F140" s="31"/>
+      <x:c r="G140" s="31"/>
+      <x:c r="H140" s="31"/>
+      <x:c r="I140" s="31"/>
+      <x:c r="J140" s="31"/>
+      <x:c r="K140" s="31"/>
+      <x:c r="L140" s="31"/>
+      <x:c r="M140" s="31"/>
+      <x:c r="N140" s="31"/>
+      <x:c r="O140" s="31"/>
+      <x:c r="P140" s="31"/>
+      <x:c r="Q140" s="31"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="31"/>
+      <x:c r="B141" s="31"/>
+      <x:c r="C141" s="31"/>
+      <x:c r="D141" s="31"/>
+      <x:c r="E141" s="31"/>
+      <x:c r="F141" s="31"/>
+      <x:c r="G141" s="31"/>
+      <x:c r="H141" s="31"/>
+      <x:c r="I141" s="31"/>
+      <x:c r="J141" s="31"/>
+      <x:c r="K141" s="31"/>
+      <x:c r="L141" s="31"/>
+      <x:c r="M141" s="31"/>
+      <x:c r="N141" s="31"/>
+      <x:c r="O141" s="31"/>
+      <x:c r="P141" s="31"/>
+      <x:c r="Q141" s="31"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="31"/>
+      <x:c r="B142" s="31"/>
+      <x:c r="C142" s="31"/>
+      <x:c r="D142" s="31"/>
+      <x:c r="E142" s="31"/>
+      <x:c r="F142" s="31"/>
+      <x:c r="G142" s="31"/>
+      <x:c r="H142" s="31"/>
+      <x:c r="I142" s="31"/>
+      <x:c r="J142" s="31"/>
+      <x:c r="K142" s="31"/>
+      <x:c r="L142" s="31"/>
+      <x:c r="M142" s="31"/>
+      <x:c r="N142" s="31"/>
+      <x:c r="O142" s="31"/>
+      <x:c r="P142" s="31"/>
+      <x:c r="Q142" s="31"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="31"/>
+      <x:c r="B143" s="31"/>
+      <x:c r="C143" s="31"/>
+      <x:c r="D143" s="31"/>
+      <x:c r="E143" s="31"/>
+      <x:c r="F143" s="31"/>
+      <x:c r="G143" s="31"/>
+      <x:c r="H143" s="31"/>
+      <x:c r="I143" s="31"/>
+      <x:c r="J143" s="31"/>
+      <x:c r="K143" s="31"/>
+      <x:c r="L143" s="31"/>
+      <x:c r="M143" s="31"/>
+      <x:c r="N143" s="31"/>
+      <x:c r="O143" s="31"/>
+      <x:c r="P143" s="31"/>
+      <x:c r="Q143" s="31"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="31"/>
+      <x:c r="B144" s="31"/>
+      <x:c r="C144" s="31"/>
+      <x:c r="D144" s="31"/>
+      <x:c r="E144" s="31"/>
+      <x:c r="F144" s="31"/>
+      <x:c r="G144" s="31"/>
+      <x:c r="H144" s="31"/>
+      <x:c r="I144" s="31"/>
+      <x:c r="J144" s="31"/>
+      <x:c r="K144" s="31"/>
+      <x:c r="L144" s="31"/>
+      <x:c r="M144" s="31"/>
+      <x:c r="N144" s="31"/>
+      <x:c r="O144" s="31"/>
+      <x:c r="P144" s="31"/>
+      <x:c r="Q144" s="31"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="31"/>
+      <x:c r="B145" s="31"/>
+      <x:c r="C145" s="31"/>
+      <x:c r="D145" s="31"/>
+      <x:c r="E145" s="31"/>
+      <x:c r="F145" s="31"/>
+      <x:c r="G145" s="31"/>
+      <x:c r="H145" s="31"/>
+      <x:c r="I145" s="31"/>
+      <x:c r="J145" s="31"/>
+      <x:c r="K145" s="31"/>
+      <x:c r="L145" s="31"/>
+      <x:c r="M145" s="31"/>
+      <x:c r="N145" s="31"/>
+      <x:c r="O145" s="31"/>
+      <x:c r="P145" s="31"/>
+      <x:c r="Q145" s="31"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="31"/>
+      <x:c r="B146" s="31"/>
+      <x:c r="C146" s="31"/>
+      <x:c r="D146" s="31"/>
+      <x:c r="E146" s="31"/>
+      <x:c r="F146" s="31"/>
+      <x:c r="G146" s="31"/>
+      <x:c r="H146" s="31"/>
+      <x:c r="I146" s="31"/>
+      <x:c r="J146" s="31"/>
+      <x:c r="K146" s="31"/>
+      <x:c r="L146" s="31"/>
+      <x:c r="M146" s="31"/>
+      <x:c r="N146" s="31"/>
+      <x:c r="O146" s="31"/>
+      <x:c r="P146" s="31"/>
+      <x:c r="Q146" s="31"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="31"/>
+      <x:c r="B147" s="31"/>
+      <x:c r="C147" s="31"/>
+      <x:c r="D147" s="31"/>
+      <x:c r="E147" s="31"/>
+      <x:c r="F147" s="31"/>
+      <x:c r="G147" s="31"/>
+      <x:c r="H147" s="31"/>
+      <x:c r="I147" s="31"/>
+      <x:c r="J147" s="31"/>
+      <x:c r="K147" s="31"/>
+      <x:c r="L147" s="31"/>
+      <x:c r="M147" s="31"/>
+      <x:c r="N147" s="31"/>
+      <x:c r="O147" s="31"/>
+      <x:c r="P147" s="31"/>
+      <x:c r="Q147" s="31"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="31"/>
+      <x:c r="B148" s="31"/>
+      <x:c r="C148" s="31"/>
+      <x:c r="D148" s="31"/>
+      <x:c r="E148" s="31"/>
+      <x:c r="F148" s="31"/>
+      <x:c r="G148" s="31"/>
+      <x:c r="H148" s="31"/>
+      <x:c r="I148" s="31"/>
+      <x:c r="J148" s="31"/>
+      <x:c r="K148" s="31"/>
+      <x:c r="L148" s="31"/>
+      <x:c r="M148" s="31"/>
+      <x:c r="N148" s="31"/>
+      <x:c r="O148" s="31"/>
+      <x:c r="P148" s="31"/>
+      <x:c r="Q148" s="31"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="31"/>
+      <x:c r="B149" s="31"/>
+      <x:c r="C149" s="31"/>
+      <x:c r="D149" s="31"/>
+      <x:c r="E149" s="31"/>
+      <x:c r="F149" s="31"/>
+      <x:c r="G149" s="31"/>
+      <x:c r="H149" s="31"/>
+      <x:c r="I149" s="31"/>
+      <x:c r="J149" s="31"/>
+      <x:c r="K149" s="31"/>
+      <x:c r="L149" s="31"/>
+      <x:c r="M149" s="31"/>
+      <x:c r="N149" s="31"/>
+      <x:c r="O149" s="31"/>
+      <x:c r="P149" s="31"/>
+      <x:c r="Q149" s="31"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="31"/>
+      <x:c r="B150" s="31"/>
+      <x:c r="C150" s="31"/>
+      <x:c r="D150" s="31"/>
+      <x:c r="E150" s="31"/>
+      <x:c r="F150" s="31"/>
+      <x:c r="G150" s="31"/>
+      <x:c r="H150" s="31"/>
+      <x:c r="I150" s="31"/>
+      <x:c r="J150" s="31"/>
+      <x:c r="K150" s="31"/>
+      <x:c r="L150" s="31"/>
+      <x:c r="M150" s="31"/>
+      <x:c r="N150" s="31"/>
+      <x:c r="O150" s="31"/>
+      <x:c r="P150" s="31"/>
+      <x:c r="Q150" s="31"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="31"/>
+      <x:c r="B151" s="31"/>
+      <x:c r="C151" s="31"/>
+      <x:c r="D151" s="31"/>
+      <x:c r="E151" s="31"/>
+      <x:c r="F151" s="31"/>
+      <x:c r="G151" s="31"/>
+      <x:c r="H151" s="31"/>
+      <x:c r="I151" s="31"/>
+      <x:c r="J151" s="31"/>
+      <x:c r="K151" s="31"/>
+      <x:c r="L151" s="31"/>
+      <x:c r="M151" s="31"/>
+      <x:c r="N151" s="31"/>
+      <x:c r="O151" s="31"/>
+      <x:c r="P151" s="31"/>
+      <x:c r="Q151" s="31"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="31"/>
+      <x:c r="B152" s="31"/>
+      <x:c r="C152" s="31"/>
+      <x:c r="D152" s="31"/>
+      <x:c r="E152" s="31"/>
+      <x:c r="F152" s="31"/>
+      <x:c r="G152" s="31"/>
+      <x:c r="H152" s="31"/>
+      <x:c r="I152" s="31"/>
+      <x:c r="J152" s="31"/>
+      <x:c r="K152" s="31"/>
+      <x:c r="L152" s="31"/>
+      <x:c r="M152" s="31"/>
+      <x:c r="N152" s="31"/>
+      <x:c r="O152" s="31"/>
+      <x:c r="P152" s="31"/>
+      <x:c r="Q152" s="31"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="31"/>
+      <x:c r="B153" s="31"/>
+      <x:c r="C153" s="31"/>
+      <x:c r="D153" s="31"/>
+      <x:c r="E153" s="31"/>
+      <x:c r="F153" s="31"/>
+      <x:c r="G153" s="31"/>
+      <x:c r="H153" s="31"/>
+      <x:c r="I153" s="31"/>
+      <x:c r="J153" s="31"/>
+      <x:c r="K153" s="31"/>
+      <x:c r="L153" s="31"/>
+      <x:c r="M153" s="31"/>
+      <x:c r="N153" s="31"/>
+      <x:c r="O153" s="31"/>
+      <x:c r="P153" s="31"/>
+      <x:c r="Q153" s="31"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="31"/>
+      <x:c r="B154" s="31"/>
+      <x:c r="C154" s="31"/>
+      <x:c r="D154" s="31"/>
+      <x:c r="E154" s="31"/>
+      <x:c r="F154" s="31"/>
+      <x:c r="G154" s="31"/>
+      <x:c r="H154" s="31"/>
+      <x:c r="I154" s="31"/>
+      <x:c r="J154" s="31"/>
+      <x:c r="K154" s="31"/>
+      <x:c r="L154" s="31"/>
+      <x:c r="M154" s="31"/>
+      <x:c r="N154" s="31"/>
+      <x:c r="O154" s="31"/>
+      <x:c r="P154" s="31"/>
+      <x:c r="Q154" s="31"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="31"/>
+      <x:c r="B155" s="31"/>
+      <x:c r="C155" s="31"/>
+      <x:c r="D155" s="31"/>
+      <x:c r="E155" s="31"/>
+      <x:c r="F155" s="31"/>
+      <x:c r="G155" s="31"/>
+      <x:c r="H155" s="31"/>
+      <x:c r="I155" s="31"/>
+      <x:c r="J155" s="31"/>
+      <x:c r="K155" s="31"/>
+      <x:c r="L155" s="31"/>
+      <x:c r="M155" s="31"/>
+      <x:c r="N155" s="31"/>
+      <x:c r="O155" s="31"/>
+      <x:c r="P155" s="31"/>
+      <x:c r="Q155" s="31"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="31"/>
+      <x:c r="B156" s="31"/>
+      <x:c r="C156" s="31"/>
+      <x:c r="D156" s="31"/>
+      <x:c r="E156" s="31"/>
+      <x:c r="F156" s="31"/>
+      <x:c r="G156" s="31"/>
+      <x:c r="H156" s="31"/>
+      <x:c r="I156" s="31"/>
+      <x:c r="J156" s="31"/>
+      <x:c r="K156" s="31"/>
+      <x:c r="L156" s="31"/>
+      <x:c r="M156" s="31"/>
+      <x:c r="N156" s="31"/>
+      <x:c r="O156" s="31"/>
+      <x:c r="P156" s="31"/>
+      <x:c r="Q156" s="31"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="31"/>
+      <x:c r="B157" s="31"/>
+      <x:c r="C157" s="31"/>
+      <x:c r="D157" s="31"/>
+      <x:c r="E157" s="31"/>
+      <x:c r="F157" s="31"/>
+      <x:c r="G157" s="31"/>
+      <x:c r="H157" s="31"/>
+      <x:c r="I157" s="31"/>
+      <x:c r="J157" s="31"/>
+      <x:c r="K157" s="31"/>
+      <x:c r="L157" s="31"/>
+      <x:c r="M157" s="31"/>
+      <x:c r="N157" s="31"/>
+      <x:c r="O157" s="31"/>
+      <x:c r="P157" s="31"/>
+      <x:c r="Q157" s="31"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="31"/>
+      <x:c r="B158" s="31"/>
+      <x:c r="C158" s="31"/>
+      <x:c r="D158" s="31"/>
+      <x:c r="E158" s="31"/>
+      <x:c r="F158" s="31"/>
+      <x:c r="G158" s="31"/>
+      <x:c r="H158" s="31"/>
+      <x:c r="I158" s="31"/>
+      <x:c r="J158" s="31"/>
+      <x:c r="K158" s="31"/>
+      <x:c r="L158" s="31"/>
+      <x:c r="M158" s="31"/>
+      <x:c r="N158" s="31"/>
+      <x:c r="O158" s="31"/>
+      <x:c r="P158" s="31"/>
+      <x:c r="Q158" s="31"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="31"/>
+      <x:c r="B159" s="31"/>
+      <x:c r="C159" s="31"/>
+      <x:c r="D159" s="31"/>
+      <x:c r="E159" s="31"/>
+      <x:c r="F159" s="31"/>
+      <x:c r="G159" s="31"/>
+      <x:c r="H159" s="31"/>
+      <x:c r="I159" s="31"/>
+      <x:c r="J159" s="31"/>
+      <x:c r="K159" s="31"/>
+      <x:c r="L159" s="31"/>
+      <x:c r="M159" s="31"/>
+      <x:c r="N159" s="31"/>
+      <x:c r="O159" s="31"/>
+      <x:c r="P159" s="31"/>
+      <x:c r="Q159" s="31"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="31"/>
+      <x:c r="B160" s="31"/>
+      <x:c r="C160" s="31"/>
+      <x:c r="D160" s="31"/>
+      <x:c r="E160" s="31"/>
+      <x:c r="F160" s="31"/>
+      <x:c r="G160" s="31"/>
+      <x:c r="H160" s="31"/>
+      <x:c r="I160" s="31"/>
+      <x:c r="J160" s="31"/>
+      <x:c r="K160" s="31"/>
+      <x:c r="L160" s="31"/>
+      <x:c r="M160" s="31"/>
+      <x:c r="N160" s="31"/>
+      <x:c r="O160" s="31"/>
+      <x:c r="P160" s="31"/>
+      <x:c r="Q160" s="31"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="31"/>
+      <x:c r="B161" s="31"/>
+      <x:c r="C161" s="31"/>
+      <x:c r="D161" s="31"/>
+      <x:c r="E161" s="31"/>
+      <x:c r="F161" s="31"/>
+      <x:c r="G161" s="31"/>
+      <x:c r="H161" s="31"/>
+      <x:c r="I161" s="31"/>
+      <x:c r="J161" s="31"/>
+      <x:c r="K161" s="31"/>
+      <x:c r="L161" s="31"/>
+      <x:c r="M161" s="31"/>
+      <x:c r="N161" s="31"/>
+      <x:c r="O161" s="31"/>
+      <x:c r="P161" s="31"/>
+      <x:c r="Q161" s="31"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="31"/>
+      <x:c r="B162" s="31"/>
+      <x:c r="C162" s="31"/>
+      <x:c r="D162" s="31"/>
+      <x:c r="E162" s="31"/>
+      <x:c r="F162" s="31"/>
+      <x:c r="G162" s="31"/>
+      <x:c r="H162" s="31"/>
+      <x:c r="I162" s="31"/>
+      <x:c r="J162" s="31"/>
+      <x:c r="K162" s="31"/>
+      <x:c r="L162" s="31"/>
+      <x:c r="M162" s="31"/>
+      <x:c r="N162" s="31"/>
+      <x:c r="O162" s="31"/>
+      <x:c r="P162" s="31"/>
+      <x:c r="Q162" s="31"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="31"/>
+      <x:c r="B163" s="31"/>
+      <x:c r="C163" s="31"/>
+      <x:c r="D163" s="31"/>
+      <x:c r="E163" s="31"/>
+      <x:c r="F163" s="31"/>
+      <x:c r="G163" s="31"/>
+      <x:c r="H163" s="31"/>
+      <x:c r="I163" s="31"/>
+      <x:c r="J163" s="31"/>
+      <x:c r="K163" s="31"/>
+      <x:c r="L163" s="31"/>
+      <x:c r="M163" s="31"/>
+      <x:c r="N163" s="31"/>
+      <x:c r="O163" s="31"/>
+      <x:c r="P163" s="31"/>
+      <x:c r="Q163" s="31"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="31"/>
+      <x:c r="B164" s="31"/>
+      <x:c r="C164" s="31"/>
+      <x:c r="D164" s="31"/>
+      <x:c r="E164" s="31"/>
+      <x:c r="F164" s="31"/>
+      <x:c r="G164" s="31"/>
+      <x:c r="H164" s="31"/>
+      <x:c r="I164" s="31"/>
+      <x:c r="J164" s="31"/>
+      <x:c r="K164" s="31"/>
+      <x:c r="L164" s="31"/>
+      <x:c r="M164" s="31"/>
+      <x:c r="N164" s="31"/>
+      <x:c r="O164" s="31"/>
+      <x:c r="P164" s="31"/>
+      <x:c r="Q164" s="31"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="31"/>
+      <x:c r="B165" s="31"/>
+      <x:c r="C165" s="31"/>
+      <x:c r="D165" s="31"/>
+      <x:c r="E165" s="31"/>
+      <x:c r="F165" s="31"/>
+      <x:c r="G165" s="31"/>
+      <x:c r="H165" s="31"/>
+      <x:c r="I165" s="31"/>
+      <x:c r="J165" s="31"/>
+      <x:c r="K165" s="31"/>
+      <x:c r="L165" s="31"/>
+      <x:c r="M165" s="31"/>
+      <x:c r="N165" s="31"/>
+      <x:c r="O165" s="31"/>
+      <x:c r="P165" s="31"/>
+      <x:c r="Q165" s="31"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="31"/>
+      <x:c r="B166" s="31"/>
+      <x:c r="C166" s="31"/>
+      <x:c r="D166" s="31"/>
+      <x:c r="E166" s="31"/>
+      <x:c r="F166" s="31"/>
+      <x:c r="G166" s="31"/>
+      <x:c r="H166" s="31"/>
+      <x:c r="I166" s="31"/>
+      <x:c r="J166" s="31"/>
+      <x:c r="K166" s="31"/>
+      <x:c r="L166" s="31"/>
+      <x:c r="M166" s="31"/>
+      <x:c r="N166" s="31"/>
+      <x:c r="O166" s="31"/>
+      <x:c r="P166" s="31"/>
+      <x:c r="Q166" s="31"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="31"/>
+      <x:c r="B167" s="31"/>
+      <x:c r="C167" s="31"/>
+      <x:c r="D167" s="31"/>
+      <x:c r="E167" s="31"/>
+      <x:c r="F167" s="31"/>
+      <x:c r="G167" s="31"/>
+      <x:c r="H167" s="31"/>
+      <x:c r="I167" s="31"/>
+      <x:c r="J167" s="31"/>
+      <x:c r="K167" s="31"/>
+      <x:c r="L167" s="31"/>
+      <x:c r="M167" s="31"/>
+      <x:c r="N167" s="31"/>
+      <x:c r="O167" s="31"/>
+      <x:c r="P167" s="31"/>
+      <x:c r="Q167" s="31"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="31"/>
+      <x:c r="B168" s="31"/>
+      <x:c r="C168" s="31"/>
+      <x:c r="D168" s="31"/>
+      <x:c r="E168" s="31"/>
+      <x:c r="F168" s="31"/>
+      <x:c r="G168" s="31"/>
+      <x:c r="H168" s="31"/>
+      <x:c r="I168" s="31"/>
+      <x:c r="J168" s="31"/>
+      <x:c r="K168" s="31"/>
+      <x:c r="L168" s="31"/>
+      <x:c r="M168" s="31"/>
+      <x:c r="N168" s="31"/>
+      <x:c r="O168" s="31"/>
+      <x:c r="P168" s="31"/>
+      <x:c r="Q168" s="31"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="31"/>
+      <x:c r="B169" s="31"/>
+      <x:c r="C169" s="31"/>
+      <x:c r="D169" s="31"/>
+      <x:c r="E169" s="31"/>
+      <x:c r="F169" s="31"/>
+      <x:c r="G169" s="31"/>
+      <x:c r="H169" s="31"/>
+      <x:c r="I169" s="31"/>
+      <x:c r="J169" s="31"/>
+      <x:c r="K169" s="31"/>
+      <x:c r="L169" s="31"/>
+      <x:c r="M169" s="31"/>
+      <x:c r="N169" s="31"/>
+      <x:c r="O169" s="31"/>
+      <x:c r="P169" s="31"/>
+      <x:c r="Q169" s="31"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="31"/>
+      <x:c r="B170" s="31"/>
+      <x:c r="C170" s="31"/>
+      <x:c r="D170" s="31"/>
+      <x:c r="E170" s="31"/>
+      <x:c r="F170" s="31"/>
+      <x:c r="G170" s="31"/>
+      <x:c r="H170" s="31"/>
+      <x:c r="I170" s="31"/>
+      <x:c r="J170" s="31"/>
+      <x:c r="K170" s="31"/>
+      <x:c r="L170" s="31"/>
+      <x:c r="M170" s="31"/>
+      <x:c r="N170" s="31"/>
+      <x:c r="O170" s="31"/>
+      <x:c r="P170" s="31"/>
+      <x:c r="Q170" s="31"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="31"/>
+      <x:c r="B171" s="31"/>
+      <x:c r="C171" s="31"/>
+      <x:c r="D171" s="31"/>
+      <x:c r="E171" s="31"/>
+      <x:c r="F171" s="31"/>
+      <x:c r="G171" s="31"/>
+      <x:c r="H171" s="31"/>
+      <x:c r="I171" s="31"/>
+      <x:c r="J171" s="31"/>
+      <x:c r="K171" s="31"/>
+      <x:c r="L171" s="31"/>
+      <x:c r="M171" s="31"/>
+      <x:c r="N171" s="31"/>
+      <x:c r="O171" s="31"/>
+      <x:c r="P171" s="31"/>
+      <x:c r="Q171" s="31"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="31"/>
+      <x:c r="B172" s="31"/>
+      <x:c r="C172" s="31"/>
+      <x:c r="D172" s="31"/>
+      <x:c r="E172" s="31"/>
+      <x:c r="F172" s="31"/>
+      <x:c r="G172" s="31"/>
+      <x:c r="H172" s="31"/>
+      <x:c r="I172" s="31"/>
+      <x:c r="J172" s="31"/>
+      <x:c r="K172" s="31"/>
+      <x:c r="L172" s="31"/>
+      <x:c r="M172" s="31"/>
+      <x:c r="N172" s="31"/>
+      <x:c r="O172" s="31"/>
+      <x:c r="P172" s="31"/>
+      <x:c r="Q172" s="31"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="31"/>
+      <x:c r="B173" s="31"/>
+      <x:c r="C173" s="31"/>
+      <x:c r="D173" s="31"/>
+      <x:c r="E173" s="31"/>
+      <x:c r="F173" s="31"/>
+      <x:c r="G173" s="31"/>
+      <x:c r="H173" s="31"/>
+      <x:c r="I173" s="31"/>
+      <x:c r="J173" s="31"/>
+      <x:c r="K173" s="31"/>
+      <x:c r="L173" s="31"/>
+      <x:c r="M173" s="31"/>
+      <x:c r="N173" s="31"/>
+      <x:c r="O173" s="31"/>
+      <x:c r="P173" s="31"/>
+      <x:c r="Q173" s="31"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="31"/>
+      <x:c r="B174" s="31"/>
+      <x:c r="C174" s="31"/>
+      <x:c r="D174" s="31"/>
+      <x:c r="E174" s="31"/>
+      <x:c r="F174" s="31"/>
+      <x:c r="G174" s="31"/>
+      <x:c r="H174" s="31"/>
+      <x:c r="I174" s="31"/>
+      <x:c r="J174" s="31"/>
+      <x:c r="K174" s="31"/>
+      <x:c r="L174" s="31"/>
+      <x:c r="M174" s="31"/>
+      <x:c r="N174" s="31"/>
+      <x:c r="O174" s="31"/>
+      <x:c r="P174" s="31"/>
+      <x:c r="Q174" s="31"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="31"/>
+      <x:c r="B175" s="31"/>
+      <x:c r="C175" s="31"/>
+      <x:c r="D175" s="31"/>
+      <x:c r="E175" s="31"/>
+      <x:c r="F175" s="31"/>
+      <x:c r="G175" s="31"/>
+      <x:c r="H175" s="31"/>
+      <x:c r="I175" s="31"/>
+      <x:c r="J175" s="31"/>
+      <x:c r="K175" s="31"/>
+      <x:c r="L175" s="31"/>
+      <x:c r="M175" s="31"/>
+      <x:c r="N175" s="31"/>
+      <x:c r="O175" s="31"/>
+      <x:c r="P175" s="31"/>
+      <x:c r="Q175" s="31"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="31"/>
+      <x:c r="B176" s="31"/>
+      <x:c r="C176" s="31"/>
+      <x:c r="D176" s="31"/>
+      <x:c r="E176" s="31"/>
+      <x:c r="F176" s="31"/>
+      <x:c r="G176" s="31"/>
+      <x:c r="H176" s="31"/>
+      <x:c r="I176" s="31"/>
+      <x:c r="J176" s="31"/>
+      <x:c r="K176" s="31"/>
+      <x:c r="L176" s="31"/>
+      <x:c r="M176" s="31"/>
+      <x:c r="N176" s="31"/>
+      <x:c r="O176" s="31"/>
+      <x:c r="P176" s="31"/>
+      <x:c r="Q176" s="31"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="31"/>
+      <x:c r="B177" s="31"/>
+      <x:c r="C177" s="31"/>
+      <x:c r="D177" s="31"/>
+      <x:c r="E177" s="31"/>
+      <x:c r="F177" s="31"/>
+      <x:c r="G177" s="31"/>
+      <x:c r="H177" s="31"/>
+      <x:c r="I177" s="31"/>
+      <x:c r="J177" s="31"/>
+      <x:c r="K177" s="31"/>
+      <x:c r="L177" s="31"/>
+      <x:c r="M177" s="31"/>
+      <x:c r="N177" s="31"/>
+      <x:c r="O177" s="31"/>
+      <x:c r="P177" s="31"/>
+      <x:c r="Q177" s="31"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="31"/>
+      <x:c r="B178" s="31"/>
+      <x:c r="C178" s="31"/>
+      <x:c r="D178" s="31"/>
+      <x:c r="E178" s="31"/>
+      <x:c r="F178" s="31"/>
+      <x:c r="G178" s="31"/>
+      <x:c r="H178" s="31"/>
+      <x:c r="I178" s="31"/>
+      <x:c r="J178" s="31"/>
+      <x:c r="K178" s="31"/>
+      <x:c r="L178" s="31"/>
+      <x:c r="M178" s="31"/>
+      <x:c r="N178" s="31"/>
+      <x:c r="O178" s="31"/>
+      <x:c r="P178" s="31"/>
+      <x:c r="Q178" s="31"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="31"/>
+      <x:c r="B179" s="31"/>
+      <x:c r="C179" s="31"/>
+      <x:c r="D179" s="31"/>
+      <x:c r="E179" s="31"/>
+      <x:c r="F179" s="31"/>
+      <x:c r="G179" s="31"/>
+      <x:c r="H179" s="31"/>
+      <x:c r="I179" s="31"/>
+      <x:c r="J179" s="31"/>
+      <x:c r="K179" s="31"/>
+      <x:c r="L179" s="31"/>
+      <x:c r="M179" s="31"/>
+      <x:c r="N179" s="31"/>
+      <x:c r="O179" s="31"/>
+      <x:c r="P179" s="31"/>
+      <x:c r="Q179" s="31"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="31"/>
+      <x:c r="B180" s="31"/>
+      <x:c r="C180" s="31"/>
+      <x:c r="D180" s="31"/>
+      <x:c r="E180" s="31"/>
+      <x:c r="F180" s="31"/>
+      <x:c r="G180" s="31"/>
+      <x:c r="H180" s="31"/>
+      <x:c r="I180" s="31"/>
+      <x:c r="J180" s="31"/>
+      <x:c r="K180" s="31"/>
+      <x:c r="L180" s="31"/>
+      <x:c r="M180" s="31"/>
+      <x:c r="N180" s="31"/>
+      <x:c r="O180" s="31"/>
+      <x:c r="P180" s="31"/>
+      <x:c r="Q180" s="31"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="31"/>
+      <x:c r="B181" s="31"/>
+      <x:c r="C181" s="31"/>
+      <x:c r="D181" s="31"/>
+      <x:c r="E181" s="31"/>
+      <x:c r="F181" s="31"/>
+      <x:c r="G181" s="31"/>
+      <x:c r="H181" s="31"/>
+      <x:c r="I181" s="31"/>
+      <x:c r="J181" s="31"/>
+      <x:c r="K181" s="31"/>
+      <x:c r="L181" s="31"/>
+      <x:c r="M181" s="31"/>
+      <x:c r="N181" s="31"/>
+      <x:c r="O181" s="31"/>
+      <x:c r="P181" s="31"/>
+      <x:c r="Q181" s="31"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31"/>
+      <x:c r="B182" s="31"/>
+      <x:c r="C182" s="31"/>
+      <x:c r="D182" s="31"/>
+      <x:c r="E182" s="31"/>
+      <x:c r="F182" s="31"/>
+      <x:c r="G182" s="31"/>
+      <x:c r="H182" s="31"/>
+      <x:c r="I182" s="31"/>
+      <x:c r="J182" s="31"/>
+      <x:c r="K182" s="31"/>
+      <x:c r="L182" s="31"/>
+      <x:c r="M182" s="31"/>
+      <x:c r="N182" s="31"/>
+      <x:c r="O182" s="31"/>
+      <x:c r="P182" s="31"/>
+      <x:c r="Q182" s="31"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31"/>
+      <x:c r="B183" s="31"/>
+      <x:c r="C183" s="31"/>
+      <x:c r="D183" s="31"/>
+      <x:c r="E183" s="31"/>
+      <x:c r="F183" s="31"/>
+      <x:c r="G183" s="31"/>
+      <x:c r="H183" s="31"/>
+      <x:c r="I183" s="31"/>
+      <x:c r="J183" s="31"/>
+      <x:c r="K183" s="31"/>
+      <x:c r="L183" s="31"/>
+      <x:c r="M183" s="31"/>
+      <x:c r="N183" s="31"/>
+      <x:c r="O183" s="31"/>
+      <x:c r="P183" s="31"/>
+      <x:c r="Q183" s="31"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31"/>
+      <x:c r="B184" s="31"/>
+      <x:c r="C184" s="31"/>
+      <x:c r="D184" s="31"/>
+      <x:c r="E184" s="31"/>
+      <x:c r="F184" s="31"/>
+      <x:c r="G184" s="31"/>
+      <x:c r="H184" s="31"/>
+      <x:c r="I184" s="31"/>
+      <x:c r="J184" s="31"/>
+      <x:c r="K184" s="31"/>
+      <x:c r="L184" s="31"/>
+      <x:c r="M184" s="31"/>
+      <x:c r="N184" s="31"/>
+      <x:c r="O184" s="31"/>
+      <x:c r="P184" s="31"/>
+      <x:c r="Q184" s="31"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31"/>
+      <x:c r="B185" s="31"/>
+      <x:c r="C185" s="31"/>
+      <x:c r="D185" s="31"/>
+      <x:c r="E185" s="31"/>
+      <x:c r="F185" s="31"/>
+      <x:c r="G185" s="31"/>
+      <x:c r="H185" s="31"/>
+      <x:c r="I185" s="31"/>
+      <x:c r="J185" s="31"/>
+      <x:c r="K185" s="31"/>
+      <x:c r="L185" s="31"/>
+      <x:c r="M185" s="31"/>
+      <x:c r="N185" s="31"/>
+      <x:c r="O185" s="31"/>
+      <x:c r="P185" s="31"/>
+      <x:c r="Q185" s="31"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31"/>
+      <x:c r="B186" s="31"/>
+      <x:c r="C186" s="31"/>
+      <x:c r="D186" s="31"/>
+      <x:c r="E186" s="31"/>
+      <x:c r="F186" s="31"/>
+      <x:c r="G186" s="31"/>
+      <x:c r="H186" s="31"/>
+      <x:c r="I186" s="31"/>
+      <x:c r="J186" s="31"/>
+      <x:c r="K186" s="31"/>
+      <x:c r="L186" s="31"/>
+      <x:c r="M186" s="31"/>
+      <x:c r="N186" s="31"/>
+      <x:c r="O186" s="31"/>
+      <x:c r="P186" s="31"/>
+      <x:c r="Q186" s="31"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31"/>
+      <x:c r="B187" s="31"/>
+      <x:c r="C187" s="31"/>
+      <x:c r="D187" s="31"/>
+      <x:c r="E187" s="31"/>
+      <x:c r="F187" s="31"/>
+      <x:c r="G187" s="31"/>
+      <x:c r="H187" s="31"/>
+      <x:c r="I187" s="31"/>
+      <x:c r="J187" s="31"/>
+      <x:c r="K187" s="31"/>
+      <x:c r="L187" s="31"/>
+      <x:c r="M187" s="31"/>
+      <x:c r="N187" s="31"/>
+      <x:c r="O187" s="31"/>
+      <x:c r="P187" s="31"/>
+      <x:c r="Q187" s="31"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31"/>
+      <x:c r="B188" s="31"/>
+      <x:c r="C188" s="31"/>
+      <x:c r="D188" s="31"/>
+      <x:c r="E188" s="31"/>
+      <x:c r="F188" s="31"/>
+      <x:c r="G188" s="31"/>
+      <x:c r="H188" s="31"/>
+      <x:c r="I188" s="31"/>
+      <x:c r="J188" s="31"/>
+      <x:c r="K188" s="31"/>
+      <x:c r="L188" s="31"/>
+      <x:c r="M188" s="31"/>
+      <x:c r="N188" s="31"/>
+      <x:c r="O188" s="31"/>
+      <x:c r="P188" s="31"/>
+      <x:c r="Q188" s="31"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31"/>
+      <x:c r="B189" s="31"/>
+      <x:c r="C189" s="31"/>
+      <x:c r="D189" s="31"/>
+      <x:c r="E189" s="31"/>
+      <x:c r="F189" s="31"/>
+      <x:c r="G189" s="31"/>
+      <x:c r="H189" s="31"/>
+      <x:c r="I189" s="31"/>
+      <x:c r="J189" s="31"/>
+      <x:c r="K189" s="31"/>
+      <x:c r="L189" s="31"/>
+      <x:c r="M189" s="31"/>
+      <x:c r="N189" s="31"/>
+      <x:c r="O189" s="31"/>
+      <x:c r="P189" s="31"/>
+      <x:c r="Q189" s="31"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31"/>
+      <x:c r="B190" s="31"/>
+      <x:c r="C190" s="31"/>
+      <x:c r="D190" s="31"/>
+      <x:c r="E190" s="31"/>
+      <x:c r="F190" s="31"/>
+      <x:c r="G190" s="31"/>
+      <x:c r="H190" s="31"/>
+      <x:c r="I190" s="31"/>
+      <x:c r="J190" s="31"/>
+      <x:c r="K190" s="31"/>
+      <x:c r="L190" s="31"/>
+      <x:c r="M190" s="31"/>
+      <x:c r="N190" s="31"/>
+      <x:c r="O190" s="31"/>
+      <x:c r="P190" s="31"/>
+      <x:c r="Q190" s="31"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="31"/>
+      <x:c r="B191" s="31"/>
+      <x:c r="C191" s="31"/>
+      <x:c r="D191" s="31"/>
+      <x:c r="E191" s="31"/>
+      <x:c r="F191" s="31"/>
+      <x:c r="G191" s="31"/>
+      <x:c r="H191" s="31"/>
+      <x:c r="I191" s="31"/>
+      <x:c r="J191" s="31"/>
+      <x:c r="K191" s="31"/>
+      <x:c r="L191" s="31"/>
+      <x:c r="M191" s="31"/>
+      <x:c r="N191" s="31"/>
+      <x:c r="O191" s="31"/>
+      <x:c r="P191" s="31"/>
+      <x:c r="Q191" s="31"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31"/>
+      <x:c r="B192" s="31"/>
+      <x:c r="C192" s="31"/>
+      <x:c r="D192" s="31"/>
+      <x:c r="E192" s="31"/>
+      <x:c r="F192" s="31"/>
+      <x:c r="G192" s="31"/>
+      <x:c r="H192" s="31"/>
+      <x:c r="I192" s="31"/>
+      <x:c r="J192" s="31"/>
+      <x:c r="K192" s="31"/>
+      <x:c r="L192" s="31"/>
+      <x:c r="M192" s="31"/>
+      <x:c r="N192" s="31"/>
+      <x:c r="O192" s="31"/>
+      <x:c r="P192" s="31"/>
+      <x:c r="Q192" s="31"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31"/>
+      <x:c r="B193" s="31"/>
+      <x:c r="C193" s="31"/>
+      <x:c r="D193" s="31"/>
+      <x:c r="E193" s="31"/>
+      <x:c r="F193" s="31"/>
+      <x:c r="G193" s="31"/>
+      <x:c r="H193" s="31"/>
+      <x:c r="I193" s="31"/>
+      <x:c r="J193" s="31"/>
+      <x:c r="K193" s="31"/>
+      <x:c r="L193" s="31"/>
+      <x:c r="M193" s="31"/>
+      <x:c r="N193" s="31"/>
+      <x:c r="O193" s="31"/>
+      <x:c r="P193" s="31"/>
+      <x:c r="Q193" s="31"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31"/>
+      <x:c r="B194" s="31"/>
+      <x:c r="C194" s="31"/>
+      <x:c r="D194" s="31"/>
+      <x:c r="E194" s="31"/>
+      <x:c r="F194" s="31"/>
+      <x:c r="G194" s="31"/>
+      <x:c r="H194" s="31"/>
+      <x:c r="I194" s="31"/>
+      <x:c r="J194" s="31"/>
+      <x:c r="K194" s="31"/>
+      <x:c r="L194" s="31"/>
+      <x:c r="M194" s="31"/>
+      <x:c r="N194" s="31"/>
+      <x:c r="O194" s="31"/>
+      <x:c r="P194" s="31"/>
+      <x:c r="Q194" s="31"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31"/>
+      <x:c r="B195" s="31"/>
+      <x:c r="C195" s="31"/>
+      <x:c r="D195" s="31"/>
+      <x:c r="E195" s="31"/>
+      <x:c r="F195" s="31"/>
+      <x:c r="G195" s="31"/>
+      <x:c r="H195" s="31"/>
+      <x:c r="I195" s="31"/>
+      <x:c r="J195" s="31"/>
+      <x:c r="K195" s="31"/>
+      <x:c r="L195" s="31"/>
+      <x:c r="M195" s="31"/>
+      <x:c r="N195" s="31"/>
+      <x:c r="O195" s="31"/>
+      <x:c r="P195" s="31"/>
+      <x:c r="Q195" s="31"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="31"/>
+      <x:c r="B196" s="31"/>
+      <x:c r="C196" s="31"/>
+      <x:c r="D196" s="31"/>
+      <x:c r="E196" s="31"/>
+      <x:c r="F196" s="31"/>
+      <x:c r="G196" s="31"/>
+      <x:c r="H196" s="31"/>
+      <x:c r="I196" s="31"/>
+      <x:c r="J196" s="31"/>
+      <x:c r="K196" s="31"/>
+      <x:c r="L196" s="31"/>
+      <x:c r="M196" s="31"/>
+      <x:c r="N196" s="31"/>
+      <x:c r="O196" s="31"/>
+      <x:c r="P196" s="31"/>
+      <x:c r="Q196" s="31"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="31"/>
+      <x:c r="B197" s="31"/>
+      <x:c r="C197" s="31"/>
+      <x:c r="D197" s="31"/>
+      <x:c r="E197" s="31"/>
+      <x:c r="F197" s="31"/>
+      <x:c r="G197" s="31"/>
+      <x:c r="H197" s="31"/>
+      <x:c r="I197" s="31"/>
+      <x:c r="J197" s="31"/>
+      <x:c r="K197" s="31"/>
+      <x:c r="L197" s="31"/>
+      <x:c r="M197" s="31"/>
+      <x:c r="N197" s="31"/>
+      <x:c r="O197" s="31"/>
+      <x:c r="P197" s="31"/>
+      <x:c r="Q197" s="31"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="31"/>
+      <x:c r="B198" s="31"/>
+      <x:c r="C198" s="31"/>
+      <x:c r="D198" s="31"/>
+      <x:c r="E198" s="31"/>
+      <x:c r="F198" s="31"/>
+      <x:c r="G198" s="31"/>
+      <x:c r="H198" s="31"/>
+      <x:c r="I198" s="31"/>
+      <x:c r="J198" s="31"/>
+      <x:c r="K198" s="31"/>
+      <x:c r="L198" s="31"/>
+      <x:c r="M198" s="31"/>
+      <x:c r="N198" s="31"/>
+      <x:c r="O198" s="31"/>
+      <x:c r="P198" s="31"/>
+      <x:c r="Q198" s="31"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="31"/>
+      <x:c r="B199" s="31"/>
+      <x:c r="C199" s="31"/>
+      <x:c r="D199" s="31"/>
+      <x:c r="E199" s="31"/>
+      <x:c r="F199" s="31"/>
+      <x:c r="G199" s="31"/>
+      <x:c r="H199" s="31"/>
+      <x:c r="I199" s="31"/>
+      <x:c r="J199" s="31"/>
+      <x:c r="K199" s="31"/>
+      <x:c r="L199" s="31"/>
+      <x:c r="M199" s="31"/>
+      <x:c r="N199" s="31"/>
+      <x:c r="O199" s="31"/>
+      <x:c r="P199" s="31"/>
+      <x:c r="Q199" s="31"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="31"/>
+      <x:c r="B200" s="31"/>
+      <x:c r="C200" s="31"/>
+      <x:c r="D200" s="31"/>
+      <x:c r="E200" s="31"/>
+      <x:c r="F200" s="31"/>
+      <x:c r="G200" s="31"/>
+      <x:c r="H200" s="31"/>
+      <x:c r="I200" s="31"/>
+      <x:c r="J200" s="31"/>
+      <x:c r="K200" s="31"/>
+      <x:c r="L200" s="31"/>
+      <x:c r="M200" s="31"/>
+      <x:c r="N200" s="31"/>
+      <x:c r="O200" s="31"/>
+      <x:c r="P200" s="31"/>
+      <x:c r="Q200" s="31"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="31"/>
+      <x:c r="B201" s="31"/>
+      <x:c r="C201" s="31"/>
+      <x:c r="D201" s="31"/>
+      <x:c r="E201" s="31"/>
+      <x:c r="F201" s="31"/>
+      <x:c r="G201" s="31"/>
+      <x:c r="H201" s="31"/>
+      <x:c r="I201" s="31"/>
+      <x:c r="J201" s="31"/>
+      <x:c r="K201" s="31"/>
+      <x:c r="L201" s="31"/>
+      <x:c r="M201" s="31"/>
+      <x:c r="N201" s="31"/>
+      <x:c r="O201" s="31"/>
+      <x:c r="P201" s="31"/>
+      <x:c r="Q201" s="31"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="31"/>
+      <x:c r="B202" s="31"/>
+      <x:c r="C202" s="31"/>
+      <x:c r="D202" s="31"/>
+      <x:c r="E202" s="31"/>
+      <x:c r="F202" s="31"/>
+      <x:c r="G202" s="31"/>
+      <x:c r="H202" s="31"/>
+      <x:c r="I202" s="31"/>
+      <x:c r="J202" s="31"/>
+      <x:c r="K202" s="31"/>
+      <x:c r="L202" s="31"/>
+      <x:c r="M202" s="31"/>
+      <x:c r="N202" s="31"/>
+      <x:c r="O202" s="31"/>
+      <x:c r="P202" s="31"/>
+      <x:c r="Q202" s="31"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="31"/>
+      <x:c r="B203" s="31"/>
+      <x:c r="C203" s="31"/>
+      <x:c r="D203" s="31"/>
+      <x:c r="E203" s="31"/>
+      <x:c r="F203" s="31"/>
+      <x:c r="G203" s="31"/>
+      <x:c r="H203" s="31"/>
+      <x:c r="I203" s="31"/>
+      <x:c r="J203" s="31"/>
+      <x:c r="K203" s="31"/>
+      <x:c r="L203" s="31"/>
+      <x:c r="M203" s="31"/>
+      <x:c r="N203" s="31"/>
+      <x:c r="O203" s="31"/>
+      <x:c r="P203" s="31"/>
+      <x:c r="Q203" s="31"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="31"/>
+      <x:c r="B204" s="31"/>
+      <x:c r="C204" s="31"/>
+      <x:c r="D204" s="31"/>
+      <x:c r="E204" s="31"/>
+      <x:c r="F204" s="31"/>
+      <x:c r="G204" s="31"/>
+      <x:c r="H204" s="31"/>
+      <x:c r="I204" s="31"/>
+      <x:c r="J204" s="31"/>
+      <x:c r="K204" s="31"/>
+      <x:c r="L204" s="31"/>
+      <x:c r="M204" s="31"/>
+      <x:c r="N204" s="31"/>
+      <x:c r="O204" s="31"/>
+      <x:c r="P204" s="31"/>
+      <x:c r="Q204" s="31"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="31"/>
+      <x:c r="B205" s="31"/>
+      <x:c r="C205" s="31"/>
+      <x:c r="D205" s="31"/>
+      <x:c r="E205" s="31"/>
+      <x:c r="F205" s="31"/>
+      <x:c r="G205" s="31"/>
+      <x:c r="H205" s="31"/>
+      <x:c r="I205" s="31"/>
+      <x:c r="J205" s="31"/>
+      <x:c r="K205" s="31"/>
+      <x:c r="L205" s="31"/>
+      <x:c r="M205" s="31"/>
+      <x:c r="N205" s="31"/>
+      <x:c r="O205" s="31"/>
+      <x:c r="P205" s="31"/>
+      <x:c r="Q205" s="31"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="31"/>
+      <x:c r="B206" s="31"/>
+      <x:c r="C206" s="31"/>
+      <x:c r="D206" s="31"/>
+      <x:c r="E206" s="31"/>
+      <x:c r="F206" s="31"/>
+      <x:c r="G206" s="31"/>
+      <x:c r="H206" s="31"/>
+      <x:c r="I206" s="31"/>
+      <x:c r="J206" s="31"/>
+      <x:c r="K206" s="31"/>
+      <x:c r="L206" s="31"/>
+      <x:c r="M206" s="31"/>
+      <x:c r="N206" s="31"/>
+      <x:c r="O206" s="31"/>
+      <x:c r="P206" s="31"/>
+      <x:c r="Q206" s="31"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="31"/>
+      <x:c r="B207" s="31"/>
+      <x:c r="C207" s="31"/>
+      <x:c r="D207" s="31"/>
+      <x:c r="E207" s="31"/>
+      <x:c r="F207" s="31"/>
+      <x:c r="G207" s="31"/>
+      <x:c r="H207" s="31"/>
+      <x:c r="I207" s="31"/>
+      <x:c r="J207" s="31"/>
+      <x:c r="K207" s="31"/>
+      <x:c r="L207" s="31"/>
+      <x:c r="M207" s="31"/>
+      <x:c r="N207" s="31"/>
+      <x:c r="O207" s="31"/>
+      <x:c r="P207" s="31"/>
+      <x:c r="Q207" s="31"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="31"/>
+      <x:c r="B208" s="31"/>
+      <x:c r="C208" s="31"/>
+      <x:c r="D208" s="31"/>
+      <x:c r="E208" s="31"/>
+      <x:c r="F208" s="31"/>
+      <x:c r="G208" s="31"/>
+      <x:c r="H208" s="31"/>
+      <x:c r="I208" s="31"/>
+      <x:c r="J208" s="31"/>
+      <x:c r="K208" s="31"/>
+      <x:c r="L208" s="31"/>
+      <x:c r="M208" s="31"/>
+      <x:c r="N208" s="31"/>
+      <x:c r="O208" s="31"/>
+      <x:c r="P208" s="31"/>
+      <x:c r="Q208" s="31"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="31"/>
+      <x:c r="B209" s="31"/>
+      <x:c r="C209" s="31"/>
+      <x:c r="D209" s="31"/>
+      <x:c r="E209" s="31"/>
+      <x:c r="F209" s="31"/>
+      <x:c r="G209" s="31"/>
+      <x:c r="H209" s="31"/>
+      <x:c r="I209" s="31"/>
+      <x:c r="J209" s="31"/>
+      <x:c r="K209" s="31"/>
+      <x:c r="L209" s="31"/>
+      <x:c r="M209" s="31"/>
+      <x:c r="N209" s="31"/>
+      <x:c r="O209" s="31"/>
+      <x:c r="P209" s="31"/>
+      <x:c r="Q209" s="31"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="31"/>
+      <x:c r="B210" s="31"/>
+      <x:c r="C210" s="31"/>
+      <x:c r="D210" s="31"/>
+      <x:c r="E210" s="31"/>
+      <x:c r="F210" s="31"/>
+      <x:c r="G210" s="31"/>
+      <x:c r="H210" s="31"/>
+      <x:c r="I210" s="31"/>
+      <x:c r="J210" s="31"/>
+      <x:c r="K210" s="31"/>
+      <x:c r="L210" s="31"/>
+      <x:c r="M210" s="31"/>
+      <x:c r="N210" s="31"/>
+      <x:c r="O210" s="31"/>
+      <x:c r="P210" s="31"/>
+      <x:c r="Q210" s="31"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="31"/>
+      <x:c r="B211" s="31"/>
+      <x:c r="C211" s="31"/>
+      <x:c r="D211" s="31"/>
+      <x:c r="E211" s="31"/>
+      <x:c r="F211" s="31"/>
+      <x:c r="G211" s="31"/>
+      <x:c r="H211" s="31"/>
+      <x:c r="I211" s="31"/>
+      <x:c r="J211" s="31"/>
+      <x:c r="K211" s="31"/>
+      <x:c r="L211" s="31"/>
+      <x:c r="M211" s="31"/>
+      <x:c r="N211" s="31"/>
+      <x:c r="O211" s="31"/>
+      <x:c r="P211" s="31"/>
+      <x:c r="Q211" s="31"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31"/>
+      <x:c r="B212" s="31"/>
+      <x:c r="C212" s="31"/>
+      <x:c r="D212" s="31"/>
+      <x:c r="E212" s="31"/>
+      <x:c r="F212" s="31"/>
+      <x:c r="G212" s="31"/>
+      <x:c r="H212" s="31"/>
+      <x:c r="I212" s="31"/>
+      <x:c r="J212" s="31"/>
+      <x:c r="K212" s="31"/>
+      <x:c r="L212" s="31"/>
+      <x:c r="M212" s="31"/>
+      <x:c r="N212" s="31"/>
+      <x:c r="O212" s="31"/>
+      <x:c r="P212" s="31"/>
+      <x:c r="Q212" s="31"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31"/>
+      <x:c r="B213" s="31"/>
+      <x:c r="C213" s="31"/>
+      <x:c r="D213" s="31"/>
+      <x:c r="E213" s="31"/>
+      <x:c r="F213" s="31"/>
+      <x:c r="G213" s="31"/>
+      <x:c r="H213" s="31"/>
+      <x:c r="I213" s="31"/>
+      <x:c r="J213" s="31"/>
+      <x:c r="K213" s="31"/>
+      <x:c r="L213" s="31"/>
+      <x:c r="M213" s="31"/>
+      <x:c r="N213" s="31"/>
+      <x:c r="O213" s="31"/>
+      <x:c r="P213" s="31"/>
+      <x:c r="Q213" s="31"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31"/>
+      <x:c r="B214" s="31"/>
+      <x:c r="C214" s="31"/>
+      <x:c r="D214" s="31"/>
+      <x:c r="E214" s="31"/>
+      <x:c r="F214" s="31"/>
+      <x:c r="G214" s="31"/>
+      <x:c r="H214" s="31"/>
+      <x:c r="I214" s="31"/>
+      <x:c r="J214" s="31"/>
+      <x:c r="K214" s="31"/>
+      <x:c r="L214" s="31"/>
+      <x:c r="M214" s="31"/>
+      <x:c r="N214" s="31"/>
+      <x:c r="O214" s="31"/>
+      <x:c r="P214" s="31"/>
+      <x:c r="Q214" s="31"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31"/>
+      <x:c r="B215" s="31"/>
+      <x:c r="C215" s="31"/>
+      <x:c r="D215" s="31"/>
+      <x:c r="E215" s="31"/>
+      <x:c r="F215" s="31"/>
+      <x:c r="G215" s="31"/>
+      <x:c r="H215" s="31"/>
+      <x:c r="I215" s="31"/>
+      <x:c r="J215" s="31"/>
+      <x:c r="K215" s="31"/>
+      <x:c r="L215" s="31"/>
+      <x:c r="M215" s="31"/>
+      <x:c r="N215" s="31"/>
+      <x:c r="O215" s="31"/>
+      <x:c r="P215" s="31"/>
+      <x:c r="Q215" s="31"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="31"/>
+      <x:c r="B216" s="31"/>
+      <x:c r="C216" s="31"/>
+      <x:c r="D216" s="31"/>
+      <x:c r="E216" s="31"/>
+      <x:c r="F216" s="31"/>
+      <x:c r="G216" s="31"/>
+      <x:c r="H216" s="31"/>
+      <x:c r="I216" s="31"/>
+      <x:c r="J216" s="31"/>
+      <x:c r="K216" s="31"/>
+      <x:c r="L216" s="31"/>
+      <x:c r="M216" s="31"/>
+      <x:c r="N216" s="31"/>
+      <x:c r="O216" s="31"/>
+      <x:c r="P216" s="31"/>
+      <x:c r="Q216" s="31"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31"/>
+      <x:c r="B217" s="31"/>
+      <x:c r="C217" s="31"/>
+      <x:c r="D217" s="31"/>
+      <x:c r="E217" s="31"/>
+      <x:c r="F217" s="31"/>
+      <x:c r="G217" s="31"/>
+      <x:c r="H217" s="31"/>
+      <x:c r="I217" s="31"/>
+      <x:c r="J217" s="31"/>
+      <x:c r="K217" s="31"/>
+      <x:c r="L217" s="31"/>
+      <x:c r="M217" s="31"/>
+      <x:c r="N217" s="31"/>
+      <x:c r="O217" s="31"/>
+      <x:c r="P217" s="31"/>
+      <x:c r="Q217" s="31"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31"/>
+      <x:c r="B218" s="31"/>
+      <x:c r="C218" s="31"/>
+      <x:c r="D218" s="31"/>
+      <x:c r="E218" s="31"/>
+      <x:c r="F218" s="31"/>
+      <x:c r="G218" s="31"/>
+      <x:c r="H218" s="31"/>
+      <x:c r="I218" s="31"/>
+      <x:c r="J218" s="31"/>
+      <x:c r="K218" s="31"/>
+      <x:c r="L218" s="31"/>
+      <x:c r="M218" s="31"/>
+      <x:c r="N218" s="31"/>
+      <x:c r="O218" s="31"/>
+      <x:c r="P218" s="31"/>
+      <x:c r="Q218" s="31"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31"/>
+      <x:c r="B219" s="31"/>
+      <x:c r="C219" s="31"/>
+      <x:c r="D219" s="31"/>
+      <x:c r="E219" s="31"/>
+      <x:c r="F219" s="31"/>
+      <x:c r="G219" s="31"/>
+      <x:c r="H219" s="31"/>
+      <x:c r="I219" s="31"/>
+      <x:c r="J219" s="31"/>
+      <x:c r="K219" s="31"/>
+      <x:c r="L219" s="31"/>
+      <x:c r="M219" s="31"/>
+      <x:c r="N219" s="31"/>
+      <x:c r="O219" s="31"/>
+      <x:c r="P219" s="31"/>
+      <x:c r="Q219" s="31"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31"/>
+      <x:c r="B220" s="31"/>
+      <x:c r="C220" s="31"/>
+      <x:c r="D220" s="31"/>
+      <x:c r="E220" s="31"/>
+      <x:c r="F220" s="31"/>
+      <x:c r="G220" s="31"/>
+      <x:c r="H220" s="31"/>
+      <x:c r="I220" s="31"/>
+      <x:c r="J220" s="31"/>
+      <x:c r="K220" s="31"/>
+      <x:c r="L220" s="31"/>
+      <x:c r="M220" s="31"/>
+      <x:c r="N220" s="31"/>
+      <x:c r="O220" s="31"/>
+      <x:c r="P220" s="31"/>
+      <x:c r="Q220" s="31"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31"/>
+      <x:c r="B221" s="31"/>
+      <x:c r="C221" s="31"/>
+      <x:c r="D221" s="31"/>
+      <x:c r="E221" s="31"/>
+      <x:c r="F221" s="31"/>
+      <x:c r="G221" s="31"/>
+      <x:c r="H221" s="31"/>
+      <x:c r="I221" s="31"/>
+      <x:c r="J221" s="31"/>
+      <x:c r="K221" s="31"/>
+      <x:c r="L221" s="31"/>
+      <x:c r="M221" s="31"/>
+      <x:c r="N221" s="31"/>
+      <x:c r="O221" s="31"/>
+      <x:c r="P221" s="31"/>
+      <x:c r="Q221" s="31"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31"/>
+      <x:c r="B222" s="31"/>
+      <x:c r="C222" s="31"/>
+      <x:c r="D222" s="31"/>
+      <x:c r="E222" s="31"/>
+      <x:c r="F222" s="31"/>
+      <x:c r="G222" s="31"/>
+      <x:c r="H222" s="31"/>
+      <x:c r="I222" s="31"/>
+      <x:c r="J222" s="31"/>
+      <x:c r="K222" s="31"/>
+      <x:c r="L222" s="31"/>
+      <x:c r="M222" s="31"/>
+      <x:c r="N222" s="31"/>
+      <x:c r="O222" s="31"/>
+      <x:c r="P222" s="31"/>
+      <x:c r="Q222" s="31"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31"/>
+      <x:c r="B223" s="31"/>
+      <x:c r="C223" s="31"/>
+      <x:c r="D223" s="31"/>
+      <x:c r="E223" s="31"/>
+      <x:c r="F223" s="31"/>
+      <x:c r="G223" s="31"/>
+      <x:c r="H223" s="31"/>
+      <x:c r="I223" s="31"/>
+      <x:c r="J223" s="31"/>
+      <x:c r="K223" s="31"/>
+      <x:c r="L223" s="31"/>
+      <x:c r="M223" s="31"/>
+      <x:c r="N223" s="31"/>
+      <x:c r="O223" s="31"/>
+      <x:c r="P223" s="31"/>
+      <x:c r="Q223" s="31"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31"/>
+      <x:c r="B224" s="31"/>
+      <x:c r="C224" s="31"/>
+      <x:c r="D224" s="31"/>
+      <x:c r="E224" s="31"/>
+      <x:c r="F224" s="31"/>
+      <x:c r="G224" s="31"/>
+      <x:c r="H224" s="31"/>
+      <x:c r="I224" s="31"/>
+      <x:c r="J224" s="31"/>
+      <x:c r="K224" s="31"/>
+      <x:c r="L224" s="31"/>
+      <x:c r="M224" s="31"/>
+      <x:c r="N224" s="31"/>
+      <x:c r="O224" s="31"/>
+      <x:c r="P224" s="31"/>
+      <x:c r="Q224" s="31"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="31"/>
+      <x:c r="B225" s="31"/>
+      <x:c r="C225" s="31"/>
+      <x:c r="D225" s="31"/>
+      <x:c r="E225" s="31"/>
+      <x:c r="F225" s="31"/>
+      <x:c r="G225" s="31"/>
+      <x:c r="H225" s="31"/>
+      <x:c r="I225" s="31"/>
+      <x:c r="J225" s="31"/>
+      <x:c r="K225" s="31"/>
+      <x:c r="L225" s="31"/>
+      <x:c r="M225" s="31"/>
+      <x:c r="N225" s="31"/>
+      <x:c r="O225" s="31"/>
+      <x:c r="P225" s="31"/>
+      <x:c r="Q225" s="31"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31"/>
+      <x:c r="B226" s="31"/>
+      <x:c r="C226" s="31"/>
+      <x:c r="D226" s="31"/>
+      <x:c r="E226" s="31"/>
+      <x:c r="F226" s="31"/>
+      <x:c r="G226" s="31"/>
+      <x:c r="H226" s="31"/>
+      <x:c r="I226" s="31"/>
+      <x:c r="J226" s="31"/>
+      <x:c r="K226" s="31"/>
+      <x:c r="L226" s="31"/>
+      <x:c r="M226" s="31"/>
+      <x:c r="N226" s="31"/>
+      <x:c r="O226" s="31"/>
+      <x:c r="P226" s="31"/>
+      <x:c r="Q226" s="31"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31"/>
+      <x:c r="B227" s="31"/>
+      <x:c r="C227" s="31"/>
+      <x:c r="D227" s="31"/>
+      <x:c r="E227" s="31"/>
+      <x:c r="F227" s="31"/>
+      <x:c r="G227" s="31"/>
+      <x:c r="H227" s="31"/>
+      <x:c r="I227" s="31"/>
+      <x:c r="J227" s="31"/>
+      <x:c r="K227" s="31"/>
+      <x:c r="L227" s="31"/>
+      <x:c r="M227" s="31"/>
+      <x:c r="N227" s="31"/>
+      <x:c r="O227" s="31"/>
+      <x:c r="P227" s="31"/>
+      <x:c r="Q227" s="31"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="31"/>
+      <x:c r="B228" s="31"/>
+      <x:c r="C228" s="31"/>
+      <x:c r="D228" s="31"/>
+      <x:c r="E228" s="31"/>
+      <x:c r="F228" s="31"/>
+      <x:c r="G228" s="31"/>
+      <x:c r="H228" s="31"/>
+      <x:c r="I228" s="31"/>
+      <x:c r="J228" s="31"/>
+      <x:c r="K228" s="31"/>
+      <x:c r="L228" s="31"/>
+      <x:c r="M228" s="31"/>
+      <x:c r="N228" s="31"/>
+      <x:c r="O228" s="31"/>
+      <x:c r="P228" s="31"/>
+      <x:c r="Q228" s="31"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="31"/>
+      <x:c r="B229" s="31"/>
+      <x:c r="C229" s="31"/>
+      <x:c r="D229" s="31"/>
+      <x:c r="E229" s="31"/>
+      <x:c r="F229" s="31"/>
+      <x:c r="G229" s="31"/>
+      <x:c r="H229" s="31"/>
+      <x:c r="I229" s="31"/>
+      <x:c r="J229" s="31"/>
+      <x:c r="K229" s="31"/>
+      <x:c r="L229" s="31"/>
+      <x:c r="M229" s="31"/>
+      <x:c r="N229" s="31"/>
+      <x:c r="O229" s="31"/>
+      <x:c r="P229" s="31"/>
+      <x:c r="Q229" s="31"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="31"/>
+      <x:c r="B230" s="31"/>
+      <x:c r="C230" s="31"/>
+      <x:c r="D230" s="31"/>
+      <x:c r="E230" s="31"/>
+      <x:c r="F230" s="31"/>
+      <x:c r="G230" s="31"/>
+      <x:c r="H230" s="31"/>
+      <x:c r="I230" s="31"/>
+      <x:c r="J230" s="31"/>
+      <x:c r="K230" s="31"/>
+      <x:c r="L230" s="31"/>
+      <x:c r="M230" s="31"/>
+      <x:c r="N230" s="31"/>
+      <x:c r="O230" s="31"/>
+      <x:c r="P230" s="31"/>
+      <x:c r="Q230" s="31"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="31"/>
+      <x:c r="B231" s="31"/>
+      <x:c r="C231" s="31"/>
+      <x:c r="D231" s="31"/>
+      <x:c r="E231" s="31"/>
+      <x:c r="F231" s="31"/>
+      <x:c r="G231" s="31"/>
+      <x:c r="H231" s="31"/>
+      <x:c r="I231" s="31"/>
+      <x:c r="J231" s="31"/>
+      <x:c r="K231" s="31"/>
+      <x:c r="L231" s="31"/>
+      <x:c r="M231" s="31"/>
+      <x:c r="N231" s="31"/>
+      <x:c r="O231" s="31"/>
+      <x:c r="P231" s="31"/>
+      <x:c r="Q231" s="31"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="31"/>
+      <x:c r="B232" s="31"/>
+      <x:c r="C232" s="31"/>
+      <x:c r="D232" s="31"/>
+      <x:c r="E232" s="31"/>
+      <x:c r="F232" s="31"/>
+      <x:c r="G232" s="31"/>
+      <x:c r="H232" s="31"/>
+      <x:c r="I232" s="31"/>
+      <x:c r="J232" s="31"/>
+      <x:c r="K232" s="31"/>
+      <x:c r="L232" s="31"/>
+      <x:c r="M232" s="31"/>
+      <x:c r="N232" s="31"/>
+      <x:c r="O232" s="31"/>
+      <x:c r="P232" s="31"/>
+      <x:c r="Q232" s="31"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="31"/>
+      <x:c r="B233" s="31"/>
+      <x:c r="C233" s="31"/>
+      <x:c r="D233" s="31"/>
+      <x:c r="E233" s="31"/>
+      <x:c r="F233" s="31"/>
+      <x:c r="G233" s="31"/>
+      <x:c r="H233" s="31"/>
+      <x:c r="I233" s="31"/>
+      <x:c r="J233" s="31"/>
+      <x:c r="K233" s="31"/>
+      <x:c r="L233" s="31"/>
+      <x:c r="M233" s="31"/>
+      <x:c r="N233" s="31"/>
+      <x:c r="O233" s="31"/>
+      <x:c r="P233" s="31"/>
+      <x:c r="Q233" s="31"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31"/>
+      <x:c r="B234" s="31"/>
+      <x:c r="C234" s="31"/>
+      <x:c r="D234" s="31"/>
+      <x:c r="E234" s="31"/>
+      <x:c r="F234" s="31"/>
+      <x:c r="G234" s="31"/>
+      <x:c r="H234" s="31"/>
+      <x:c r="I234" s="31"/>
+      <x:c r="J234" s="31"/>
+      <x:c r="K234" s="31"/>
+      <x:c r="L234" s="31"/>
+      <x:c r="M234" s="31"/>
+      <x:c r="N234" s="31"/>
+      <x:c r="O234" s="31"/>
+      <x:c r="P234" s="31"/>
+      <x:c r="Q234" s="31"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="31"/>
+      <x:c r="B235" s="31"/>
+      <x:c r="C235" s="31"/>
+      <x:c r="D235" s="31"/>
+      <x:c r="E235" s="31"/>
+      <x:c r="F235" s="31"/>
+      <x:c r="G235" s="31"/>
+      <x:c r="H235" s="31"/>
+      <x:c r="I235" s="31"/>
+      <x:c r="J235" s="31"/>
+      <x:c r="K235" s="31"/>
+      <x:c r="L235" s="31"/>
+      <x:c r="M235" s="31"/>
+      <x:c r="N235" s="31"/>
+      <x:c r="O235" s="31"/>
+      <x:c r="P235" s="31"/>
+      <x:c r="Q235" s="31"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31"/>
+      <x:c r="B236" s="31"/>
+      <x:c r="C236" s="31"/>
+      <x:c r="D236" s="31"/>
+      <x:c r="E236" s="31"/>
+      <x:c r="F236" s="31"/>
+      <x:c r="G236" s="31"/>
+      <x:c r="H236" s="31"/>
+      <x:c r="I236" s="31"/>
+      <x:c r="J236" s="31"/>
+      <x:c r="K236" s="31"/>
+      <x:c r="L236" s="31"/>
+      <x:c r="M236" s="31"/>
+      <x:c r="N236" s="31"/>
+      <x:c r="O236" s="31"/>
+      <x:c r="P236" s="31"/>
+      <x:c r="Q236" s="31"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31"/>
+      <x:c r="B237" s="31"/>
+      <x:c r="C237" s="31"/>
+      <x:c r="D237" s="31"/>
+      <x:c r="E237" s="31"/>
+      <x:c r="F237" s="31"/>
+      <x:c r="G237" s="31"/>
+      <x:c r="H237" s="31"/>
+      <x:c r="I237" s="31"/>
+      <x:c r="J237" s="31"/>
+      <x:c r="K237" s="31"/>
+      <x:c r="L237" s="31"/>
+      <x:c r="M237" s="31"/>
+      <x:c r="N237" s="31"/>
+      <x:c r="O237" s="31"/>
+      <x:c r="P237" s="31"/>
+      <x:c r="Q237" s="31"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="31"/>
+      <x:c r="B238" s="31"/>
+      <x:c r="C238" s="31"/>
+      <x:c r="D238" s="31"/>
+      <x:c r="E238" s="31"/>
+      <x:c r="F238" s="31"/>
+      <x:c r="G238" s="31"/>
+      <x:c r="H238" s="31"/>
+      <x:c r="I238" s="31"/>
+      <x:c r="J238" s="31"/>
+      <x:c r="K238" s="31"/>
+      <x:c r="L238" s="31"/>
+      <x:c r="M238" s="31"/>
+      <x:c r="N238" s="31"/>
+      <x:c r="O238" s="31"/>
+      <x:c r="P238" s="31"/>
+      <x:c r="Q238" s="31"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="31"/>
+      <x:c r="B239" s="31"/>
+      <x:c r="C239" s="31"/>
+      <x:c r="D239" s="31"/>
+      <x:c r="E239" s="31"/>
+      <x:c r="F239" s="31"/>
+      <x:c r="G239" s="31"/>
+      <x:c r="H239" s="31"/>
+      <x:c r="I239" s="31"/>
+      <x:c r="J239" s="31"/>
+      <x:c r="K239" s="31"/>
+      <x:c r="L239" s="31"/>
+      <x:c r="M239" s="31"/>
+      <x:c r="N239" s="31"/>
+      <x:c r="O239" s="31"/>
+      <x:c r="P239" s="31"/>
+      <x:c r="Q239" s="31"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="31"/>
+      <x:c r="B240" s="31"/>
+      <x:c r="C240" s="31"/>
+      <x:c r="D240" s="31"/>
+      <x:c r="E240" s="31"/>
+      <x:c r="F240" s="31"/>
+      <x:c r="G240" s="31"/>
+      <x:c r="H240" s="31"/>
+      <x:c r="I240" s="31"/>
+      <x:c r="J240" s="31"/>
+      <x:c r="K240" s="31"/>
+      <x:c r="L240" s="31"/>
+      <x:c r="M240" s="31"/>
+      <x:c r="N240" s="31"/>
+      <x:c r="O240" s="31"/>
+      <x:c r="P240" s="31"/>
+      <x:c r="Q240" s="31"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="31"/>
+      <x:c r="B241" s="31"/>
+      <x:c r="C241" s="31"/>
+      <x:c r="D241" s="31"/>
+      <x:c r="E241" s="31"/>
+      <x:c r="F241" s="31"/>
+      <x:c r="G241" s="31"/>
+      <x:c r="H241" s="31"/>
+      <x:c r="I241" s="31"/>
+      <x:c r="J241" s="31"/>
+      <x:c r="K241" s="31"/>
+      <x:c r="L241" s="31"/>
+      <x:c r="M241" s="31"/>
+      <x:c r="N241" s="31"/>
+      <x:c r="O241" s="31"/>
+      <x:c r="P241" s="31"/>
+      <x:c r="Q241" s="31"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="31"/>
+      <x:c r="B242" s="31"/>
+      <x:c r="C242" s="31"/>
+      <x:c r="D242" s="31"/>
+      <x:c r="E242" s="31"/>
+      <x:c r="F242" s="31"/>
+      <x:c r="G242" s="31"/>
+      <x:c r="H242" s="31"/>
+      <x:c r="I242" s="31"/>
+      <x:c r="J242" s="31"/>
+      <x:c r="K242" s="31"/>
+      <x:c r="L242" s="31"/>
+      <x:c r="M242" s="31"/>
+      <x:c r="N242" s="31"/>
+      <x:c r="O242" s="31"/>
+      <x:c r="P242" s="31"/>
+      <x:c r="Q242" s="31"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="31"/>
+      <x:c r="B243" s="31"/>
+      <x:c r="C243" s="31"/>
+      <x:c r="D243" s="31"/>
+      <x:c r="E243" s="31"/>
+      <x:c r="F243" s="31"/>
+      <x:c r="G243" s="31"/>
+      <x:c r="H243" s="31"/>
+      <x:c r="I243" s="31"/>
+      <x:c r="J243" s="31"/>
+      <x:c r="K243" s="31"/>
+      <x:c r="L243" s="31"/>
+      <x:c r="M243" s="31"/>
+      <x:c r="N243" s="31"/>
+      <x:c r="O243" s="31"/>
+      <x:c r="P243" s="31"/>
+      <x:c r="Q243" s="31"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="31"/>
+      <x:c r="B244" s="31"/>
+      <x:c r="C244" s="31"/>
+      <x:c r="D244" s="31"/>
+      <x:c r="E244" s="31"/>
+      <x:c r="F244" s="31"/>
+      <x:c r="G244" s="31"/>
+      <x:c r="H244" s="31"/>
+      <x:c r="I244" s="31"/>
+      <x:c r="J244" s="31"/>
+      <x:c r="K244" s="31"/>
+      <x:c r="L244" s="31"/>
+      <x:c r="M244" s="31"/>
+      <x:c r="N244" s="31"/>
+      <x:c r="O244" s="31"/>
+      <x:c r="P244" s="31"/>
+      <x:c r="Q244" s="31"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="31"/>
+      <x:c r="B245" s="31"/>
+      <x:c r="C245" s="31"/>
+      <x:c r="D245" s="31"/>
+      <x:c r="E245" s="31"/>
+      <x:c r="F245" s="31"/>
+      <x:c r="G245" s="31"/>
+      <x:c r="H245" s="31"/>
+      <x:c r="I245" s="31"/>
+      <x:c r="J245" s="31"/>
+      <x:c r="K245" s="31"/>
+      <x:c r="L245" s="31"/>
+      <x:c r="M245" s="31"/>
+      <x:c r="N245" s="31"/>
+      <x:c r="O245" s="31"/>
+      <x:c r="P245" s="31"/>
+      <x:c r="Q245" s="31"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="31"/>
+      <x:c r="B246" s="31"/>
+      <x:c r="C246" s="31"/>
+      <x:c r="D246" s="31"/>
+      <x:c r="E246" s="31"/>
+      <x:c r="F246" s="31"/>
+      <x:c r="G246" s="31"/>
+      <x:c r="H246" s="31"/>
+      <x:c r="I246" s="31"/>
+      <x:c r="J246" s="31"/>
+      <x:c r="K246" s="31"/>
+      <x:c r="L246" s="31"/>
+      <x:c r="M246" s="31"/>
+      <x:c r="N246" s="31"/>
+      <x:c r="O246" s="31"/>
+      <x:c r="P246" s="31"/>
+      <x:c r="Q246" s="31"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="31"/>
+      <x:c r="B247" s="31"/>
+      <x:c r="C247" s="31"/>
+      <x:c r="D247" s="31"/>
+      <x:c r="E247" s="31"/>
+      <x:c r="F247" s="31"/>
+      <x:c r="G247" s="31"/>
+      <x:c r="H247" s="31"/>
+      <x:c r="I247" s="31"/>
+      <x:c r="J247" s="31"/>
+      <x:c r="K247" s="31"/>
+      <x:c r="L247" s="31"/>
+      <x:c r="M247" s="31"/>
+      <x:c r="N247" s="31"/>
+      <x:c r="O247" s="31"/>
+      <x:c r="P247" s="31"/>
+      <x:c r="Q247" s="31"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="31"/>
+      <x:c r="B248" s="31"/>
+      <x:c r="C248" s="31"/>
+      <x:c r="D248" s="31"/>
+      <x:c r="E248" s="31"/>
+      <x:c r="F248" s="31"/>
+      <x:c r="G248" s="31"/>
+      <x:c r="H248" s="31"/>
+      <x:c r="I248" s="31"/>
+      <x:c r="J248" s="31"/>
+      <x:c r="K248" s="31"/>
+      <x:c r="L248" s="31"/>
+      <x:c r="M248" s="31"/>
+      <x:c r="N248" s="31"/>
+      <x:c r="O248" s="31"/>
+      <x:c r="P248" s="31"/>
+      <x:c r="Q248" s="31"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="31"/>
+      <x:c r="B249" s="31"/>
+      <x:c r="C249" s="31"/>
+      <x:c r="D249" s="31"/>
+      <x:c r="E249" s="31"/>
+      <x:c r="F249" s="31"/>
+      <x:c r="G249" s="31"/>
+      <x:c r="H249" s="31"/>
+      <x:c r="I249" s="31"/>
+      <x:c r="J249" s="31"/>
+      <x:c r="K249" s="31"/>
+      <x:c r="L249" s="31"/>
+      <x:c r="M249" s="31"/>
+      <x:c r="N249" s="31"/>
+      <x:c r="O249" s="31"/>
+      <x:c r="P249" s="31"/>
+      <x:c r="Q249" s="31"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="31"/>
+      <x:c r="B250" s="31"/>
+      <x:c r="C250" s="31"/>
+      <x:c r="D250" s="31"/>
+      <x:c r="E250" s="31"/>
+      <x:c r="F250" s="31"/>
+      <x:c r="G250" s="31"/>
+      <x:c r="H250" s="31"/>
+      <x:c r="I250" s="31"/>
+      <x:c r="J250" s="31"/>
+      <x:c r="K250" s="31"/>
+      <x:c r="L250" s="31"/>
+      <x:c r="M250" s="31"/>
+      <x:c r="N250" s="31"/>
+      <x:c r="O250" s="31"/>
+      <x:c r="P250" s="31"/>
+      <x:c r="Q250" s="31"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="31"/>
+      <x:c r="B251" s="31"/>
+      <x:c r="C251" s="31"/>
+      <x:c r="D251" s="31"/>
+      <x:c r="E251" s="31"/>
+      <x:c r="F251" s="31"/>
+      <x:c r="G251" s="31"/>
+      <x:c r="H251" s="31"/>
+      <x:c r="I251" s="31"/>
+      <x:c r="J251" s="31"/>
+      <x:c r="K251" s="31"/>
+      <x:c r="L251" s="31"/>
+      <x:c r="M251" s="31"/>
+      <x:c r="N251" s="31"/>
+      <x:c r="O251" s="31"/>
+      <x:c r="P251" s="31"/>
+      <x:c r="Q251" s="31"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="31"/>
+      <x:c r="B252" s="31"/>
+      <x:c r="C252" s="31"/>
+      <x:c r="D252" s="31"/>
+      <x:c r="E252" s="31"/>
+      <x:c r="F252" s="31"/>
+      <x:c r="G252" s="31"/>
+      <x:c r="H252" s="31"/>
+      <x:c r="I252" s="31"/>
+      <x:c r="J252" s="31"/>
+      <x:c r="K252" s="31"/>
+      <x:c r="L252" s="31"/>
+      <x:c r="M252" s="31"/>
+      <x:c r="N252" s="31"/>
+      <x:c r="O252" s="31"/>
+      <x:c r="P252" s="31"/>
+      <x:c r="Q252" s="31"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="31"/>
+      <x:c r="B253" s="31"/>
+      <x:c r="C253" s="31"/>
+      <x:c r="D253" s="31"/>
+      <x:c r="E253" s="31"/>
+      <x:c r="F253" s="31"/>
+      <x:c r="G253" s="31"/>
+      <x:c r="H253" s="31"/>
+      <x:c r="I253" s="31"/>
+      <x:c r="J253" s="31"/>
+      <x:c r="K253" s="31"/>
+      <x:c r="L253" s="31"/>
+      <x:c r="M253" s="31"/>
+      <x:c r="N253" s="31"/>
+      <x:c r="O253" s="31"/>
+      <x:c r="P253" s="31"/>
+      <x:c r="Q253" s="31"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="31"/>
+      <x:c r="B254" s="31"/>
+      <x:c r="C254" s="31"/>
+      <x:c r="D254" s="31"/>
+      <x:c r="E254" s="31"/>
+      <x:c r="F254" s="31"/>
+      <x:c r="G254" s="31"/>
+      <x:c r="H254" s="31"/>
+      <x:c r="I254" s="31"/>
+      <x:c r="J254" s="31"/>
+      <x:c r="K254" s="31"/>
+      <x:c r="L254" s="31"/>
+      <x:c r="M254" s="31"/>
+      <x:c r="N254" s="31"/>
+      <x:c r="O254" s="31"/>
+      <x:c r="P254" s="31"/>
+      <x:c r="Q254" s="31"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="31"/>
+      <x:c r="B255" s="31"/>
+      <x:c r="C255" s="31"/>
+      <x:c r="D255" s="31"/>
+      <x:c r="E255" s="31"/>
+      <x:c r="F255" s="31"/>
+      <x:c r="G255" s="31"/>
+      <x:c r="H255" s="31"/>
+      <x:c r="I255" s="31"/>
+      <x:c r="J255" s="31"/>
+      <x:c r="K255" s="31"/>
+      <x:c r="L255" s="31"/>
+      <x:c r="M255" s="31"/>
+      <x:c r="N255" s="31"/>
+      <x:c r="O255" s="31"/>
+      <x:c r="P255" s="31"/>
+      <x:c r="Q255" s="31"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="31"/>
+      <x:c r="B256" s="31"/>
+      <x:c r="C256" s="31"/>
+      <x:c r="D256" s="31"/>
+      <x:c r="E256" s="31"/>
+      <x:c r="F256" s="31"/>
+      <x:c r="G256" s="31"/>
+      <x:c r="H256" s="31"/>
+      <x:c r="I256" s="31"/>
+      <x:c r="J256" s="31"/>
+      <x:c r="K256" s="31"/>
+      <x:c r="L256" s="31"/>
+      <x:c r="M256" s="31"/>
+      <x:c r="N256" s="31"/>
+      <x:c r="O256" s="31"/>
+      <x:c r="P256" s="31"/>
+      <x:c r="Q256" s="31"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="31"/>
+      <x:c r="B257" s="31"/>
+      <x:c r="C257" s="31"/>
+      <x:c r="D257" s="31"/>
+      <x:c r="E257" s="31"/>
+      <x:c r="F257" s="31"/>
+      <x:c r="G257" s="31"/>
+      <x:c r="H257" s="31"/>
+      <x:c r="I257" s="31"/>
+      <x:c r="J257" s="31"/>
+      <x:c r="K257" s="31"/>
+      <x:c r="L257" s="31"/>
+      <x:c r="M257" s="31"/>
+      <x:c r="N257" s="31"/>
+      <x:c r="O257" s="31"/>
+      <x:c r="P257" s="31"/>
+      <x:c r="Q257" s="31"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="31"/>
+      <x:c r="B258" s="31"/>
+      <x:c r="C258" s="31"/>
+      <x:c r="D258" s="31"/>
+      <x:c r="E258" s="31"/>
+      <x:c r="F258" s="31"/>
+      <x:c r="G258" s="31"/>
+      <x:c r="H258" s="31"/>
+      <x:c r="I258" s="31"/>
+      <x:c r="J258" s="31"/>
+      <x:c r="K258" s="31"/>
+      <x:c r="L258" s="31"/>
+      <x:c r="M258" s="31"/>
+      <x:c r="N258" s="31"/>
+      <x:c r="O258" s="31"/>
+      <x:c r="P258" s="31"/>
+      <x:c r="Q258" s="31"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="31"/>
+      <x:c r="B259" s="31"/>
+      <x:c r="C259" s="31"/>
+      <x:c r="D259" s="31"/>
+      <x:c r="E259" s="31"/>
+      <x:c r="F259" s="31"/>
+      <x:c r="G259" s="31"/>
+      <x:c r="H259" s="31"/>
+      <x:c r="I259" s="31"/>
+      <x:c r="J259" s="31"/>
+      <x:c r="K259" s="31"/>
+      <x:c r="L259" s="31"/>
+      <x:c r="M259" s="31"/>
+      <x:c r="N259" s="31"/>
+      <x:c r="O259" s="31"/>
+      <x:c r="P259" s="31"/>
+      <x:c r="Q259" s="31"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="31"/>
+      <x:c r="B260" s="31"/>
+      <x:c r="C260" s="31"/>
+      <x:c r="D260" s="31"/>
+      <x:c r="E260" s="31"/>
+      <x:c r="F260" s="31"/>
+      <x:c r="G260" s="31"/>
+      <x:c r="H260" s="31"/>
+      <x:c r="I260" s="31"/>
+      <x:c r="J260" s="31"/>
+      <x:c r="K260" s="31"/>
+      <x:c r="L260" s="31"/>
+      <x:c r="M260" s="31"/>
+      <x:c r="N260" s="31"/>
+      <x:c r="O260" s="31"/>
+      <x:c r="P260" s="31"/>
+      <x:c r="Q260" s="31"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="31"/>
+      <x:c r="B261" s="31"/>
+      <x:c r="C261" s="31"/>
+      <x:c r="D261" s="31"/>
+      <x:c r="E261" s="31"/>
+      <x:c r="F261" s="31"/>
+      <x:c r="G261" s="31"/>
+      <x:c r="H261" s="31"/>
+      <x:c r="I261" s="31"/>
+      <x:c r="J261" s="31"/>
+      <x:c r="K261" s="31"/>
+      <x:c r="L261" s="31"/>
+      <x:c r="M261" s="31"/>
+      <x:c r="N261" s="31"/>
+      <x:c r="O261" s="31"/>
+      <x:c r="P261" s="31"/>
+      <x:c r="Q261" s="31"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="31"/>
+      <x:c r="B262" s="31"/>
+      <x:c r="C262" s="31"/>
+      <x:c r="D262" s="31"/>
+      <x:c r="E262" s="31"/>
+      <x:c r="F262" s="31"/>
+      <x:c r="G262" s="31"/>
+      <x:c r="H262" s="31"/>
+      <x:c r="I262" s="31"/>
+      <x:c r="J262" s="31"/>
+      <x:c r="K262" s="31"/>
+      <x:c r="L262" s="31"/>
+      <x:c r="M262" s="31"/>
+      <x:c r="N262" s="31"/>
+      <x:c r="O262" s="31"/>
+      <x:c r="P262" s="31"/>
+      <x:c r="Q262" s="31"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="31"/>
+      <x:c r="B263" s="31"/>
+      <x:c r="C263" s="31"/>
+      <x:c r="D263" s="31"/>
+      <x:c r="E263" s="31"/>
+      <x:c r="F263" s="31"/>
+      <x:c r="G263" s="31"/>
+      <x:c r="H263" s="31"/>
+      <x:c r="I263" s="31"/>
+      <x:c r="J263" s="31"/>
+      <x:c r="K263" s="31"/>
+      <x:c r="L263" s="31"/>
+      <x:c r="M263" s="31"/>
+      <x:c r="N263" s="31"/>
+      <x:c r="O263" s="31"/>
+      <x:c r="P263" s="31"/>
+      <x:c r="Q263" s="31"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="31"/>
+      <x:c r="B264" s="31"/>
+      <x:c r="C264" s="31"/>
+      <x:c r="D264" s="31"/>
+      <x:c r="E264" s="31"/>
+      <x:c r="F264" s="31"/>
+      <x:c r="G264" s="31"/>
+      <x:c r="H264" s="31"/>
+      <x:c r="I264" s="31"/>
+      <x:c r="J264" s="31"/>
+      <x:c r="K264" s="31"/>
+      <x:c r="L264" s="31"/>
+      <x:c r="M264" s="31"/>
+      <x:c r="N264" s="31"/>
+      <x:c r="O264" s="31"/>
+      <x:c r="P264" s="31"/>
+      <x:c r="Q264" s="31"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="31"/>
+      <x:c r="B265" s="31"/>
+      <x:c r="C265" s="31"/>
+      <x:c r="D265" s="31"/>
+      <x:c r="E265" s="31"/>
+      <x:c r="F265" s="31"/>
+      <x:c r="G265" s="31"/>
+      <x:c r="H265" s="31"/>
+      <x:c r="I265" s="31"/>
+      <x:c r="J265" s="31"/>
+      <x:c r="K265" s="31"/>
+      <x:c r="L265" s="31"/>
+      <x:c r="M265" s="31"/>
+      <x:c r="N265" s="31"/>
+      <x:c r="O265" s="31"/>
+      <x:c r="P265" s="31"/>
+      <x:c r="Q265" s="31"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="31"/>
+      <x:c r="B266" s="31"/>
+      <x:c r="C266" s="31"/>
+      <x:c r="D266" s="31"/>
+      <x:c r="E266" s="31"/>
+      <x:c r="F266" s="31"/>
+      <x:c r="G266" s="31"/>
+      <x:c r="H266" s="31"/>
+      <x:c r="I266" s="31"/>
+      <x:c r="J266" s="31"/>
+      <x:c r="K266" s="31"/>
+      <x:c r="L266" s="31"/>
+      <x:c r="M266" s="31"/>
+      <x:c r="N266" s="31"/>
+      <x:c r="O266" s="31"/>
+      <x:c r="P266" s="31"/>
+      <x:c r="Q266" s="31"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="31"/>
+      <x:c r="B267" s="31"/>
+      <x:c r="C267" s="31"/>
+      <x:c r="D267" s="31"/>
+      <x:c r="E267" s="31"/>
+      <x:c r="F267" s="31"/>
+      <x:c r="G267" s="31"/>
+      <x:c r="H267" s="31"/>
+      <x:c r="I267" s="31"/>
+      <x:c r="J267" s="31"/>
+      <x:c r="K267" s="31"/>
+      <x:c r="L267" s="31"/>
+      <x:c r="M267" s="31"/>
+      <x:c r="N267" s="31"/>
+      <x:c r="O267" s="31"/>
+      <x:c r="P267" s="31"/>
+      <x:c r="Q267" s="31"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="31"/>
+      <x:c r="B268" s="31"/>
+      <x:c r="C268" s="31"/>
+      <x:c r="D268" s="31"/>
+      <x:c r="E268" s="31"/>
+      <x:c r="F268" s="31"/>
+      <x:c r="G268" s="31"/>
+      <x:c r="H268" s="31"/>
+      <x:c r="I268" s="31"/>
+      <x:c r="J268" s="31"/>
+      <x:c r="K268" s="31"/>
+      <x:c r="L268" s="31"/>
+      <x:c r="M268" s="31"/>
+      <x:c r="N268" s="31"/>
+      <x:c r="O268" s="31"/>
+      <x:c r="P268" s="31"/>
+      <x:c r="Q268" s="31"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="31"/>
+      <x:c r="B269" s="31"/>
+      <x:c r="C269" s="31"/>
+      <x:c r="D269" s="31"/>
+      <x:c r="E269" s="31"/>
+      <x:c r="F269" s="31"/>
+      <x:c r="G269" s="31"/>
+      <x:c r="H269" s="31"/>
+      <x:c r="I269" s="31"/>
+      <x:c r="J269" s="31"/>
+      <x:c r="K269" s="31"/>
+      <x:c r="L269" s="31"/>
+      <x:c r="M269" s="31"/>
+      <x:c r="N269" s="31"/>
+      <x:c r="O269" s="31"/>
+      <x:c r="P269" s="31"/>
+      <x:c r="Q269" s="31"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="31"/>
+      <x:c r="B270" s="31"/>
+      <x:c r="C270" s="31"/>
+      <x:c r="D270" s="31"/>
+      <x:c r="E270" s="31"/>
+      <x:c r="F270" s="31"/>
+      <x:c r="G270" s="31"/>
+      <x:c r="H270" s="31"/>
+      <x:c r="I270" s="31"/>
+      <x:c r="J270" s="31"/>
+      <x:c r="K270" s="31"/>
+      <x:c r="L270" s="31"/>
+      <x:c r="M270" s="31"/>
+      <x:c r="N270" s="31"/>
+      <x:c r="O270" s="31"/>
+      <x:c r="P270" s="31"/>
+      <x:c r="Q270" s="31"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="31"/>
+      <x:c r="B271" s="31"/>
+      <x:c r="C271" s="31"/>
+      <x:c r="D271" s="31"/>
+      <x:c r="E271" s="31"/>
+      <x:c r="F271" s="31"/>
+      <x:c r="G271" s="31"/>
+      <x:c r="H271" s="31"/>
+      <x:c r="I271" s="31"/>
+      <x:c r="J271" s="31"/>
+      <x:c r="K271" s="31"/>
+      <x:c r="L271" s="31"/>
+      <x:c r="M271" s="31"/>
+      <x:c r="N271" s="31"/>
+      <x:c r="O271" s="31"/>
+      <x:c r="P271" s="31"/>
+      <x:c r="Q271" s="31"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="31"/>
+      <x:c r="B272" s="31"/>
+      <x:c r="C272" s="31"/>
+      <x:c r="D272" s="31"/>
+      <x:c r="E272" s="31"/>
+      <x:c r="F272" s="31"/>
+      <x:c r="G272" s="31"/>
+      <x:c r="H272" s="31"/>
+      <x:c r="I272" s="31"/>
+      <x:c r="J272" s="31"/>
+      <x:c r="K272" s="31"/>
+      <x:c r="L272" s="31"/>
+      <x:c r="M272" s="31"/>
+      <x:c r="N272" s="31"/>
+      <x:c r="O272" s="31"/>
+      <x:c r="P272" s="31"/>
+      <x:c r="Q272" s="31"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="31"/>
+      <x:c r="B273" s="31"/>
+      <x:c r="C273" s="31"/>
+      <x:c r="D273" s="31"/>
+      <x:c r="E273" s="31"/>
+      <x:c r="F273" s="31"/>
+      <x:c r="G273" s="31"/>
+      <x:c r="H273" s="31"/>
+      <x:c r="I273" s="31"/>
+      <x:c r="J273" s="31"/>
+      <x:c r="K273" s="31"/>
+      <x:c r="L273" s="31"/>
+      <x:c r="M273" s="31"/>
+      <x:c r="N273" s="31"/>
+      <x:c r="O273" s="31"/>
+      <x:c r="P273" s="31"/>
+      <x:c r="Q273" s="31"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="31"/>
+      <x:c r="B274" s="31"/>
+      <x:c r="C274" s="31"/>
+      <x:c r="D274" s="31"/>
+      <x:c r="E274" s="31"/>
+      <x:c r="F274" s="31"/>
+      <x:c r="G274" s="31"/>
+      <x:c r="H274" s="31"/>
+      <x:c r="I274" s="31"/>
+      <x:c r="J274" s="31"/>
+      <x:c r="K274" s="31"/>
+      <x:c r="L274" s="31"/>
+      <x:c r="M274" s="31"/>
+      <x:c r="N274" s="31"/>
+      <x:c r="O274" s="31"/>
+      <x:c r="P274" s="31"/>
+      <x:c r="Q274" s="31"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="31"/>
+      <x:c r="B275" s="31"/>
+      <x:c r="C275" s="31"/>
+      <x:c r="D275" s="31"/>
+      <x:c r="E275" s="31"/>
+      <x:c r="F275" s="31"/>
+      <x:c r="G275" s="31"/>
+      <x:c r="H275" s="31"/>
+      <x:c r="I275" s="31"/>
+      <x:c r="J275" s="31"/>
+      <x:c r="K275" s="31"/>
+      <x:c r="L275" s="31"/>
+      <x:c r="M275" s="31"/>
+      <x:c r="N275" s="31"/>
+      <x:c r="O275" s="31"/>
+      <x:c r="P275" s="31"/>
+      <x:c r="Q275" s="31"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="31"/>
+      <x:c r="B276" s="31"/>
+      <x:c r="C276" s="31"/>
+      <x:c r="D276" s="31"/>
+      <x:c r="E276" s="31"/>
+      <x:c r="F276" s="31"/>
+      <x:c r="G276" s="31"/>
+      <x:c r="H276" s="31"/>
+      <x:c r="I276" s="31"/>
+      <x:c r="J276" s="31"/>
+      <x:c r="K276" s="31"/>
+      <x:c r="L276" s="31"/>
+      <x:c r="M276" s="31"/>
+      <x:c r="N276" s="31"/>
+      <x:c r="O276" s="31"/>
+      <x:c r="P276" s="31"/>
+      <x:c r="Q276" s="31"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="31"/>
+      <x:c r="B277" s="31"/>
+      <x:c r="C277" s="31"/>
+      <x:c r="D277" s="31"/>
+      <x:c r="E277" s="31"/>
+      <x:c r="F277" s="31"/>
+      <x:c r="G277" s="31"/>
+      <x:c r="H277" s="31"/>
+      <x:c r="I277" s="31"/>
+      <x:c r="J277" s="31"/>
+      <x:c r="K277" s="31"/>
+      <x:c r="L277" s="31"/>
+      <x:c r="M277" s="31"/>
+      <x:c r="N277" s="31"/>
+      <x:c r="O277" s="31"/>
+      <x:c r="P277" s="31"/>
+      <x:c r="Q277" s="31"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="31"/>
+      <x:c r="B278" s="31"/>
+      <x:c r="C278" s="31"/>
+      <x:c r="D278" s="31"/>
+      <x:c r="E278" s="31"/>
+      <x:c r="F278" s="31"/>
+      <x:c r="G278" s="31"/>
+      <x:c r="H278" s="31"/>
+      <x:c r="I278" s="31"/>
+      <x:c r="J278" s="31"/>
+      <x:c r="K278" s="31"/>
+      <x:c r="L278" s="31"/>
+      <x:c r="M278" s="31"/>
+      <x:c r="N278" s="31"/>
+      <x:c r="O278" s="31"/>
+      <x:c r="P278" s="31"/>
+      <x:c r="Q278" s="31"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="31"/>
+      <x:c r="B279" s="31"/>
+      <x:c r="C279" s="31"/>
+      <x:c r="D279" s="31"/>
+      <x:c r="E279" s="31"/>
+      <x:c r="F279" s="31"/>
+      <x:c r="G279" s="31"/>
+      <x:c r="H279" s="31"/>
+      <x:c r="I279" s="31"/>
+      <x:c r="J279" s="31"/>
+      <x:c r="K279" s="31"/>
+      <x:c r="L279" s="31"/>
+      <x:c r="M279" s="31"/>
+      <x:c r="N279" s="31"/>
+      <x:c r="O279" s="31"/>
+      <x:c r="P279" s="31"/>
+      <x:c r="Q279" s="31"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="31"/>
+      <x:c r="B280" s="31"/>
+      <x:c r="C280" s="31"/>
+      <x:c r="D280" s="31"/>
+      <x:c r="E280" s="31"/>
+      <x:c r="F280" s="31"/>
+      <x:c r="G280" s="31"/>
+      <x:c r="H280" s="31"/>
+      <x:c r="I280" s="31"/>
+      <x:c r="J280" s="31"/>
+      <x:c r="K280" s="31"/>
+      <x:c r="L280" s="31"/>
+      <x:c r="M280" s="31"/>
+      <x:c r="N280" s="31"/>
+      <x:c r="O280" s="31"/>
+      <x:c r="P280" s="31"/>
+      <x:c r="Q280" s="31"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="31"/>
+      <x:c r="B281" s="31"/>
+      <x:c r="C281" s="31"/>
+      <x:c r="D281" s="31"/>
+      <x:c r="E281" s="31"/>
+      <x:c r="F281" s="31"/>
+      <x:c r="G281" s="31"/>
+      <x:c r="H281" s="31"/>
+      <x:c r="I281" s="31"/>
+      <x:c r="J281" s="31"/>
+      <x:c r="K281" s="31"/>
+      <x:c r="L281" s="31"/>
+      <x:c r="M281" s="31"/>
+      <x:c r="N281" s="31"/>
+      <x:c r="O281" s="31"/>
+      <x:c r="P281" s="31"/>
+      <x:c r="Q281" s="31"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="31"/>
+      <x:c r="B282" s="31"/>
+      <x:c r="C282" s="31"/>
+      <x:c r="D282" s="31"/>
+      <x:c r="E282" s="31"/>
+      <x:c r="F282" s="31"/>
+      <x:c r="G282" s="31"/>
+      <x:c r="H282" s="31"/>
+      <x:c r="I282" s="31"/>
+      <x:c r="J282" s="31"/>
+      <x:c r="K282" s="31"/>
+      <x:c r="L282" s="31"/>
+      <x:c r="M282" s="31"/>
+      <x:c r="N282" s="31"/>
+      <x:c r="O282" s="31"/>
+      <x:c r="P282" s="31"/>
+      <x:c r="Q282" s="31"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="31"/>
+      <x:c r="B283" s="31"/>
+      <x:c r="C283" s="31"/>
+      <x:c r="D283" s="31"/>
+      <x:c r="E283" s="31"/>
+      <x:c r="F283" s="31"/>
+      <x:c r="G283" s="31"/>
+      <x:c r="H283" s="31"/>
+      <x:c r="I283" s="31"/>
+      <x:c r="J283" s="31"/>
+      <x:c r="K283" s="31"/>
+      <x:c r="L283" s="31"/>
+      <x:c r="M283" s="31"/>
+      <x:c r="N283" s="31"/>
+      <x:c r="O283" s="31"/>
+      <x:c r="P283" s="31"/>
+      <x:c r="Q283" s="31"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="31"/>
+      <x:c r="B284" s="31"/>
+      <x:c r="C284" s="31"/>
+      <x:c r="D284" s="31"/>
+      <x:c r="E284" s="31"/>
+      <x:c r="F284" s="31"/>
+      <x:c r="G284" s="31"/>
+      <x:c r="H284" s="31"/>
+      <x:c r="I284" s="31"/>
+      <x:c r="J284" s="31"/>
+      <x:c r="K284" s="31"/>
+      <x:c r="L284" s="31"/>
+      <x:c r="M284" s="31"/>
+      <x:c r="N284" s="31"/>
+      <x:c r="O284" s="31"/>
+      <x:c r="P284" s="31"/>
+      <x:c r="Q284" s="31"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="31"/>
+      <x:c r="B285" s="31"/>
+      <x:c r="C285" s="31"/>
+      <x:c r="D285" s="31"/>
+      <x:c r="E285" s="31"/>
+      <x:c r="F285" s="31"/>
+      <x:c r="G285" s="31"/>
+      <x:c r="H285" s="31"/>
+      <x:c r="I285" s="31"/>
+      <x:c r="J285" s="31"/>
+      <x:c r="K285" s="31"/>
+      <x:c r="L285" s="31"/>
+      <x:c r="M285" s="31"/>
+      <x:c r="N285" s="31"/>
+      <x:c r="O285" s="31"/>
+      <x:c r="P285" s="31"/>
+      <x:c r="Q285" s="31"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="31"/>
+      <x:c r="B286" s="31"/>
+      <x:c r="C286" s="31"/>
+      <x:c r="D286" s="31"/>
+      <x:c r="E286" s="31"/>
+      <x:c r="F286" s="31"/>
+      <x:c r="G286" s="31"/>
+      <x:c r="H286" s="31"/>
+      <x:c r="I286" s="31"/>
+      <x:c r="J286" s="31"/>
+      <x:c r="K286" s="31"/>
+      <x:c r="L286" s="31"/>
+      <x:c r="M286" s="31"/>
+      <x:c r="N286" s="31"/>
+      <x:c r="O286" s="31"/>
+      <x:c r="P286" s="31"/>
+      <x:c r="Q286" s="31"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="31"/>
+      <x:c r="B287" s="31"/>
+      <x:c r="C287" s="31"/>
+      <x:c r="D287" s="31"/>
+      <x:c r="E287" s="31"/>
+      <x:c r="F287" s="31"/>
+      <x:c r="G287" s="31"/>
+      <x:c r="H287" s="31"/>
+      <x:c r="I287" s="31"/>
+      <x:c r="J287" s="31"/>
+      <x:c r="K287" s="31"/>
+      <x:c r="L287" s="31"/>
+      <x:c r="M287" s="31"/>
+      <x:c r="N287" s="31"/>
+      <x:c r="O287" s="31"/>
+      <x:c r="P287" s="31"/>
+      <x:c r="Q287" s="31"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="31"/>
+      <x:c r="B288" s="31"/>
+      <x:c r="C288" s="31"/>
+      <x:c r="D288" s="31"/>
+      <x:c r="E288" s="31"/>
+      <x:c r="F288" s="31"/>
+      <x:c r="G288" s="31"/>
+      <x:c r="H288" s="31"/>
+      <x:c r="I288" s="31"/>
+      <x:c r="J288" s="31"/>
+      <x:c r="K288" s="31"/>
+      <x:c r="L288" s="31"/>
+      <x:c r="M288" s="31"/>
+      <x:c r="N288" s="31"/>
+      <x:c r="O288" s="31"/>
+      <x:c r="P288" s="31"/>
+      <x:c r="Q288" s="31"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="31"/>
+      <x:c r="B289" s="31"/>
+      <x:c r="C289" s="31"/>
+      <x:c r="D289" s="31"/>
+      <x:c r="E289" s="31"/>
+      <x:c r="F289" s="31"/>
+      <x:c r="G289" s="31"/>
+      <x:c r="H289" s="31"/>
+      <x:c r="I289" s="31"/>
+      <x:c r="J289" s="31"/>
+      <x:c r="K289" s="31"/>
+      <x:c r="L289" s="31"/>
+      <x:c r="M289" s="31"/>
+      <x:c r="N289" s="31"/>
+      <x:c r="O289" s="31"/>
+      <x:c r="P289" s="31"/>
+      <x:c r="Q289" s="31"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="31"/>
+      <x:c r="B290" s="31"/>
+      <x:c r="C290" s="31"/>
+      <x:c r="D290" s="31"/>
+      <x:c r="E290" s="31"/>
+      <x:c r="F290" s="31"/>
+      <x:c r="G290" s="31"/>
+      <x:c r="H290" s="31"/>
+      <x:c r="I290" s="31"/>
+      <x:c r="J290" s="31"/>
+      <x:c r="K290" s="31"/>
+      <x:c r="L290" s="31"/>
+      <x:c r="M290" s="31"/>
+      <x:c r="N290" s="31"/>
+      <x:c r="O290" s="31"/>
+      <x:c r="P290" s="31"/>
+      <x:c r="Q290" s="31"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="31"/>
+      <x:c r="B291" s="31"/>
+      <x:c r="C291" s="31"/>
+      <x:c r="D291" s="31"/>
+      <x:c r="E291" s="31"/>
+      <x:c r="F291" s="31"/>
+      <x:c r="G291" s="31"/>
+      <x:c r="H291" s="31"/>
+      <x:c r="I291" s="31"/>
+      <x:c r="J291" s="31"/>
+      <x:c r="K291" s="31"/>
+      <x:c r="L291" s="31"/>
+      <x:c r="M291" s="31"/>
+      <x:c r="N291" s="31"/>
+      <x:c r="O291" s="31"/>
+      <x:c r="P291" s="31"/>
+      <x:c r="Q291" s="31"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="31"/>
+      <x:c r="B292" s="31"/>
+      <x:c r="C292" s="31"/>
+      <x:c r="D292" s="31"/>
+      <x:c r="E292" s="31"/>
+      <x:c r="F292" s="31"/>
+      <x:c r="G292" s="31"/>
+      <x:c r="H292" s="31"/>
+      <x:c r="I292" s="31"/>
+      <x:c r="J292" s="31"/>
+      <x:c r="K292" s="31"/>
+      <x:c r="L292" s="31"/>
+      <x:c r="M292" s="31"/>
+      <x:c r="N292" s="31"/>
+      <x:c r="O292" s="31"/>
+      <x:c r="P292" s="31"/>
+      <x:c r="Q292" s="31"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="31"/>
+      <x:c r="B293" s="31"/>
+      <x:c r="C293" s="31"/>
+      <x:c r="D293" s="31"/>
+      <x:c r="E293" s="31"/>
+      <x:c r="F293" s="31"/>
+      <x:c r="G293" s="31"/>
+      <x:c r="H293" s="31"/>
+      <x:c r="I293" s="31"/>
+      <x:c r="J293" s="31"/>
+      <x:c r="K293" s="31"/>
+      <x:c r="L293" s="31"/>
+      <x:c r="M293" s="31"/>
+      <x:c r="N293" s="31"/>
+      <x:c r="O293" s="31"/>
+      <x:c r="P293" s="31"/>
+      <x:c r="Q293" s="31"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="31"/>
+      <x:c r="B294" s="31"/>
+      <x:c r="C294" s="31"/>
+      <x:c r="D294" s="31"/>
+      <x:c r="E294" s="31"/>
+      <x:c r="F294" s="31"/>
+      <x:c r="G294" s="31"/>
+      <x:c r="H294" s="31"/>
+      <x:c r="I294" s="31"/>
+      <x:c r="J294" s="31"/>
+      <x:c r="K294" s="31"/>
+      <x:c r="L294" s="31"/>
+      <x:c r="M294" s="31"/>
+      <x:c r="N294" s="31"/>
+      <x:c r="O294" s="31"/>
+      <x:c r="P294" s="31"/>
+      <x:c r="Q294" s="31"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="31"/>
+      <x:c r="B295" s="31"/>
+      <x:c r="C295" s="31"/>
+      <x:c r="D295" s="31"/>
+      <x:c r="E295" s="31"/>
+      <x:c r="F295" s="31"/>
+      <x:c r="G295" s="31"/>
+      <x:c r="H295" s="31"/>
+      <x:c r="I295" s="31"/>
+      <x:c r="J295" s="31"/>
+      <x:c r="K295" s="31"/>
+      <x:c r="L295" s="31"/>
+      <x:c r="M295" s="31"/>
+      <x:c r="N295" s="31"/>
+      <x:c r="O295" s="31"/>
+      <x:c r="P295" s="31"/>
+      <x:c r="Q295" s="31"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="31"/>
+      <x:c r="B296" s="31"/>
+      <x:c r="C296" s="31"/>
+      <x:c r="D296" s="31"/>
+      <x:c r="E296" s="31"/>
+      <x:c r="F296" s="31"/>
+      <x:c r="G296" s="31"/>
+      <x:c r="H296" s="31"/>
+      <x:c r="I296" s="31"/>
+      <x:c r="J296" s="31"/>
+      <x:c r="K296" s="31"/>
+      <x:c r="L296" s="31"/>
+      <x:c r="M296" s="31"/>
+      <x:c r="N296" s="31"/>
+      <x:c r="O296" s="31"/>
+      <x:c r="P296" s="31"/>
+      <x:c r="Q296" s="31"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="31"/>
+      <x:c r="B297" s="31"/>
+      <x:c r="C297" s="31"/>
+      <x:c r="D297" s="31"/>
+      <x:c r="E297" s="31"/>
+      <x:c r="F297" s="31"/>
+      <x:c r="G297" s="31"/>
+      <x:c r="H297" s="31"/>
+      <x:c r="I297" s="31"/>
+      <x:c r="J297" s="31"/>
+      <x:c r="K297" s="31"/>
+      <x:c r="L297" s="31"/>
+      <x:c r="M297" s="31"/>
+      <x:c r="N297" s="31"/>
+      <x:c r="O297" s="31"/>
+      <x:c r="P297" s="31"/>
+      <x:c r="Q297" s="31"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="31"/>
+      <x:c r="B298" s="31"/>
+      <x:c r="C298" s="31"/>
+      <x:c r="D298" s="31"/>
+      <x:c r="E298" s="31"/>
+      <x:c r="F298" s="31"/>
+      <x:c r="G298" s="31"/>
+      <x:c r="H298" s="31"/>
+      <x:c r="I298" s="31"/>
+      <x:c r="J298" s="31"/>
+      <x:c r="K298" s="31"/>
+      <x:c r="L298" s="31"/>
+      <x:c r="M298" s="31"/>
+      <x:c r="N298" s="31"/>
+      <x:c r="O298" s="31"/>
+      <x:c r="P298" s="31"/>
+      <x:c r="Q298" s="31"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="31"/>
+      <x:c r="B299" s="31"/>
+      <x:c r="C299" s="31"/>
+      <x:c r="D299" s="31"/>
+      <x:c r="E299" s="31"/>
+      <x:c r="F299" s="31"/>
+      <x:c r="G299" s="31"/>
+      <x:c r="H299" s="31"/>
+      <x:c r="I299" s="31"/>
+      <x:c r="J299" s="31"/>
+      <x:c r="K299" s="31"/>
+      <x:c r="L299" s="31"/>
+      <x:c r="M299" s="31"/>
+      <x:c r="N299" s="31"/>
+      <x:c r="O299" s="31"/>
+      <x:c r="P299" s="31"/>
+      <x:c r="Q299" s="31"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="31"/>
+      <x:c r="B300" s="31"/>
+      <x:c r="C300" s="31"/>
+      <x:c r="D300" s="31"/>
+      <x:c r="E300" s="31"/>
+      <x:c r="F300" s="31"/>
+      <x:c r="G300" s="31"/>
+      <x:c r="H300" s="31"/>
+      <x:c r="I300" s="31"/>
+      <x:c r="J300" s="31"/>
+      <x:c r="K300" s="31"/>
+      <x:c r="L300" s="31"/>
+      <x:c r="M300" s="31"/>
+      <x:c r="N300" s="31"/>
+      <x:c r="O300" s="31"/>
+      <x:c r="P300" s="31"/>
+      <x:c r="Q300" s="31"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="150.6699981689453" hidden="0" customWidth="1"/>
   </x:cols>
@@ -57105,10 +62916,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="41" t="str">
-        <x:v>HRM-Text comparison</x:v>
+        <x:v>ARC-Challenge slice</x:v>
       </x:c>
       <x:c r="B9" s="41" t="str">
-        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
+        <x:v>On ARC-Challenge validation[:50], Qwen3-1.7B base scores 37/50, fixed HRM blend scores 35/50, and agreement_blend recovers 37/50.</x:v>
       </x:c>
       <x:c r="C9" s="31"/>
       <x:c r="D9" s="31"/>
@@ -57128,10 +62939,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="41" t="str">
-        <x:v>Cost</x:v>
+        <x:v>HRM-Text comparison</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
-        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
+        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
       </x:c>
       <x:c r="C10" s="31"/>
       <x:c r="D10" s="31"/>
@@ -57151,10 +62962,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="41" t="str">
-        <x:v>Correction</x:v>
+        <x:v>Cost</x:v>
       </x:c>
       <x:c r="B11" s="41" t="str">
-        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
+        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
       </x:c>
       <x:c r="C11" s="31"/>
       <x:c r="D11" s="31"/>
@@ -57174,10 +62985,10 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="41" t="str">
-        <x:v>Interpretation</x:v>
+        <x:v>Correction</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
-        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
+        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
       </x:c>
       <x:c r="C12" s="31"/>
       <x:c r="D12" s="31"/>
@@ -57197,10 +63008,10 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="41" t="str">
-        <x:v>Fusion finding</x:v>
+        <x:v>Interpretation</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
-        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
+        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
       </x:c>
       <x:c r="C13" s="31"/>
       <x:c r="D13" s="31"/>
@@ -57220,10 +63031,10 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="41" t="str">
-        <x:v>Next</x:v>
+        <x:v>Fusion finding</x:v>
       </x:c>
       <x:c r="B14" s="41" t="str">
-        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
       </x:c>
       <x:c r="C14" s="31"/>
       <x:c r="D14" s="31"/>
@@ -57242,8 +63053,12 @@
       <x:c r="Q14" s="31"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="31"/>
-      <x:c r="B15" s="31"/>
+      <x:c r="A15" s="41" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="B15" s="41" t="str">
+        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+      </x:c>
       <x:c r="C15" s="31"/>
       <x:c r="D15" s="31"/>
       <x:c r="E15" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5ea8e0be52154fe2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R4e0962bfe8f64468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R22ea8a6a15f848f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rec4894bd3c114b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R32a330b52c304f0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R79e54b233ded419a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R8c7f475fd7af43c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARC Runs" sheetId="8" r:id="Rc1acf40dc848486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" r:id="Rac6afbdc9add40da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R71cce2d008924dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="Re83cb8e2212a45ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R762bf780269046cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="R1d880d7f8350426d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="Ra792174f4d03435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R6bdffbf681d743a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R20db5caa25844681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARC Runs" sheetId="8" r:id="Rca98ba1ba11f44b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" r:id="R5b87ed333cd746b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -56972,7 +56972,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="33" t="str">
-        <x:v>Qwen3-1.7B-4bit</x:v>
+        <x:v>Qwen3-0.6B-4bit</x:v>
       </x:c>
       <x:c r="B2" s="33" t="str">
         <x:v>validation</x:v>
@@ -56990,19 +56990,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="33" t="n">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H2" s="33" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I2" s="34" t="n">
-        <x:v>0.74</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="J2" s="35" t="n">
-        <x:v>7.229978584000037</x:v>
+        <x:v>3.20136787499996</x:v>
       </x:c>
       <x:c r="K2" s="33" t="str">
-        <x:v>arc_qwen3_1_7b_base_validation50.csv</x:v>
+        <x:v>arc_qwen3_0_6b_base_validation50.csv</x:v>
       </x:c>
       <x:c r="L2" s="31"/>
       <x:c r="M2" s="31"/>
@@ -57013,7 +57013,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="33" t="str">
-        <x:v>Qwen3-1.7B-4bit</x:v>
+        <x:v>Qwen3-0.6B-4bit</x:v>
       </x:c>
       <x:c r="B3" s="33" t="str">
         <x:v>validation</x:v>
@@ -57031,19 +57031,19 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="G3" s="33" t="n">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H3" s="33" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I3" s="34" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="J3" s="35" t="n">
-        <x:v>20.041542333000052</x:v>
+        <x:v>8.204612542000177</x:v>
       </x:c>
       <x:c r="K3" s="33" t="str">
-        <x:v>arc_qwen3_1_7b_hrm_validation50.csv</x:v>
+        <x:v>arc_qwen3_0_6b_hrm_validation50.csv</x:v>
       </x:c>
       <x:c r="L3" s="31"/>
       <x:c r="M3" s="31"/>
@@ -57054,7 +57054,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="33" t="str">
-        <x:v>Qwen3-1.7B-4bit</x:v>
+        <x:v>Qwen3-0.6B-4bit</x:v>
       </x:c>
       <x:c r="B4" s="33" t="str">
         <x:v>validation</x:v>
@@ -57072,19 +57072,19 @@
         <x:v>0.2</x:v>
       </x:c>
       <x:c r="G4" s="33" t="n">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H4" s="33" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="I4" s="34" t="n">
-        <x:v>0.74</x:v>
+        <x:v>0.42</x:v>
       </x:c>
       <x:c r="J4" s="35" t="n">
-        <x:v>20.54996462500003</x:v>
+        <x:v>8.522171374999743</x:v>
       </x:c>
       <x:c r="K4" s="33" t="str">
-        <x:v>arc_qwen3_1_7b_hrm_agreement_validation50.csv</x:v>
+        <x:v>arc_qwen3_0_6b_hrm_agreement_validation50.csv</x:v>
       </x:c>
       <x:c r="L4" s="31"/>
       <x:c r="M4" s="31"/>
@@ -57094,17 +57094,39 @@
       <x:c r="Q4" s="31"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="31"/>
-      <x:c r="B5" s="31"/>
-      <x:c r="C5" s="31"/>
-      <x:c r="D5" s="31"/>
-      <x:c r="E5" s="31"/>
-      <x:c r="F5" s="31"/>
-      <x:c r="G5" s="31"/>
-      <x:c r="H5" s="31"/>
-      <x:c r="I5" s="36"/>
-      <x:c r="J5" s="37"/>
-      <x:c r="K5" s="31"/>
+      <x:c r="A5" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B5" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C5" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="E5" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F5" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="33" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H5" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I5" s="34" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="J5" s="35" t="n">
+        <x:v>7.229978584000037</x:v>
+      </x:c>
+      <x:c r="K5" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_base_validation50.csv</x:v>
+      </x:c>
       <x:c r="L5" s="31"/>
       <x:c r="M5" s="31"/>
       <x:c r="N5" s="31"/>
@@ -57113,17 +57135,39 @@
       <x:c r="Q5" s="31"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="31"/>
-      <x:c r="B6" s="31"/>
-      <x:c r="C6" s="31"/>
-      <x:c r="D6" s="31"/>
-      <x:c r="E6" s="31"/>
-      <x:c r="F6" s="31"/>
-      <x:c r="G6" s="31"/>
-      <x:c r="H6" s="31"/>
-      <x:c r="I6" s="36"/>
-      <x:c r="J6" s="37"/>
-      <x:c r="K6" s="31"/>
+      <x:c r="A6" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>hrm</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="str">
+        <x:v>blend</x:v>
+      </x:c>
+      <x:c r="F6" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="G6" s="33" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H6" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I6" s="34" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="J6" s="35" t="n">
+        <x:v>20.041542333000052</x:v>
+      </x:c>
+      <x:c r="K6" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_hrm_validation50.csv</x:v>
+      </x:c>
       <x:c r="L6" s="31"/>
       <x:c r="M6" s="31"/>
       <x:c r="N6" s="31"/>
@@ -57132,17 +57176,39 @@
       <x:c r="Q6" s="31"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="31"/>
-      <x:c r="B7" s="31"/>
-      <x:c r="C7" s="31"/>
-      <x:c r="D7" s="31"/>
-      <x:c r="E7" s="31"/>
-      <x:c r="F7" s="31"/>
-      <x:c r="G7" s="31"/>
-      <x:c r="H7" s="31"/>
-      <x:c r="I7" s="36"/>
-      <x:c r="J7" s="37"/>
-      <x:c r="K7" s="31"/>
+      <x:c r="A7" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B7" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C7" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D7" s="33" t="str">
+        <x:v>hrm</x:v>
+      </x:c>
+      <x:c r="E7" s="33" t="str">
+        <x:v>agreement_blend</x:v>
+      </x:c>
+      <x:c r="F7" s="33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="G7" s="33" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H7" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I7" s="34" t="n">
+        <x:v>0.74</x:v>
+      </x:c>
+      <x:c r="J7" s="35" t="n">
+        <x:v>20.54996462500003</x:v>
+      </x:c>
+      <x:c r="K7" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_hrm_agreement_validation50.csv</x:v>
+      </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="31"/>
       <x:c r="N7" s="31"/>
@@ -62727,7 +62793,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="150.6699981689453" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="156.1999969482422" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -62919,7 +62985,7 @@
         <x:v>ARC-Challenge slice</x:v>
       </x:c>
       <x:c r="B9" s="41" t="str">
-        <x:v>On ARC-Challenge validation[:50], Qwen3-1.7B base scores 37/50, fixed HRM blend scores 35/50, and agreement_blend recovers 37/50.</x:v>
+        <x:v>On ARC-Challenge validation[:50], Qwen3-0.6B is flat at 21/50 for base, fixed blend, and agreement_blend; Qwen3-1.7B base is 37/50, fixed blend is 35/50, and agreement_blend recovers 37/50.</x:v>
       </x:c>
       <x:c r="C9" s="31"/>
       <x:c r="D9" s="31"/>

--- a/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
+++ b/outputs/qwen_hrm_metrics/qwen_hrm_conversion_metrics.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R71cce2d008924dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="Re83cb8e2212a45ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="R762bf780269046cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="R1d880d7f8350426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="Ra792174f4d03435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R6bdffbf681d743a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R20db5caa25844681"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARC Runs" sheetId="8" r:id="Rca98ba1ba11f44b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" r:id="R5b87ed333cd746b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R67dc87e2b293427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Runs" sheetId="2" r:id="R0ca0b9a28eae4fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Outcomes" sheetId="3" r:id="Rfe3376cdafcc437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sweep Runs" sheetId="4" r:id="Rb12572d04e7c46d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Runs" sheetId="5" r:id="R707fba9591b94040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exact Outcomes" sheetId="6" r:id="R715d228681f64e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rerank Runs" sheetId="7" r:id="R83379fa8bdbb4b6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARC Runs" sheetId="8" r:id="R54bae953427e4a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARC Ensembles" sheetId="9" r:id="Raf495af0f1d84818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="10" r:id="R4093ccdfb5b244fc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6374,6 +6375,5783 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="157.17999267578125" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="40" t="str">
+        <x:v>Item</x:v>
+      </x:c>
+      <x:c r="B1" s="40" t="str">
+        <x:v>Note</x:v>
+      </x:c>
+      <x:c r="C1" s="31"/>
+      <x:c r="D1" s="31"/>
+      <x:c r="E1" s="31"/>
+      <x:c r="F1" s="31"/>
+      <x:c r="G1" s="31"/>
+      <x:c r="H1" s="31"/>
+      <x:c r="I1" s="31"/>
+      <x:c r="J1" s="31"/>
+      <x:c r="K1" s="31"/>
+      <x:c r="L1" s="31"/>
+      <x:c r="M1" s="31"/>
+      <x:c r="N1" s="31"/>
+      <x:c r="O1" s="31"/>
+      <x:c r="P1" s="31"/>
+      <x:c r="Q1" s="31"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="41" t="str">
+        <x:v>Benchmark</x:v>
+      </x:c>
+      <x:c r="B2" s="41" t="str">
+        <x:v>Closed-form multiple-choice probe scored by candidate letter log-probability.</x:v>
+      </x:c>
+      <x:c r="C2" s="31"/>
+      <x:c r="D2" s="31"/>
+      <x:c r="E2" s="31"/>
+      <x:c r="F2" s="31"/>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="31"/>
+      <x:c r="J2" s="31"/>
+      <x:c r="K2" s="31"/>
+      <x:c r="L2" s="31"/>
+      <x:c r="M2" s="31"/>
+      <x:c r="N2" s="31"/>
+      <x:c r="O2" s="31"/>
+      <x:c r="P2" s="31"/>
+      <x:c r="Q2" s="31"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="41" t="str">
+        <x:v>Current wins</x:v>
+      </x:c>
+      <x:c r="B3" s="41" t="str">
+        <x:v>Qwen3-0.6B-4bit improves from 5/17 to 7/17 with split 14; Qwen3-1.7B-4bit improves from 10/17 to 11/17 with split 10.</x:v>
+      </x:c>
+      <x:c r="C3" s="31"/>
+      <x:c r="D3" s="31"/>
+      <x:c r="E3" s="31"/>
+      <x:c r="F3" s="31"/>
+      <x:c r="G3" s="31"/>
+      <x:c r="H3" s="31"/>
+      <x:c r="I3" s="31"/>
+      <x:c r="J3" s="31"/>
+      <x:c r="K3" s="31"/>
+      <x:c r="L3" s="31"/>
+      <x:c r="M3" s="31"/>
+      <x:c r="N3" s="31"/>
+      <x:c r="O3" s="31"/>
+      <x:c r="P3" s="31"/>
+      <x:c r="Q3" s="31"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="41" t="str">
+        <x:v>Split finding</x:v>
+      </x:c>
+      <x:c r="B4" s="41" t="str">
+        <x:v>The symmetric 14/14 split is best for 0.6B; an earlier split at 10 lower layers is best for 1.7B on the corrected probe.</x:v>
+      </x:c>
+      <x:c r="C4" s="31"/>
+      <x:c r="D4" s="31"/>
+      <x:c r="E4" s="31"/>
+      <x:c r="F4" s="31"/>
+      <x:c r="G4" s="31"/>
+      <x:c r="H4" s="31"/>
+      <x:c r="I4" s="31"/>
+      <x:c r="J4" s="31"/>
+      <x:c r="K4" s="31"/>
+      <x:c r="L4" s="31"/>
+      <x:c r="M4" s="31"/>
+      <x:c r="N4" s="31"/>
+      <x:c r="O4" s="31"/>
+      <x:c r="P4" s="31"/>
+      <x:c r="Q4" s="31"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="41" t="str">
+        <x:v>Exact-answer probe</x:v>
+      </x:c>
+      <x:c r="B5" s="41" t="str">
+        <x:v>Added a stricter generative probe with exact extraction. Qwen3-0.6B moves from 1/17 base to 2/17 HRM; Qwen3-1.7B is 6/17 for both base and HRM after corrected text-answer scoring.</x:v>
+      </x:c>
+      <x:c r="C5" s="31"/>
+      <x:c r="D5" s="31"/>
+      <x:c r="E5" s="31"/>
+      <x:c r="F5" s="31"/>
+      <x:c r="G5" s="31"/>
+      <x:c r="H5" s="31"/>
+      <x:c r="I5" s="31"/>
+      <x:c r="J5" s="31"/>
+      <x:c r="K5" s="31"/>
+      <x:c r="L5" s="31"/>
+      <x:c r="M5" s="31"/>
+      <x:c r="N5" s="31"/>
+      <x:c r="O5" s="31"/>
+      <x:c r="P5" s="31"/>
+      <x:c r="Q5" s="31"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="41" t="str">
+        <x:v>Qwen chat exact</x:v>
+      </x:c>
+      <x:c r="B6" s="41" t="str">
+        <x:v>On Qwen3-1.7B chat-template boxed runs, fixed blend scores 5/17 while agreement_blend and confidence_gate recover the 6/17 base score. Use gated fusion for open-ended generation.</x:v>
+      </x:c>
+      <x:c r="C6" s="31"/>
+      <x:c r="D6" s="31"/>
+      <x:c r="E6" s="31"/>
+      <x:c r="F6" s="31"/>
+      <x:c r="G6" s="31"/>
+      <x:c r="H6" s="31"/>
+      <x:c r="I6" s="31"/>
+      <x:c r="J6" s="31"/>
+      <x:c r="K6" s="31"/>
+      <x:c r="L6" s="31"/>
+      <x:c r="M6" s="31"/>
+      <x:c r="N6" s="31"/>
+      <x:c r="O6" s="31"/>
+      <x:c r="P6" s="31"/>
+      <x:c r="Q6" s="31"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="41" t="str">
+        <x:v>Delayed fusion</x:v>
+      </x:c>
+      <x:c r="B7" s="41" t="str">
+        <x:v>Final-answer-triggered HRM fusion also recovers the 6/17 base score on Qwen3-1.7B chat-template boxed runs. It is safer than full-sequence fixed blending but still not above base.</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="31"/>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="31"/>
+      <x:c r="H7" s="31"/>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="31"/>
+      <x:c r="K7" s="31"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="31"/>
+      <x:c r="N7" s="31"/>
+      <x:c r="O7" s="31"/>
+      <x:c r="P7" s="31"/>
+      <x:c r="Q7" s="31"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="41" t="str">
+        <x:v>Candidate rerank</x:v>
+      </x:c>
+      <x:c r="B8" s="41" t="str">
+        <x:v>Saved-output candidate reranking found an 11/17 oracle union across raw/chat candidates, but naive yes/no and answer-likelihood rerankers selected only 6/17. Need a stronger verifier.</x:v>
+      </x:c>
+      <x:c r="C8" s="31"/>
+      <x:c r="D8" s="31"/>
+      <x:c r="E8" s="31"/>
+      <x:c r="F8" s="31"/>
+      <x:c r="G8" s="31"/>
+      <x:c r="H8" s="31"/>
+      <x:c r="I8" s="31"/>
+      <x:c r="J8" s="31"/>
+      <x:c r="K8" s="31"/>
+      <x:c r="L8" s="31"/>
+      <x:c r="M8" s="31"/>
+      <x:c r="N8" s="31"/>
+      <x:c r="O8" s="31"/>
+      <x:c r="P8" s="31"/>
+      <x:c r="Q8" s="31"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="41" t="str">
+        <x:v>ARC-Challenge slice</x:v>
+      </x:c>
+      <x:c r="B9" s="41" t="str">
+        <x:v>On ARC-Challenge validation[:50], Qwen3-0.6B is flat at 21/50 for base, fixed blend, and agreement_blend; Qwen3-1.7B base is 37/50, fixed blend is 35/50, and agreement_blend recovers 37/50.</x:v>
+      </x:c>
+      <x:c r="C9" s="31"/>
+      <x:c r="D9" s="31"/>
+      <x:c r="E9" s="31"/>
+      <x:c r="F9" s="31"/>
+      <x:c r="G9" s="31"/>
+      <x:c r="H9" s="31"/>
+      <x:c r="I9" s="31"/>
+      <x:c r="J9" s="31"/>
+      <x:c r="K9" s="31"/>
+      <x:c r="L9" s="31"/>
+      <x:c r="M9" s="31"/>
+      <x:c r="N9" s="31"/>
+      <x:c r="O9" s="31"/>
+      <x:c r="P9" s="31"/>
+      <x:c r="Q9" s="31"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="41" t="str">
+        <x:v>ARC margin ensemble</x:v>
+      </x:c>
+      <x:c r="B10" s="41" t="str">
+        <x:v>A base-margin switch to HRM when base top-two margin &lt;= 0.25 improves Qwen3-0.6B from 21/50 to 23/50, but drops Qwen3-1.7B from 37/50 to 36/50. Treat as model-specific and unvalidated.</x:v>
+      </x:c>
+      <x:c r="C10" s="31"/>
+      <x:c r="D10" s="31"/>
+      <x:c r="E10" s="31"/>
+      <x:c r="F10" s="31"/>
+      <x:c r="G10" s="31"/>
+      <x:c r="H10" s="31"/>
+      <x:c r="I10" s="31"/>
+      <x:c r="J10" s="31"/>
+      <x:c r="K10" s="31"/>
+      <x:c r="L10" s="31"/>
+      <x:c r="M10" s="31"/>
+      <x:c r="N10" s="31"/>
+      <x:c r="O10" s="31"/>
+      <x:c r="P10" s="31"/>
+      <x:c r="Q10" s="31"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="41" t="str">
+        <x:v>HRM-Text comparison</x:v>
+      </x:c>
+      <x:c r="B11" s="41" t="str">
+        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
+      </x:c>
+      <x:c r="C11" s="31"/>
+      <x:c r="D11" s="31"/>
+      <x:c r="E11" s="31"/>
+      <x:c r="F11" s="31"/>
+      <x:c r="G11" s="31"/>
+      <x:c r="H11" s="31"/>
+      <x:c r="I11" s="31"/>
+      <x:c r="J11" s="31"/>
+      <x:c r="K11" s="31"/>
+      <x:c r="L11" s="31"/>
+      <x:c r="M11" s="31"/>
+      <x:c r="N11" s="31"/>
+      <x:c r="O11" s="31"/>
+      <x:c r="P11" s="31"/>
+      <x:c r="Q11" s="31"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="41" t="str">
+        <x:v>Cost</x:v>
+      </x:c>
+      <x:c r="B12" s="41" t="str">
+        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
+      </x:c>
+      <x:c r="C12" s="31"/>
+      <x:c r="D12" s="31"/>
+      <x:c r="E12" s="31"/>
+      <x:c r="F12" s="31"/>
+      <x:c r="G12" s="31"/>
+      <x:c r="H12" s="31"/>
+      <x:c r="I12" s="31"/>
+      <x:c r="J12" s="31"/>
+      <x:c r="K12" s="31"/>
+      <x:c r="L12" s="31"/>
+      <x:c r="M12" s="31"/>
+      <x:c r="N12" s="31"/>
+      <x:c r="O12" s="31"/>
+      <x:c r="P12" s="31"/>
+      <x:c r="Q12" s="31"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="41" t="str">
+        <x:v>Correction</x:v>
+      </x:c>
+      <x:c r="B13" s="41" t="str">
+        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
+      </x:c>
+      <x:c r="C13" s="31"/>
+      <x:c r="D13" s="31"/>
+      <x:c r="E13" s="31"/>
+      <x:c r="F13" s="31"/>
+      <x:c r="G13" s="31"/>
+      <x:c r="H13" s="31"/>
+      <x:c r="I13" s="31"/>
+      <x:c r="J13" s="31"/>
+      <x:c r="K13" s="31"/>
+      <x:c r="L13" s="31"/>
+      <x:c r="M13" s="31"/>
+      <x:c r="N13" s="31"/>
+      <x:c r="O13" s="31"/>
+      <x:c r="P13" s="31"/>
+      <x:c r="Q13" s="31"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="41" t="str">
+        <x:v>Interpretation</x:v>
+      </x:c>
+      <x:c r="B14" s="41" t="str">
+        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
+      </x:c>
+      <x:c r="C14" s="31"/>
+      <x:c r="D14" s="31"/>
+      <x:c r="E14" s="31"/>
+      <x:c r="F14" s="31"/>
+      <x:c r="G14" s="31"/>
+      <x:c r="H14" s="31"/>
+      <x:c r="I14" s="31"/>
+      <x:c r="J14" s="31"/>
+      <x:c r="K14" s="31"/>
+      <x:c r="L14" s="31"/>
+      <x:c r="M14" s="31"/>
+      <x:c r="N14" s="31"/>
+      <x:c r="O14" s="31"/>
+      <x:c r="P14" s="31"/>
+      <x:c r="Q14" s="31"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="41" t="str">
+        <x:v>Fusion finding</x:v>
+      </x:c>
+      <x:c r="B15" s="41" t="str">
+        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
+      </x:c>
+      <x:c r="C15" s="31"/>
+      <x:c r="D15" s="31"/>
+      <x:c r="E15" s="31"/>
+      <x:c r="F15" s="31"/>
+      <x:c r="G15" s="31"/>
+      <x:c r="H15" s="31"/>
+      <x:c r="I15" s="31"/>
+      <x:c r="J15" s="31"/>
+      <x:c r="K15" s="31"/>
+      <x:c r="L15" s="31"/>
+      <x:c r="M15" s="31"/>
+      <x:c r="N15" s="31"/>
+      <x:c r="O15" s="31"/>
+      <x:c r="P15" s="31"/>
+      <x:c r="Q15" s="31"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="41" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+      <x:c r="B16" s="41" t="str">
+        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
+      </x:c>
+      <x:c r="C16" s="31"/>
+      <x:c r="D16" s="31"/>
+      <x:c r="E16" s="31"/>
+      <x:c r="F16" s="31"/>
+      <x:c r="G16" s="31"/>
+      <x:c r="H16" s="31"/>
+      <x:c r="I16" s="31"/>
+      <x:c r="J16" s="31"/>
+      <x:c r="K16" s="31"/>
+      <x:c r="L16" s="31"/>
+      <x:c r="M16" s="31"/>
+      <x:c r="N16" s="31"/>
+      <x:c r="O16" s="31"/>
+      <x:c r="P16" s="31"/>
+      <x:c r="Q16" s="31"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="31"/>
+      <x:c r="B17" s="31"/>
+      <x:c r="C17" s="31"/>
+      <x:c r="D17" s="31"/>
+      <x:c r="E17" s="31"/>
+      <x:c r="F17" s="31"/>
+      <x:c r="G17" s="31"/>
+      <x:c r="H17" s="31"/>
+      <x:c r="I17" s="31"/>
+      <x:c r="J17" s="31"/>
+      <x:c r="K17" s="31"/>
+      <x:c r="L17" s="31"/>
+      <x:c r="M17" s="31"/>
+      <x:c r="N17" s="31"/>
+      <x:c r="O17" s="31"/>
+      <x:c r="P17" s="31"/>
+      <x:c r="Q17" s="31"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="31"/>
+      <x:c r="B18" s="31"/>
+      <x:c r="C18" s="31"/>
+      <x:c r="D18" s="31"/>
+      <x:c r="E18" s="31"/>
+      <x:c r="F18" s="31"/>
+      <x:c r="G18" s="31"/>
+      <x:c r="H18" s="31"/>
+      <x:c r="I18" s="31"/>
+      <x:c r="J18" s="31"/>
+      <x:c r="K18" s="31"/>
+      <x:c r="L18" s="31"/>
+      <x:c r="M18" s="31"/>
+      <x:c r="N18" s="31"/>
+      <x:c r="O18" s="31"/>
+      <x:c r="P18" s="31"/>
+      <x:c r="Q18" s="31"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="31"/>
+      <x:c r="B19" s="31"/>
+      <x:c r="C19" s="31"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="31"/>
+      <x:c r="F19" s="31"/>
+      <x:c r="G19" s="31"/>
+      <x:c r="H19" s="31"/>
+      <x:c r="I19" s="31"/>
+      <x:c r="J19" s="31"/>
+      <x:c r="K19" s="31"/>
+      <x:c r="L19" s="31"/>
+      <x:c r="M19" s="31"/>
+      <x:c r="N19" s="31"/>
+      <x:c r="O19" s="31"/>
+      <x:c r="P19" s="31"/>
+      <x:c r="Q19" s="31"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="31"/>
+      <x:c r="B20" s="31"/>
+      <x:c r="C20" s="31"/>
+      <x:c r="D20" s="31"/>
+      <x:c r="E20" s="31"/>
+      <x:c r="F20" s="31"/>
+      <x:c r="G20" s="31"/>
+      <x:c r="H20" s="31"/>
+      <x:c r="I20" s="31"/>
+      <x:c r="J20" s="31"/>
+      <x:c r="K20" s="31"/>
+      <x:c r="L20" s="31"/>
+      <x:c r="M20" s="31"/>
+      <x:c r="N20" s="31"/>
+      <x:c r="O20" s="31"/>
+      <x:c r="P20" s="31"/>
+      <x:c r="Q20" s="31"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="31"/>
+      <x:c r="B21" s="31"/>
+      <x:c r="C21" s="31"/>
+      <x:c r="D21" s="31"/>
+      <x:c r="E21" s="31"/>
+      <x:c r="F21" s="31"/>
+      <x:c r="G21" s="31"/>
+      <x:c r="H21" s="31"/>
+      <x:c r="I21" s="31"/>
+      <x:c r="J21" s="31"/>
+      <x:c r="K21" s="31"/>
+      <x:c r="L21" s="31"/>
+      <x:c r="M21" s="31"/>
+      <x:c r="N21" s="31"/>
+      <x:c r="O21" s="31"/>
+      <x:c r="P21" s="31"/>
+      <x:c r="Q21" s="31"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="31"/>
+      <x:c r="B22" s="31"/>
+      <x:c r="C22" s="31"/>
+      <x:c r="D22" s="31"/>
+      <x:c r="E22" s="31"/>
+      <x:c r="F22" s="31"/>
+      <x:c r="G22" s="31"/>
+      <x:c r="H22" s="31"/>
+      <x:c r="I22" s="31"/>
+      <x:c r="J22" s="31"/>
+      <x:c r="K22" s="31"/>
+      <x:c r="L22" s="31"/>
+      <x:c r="M22" s="31"/>
+      <x:c r="N22" s="31"/>
+      <x:c r="O22" s="31"/>
+      <x:c r="P22" s="31"/>
+      <x:c r="Q22" s="31"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="31"/>
+      <x:c r="B23" s="31"/>
+      <x:c r="C23" s="31"/>
+      <x:c r="D23" s="31"/>
+      <x:c r="E23" s="31"/>
+      <x:c r="F23" s="31"/>
+      <x:c r="G23" s="31"/>
+      <x:c r="H23" s="31"/>
+      <x:c r="I23" s="31"/>
+      <x:c r="J23" s="31"/>
+      <x:c r="K23" s="31"/>
+      <x:c r="L23" s="31"/>
+      <x:c r="M23" s="31"/>
+      <x:c r="N23" s="31"/>
+      <x:c r="O23" s="31"/>
+      <x:c r="P23" s="31"/>
+      <x:c r="Q23" s="31"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="31"/>
+      <x:c r="B24" s="31"/>
+      <x:c r="C24" s="31"/>
+      <x:c r="D24" s="31"/>
+      <x:c r="E24" s="31"/>
+      <x:c r="F24" s="31"/>
+      <x:c r="G24" s="31"/>
+      <x:c r="H24" s="31"/>
+      <x:c r="I24" s="31"/>
+      <x:c r="J24" s="31"/>
+      <x:c r="K24" s="31"/>
+      <x:c r="L24" s="31"/>
+      <x:c r="M24" s="31"/>
+      <x:c r="N24" s="31"/>
+      <x:c r="O24" s="31"/>
+      <x:c r="P24" s="31"/>
+      <x:c r="Q24" s="31"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="31"/>
+      <x:c r="B25" s="31"/>
+      <x:c r="C25" s="31"/>
+      <x:c r="D25" s="31"/>
+      <x:c r="E25" s="31"/>
+      <x:c r="F25" s="31"/>
+      <x:c r="G25" s="31"/>
+      <x:c r="H25" s="31"/>
+      <x:c r="I25" s="31"/>
+      <x:c r="J25" s="31"/>
+      <x:c r="K25" s="31"/>
+      <x:c r="L25" s="31"/>
+      <x:c r="M25" s="31"/>
+      <x:c r="N25" s="31"/>
+      <x:c r="O25" s="31"/>
+      <x:c r="P25" s="31"/>
+      <x:c r="Q25" s="31"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="31"/>
+      <x:c r="B26" s="31"/>
+      <x:c r="C26" s="31"/>
+      <x:c r="D26" s="31"/>
+      <x:c r="E26" s="31"/>
+      <x:c r="F26" s="31"/>
+      <x:c r="G26" s="31"/>
+      <x:c r="H26" s="31"/>
+      <x:c r="I26" s="31"/>
+      <x:c r="J26" s="31"/>
+      <x:c r="K26" s="31"/>
+      <x:c r="L26" s="31"/>
+      <x:c r="M26" s="31"/>
+      <x:c r="N26" s="31"/>
+      <x:c r="O26" s="31"/>
+      <x:c r="P26" s="31"/>
+      <x:c r="Q26" s="31"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="31"/>
+      <x:c r="B27" s="31"/>
+      <x:c r="C27" s="31"/>
+      <x:c r="D27" s="31"/>
+      <x:c r="E27" s="31"/>
+      <x:c r="F27" s="31"/>
+      <x:c r="G27" s="31"/>
+      <x:c r="H27" s="31"/>
+      <x:c r="I27" s="31"/>
+      <x:c r="J27" s="31"/>
+      <x:c r="K27" s="31"/>
+      <x:c r="L27" s="31"/>
+      <x:c r="M27" s="31"/>
+      <x:c r="N27" s="31"/>
+      <x:c r="O27" s="31"/>
+      <x:c r="P27" s="31"/>
+      <x:c r="Q27" s="31"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="31"/>
+      <x:c r="B28" s="31"/>
+      <x:c r="C28" s="31"/>
+      <x:c r="D28" s="31"/>
+      <x:c r="E28" s="31"/>
+      <x:c r="F28" s="31"/>
+      <x:c r="G28" s="31"/>
+      <x:c r="H28" s="31"/>
+      <x:c r="I28" s="31"/>
+      <x:c r="J28" s="31"/>
+      <x:c r="K28" s="31"/>
+      <x:c r="L28" s="31"/>
+      <x:c r="M28" s="31"/>
+      <x:c r="N28" s="31"/>
+      <x:c r="O28" s="31"/>
+      <x:c r="P28" s="31"/>
+      <x:c r="Q28" s="31"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="31"/>
+      <x:c r="B29" s="31"/>
+      <x:c r="C29" s="31"/>
+      <x:c r="D29" s="31"/>
+      <x:c r="E29" s="31"/>
+      <x:c r="F29" s="31"/>
+      <x:c r="G29" s="31"/>
+      <x:c r="H29" s="31"/>
+      <x:c r="I29" s="31"/>
+      <x:c r="J29" s="31"/>
+      <x:c r="K29" s="31"/>
+      <x:c r="L29" s="31"/>
+      <x:c r="M29" s="31"/>
+      <x:c r="N29" s="31"/>
+      <x:c r="O29" s="31"/>
+      <x:c r="P29" s="31"/>
+      <x:c r="Q29" s="31"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="31"/>
+      <x:c r="B30" s="31"/>
+      <x:c r="C30" s="31"/>
+      <x:c r="D30" s="31"/>
+      <x:c r="E30" s="31"/>
+      <x:c r="F30" s="31"/>
+      <x:c r="G30" s="31"/>
+      <x:c r="H30" s="31"/>
+      <x:c r="I30" s="31"/>
+      <x:c r="J30" s="31"/>
+      <x:c r="K30" s="31"/>
+      <x:c r="L30" s="31"/>
+      <x:c r="M30" s="31"/>
+      <x:c r="N30" s="31"/>
+      <x:c r="O30" s="31"/>
+      <x:c r="P30" s="31"/>
+      <x:c r="Q30" s="31"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="31"/>
+      <x:c r="B31" s="31"/>
+      <x:c r="C31" s="31"/>
+      <x:c r="D31" s="31"/>
+      <x:c r="E31" s="31"/>
+      <x:c r="F31" s="31"/>
+      <x:c r="G31" s="31"/>
+      <x:c r="H31" s="31"/>
+      <x:c r="I31" s="31"/>
+      <x:c r="J31" s="31"/>
+      <x:c r="K31" s="31"/>
+      <x:c r="L31" s="31"/>
+      <x:c r="M31" s="31"/>
+      <x:c r="N31" s="31"/>
+      <x:c r="O31" s="31"/>
+      <x:c r="P31" s="31"/>
+      <x:c r="Q31" s="31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="31"/>
+      <x:c r="B32" s="31"/>
+      <x:c r="C32" s="31"/>
+      <x:c r="D32" s="31"/>
+      <x:c r="E32" s="31"/>
+      <x:c r="F32" s="31"/>
+      <x:c r="G32" s="31"/>
+      <x:c r="H32" s="31"/>
+      <x:c r="I32" s="31"/>
+      <x:c r="J32" s="31"/>
+      <x:c r="K32" s="31"/>
+      <x:c r="L32" s="31"/>
+      <x:c r="M32" s="31"/>
+      <x:c r="N32" s="31"/>
+      <x:c r="O32" s="31"/>
+      <x:c r="P32" s="31"/>
+      <x:c r="Q32" s="31"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="31"/>
+      <x:c r="B33" s="31"/>
+      <x:c r="C33" s="31"/>
+      <x:c r="D33" s="31"/>
+      <x:c r="E33" s="31"/>
+      <x:c r="F33" s="31"/>
+      <x:c r="G33" s="31"/>
+      <x:c r="H33" s="31"/>
+      <x:c r="I33" s="31"/>
+      <x:c r="J33" s="31"/>
+      <x:c r="K33" s="31"/>
+      <x:c r="L33" s="31"/>
+      <x:c r="M33" s="31"/>
+      <x:c r="N33" s="31"/>
+      <x:c r="O33" s="31"/>
+      <x:c r="P33" s="31"/>
+      <x:c r="Q33" s="31"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="31"/>
+      <x:c r="B34" s="31"/>
+      <x:c r="C34" s="31"/>
+      <x:c r="D34" s="31"/>
+      <x:c r="E34" s="31"/>
+      <x:c r="F34" s="31"/>
+      <x:c r="G34" s="31"/>
+      <x:c r="H34" s="31"/>
+      <x:c r="I34" s="31"/>
+      <x:c r="J34" s="31"/>
+      <x:c r="K34" s="31"/>
+      <x:c r="L34" s="31"/>
+      <x:c r="M34" s="31"/>
+      <x:c r="N34" s="31"/>
+      <x:c r="O34" s="31"/>
+      <x:c r="P34" s="31"/>
+      <x:c r="Q34" s="31"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="31"/>
+      <x:c r="B35" s="31"/>
+      <x:c r="C35" s="31"/>
+      <x:c r="D35" s="31"/>
+      <x:c r="E35" s="31"/>
+      <x:c r="F35" s="31"/>
+      <x:c r="G35" s="31"/>
+      <x:c r="H35" s="31"/>
+      <x:c r="I35" s="31"/>
+      <x:c r="J35" s="31"/>
+      <x:c r="K35" s="31"/>
+      <x:c r="L35" s="31"/>
+      <x:c r="M35" s="31"/>
+      <x:c r="N35" s="31"/>
+      <x:c r="O35" s="31"/>
+      <x:c r="P35" s="31"/>
+      <x:c r="Q35" s="31"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="31"/>
+      <x:c r="B36" s="31"/>
+      <x:c r="C36" s="31"/>
+      <x:c r="D36" s="31"/>
+      <x:c r="E36" s="31"/>
+      <x:c r="F36" s="31"/>
+      <x:c r="G36" s="31"/>
+      <x:c r="H36" s="31"/>
+      <x:c r="I36" s="31"/>
+      <x:c r="J36" s="31"/>
+      <x:c r="K36" s="31"/>
+      <x:c r="L36" s="31"/>
+      <x:c r="M36" s="31"/>
+      <x:c r="N36" s="31"/>
+      <x:c r="O36" s="31"/>
+      <x:c r="P36" s="31"/>
+      <x:c r="Q36" s="31"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="31"/>
+      <x:c r="B37" s="31"/>
+      <x:c r="C37" s="31"/>
+      <x:c r="D37" s="31"/>
+      <x:c r="E37" s="31"/>
+      <x:c r="F37" s="31"/>
+      <x:c r="G37" s="31"/>
+      <x:c r="H37" s="31"/>
+      <x:c r="I37" s="31"/>
+      <x:c r="J37" s="31"/>
+      <x:c r="K37" s="31"/>
+      <x:c r="L37" s="31"/>
+      <x:c r="M37" s="31"/>
+      <x:c r="N37" s="31"/>
+      <x:c r="O37" s="31"/>
+      <x:c r="P37" s="31"/>
+      <x:c r="Q37" s="31"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="31"/>
+      <x:c r="B38" s="31"/>
+      <x:c r="C38" s="31"/>
+      <x:c r="D38" s="31"/>
+      <x:c r="E38" s="31"/>
+      <x:c r="F38" s="31"/>
+      <x:c r="G38" s="31"/>
+      <x:c r="H38" s="31"/>
+      <x:c r="I38" s="31"/>
+      <x:c r="J38" s="31"/>
+      <x:c r="K38" s="31"/>
+      <x:c r="L38" s="31"/>
+      <x:c r="M38" s="31"/>
+      <x:c r="N38" s="31"/>
+      <x:c r="O38" s="31"/>
+      <x:c r="P38" s="31"/>
+      <x:c r="Q38" s="31"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="31"/>
+      <x:c r="B39" s="31"/>
+      <x:c r="C39" s="31"/>
+      <x:c r="D39" s="31"/>
+      <x:c r="E39" s="31"/>
+      <x:c r="F39" s="31"/>
+      <x:c r="G39" s="31"/>
+      <x:c r="H39" s="31"/>
+      <x:c r="I39" s="31"/>
+      <x:c r="J39" s="31"/>
+      <x:c r="K39" s="31"/>
+      <x:c r="L39" s="31"/>
+      <x:c r="M39" s="31"/>
+      <x:c r="N39" s="31"/>
+      <x:c r="O39" s="31"/>
+      <x:c r="P39" s="31"/>
+      <x:c r="Q39" s="31"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="31"/>
+      <x:c r="B40" s="31"/>
+      <x:c r="C40" s="31"/>
+      <x:c r="D40" s="31"/>
+      <x:c r="E40" s="31"/>
+      <x:c r="F40" s="31"/>
+      <x:c r="G40" s="31"/>
+      <x:c r="H40" s="31"/>
+      <x:c r="I40" s="31"/>
+      <x:c r="J40" s="31"/>
+      <x:c r="K40" s="31"/>
+      <x:c r="L40" s="31"/>
+      <x:c r="M40" s="31"/>
+      <x:c r="N40" s="31"/>
+      <x:c r="O40" s="31"/>
+      <x:c r="P40" s="31"/>
+      <x:c r="Q40" s="31"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="31"/>
+      <x:c r="B41" s="31"/>
+      <x:c r="C41" s="31"/>
+      <x:c r="D41" s="31"/>
+      <x:c r="E41" s="31"/>
+      <x:c r="F41" s="31"/>
+      <x:c r="G41" s="31"/>
+      <x:c r="H41" s="31"/>
+      <x:c r="I41" s="31"/>
+      <x:c r="J41" s="31"/>
+      <x:c r="K41" s="31"/>
+      <x:c r="L41" s="31"/>
+      <x:c r="M41" s="31"/>
+      <x:c r="N41" s="31"/>
+      <x:c r="O41" s="31"/>
+      <x:c r="P41" s="31"/>
+      <x:c r="Q41" s="31"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="31"/>
+      <x:c r="B42" s="31"/>
+      <x:c r="C42" s="31"/>
+      <x:c r="D42" s="31"/>
+      <x:c r="E42" s="31"/>
+      <x:c r="F42" s="31"/>
+      <x:c r="G42" s="31"/>
+      <x:c r="H42" s="31"/>
+      <x:c r="I42" s="31"/>
+      <x:c r="J42" s="31"/>
+      <x:c r="K42" s="31"/>
+      <x:c r="L42" s="31"/>
+      <x:c r="M42" s="31"/>
+      <x:c r="N42" s="31"/>
+      <x:c r="O42" s="31"/>
+      <x:c r="P42" s="31"/>
+      <x:c r="Q42" s="31"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="31"/>
+      <x:c r="B43" s="31"/>
+      <x:c r="C43" s="31"/>
+      <x:c r="D43" s="31"/>
+      <x:c r="E43" s="31"/>
+      <x:c r="F43" s="31"/>
+      <x:c r="G43" s="31"/>
+      <x:c r="H43" s="31"/>
+      <x:c r="I43" s="31"/>
+      <x:c r="J43" s="31"/>
+      <x:c r="K43" s="31"/>
+      <x:c r="L43" s="31"/>
+      <x:c r="M43" s="31"/>
+      <x:c r="N43" s="31"/>
+      <x:c r="O43" s="31"/>
+      <x:c r="P43" s="31"/>
+      <x:c r="Q43" s="31"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="31"/>
+      <x:c r="B44" s="31"/>
+      <x:c r="C44" s="31"/>
+      <x:c r="D44" s="31"/>
+      <x:c r="E44" s="31"/>
+      <x:c r="F44" s="31"/>
+      <x:c r="G44" s="31"/>
+      <x:c r="H44" s="31"/>
+      <x:c r="I44" s="31"/>
+      <x:c r="J44" s="31"/>
+      <x:c r="K44" s="31"/>
+      <x:c r="L44" s="31"/>
+      <x:c r="M44" s="31"/>
+      <x:c r="N44" s="31"/>
+      <x:c r="O44" s="31"/>
+      <x:c r="P44" s="31"/>
+      <x:c r="Q44" s="31"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="31"/>
+      <x:c r="B45" s="31"/>
+      <x:c r="C45" s="31"/>
+      <x:c r="D45" s="31"/>
+      <x:c r="E45" s="31"/>
+      <x:c r="F45" s="31"/>
+      <x:c r="G45" s="31"/>
+      <x:c r="H45" s="31"/>
+      <x:c r="I45" s="31"/>
+      <x:c r="J45" s="31"/>
+      <x:c r="K45" s="31"/>
+      <x:c r="L45" s="31"/>
+      <x:c r="M45" s="31"/>
+      <x:c r="N45" s="31"/>
+      <x:c r="O45" s="31"/>
+      <x:c r="P45" s="31"/>
+      <x:c r="Q45" s="31"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="31"/>
+      <x:c r="B46" s="31"/>
+      <x:c r="C46" s="31"/>
+      <x:c r="D46" s="31"/>
+      <x:c r="E46" s="31"/>
+      <x:c r="F46" s="31"/>
+      <x:c r="G46" s="31"/>
+      <x:c r="H46" s="31"/>
+      <x:c r="I46" s="31"/>
+      <x:c r="J46" s="31"/>
+      <x:c r="K46" s="31"/>
+      <x:c r="L46" s="31"/>
+      <x:c r="M46" s="31"/>
+      <x:c r="N46" s="31"/>
+      <x:c r="O46" s="31"/>
+      <x:c r="P46" s="31"/>
+      <x:c r="Q46" s="31"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="31"/>
+      <x:c r="B47" s="31"/>
+      <x:c r="C47" s="31"/>
+      <x:c r="D47" s="31"/>
+      <x:c r="E47" s="31"/>
+      <x:c r="F47" s="31"/>
+      <x:c r="G47" s="31"/>
+      <x:c r="H47" s="31"/>
+      <x:c r="I47" s="31"/>
+      <x:c r="J47" s="31"/>
+      <x:c r="K47" s="31"/>
+      <x:c r="L47" s="31"/>
+      <x:c r="M47" s="31"/>
+      <x:c r="N47" s="31"/>
+      <x:c r="O47" s="31"/>
+      <x:c r="P47" s="31"/>
+      <x:c r="Q47" s="31"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="31"/>
+      <x:c r="B48" s="31"/>
+      <x:c r="C48" s="31"/>
+      <x:c r="D48" s="31"/>
+      <x:c r="E48" s="31"/>
+      <x:c r="F48" s="31"/>
+      <x:c r="G48" s="31"/>
+      <x:c r="H48" s="31"/>
+      <x:c r="I48" s="31"/>
+      <x:c r="J48" s="31"/>
+      <x:c r="K48" s="31"/>
+      <x:c r="L48" s="31"/>
+      <x:c r="M48" s="31"/>
+      <x:c r="N48" s="31"/>
+      <x:c r="O48" s="31"/>
+      <x:c r="P48" s="31"/>
+      <x:c r="Q48" s="31"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="31"/>
+      <x:c r="B49" s="31"/>
+      <x:c r="C49" s="31"/>
+      <x:c r="D49" s="31"/>
+      <x:c r="E49" s="31"/>
+      <x:c r="F49" s="31"/>
+      <x:c r="G49" s="31"/>
+      <x:c r="H49" s="31"/>
+      <x:c r="I49" s="31"/>
+      <x:c r="J49" s="31"/>
+      <x:c r="K49" s="31"/>
+      <x:c r="L49" s="31"/>
+      <x:c r="M49" s="31"/>
+      <x:c r="N49" s="31"/>
+      <x:c r="O49" s="31"/>
+      <x:c r="P49" s="31"/>
+      <x:c r="Q49" s="31"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="31"/>
+      <x:c r="B50" s="31"/>
+      <x:c r="C50" s="31"/>
+      <x:c r="D50" s="31"/>
+      <x:c r="E50" s="31"/>
+      <x:c r="F50" s="31"/>
+      <x:c r="G50" s="31"/>
+      <x:c r="H50" s="31"/>
+      <x:c r="I50" s="31"/>
+      <x:c r="J50" s="31"/>
+      <x:c r="K50" s="31"/>
+      <x:c r="L50" s="31"/>
+      <x:c r="M50" s="31"/>
+      <x:c r="N50" s="31"/>
+      <x:c r="O50" s="31"/>
+      <x:c r="P50" s="31"/>
+      <x:c r="Q50" s="31"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="31"/>
+      <x:c r="B51" s="31"/>
+      <x:c r="C51" s="31"/>
+      <x:c r="D51" s="31"/>
+      <x:c r="E51" s="31"/>
+      <x:c r="F51" s="31"/>
+      <x:c r="G51" s="31"/>
+      <x:c r="H51" s="31"/>
+      <x:c r="I51" s="31"/>
+      <x:c r="J51" s="31"/>
+      <x:c r="K51" s="31"/>
+      <x:c r="L51" s="31"/>
+      <x:c r="M51" s="31"/>
+      <x:c r="N51" s="31"/>
+      <x:c r="O51" s="31"/>
+      <x:c r="P51" s="31"/>
+      <x:c r="Q51" s="31"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="31"/>
+      <x:c r="B52" s="31"/>
+      <x:c r="C52" s="31"/>
+      <x:c r="D52" s="31"/>
+      <x:c r="E52" s="31"/>
+      <x:c r="F52" s="31"/>
+      <x:c r="G52" s="31"/>
+      <x:c r="H52" s="31"/>
+      <x:c r="I52" s="31"/>
+      <x:c r="J52" s="31"/>
+      <x:c r="K52" s="31"/>
+      <x:c r="L52" s="31"/>
+      <x:c r="M52" s="31"/>
+      <x:c r="N52" s="31"/>
+      <x:c r="O52" s="31"/>
+      <x:c r="P52" s="31"/>
+      <x:c r="Q52" s="31"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="31"/>
+      <x:c r="B53" s="31"/>
+      <x:c r="C53" s="31"/>
+      <x:c r="D53" s="31"/>
+      <x:c r="E53" s="31"/>
+      <x:c r="F53" s="31"/>
+      <x:c r="G53" s="31"/>
+      <x:c r="H53" s="31"/>
+      <x:c r="I53" s="31"/>
+      <x:c r="J53" s="31"/>
+      <x:c r="K53" s="31"/>
+      <x:c r="L53" s="31"/>
+      <x:c r="M53" s="31"/>
+      <x:c r="N53" s="31"/>
+      <x:c r="O53" s="31"/>
+      <x:c r="P53" s="31"/>
+      <x:c r="Q53" s="31"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="31"/>
+      <x:c r="B54" s="31"/>
+      <x:c r="C54" s="31"/>
+      <x:c r="D54" s="31"/>
+      <x:c r="E54" s="31"/>
+      <x:c r="F54" s="31"/>
+      <x:c r="G54" s="31"/>
+      <x:c r="H54" s="31"/>
+      <x:c r="I54" s="31"/>
+      <x:c r="J54" s="31"/>
+      <x:c r="K54" s="31"/>
+      <x:c r="L54" s="31"/>
+      <x:c r="M54" s="31"/>
+      <x:c r="N54" s="31"/>
+      <x:c r="O54" s="31"/>
+      <x:c r="P54" s="31"/>
+      <x:c r="Q54" s="31"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="31"/>
+      <x:c r="B55" s="31"/>
+      <x:c r="C55" s="31"/>
+      <x:c r="D55" s="31"/>
+      <x:c r="E55" s="31"/>
+      <x:c r="F55" s="31"/>
+      <x:c r="G55" s="31"/>
+      <x:c r="H55" s="31"/>
+      <x:c r="I55" s="31"/>
+      <x:c r="J55" s="31"/>
+      <x:c r="K55" s="31"/>
+      <x:c r="L55" s="31"/>
+      <x:c r="M55" s="31"/>
+      <x:c r="N55" s="31"/>
+      <x:c r="O55" s="31"/>
+      <x:c r="P55" s="31"/>
+      <x:c r="Q55" s="31"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="31"/>
+      <x:c r="B56" s="31"/>
+      <x:c r="C56" s="31"/>
+      <x:c r="D56" s="31"/>
+      <x:c r="E56" s="31"/>
+      <x:c r="F56" s="31"/>
+      <x:c r="G56" s="31"/>
+      <x:c r="H56" s="31"/>
+      <x:c r="I56" s="31"/>
+      <x:c r="J56" s="31"/>
+      <x:c r="K56" s="31"/>
+      <x:c r="L56" s="31"/>
+      <x:c r="M56" s="31"/>
+      <x:c r="N56" s="31"/>
+      <x:c r="O56" s="31"/>
+      <x:c r="P56" s="31"/>
+      <x:c r="Q56" s="31"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="31"/>
+      <x:c r="B57" s="31"/>
+      <x:c r="C57" s="31"/>
+      <x:c r="D57" s="31"/>
+      <x:c r="E57" s="31"/>
+      <x:c r="F57" s="31"/>
+      <x:c r="G57" s="31"/>
+      <x:c r="H57" s="31"/>
+      <x:c r="I57" s="31"/>
+      <x:c r="J57" s="31"/>
+      <x:c r="K57" s="31"/>
+      <x:c r="L57" s="31"/>
+      <x:c r="M57" s="31"/>
+      <x:c r="N57" s="31"/>
+      <x:c r="O57" s="31"/>
+      <x:c r="P57" s="31"/>
+      <x:c r="Q57" s="31"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="31"/>
+      <x:c r="B58" s="31"/>
+      <x:c r="C58" s="31"/>
+      <x:c r="D58" s="31"/>
+      <x:c r="E58" s="31"/>
+      <x:c r="F58" s="31"/>
+      <x:c r="G58" s="31"/>
+      <x:c r="H58" s="31"/>
+      <x:c r="I58" s="31"/>
+      <x:c r="J58" s="31"/>
+      <x:c r="K58" s="31"/>
+      <x:c r="L58" s="31"/>
+      <x:c r="M58" s="31"/>
+      <x:c r="N58" s="31"/>
+      <x:c r="O58" s="31"/>
+      <x:c r="P58" s="31"/>
+      <x:c r="Q58" s="31"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="31"/>
+      <x:c r="B59" s="31"/>
+      <x:c r="C59" s="31"/>
+      <x:c r="D59" s="31"/>
+      <x:c r="E59" s="31"/>
+      <x:c r="F59" s="31"/>
+      <x:c r="G59" s="31"/>
+      <x:c r="H59" s="31"/>
+      <x:c r="I59" s="31"/>
+      <x:c r="J59" s="31"/>
+      <x:c r="K59" s="31"/>
+      <x:c r="L59" s="31"/>
+      <x:c r="M59" s="31"/>
+      <x:c r="N59" s="31"/>
+      <x:c r="O59" s="31"/>
+      <x:c r="P59" s="31"/>
+      <x:c r="Q59" s="31"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="31"/>
+      <x:c r="B60" s="31"/>
+      <x:c r="C60" s="31"/>
+      <x:c r="D60" s="31"/>
+      <x:c r="E60" s="31"/>
+      <x:c r="F60" s="31"/>
+      <x:c r="G60" s="31"/>
+      <x:c r="H60" s="31"/>
+      <x:c r="I60" s="31"/>
+      <x:c r="J60" s="31"/>
+      <x:c r="K60" s="31"/>
+      <x:c r="L60" s="31"/>
+      <x:c r="M60" s="31"/>
+      <x:c r="N60" s="31"/>
+      <x:c r="O60" s="31"/>
+      <x:c r="P60" s="31"/>
+      <x:c r="Q60" s="31"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="31"/>
+      <x:c r="B61" s="31"/>
+      <x:c r="C61" s="31"/>
+      <x:c r="D61" s="31"/>
+      <x:c r="E61" s="31"/>
+      <x:c r="F61" s="31"/>
+      <x:c r="G61" s="31"/>
+      <x:c r="H61" s="31"/>
+      <x:c r="I61" s="31"/>
+      <x:c r="J61" s="31"/>
+      <x:c r="K61" s="31"/>
+      <x:c r="L61" s="31"/>
+      <x:c r="M61" s="31"/>
+      <x:c r="N61" s="31"/>
+      <x:c r="O61" s="31"/>
+      <x:c r="P61" s="31"/>
+      <x:c r="Q61" s="31"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="31"/>
+      <x:c r="B62" s="31"/>
+      <x:c r="C62" s="31"/>
+      <x:c r="D62" s="31"/>
+      <x:c r="E62" s="31"/>
+      <x:c r="F62" s="31"/>
+      <x:c r="G62" s="31"/>
+      <x:c r="H62" s="31"/>
+      <x:c r="I62" s="31"/>
+      <x:c r="J62" s="31"/>
+      <x:c r="K62" s="31"/>
+      <x:c r="L62" s="31"/>
+      <x:c r="M62" s="31"/>
+      <x:c r="N62" s="31"/>
+      <x:c r="O62" s="31"/>
+      <x:c r="P62" s="31"/>
+      <x:c r="Q62" s="31"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="31"/>
+      <x:c r="B63" s="31"/>
+      <x:c r="C63" s="31"/>
+      <x:c r="D63" s="31"/>
+      <x:c r="E63" s="31"/>
+      <x:c r="F63" s="31"/>
+      <x:c r="G63" s="31"/>
+      <x:c r="H63" s="31"/>
+      <x:c r="I63" s="31"/>
+      <x:c r="J63" s="31"/>
+      <x:c r="K63" s="31"/>
+      <x:c r="L63" s="31"/>
+      <x:c r="M63" s="31"/>
+      <x:c r="N63" s="31"/>
+      <x:c r="O63" s="31"/>
+      <x:c r="P63" s="31"/>
+      <x:c r="Q63" s="31"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="31"/>
+      <x:c r="B64" s="31"/>
+      <x:c r="C64" s="31"/>
+      <x:c r="D64" s="31"/>
+      <x:c r="E64" s="31"/>
+      <x:c r="F64" s="31"/>
+      <x:c r="G64" s="31"/>
+      <x:c r="H64" s="31"/>
+      <x:c r="I64" s="31"/>
+      <x:c r="J64" s="31"/>
+      <x:c r="K64" s="31"/>
+      <x:c r="L64" s="31"/>
+      <x:c r="M64" s="31"/>
+      <x:c r="N64" s="31"/>
+      <x:c r="O64" s="31"/>
+      <x:c r="P64" s="31"/>
+      <x:c r="Q64" s="31"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="31"/>
+      <x:c r="B65" s="31"/>
+      <x:c r="C65" s="31"/>
+      <x:c r="D65" s="31"/>
+      <x:c r="E65" s="31"/>
+      <x:c r="F65" s="31"/>
+      <x:c r="G65" s="31"/>
+      <x:c r="H65" s="31"/>
+      <x:c r="I65" s="31"/>
+      <x:c r="J65" s="31"/>
+      <x:c r="K65" s="31"/>
+      <x:c r="L65" s="31"/>
+      <x:c r="M65" s="31"/>
+      <x:c r="N65" s="31"/>
+      <x:c r="O65" s="31"/>
+      <x:c r="P65" s="31"/>
+      <x:c r="Q65" s="31"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="31"/>
+      <x:c r="B66" s="31"/>
+      <x:c r="C66" s="31"/>
+      <x:c r="D66" s="31"/>
+      <x:c r="E66" s="31"/>
+      <x:c r="F66" s="31"/>
+      <x:c r="G66" s="31"/>
+      <x:c r="H66" s="31"/>
+      <x:c r="I66" s="31"/>
+      <x:c r="J66" s="31"/>
+      <x:c r="K66" s="31"/>
+      <x:c r="L66" s="31"/>
+      <x:c r="M66" s="31"/>
+      <x:c r="N66" s="31"/>
+      <x:c r="O66" s="31"/>
+      <x:c r="P66" s="31"/>
+      <x:c r="Q66" s="31"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="31"/>
+      <x:c r="B67" s="31"/>
+      <x:c r="C67" s="31"/>
+      <x:c r="D67" s="31"/>
+      <x:c r="E67" s="31"/>
+      <x:c r="F67" s="31"/>
+      <x:c r="G67" s="31"/>
+      <x:c r="H67" s="31"/>
+      <x:c r="I67" s="31"/>
+      <x:c r="J67" s="31"/>
+      <x:c r="K67" s="31"/>
+      <x:c r="L67" s="31"/>
+      <x:c r="M67" s="31"/>
+      <x:c r="N67" s="31"/>
+      <x:c r="O67" s="31"/>
+      <x:c r="P67" s="31"/>
+      <x:c r="Q67" s="31"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="31"/>
+      <x:c r="B68" s="31"/>
+      <x:c r="C68" s="31"/>
+      <x:c r="D68" s="31"/>
+      <x:c r="E68" s="31"/>
+      <x:c r="F68" s="31"/>
+      <x:c r="G68" s="31"/>
+      <x:c r="H68" s="31"/>
+      <x:c r="I68" s="31"/>
+      <x:c r="J68" s="31"/>
+      <x:c r="K68" s="31"/>
+      <x:c r="L68" s="31"/>
+      <x:c r="M68" s="31"/>
+      <x:c r="N68" s="31"/>
+      <x:c r="O68" s="31"/>
+      <x:c r="P68" s="31"/>
+      <x:c r="Q68" s="31"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="31"/>
+      <x:c r="B69" s="31"/>
+      <x:c r="C69" s="31"/>
+      <x:c r="D69" s="31"/>
+      <x:c r="E69" s="31"/>
+      <x:c r="F69" s="31"/>
+      <x:c r="G69" s="31"/>
+      <x:c r="H69" s="31"/>
+      <x:c r="I69" s="31"/>
+      <x:c r="J69" s="31"/>
+      <x:c r="K69" s="31"/>
+      <x:c r="L69" s="31"/>
+      <x:c r="M69" s="31"/>
+      <x:c r="N69" s="31"/>
+      <x:c r="O69" s="31"/>
+      <x:c r="P69" s="31"/>
+      <x:c r="Q69" s="31"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="31"/>
+      <x:c r="B70" s="31"/>
+      <x:c r="C70" s="31"/>
+      <x:c r="D70" s="31"/>
+      <x:c r="E70" s="31"/>
+      <x:c r="F70" s="31"/>
+      <x:c r="G70" s="31"/>
+      <x:c r="H70" s="31"/>
+      <x:c r="I70" s="31"/>
+      <x:c r="J70" s="31"/>
+      <x:c r="K70" s="31"/>
+      <x:c r="L70" s="31"/>
+      <x:c r="M70" s="31"/>
+      <x:c r="N70" s="31"/>
+      <x:c r="O70" s="31"/>
+      <x:c r="P70" s="31"/>
+      <x:c r="Q70" s="31"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="31"/>
+      <x:c r="B71" s="31"/>
+      <x:c r="C71" s="31"/>
+      <x:c r="D71" s="31"/>
+      <x:c r="E71" s="31"/>
+      <x:c r="F71" s="31"/>
+      <x:c r="G71" s="31"/>
+      <x:c r="H71" s="31"/>
+      <x:c r="I71" s="31"/>
+      <x:c r="J71" s="31"/>
+      <x:c r="K71" s="31"/>
+      <x:c r="L71" s="31"/>
+      <x:c r="M71" s="31"/>
+      <x:c r="N71" s="31"/>
+      <x:c r="O71" s="31"/>
+      <x:c r="P71" s="31"/>
+      <x:c r="Q71" s="31"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="31"/>
+      <x:c r="B72" s="31"/>
+      <x:c r="C72" s="31"/>
+      <x:c r="D72" s="31"/>
+      <x:c r="E72" s="31"/>
+      <x:c r="F72" s="31"/>
+      <x:c r="G72" s="31"/>
+      <x:c r="H72" s="31"/>
+      <x:c r="I72" s="31"/>
+      <x:c r="J72" s="31"/>
+      <x:c r="K72" s="31"/>
+      <x:c r="L72" s="31"/>
+      <x:c r="M72" s="31"/>
+      <x:c r="N72" s="31"/>
+      <x:c r="O72" s="31"/>
+      <x:c r="P72" s="31"/>
+      <x:c r="Q72" s="31"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="31"/>
+      <x:c r="B73" s="31"/>
+      <x:c r="C73" s="31"/>
+      <x:c r="D73" s="31"/>
+      <x:c r="E73" s="31"/>
+      <x:c r="F73" s="31"/>
+      <x:c r="G73" s="31"/>
+      <x:c r="H73" s="31"/>
+      <x:c r="I73" s="31"/>
+      <x:c r="J73" s="31"/>
+      <x:c r="K73" s="31"/>
+      <x:c r="L73" s="31"/>
+      <x:c r="M73" s="31"/>
+      <x:c r="N73" s="31"/>
+      <x:c r="O73" s="31"/>
+      <x:c r="P73" s="31"/>
+      <x:c r="Q73" s="31"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="31"/>
+      <x:c r="B74" s="31"/>
+      <x:c r="C74" s="31"/>
+      <x:c r="D74" s="31"/>
+      <x:c r="E74" s="31"/>
+      <x:c r="F74" s="31"/>
+      <x:c r="G74" s="31"/>
+      <x:c r="H74" s="31"/>
+      <x:c r="I74" s="31"/>
+      <x:c r="J74" s="31"/>
+      <x:c r="K74" s="31"/>
+      <x:c r="L74" s="31"/>
+      <x:c r="M74" s="31"/>
+      <x:c r="N74" s="31"/>
+      <x:c r="O74" s="31"/>
+      <x:c r="P74" s="31"/>
+      <x:c r="Q74" s="31"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="31"/>
+      <x:c r="B75" s="31"/>
+      <x:c r="C75" s="31"/>
+      <x:c r="D75" s="31"/>
+      <x:c r="E75" s="31"/>
+      <x:c r="F75" s="31"/>
+      <x:c r="G75" s="31"/>
+      <x:c r="H75" s="31"/>
+      <x:c r="I75" s="31"/>
+      <x:c r="J75" s="31"/>
+      <x:c r="K75" s="31"/>
+      <x:c r="L75" s="31"/>
+      <x:c r="M75" s="31"/>
+      <x:c r="N75" s="31"/>
+      <x:c r="O75" s="31"/>
+      <x:c r="P75" s="31"/>
+      <x:c r="Q75" s="31"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="31"/>
+      <x:c r="B76" s="31"/>
+      <x:c r="C76" s="31"/>
+      <x:c r="D76" s="31"/>
+      <x:c r="E76" s="31"/>
+      <x:c r="F76" s="31"/>
+      <x:c r="G76" s="31"/>
+      <x:c r="H76" s="31"/>
+      <x:c r="I76" s="31"/>
+      <x:c r="J76" s="31"/>
+      <x:c r="K76" s="31"/>
+      <x:c r="L76" s="31"/>
+      <x:c r="M76" s="31"/>
+      <x:c r="N76" s="31"/>
+      <x:c r="O76" s="31"/>
+      <x:c r="P76" s="31"/>
+      <x:c r="Q76" s="31"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="31"/>
+      <x:c r="B77" s="31"/>
+      <x:c r="C77" s="31"/>
+      <x:c r="D77" s="31"/>
+      <x:c r="E77" s="31"/>
+      <x:c r="F77" s="31"/>
+      <x:c r="G77" s="31"/>
+      <x:c r="H77" s="31"/>
+      <x:c r="I77" s="31"/>
+      <x:c r="J77" s="31"/>
+      <x:c r="K77" s="31"/>
+      <x:c r="L77" s="31"/>
+      <x:c r="M77" s="31"/>
+      <x:c r="N77" s="31"/>
+      <x:c r="O77" s="31"/>
+      <x:c r="P77" s="31"/>
+      <x:c r="Q77" s="31"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="31"/>
+      <x:c r="B78" s="31"/>
+      <x:c r="C78" s="31"/>
+      <x:c r="D78" s="31"/>
+      <x:c r="E78" s="31"/>
+      <x:c r="F78" s="31"/>
+      <x:c r="G78" s="31"/>
+      <x:c r="H78" s="31"/>
+      <x:c r="I78" s="31"/>
+      <x:c r="J78" s="31"/>
+      <x:c r="K78" s="31"/>
+      <x:c r="L78" s="31"/>
+      <x:c r="M78" s="31"/>
+      <x:c r="N78" s="31"/>
+      <x:c r="O78" s="31"/>
+      <x:c r="P78" s="31"/>
+      <x:c r="Q78" s="31"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="31"/>
+      <x:c r="B79" s="31"/>
+      <x:c r="C79" s="31"/>
+      <x:c r="D79" s="31"/>
+      <x:c r="E79" s="31"/>
+      <x:c r="F79" s="31"/>
+      <x:c r="G79" s="31"/>
+      <x:c r="H79" s="31"/>
+      <x:c r="I79" s="31"/>
+      <x:c r="J79" s="31"/>
+      <x:c r="K79" s="31"/>
+      <x:c r="L79" s="31"/>
+      <x:c r="M79" s="31"/>
+      <x:c r="N79" s="31"/>
+      <x:c r="O79" s="31"/>
+      <x:c r="P79" s="31"/>
+      <x:c r="Q79" s="31"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="31"/>
+      <x:c r="B80" s="31"/>
+      <x:c r="C80" s="31"/>
+      <x:c r="D80" s="31"/>
+      <x:c r="E80" s="31"/>
+      <x:c r="F80" s="31"/>
+      <x:c r="G80" s="31"/>
+      <x:c r="H80" s="31"/>
+      <x:c r="I80" s="31"/>
+      <x:c r="J80" s="31"/>
+      <x:c r="K80" s="31"/>
+      <x:c r="L80" s="31"/>
+      <x:c r="M80" s="31"/>
+      <x:c r="N80" s="31"/>
+      <x:c r="O80" s="31"/>
+      <x:c r="P80" s="31"/>
+      <x:c r="Q80" s="31"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="31"/>
+      <x:c r="B81" s="31"/>
+      <x:c r="C81" s="31"/>
+      <x:c r="D81" s="31"/>
+      <x:c r="E81" s="31"/>
+      <x:c r="F81" s="31"/>
+      <x:c r="G81" s="31"/>
+      <x:c r="H81" s="31"/>
+      <x:c r="I81" s="31"/>
+      <x:c r="J81" s="31"/>
+      <x:c r="K81" s="31"/>
+      <x:c r="L81" s="31"/>
+      <x:c r="M81" s="31"/>
+      <x:c r="N81" s="31"/>
+      <x:c r="O81" s="31"/>
+      <x:c r="P81" s="31"/>
+      <x:c r="Q81" s="31"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="31"/>
+      <x:c r="B82" s="31"/>
+      <x:c r="C82" s="31"/>
+      <x:c r="D82" s="31"/>
+      <x:c r="E82" s="31"/>
+      <x:c r="F82" s="31"/>
+      <x:c r="G82" s="31"/>
+      <x:c r="H82" s="31"/>
+      <x:c r="I82" s="31"/>
+      <x:c r="J82" s="31"/>
+      <x:c r="K82" s="31"/>
+      <x:c r="L82" s="31"/>
+      <x:c r="M82" s="31"/>
+      <x:c r="N82" s="31"/>
+      <x:c r="O82" s="31"/>
+      <x:c r="P82" s="31"/>
+      <x:c r="Q82" s="31"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="31"/>
+      <x:c r="B83" s="31"/>
+      <x:c r="C83" s="31"/>
+      <x:c r="D83" s="31"/>
+      <x:c r="E83" s="31"/>
+      <x:c r="F83" s="31"/>
+      <x:c r="G83" s="31"/>
+      <x:c r="H83" s="31"/>
+      <x:c r="I83" s="31"/>
+      <x:c r="J83" s="31"/>
+      <x:c r="K83" s="31"/>
+      <x:c r="L83" s="31"/>
+      <x:c r="M83" s="31"/>
+      <x:c r="N83" s="31"/>
+      <x:c r="O83" s="31"/>
+      <x:c r="P83" s="31"/>
+      <x:c r="Q83" s="31"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="31"/>
+      <x:c r="B84" s="31"/>
+      <x:c r="C84" s="31"/>
+      <x:c r="D84" s="31"/>
+      <x:c r="E84" s="31"/>
+      <x:c r="F84" s="31"/>
+      <x:c r="G84" s="31"/>
+      <x:c r="H84" s="31"/>
+      <x:c r="I84" s="31"/>
+      <x:c r="J84" s="31"/>
+      <x:c r="K84" s="31"/>
+      <x:c r="L84" s="31"/>
+      <x:c r="M84" s="31"/>
+      <x:c r="N84" s="31"/>
+      <x:c r="O84" s="31"/>
+      <x:c r="P84" s="31"/>
+      <x:c r="Q84" s="31"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="31"/>
+      <x:c r="B85" s="31"/>
+      <x:c r="C85" s="31"/>
+      <x:c r="D85" s="31"/>
+      <x:c r="E85" s="31"/>
+      <x:c r="F85" s="31"/>
+      <x:c r="G85" s="31"/>
+      <x:c r="H85" s="31"/>
+      <x:c r="I85" s="31"/>
+      <x:c r="J85" s="31"/>
+      <x:c r="K85" s="31"/>
+      <x:c r="L85" s="31"/>
+      <x:c r="M85" s="31"/>
+      <x:c r="N85" s="31"/>
+      <x:c r="O85" s="31"/>
+      <x:c r="P85" s="31"/>
+      <x:c r="Q85" s="31"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="31"/>
+      <x:c r="B86" s="31"/>
+      <x:c r="C86" s="31"/>
+      <x:c r="D86" s="31"/>
+      <x:c r="E86" s="31"/>
+      <x:c r="F86" s="31"/>
+      <x:c r="G86" s="31"/>
+      <x:c r="H86" s="31"/>
+      <x:c r="I86" s="31"/>
+      <x:c r="J86" s="31"/>
+      <x:c r="K86" s="31"/>
+      <x:c r="L86" s="31"/>
+      <x:c r="M86" s="31"/>
+      <x:c r="N86" s="31"/>
+      <x:c r="O86" s="31"/>
+      <x:c r="P86" s="31"/>
+      <x:c r="Q86" s="31"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="31"/>
+      <x:c r="B87" s="31"/>
+      <x:c r="C87" s="31"/>
+      <x:c r="D87" s="31"/>
+      <x:c r="E87" s="31"/>
+      <x:c r="F87" s="31"/>
+      <x:c r="G87" s="31"/>
+      <x:c r="H87" s="31"/>
+      <x:c r="I87" s="31"/>
+      <x:c r="J87" s="31"/>
+      <x:c r="K87" s="31"/>
+      <x:c r="L87" s="31"/>
+      <x:c r="M87" s="31"/>
+      <x:c r="N87" s="31"/>
+      <x:c r="O87" s="31"/>
+      <x:c r="P87" s="31"/>
+      <x:c r="Q87" s="31"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="31"/>
+      <x:c r="B88" s="31"/>
+      <x:c r="C88" s="31"/>
+      <x:c r="D88" s="31"/>
+      <x:c r="E88" s="31"/>
+      <x:c r="F88" s="31"/>
+      <x:c r="G88" s="31"/>
+      <x:c r="H88" s="31"/>
+      <x:c r="I88" s="31"/>
+      <x:c r="J88" s="31"/>
+      <x:c r="K88" s="31"/>
+      <x:c r="L88" s="31"/>
+      <x:c r="M88" s="31"/>
+      <x:c r="N88" s="31"/>
+      <x:c r="O88" s="31"/>
+      <x:c r="P88" s="31"/>
+      <x:c r="Q88" s="31"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="31"/>
+      <x:c r="B89" s="31"/>
+      <x:c r="C89" s="31"/>
+      <x:c r="D89" s="31"/>
+      <x:c r="E89" s="31"/>
+      <x:c r="F89" s="31"/>
+      <x:c r="G89" s="31"/>
+      <x:c r="H89" s="31"/>
+      <x:c r="I89" s="31"/>
+      <x:c r="J89" s="31"/>
+      <x:c r="K89" s="31"/>
+      <x:c r="L89" s="31"/>
+      <x:c r="M89" s="31"/>
+      <x:c r="N89" s="31"/>
+      <x:c r="O89" s="31"/>
+      <x:c r="P89" s="31"/>
+      <x:c r="Q89" s="31"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="31"/>
+      <x:c r="B90" s="31"/>
+      <x:c r="C90" s="31"/>
+      <x:c r="D90" s="31"/>
+      <x:c r="E90" s="31"/>
+      <x:c r="F90" s="31"/>
+      <x:c r="G90" s="31"/>
+      <x:c r="H90" s="31"/>
+      <x:c r="I90" s="31"/>
+      <x:c r="J90" s="31"/>
+      <x:c r="K90" s="31"/>
+      <x:c r="L90" s="31"/>
+      <x:c r="M90" s="31"/>
+      <x:c r="N90" s="31"/>
+      <x:c r="O90" s="31"/>
+      <x:c r="P90" s="31"/>
+      <x:c r="Q90" s="31"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="31"/>
+      <x:c r="B91" s="31"/>
+      <x:c r="C91" s="31"/>
+      <x:c r="D91" s="31"/>
+      <x:c r="E91" s="31"/>
+      <x:c r="F91" s="31"/>
+      <x:c r="G91" s="31"/>
+      <x:c r="H91" s="31"/>
+      <x:c r="I91" s="31"/>
+      <x:c r="J91" s="31"/>
+      <x:c r="K91" s="31"/>
+      <x:c r="L91" s="31"/>
+      <x:c r="M91" s="31"/>
+      <x:c r="N91" s="31"/>
+      <x:c r="O91" s="31"/>
+      <x:c r="P91" s="31"/>
+      <x:c r="Q91" s="31"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="31"/>
+      <x:c r="B92" s="31"/>
+      <x:c r="C92" s="31"/>
+      <x:c r="D92" s="31"/>
+      <x:c r="E92" s="31"/>
+      <x:c r="F92" s="31"/>
+      <x:c r="G92" s="31"/>
+      <x:c r="H92" s="31"/>
+      <x:c r="I92" s="31"/>
+      <x:c r="J92" s="31"/>
+      <x:c r="K92" s="31"/>
+      <x:c r="L92" s="31"/>
+      <x:c r="M92" s="31"/>
+      <x:c r="N92" s="31"/>
+      <x:c r="O92" s="31"/>
+      <x:c r="P92" s="31"/>
+      <x:c r="Q92" s="31"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="31"/>
+      <x:c r="B93" s="31"/>
+      <x:c r="C93" s="31"/>
+      <x:c r="D93" s="31"/>
+      <x:c r="E93" s="31"/>
+      <x:c r="F93" s="31"/>
+      <x:c r="G93" s="31"/>
+      <x:c r="H93" s="31"/>
+      <x:c r="I93" s="31"/>
+      <x:c r="J93" s="31"/>
+      <x:c r="K93" s="31"/>
+      <x:c r="L93" s="31"/>
+      <x:c r="M93" s="31"/>
+      <x:c r="N93" s="31"/>
+      <x:c r="O93" s="31"/>
+      <x:c r="P93" s="31"/>
+      <x:c r="Q93" s="31"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="31"/>
+      <x:c r="B94" s="31"/>
+      <x:c r="C94" s="31"/>
+      <x:c r="D94" s="31"/>
+      <x:c r="E94" s="31"/>
+      <x:c r="F94" s="31"/>
+      <x:c r="G94" s="31"/>
+      <x:c r="H94" s="31"/>
+      <x:c r="I94" s="31"/>
+      <x:c r="J94" s="31"/>
+      <x:c r="K94" s="31"/>
+      <x:c r="L94" s="31"/>
+      <x:c r="M94" s="31"/>
+      <x:c r="N94" s="31"/>
+      <x:c r="O94" s="31"/>
+      <x:c r="P94" s="31"/>
+      <x:c r="Q94" s="31"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="31"/>
+      <x:c r="B95" s="31"/>
+      <x:c r="C95" s="31"/>
+      <x:c r="D95" s="31"/>
+      <x:c r="E95" s="31"/>
+      <x:c r="F95" s="31"/>
+      <x:c r="G95" s="31"/>
+      <x:c r="H95" s="31"/>
+      <x:c r="I95" s="31"/>
+      <x:c r="J95" s="31"/>
+      <x:c r="K95" s="31"/>
+      <x:c r="L95" s="31"/>
+      <x:c r="M95" s="31"/>
+      <x:c r="N95" s="31"/>
+      <x:c r="O95" s="31"/>
+      <x:c r="P95" s="31"/>
+      <x:c r="Q95" s="31"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="31"/>
+      <x:c r="B96" s="31"/>
+      <x:c r="C96" s="31"/>
+      <x:c r="D96" s="31"/>
+      <x:c r="E96" s="31"/>
+      <x:c r="F96" s="31"/>
+      <x:c r="G96" s="31"/>
+      <x:c r="H96" s="31"/>
+      <x:c r="I96" s="31"/>
+      <x:c r="J96" s="31"/>
+      <x:c r="K96" s="31"/>
+      <x:c r="L96" s="31"/>
+      <x:c r="M96" s="31"/>
+      <x:c r="N96" s="31"/>
+      <x:c r="O96" s="31"/>
+      <x:c r="P96" s="31"/>
+      <x:c r="Q96" s="31"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="31"/>
+      <x:c r="B97" s="31"/>
+      <x:c r="C97" s="31"/>
+      <x:c r="D97" s="31"/>
+      <x:c r="E97" s="31"/>
+      <x:c r="F97" s="31"/>
+      <x:c r="G97" s="31"/>
+      <x:c r="H97" s="31"/>
+      <x:c r="I97" s="31"/>
+      <x:c r="J97" s="31"/>
+      <x:c r="K97" s="31"/>
+      <x:c r="L97" s="31"/>
+      <x:c r="M97" s="31"/>
+      <x:c r="N97" s="31"/>
+      <x:c r="O97" s="31"/>
+      <x:c r="P97" s="31"/>
+      <x:c r="Q97" s="31"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="31"/>
+      <x:c r="B98" s="31"/>
+      <x:c r="C98" s="31"/>
+      <x:c r="D98" s="31"/>
+      <x:c r="E98" s="31"/>
+      <x:c r="F98" s="31"/>
+      <x:c r="G98" s="31"/>
+      <x:c r="H98" s="31"/>
+      <x:c r="I98" s="31"/>
+      <x:c r="J98" s="31"/>
+      <x:c r="K98" s="31"/>
+      <x:c r="L98" s="31"/>
+      <x:c r="M98" s="31"/>
+      <x:c r="N98" s="31"/>
+      <x:c r="O98" s="31"/>
+      <x:c r="P98" s="31"/>
+      <x:c r="Q98" s="31"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="31"/>
+      <x:c r="B99" s="31"/>
+      <x:c r="C99" s="31"/>
+      <x:c r="D99" s="31"/>
+      <x:c r="E99" s="31"/>
+      <x:c r="F99" s="31"/>
+      <x:c r="G99" s="31"/>
+      <x:c r="H99" s="31"/>
+      <x:c r="I99" s="31"/>
+      <x:c r="J99" s="31"/>
+      <x:c r="K99" s="31"/>
+      <x:c r="L99" s="31"/>
+      <x:c r="M99" s="31"/>
+      <x:c r="N99" s="31"/>
+      <x:c r="O99" s="31"/>
+      <x:c r="P99" s="31"/>
+      <x:c r="Q99" s="31"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="31"/>
+      <x:c r="B100" s="31"/>
+      <x:c r="C100" s="31"/>
+      <x:c r="D100" s="31"/>
+      <x:c r="E100" s="31"/>
+      <x:c r="F100" s="31"/>
+      <x:c r="G100" s="31"/>
+      <x:c r="H100" s="31"/>
+      <x:c r="I100" s="31"/>
+      <x:c r="J100" s="31"/>
+      <x:c r="K100" s="31"/>
+      <x:c r="L100" s="31"/>
+      <x:c r="M100" s="31"/>
+      <x:c r="N100" s="31"/>
+      <x:c r="O100" s="31"/>
+      <x:c r="P100" s="31"/>
+      <x:c r="Q100" s="31"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="31"/>
+      <x:c r="B101" s="31"/>
+      <x:c r="C101" s="31"/>
+      <x:c r="D101" s="31"/>
+      <x:c r="E101" s="31"/>
+      <x:c r="F101" s="31"/>
+      <x:c r="G101" s="31"/>
+      <x:c r="H101" s="31"/>
+      <x:c r="I101" s="31"/>
+      <x:c r="J101" s="31"/>
+      <x:c r="K101" s="31"/>
+      <x:c r="L101" s="31"/>
+      <x:c r="M101" s="31"/>
+      <x:c r="N101" s="31"/>
+      <x:c r="O101" s="31"/>
+      <x:c r="P101" s="31"/>
+      <x:c r="Q101" s="31"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="31"/>
+      <x:c r="B102" s="31"/>
+      <x:c r="C102" s="31"/>
+      <x:c r="D102" s="31"/>
+      <x:c r="E102" s="31"/>
+      <x:c r="F102" s="31"/>
+      <x:c r="G102" s="31"/>
+      <x:c r="H102" s="31"/>
+      <x:c r="I102" s="31"/>
+      <x:c r="J102" s="31"/>
+      <x:c r="K102" s="31"/>
+      <x:c r="L102" s="31"/>
+      <x:c r="M102" s="31"/>
+      <x:c r="N102" s="31"/>
+      <x:c r="O102" s="31"/>
+      <x:c r="P102" s="31"/>
+      <x:c r="Q102" s="31"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="31"/>
+      <x:c r="B103" s="31"/>
+      <x:c r="C103" s="31"/>
+      <x:c r="D103" s="31"/>
+      <x:c r="E103" s="31"/>
+      <x:c r="F103" s="31"/>
+      <x:c r="G103" s="31"/>
+      <x:c r="H103" s="31"/>
+      <x:c r="I103" s="31"/>
+      <x:c r="J103" s="31"/>
+      <x:c r="K103" s="31"/>
+      <x:c r="L103" s="31"/>
+      <x:c r="M103" s="31"/>
+      <x:c r="N103" s="31"/>
+      <x:c r="O103" s="31"/>
+      <x:c r="P103" s="31"/>
+      <x:c r="Q103" s="31"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="31"/>
+      <x:c r="B104" s="31"/>
+      <x:c r="C104" s="31"/>
+      <x:c r="D104" s="31"/>
+      <x:c r="E104" s="31"/>
+      <x:c r="F104" s="31"/>
+      <x:c r="G104" s="31"/>
+      <x:c r="H104" s="31"/>
+      <x:c r="I104" s="31"/>
+      <x:c r="J104" s="31"/>
+      <x:c r="K104" s="31"/>
+      <x:c r="L104" s="31"/>
+      <x:c r="M104" s="31"/>
+      <x:c r="N104" s="31"/>
+      <x:c r="O104" s="31"/>
+      <x:c r="P104" s="31"/>
+      <x:c r="Q104" s="31"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="31"/>
+      <x:c r="B105" s="31"/>
+      <x:c r="C105" s="31"/>
+      <x:c r="D105" s="31"/>
+      <x:c r="E105" s="31"/>
+      <x:c r="F105" s="31"/>
+      <x:c r="G105" s="31"/>
+      <x:c r="H105" s="31"/>
+      <x:c r="I105" s="31"/>
+      <x:c r="J105" s="31"/>
+      <x:c r="K105" s="31"/>
+      <x:c r="L105" s="31"/>
+      <x:c r="M105" s="31"/>
+      <x:c r="N105" s="31"/>
+      <x:c r="O105" s="31"/>
+      <x:c r="P105" s="31"/>
+      <x:c r="Q105" s="31"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="31"/>
+      <x:c r="B106" s="31"/>
+      <x:c r="C106" s="31"/>
+      <x:c r="D106" s="31"/>
+      <x:c r="E106" s="31"/>
+      <x:c r="F106" s="31"/>
+      <x:c r="G106" s="31"/>
+      <x:c r="H106" s="31"/>
+      <x:c r="I106" s="31"/>
+      <x:c r="J106" s="31"/>
+      <x:c r="K106" s="31"/>
+      <x:c r="L106" s="31"/>
+      <x:c r="M106" s="31"/>
+      <x:c r="N106" s="31"/>
+      <x:c r="O106" s="31"/>
+      <x:c r="P106" s="31"/>
+      <x:c r="Q106" s="31"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="31"/>
+      <x:c r="B107" s="31"/>
+      <x:c r="C107" s="31"/>
+      <x:c r="D107" s="31"/>
+      <x:c r="E107" s="31"/>
+      <x:c r="F107" s="31"/>
+      <x:c r="G107" s="31"/>
+      <x:c r="H107" s="31"/>
+      <x:c r="I107" s="31"/>
+      <x:c r="J107" s="31"/>
+      <x:c r="K107" s="31"/>
+      <x:c r="L107" s="31"/>
+      <x:c r="M107" s="31"/>
+      <x:c r="N107" s="31"/>
+      <x:c r="O107" s="31"/>
+      <x:c r="P107" s="31"/>
+      <x:c r="Q107" s="31"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="31"/>
+      <x:c r="B108" s="31"/>
+      <x:c r="C108" s="31"/>
+      <x:c r="D108" s="31"/>
+      <x:c r="E108" s="31"/>
+      <x:c r="F108" s="31"/>
+      <x:c r="G108" s="31"/>
+      <x:c r="H108" s="31"/>
+      <x:c r="I108" s="31"/>
+      <x:c r="J108" s="31"/>
+      <x:c r="K108" s="31"/>
+      <x:c r="L108" s="31"/>
+      <x:c r="M108" s="31"/>
+      <x:c r="N108" s="31"/>
+      <x:c r="O108" s="31"/>
+      <x:c r="P108" s="31"/>
+      <x:c r="Q108" s="31"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="31"/>
+      <x:c r="B109" s="31"/>
+      <x:c r="C109" s="31"/>
+      <x:c r="D109" s="31"/>
+      <x:c r="E109" s="31"/>
+      <x:c r="F109" s="31"/>
+      <x:c r="G109" s="31"/>
+      <x:c r="H109" s="31"/>
+      <x:c r="I109" s="31"/>
+      <x:c r="J109" s="31"/>
+      <x:c r="K109" s="31"/>
+      <x:c r="L109" s="31"/>
+      <x:c r="M109" s="31"/>
+      <x:c r="N109" s="31"/>
+      <x:c r="O109" s="31"/>
+      <x:c r="P109" s="31"/>
+      <x:c r="Q109" s="31"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="31"/>
+      <x:c r="B110" s="31"/>
+      <x:c r="C110" s="31"/>
+      <x:c r="D110" s="31"/>
+      <x:c r="E110" s="31"/>
+      <x:c r="F110" s="31"/>
+      <x:c r="G110" s="31"/>
+      <x:c r="H110" s="31"/>
+      <x:c r="I110" s="31"/>
+      <x:c r="J110" s="31"/>
+      <x:c r="K110" s="31"/>
+      <x:c r="L110" s="31"/>
+      <x:c r="M110" s="31"/>
+      <x:c r="N110" s="31"/>
+      <x:c r="O110" s="31"/>
+      <x:c r="P110" s="31"/>
+      <x:c r="Q110" s="31"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="31"/>
+      <x:c r="B111" s="31"/>
+      <x:c r="C111" s="31"/>
+      <x:c r="D111" s="31"/>
+      <x:c r="E111" s="31"/>
+      <x:c r="F111" s="31"/>
+      <x:c r="G111" s="31"/>
+      <x:c r="H111" s="31"/>
+      <x:c r="I111" s="31"/>
+      <x:c r="J111" s="31"/>
+      <x:c r="K111" s="31"/>
+      <x:c r="L111" s="31"/>
+      <x:c r="M111" s="31"/>
+      <x:c r="N111" s="31"/>
+      <x:c r="O111" s="31"/>
+      <x:c r="P111" s="31"/>
+      <x:c r="Q111" s="31"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="31"/>
+      <x:c r="B112" s="31"/>
+      <x:c r="C112" s="31"/>
+      <x:c r="D112" s="31"/>
+      <x:c r="E112" s="31"/>
+      <x:c r="F112" s="31"/>
+      <x:c r="G112" s="31"/>
+      <x:c r="H112" s="31"/>
+      <x:c r="I112" s="31"/>
+      <x:c r="J112" s="31"/>
+      <x:c r="K112" s="31"/>
+      <x:c r="L112" s="31"/>
+      <x:c r="M112" s="31"/>
+      <x:c r="N112" s="31"/>
+      <x:c r="O112" s="31"/>
+      <x:c r="P112" s="31"/>
+      <x:c r="Q112" s="31"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="31"/>
+      <x:c r="B113" s="31"/>
+      <x:c r="C113" s="31"/>
+      <x:c r="D113" s="31"/>
+      <x:c r="E113" s="31"/>
+      <x:c r="F113" s="31"/>
+      <x:c r="G113" s="31"/>
+      <x:c r="H113" s="31"/>
+      <x:c r="I113" s="31"/>
+      <x:c r="J113" s="31"/>
+      <x:c r="K113" s="31"/>
+      <x:c r="L113" s="31"/>
+      <x:c r="M113" s="31"/>
+      <x:c r="N113" s="31"/>
+      <x:c r="O113" s="31"/>
+      <x:c r="P113" s="31"/>
+      <x:c r="Q113" s="31"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="31"/>
+      <x:c r="B114" s="31"/>
+      <x:c r="C114" s="31"/>
+      <x:c r="D114" s="31"/>
+      <x:c r="E114" s="31"/>
+      <x:c r="F114" s="31"/>
+      <x:c r="G114" s="31"/>
+      <x:c r="H114" s="31"/>
+      <x:c r="I114" s="31"/>
+      <x:c r="J114" s="31"/>
+      <x:c r="K114" s="31"/>
+      <x:c r="L114" s="31"/>
+      <x:c r="M114" s="31"/>
+      <x:c r="N114" s="31"/>
+      <x:c r="O114" s="31"/>
+      <x:c r="P114" s="31"/>
+      <x:c r="Q114" s="31"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="31"/>
+      <x:c r="B115" s="31"/>
+      <x:c r="C115" s="31"/>
+      <x:c r="D115" s="31"/>
+      <x:c r="E115" s="31"/>
+      <x:c r="F115" s="31"/>
+      <x:c r="G115" s="31"/>
+      <x:c r="H115" s="31"/>
+      <x:c r="I115" s="31"/>
+      <x:c r="J115" s="31"/>
+      <x:c r="K115" s="31"/>
+      <x:c r="L115" s="31"/>
+      <x:c r="M115" s="31"/>
+      <x:c r="N115" s="31"/>
+      <x:c r="O115" s="31"/>
+      <x:c r="P115" s="31"/>
+      <x:c r="Q115" s="31"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="31"/>
+      <x:c r="B116" s="31"/>
+      <x:c r="C116" s="31"/>
+      <x:c r="D116" s="31"/>
+      <x:c r="E116" s="31"/>
+      <x:c r="F116" s="31"/>
+      <x:c r="G116" s="31"/>
+      <x:c r="H116" s="31"/>
+      <x:c r="I116" s="31"/>
+      <x:c r="J116" s="31"/>
+      <x:c r="K116" s="31"/>
+      <x:c r="L116" s="31"/>
+      <x:c r="M116" s="31"/>
+      <x:c r="N116" s="31"/>
+      <x:c r="O116" s="31"/>
+      <x:c r="P116" s="31"/>
+      <x:c r="Q116" s="31"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="31"/>
+      <x:c r="B117" s="31"/>
+      <x:c r="C117" s="31"/>
+      <x:c r="D117" s="31"/>
+      <x:c r="E117" s="31"/>
+      <x:c r="F117" s="31"/>
+      <x:c r="G117" s="31"/>
+      <x:c r="H117" s="31"/>
+      <x:c r="I117" s="31"/>
+      <x:c r="J117" s="31"/>
+      <x:c r="K117" s="31"/>
+      <x:c r="L117" s="31"/>
+      <x:c r="M117" s="31"/>
+      <x:c r="N117" s="31"/>
+      <x:c r="O117" s="31"/>
+      <x:c r="P117" s="31"/>
+      <x:c r="Q117" s="31"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="31"/>
+      <x:c r="B118" s="31"/>
+      <x:c r="C118" s="31"/>
+      <x:c r="D118" s="31"/>
+      <x:c r="E118" s="31"/>
+      <x:c r="F118" s="31"/>
+      <x:c r="G118" s="31"/>
+      <x:c r="H118" s="31"/>
+      <x:c r="I118" s="31"/>
+      <x:c r="J118" s="31"/>
+      <x:c r="K118" s="31"/>
+      <x:c r="L118" s="31"/>
+      <x:c r="M118" s="31"/>
+      <x:c r="N118" s="31"/>
+      <x:c r="O118" s="31"/>
+      <x:c r="P118" s="31"/>
+      <x:c r="Q118" s="31"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="31"/>
+      <x:c r="B119" s="31"/>
+      <x:c r="C119" s="31"/>
+      <x:c r="D119" s="31"/>
+      <x:c r="E119" s="31"/>
+      <x:c r="F119" s="31"/>
+      <x:c r="G119" s="31"/>
+      <x:c r="H119" s="31"/>
+      <x:c r="I119" s="31"/>
+      <x:c r="J119" s="31"/>
+      <x:c r="K119" s="31"/>
+      <x:c r="L119" s="31"/>
+      <x:c r="M119" s="31"/>
+      <x:c r="N119" s="31"/>
+      <x:c r="O119" s="31"/>
+      <x:c r="P119" s="31"/>
+      <x:c r="Q119" s="31"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="31"/>
+      <x:c r="B120" s="31"/>
+      <x:c r="C120" s="31"/>
+      <x:c r="D120" s="31"/>
+      <x:c r="E120" s="31"/>
+      <x:c r="F120" s="31"/>
+      <x:c r="G120" s="31"/>
+      <x:c r="H120" s="31"/>
+      <x:c r="I120" s="31"/>
+      <x:c r="J120" s="31"/>
+      <x:c r="K120" s="31"/>
+      <x:c r="L120" s="31"/>
+      <x:c r="M120" s="31"/>
+      <x:c r="N120" s="31"/>
+      <x:c r="O120" s="31"/>
+      <x:c r="P120" s="31"/>
+      <x:c r="Q120" s="31"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="31"/>
+      <x:c r="B121" s="31"/>
+      <x:c r="C121" s="31"/>
+      <x:c r="D121" s="31"/>
+      <x:c r="E121" s="31"/>
+      <x:c r="F121" s="31"/>
+      <x:c r="G121" s="31"/>
+      <x:c r="H121" s="31"/>
+      <x:c r="I121" s="31"/>
+      <x:c r="J121" s="31"/>
+      <x:c r="K121" s="31"/>
+      <x:c r="L121" s="31"/>
+      <x:c r="M121" s="31"/>
+      <x:c r="N121" s="31"/>
+      <x:c r="O121" s="31"/>
+      <x:c r="P121" s="31"/>
+      <x:c r="Q121" s="31"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="31"/>
+      <x:c r="B122" s="31"/>
+      <x:c r="C122" s="31"/>
+      <x:c r="D122" s="31"/>
+      <x:c r="E122" s="31"/>
+      <x:c r="F122" s="31"/>
+      <x:c r="G122" s="31"/>
+      <x:c r="H122" s="31"/>
+      <x:c r="I122" s="31"/>
+      <x:c r="J122" s="31"/>
+      <x:c r="K122" s="31"/>
+      <x:c r="L122" s="31"/>
+      <x:c r="M122" s="31"/>
+      <x:c r="N122" s="31"/>
+      <x:c r="O122" s="31"/>
+      <x:c r="P122" s="31"/>
+      <x:c r="Q122" s="31"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="31"/>
+      <x:c r="B123" s="31"/>
+      <x:c r="C123" s="31"/>
+      <x:c r="D123" s="31"/>
+      <x:c r="E123" s="31"/>
+      <x:c r="F123" s="31"/>
+      <x:c r="G123" s="31"/>
+      <x:c r="H123" s="31"/>
+      <x:c r="I123" s="31"/>
+      <x:c r="J123" s="31"/>
+      <x:c r="K123" s="31"/>
+      <x:c r="L123" s="31"/>
+      <x:c r="M123" s="31"/>
+      <x:c r="N123" s="31"/>
+      <x:c r="O123" s="31"/>
+      <x:c r="P123" s="31"/>
+      <x:c r="Q123" s="31"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="31"/>
+      <x:c r="B124" s="31"/>
+      <x:c r="C124" s="31"/>
+      <x:c r="D124" s="31"/>
+      <x:c r="E124" s="31"/>
+      <x:c r="F124" s="31"/>
+      <x:c r="G124" s="31"/>
+      <x:c r="H124" s="31"/>
+      <x:c r="I124" s="31"/>
+      <x:c r="J124" s="31"/>
+      <x:c r="K124" s="31"/>
+      <x:c r="L124" s="31"/>
+      <x:c r="M124" s="31"/>
+      <x:c r="N124" s="31"/>
+      <x:c r="O124" s="31"/>
+      <x:c r="P124" s="31"/>
+      <x:c r="Q124" s="31"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="31"/>
+      <x:c r="B125" s="31"/>
+      <x:c r="C125" s="31"/>
+      <x:c r="D125" s="31"/>
+      <x:c r="E125" s="31"/>
+      <x:c r="F125" s="31"/>
+      <x:c r="G125" s="31"/>
+      <x:c r="H125" s="31"/>
+      <x:c r="I125" s="31"/>
+      <x:c r="J125" s="31"/>
+      <x:c r="K125" s="31"/>
+      <x:c r="L125" s="31"/>
+      <x:c r="M125" s="31"/>
+      <x:c r="N125" s="31"/>
+      <x:c r="O125" s="31"/>
+      <x:c r="P125" s="31"/>
+      <x:c r="Q125" s="31"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="31"/>
+      <x:c r="B126" s="31"/>
+      <x:c r="C126" s="31"/>
+      <x:c r="D126" s="31"/>
+      <x:c r="E126" s="31"/>
+      <x:c r="F126" s="31"/>
+      <x:c r="G126" s="31"/>
+      <x:c r="H126" s="31"/>
+      <x:c r="I126" s="31"/>
+      <x:c r="J126" s="31"/>
+      <x:c r="K126" s="31"/>
+      <x:c r="L126" s="31"/>
+      <x:c r="M126" s="31"/>
+      <x:c r="N126" s="31"/>
+      <x:c r="O126" s="31"/>
+      <x:c r="P126" s="31"/>
+      <x:c r="Q126" s="31"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="31"/>
+      <x:c r="B127" s="31"/>
+      <x:c r="C127" s="31"/>
+      <x:c r="D127" s="31"/>
+      <x:c r="E127" s="31"/>
+      <x:c r="F127" s="31"/>
+      <x:c r="G127" s="31"/>
+      <x:c r="H127" s="31"/>
+      <x:c r="I127" s="31"/>
+      <x:c r="J127" s="31"/>
+      <x:c r="K127" s="31"/>
+      <x:c r="L127" s="31"/>
+      <x:c r="M127" s="31"/>
+      <x:c r="N127" s="31"/>
+      <x:c r="O127" s="31"/>
+      <x:c r="P127" s="31"/>
+      <x:c r="Q127" s="31"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="31"/>
+      <x:c r="B128" s="31"/>
+      <x:c r="C128" s="31"/>
+      <x:c r="D128" s="31"/>
+      <x:c r="E128" s="31"/>
+      <x:c r="F128" s="31"/>
+      <x:c r="G128" s="31"/>
+      <x:c r="H128" s="31"/>
+      <x:c r="I128" s="31"/>
+      <x:c r="J128" s="31"/>
+      <x:c r="K128" s="31"/>
+      <x:c r="L128" s="31"/>
+      <x:c r="M128" s="31"/>
+      <x:c r="N128" s="31"/>
+      <x:c r="O128" s="31"/>
+      <x:c r="P128" s="31"/>
+      <x:c r="Q128" s="31"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="31"/>
+      <x:c r="B129" s="31"/>
+      <x:c r="C129" s="31"/>
+      <x:c r="D129" s="31"/>
+      <x:c r="E129" s="31"/>
+      <x:c r="F129" s="31"/>
+      <x:c r="G129" s="31"/>
+      <x:c r="H129" s="31"/>
+      <x:c r="I129" s="31"/>
+      <x:c r="J129" s="31"/>
+      <x:c r="K129" s="31"/>
+      <x:c r="L129" s="31"/>
+      <x:c r="M129" s="31"/>
+      <x:c r="N129" s="31"/>
+      <x:c r="O129" s="31"/>
+      <x:c r="P129" s="31"/>
+      <x:c r="Q129" s="31"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="31"/>
+      <x:c r="B130" s="31"/>
+      <x:c r="C130" s="31"/>
+      <x:c r="D130" s="31"/>
+      <x:c r="E130" s="31"/>
+      <x:c r="F130" s="31"/>
+      <x:c r="G130" s="31"/>
+      <x:c r="H130" s="31"/>
+      <x:c r="I130" s="31"/>
+      <x:c r="J130" s="31"/>
+      <x:c r="K130" s="31"/>
+      <x:c r="L130" s="31"/>
+      <x:c r="M130" s="31"/>
+      <x:c r="N130" s="31"/>
+      <x:c r="O130" s="31"/>
+      <x:c r="P130" s="31"/>
+      <x:c r="Q130" s="31"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="31"/>
+      <x:c r="B131" s="31"/>
+      <x:c r="C131" s="31"/>
+      <x:c r="D131" s="31"/>
+      <x:c r="E131" s="31"/>
+      <x:c r="F131" s="31"/>
+      <x:c r="G131" s="31"/>
+      <x:c r="H131" s="31"/>
+      <x:c r="I131" s="31"/>
+      <x:c r="J131" s="31"/>
+      <x:c r="K131" s="31"/>
+      <x:c r="L131" s="31"/>
+      <x:c r="M131" s="31"/>
+      <x:c r="N131" s="31"/>
+      <x:c r="O131" s="31"/>
+      <x:c r="P131" s="31"/>
+      <x:c r="Q131" s="31"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="31"/>
+      <x:c r="B132" s="31"/>
+      <x:c r="C132" s="31"/>
+      <x:c r="D132" s="31"/>
+      <x:c r="E132" s="31"/>
+      <x:c r="F132" s="31"/>
+      <x:c r="G132" s="31"/>
+      <x:c r="H132" s="31"/>
+      <x:c r="I132" s="31"/>
+      <x:c r="J132" s="31"/>
+      <x:c r="K132" s="31"/>
+      <x:c r="L132" s="31"/>
+      <x:c r="M132" s="31"/>
+      <x:c r="N132" s="31"/>
+      <x:c r="O132" s="31"/>
+      <x:c r="P132" s="31"/>
+      <x:c r="Q132" s="31"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="31"/>
+      <x:c r="B133" s="31"/>
+      <x:c r="C133" s="31"/>
+      <x:c r="D133" s="31"/>
+      <x:c r="E133" s="31"/>
+      <x:c r="F133" s="31"/>
+      <x:c r="G133" s="31"/>
+      <x:c r="H133" s="31"/>
+      <x:c r="I133" s="31"/>
+      <x:c r="J133" s="31"/>
+      <x:c r="K133" s="31"/>
+      <x:c r="L133" s="31"/>
+      <x:c r="M133" s="31"/>
+      <x:c r="N133" s="31"/>
+      <x:c r="O133" s="31"/>
+      <x:c r="P133" s="31"/>
+      <x:c r="Q133" s="31"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="31"/>
+      <x:c r="B134" s="31"/>
+      <x:c r="C134" s="31"/>
+      <x:c r="D134" s="31"/>
+      <x:c r="E134" s="31"/>
+      <x:c r="F134" s="31"/>
+      <x:c r="G134" s="31"/>
+      <x:c r="H134" s="31"/>
+      <x:c r="I134" s="31"/>
+      <x:c r="J134" s="31"/>
+      <x:c r="K134" s="31"/>
+      <x:c r="L134" s="31"/>
+      <x:c r="M134" s="31"/>
+      <x:c r="N134" s="31"/>
+      <x:c r="O134" s="31"/>
+      <x:c r="P134" s="31"/>
+      <x:c r="Q134" s="31"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="31"/>
+      <x:c r="B135" s="31"/>
+      <x:c r="C135" s="31"/>
+      <x:c r="D135" s="31"/>
+      <x:c r="E135" s="31"/>
+      <x:c r="F135" s="31"/>
+      <x:c r="G135" s="31"/>
+      <x:c r="H135" s="31"/>
+      <x:c r="I135" s="31"/>
+      <x:c r="J135" s="31"/>
+      <x:c r="K135" s="31"/>
+      <x:c r="L135" s="31"/>
+      <x:c r="M135" s="31"/>
+      <x:c r="N135" s="31"/>
+      <x:c r="O135" s="31"/>
+      <x:c r="P135" s="31"/>
+      <x:c r="Q135" s="31"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="31"/>
+      <x:c r="B136" s="31"/>
+      <x:c r="C136" s="31"/>
+      <x:c r="D136" s="31"/>
+      <x:c r="E136" s="31"/>
+      <x:c r="F136" s="31"/>
+      <x:c r="G136" s="31"/>
+      <x:c r="H136" s="31"/>
+      <x:c r="I136" s="31"/>
+      <x:c r="J136" s="31"/>
+      <x:c r="K136" s="31"/>
+      <x:c r="L136" s="31"/>
+      <x:c r="M136" s="31"/>
+      <x:c r="N136" s="31"/>
+      <x:c r="O136" s="31"/>
+      <x:c r="P136" s="31"/>
+      <x:c r="Q136" s="31"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="31"/>
+      <x:c r="B137" s="31"/>
+      <x:c r="C137" s="31"/>
+      <x:c r="D137" s="31"/>
+      <x:c r="E137" s="31"/>
+      <x:c r="F137" s="31"/>
+      <x:c r="G137" s="31"/>
+      <x:c r="H137" s="31"/>
+      <x:c r="I137" s="31"/>
+      <x:c r="J137" s="31"/>
+      <x:c r="K137" s="31"/>
+      <x:c r="L137" s="31"/>
+      <x:c r="M137" s="31"/>
+      <x:c r="N137" s="31"/>
+      <x:c r="O137" s="31"/>
+      <x:c r="P137" s="31"/>
+      <x:c r="Q137" s="31"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="31"/>
+      <x:c r="B138" s="31"/>
+      <x:c r="C138" s="31"/>
+      <x:c r="D138" s="31"/>
+      <x:c r="E138" s="31"/>
+      <x:c r="F138" s="31"/>
+      <x:c r="G138" s="31"/>
+      <x:c r="H138" s="31"/>
+      <x:c r="I138" s="31"/>
+      <x:c r="J138" s="31"/>
+      <x:c r="K138" s="31"/>
+      <x:c r="L138" s="31"/>
+      <x:c r="M138" s="31"/>
+      <x:c r="N138" s="31"/>
+      <x:c r="O138" s="31"/>
+      <x:c r="P138" s="31"/>
+      <x:c r="Q138" s="31"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="31"/>
+      <x:c r="B139" s="31"/>
+      <x:c r="C139" s="31"/>
+      <x:c r="D139" s="31"/>
+      <x:c r="E139" s="31"/>
+      <x:c r="F139" s="31"/>
+      <x:c r="G139" s="31"/>
+      <x:c r="H139" s="31"/>
+      <x:c r="I139" s="31"/>
+      <x:c r="J139" s="31"/>
+      <x:c r="K139" s="31"/>
+      <x:c r="L139" s="31"/>
+      <x:c r="M139" s="31"/>
+      <x:c r="N139" s="31"/>
+      <x:c r="O139" s="31"/>
+      <x:c r="P139" s="31"/>
+      <x:c r="Q139" s="31"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="31"/>
+      <x:c r="B140" s="31"/>
+      <x:c r="C140" s="31"/>
+      <x:c r="D140" s="31"/>
+      <x:c r="E140" s="31"/>
+      <x:c r="F140" s="31"/>
+      <x:c r="G140" s="31"/>
+      <x:c r="H140" s="31"/>
+      <x:c r="I140" s="31"/>
+      <x:c r="J140" s="31"/>
+      <x:c r="K140" s="31"/>
+      <x:c r="L140" s="31"/>
+      <x:c r="M140" s="31"/>
+      <x:c r="N140" s="31"/>
+      <x:c r="O140" s="31"/>
+      <x:c r="P140" s="31"/>
+      <x:c r="Q140" s="31"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="31"/>
+      <x:c r="B141" s="31"/>
+      <x:c r="C141" s="31"/>
+      <x:c r="D141" s="31"/>
+      <x:c r="E141" s="31"/>
+      <x:c r="F141" s="31"/>
+      <x:c r="G141" s="31"/>
+      <x:c r="H141" s="31"/>
+      <x:c r="I141" s="31"/>
+      <x:c r="J141" s="31"/>
+      <x:c r="K141" s="31"/>
+      <x:c r="L141" s="31"/>
+      <x:c r="M141" s="31"/>
+      <x:c r="N141" s="31"/>
+      <x:c r="O141" s="31"/>
+      <x:c r="P141" s="31"/>
+      <x:c r="Q141" s="31"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="31"/>
+      <x:c r="B142" s="31"/>
+      <x:c r="C142" s="31"/>
+      <x:c r="D142" s="31"/>
+      <x:c r="E142" s="31"/>
+      <x:c r="F142" s="31"/>
+      <x:c r="G142" s="31"/>
+      <x:c r="H142" s="31"/>
+      <x:c r="I142" s="31"/>
+      <x:c r="J142" s="31"/>
+      <x:c r="K142" s="31"/>
+      <x:c r="L142" s="31"/>
+      <x:c r="M142" s="31"/>
+      <x:c r="N142" s="31"/>
+      <x:c r="O142" s="31"/>
+      <x:c r="P142" s="31"/>
+      <x:c r="Q142" s="31"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="31"/>
+      <x:c r="B143" s="31"/>
+      <x:c r="C143" s="31"/>
+      <x:c r="D143" s="31"/>
+      <x:c r="E143" s="31"/>
+      <x:c r="F143" s="31"/>
+      <x:c r="G143" s="31"/>
+      <x:c r="H143" s="31"/>
+      <x:c r="I143" s="31"/>
+      <x:c r="J143" s="31"/>
+      <x:c r="K143" s="31"/>
+      <x:c r="L143" s="31"/>
+      <x:c r="M143" s="31"/>
+      <x:c r="N143" s="31"/>
+      <x:c r="O143" s="31"/>
+      <x:c r="P143" s="31"/>
+      <x:c r="Q143" s="31"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="31"/>
+      <x:c r="B144" s="31"/>
+      <x:c r="C144" s="31"/>
+      <x:c r="D144" s="31"/>
+      <x:c r="E144" s="31"/>
+      <x:c r="F144" s="31"/>
+      <x:c r="G144" s="31"/>
+      <x:c r="H144" s="31"/>
+      <x:c r="I144" s="31"/>
+      <x:c r="J144" s="31"/>
+      <x:c r="K144" s="31"/>
+      <x:c r="L144" s="31"/>
+      <x:c r="M144" s="31"/>
+      <x:c r="N144" s="31"/>
+      <x:c r="O144" s="31"/>
+      <x:c r="P144" s="31"/>
+      <x:c r="Q144" s="31"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="31"/>
+      <x:c r="B145" s="31"/>
+      <x:c r="C145" s="31"/>
+      <x:c r="D145" s="31"/>
+      <x:c r="E145" s="31"/>
+      <x:c r="F145" s="31"/>
+      <x:c r="G145" s="31"/>
+      <x:c r="H145" s="31"/>
+      <x:c r="I145" s="31"/>
+      <x:c r="J145" s="31"/>
+      <x:c r="K145" s="31"/>
+      <x:c r="L145" s="31"/>
+      <x:c r="M145" s="31"/>
+      <x:c r="N145" s="31"/>
+      <x:c r="O145" s="31"/>
+      <x:c r="P145" s="31"/>
+      <x:c r="Q145" s="31"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="31"/>
+      <x:c r="B146" s="31"/>
+      <x:c r="C146" s="31"/>
+      <x:c r="D146" s="31"/>
+      <x:c r="E146" s="31"/>
+      <x:c r="F146" s="31"/>
+      <x:c r="G146" s="31"/>
+      <x:c r="H146" s="31"/>
+      <x:c r="I146" s="31"/>
+      <x:c r="J146" s="31"/>
+      <x:c r="K146" s="31"/>
+      <x:c r="L146" s="31"/>
+      <x:c r="M146" s="31"/>
+      <x:c r="N146" s="31"/>
+      <x:c r="O146" s="31"/>
+      <x:c r="P146" s="31"/>
+      <x:c r="Q146" s="31"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="31"/>
+      <x:c r="B147" s="31"/>
+      <x:c r="C147" s="31"/>
+      <x:c r="D147" s="31"/>
+      <x:c r="E147" s="31"/>
+      <x:c r="F147" s="31"/>
+      <x:c r="G147" s="31"/>
+      <x:c r="H147" s="31"/>
+      <x:c r="I147" s="31"/>
+      <x:c r="J147" s="31"/>
+      <x:c r="K147" s="31"/>
+      <x:c r="L147" s="31"/>
+      <x:c r="M147" s="31"/>
+      <x:c r="N147" s="31"/>
+      <x:c r="O147" s="31"/>
+      <x:c r="P147" s="31"/>
+      <x:c r="Q147" s="31"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="31"/>
+      <x:c r="B148" s="31"/>
+      <x:c r="C148" s="31"/>
+      <x:c r="D148" s="31"/>
+      <x:c r="E148" s="31"/>
+      <x:c r="F148" s="31"/>
+      <x:c r="G148" s="31"/>
+      <x:c r="H148" s="31"/>
+      <x:c r="I148" s="31"/>
+      <x:c r="J148" s="31"/>
+      <x:c r="K148" s="31"/>
+      <x:c r="L148" s="31"/>
+      <x:c r="M148" s="31"/>
+      <x:c r="N148" s="31"/>
+      <x:c r="O148" s="31"/>
+      <x:c r="P148" s="31"/>
+      <x:c r="Q148" s="31"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="31"/>
+      <x:c r="B149" s="31"/>
+      <x:c r="C149" s="31"/>
+      <x:c r="D149" s="31"/>
+      <x:c r="E149" s="31"/>
+      <x:c r="F149" s="31"/>
+      <x:c r="G149" s="31"/>
+      <x:c r="H149" s="31"/>
+      <x:c r="I149" s="31"/>
+      <x:c r="J149" s="31"/>
+      <x:c r="K149" s="31"/>
+      <x:c r="L149" s="31"/>
+      <x:c r="M149" s="31"/>
+      <x:c r="N149" s="31"/>
+      <x:c r="O149" s="31"/>
+      <x:c r="P149" s="31"/>
+      <x:c r="Q149" s="31"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="31"/>
+      <x:c r="B150" s="31"/>
+      <x:c r="C150" s="31"/>
+      <x:c r="D150" s="31"/>
+      <x:c r="E150" s="31"/>
+      <x:c r="F150" s="31"/>
+      <x:c r="G150" s="31"/>
+      <x:c r="H150" s="31"/>
+      <x:c r="I150" s="31"/>
+      <x:c r="J150" s="31"/>
+      <x:c r="K150" s="31"/>
+      <x:c r="L150" s="31"/>
+      <x:c r="M150" s="31"/>
+      <x:c r="N150" s="31"/>
+      <x:c r="O150" s="31"/>
+      <x:c r="P150" s="31"/>
+      <x:c r="Q150" s="31"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="31"/>
+      <x:c r="B151" s="31"/>
+      <x:c r="C151" s="31"/>
+      <x:c r="D151" s="31"/>
+      <x:c r="E151" s="31"/>
+      <x:c r="F151" s="31"/>
+      <x:c r="G151" s="31"/>
+      <x:c r="H151" s="31"/>
+      <x:c r="I151" s="31"/>
+      <x:c r="J151" s="31"/>
+      <x:c r="K151" s="31"/>
+      <x:c r="L151" s="31"/>
+      <x:c r="M151" s="31"/>
+      <x:c r="N151" s="31"/>
+      <x:c r="O151" s="31"/>
+      <x:c r="P151" s="31"/>
+      <x:c r="Q151" s="31"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="31"/>
+      <x:c r="B152" s="31"/>
+      <x:c r="C152" s="31"/>
+      <x:c r="D152" s="31"/>
+      <x:c r="E152" s="31"/>
+      <x:c r="F152" s="31"/>
+      <x:c r="G152" s="31"/>
+      <x:c r="H152" s="31"/>
+      <x:c r="I152" s="31"/>
+      <x:c r="J152" s="31"/>
+      <x:c r="K152" s="31"/>
+      <x:c r="L152" s="31"/>
+      <x:c r="M152" s="31"/>
+      <x:c r="N152" s="31"/>
+      <x:c r="O152" s="31"/>
+      <x:c r="P152" s="31"/>
+      <x:c r="Q152" s="31"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="31"/>
+      <x:c r="B153" s="31"/>
+      <x:c r="C153" s="31"/>
+      <x:c r="D153" s="31"/>
+      <x:c r="E153" s="31"/>
+      <x:c r="F153" s="31"/>
+      <x:c r="G153" s="31"/>
+      <x:c r="H153" s="31"/>
+      <x:c r="I153" s="31"/>
+      <x:c r="J153" s="31"/>
+      <x:c r="K153" s="31"/>
+      <x:c r="L153" s="31"/>
+      <x:c r="M153" s="31"/>
+      <x:c r="N153" s="31"/>
+      <x:c r="O153" s="31"/>
+      <x:c r="P153" s="31"/>
+      <x:c r="Q153" s="31"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="31"/>
+      <x:c r="B154" s="31"/>
+      <x:c r="C154" s="31"/>
+      <x:c r="D154" s="31"/>
+      <x:c r="E154" s="31"/>
+      <x:c r="F154" s="31"/>
+      <x:c r="G154" s="31"/>
+      <x:c r="H154" s="31"/>
+      <x:c r="I154" s="31"/>
+      <x:c r="J154" s="31"/>
+      <x:c r="K154" s="31"/>
+      <x:c r="L154" s="31"/>
+      <x:c r="M154" s="31"/>
+      <x:c r="N154" s="31"/>
+      <x:c r="O154" s="31"/>
+      <x:c r="P154" s="31"/>
+      <x:c r="Q154" s="31"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="31"/>
+      <x:c r="B155" s="31"/>
+      <x:c r="C155" s="31"/>
+      <x:c r="D155" s="31"/>
+      <x:c r="E155" s="31"/>
+      <x:c r="F155" s="31"/>
+      <x:c r="G155" s="31"/>
+      <x:c r="H155" s="31"/>
+      <x:c r="I155" s="31"/>
+      <x:c r="J155" s="31"/>
+      <x:c r="K155" s="31"/>
+      <x:c r="L155" s="31"/>
+      <x:c r="M155" s="31"/>
+      <x:c r="N155" s="31"/>
+      <x:c r="O155" s="31"/>
+      <x:c r="P155" s="31"/>
+      <x:c r="Q155" s="31"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="31"/>
+      <x:c r="B156" s="31"/>
+      <x:c r="C156" s="31"/>
+      <x:c r="D156" s="31"/>
+      <x:c r="E156" s="31"/>
+      <x:c r="F156" s="31"/>
+      <x:c r="G156" s="31"/>
+      <x:c r="H156" s="31"/>
+      <x:c r="I156" s="31"/>
+      <x:c r="J156" s="31"/>
+      <x:c r="K156" s="31"/>
+      <x:c r="L156" s="31"/>
+      <x:c r="M156" s="31"/>
+      <x:c r="N156" s="31"/>
+      <x:c r="O156" s="31"/>
+      <x:c r="P156" s="31"/>
+      <x:c r="Q156" s="31"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="31"/>
+      <x:c r="B157" s="31"/>
+      <x:c r="C157" s="31"/>
+      <x:c r="D157" s="31"/>
+      <x:c r="E157" s="31"/>
+      <x:c r="F157" s="31"/>
+      <x:c r="G157" s="31"/>
+      <x:c r="H157" s="31"/>
+      <x:c r="I157" s="31"/>
+      <x:c r="J157" s="31"/>
+      <x:c r="K157" s="31"/>
+      <x:c r="L157" s="31"/>
+      <x:c r="M157" s="31"/>
+      <x:c r="N157" s="31"/>
+      <x:c r="O157" s="31"/>
+      <x:c r="P157" s="31"/>
+      <x:c r="Q157" s="31"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="31"/>
+      <x:c r="B158" s="31"/>
+      <x:c r="C158" s="31"/>
+      <x:c r="D158" s="31"/>
+      <x:c r="E158" s="31"/>
+      <x:c r="F158" s="31"/>
+      <x:c r="G158" s="31"/>
+      <x:c r="H158" s="31"/>
+      <x:c r="I158" s="31"/>
+      <x:c r="J158" s="31"/>
+      <x:c r="K158" s="31"/>
+      <x:c r="L158" s="31"/>
+      <x:c r="M158" s="31"/>
+      <x:c r="N158" s="31"/>
+      <x:c r="O158" s="31"/>
+      <x:c r="P158" s="31"/>
+      <x:c r="Q158" s="31"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="31"/>
+      <x:c r="B159" s="31"/>
+      <x:c r="C159" s="31"/>
+      <x:c r="D159" s="31"/>
+      <x:c r="E159" s="31"/>
+      <x:c r="F159" s="31"/>
+      <x:c r="G159" s="31"/>
+      <x:c r="H159" s="31"/>
+      <x:c r="I159" s="31"/>
+      <x:c r="J159" s="31"/>
+      <x:c r="K159" s="31"/>
+      <x:c r="L159" s="31"/>
+      <x:c r="M159" s="31"/>
+      <x:c r="N159" s="31"/>
+      <x:c r="O159" s="31"/>
+      <x:c r="P159" s="31"/>
+      <x:c r="Q159" s="31"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="31"/>
+      <x:c r="B160" s="31"/>
+      <x:c r="C160" s="31"/>
+      <x:c r="D160" s="31"/>
+      <x:c r="E160" s="31"/>
+      <x:c r="F160" s="31"/>
+      <x:c r="G160" s="31"/>
+      <x:c r="H160" s="31"/>
+      <x:c r="I160" s="31"/>
+      <x:c r="J160" s="31"/>
+      <x:c r="K160" s="31"/>
+      <x:c r="L160" s="31"/>
+      <x:c r="M160" s="31"/>
+      <x:c r="N160" s="31"/>
+      <x:c r="O160" s="31"/>
+      <x:c r="P160" s="31"/>
+      <x:c r="Q160" s="31"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="31"/>
+      <x:c r="B161" s="31"/>
+      <x:c r="C161" s="31"/>
+      <x:c r="D161" s="31"/>
+      <x:c r="E161" s="31"/>
+      <x:c r="F161" s="31"/>
+      <x:c r="G161" s="31"/>
+      <x:c r="H161" s="31"/>
+      <x:c r="I161" s="31"/>
+      <x:c r="J161" s="31"/>
+      <x:c r="K161" s="31"/>
+      <x:c r="L161" s="31"/>
+      <x:c r="M161" s="31"/>
+      <x:c r="N161" s="31"/>
+      <x:c r="O161" s="31"/>
+      <x:c r="P161" s="31"/>
+      <x:c r="Q161" s="31"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="31"/>
+      <x:c r="B162" s="31"/>
+      <x:c r="C162" s="31"/>
+      <x:c r="D162" s="31"/>
+      <x:c r="E162" s="31"/>
+      <x:c r="F162" s="31"/>
+      <x:c r="G162" s="31"/>
+      <x:c r="H162" s="31"/>
+      <x:c r="I162" s="31"/>
+      <x:c r="J162" s="31"/>
+      <x:c r="K162" s="31"/>
+      <x:c r="L162" s="31"/>
+      <x:c r="M162" s="31"/>
+      <x:c r="N162" s="31"/>
+      <x:c r="O162" s="31"/>
+      <x:c r="P162" s="31"/>
+      <x:c r="Q162" s="31"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="31"/>
+      <x:c r="B163" s="31"/>
+      <x:c r="C163" s="31"/>
+      <x:c r="D163" s="31"/>
+      <x:c r="E163" s="31"/>
+      <x:c r="F163" s="31"/>
+      <x:c r="G163" s="31"/>
+      <x:c r="H163" s="31"/>
+      <x:c r="I163" s="31"/>
+      <x:c r="J163" s="31"/>
+      <x:c r="K163" s="31"/>
+      <x:c r="L163" s="31"/>
+      <x:c r="M163" s="31"/>
+      <x:c r="N163" s="31"/>
+      <x:c r="O163" s="31"/>
+      <x:c r="P163" s="31"/>
+      <x:c r="Q163" s="31"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="31"/>
+      <x:c r="B164" s="31"/>
+      <x:c r="C164" s="31"/>
+      <x:c r="D164" s="31"/>
+      <x:c r="E164" s="31"/>
+      <x:c r="F164" s="31"/>
+      <x:c r="G164" s="31"/>
+      <x:c r="H164" s="31"/>
+      <x:c r="I164" s="31"/>
+      <x:c r="J164" s="31"/>
+      <x:c r="K164" s="31"/>
+      <x:c r="L164" s="31"/>
+      <x:c r="M164" s="31"/>
+      <x:c r="N164" s="31"/>
+      <x:c r="O164" s="31"/>
+      <x:c r="P164" s="31"/>
+      <x:c r="Q164" s="31"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="31"/>
+      <x:c r="B165" s="31"/>
+      <x:c r="C165" s="31"/>
+      <x:c r="D165" s="31"/>
+      <x:c r="E165" s="31"/>
+      <x:c r="F165" s="31"/>
+      <x:c r="G165" s="31"/>
+      <x:c r="H165" s="31"/>
+      <x:c r="I165" s="31"/>
+      <x:c r="J165" s="31"/>
+      <x:c r="K165" s="31"/>
+      <x:c r="L165" s="31"/>
+      <x:c r="M165" s="31"/>
+      <x:c r="N165" s="31"/>
+      <x:c r="O165" s="31"/>
+      <x:c r="P165" s="31"/>
+      <x:c r="Q165" s="31"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="31"/>
+      <x:c r="B166" s="31"/>
+      <x:c r="C166" s="31"/>
+      <x:c r="D166" s="31"/>
+      <x:c r="E166" s="31"/>
+      <x:c r="F166" s="31"/>
+      <x:c r="G166" s="31"/>
+      <x:c r="H166" s="31"/>
+      <x:c r="I166" s="31"/>
+      <x:c r="J166" s="31"/>
+      <x:c r="K166" s="31"/>
+      <x:c r="L166" s="31"/>
+      <x:c r="M166" s="31"/>
+      <x:c r="N166" s="31"/>
+      <x:c r="O166" s="31"/>
+      <x:c r="P166" s="31"/>
+      <x:c r="Q166" s="31"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="31"/>
+      <x:c r="B167" s="31"/>
+      <x:c r="C167" s="31"/>
+      <x:c r="D167" s="31"/>
+      <x:c r="E167" s="31"/>
+      <x:c r="F167" s="31"/>
+      <x:c r="G167" s="31"/>
+      <x:c r="H167" s="31"/>
+      <x:c r="I167" s="31"/>
+      <x:c r="J167" s="31"/>
+      <x:c r="K167" s="31"/>
+      <x:c r="L167" s="31"/>
+      <x:c r="M167" s="31"/>
+      <x:c r="N167" s="31"/>
+      <x:c r="O167" s="31"/>
+      <x:c r="P167" s="31"/>
+      <x:c r="Q167" s="31"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="31"/>
+      <x:c r="B168" s="31"/>
+      <x:c r="C168" s="31"/>
+      <x:c r="D168" s="31"/>
+      <x:c r="E168" s="31"/>
+      <x:c r="F168" s="31"/>
+      <x:c r="G168" s="31"/>
+      <x:c r="H168" s="31"/>
+      <x:c r="I168" s="31"/>
+      <x:c r="J168" s="31"/>
+      <x:c r="K168" s="31"/>
+      <x:c r="L168" s="31"/>
+      <x:c r="M168" s="31"/>
+      <x:c r="N168" s="31"/>
+      <x:c r="O168" s="31"/>
+      <x:c r="P168" s="31"/>
+      <x:c r="Q168" s="31"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="31"/>
+      <x:c r="B169" s="31"/>
+      <x:c r="C169" s="31"/>
+      <x:c r="D169" s="31"/>
+      <x:c r="E169" s="31"/>
+      <x:c r="F169" s="31"/>
+      <x:c r="G169" s="31"/>
+      <x:c r="H169" s="31"/>
+      <x:c r="I169" s="31"/>
+      <x:c r="J169" s="31"/>
+      <x:c r="K169" s="31"/>
+      <x:c r="L169" s="31"/>
+      <x:c r="M169" s="31"/>
+      <x:c r="N169" s="31"/>
+      <x:c r="O169" s="31"/>
+      <x:c r="P169" s="31"/>
+      <x:c r="Q169" s="31"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="31"/>
+      <x:c r="B170" s="31"/>
+      <x:c r="C170" s="31"/>
+      <x:c r="D170" s="31"/>
+      <x:c r="E170" s="31"/>
+      <x:c r="F170" s="31"/>
+      <x:c r="G170" s="31"/>
+      <x:c r="H170" s="31"/>
+      <x:c r="I170" s="31"/>
+      <x:c r="J170" s="31"/>
+      <x:c r="K170" s="31"/>
+      <x:c r="L170" s="31"/>
+      <x:c r="M170" s="31"/>
+      <x:c r="N170" s="31"/>
+      <x:c r="O170" s="31"/>
+      <x:c r="P170" s="31"/>
+      <x:c r="Q170" s="31"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="31"/>
+      <x:c r="B171" s="31"/>
+      <x:c r="C171" s="31"/>
+      <x:c r="D171" s="31"/>
+      <x:c r="E171" s="31"/>
+      <x:c r="F171" s="31"/>
+      <x:c r="G171" s="31"/>
+      <x:c r="H171" s="31"/>
+      <x:c r="I171" s="31"/>
+      <x:c r="J171" s="31"/>
+      <x:c r="K171" s="31"/>
+      <x:c r="L171" s="31"/>
+      <x:c r="M171" s="31"/>
+      <x:c r="N171" s="31"/>
+      <x:c r="O171" s="31"/>
+      <x:c r="P171" s="31"/>
+      <x:c r="Q171" s="31"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="31"/>
+      <x:c r="B172" s="31"/>
+      <x:c r="C172" s="31"/>
+      <x:c r="D172" s="31"/>
+      <x:c r="E172" s="31"/>
+      <x:c r="F172" s="31"/>
+      <x:c r="G172" s="31"/>
+      <x:c r="H172" s="31"/>
+      <x:c r="I172" s="31"/>
+      <x:c r="J172" s="31"/>
+      <x:c r="K172" s="31"/>
+      <x:c r="L172" s="31"/>
+      <x:c r="M172" s="31"/>
+      <x:c r="N172" s="31"/>
+      <x:c r="O172" s="31"/>
+      <x:c r="P172" s="31"/>
+      <x:c r="Q172" s="31"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="31"/>
+      <x:c r="B173" s="31"/>
+      <x:c r="C173" s="31"/>
+      <x:c r="D173" s="31"/>
+      <x:c r="E173" s="31"/>
+      <x:c r="F173" s="31"/>
+      <x:c r="G173" s="31"/>
+      <x:c r="H173" s="31"/>
+      <x:c r="I173" s="31"/>
+      <x:c r="J173" s="31"/>
+      <x:c r="K173" s="31"/>
+      <x:c r="L173" s="31"/>
+      <x:c r="M173" s="31"/>
+      <x:c r="N173" s="31"/>
+      <x:c r="O173" s="31"/>
+      <x:c r="P173" s="31"/>
+      <x:c r="Q173" s="31"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="31"/>
+      <x:c r="B174" s="31"/>
+      <x:c r="C174" s="31"/>
+      <x:c r="D174" s="31"/>
+      <x:c r="E174" s="31"/>
+      <x:c r="F174" s="31"/>
+      <x:c r="G174" s="31"/>
+      <x:c r="H174" s="31"/>
+      <x:c r="I174" s="31"/>
+      <x:c r="J174" s="31"/>
+      <x:c r="K174" s="31"/>
+      <x:c r="L174" s="31"/>
+      <x:c r="M174" s="31"/>
+      <x:c r="N174" s="31"/>
+      <x:c r="O174" s="31"/>
+      <x:c r="P174" s="31"/>
+      <x:c r="Q174" s="31"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="31"/>
+      <x:c r="B175" s="31"/>
+      <x:c r="C175" s="31"/>
+      <x:c r="D175" s="31"/>
+      <x:c r="E175" s="31"/>
+      <x:c r="F175" s="31"/>
+      <x:c r="G175" s="31"/>
+      <x:c r="H175" s="31"/>
+      <x:c r="I175" s="31"/>
+      <x:c r="J175" s="31"/>
+      <x:c r="K175" s="31"/>
+      <x:c r="L175" s="31"/>
+      <x:c r="M175" s="31"/>
+      <x:c r="N175" s="31"/>
+      <x:c r="O175" s="31"/>
+      <x:c r="P175" s="31"/>
+      <x:c r="Q175" s="31"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="31"/>
+      <x:c r="B176" s="31"/>
+      <x:c r="C176" s="31"/>
+      <x:c r="D176" s="31"/>
+      <x:c r="E176" s="31"/>
+      <x:c r="F176" s="31"/>
+      <x:c r="G176" s="31"/>
+      <x:c r="H176" s="31"/>
+      <x:c r="I176" s="31"/>
+      <x:c r="J176" s="31"/>
+      <x:c r="K176" s="31"/>
+      <x:c r="L176" s="31"/>
+      <x:c r="M176" s="31"/>
+      <x:c r="N176" s="31"/>
+      <x:c r="O176" s="31"/>
+      <x:c r="P176" s="31"/>
+      <x:c r="Q176" s="31"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="31"/>
+      <x:c r="B177" s="31"/>
+      <x:c r="C177" s="31"/>
+      <x:c r="D177" s="31"/>
+      <x:c r="E177" s="31"/>
+      <x:c r="F177" s="31"/>
+      <x:c r="G177" s="31"/>
+      <x:c r="H177" s="31"/>
+      <x:c r="I177" s="31"/>
+      <x:c r="J177" s="31"/>
+      <x:c r="K177" s="31"/>
+      <x:c r="L177" s="31"/>
+      <x:c r="M177" s="31"/>
+      <x:c r="N177" s="31"/>
+      <x:c r="O177" s="31"/>
+      <x:c r="P177" s="31"/>
+      <x:c r="Q177" s="31"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="31"/>
+      <x:c r="B178" s="31"/>
+      <x:c r="C178" s="31"/>
+      <x:c r="D178" s="31"/>
+      <x:c r="E178" s="31"/>
+      <x:c r="F178" s="31"/>
+      <x:c r="G178" s="31"/>
+      <x:c r="H178" s="31"/>
+      <x:c r="I178" s="31"/>
+      <x:c r="J178" s="31"/>
+      <x:c r="K178" s="31"/>
+      <x:c r="L178" s="31"/>
+      <x:c r="M178" s="31"/>
+      <x:c r="N178" s="31"/>
+      <x:c r="O178" s="31"/>
+      <x:c r="P178" s="31"/>
+      <x:c r="Q178" s="31"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="31"/>
+      <x:c r="B179" s="31"/>
+      <x:c r="C179" s="31"/>
+      <x:c r="D179" s="31"/>
+      <x:c r="E179" s="31"/>
+      <x:c r="F179" s="31"/>
+      <x:c r="G179" s="31"/>
+      <x:c r="H179" s="31"/>
+      <x:c r="I179" s="31"/>
+      <x:c r="J179" s="31"/>
+      <x:c r="K179" s="31"/>
+      <x:c r="L179" s="31"/>
+      <x:c r="M179" s="31"/>
+      <x:c r="N179" s="31"/>
+      <x:c r="O179" s="31"/>
+      <x:c r="P179" s="31"/>
+      <x:c r="Q179" s="31"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="31"/>
+      <x:c r="B180" s="31"/>
+      <x:c r="C180" s="31"/>
+      <x:c r="D180" s="31"/>
+      <x:c r="E180" s="31"/>
+      <x:c r="F180" s="31"/>
+      <x:c r="G180" s="31"/>
+      <x:c r="H180" s="31"/>
+      <x:c r="I180" s="31"/>
+      <x:c r="J180" s="31"/>
+      <x:c r="K180" s="31"/>
+      <x:c r="L180" s="31"/>
+      <x:c r="M180" s="31"/>
+      <x:c r="N180" s="31"/>
+      <x:c r="O180" s="31"/>
+      <x:c r="P180" s="31"/>
+      <x:c r="Q180" s="31"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="31"/>
+      <x:c r="B181" s="31"/>
+      <x:c r="C181" s="31"/>
+      <x:c r="D181" s="31"/>
+      <x:c r="E181" s="31"/>
+      <x:c r="F181" s="31"/>
+      <x:c r="G181" s="31"/>
+      <x:c r="H181" s="31"/>
+      <x:c r="I181" s="31"/>
+      <x:c r="J181" s="31"/>
+      <x:c r="K181" s="31"/>
+      <x:c r="L181" s="31"/>
+      <x:c r="M181" s="31"/>
+      <x:c r="N181" s="31"/>
+      <x:c r="O181" s="31"/>
+      <x:c r="P181" s="31"/>
+      <x:c r="Q181" s="31"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="31"/>
+      <x:c r="B182" s="31"/>
+      <x:c r="C182" s="31"/>
+      <x:c r="D182" s="31"/>
+      <x:c r="E182" s="31"/>
+      <x:c r="F182" s="31"/>
+      <x:c r="G182" s="31"/>
+      <x:c r="H182" s="31"/>
+      <x:c r="I182" s="31"/>
+      <x:c r="J182" s="31"/>
+      <x:c r="K182" s="31"/>
+      <x:c r="L182" s="31"/>
+      <x:c r="M182" s="31"/>
+      <x:c r="N182" s="31"/>
+      <x:c r="O182" s="31"/>
+      <x:c r="P182" s="31"/>
+      <x:c r="Q182" s="31"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="31"/>
+      <x:c r="B183" s="31"/>
+      <x:c r="C183" s="31"/>
+      <x:c r="D183" s="31"/>
+      <x:c r="E183" s="31"/>
+      <x:c r="F183" s="31"/>
+      <x:c r="G183" s="31"/>
+      <x:c r="H183" s="31"/>
+      <x:c r="I183" s="31"/>
+      <x:c r="J183" s="31"/>
+      <x:c r="K183" s="31"/>
+      <x:c r="L183" s="31"/>
+      <x:c r="M183" s="31"/>
+      <x:c r="N183" s="31"/>
+      <x:c r="O183" s="31"/>
+      <x:c r="P183" s="31"/>
+      <x:c r="Q183" s="31"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="31"/>
+      <x:c r="B184" s="31"/>
+      <x:c r="C184" s="31"/>
+      <x:c r="D184" s="31"/>
+      <x:c r="E184" s="31"/>
+      <x:c r="F184" s="31"/>
+      <x:c r="G184" s="31"/>
+      <x:c r="H184" s="31"/>
+      <x:c r="I184" s="31"/>
+      <x:c r="J184" s="31"/>
+      <x:c r="K184" s="31"/>
+      <x:c r="L184" s="31"/>
+      <x:c r="M184" s="31"/>
+      <x:c r="N184" s="31"/>
+      <x:c r="O184" s="31"/>
+      <x:c r="P184" s="31"/>
+      <x:c r="Q184" s="31"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="31"/>
+      <x:c r="B185" s="31"/>
+      <x:c r="C185" s="31"/>
+      <x:c r="D185" s="31"/>
+      <x:c r="E185" s="31"/>
+      <x:c r="F185" s="31"/>
+      <x:c r="G185" s="31"/>
+      <x:c r="H185" s="31"/>
+      <x:c r="I185" s="31"/>
+      <x:c r="J185" s="31"/>
+      <x:c r="K185" s="31"/>
+      <x:c r="L185" s="31"/>
+      <x:c r="M185" s="31"/>
+      <x:c r="N185" s="31"/>
+      <x:c r="O185" s="31"/>
+      <x:c r="P185" s="31"/>
+      <x:c r="Q185" s="31"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="31"/>
+      <x:c r="B186" s="31"/>
+      <x:c r="C186" s="31"/>
+      <x:c r="D186" s="31"/>
+      <x:c r="E186" s="31"/>
+      <x:c r="F186" s="31"/>
+      <x:c r="G186" s="31"/>
+      <x:c r="H186" s="31"/>
+      <x:c r="I186" s="31"/>
+      <x:c r="J186" s="31"/>
+      <x:c r="K186" s="31"/>
+      <x:c r="L186" s="31"/>
+      <x:c r="M186" s="31"/>
+      <x:c r="N186" s="31"/>
+      <x:c r="O186" s="31"/>
+      <x:c r="P186" s="31"/>
+      <x:c r="Q186" s="31"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="31"/>
+      <x:c r="B187" s="31"/>
+      <x:c r="C187" s="31"/>
+      <x:c r="D187" s="31"/>
+      <x:c r="E187" s="31"/>
+      <x:c r="F187" s="31"/>
+      <x:c r="G187" s="31"/>
+      <x:c r="H187" s="31"/>
+      <x:c r="I187" s="31"/>
+      <x:c r="J187" s="31"/>
+      <x:c r="K187" s="31"/>
+      <x:c r="L187" s="31"/>
+      <x:c r="M187" s="31"/>
+      <x:c r="N187" s="31"/>
+      <x:c r="O187" s="31"/>
+      <x:c r="P187" s="31"/>
+      <x:c r="Q187" s="31"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="31"/>
+      <x:c r="B188" s="31"/>
+      <x:c r="C188" s="31"/>
+      <x:c r="D188" s="31"/>
+      <x:c r="E188" s="31"/>
+      <x:c r="F188" s="31"/>
+      <x:c r="G188" s="31"/>
+      <x:c r="H188" s="31"/>
+      <x:c r="I188" s="31"/>
+      <x:c r="J188" s="31"/>
+      <x:c r="K188" s="31"/>
+      <x:c r="L188" s="31"/>
+      <x:c r="M188" s="31"/>
+      <x:c r="N188" s="31"/>
+      <x:c r="O188" s="31"/>
+      <x:c r="P188" s="31"/>
+      <x:c r="Q188" s="31"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="31"/>
+      <x:c r="B189" s="31"/>
+      <x:c r="C189" s="31"/>
+      <x:c r="D189" s="31"/>
+      <x:c r="E189" s="31"/>
+      <x:c r="F189" s="31"/>
+      <x:c r="G189" s="31"/>
+      <x:c r="H189" s="31"/>
+      <x:c r="I189" s="31"/>
+      <x:c r="J189" s="31"/>
+      <x:c r="K189" s="31"/>
+      <x:c r="L189" s="31"/>
+      <x:c r="M189" s="31"/>
+      <x:c r="N189" s="31"/>
+      <x:c r="O189" s="31"/>
+      <x:c r="P189" s="31"/>
+      <x:c r="Q189" s="31"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="31"/>
+      <x:c r="B190" s="31"/>
+      <x:c r="C190" s="31"/>
+      <x:c r="D190" s="31"/>
+      <x:c r="E190" s="31"/>
+      <x:c r="F190" s="31"/>
+      <x:c r="G190" s="31"/>
+      <x:c r="H190" s="31"/>
+      <x:c r="I190" s="31"/>
+      <x:c r="J190" s="31"/>
+      <x:c r="K190" s="31"/>
+      <x:c r="L190" s="31"/>
+      <x:c r="M190" s="31"/>
+      <x:c r="N190" s="31"/>
+      <x:c r="O190" s="31"/>
+      <x:c r="P190" s="31"/>
+      <x:c r="Q190" s="31"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="31"/>
+      <x:c r="B191" s="31"/>
+      <x:c r="C191" s="31"/>
+      <x:c r="D191" s="31"/>
+      <x:c r="E191" s="31"/>
+      <x:c r="F191" s="31"/>
+      <x:c r="G191" s="31"/>
+      <x:c r="H191" s="31"/>
+      <x:c r="I191" s="31"/>
+      <x:c r="J191" s="31"/>
+      <x:c r="K191" s="31"/>
+      <x:c r="L191" s="31"/>
+      <x:c r="M191" s="31"/>
+      <x:c r="N191" s="31"/>
+      <x:c r="O191" s="31"/>
+      <x:c r="P191" s="31"/>
+      <x:c r="Q191" s="31"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="31"/>
+      <x:c r="B192" s="31"/>
+      <x:c r="C192" s="31"/>
+      <x:c r="D192" s="31"/>
+      <x:c r="E192" s="31"/>
+      <x:c r="F192" s="31"/>
+      <x:c r="G192" s="31"/>
+      <x:c r="H192" s="31"/>
+      <x:c r="I192" s="31"/>
+      <x:c r="J192" s="31"/>
+      <x:c r="K192" s="31"/>
+      <x:c r="L192" s="31"/>
+      <x:c r="M192" s="31"/>
+      <x:c r="N192" s="31"/>
+      <x:c r="O192" s="31"/>
+      <x:c r="P192" s="31"/>
+      <x:c r="Q192" s="31"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="31"/>
+      <x:c r="B193" s="31"/>
+      <x:c r="C193" s="31"/>
+      <x:c r="D193" s="31"/>
+      <x:c r="E193" s="31"/>
+      <x:c r="F193" s="31"/>
+      <x:c r="G193" s="31"/>
+      <x:c r="H193" s="31"/>
+      <x:c r="I193" s="31"/>
+      <x:c r="J193" s="31"/>
+      <x:c r="K193" s="31"/>
+      <x:c r="L193" s="31"/>
+      <x:c r="M193" s="31"/>
+      <x:c r="N193" s="31"/>
+      <x:c r="O193" s="31"/>
+      <x:c r="P193" s="31"/>
+      <x:c r="Q193" s="31"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="31"/>
+      <x:c r="B194" s="31"/>
+      <x:c r="C194" s="31"/>
+      <x:c r="D194" s="31"/>
+      <x:c r="E194" s="31"/>
+      <x:c r="F194" s="31"/>
+      <x:c r="G194" s="31"/>
+      <x:c r="H194" s="31"/>
+      <x:c r="I194" s="31"/>
+      <x:c r="J194" s="31"/>
+      <x:c r="K194" s="31"/>
+      <x:c r="L194" s="31"/>
+      <x:c r="M194" s="31"/>
+      <x:c r="N194" s="31"/>
+      <x:c r="O194" s="31"/>
+      <x:c r="P194" s="31"/>
+      <x:c r="Q194" s="31"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="31"/>
+      <x:c r="B195" s="31"/>
+      <x:c r="C195" s="31"/>
+      <x:c r="D195" s="31"/>
+      <x:c r="E195" s="31"/>
+      <x:c r="F195" s="31"/>
+      <x:c r="G195" s="31"/>
+      <x:c r="H195" s="31"/>
+      <x:c r="I195" s="31"/>
+      <x:c r="J195" s="31"/>
+      <x:c r="K195" s="31"/>
+      <x:c r="L195" s="31"/>
+      <x:c r="M195" s="31"/>
+      <x:c r="N195" s="31"/>
+      <x:c r="O195" s="31"/>
+      <x:c r="P195" s="31"/>
+      <x:c r="Q195" s="31"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="31"/>
+      <x:c r="B196" s="31"/>
+      <x:c r="C196" s="31"/>
+      <x:c r="D196" s="31"/>
+      <x:c r="E196" s="31"/>
+      <x:c r="F196" s="31"/>
+      <x:c r="G196" s="31"/>
+      <x:c r="H196" s="31"/>
+      <x:c r="I196" s="31"/>
+      <x:c r="J196" s="31"/>
+      <x:c r="K196" s="31"/>
+      <x:c r="L196" s="31"/>
+      <x:c r="M196" s="31"/>
+      <x:c r="N196" s="31"/>
+      <x:c r="O196" s="31"/>
+      <x:c r="P196" s="31"/>
+      <x:c r="Q196" s="31"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="31"/>
+      <x:c r="B197" s="31"/>
+      <x:c r="C197" s="31"/>
+      <x:c r="D197" s="31"/>
+      <x:c r="E197" s="31"/>
+      <x:c r="F197" s="31"/>
+      <x:c r="G197" s="31"/>
+      <x:c r="H197" s="31"/>
+      <x:c r="I197" s="31"/>
+      <x:c r="J197" s="31"/>
+      <x:c r="K197" s="31"/>
+      <x:c r="L197" s="31"/>
+      <x:c r="M197" s="31"/>
+      <x:c r="N197" s="31"/>
+      <x:c r="O197" s="31"/>
+      <x:c r="P197" s="31"/>
+      <x:c r="Q197" s="31"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="31"/>
+      <x:c r="B198" s="31"/>
+      <x:c r="C198" s="31"/>
+      <x:c r="D198" s="31"/>
+      <x:c r="E198" s="31"/>
+      <x:c r="F198" s="31"/>
+      <x:c r="G198" s="31"/>
+      <x:c r="H198" s="31"/>
+      <x:c r="I198" s="31"/>
+      <x:c r="J198" s="31"/>
+      <x:c r="K198" s="31"/>
+      <x:c r="L198" s="31"/>
+      <x:c r="M198" s="31"/>
+      <x:c r="N198" s="31"/>
+      <x:c r="O198" s="31"/>
+      <x:c r="P198" s="31"/>
+      <x:c r="Q198" s="31"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="31"/>
+      <x:c r="B199" s="31"/>
+      <x:c r="C199" s="31"/>
+      <x:c r="D199" s="31"/>
+      <x:c r="E199" s="31"/>
+      <x:c r="F199" s="31"/>
+      <x:c r="G199" s="31"/>
+      <x:c r="H199" s="31"/>
+      <x:c r="I199" s="31"/>
+      <x:c r="J199" s="31"/>
+      <x:c r="K199" s="31"/>
+      <x:c r="L199" s="31"/>
+      <x:c r="M199" s="31"/>
+      <x:c r="N199" s="31"/>
+      <x:c r="O199" s="31"/>
+      <x:c r="P199" s="31"/>
+      <x:c r="Q199" s="31"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="31"/>
+      <x:c r="B200" s="31"/>
+      <x:c r="C200" s="31"/>
+      <x:c r="D200" s="31"/>
+      <x:c r="E200" s="31"/>
+      <x:c r="F200" s="31"/>
+      <x:c r="G200" s="31"/>
+      <x:c r="H200" s="31"/>
+      <x:c r="I200" s="31"/>
+      <x:c r="J200" s="31"/>
+      <x:c r="K200" s="31"/>
+      <x:c r="L200" s="31"/>
+      <x:c r="M200" s="31"/>
+      <x:c r="N200" s="31"/>
+      <x:c r="O200" s="31"/>
+      <x:c r="P200" s="31"/>
+      <x:c r="Q200" s="31"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="31"/>
+      <x:c r="B201" s="31"/>
+      <x:c r="C201" s="31"/>
+      <x:c r="D201" s="31"/>
+      <x:c r="E201" s="31"/>
+      <x:c r="F201" s="31"/>
+      <x:c r="G201" s="31"/>
+      <x:c r="H201" s="31"/>
+      <x:c r="I201" s="31"/>
+      <x:c r="J201" s="31"/>
+      <x:c r="K201" s="31"/>
+      <x:c r="L201" s="31"/>
+      <x:c r="M201" s="31"/>
+      <x:c r="N201" s="31"/>
+      <x:c r="O201" s="31"/>
+      <x:c r="P201" s="31"/>
+      <x:c r="Q201" s="31"/>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="31"/>
+      <x:c r="B202" s="31"/>
+      <x:c r="C202" s="31"/>
+      <x:c r="D202" s="31"/>
+      <x:c r="E202" s="31"/>
+      <x:c r="F202" s="31"/>
+      <x:c r="G202" s="31"/>
+      <x:c r="H202" s="31"/>
+      <x:c r="I202" s="31"/>
+      <x:c r="J202" s="31"/>
+      <x:c r="K202" s="31"/>
+      <x:c r="L202" s="31"/>
+      <x:c r="M202" s="31"/>
+      <x:c r="N202" s="31"/>
+      <x:c r="O202" s="31"/>
+      <x:c r="P202" s="31"/>
+      <x:c r="Q202" s="31"/>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="31"/>
+      <x:c r="B203" s="31"/>
+      <x:c r="C203" s="31"/>
+      <x:c r="D203" s="31"/>
+      <x:c r="E203" s="31"/>
+      <x:c r="F203" s="31"/>
+      <x:c r="G203" s="31"/>
+      <x:c r="H203" s="31"/>
+      <x:c r="I203" s="31"/>
+      <x:c r="J203" s="31"/>
+      <x:c r="K203" s="31"/>
+      <x:c r="L203" s="31"/>
+      <x:c r="M203" s="31"/>
+      <x:c r="N203" s="31"/>
+      <x:c r="O203" s="31"/>
+      <x:c r="P203" s="31"/>
+      <x:c r="Q203" s="31"/>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="31"/>
+      <x:c r="B204" s="31"/>
+      <x:c r="C204" s="31"/>
+      <x:c r="D204" s="31"/>
+      <x:c r="E204" s="31"/>
+      <x:c r="F204" s="31"/>
+      <x:c r="G204" s="31"/>
+      <x:c r="H204" s="31"/>
+      <x:c r="I204" s="31"/>
+      <x:c r="J204" s="31"/>
+      <x:c r="K204" s="31"/>
+      <x:c r="L204" s="31"/>
+      <x:c r="M204" s="31"/>
+      <x:c r="N204" s="31"/>
+      <x:c r="O204" s="31"/>
+      <x:c r="P204" s="31"/>
+      <x:c r="Q204" s="31"/>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="31"/>
+      <x:c r="B205" s="31"/>
+      <x:c r="C205" s="31"/>
+      <x:c r="D205" s="31"/>
+      <x:c r="E205" s="31"/>
+      <x:c r="F205" s="31"/>
+      <x:c r="G205" s="31"/>
+      <x:c r="H205" s="31"/>
+      <x:c r="I205" s="31"/>
+      <x:c r="J205" s="31"/>
+      <x:c r="K205" s="31"/>
+      <x:c r="L205" s="31"/>
+      <x:c r="M205" s="31"/>
+      <x:c r="N205" s="31"/>
+      <x:c r="O205" s="31"/>
+      <x:c r="P205" s="31"/>
+      <x:c r="Q205" s="31"/>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="31"/>
+      <x:c r="B206" s="31"/>
+      <x:c r="C206" s="31"/>
+      <x:c r="D206" s="31"/>
+      <x:c r="E206" s="31"/>
+      <x:c r="F206" s="31"/>
+      <x:c r="G206" s="31"/>
+      <x:c r="H206" s="31"/>
+      <x:c r="I206" s="31"/>
+      <x:c r="J206" s="31"/>
+      <x:c r="K206" s="31"/>
+      <x:c r="L206" s="31"/>
+      <x:c r="M206" s="31"/>
+      <x:c r="N206" s="31"/>
+      <x:c r="O206" s="31"/>
+      <x:c r="P206" s="31"/>
+      <x:c r="Q206" s="31"/>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="31"/>
+      <x:c r="B207" s="31"/>
+      <x:c r="C207" s="31"/>
+      <x:c r="D207" s="31"/>
+      <x:c r="E207" s="31"/>
+      <x:c r="F207" s="31"/>
+      <x:c r="G207" s="31"/>
+      <x:c r="H207" s="31"/>
+      <x:c r="I207" s="31"/>
+      <x:c r="J207" s="31"/>
+      <x:c r="K207" s="31"/>
+      <x:c r="L207" s="31"/>
+      <x:c r="M207" s="31"/>
+      <x:c r="N207" s="31"/>
+      <x:c r="O207" s="31"/>
+      <x:c r="P207" s="31"/>
+      <x:c r="Q207" s="31"/>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="31"/>
+      <x:c r="B208" s="31"/>
+      <x:c r="C208" s="31"/>
+      <x:c r="D208" s="31"/>
+      <x:c r="E208" s="31"/>
+      <x:c r="F208" s="31"/>
+      <x:c r="G208" s="31"/>
+      <x:c r="H208" s="31"/>
+      <x:c r="I208" s="31"/>
+      <x:c r="J208" s="31"/>
+      <x:c r="K208" s="31"/>
+      <x:c r="L208" s="31"/>
+      <x:c r="M208" s="31"/>
+      <x:c r="N208" s="31"/>
+      <x:c r="O208" s="31"/>
+      <x:c r="P208" s="31"/>
+      <x:c r="Q208" s="31"/>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="31"/>
+      <x:c r="B209" s="31"/>
+      <x:c r="C209" s="31"/>
+      <x:c r="D209" s="31"/>
+      <x:c r="E209" s="31"/>
+      <x:c r="F209" s="31"/>
+      <x:c r="G209" s="31"/>
+      <x:c r="H209" s="31"/>
+      <x:c r="I209" s="31"/>
+      <x:c r="J209" s="31"/>
+      <x:c r="K209" s="31"/>
+      <x:c r="L209" s="31"/>
+      <x:c r="M209" s="31"/>
+      <x:c r="N209" s="31"/>
+      <x:c r="O209" s="31"/>
+      <x:c r="P209" s="31"/>
+      <x:c r="Q209" s="31"/>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="31"/>
+      <x:c r="B210" s="31"/>
+      <x:c r="C210" s="31"/>
+      <x:c r="D210" s="31"/>
+      <x:c r="E210" s="31"/>
+      <x:c r="F210" s="31"/>
+      <x:c r="G210" s="31"/>
+      <x:c r="H210" s="31"/>
+      <x:c r="I210" s="31"/>
+      <x:c r="J210" s="31"/>
+      <x:c r="K210" s="31"/>
+      <x:c r="L210" s="31"/>
+      <x:c r="M210" s="31"/>
+      <x:c r="N210" s="31"/>
+      <x:c r="O210" s="31"/>
+      <x:c r="P210" s="31"/>
+      <x:c r="Q210" s="31"/>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="31"/>
+      <x:c r="B211" s="31"/>
+      <x:c r="C211" s="31"/>
+      <x:c r="D211" s="31"/>
+      <x:c r="E211" s="31"/>
+      <x:c r="F211" s="31"/>
+      <x:c r="G211" s="31"/>
+      <x:c r="H211" s="31"/>
+      <x:c r="I211" s="31"/>
+      <x:c r="J211" s="31"/>
+      <x:c r="K211" s="31"/>
+      <x:c r="L211" s="31"/>
+      <x:c r="M211" s="31"/>
+      <x:c r="N211" s="31"/>
+      <x:c r="O211" s="31"/>
+      <x:c r="P211" s="31"/>
+      <x:c r="Q211" s="31"/>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="31"/>
+      <x:c r="B212" s="31"/>
+      <x:c r="C212" s="31"/>
+      <x:c r="D212" s="31"/>
+      <x:c r="E212" s="31"/>
+      <x:c r="F212" s="31"/>
+      <x:c r="G212" s="31"/>
+      <x:c r="H212" s="31"/>
+      <x:c r="I212" s="31"/>
+      <x:c r="J212" s="31"/>
+      <x:c r="K212" s="31"/>
+      <x:c r="L212" s="31"/>
+      <x:c r="M212" s="31"/>
+      <x:c r="N212" s="31"/>
+      <x:c r="O212" s="31"/>
+      <x:c r="P212" s="31"/>
+      <x:c r="Q212" s="31"/>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="31"/>
+      <x:c r="B213" s="31"/>
+      <x:c r="C213" s="31"/>
+      <x:c r="D213" s="31"/>
+      <x:c r="E213" s="31"/>
+      <x:c r="F213" s="31"/>
+      <x:c r="G213" s="31"/>
+      <x:c r="H213" s="31"/>
+      <x:c r="I213" s="31"/>
+      <x:c r="J213" s="31"/>
+      <x:c r="K213" s="31"/>
+      <x:c r="L213" s="31"/>
+      <x:c r="M213" s="31"/>
+      <x:c r="N213" s="31"/>
+      <x:c r="O213" s="31"/>
+      <x:c r="P213" s="31"/>
+      <x:c r="Q213" s="31"/>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="31"/>
+      <x:c r="B214" s="31"/>
+      <x:c r="C214" s="31"/>
+      <x:c r="D214" s="31"/>
+      <x:c r="E214" s="31"/>
+      <x:c r="F214" s="31"/>
+      <x:c r="G214" s="31"/>
+      <x:c r="H214" s="31"/>
+      <x:c r="I214" s="31"/>
+      <x:c r="J214" s="31"/>
+      <x:c r="K214" s="31"/>
+      <x:c r="L214" s="31"/>
+      <x:c r="M214" s="31"/>
+      <x:c r="N214" s="31"/>
+      <x:c r="O214" s="31"/>
+      <x:c r="P214" s="31"/>
+      <x:c r="Q214" s="31"/>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="31"/>
+      <x:c r="B215" s="31"/>
+      <x:c r="C215" s="31"/>
+      <x:c r="D215" s="31"/>
+      <x:c r="E215" s="31"/>
+      <x:c r="F215" s="31"/>
+      <x:c r="G215" s="31"/>
+      <x:c r="H215" s="31"/>
+      <x:c r="I215" s="31"/>
+      <x:c r="J215" s="31"/>
+      <x:c r="K215" s="31"/>
+      <x:c r="L215" s="31"/>
+      <x:c r="M215" s="31"/>
+      <x:c r="N215" s="31"/>
+      <x:c r="O215" s="31"/>
+      <x:c r="P215" s="31"/>
+      <x:c r="Q215" s="31"/>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="31"/>
+      <x:c r="B216" s="31"/>
+      <x:c r="C216" s="31"/>
+      <x:c r="D216" s="31"/>
+      <x:c r="E216" s="31"/>
+      <x:c r="F216" s="31"/>
+      <x:c r="G216" s="31"/>
+      <x:c r="H216" s="31"/>
+      <x:c r="I216" s="31"/>
+      <x:c r="J216" s="31"/>
+      <x:c r="K216" s="31"/>
+      <x:c r="L216" s="31"/>
+      <x:c r="M216" s="31"/>
+      <x:c r="N216" s="31"/>
+      <x:c r="O216" s="31"/>
+      <x:c r="P216" s="31"/>
+      <x:c r="Q216" s="31"/>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="31"/>
+      <x:c r="B217" s="31"/>
+      <x:c r="C217" s="31"/>
+      <x:c r="D217" s="31"/>
+      <x:c r="E217" s="31"/>
+      <x:c r="F217" s="31"/>
+      <x:c r="G217" s="31"/>
+      <x:c r="H217" s="31"/>
+      <x:c r="I217" s="31"/>
+      <x:c r="J217" s="31"/>
+      <x:c r="K217" s="31"/>
+      <x:c r="L217" s="31"/>
+      <x:c r="M217" s="31"/>
+      <x:c r="N217" s="31"/>
+      <x:c r="O217" s="31"/>
+      <x:c r="P217" s="31"/>
+      <x:c r="Q217" s="31"/>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="31"/>
+      <x:c r="B218" s="31"/>
+      <x:c r="C218" s="31"/>
+      <x:c r="D218" s="31"/>
+      <x:c r="E218" s="31"/>
+      <x:c r="F218" s="31"/>
+      <x:c r="G218" s="31"/>
+      <x:c r="H218" s="31"/>
+      <x:c r="I218" s="31"/>
+      <x:c r="J218" s="31"/>
+      <x:c r="K218" s="31"/>
+      <x:c r="L218" s="31"/>
+      <x:c r="M218" s="31"/>
+      <x:c r="N218" s="31"/>
+      <x:c r="O218" s="31"/>
+      <x:c r="P218" s="31"/>
+      <x:c r="Q218" s="31"/>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="31"/>
+      <x:c r="B219" s="31"/>
+      <x:c r="C219" s="31"/>
+      <x:c r="D219" s="31"/>
+      <x:c r="E219" s="31"/>
+      <x:c r="F219" s="31"/>
+      <x:c r="G219" s="31"/>
+      <x:c r="H219" s="31"/>
+      <x:c r="I219" s="31"/>
+      <x:c r="J219" s="31"/>
+      <x:c r="K219" s="31"/>
+      <x:c r="L219" s="31"/>
+      <x:c r="M219" s="31"/>
+      <x:c r="N219" s="31"/>
+      <x:c r="O219" s="31"/>
+      <x:c r="P219" s="31"/>
+      <x:c r="Q219" s="31"/>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="31"/>
+      <x:c r="B220" s="31"/>
+      <x:c r="C220" s="31"/>
+      <x:c r="D220" s="31"/>
+      <x:c r="E220" s="31"/>
+      <x:c r="F220" s="31"/>
+      <x:c r="G220" s="31"/>
+      <x:c r="H220" s="31"/>
+      <x:c r="I220" s="31"/>
+      <x:c r="J220" s="31"/>
+      <x:c r="K220" s="31"/>
+      <x:c r="L220" s="31"/>
+      <x:c r="M220" s="31"/>
+      <x:c r="N220" s="31"/>
+      <x:c r="O220" s="31"/>
+      <x:c r="P220" s="31"/>
+      <x:c r="Q220" s="31"/>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="31"/>
+      <x:c r="B221" s="31"/>
+      <x:c r="C221" s="31"/>
+      <x:c r="D221" s="31"/>
+      <x:c r="E221" s="31"/>
+      <x:c r="F221" s="31"/>
+      <x:c r="G221" s="31"/>
+      <x:c r="H221" s="31"/>
+      <x:c r="I221" s="31"/>
+      <x:c r="J221" s="31"/>
+      <x:c r="K221" s="31"/>
+      <x:c r="L221" s="31"/>
+      <x:c r="M221" s="31"/>
+      <x:c r="N221" s="31"/>
+      <x:c r="O221" s="31"/>
+      <x:c r="P221" s="31"/>
+      <x:c r="Q221" s="31"/>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="31"/>
+      <x:c r="B222" s="31"/>
+      <x:c r="C222" s="31"/>
+      <x:c r="D222" s="31"/>
+      <x:c r="E222" s="31"/>
+      <x:c r="F222" s="31"/>
+      <x:c r="G222" s="31"/>
+      <x:c r="H222" s="31"/>
+      <x:c r="I222" s="31"/>
+      <x:c r="J222" s="31"/>
+      <x:c r="K222" s="31"/>
+      <x:c r="L222" s="31"/>
+      <x:c r="M222" s="31"/>
+      <x:c r="N222" s="31"/>
+      <x:c r="O222" s="31"/>
+      <x:c r="P222" s="31"/>
+      <x:c r="Q222" s="31"/>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="31"/>
+      <x:c r="B223" s="31"/>
+      <x:c r="C223" s="31"/>
+      <x:c r="D223" s="31"/>
+      <x:c r="E223" s="31"/>
+      <x:c r="F223" s="31"/>
+      <x:c r="G223" s="31"/>
+      <x:c r="H223" s="31"/>
+      <x:c r="I223" s="31"/>
+      <x:c r="J223" s="31"/>
+      <x:c r="K223" s="31"/>
+      <x:c r="L223" s="31"/>
+      <x:c r="M223" s="31"/>
+      <x:c r="N223" s="31"/>
+      <x:c r="O223" s="31"/>
+      <x:c r="P223" s="31"/>
+      <x:c r="Q223" s="31"/>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="31"/>
+      <x:c r="B224" s="31"/>
+      <x:c r="C224" s="31"/>
+      <x:c r="D224" s="31"/>
+      <x:c r="E224" s="31"/>
+      <x:c r="F224" s="31"/>
+      <x:c r="G224" s="31"/>
+      <x:c r="H224" s="31"/>
+      <x:c r="I224" s="31"/>
+      <x:c r="J224" s="31"/>
+      <x:c r="K224" s="31"/>
+      <x:c r="L224" s="31"/>
+      <x:c r="M224" s="31"/>
+      <x:c r="N224" s="31"/>
+      <x:c r="O224" s="31"/>
+      <x:c r="P224" s="31"/>
+      <x:c r="Q224" s="31"/>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="31"/>
+      <x:c r="B225" s="31"/>
+      <x:c r="C225" s="31"/>
+      <x:c r="D225" s="31"/>
+      <x:c r="E225" s="31"/>
+      <x:c r="F225" s="31"/>
+      <x:c r="G225" s="31"/>
+      <x:c r="H225" s="31"/>
+      <x:c r="I225" s="31"/>
+      <x:c r="J225" s="31"/>
+      <x:c r="K225" s="31"/>
+      <x:c r="L225" s="31"/>
+      <x:c r="M225" s="31"/>
+      <x:c r="N225" s="31"/>
+      <x:c r="O225" s="31"/>
+      <x:c r="P225" s="31"/>
+      <x:c r="Q225" s="31"/>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="31"/>
+      <x:c r="B226" s="31"/>
+      <x:c r="C226" s="31"/>
+      <x:c r="D226" s="31"/>
+      <x:c r="E226" s="31"/>
+      <x:c r="F226" s="31"/>
+      <x:c r="G226" s="31"/>
+      <x:c r="H226" s="31"/>
+      <x:c r="I226" s="31"/>
+      <x:c r="J226" s="31"/>
+      <x:c r="K226" s="31"/>
+      <x:c r="L226" s="31"/>
+      <x:c r="M226" s="31"/>
+      <x:c r="N226" s="31"/>
+      <x:c r="O226" s="31"/>
+      <x:c r="P226" s="31"/>
+      <x:c r="Q226" s="31"/>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="31"/>
+      <x:c r="B227" s="31"/>
+      <x:c r="C227" s="31"/>
+      <x:c r="D227" s="31"/>
+      <x:c r="E227" s="31"/>
+      <x:c r="F227" s="31"/>
+      <x:c r="G227" s="31"/>
+      <x:c r="H227" s="31"/>
+      <x:c r="I227" s="31"/>
+      <x:c r="J227" s="31"/>
+      <x:c r="K227" s="31"/>
+      <x:c r="L227" s="31"/>
+      <x:c r="M227" s="31"/>
+      <x:c r="N227" s="31"/>
+      <x:c r="O227" s="31"/>
+      <x:c r="P227" s="31"/>
+      <x:c r="Q227" s="31"/>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="31"/>
+      <x:c r="B228" s="31"/>
+      <x:c r="C228" s="31"/>
+      <x:c r="D228" s="31"/>
+      <x:c r="E228" s="31"/>
+      <x:c r="F228" s="31"/>
+      <x:c r="G228" s="31"/>
+      <x:c r="H228" s="31"/>
+      <x:c r="I228" s="31"/>
+      <x:c r="J228" s="31"/>
+      <x:c r="K228" s="31"/>
+      <x:c r="L228" s="31"/>
+      <x:c r="M228" s="31"/>
+      <x:c r="N228" s="31"/>
+      <x:c r="O228" s="31"/>
+      <x:c r="P228" s="31"/>
+      <x:c r="Q228" s="31"/>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="31"/>
+      <x:c r="B229" s="31"/>
+      <x:c r="C229" s="31"/>
+      <x:c r="D229" s="31"/>
+      <x:c r="E229" s="31"/>
+      <x:c r="F229" s="31"/>
+      <x:c r="G229" s="31"/>
+      <x:c r="H229" s="31"/>
+      <x:c r="I229" s="31"/>
+      <x:c r="J229" s="31"/>
+      <x:c r="K229" s="31"/>
+      <x:c r="L229" s="31"/>
+      <x:c r="M229" s="31"/>
+      <x:c r="N229" s="31"/>
+      <x:c r="O229" s="31"/>
+      <x:c r="P229" s="31"/>
+      <x:c r="Q229" s="31"/>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="31"/>
+      <x:c r="B230" s="31"/>
+      <x:c r="C230" s="31"/>
+      <x:c r="D230" s="31"/>
+      <x:c r="E230" s="31"/>
+      <x:c r="F230" s="31"/>
+      <x:c r="G230" s="31"/>
+      <x:c r="H230" s="31"/>
+      <x:c r="I230" s="31"/>
+      <x:c r="J230" s="31"/>
+      <x:c r="K230" s="31"/>
+      <x:c r="L230" s="31"/>
+      <x:c r="M230" s="31"/>
+      <x:c r="N230" s="31"/>
+      <x:c r="O230" s="31"/>
+      <x:c r="P230" s="31"/>
+      <x:c r="Q230" s="31"/>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="31"/>
+      <x:c r="B231" s="31"/>
+      <x:c r="C231" s="31"/>
+      <x:c r="D231" s="31"/>
+      <x:c r="E231" s="31"/>
+      <x:c r="F231" s="31"/>
+      <x:c r="G231" s="31"/>
+      <x:c r="H231" s="31"/>
+      <x:c r="I231" s="31"/>
+      <x:c r="J231" s="31"/>
+      <x:c r="K231" s="31"/>
+      <x:c r="L231" s="31"/>
+      <x:c r="M231" s="31"/>
+      <x:c r="N231" s="31"/>
+      <x:c r="O231" s="31"/>
+      <x:c r="P231" s="31"/>
+      <x:c r="Q231" s="31"/>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="31"/>
+      <x:c r="B232" s="31"/>
+      <x:c r="C232" s="31"/>
+      <x:c r="D232" s="31"/>
+      <x:c r="E232" s="31"/>
+      <x:c r="F232" s="31"/>
+      <x:c r="G232" s="31"/>
+      <x:c r="H232" s="31"/>
+      <x:c r="I232" s="31"/>
+      <x:c r="J232" s="31"/>
+      <x:c r="K232" s="31"/>
+      <x:c r="L232" s="31"/>
+      <x:c r="M232" s="31"/>
+      <x:c r="N232" s="31"/>
+      <x:c r="O232" s="31"/>
+      <x:c r="P232" s="31"/>
+      <x:c r="Q232" s="31"/>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="31"/>
+      <x:c r="B233" s="31"/>
+      <x:c r="C233" s="31"/>
+      <x:c r="D233" s="31"/>
+      <x:c r="E233" s="31"/>
+      <x:c r="F233" s="31"/>
+      <x:c r="G233" s="31"/>
+      <x:c r="H233" s="31"/>
+      <x:c r="I233" s="31"/>
+      <x:c r="J233" s="31"/>
+      <x:c r="K233" s="31"/>
+      <x:c r="L233" s="31"/>
+      <x:c r="M233" s="31"/>
+      <x:c r="N233" s="31"/>
+      <x:c r="O233" s="31"/>
+      <x:c r="P233" s="31"/>
+      <x:c r="Q233" s="31"/>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="31"/>
+      <x:c r="B234" s="31"/>
+      <x:c r="C234" s="31"/>
+      <x:c r="D234" s="31"/>
+      <x:c r="E234" s="31"/>
+      <x:c r="F234" s="31"/>
+      <x:c r="G234" s="31"/>
+      <x:c r="H234" s="31"/>
+      <x:c r="I234" s="31"/>
+      <x:c r="J234" s="31"/>
+      <x:c r="K234" s="31"/>
+      <x:c r="L234" s="31"/>
+      <x:c r="M234" s="31"/>
+      <x:c r="N234" s="31"/>
+      <x:c r="O234" s="31"/>
+      <x:c r="P234" s="31"/>
+      <x:c r="Q234" s="31"/>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="31"/>
+      <x:c r="B235" s="31"/>
+      <x:c r="C235" s="31"/>
+      <x:c r="D235" s="31"/>
+      <x:c r="E235" s="31"/>
+      <x:c r="F235" s="31"/>
+      <x:c r="G235" s="31"/>
+      <x:c r="H235" s="31"/>
+      <x:c r="I235" s="31"/>
+      <x:c r="J235" s="31"/>
+      <x:c r="K235" s="31"/>
+      <x:c r="L235" s="31"/>
+      <x:c r="M235" s="31"/>
+      <x:c r="N235" s="31"/>
+      <x:c r="O235" s="31"/>
+      <x:c r="P235" s="31"/>
+      <x:c r="Q235" s="31"/>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="31"/>
+      <x:c r="B236" s="31"/>
+      <x:c r="C236" s="31"/>
+      <x:c r="D236" s="31"/>
+      <x:c r="E236" s="31"/>
+      <x:c r="F236" s="31"/>
+      <x:c r="G236" s="31"/>
+      <x:c r="H236" s="31"/>
+      <x:c r="I236" s="31"/>
+      <x:c r="J236" s="31"/>
+      <x:c r="K236" s="31"/>
+      <x:c r="L236" s="31"/>
+      <x:c r="M236" s="31"/>
+      <x:c r="N236" s="31"/>
+      <x:c r="O236" s="31"/>
+      <x:c r="P236" s="31"/>
+      <x:c r="Q236" s="31"/>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="31"/>
+      <x:c r="B237" s="31"/>
+      <x:c r="C237" s="31"/>
+      <x:c r="D237" s="31"/>
+      <x:c r="E237" s="31"/>
+      <x:c r="F237" s="31"/>
+      <x:c r="G237" s="31"/>
+      <x:c r="H237" s="31"/>
+      <x:c r="I237" s="31"/>
+      <x:c r="J237" s="31"/>
+      <x:c r="K237" s="31"/>
+      <x:c r="L237" s="31"/>
+      <x:c r="M237" s="31"/>
+      <x:c r="N237" s="31"/>
+      <x:c r="O237" s="31"/>
+      <x:c r="P237" s="31"/>
+      <x:c r="Q237" s="31"/>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="31"/>
+      <x:c r="B238" s="31"/>
+      <x:c r="C238" s="31"/>
+      <x:c r="D238" s="31"/>
+      <x:c r="E238" s="31"/>
+      <x:c r="F238" s="31"/>
+      <x:c r="G238" s="31"/>
+      <x:c r="H238" s="31"/>
+      <x:c r="I238" s="31"/>
+      <x:c r="J238" s="31"/>
+      <x:c r="K238" s="31"/>
+      <x:c r="L238" s="31"/>
+      <x:c r="M238" s="31"/>
+      <x:c r="N238" s="31"/>
+      <x:c r="O238" s="31"/>
+      <x:c r="P238" s="31"/>
+      <x:c r="Q238" s="31"/>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="31"/>
+      <x:c r="B239" s="31"/>
+      <x:c r="C239" s="31"/>
+      <x:c r="D239" s="31"/>
+      <x:c r="E239" s="31"/>
+      <x:c r="F239" s="31"/>
+      <x:c r="G239" s="31"/>
+      <x:c r="H239" s="31"/>
+      <x:c r="I239" s="31"/>
+      <x:c r="J239" s="31"/>
+      <x:c r="K239" s="31"/>
+      <x:c r="L239" s="31"/>
+      <x:c r="M239" s="31"/>
+      <x:c r="N239" s="31"/>
+      <x:c r="O239" s="31"/>
+      <x:c r="P239" s="31"/>
+      <x:c r="Q239" s="31"/>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="31"/>
+      <x:c r="B240" s="31"/>
+      <x:c r="C240" s="31"/>
+      <x:c r="D240" s="31"/>
+      <x:c r="E240" s="31"/>
+      <x:c r="F240" s="31"/>
+      <x:c r="G240" s="31"/>
+      <x:c r="H240" s="31"/>
+      <x:c r="I240" s="31"/>
+      <x:c r="J240" s="31"/>
+      <x:c r="K240" s="31"/>
+      <x:c r="L240" s="31"/>
+      <x:c r="M240" s="31"/>
+      <x:c r="N240" s="31"/>
+      <x:c r="O240" s="31"/>
+      <x:c r="P240" s="31"/>
+      <x:c r="Q240" s="31"/>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="31"/>
+      <x:c r="B241" s="31"/>
+      <x:c r="C241" s="31"/>
+      <x:c r="D241" s="31"/>
+      <x:c r="E241" s="31"/>
+      <x:c r="F241" s="31"/>
+      <x:c r="G241" s="31"/>
+      <x:c r="H241" s="31"/>
+      <x:c r="I241" s="31"/>
+      <x:c r="J241" s="31"/>
+      <x:c r="K241" s="31"/>
+      <x:c r="L241" s="31"/>
+      <x:c r="M241" s="31"/>
+      <x:c r="N241" s="31"/>
+      <x:c r="O241" s="31"/>
+      <x:c r="P241" s="31"/>
+      <x:c r="Q241" s="31"/>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="31"/>
+      <x:c r="B242" s="31"/>
+      <x:c r="C242" s="31"/>
+      <x:c r="D242" s="31"/>
+      <x:c r="E242" s="31"/>
+      <x:c r="F242" s="31"/>
+      <x:c r="G242" s="31"/>
+      <x:c r="H242" s="31"/>
+      <x:c r="I242" s="31"/>
+      <x:c r="J242" s="31"/>
+      <x:c r="K242" s="31"/>
+      <x:c r="L242" s="31"/>
+      <x:c r="M242" s="31"/>
+      <x:c r="N242" s="31"/>
+      <x:c r="O242" s="31"/>
+      <x:c r="P242" s="31"/>
+      <x:c r="Q242" s="31"/>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="31"/>
+      <x:c r="B243" s="31"/>
+      <x:c r="C243" s="31"/>
+      <x:c r="D243" s="31"/>
+      <x:c r="E243" s="31"/>
+      <x:c r="F243" s="31"/>
+      <x:c r="G243" s="31"/>
+      <x:c r="H243" s="31"/>
+      <x:c r="I243" s="31"/>
+      <x:c r="J243" s="31"/>
+      <x:c r="K243" s="31"/>
+      <x:c r="L243" s="31"/>
+      <x:c r="M243" s="31"/>
+      <x:c r="N243" s="31"/>
+      <x:c r="O243" s="31"/>
+      <x:c r="P243" s="31"/>
+      <x:c r="Q243" s="31"/>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="31"/>
+      <x:c r="B244" s="31"/>
+      <x:c r="C244" s="31"/>
+      <x:c r="D244" s="31"/>
+      <x:c r="E244" s="31"/>
+      <x:c r="F244" s="31"/>
+      <x:c r="G244" s="31"/>
+      <x:c r="H244" s="31"/>
+      <x:c r="I244" s="31"/>
+      <x:c r="J244" s="31"/>
+      <x:c r="K244" s="31"/>
+      <x:c r="L244" s="31"/>
+      <x:c r="M244" s="31"/>
+      <x:c r="N244" s="31"/>
+      <x:c r="O244" s="31"/>
+      <x:c r="P244" s="31"/>
+      <x:c r="Q244" s="31"/>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="31"/>
+      <x:c r="B245" s="31"/>
+      <x:c r="C245" s="31"/>
+      <x:c r="D245" s="31"/>
+      <x:c r="E245" s="31"/>
+      <x:c r="F245" s="31"/>
+      <x:c r="G245" s="31"/>
+      <x:c r="H245" s="31"/>
+      <x:c r="I245" s="31"/>
+      <x:c r="J245" s="31"/>
+      <x:c r="K245" s="31"/>
+      <x:c r="L245" s="31"/>
+      <x:c r="M245" s="31"/>
+      <x:c r="N245" s="31"/>
+      <x:c r="O245" s="31"/>
+      <x:c r="P245" s="31"/>
+      <x:c r="Q245" s="31"/>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="31"/>
+      <x:c r="B246" s="31"/>
+      <x:c r="C246" s="31"/>
+      <x:c r="D246" s="31"/>
+      <x:c r="E246" s="31"/>
+      <x:c r="F246" s="31"/>
+      <x:c r="G246" s="31"/>
+      <x:c r="H246" s="31"/>
+      <x:c r="I246" s="31"/>
+      <x:c r="J246" s="31"/>
+      <x:c r="K246" s="31"/>
+      <x:c r="L246" s="31"/>
+      <x:c r="M246" s="31"/>
+      <x:c r="N246" s="31"/>
+      <x:c r="O246" s="31"/>
+      <x:c r="P246" s="31"/>
+      <x:c r="Q246" s="31"/>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="31"/>
+      <x:c r="B247" s="31"/>
+      <x:c r="C247" s="31"/>
+      <x:c r="D247" s="31"/>
+      <x:c r="E247" s="31"/>
+      <x:c r="F247" s="31"/>
+      <x:c r="G247" s="31"/>
+      <x:c r="H247" s="31"/>
+      <x:c r="I247" s="31"/>
+      <x:c r="J247" s="31"/>
+      <x:c r="K247" s="31"/>
+      <x:c r="L247" s="31"/>
+      <x:c r="M247" s="31"/>
+      <x:c r="N247" s="31"/>
+      <x:c r="O247" s="31"/>
+      <x:c r="P247" s="31"/>
+      <x:c r="Q247" s="31"/>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="31"/>
+      <x:c r="B248" s="31"/>
+      <x:c r="C248" s="31"/>
+      <x:c r="D248" s="31"/>
+      <x:c r="E248" s="31"/>
+      <x:c r="F248" s="31"/>
+      <x:c r="G248" s="31"/>
+      <x:c r="H248" s="31"/>
+      <x:c r="I248" s="31"/>
+      <x:c r="J248" s="31"/>
+      <x:c r="K248" s="31"/>
+      <x:c r="L248" s="31"/>
+      <x:c r="M248" s="31"/>
+      <x:c r="N248" s="31"/>
+      <x:c r="O248" s="31"/>
+      <x:c r="P248" s="31"/>
+      <x:c r="Q248" s="31"/>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="31"/>
+      <x:c r="B249" s="31"/>
+      <x:c r="C249" s="31"/>
+      <x:c r="D249" s="31"/>
+      <x:c r="E249" s="31"/>
+      <x:c r="F249" s="31"/>
+      <x:c r="G249" s="31"/>
+      <x:c r="H249" s="31"/>
+      <x:c r="I249" s="31"/>
+      <x:c r="J249" s="31"/>
+      <x:c r="K249" s="31"/>
+      <x:c r="L249" s="31"/>
+      <x:c r="M249" s="31"/>
+      <x:c r="N249" s="31"/>
+      <x:c r="O249" s="31"/>
+      <x:c r="P249" s="31"/>
+      <x:c r="Q249" s="31"/>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="31"/>
+      <x:c r="B250" s="31"/>
+      <x:c r="C250" s="31"/>
+      <x:c r="D250" s="31"/>
+      <x:c r="E250" s="31"/>
+      <x:c r="F250" s="31"/>
+      <x:c r="G250" s="31"/>
+      <x:c r="H250" s="31"/>
+      <x:c r="I250" s="31"/>
+      <x:c r="J250" s="31"/>
+      <x:c r="K250" s="31"/>
+      <x:c r="L250" s="31"/>
+      <x:c r="M250" s="31"/>
+      <x:c r="N250" s="31"/>
+      <x:c r="O250" s="31"/>
+      <x:c r="P250" s="31"/>
+      <x:c r="Q250" s="31"/>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="31"/>
+      <x:c r="B251" s="31"/>
+      <x:c r="C251" s="31"/>
+      <x:c r="D251" s="31"/>
+      <x:c r="E251" s="31"/>
+      <x:c r="F251" s="31"/>
+      <x:c r="G251" s="31"/>
+      <x:c r="H251" s="31"/>
+      <x:c r="I251" s="31"/>
+      <x:c r="J251" s="31"/>
+      <x:c r="K251" s="31"/>
+      <x:c r="L251" s="31"/>
+      <x:c r="M251" s="31"/>
+      <x:c r="N251" s="31"/>
+      <x:c r="O251" s="31"/>
+      <x:c r="P251" s="31"/>
+      <x:c r="Q251" s="31"/>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="31"/>
+      <x:c r="B252" s="31"/>
+      <x:c r="C252" s="31"/>
+      <x:c r="D252" s="31"/>
+      <x:c r="E252" s="31"/>
+      <x:c r="F252" s="31"/>
+      <x:c r="G252" s="31"/>
+      <x:c r="H252" s="31"/>
+      <x:c r="I252" s="31"/>
+      <x:c r="J252" s="31"/>
+      <x:c r="K252" s="31"/>
+      <x:c r="L252" s="31"/>
+      <x:c r="M252" s="31"/>
+      <x:c r="N252" s="31"/>
+      <x:c r="O252" s="31"/>
+      <x:c r="P252" s="31"/>
+      <x:c r="Q252" s="31"/>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="31"/>
+      <x:c r="B253" s="31"/>
+      <x:c r="C253" s="31"/>
+      <x:c r="D253" s="31"/>
+      <x:c r="E253" s="31"/>
+      <x:c r="F253" s="31"/>
+      <x:c r="G253" s="31"/>
+      <x:c r="H253" s="31"/>
+      <x:c r="I253" s="31"/>
+      <x:c r="J253" s="31"/>
+      <x:c r="K253" s="31"/>
+      <x:c r="L253" s="31"/>
+      <x:c r="M253" s="31"/>
+      <x:c r="N253" s="31"/>
+      <x:c r="O253" s="31"/>
+      <x:c r="P253" s="31"/>
+      <x:c r="Q253" s="31"/>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="31"/>
+      <x:c r="B254" s="31"/>
+      <x:c r="C254" s="31"/>
+      <x:c r="D254" s="31"/>
+      <x:c r="E254" s="31"/>
+      <x:c r="F254" s="31"/>
+      <x:c r="G254" s="31"/>
+      <x:c r="H254" s="31"/>
+      <x:c r="I254" s="31"/>
+      <x:c r="J254" s="31"/>
+      <x:c r="K254" s="31"/>
+      <x:c r="L254" s="31"/>
+      <x:c r="M254" s="31"/>
+      <x:c r="N254" s="31"/>
+      <x:c r="O254" s="31"/>
+      <x:c r="P254" s="31"/>
+      <x:c r="Q254" s="31"/>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="31"/>
+      <x:c r="B255" s="31"/>
+      <x:c r="C255" s="31"/>
+      <x:c r="D255" s="31"/>
+      <x:c r="E255" s="31"/>
+      <x:c r="F255" s="31"/>
+      <x:c r="G255" s="31"/>
+      <x:c r="H255" s="31"/>
+      <x:c r="I255" s="31"/>
+      <x:c r="J255" s="31"/>
+      <x:c r="K255" s="31"/>
+      <x:c r="L255" s="31"/>
+      <x:c r="M255" s="31"/>
+      <x:c r="N255" s="31"/>
+      <x:c r="O255" s="31"/>
+      <x:c r="P255" s="31"/>
+      <x:c r="Q255" s="31"/>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="31"/>
+      <x:c r="B256" s="31"/>
+      <x:c r="C256" s="31"/>
+      <x:c r="D256" s="31"/>
+      <x:c r="E256" s="31"/>
+      <x:c r="F256" s="31"/>
+      <x:c r="G256" s="31"/>
+      <x:c r="H256" s="31"/>
+      <x:c r="I256" s="31"/>
+      <x:c r="J256" s="31"/>
+      <x:c r="K256" s="31"/>
+      <x:c r="L256" s="31"/>
+      <x:c r="M256" s="31"/>
+      <x:c r="N256" s="31"/>
+      <x:c r="O256" s="31"/>
+      <x:c r="P256" s="31"/>
+      <x:c r="Q256" s="31"/>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="31"/>
+      <x:c r="B257" s="31"/>
+      <x:c r="C257" s="31"/>
+      <x:c r="D257" s="31"/>
+      <x:c r="E257" s="31"/>
+      <x:c r="F257" s="31"/>
+      <x:c r="G257" s="31"/>
+      <x:c r="H257" s="31"/>
+      <x:c r="I257" s="31"/>
+      <x:c r="J257" s="31"/>
+      <x:c r="K257" s="31"/>
+      <x:c r="L257" s="31"/>
+      <x:c r="M257" s="31"/>
+      <x:c r="N257" s="31"/>
+      <x:c r="O257" s="31"/>
+      <x:c r="P257" s="31"/>
+      <x:c r="Q257" s="31"/>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="31"/>
+      <x:c r="B258" s="31"/>
+      <x:c r="C258" s="31"/>
+      <x:c r="D258" s="31"/>
+      <x:c r="E258" s="31"/>
+      <x:c r="F258" s="31"/>
+      <x:c r="G258" s="31"/>
+      <x:c r="H258" s="31"/>
+      <x:c r="I258" s="31"/>
+      <x:c r="J258" s="31"/>
+      <x:c r="K258" s="31"/>
+      <x:c r="L258" s="31"/>
+      <x:c r="M258" s="31"/>
+      <x:c r="N258" s="31"/>
+      <x:c r="O258" s="31"/>
+      <x:c r="P258" s="31"/>
+      <x:c r="Q258" s="31"/>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" s="31"/>
+      <x:c r="B259" s="31"/>
+      <x:c r="C259" s="31"/>
+      <x:c r="D259" s="31"/>
+      <x:c r="E259" s="31"/>
+      <x:c r="F259" s="31"/>
+      <x:c r="G259" s="31"/>
+      <x:c r="H259" s="31"/>
+      <x:c r="I259" s="31"/>
+      <x:c r="J259" s="31"/>
+      <x:c r="K259" s="31"/>
+      <x:c r="L259" s="31"/>
+      <x:c r="M259" s="31"/>
+      <x:c r="N259" s="31"/>
+      <x:c r="O259" s="31"/>
+      <x:c r="P259" s="31"/>
+      <x:c r="Q259" s="31"/>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" s="31"/>
+      <x:c r="B260" s="31"/>
+      <x:c r="C260" s="31"/>
+      <x:c r="D260" s="31"/>
+      <x:c r="E260" s="31"/>
+      <x:c r="F260" s="31"/>
+      <x:c r="G260" s="31"/>
+      <x:c r="H260" s="31"/>
+      <x:c r="I260" s="31"/>
+      <x:c r="J260" s="31"/>
+      <x:c r="K260" s="31"/>
+      <x:c r="L260" s="31"/>
+      <x:c r="M260" s="31"/>
+      <x:c r="N260" s="31"/>
+      <x:c r="O260" s="31"/>
+      <x:c r="P260" s="31"/>
+      <x:c r="Q260" s="31"/>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" s="31"/>
+      <x:c r="B261" s="31"/>
+      <x:c r="C261" s="31"/>
+      <x:c r="D261" s="31"/>
+      <x:c r="E261" s="31"/>
+      <x:c r="F261" s="31"/>
+      <x:c r="G261" s="31"/>
+      <x:c r="H261" s="31"/>
+      <x:c r="I261" s="31"/>
+      <x:c r="J261" s="31"/>
+      <x:c r="K261" s="31"/>
+      <x:c r="L261" s="31"/>
+      <x:c r="M261" s="31"/>
+      <x:c r="N261" s="31"/>
+      <x:c r="O261" s="31"/>
+      <x:c r="P261" s="31"/>
+      <x:c r="Q261" s="31"/>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" s="31"/>
+      <x:c r="B262" s="31"/>
+      <x:c r="C262" s="31"/>
+      <x:c r="D262" s="31"/>
+      <x:c r="E262" s="31"/>
+      <x:c r="F262" s="31"/>
+      <x:c r="G262" s="31"/>
+      <x:c r="H262" s="31"/>
+      <x:c r="I262" s="31"/>
+      <x:c r="J262" s="31"/>
+      <x:c r="K262" s="31"/>
+      <x:c r="L262" s="31"/>
+      <x:c r="M262" s="31"/>
+      <x:c r="N262" s="31"/>
+      <x:c r="O262" s="31"/>
+      <x:c r="P262" s="31"/>
+      <x:c r="Q262" s="31"/>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" s="31"/>
+      <x:c r="B263" s="31"/>
+      <x:c r="C263" s="31"/>
+      <x:c r="D263" s="31"/>
+      <x:c r="E263" s="31"/>
+      <x:c r="F263" s="31"/>
+      <x:c r="G263" s="31"/>
+      <x:c r="H263" s="31"/>
+      <x:c r="I263" s="31"/>
+      <x:c r="J263" s="31"/>
+      <x:c r="K263" s="31"/>
+      <x:c r="L263" s="31"/>
+      <x:c r="M263" s="31"/>
+      <x:c r="N263" s="31"/>
+      <x:c r="O263" s="31"/>
+      <x:c r="P263" s="31"/>
+      <x:c r="Q263" s="31"/>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" s="31"/>
+      <x:c r="B264" s="31"/>
+      <x:c r="C264" s="31"/>
+      <x:c r="D264" s="31"/>
+      <x:c r="E264" s="31"/>
+      <x:c r="F264" s="31"/>
+      <x:c r="G264" s="31"/>
+      <x:c r="H264" s="31"/>
+      <x:c r="I264" s="31"/>
+      <x:c r="J264" s="31"/>
+      <x:c r="K264" s="31"/>
+      <x:c r="L264" s="31"/>
+      <x:c r="M264" s="31"/>
+      <x:c r="N264" s="31"/>
+      <x:c r="O264" s="31"/>
+      <x:c r="P264" s="31"/>
+      <x:c r="Q264" s="31"/>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" s="31"/>
+      <x:c r="B265" s="31"/>
+      <x:c r="C265" s="31"/>
+      <x:c r="D265" s="31"/>
+      <x:c r="E265" s="31"/>
+      <x:c r="F265" s="31"/>
+      <x:c r="G265" s="31"/>
+      <x:c r="H265" s="31"/>
+      <x:c r="I265" s="31"/>
+      <x:c r="J265" s="31"/>
+      <x:c r="K265" s="31"/>
+      <x:c r="L265" s="31"/>
+      <x:c r="M265" s="31"/>
+      <x:c r="N265" s="31"/>
+      <x:c r="O265" s="31"/>
+      <x:c r="P265" s="31"/>
+      <x:c r="Q265" s="31"/>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="31"/>
+      <x:c r="B266" s="31"/>
+      <x:c r="C266" s="31"/>
+      <x:c r="D266" s="31"/>
+      <x:c r="E266" s="31"/>
+      <x:c r="F266" s="31"/>
+      <x:c r="G266" s="31"/>
+      <x:c r="H266" s="31"/>
+      <x:c r="I266" s="31"/>
+      <x:c r="J266" s="31"/>
+      <x:c r="K266" s="31"/>
+      <x:c r="L266" s="31"/>
+      <x:c r="M266" s="31"/>
+      <x:c r="N266" s="31"/>
+      <x:c r="O266" s="31"/>
+      <x:c r="P266" s="31"/>
+      <x:c r="Q266" s="31"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="31"/>
+      <x:c r="B267" s="31"/>
+      <x:c r="C267" s="31"/>
+      <x:c r="D267" s="31"/>
+      <x:c r="E267" s="31"/>
+      <x:c r="F267" s="31"/>
+      <x:c r="G267" s="31"/>
+      <x:c r="H267" s="31"/>
+      <x:c r="I267" s="31"/>
+      <x:c r="J267" s="31"/>
+      <x:c r="K267" s="31"/>
+      <x:c r="L267" s="31"/>
+      <x:c r="M267" s="31"/>
+      <x:c r="N267" s="31"/>
+      <x:c r="O267" s="31"/>
+      <x:c r="P267" s="31"/>
+      <x:c r="Q267" s="31"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" s="31"/>
+      <x:c r="B268" s="31"/>
+      <x:c r="C268" s="31"/>
+      <x:c r="D268" s="31"/>
+      <x:c r="E268" s="31"/>
+      <x:c r="F268" s="31"/>
+      <x:c r="G268" s="31"/>
+      <x:c r="H268" s="31"/>
+      <x:c r="I268" s="31"/>
+      <x:c r="J268" s="31"/>
+      <x:c r="K268" s="31"/>
+      <x:c r="L268" s="31"/>
+      <x:c r="M268" s="31"/>
+      <x:c r="N268" s="31"/>
+      <x:c r="O268" s="31"/>
+      <x:c r="P268" s="31"/>
+      <x:c r="Q268" s="31"/>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" s="31"/>
+      <x:c r="B269" s="31"/>
+      <x:c r="C269" s="31"/>
+      <x:c r="D269" s="31"/>
+      <x:c r="E269" s="31"/>
+      <x:c r="F269" s="31"/>
+      <x:c r="G269" s="31"/>
+      <x:c r="H269" s="31"/>
+      <x:c r="I269" s="31"/>
+      <x:c r="J269" s="31"/>
+      <x:c r="K269" s="31"/>
+      <x:c r="L269" s="31"/>
+      <x:c r="M269" s="31"/>
+      <x:c r="N269" s="31"/>
+      <x:c r="O269" s="31"/>
+      <x:c r="P269" s="31"/>
+      <x:c r="Q269" s="31"/>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" s="31"/>
+      <x:c r="B270" s="31"/>
+      <x:c r="C270" s="31"/>
+      <x:c r="D270" s="31"/>
+      <x:c r="E270" s="31"/>
+      <x:c r="F270" s="31"/>
+      <x:c r="G270" s="31"/>
+      <x:c r="H270" s="31"/>
+      <x:c r="I270" s="31"/>
+      <x:c r="J270" s="31"/>
+      <x:c r="K270" s="31"/>
+      <x:c r="L270" s="31"/>
+      <x:c r="M270" s="31"/>
+      <x:c r="N270" s="31"/>
+      <x:c r="O270" s="31"/>
+      <x:c r="P270" s="31"/>
+      <x:c r="Q270" s="31"/>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" s="31"/>
+      <x:c r="B271" s="31"/>
+      <x:c r="C271" s="31"/>
+      <x:c r="D271" s="31"/>
+      <x:c r="E271" s="31"/>
+      <x:c r="F271" s="31"/>
+      <x:c r="G271" s="31"/>
+      <x:c r="H271" s="31"/>
+      <x:c r="I271" s="31"/>
+      <x:c r="J271" s="31"/>
+      <x:c r="K271" s="31"/>
+      <x:c r="L271" s="31"/>
+      <x:c r="M271" s="31"/>
+      <x:c r="N271" s="31"/>
+      <x:c r="O271" s="31"/>
+      <x:c r="P271" s="31"/>
+      <x:c r="Q271" s="31"/>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" s="31"/>
+      <x:c r="B272" s="31"/>
+      <x:c r="C272" s="31"/>
+      <x:c r="D272" s="31"/>
+      <x:c r="E272" s="31"/>
+      <x:c r="F272" s="31"/>
+      <x:c r="G272" s="31"/>
+      <x:c r="H272" s="31"/>
+      <x:c r="I272" s="31"/>
+      <x:c r="J272" s="31"/>
+      <x:c r="K272" s="31"/>
+      <x:c r="L272" s="31"/>
+      <x:c r="M272" s="31"/>
+      <x:c r="N272" s="31"/>
+      <x:c r="O272" s="31"/>
+      <x:c r="P272" s="31"/>
+      <x:c r="Q272" s="31"/>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" s="31"/>
+      <x:c r="B273" s="31"/>
+      <x:c r="C273" s="31"/>
+      <x:c r="D273" s="31"/>
+      <x:c r="E273" s="31"/>
+      <x:c r="F273" s="31"/>
+      <x:c r="G273" s="31"/>
+      <x:c r="H273" s="31"/>
+      <x:c r="I273" s="31"/>
+      <x:c r="J273" s="31"/>
+      <x:c r="K273" s="31"/>
+      <x:c r="L273" s="31"/>
+      <x:c r="M273" s="31"/>
+      <x:c r="N273" s="31"/>
+      <x:c r="O273" s="31"/>
+      <x:c r="P273" s="31"/>
+      <x:c r="Q273" s="31"/>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" s="31"/>
+      <x:c r="B274" s="31"/>
+      <x:c r="C274" s="31"/>
+      <x:c r="D274" s="31"/>
+      <x:c r="E274" s="31"/>
+      <x:c r="F274" s="31"/>
+      <x:c r="G274" s="31"/>
+      <x:c r="H274" s="31"/>
+      <x:c r="I274" s="31"/>
+      <x:c r="J274" s="31"/>
+      <x:c r="K274" s="31"/>
+      <x:c r="L274" s="31"/>
+      <x:c r="M274" s="31"/>
+      <x:c r="N274" s="31"/>
+      <x:c r="O274" s="31"/>
+      <x:c r="P274" s="31"/>
+      <x:c r="Q274" s="31"/>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" s="31"/>
+      <x:c r="B275" s="31"/>
+      <x:c r="C275" s="31"/>
+      <x:c r="D275" s="31"/>
+      <x:c r="E275" s="31"/>
+      <x:c r="F275" s="31"/>
+      <x:c r="G275" s="31"/>
+      <x:c r="H275" s="31"/>
+      <x:c r="I275" s="31"/>
+      <x:c r="J275" s="31"/>
+      <x:c r="K275" s="31"/>
+      <x:c r="L275" s="31"/>
+      <x:c r="M275" s="31"/>
+      <x:c r="N275" s="31"/>
+      <x:c r="O275" s="31"/>
+      <x:c r="P275" s="31"/>
+      <x:c r="Q275" s="31"/>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" s="31"/>
+      <x:c r="B276" s="31"/>
+      <x:c r="C276" s="31"/>
+      <x:c r="D276" s="31"/>
+      <x:c r="E276" s="31"/>
+      <x:c r="F276" s="31"/>
+      <x:c r="G276" s="31"/>
+      <x:c r="H276" s="31"/>
+      <x:c r="I276" s="31"/>
+      <x:c r="J276" s="31"/>
+      <x:c r="K276" s="31"/>
+      <x:c r="L276" s="31"/>
+      <x:c r="M276" s="31"/>
+      <x:c r="N276" s="31"/>
+      <x:c r="O276" s="31"/>
+      <x:c r="P276" s="31"/>
+      <x:c r="Q276" s="31"/>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" s="31"/>
+      <x:c r="B277" s="31"/>
+      <x:c r="C277" s="31"/>
+      <x:c r="D277" s="31"/>
+      <x:c r="E277" s="31"/>
+      <x:c r="F277" s="31"/>
+      <x:c r="G277" s="31"/>
+      <x:c r="H277" s="31"/>
+      <x:c r="I277" s="31"/>
+      <x:c r="J277" s="31"/>
+      <x:c r="K277" s="31"/>
+      <x:c r="L277" s="31"/>
+      <x:c r="M277" s="31"/>
+      <x:c r="N277" s="31"/>
+      <x:c r="O277" s="31"/>
+      <x:c r="P277" s="31"/>
+      <x:c r="Q277" s="31"/>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" s="31"/>
+      <x:c r="B278" s="31"/>
+      <x:c r="C278" s="31"/>
+      <x:c r="D278" s="31"/>
+      <x:c r="E278" s="31"/>
+      <x:c r="F278" s="31"/>
+      <x:c r="G278" s="31"/>
+      <x:c r="H278" s="31"/>
+      <x:c r="I278" s="31"/>
+      <x:c r="J278" s="31"/>
+      <x:c r="K278" s="31"/>
+      <x:c r="L278" s="31"/>
+      <x:c r="M278" s="31"/>
+      <x:c r="N278" s="31"/>
+      <x:c r="O278" s="31"/>
+      <x:c r="P278" s="31"/>
+      <x:c r="Q278" s="31"/>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" s="31"/>
+      <x:c r="B279" s="31"/>
+      <x:c r="C279" s="31"/>
+      <x:c r="D279" s="31"/>
+      <x:c r="E279" s="31"/>
+      <x:c r="F279" s="31"/>
+      <x:c r="G279" s="31"/>
+      <x:c r="H279" s="31"/>
+      <x:c r="I279" s="31"/>
+      <x:c r="J279" s="31"/>
+      <x:c r="K279" s="31"/>
+      <x:c r="L279" s="31"/>
+      <x:c r="M279" s="31"/>
+      <x:c r="N279" s="31"/>
+      <x:c r="O279" s="31"/>
+      <x:c r="P279" s="31"/>
+      <x:c r="Q279" s="31"/>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" s="31"/>
+      <x:c r="B280" s="31"/>
+      <x:c r="C280" s="31"/>
+      <x:c r="D280" s="31"/>
+      <x:c r="E280" s="31"/>
+      <x:c r="F280" s="31"/>
+      <x:c r="G280" s="31"/>
+      <x:c r="H280" s="31"/>
+      <x:c r="I280" s="31"/>
+      <x:c r="J280" s="31"/>
+      <x:c r="K280" s="31"/>
+      <x:c r="L280" s="31"/>
+      <x:c r="M280" s="31"/>
+      <x:c r="N280" s="31"/>
+      <x:c r="O280" s="31"/>
+      <x:c r="P280" s="31"/>
+      <x:c r="Q280" s="31"/>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" s="31"/>
+      <x:c r="B281" s="31"/>
+      <x:c r="C281" s="31"/>
+      <x:c r="D281" s="31"/>
+      <x:c r="E281" s="31"/>
+      <x:c r="F281" s="31"/>
+      <x:c r="G281" s="31"/>
+      <x:c r="H281" s="31"/>
+      <x:c r="I281" s="31"/>
+      <x:c r="J281" s="31"/>
+      <x:c r="K281" s="31"/>
+      <x:c r="L281" s="31"/>
+      <x:c r="M281" s="31"/>
+      <x:c r="N281" s="31"/>
+      <x:c r="O281" s="31"/>
+      <x:c r="P281" s="31"/>
+      <x:c r="Q281" s="31"/>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" s="31"/>
+      <x:c r="B282" s="31"/>
+      <x:c r="C282" s="31"/>
+      <x:c r="D282" s="31"/>
+      <x:c r="E282" s="31"/>
+      <x:c r="F282" s="31"/>
+      <x:c r="G282" s="31"/>
+      <x:c r="H282" s="31"/>
+      <x:c r="I282" s="31"/>
+      <x:c r="J282" s="31"/>
+      <x:c r="K282" s="31"/>
+      <x:c r="L282" s="31"/>
+      <x:c r="M282" s="31"/>
+      <x:c r="N282" s="31"/>
+      <x:c r="O282" s="31"/>
+      <x:c r="P282" s="31"/>
+      <x:c r="Q282" s="31"/>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" s="31"/>
+      <x:c r="B283" s="31"/>
+      <x:c r="C283" s="31"/>
+      <x:c r="D283" s="31"/>
+      <x:c r="E283" s="31"/>
+      <x:c r="F283" s="31"/>
+      <x:c r="G283" s="31"/>
+      <x:c r="H283" s="31"/>
+      <x:c r="I283" s="31"/>
+      <x:c r="J283" s="31"/>
+      <x:c r="K283" s="31"/>
+      <x:c r="L283" s="31"/>
+      <x:c r="M283" s="31"/>
+      <x:c r="N283" s="31"/>
+      <x:c r="O283" s="31"/>
+      <x:c r="P283" s="31"/>
+      <x:c r="Q283" s="31"/>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" s="31"/>
+      <x:c r="B284" s="31"/>
+      <x:c r="C284" s="31"/>
+      <x:c r="D284" s="31"/>
+      <x:c r="E284" s="31"/>
+      <x:c r="F284" s="31"/>
+      <x:c r="G284" s="31"/>
+      <x:c r="H284" s="31"/>
+      <x:c r="I284" s="31"/>
+      <x:c r="J284" s="31"/>
+      <x:c r="K284" s="31"/>
+      <x:c r="L284" s="31"/>
+      <x:c r="M284" s="31"/>
+      <x:c r="N284" s="31"/>
+      <x:c r="O284" s="31"/>
+      <x:c r="P284" s="31"/>
+      <x:c r="Q284" s="31"/>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" s="31"/>
+      <x:c r="B285" s="31"/>
+      <x:c r="C285" s="31"/>
+      <x:c r="D285" s="31"/>
+      <x:c r="E285" s="31"/>
+      <x:c r="F285" s="31"/>
+      <x:c r="G285" s="31"/>
+      <x:c r="H285" s="31"/>
+      <x:c r="I285" s="31"/>
+      <x:c r="J285" s="31"/>
+      <x:c r="K285" s="31"/>
+      <x:c r="L285" s="31"/>
+      <x:c r="M285" s="31"/>
+      <x:c r="N285" s="31"/>
+      <x:c r="O285" s="31"/>
+      <x:c r="P285" s="31"/>
+      <x:c r="Q285" s="31"/>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A286" s="31"/>
+      <x:c r="B286" s="31"/>
+      <x:c r="C286" s="31"/>
+      <x:c r="D286" s="31"/>
+      <x:c r="E286" s="31"/>
+      <x:c r="F286" s="31"/>
+      <x:c r="G286" s="31"/>
+      <x:c r="H286" s="31"/>
+      <x:c r="I286" s="31"/>
+      <x:c r="J286" s="31"/>
+      <x:c r="K286" s="31"/>
+      <x:c r="L286" s="31"/>
+      <x:c r="M286" s="31"/>
+      <x:c r="N286" s="31"/>
+      <x:c r="O286" s="31"/>
+      <x:c r="P286" s="31"/>
+      <x:c r="Q286" s="31"/>
+    </x:row>
+    <x:row r="287">
+      <x:c r="A287" s="31"/>
+      <x:c r="B287" s="31"/>
+      <x:c r="C287" s="31"/>
+      <x:c r="D287" s="31"/>
+      <x:c r="E287" s="31"/>
+      <x:c r="F287" s="31"/>
+      <x:c r="G287" s="31"/>
+      <x:c r="H287" s="31"/>
+      <x:c r="I287" s="31"/>
+      <x:c r="J287" s="31"/>
+      <x:c r="K287" s="31"/>
+      <x:c r="L287" s="31"/>
+      <x:c r="M287" s="31"/>
+      <x:c r="N287" s="31"/>
+      <x:c r="O287" s="31"/>
+      <x:c r="P287" s="31"/>
+      <x:c r="Q287" s="31"/>
+    </x:row>
+    <x:row r="288">
+      <x:c r="A288" s="31"/>
+      <x:c r="B288" s="31"/>
+      <x:c r="C288" s="31"/>
+      <x:c r="D288" s="31"/>
+      <x:c r="E288" s="31"/>
+      <x:c r="F288" s="31"/>
+      <x:c r="G288" s="31"/>
+      <x:c r="H288" s="31"/>
+      <x:c r="I288" s="31"/>
+      <x:c r="J288" s="31"/>
+      <x:c r="K288" s="31"/>
+      <x:c r="L288" s="31"/>
+      <x:c r="M288" s="31"/>
+      <x:c r="N288" s="31"/>
+      <x:c r="O288" s="31"/>
+      <x:c r="P288" s="31"/>
+      <x:c r="Q288" s="31"/>
+    </x:row>
+    <x:row r="289">
+      <x:c r="A289" s="31"/>
+      <x:c r="B289" s="31"/>
+      <x:c r="C289" s="31"/>
+      <x:c r="D289" s="31"/>
+      <x:c r="E289" s="31"/>
+      <x:c r="F289" s="31"/>
+      <x:c r="G289" s="31"/>
+      <x:c r="H289" s="31"/>
+      <x:c r="I289" s="31"/>
+      <x:c r="J289" s="31"/>
+      <x:c r="K289" s="31"/>
+      <x:c r="L289" s="31"/>
+      <x:c r="M289" s="31"/>
+      <x:c r="N289" s="31"/>
+      <x:c r="O289" s="31"/>
+      <x:c r="P289" s="31"/>
+      <x:c r="Q289" s="31"/>
+    </x:row>
+    <x:row r="290">
+      <x:c r="A290" s="31"/>
+      <x:c r="B290" s="31"/>
+      <x:c r="C290" s="31"/>
+      <x:c r="D290" s="31"/>
+      <x:c r="E290" s="31"/>
+      <x:c r="F290" s="31"/>
+      <x:c r="G290" s="31"/>
+      <x:c r="H290" s="31"/>
+      <x:c r="I290" s="31"/>
+      <x:c r="J290" s="31"/>
+      <x:c r="K290" s="31"/>
+      <x:c r="L290" s="31"/>
+      <x:c r="M290" s="31"/>
+      <x:c r="N290" s="31"/>
+      <x:c r="O290" s="31"/>
+      <x:c r="P290" s="31"/>
+      <x:c r="Q290" s="31"/>
+    </x:row>
+    <x:row r="291">
+      <x:c r="A291" s="31"/>
+      <x:c r="B291" s="31"/>
+      <x:c r="C291" s="31"/>
+      <x:c r="D291" s="31"/>
+      <x:c r="E291" s="31"/>
+      <x:c r="F291" s="31"/>
+      <x:c r="G291" s="31"/>
+      <x:c r="H291" s="31"/>
+      <x:c r="I291" s="31"/>
+      <x:c r="J291" s="31"/>
+      <x:c r="K291" s="31"/>
+      <x:c r="L291" s="31"/>
+      <x:c r="M291" s="31"/>
+      <x:c r="N291" s="31"/>
+      <x:c r="O291" s="31"/>
+      <x:c r="P291" s="31"/>
+      <x:c r="Q291" s="31"/>
+    </x:row>
+    <x:row r="292">
+      <x:c r="A292" s="31"/>
+      <x:c r="B292" s="31"/>
+      <x:c r="C292" s="31"/>
+      <x:c r="D292" s="31"/>
+      <x:c r="E292" s="31"/>
+      <x:c r="F292" s="31"/>
+      <x:c r="G292" s="31"/>
+      <x:c r="H292" s="31"/>
+      <x:c r="I292" s="31"/>
+      <x:c r="J292" s="31"/>
+      <x:c r="K292" s="31"/>
+      <x:c r="L292" s="31"/>
+      <x:c r="M292" s="31"/>
+      <x:c r="N292" s="31"/>
+      <x:c r="O292" s="31"/>
+      <x:c r="P292" s="31"/>
+      <x:c r="Q292" s="31"/>
+    </x:row>
+    <x:row r="293">
+      <x:c r="A293" s="31"/>
+      <x:c r="B293" s="31"/>
+      <x:c r="C293" s="31"/>
+      <x:c r="D293" s="31"/>
+      <x:c r="E293" s="31"/>
+      <x:c r="F293" s="31"/>
+      <x:c r="G293" s="31"/>
+      <x:c r="H293" s="31"/>
+      <x:c r="I293" s="31"/>
+      <x:c r="J293" s="31"/>
+      <x:c r="K293" s="31"/>
+      <x:c r="L293" s="31"/>
+      <x:c r="M293" s="31"/>
+      <x:c r="N293" s="31"/>
+      <x:c r="O293" s="31"/>
+      <x:c r="P293" s="31"/>
+      <x:c r="Q293" s="31"/>
+    </x:row>
+    <x:row r="294">
+      <x:c r="A294" s="31"/>
+      <x:c r="B294" s="31"/>
+      <x:c r="C294" s="31"/>
+      <x:c r="D294" s="31"/>
+      <x:c r="E294" s="31"/>
+      <x:c r="F294" s="31"/>
+      <x:c r="G294" s="31"/>
+      <x:c r="H294" s="31"/>
+      <x:c r="I294" s="31"/>
+      <x:c r="J294" s="31"/>
+      <x:c r="K294" s="31"/>
+      <x:c r="L294" s="31"/>
+      <x:c r="M294" s="31"/>
+      <x:c r="N294" s="31"/>
+      <x:c r="O294" s="31"/>
+      <x:c r="P294" s="31"/>
+      <x:c r="Q294" s="31"/>
+    </x:row>
+    <x:row r="295">
+      <x:c r="A295" s="31"/>
+      <x:c r="B295" s="31"/>
+      <x:c r="C295" s="31"/>
+      <x:c r="D295" s="31"/>
+      <x:c r="E295" s="31"/>
+      <x:c r="F295" s="31"/>
+      <x:c r="G295" s="31"/>
+      <x:c r="H295" s="31"/>
+      <x:c r="I295" s="31"/>
+      <x:c r="J295" s="31"/>
+      <x:c r="K295" s="31"/>
+      <x:c r="L295" s="31"/>
+      <x:c r="M295" s="31"/>
+      <x:c r="N295" s="31"/>
+      <x:c r="O295" s="31"/>
+      <x:c r="P295" s="31"/>
+      <x:c r="Q295" s="31"/>
+    </x:row>
+    <x:row r="296">
+      <x:c r="A296" s="31"/>
+      <x:c r="B296" s="31"/>
+      <x:c r="C296" s="31"/>
+      <x:c r="D296" s="31"/>
+      <x:c r="E296" s="31"/>
+      <x:c r="F296" s="31"/>
+      <x:c r="G296" s="31"/>
+      <x:c r="H296" s="31"/>
+      <x:c r="I296" s="31"/>
+      <x:c r="J296" s="31"/>
+      <x:c r="K296" s="31"/>
+      <x:c r="L296" s="31"/>
+      <x:c r="M296" s="31"/>
+      <x:c r="N296" s="31"/>
+      <x:c r="O296" s="31"/>
+      <x:c r="P296" s="31"/>
+      <x:c r="Q296" s="31"/>
+    </x:row>
+    <x:row r="297">
+      <x:c r="A297" s="31"/>
+      <x:c r="B297" s="31"/>
+      <x:c r="C297" s="31"/>
+      <x:c r="D297" s="31"/>
+      <x:c r="E297" s="31"/>
+      <x:c r="F297" s="31"/>
+      <x:c r="G297" s="31"/>
+      <x:c r="H297" s="31"/>
+      <x:c r="I297" s="31"/>
+      <x:c r="J297" s="31"/>
+      <x:c r="K297" s="31"/>
+      <x:c r="L297" s="31"/>
+      <x:c r="M297" s="31"/>
+      <x:c r="N297" s="31"/>
+      <x:c r="O297" s="31"/>
+      <x:c r="P297" s="31"/>
+      <x:c r="Q297" s="31"/>
+    </x:row>
+    <x:row r="298">
+      <x:c r="A298" s="31"/>
+      <x:c r="B298" s="31"/>
+      <x:c r="C298" s="31"/>
+      <x:c r="D298" s="31"/>
+      <x:c r="E298" s="31"/>
+      <x:c r="F298" s="31"/>
+      <x:c r="G298" s="31"/>
+      <x:c r="H298" s="31"/>
+      <x:c r="I298" s="31"/>
+      <x:c r="J298" s="31"/>
+      <x:c r="K298" s="31"/>
+      <x:c r="L298" s="31"/>
+      <x:c r="M298" s="31"/>
+      <x:c r="N298" s="31"/>
+      <x:c r="O298" s="31"/>
+      <x:c r="P298" s="31"/>
+      <x:c r="Q298" s="31"/>
+    </x:row>
+    <x:row r="299">
+      <x:c r="A299" s="31"/>
+      <x:c r="B299" s="31"/>
+      <x:c r="C299" s="31"/>
+      <x:c r="D299" s="31"/>
+      <x:c r="E299" s="31"/>
+      <x:c r="F299" s="31"/>
+      <x:c r="G299" s="31"/>
+      <x:c r="H299" s="31"/>
+      <x:c r="I299" s="31"/>
+      <x:c r="J299" s="31"/>
+      <x:c r="K299" s="31"/>
+      <x:c r="L299" s="31"/>
+      <x:c r="M299" s="31"/>
+      <x:c r="N299" s="31"/>
+      <x:c r="O299" s="31"/>
+      <x:c r="P299" s="31"/>
+      <x:c r="Q299" s="31"/>
+    </x:row>
+    <x:row r="300">
+      <x:c r="A300" s="31"/>
+      <x:c r="B300" s="31"/>
+      <x:c r="C300" s="31"/>
+      <x:c r="D300" s="31"/>
+      <x:c r="E300" s="31"/>
+      <x:c r="F300" s="31"/>
+      <x:c r="G300" s="31"/>
+      <x:c r="H300" s="31"/>
+      <x:c r="I300" s="31"/>
+      <x:c r="J300" s="31"/>
+      <x:c r="K300" s="31"/>
+      <x:c r="L300" s="31"/>
+      <x:c r="M300" s="31"/>
+      <x:c r="N300" s="31"/>
+      <x:c r="O300" s="31"/>
+      <x:c r="P300" s="31"/>
+      <x:c r="Q300" s="31"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -62792,23 +68570,41 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18.040000915527344" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="156.1999969482422" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13.869999885559082" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.610000133514404" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.470000267028809" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4.050000190734863" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="7.980000019073486" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="42.58000183105469" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="40" t="str">
-        <x:v>Item</x:v>
-      </x:c>
-      <x:c r="B1" s="40" t="str">
-        <x:v>Note</x:v>
-      </x:c>
-      <x:c r="C1" s="31"/>
-      <x:c r="D1" s="31"/>
-      <x:c r="E1" s="31"/>
-      <x:c r="F1" s="31"/>
-      <x:c r="G1" s="31"/>
-      <x:c r="H1" s="31"/>
+      <x:c r="A1" s="32" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="B1" s="32" t="str">
+        <x:v>Split</x:v>
+      </x:c>
+      <x:c r="C1" s="32" t="str">
+        <x:v>Limit</x:v>
+      </x:c>
+      <x:c r="D1" s="32" t="str">
+        <x:v>Threshold</x:v>
+      </x:c>
+      <x:c r="E1" s="32" t="str">
+        <x:v>Correct</x:v>
+      </x:c>
+      <x:c r="F1" s="32" t="str">
+        <x:v>Total</x:v>
+      </x:c>
+      <x:c r="G1" s="32" t="str">
+        <x:v>Accuracy</x:v>
+      </x:c>
+      <x:c r="H1" s="32" t="str">
+        <x:v>Source</x:v>
+      </x:c>
       <x:c r="I1" s="31"/>
       <x:c r="J1" s="31"/>
       <x:c r="K1" s="31"/>
@@ -62820,18 +68616,30 @@
       <x:c r="Q1" s="31"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="41" t="str">
-        <x:v>Benchmark</x:v>
-      </x:c>
-      <x:c r="B2" s="41" t="str">
-        <x:v>Closed-form multiple-choice probe scored by candidate letter log-probability.</x:v>
-      </x:c>
-      <x:c r="C2" s="31"/>
-      <x:c r="D2" s="31"/>
-      <x:c r="E2" s="31"/>
-      <x:c r="F2" s="31"/>
-      <x:c r="G2" s="31"/>
-      <x:c r="H2" s="31"/>
+      <x:c r="A2" s="33" t="str">
+        <x:v>Qwen3-0.6B-4bit</x:v>
+      </x:c>
+      <x:c r="B2" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C2" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D2" s="33" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E2" s="33" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F2" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G2" s="34" t="n">
+        <x:v>0.46</x:v>
+      </x:c>
+      <x:c r="H2" s="33" t="str">
+        <x:v>arc_qwen3_0_6b_margin_ensemble_validation50.csv</x:v>
+      </x:c>
       <x:c r="I2" s="31"/>
       <x:c r="J2" s="31"/>
       <x:c r="K2" s="31"/>
@@ -62843,18 +68651,30 @@
       <x:c r="Q2" s="31"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="41" t="str">
-        <x:v>Current wins</x:v>
-      </x:c>
-      <x:c r="B3" s="41" t="str">
-        <x:v>Qwen3-0.6B-4bit improves from 5/17 to 7/17 with split 14; Qwen3-1.7B-4bit improves from 10/17 to 11/17 with split 10.</x:v>
-      </x:c>
-      <x:c r="C3" s="31"/>
-      <x:c r="D3" s="31"/>
-      <x:c r="E3" s="31"/>
-      <x:c r="F3" s="31"/>
-      <x:c r="G3" s="31"/>
-      <x:c r="H3" s="31"/>
+      <x:c r="A3" s="33" t="str">
+        <x:v>Qwen3-1.7B-4bit</x:v>
+      </x:c>
+      <x:c r="B3" s="33" t="str">
+        <x:v>validation</x:v>
+      </x:c>
+      <x:c r="C3" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D3" s="33" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="E3" s="33" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F3" s="33" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G3" s="34" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="H3" s="33" t="str">
+        <x:v>arc_qwen3_1_7b_margin_ensemble_validation50.csv</x:v>
+      </x:c>
       <x:c r="I3" s="31"/>
       <x:c r="J3" s="31"/>
       <x:c r="K3" s="31"/>
@@ -62866,17 +68686,13 @@
       <x:c r="Q3" s="31"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="41" t="str">
-        <x:v>Split finding</x:v>
-      </x:c>
-      <x:c r="B4" s="41" t="str">
-        <x:v>The symmetric 14/14 split is best for 0.6B; an earlier split at 10 lower layers is best for 1.7B on the corrected probe.</x:v>
-      </x:c>
+      <x:c r="A4" s="31"/>
+      <x:c r="B4" s="31"/>
       <x:c r="C4" s="31"/>
       <x:c r="D4" s="31"/>
       <x:c r="E4" s="31"/>
       <x:c r="F4" s="31"/>
-      <x:c r="G4" s="31"/>
+      <x:c r="G4" s="36"/>
       <x:c r="H4" s="31"/>
       <x:c r="I4" s="31"/>
       <x:c r="J4" s="31"/>
@@ -62889,17 +68705,13 @@
       <x:c r="Q4" s="31"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="41" t="str">
-        <x:v>Exact-answer probe</x:v>
-      </x:c>
-      <x:c r="B5" s="41" t="str">
-        <x:v>Added a stricter generative probe with exact extraction. Qwen3-0.6B moves from 1/17 base to 2/17 HRM; Qwen3-1.7B is 6/17 for both base and HRM after corrected text-answer scoring.</x:v>
-      </x:c>
+      <x:c r="A5" s="31"/>
+      <x:c r="B5" s="31"/>
       <x:c r="C5" s="31"/>
       <x:c r="D5" s="31"/>
       <x:c r="E5" s="31"/>
       <x:c r="F5" s="31"/>
-      <x:c r="G5" s="31"/>
+      <x:c r="G5" s="36"/>
       <x:c r="H5" s="31"/>
       <x:c r="I5" s="31"/>
       <x:c r="J5" s="31"/>
@@ -62912,17 +68724,13 @@
       <x:c r="Q5" s="31"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="41" t="str">
-        <x:v>Qwen chat exact</x:v>
-      </x:c>
-      <x:c r="B6" s="41" t="str">
-        <x:v>On Qwen3-1.7B chat-template boxed runs, fixed blend scores 5/17 while agreement_blend and confidence_gate recover the 6/17 base score. Use gated fusion for open-ended generation.</x:v>
-      </x:c>
+      <x:c r="A6" s="31"/>
+      <x:c r="B6" s="31"/>
       <x:c r="C6" s="31"/>
       <x:c r="D6" s="31"/>
       <x:c r="E6" s="31"/>
       <x:c r="F6" s="31"/>
-      <x:c r="G6" s="31"/>
+      <x:c r="G6" s="36"/>
       <x:c r="H6" s="31"/>
       <x:c r="I6" s="31"/>
       <x:c r="J6" s="31"/>
@@ -62935,17 +68743,13 @@
       <x:c r="Q6" s="31"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="41" t="str">
-        <x:v>Delayed fusion</x:v>
-      </x:c>
-      <x:c r="B7" s="41" t="str">
-        <x:v>Final-answer-triggered HRM fusion also recovers the 6/17 base score on Qwen3-1.7B chat-template boxed runs. It is safer than full-sequence fixed blending but still not above base.</x:v>
-      </x:c>
+      <x:c r="A7" s="31"/>
+      <x:c r="B7" s="31"/>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="31"/>
       <x:c r="E7" s="31"/>
       <x:c r="F7" s="31"/>
-      <x:c r="G7" s="31"/>
+      <x:c r="G7" s="36"/>
       <x:c r="H7" s="31"/>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="31"/>
@@ -62958,17 +68762,13 @@
       <x:c r="Q7" s="31"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="41" t="str">
-        <x:v>Candidate rerank</x:v>
-      </x:c>
-      <x:c r="B8" s="41" t="str">
-        <x:v>Saved-output candidate reranking found an 11/17 oracle union across raw/chat candidates, but naive yes/no and answer-likelihood rerankers selected only 6/17. Need a stronger verifier.</x:v>
-      </x:c>
+      <x:c r="A8" s="31"/>
+      <x:c r="B8" s="31"/>
       <x:c r="C8" s="31"/>
       <x:c r="D8" s="31"/>
       <x:c r="E8" s="31"/>
       <x:c r="F8" s="31"/>
-      <x:c r="G8" s="31"/>
+      <x:c r="G8" s="36"/>
       <x:c r="H8" s="31"/>
       <x:c r="I8" s="31"/>
       <x:c r="J8" s="31"/>
@@ -62981,17 +68781,13 @@
       <x:c r="Q8" s="31"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="41" t="str">
-        <x:v>ARC-Challenge slice</x:v>
-      </x:c>
-      <x:c r="B9" s="41" t="str">
-        <x:v>On ARC-Challenge validation[:50], Qwen3-0.6B is flat at 21/50 for base, fixed blend, and agreement_blend; Qwen3-1.7B base is 37/50, fixed blend is 35/50, and agreement_blend recovers 37/50.</x:v>
-      </x:c>
+      <x:c r="A9" s="31"/>
+      <x:c r="B9" s="31"/>
       <x:c r="C9" s="31"/>
       <x:c r="D9" s="31"/>
       <x:c r="E9" s="31"/>
       <x:c r="F9" s="31"/>
-      <x:c r="G9" s="31"/>
+      <x:c r="G9" s="36"/>
       <x:c r="H9" s="31"/>
       <x:c r="I9" s="31"/>
       <x:c r="J9" s="31"/>
@@ -63004,17 +68800,13 @@
       <x:c r="Q9" s="31"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="41" t="str">
-        <x:v>HRM-Text comparison</x:v>
-      </x:c>
-      <x:c r="B10" s="41" t="str">
-        <x:v>The original HRM-Text exact run used the wrong final-answer prompt/extraction and too small a token cap. Corrected boxed-prompt runs score 16/17 for both 4-bit and BF16.</x:v>
-      </x:c>
+      <x:c r="A10" s="31"/>
+      <x:c r="B10" s="31"/>
       <x:c r="C10" s="31"/>
       <x:c r="D10" s="31"/>
       <x:c r="E10" s="31"/>
       <x:c r="F10" s="31"/>
-      <x:c r="G10" s="31"/>
+      <x:c r="G10" s="36"/>
       <x:c r="H10" s="31"/>
       <x:c r="I10" s="31"/>
       <x:c r="J10" s="31"/>
@@ -63027,17 +68819,13 @@
       <x:c r="Q10" s="31"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="41" t="str">
-        <x:v>Cost</x:v>
-      </x:c>
-      <x:c r="B11" s="41" t="str">
-        <x:v>HRM is slower because it adds warm split and recurrent passes per scored candidate/token.</x:v>
-      </x:c>
+      <x:c r="A11" s="31"/>
+      <x:c r="B11" s="31"/>
       <x:c r="C11" s="31"/>
       <x:c r="D11" s="31"/>
       <x:c r="E11" s="31"/>
       <x:c r="F11" s="31"/>
-      <x:c r="G11" s="31"/>
+      <x:c r="G11" s="36"/>
       <x:c r="H11" s="31"/>
       <x:c r="I11" s="31"/>
       <x:c r="J11" s="31"/>
@@ -63050,17 +68838,13 @@
       <x:c r="Q11" s="31"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="41" t="str">
-        <x:v>Correction</x:v>
-      </x:c>
-      <x:c r="B12" s="41" t="str">
-        <x:v>Earlier sequence answer was corrected from 80 to 67 before final runs.</x:v>
-      </x:c>
+      <x:c r="A12" s="31"/>
+      <x:c r="B12" s="31"/>
       <x:c r="C12" s="31"/>
       <x:c r="D12" s="31"/>
       <x:c r="E12" s="31"/>
       <x:c r="F12" s="31"/>
-      <x:c r="G12" s="31"/>
+      <x:c r="G12" s="36"/>
       <x:c r="H12" s="31"/>
       <x:c r="I12" s="31"/>
       <x:c r="J12" s="31"/>
@@ -63073,17 +68857,13 @@
       <x:c r="Q12" s="31"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="41" t="str">
-        <x:v>Interpretation</x:v>
-      </x:c>
-      <x:c r="B13" s="41" t="str">
-        <x:v>The MC probe is a fast regression test, not an optimal reasoning benchmark. The exact probe is better but still too small for broad HRM-level claims.</x:v>
-      </x:c>
+      <x:c r="A13" s="31"/>
+      <x:c r="B13" s="31"/>
       <x:c r="C13" s="31"/>
       <x:c r="D13" s="31"/>
       <x:c r="E13" s="31"/>
       <x:c r="F13" s="31"/>
-      <x:c r="G13" s="31"/>
+      <x:c r="G13" s="36"/>
       <x:c r="H13" s="31"/>
       <x:c r="I13" s="31"/>
       <x:c r="J13" s="31"/>
@@ -63096,17 +68876,13 @@
       <x:c r="Q13" s="31"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="41" t="str">
-        <x:v>Fusion finding</x:v>
-      </x:c>
-      <x:c r="B14" s="41" t="str">
-        <x:v>Confidence-gated, agreement-gated, probability-space, and extrapolated-delta fusion did not beat fixed logit blending on the current probe.</x:v>
-      </x:c>
+      <x:c r="A14" s="31"/>
+      <x:c r="B14" s="31"/>
       <x:c r="C14" s="31"/>
       <x:c r="D14" s="31"/>
       <x:c r="E14" s="31"/>
       <x:c r="F14" s="31"/>
-      <x:c r="G14" s="31"/>
+      <x:c r="G14" s="36"/>
       <x:c r="H14" s="31"/>
       <x:c r="I14" s="31"/>
       <x:c r="J14" s="31"/>
@@ -63119,17 +68895,13 @@
       <x:c r="Q14" s="31"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="41" t="str">
-        <x:v>Next</x:v>
-      </x:c>
-      <x:c r="B15" s="41" t="str">
-        <x:v>Need larger held-out probe and a stronger no-training verifier/reranker strategy, or light adapter calibration, for stronger claims.</x:v>
-      </x:c>
+      <x:c r="A15" s="31"/>
+      <x:c r="B15" s="31"/>
       <x:c r="C15" s="31"/>
       <x:c r="D15" s="31"/>
       <x:c r="E15" s="31"/>
       <x:c r="F15" s="31"/>
-      <x:c r="G15" s="31"/>
+      <x:c r="G15" s="36"/>
       <x:c r="H15" s="31"/>
       <x:c r="I15" s="31"/>
       <x:c r="J15" s="31"/>
@@ -63148,7 +68920,7 @@
       <x:c r="D16" s="31"/>
       <x:c r="E16" s="31"/>
       <x:c r="F16" s="31"/>
-      <x:c r="G16" s="31"/>
+      <x:c r="G16" s="36"/>
       <x:c r="H16" s="31"/>
       <x:c r="I16" s="31"/>
       <x:c r="J16" s="31"/>
@@ -63167,7 +68939,7 @@
       <x:c r="D17" s="31"/>
       <x:c r="E17" s="31"/>
       <x:c r="F17" s="31"/>
-      <x:c r="G17" s="31"/>
+      <x:c r="G17" s="36"/>
       <x:c r="H17" s="31"/>
       <x:c r="I17" s="31"/>
       <x:c r="J17" s="31"/>
@@ -63186,7 +68958,7 @@
       <x:c r="D18" s="31"/>
       <x:c r="E18" s="31"/>
       <x:c r="F18" s="31"/>
-      <x:c r="G18" s="31"/>
+      <x:c r="G18" s="36"/>
       <x:c r="H18" s="31"/>
       <x:c r="I18" s="31"/>
       <x:c r="J18" s="31"/>
@@ -63205,7 +68977,7 @@
       <x:c r="D19" s="31"/>
       <x:c r="E19" s="31"/>
       <x:c r="F19" s="31"/>
-      <x:c r="G19" s="31"/>
+      <x:c r="G19" s="36"/>
       <x:c r="H19" s="31"/>
       <x:c r="I19" s="31"/>
       <x:c r="J19" s="31"/>
@@ -63224,7 +68996,7 @@
       <x:c r="D20" s="31"/>
       <x:c r="E20" s="31"/>
       <x:c r="F20" s="31"/>
-      <x:c r="G20" s="31"/>
+      <x:c r="G20" s="36"/>
       <x:c r="H20" s="31"/>
       <x:c r="I20" s="31"/>
       <x:c r="J20" s="31"/>
@@ -63243,7 +69015,7 @@
       <x:c r="D21" s="31"/>
       <x:c r="E21" s="31"/>
       <x:c r="F21" s="31"/>
-      <x:c r="G21" s="31"/>
+      <x:c r="G21" s="36"/>
       <x:c r="H21" s="31"/>
       <x:c r="I21" s="31"/>
       <x:c r="J21" s="31"/>
@@ -63262,7 +69034,7 @@
       <x:c r="D22" s="31"/>
       <x:c r="E22" s="31"/>
       <x:c r="F22" s="31"/>
-      <x:c r="G22" s="31"/>
+      <x:c r="G22" s="36"/>
       <x:c r="H22" s="31"/>
       <x:c r="I22" s="31"/>
       <x:c r="J22" s="31"/>
@@ -63281,7 +69053,7 @@
       <x:c r="D23" s="31"/>
       <x:c r="E23" s="31"/>
       <x:c r="F23" s="31"/>
-      <x:c r="G23" s="31"/>
+      <x:c r="G23" s="36"/>
       <x:c r="H23" s="31"/>
       <x:c r="I23" s="31"/>
       <x:c r="J23" s="31"/>
@@ -63300,7 +69072,7 @@
       <x:c r="D24" s="31"/>
       <x:c r="E24" s="31"/>
       <x:c r="F24" s="31"/>
-      <x:c r="G24" s="31"/>
+      <x:c r="G24" s="36"/>
       <x:c r="H24" s="31"/>
       <x:c r="I24" s="31"/>
       <x:c r="J24" s="31"/>
@@ -63319,7 +69091,7 @@
       <x:c r="D25" s="31"/>
       <x:c r="E25" s="31"/>
       <x:c r="F25" s="31"/>
-      <x:c r="G25" s="31"/>
+      <x:c r="G25" s="36"/>
       <x:c r="H25" s="31"/>
       <x:c r="I25" s="31"/>
       <x:c r="J25" s="31"/>
@@ -63338,7 +69110,7 @@
       <x:c r="D26" s="31"/>
       <x:c r="E26" s="31"/>
       <x:c r="F26" s="31"/>
-      <x:c r="G26" s="31"/>
+      <x:c r="G26" s="36"/>
       <x:c r="H26" s="31"/>
       <x:c r="I26" s="31"/>
       <x:c r="J26" s="31"/>
@@ -63357,7 +69129,7 @@
       <x:c r="D27" s="31"/>
       <x:c r="E27" s="31"/>
       <x:c r="F27" s="31"/>
-      <x:c r="G27" s="31"/>
+      <x:c r="G27" s="36"/>
       <x:c r="H27" s="31"/>
       <x:c r="I27" s="31"/>
       <x:c r="J27" s="31"/>
@@ -63376,7 +69148,7 @@
       <x:c r="D28" s="31"/>
       <x:c r="E28" s="31"/>
       <x:c r="F28" s="31"/>
-      <x:c r="G28" s="31"/>
+      <x:c r="G28" s="36"/>
       <x:c r="H28" s="31"/>
       <x:c r="I28" s="31"/>
       <x:c r="J28" s="31"/>
@@ -63395,7 +69167,7 @@
       <x:c r="D29" s="31"/>
       <x:c r="E29" s="31"/>
       <x:c r="F29" s="31"/>
-      <x:c r="G29" s="31"/>
+      <x:c r="G29" s="36"/>
       <x:c r="H29" s="31"/>
       <x:c r="I29" s="31"/>
       <x:c r="J29" s="31"/>
@@ -63414,7 +69186,7 @@
       <x:c r="D30" s="31"/>
       <x:c r="E30" s="31"/>
       <x:c r="F30" s="31"/>
-      <x:c r="G30" s="31"/>
+      <x:c r="G30" s="36"/>
       <x:c r="H30" s="31"/>
       <x:c r="I30" s="31"/>
       <x:c r="J30" s="31"/>
@@ -63433,7 +69205,7 @@
       <x:c r="D31" s="31"/>
       <x:c r="E31" s="31"/>
       <x:c r="F31" s="31"/>
-      <x:c r="G31" s="31"/>
+      <x:c r="G31" s="36"/>
       <x:c r="H31" s="31"/>
       <x:c r="I31" s="31"/>
       <x:c r="J31" s="31"/>
@@ -63452,7 +69224,7 @@
       <x:c r="D32" s="31"/>
       <x:c r="E32" s="31"/>
       <x:c r="F32" s="31"/>
-      <x:c r="G32" s="31"/>
+      <x:c r="G32" s="36"/>
       <x:c r="H32" s="31"/>
       <x:c r="I32" s="31"/>
       <x:c r="J32" s="31"/>
@@ -63471,7 +69243,7 @@
       <x:c r="D33" s="31"/>
       <x:c r="E33" s="31"/>
       <x:c r="F33" s="31"/>
-      <x:c r="G33" s="31"/>
+      <x:c r="G33" s="36"/>
       <x:c r="H33" s="31"/>
       <x:c r="I33" s="31"/>
       <x:c r="J33" s="31"/>
@@ -63490,7 +69262,7 @@
       <x:c r="D34" s="31"/>
       <x:c r="E34" s="31"/>
       <x:c r="F34" s="31"/>
-      <x:c r="G34" s="31"/>
+      <x:c r="G34" s="36"/>
       <x:c r="H34" s="31"/>
       <x:c r="I34" s="31"/>
       <x:c r="J34" s="31"/>
@@ -63509,7 +69281,7 @@
       <x:c r="D35" s="31"/>
       <x:c r="E35" s="31"/>
       <x:c r="F35" s="31"/>
-      <x:c r="G35" s="31"/>
+      <x:c r="G35" s="36"/>
       <x:c r="H35" s="31"/>
       <x:c r="I35" s="31"/>
       <x:c r="J35" s="31"/>
@@ -63528,7 +69300,7 @@
       <x:c r="D36" s="31"/>
       <x:c r="E36" s="31"/>
       <x:c r="F36" s="31"/>
-      <x:c r="G36" s="31"/>
+      <x:c r="G36" s="36"/>
       <x:c r="H36" s="31"/>
       <x:c r="I36" s="31"/>
       <x:c r="J36" s="31"/>
@@ -63547,7 +69319,7 @@
       <x:c r="D37" s="31"/>
       <x:c r="E37" s="31"/>
       <x:c r="F37" s="31"/>
-      <x:c r="G37" s="31"/>
+      <x:c r="G37" s="36"/>
       <x:c r="H37" s="31"/>
       <x:c r="I37" s="31"/>
       <x:c r="J37" s="31"/>
@@ -63566,7 +69338,7 @@
       <x:c r="D38" s="31"/>
       <x:c r="E38" s="31"/>
       <x:c r="F38" s="31"/>
-      <x:c r="G38" s="31"/>
+      <x:c r="G38" s="36"/>
       <x:c r="H38" s="31"/>
       <x:c r="I38" s="31"/>
       <x:c r="J38" s="31"/>
@@ -63585,7 +69357,7 @@
       <x:c r="D39" s="31"/>
       <x:c r="E39" s="31"/>
       <x:c r="F39" s="31"/>
-      <x:c r="G39" s="31"/>
+      <x:c r="G39" s="36"/>
       <x:c r="H39" s="31"/>
       <x:c r="I39" s="31"/>
       <x:c r="J39" s="31"/>
@@ -63604,7 +69376,7 @@
       <x:c r="D40" s="31"/>
       <x:c r="E40" s="31"/>
       <x:c r="F40" s="31"/>
-      <x:c r="G40" s="31"/>
+      <x:c r="G40" s="36"/>
       <x:c r="H40" s="31"/>
       <x:c r="I40" s="31"/>
       <x:c r="J40" s="31"/>
@@ -63623,7 +69395,7 @@
       <x:c r="D41" s="31"/>
       <x:c r="E41" s="31"/>
       <x:c r="F41" s="31"/>
-      <x:c r="G41" s="31"/>
+      <x:c r="G41" s="36"/>
       <x:c r="H41" s="31"/>
       <x:c r="I41" s="31"/>
       <x:c r="J41" s="31"/>
@@ -63642,7 +69414,7 @@
       <x:c r="D42" s="31"/>
       <x:c r="E42" s="31"/>
       <x:c r="F42" s="31"/>
-      <x:c r="G42" s="31"/>
+      <x:c r="G42" s="36"/>
       <x:c r="H42" s="31"/>
       <x:c r="I42" s="31"/>
       <x:c r="J42" s="31"/>
@@ -63661,7 +69433,7 @@
       <x:c r="D43" s="31"/>
       <x:c r="E43" s="31"/>
       <x:c r="F43" s="31"/>
-      <x:c r="G43" s="31"/>
+      <x:c r="G43" s="36"/>
       <x:c r="H43" s="31"/>
       <x:c r="I43" s="31"/>
       <x:c r="J43" s="31"/>
@@ -63680,7 +69452,7 @@
       <x:c r="D44" s="31"/>
       <x:c r="E44" s="31"/>
       <x:c r="F44" s="31"/>
-      <x:c r="G44" s="31"/>
+      <x:c r="G44" s="36"/>
       <x:c r="H44" s="31"/>
       <x:c r="I44" s="31"/>
       <x:c r="J44" s="31"/>
@@ -63699,7 +69471,7 @@
       <x:c r="D45" s="31"/>
       <x:c r="E45" s="31"/>
       <x:c r="F45" s="31"/>
-      <x:c r="G45" s="31"/>
+      <x:c r="G45" s="36"/>
       <x:c r="H45" s="31"/>
       <x:c r="I45" s="31"/>
       <x:c r="J45" s="31"/>
@@ -63718,7 +69490,7 @@
       <x:c r="D46" s="31"/>
       <x:c r="E46" s="31"/>
       <x:c r="F46" s="31"/>
-      <x:c r="G46" s="31"/>
+      <x:c r="G46" s="36"/>
       <x:c r="H46" s="31"/>
       <x:c r="I46" s="31"/>
       <x:c r="J46" s="31"/>
@@ -63737,7 +69509,7 @@
       <x:c r="D47" s="31"/>
       <x:c r="E47" s="31"/>
       <x:c r="F47" s="31"/>
-      <x:c r="G47" s="31"/>
+      <x:c r="G47" s="36"/>
       <x:c r="H47" s="31"/>
       <x:c r="I47" s="31"/>
       <x:c r="J47" s="31"/>
@@ -63756,7 +69528,7 @@
       <x:c r="D48" s="31"/>
       <x:c r="E48" s="31"/>
       <x:c r="F48" s="31"/>
-      <x:c r="G48" s="31"/>
+      <x:c r="G48" s="36"/>
       <x:c r="H48" s="31"/>
       <x:c r="I48" s="31"/>
       <x:c r="J48" s="31"/>
@@ -63775,7 +69547,7 @@
       <x:c r="D49" s="31"/>
       <x:c r="E49" s="31"/>
       <x:c r="F49" s="31"/>
-      <x:c r="G49" s="31"/>
+      <x:c r="G49" s="36"/>
       <x:c r="H49" s="31"/>
       <x:c r="I49" s="31"/>
       <x:c r="J49" s="31"/>
@@ -63794,7 +69566,7 @@
       <x:c r="D50" s="31"/>
       <x:c r="E50" s="31"/>
       <x:c r="F50" s="31"/>
-      <x:c r="G50" s="31"/>
+      <x:c r="G50" s="36"/>
       <x:c r="H50" s="31"/>
       <x:c r="I50" s="31"/>
       <x:c r="J50" s="31"/>
